--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -11,14 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilla vigas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilla losas" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilla columnas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_vigas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_losas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_columnas" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria ilum. y vent." sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria vigas" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria losas" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria columnas" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundacion (inventario)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vigas de fundacion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_vigas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_losas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_columnas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria ilum. y vent." sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria vigas" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria losas" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria columnas" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundacion (inventario)" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
@@ -28,6 +29,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla losas'!$A$1:$R$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla columnas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Planilla columnas'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Vigas de fundacion'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Vigas de fundacion'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -245,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -357,6 +360,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1566,6 +1572,711 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2663,6 +3374,576 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="98" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="58" t="inlineStr">
+        <is>
+          <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
+        </is>
+      </c>
+      <c r="B1" s="59" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="59" t="inlineStr"/>
+      <c r="B2" s="60" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>NORMATIVA</t>
+        </is>
+      </c>
+      <c r="B3" s="59" t="inlineStr">
+        <is>
+          <t>CIRSOC 201. Hormigon H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200 kg/cm2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>UNIDADES</t>
+        </is>
+      </c>
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Longitudes en m y cm. Cargas en kg/m. Momentos en kgm. Tensiones en kg/cm2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="inlineStr">
+        <is>
+          <t>DIMENSIONES</t>
+        </is>
+      </c>
+      <c r="B5" s="59" t="inlineStr">
+        <is>
+          <t>b = ancho | h = altura util | d = altura total (igual criterio que la planilla de catedra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="59" t="inlineStr">
+        <is>
+          <t>1. CARGAS</t>
+        </is>
+      </c>
+      <c r="B7" s="59" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="59" t="inlineStr">
+        <is>
+          <t>Entrepiso PA</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>Losa maciza 12 cm 300 + contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr"/>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>g = 550 kg/m2       q = 200 kg/m2 (vivienda)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Azotea</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Losa 300 + contrapiso de pendiente 140 + carpeta 42 + aislacion y membrana 50 + cielorraso 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="59" t="inlineStr"/>
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>g = 560 kg/m2       q = 100 kg/m2 (cubierta no accesible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>Mamposteria</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>250 kg/m2. Altura 2,60 m en PA y 1,00 m de parapeto en azotea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>Peso propio</t>
+        </is>
+      </c>
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>2400 kg/m3 x b x d, viga por viga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="59" t="inlineStr">
+        <is>
+          <t>Carga de calculo</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>p = 1,2 (g x B + peso propio + muro) + 1,6 (q x B)        B = ancho tributario</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="59" t="inlineStr"/>
+      <c r="B15" s="60" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="59" t="inlineStr">
+        <is>
+          <t>2. SOLICITACIONES</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>Coeficientes segun esquema (tabla en hoja Datos):</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="59" t="inlineStr"/>
+      <c r="B17" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Simplemente apoyada   M = pL2/8                    R = 0,500 pL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="59" t="inlineStr"/>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Continua              M = pL2/14   Mapoyo = pL2/10  R = 0,575 pL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="inlineStr"/>
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Empotrada-apoyada     M = 9pL2/128 Mapoyo = pL2/8   R = 0,625 pL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="59" t="inlineStr"/>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Biempotrada           M = pL2/24   Mapoyo = pL2/12  R = 0,500 pL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="59" t="inlineStr"/>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Voladizo                           Mapoyo = pL2/2   R = 1,000 pL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="59" t="inlineStr"/>
+      <c r="B22" s="60" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="59" t="inlineStr">
+        <is>
+          <t>3. FLEXION</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>k = M / (phi b h2 f'c)      w = 1 - RAIZ(1 - 2k)      As = w b h f'c / fy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="59" t="inlineStr"/>
+      <c r="B24" s="60" t="inlineStr">
+        <is>
+          <t>As min = 0,0033 b h       As max = 0,0163 b h (0,75 de la cuantia balanceada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="59" t="inlineStr"/>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>Si la armadura no entra en una capa se disponen dos y el recubrimiento pasa a 6 cm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="59" t="inlineStr"/>
+      <c r="B26" s="60" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="59" t="inlineStr">
+        <is>
+          <t>4. CORTE</t>
+        </is>
+      </c>
+      <c r="B27" s="59" t="inlineStr">
+        <is>
+          <t>T = R / (b x 0,85 h)       tension tangencial en el apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="59" t="inlineStr"/>
+      <c r="B28" s="60" t="inlineStr">
+        <is>
+          <t>Vc = 0,53 RAIZ(f'c) b h        phi Vn = 0,75 (Vc + Av fy h / s)  &gt;=  R</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="59" t="inlineStr"/>
+      <c r="B29" s="60" t="inlineStr">
+        <is>
+          <t>Av = 2 ramas. Se aumenta el diametro antes que cerrar la separacion por debajo de 10 cm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="59" t="inlineStr"/>
+      <c r="B30" s="60" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="59" t="inlineStr">
+        <is>
+          <t>5. FLECHA</t>
+        </is>
+      </c>
+      <c r="B31" s="59" t="inlineStr">
+        <is>
+          <t>Altura minima: simplemente apoyada L/16, un extremo continuo L/18,5,</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="59" t="inlineStr"/>
+      <c r="B32" s="60" t="inlineStr">
+        <is>
+          <t>ambos extremos continuos L/21, voladizo L/8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="59" t="inlineStr"/>
+      <c r="B33" s="60" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="59" t="inlineStr">
+        <is>
+          <t>6. VIGAS INVERTIDAS</t>
+        </is>
+      </c>
+      <c r="B34" s="59" t="inlineStr">
+        <is>
+          <t>Las vigas de BORDE son invertidas: sobresalen 70 cm por encima del fondo de</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="59" t="inlineStr"/>
+      <c r="B35" s="60" t="inlineStr">
+        <is>
+          <t>losa (cotas N.F.L +3,50 / N.S.V +4,20 y N.F.L +6,80 / N.S.V +7,50 del plano).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="59" t="inlineStr"/>
+      <c r="B36" s="60" t="inlineStr">
+        <is>
+          <t>Son VI 01a, VI 01b, VI 07a, VI 07b, VI 07c, VI 11a, VI 11b, VI 11c, VI 15a y VI 15b,</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="59" t="inlineStr"/>
+      <c r="B37" s="60" t="inlineStr">
+        <is>
+          <t>identificadas por coincidir su eje con el contorno del edificio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="59" t="inlineStr"/>
+      <c r="B38" s="60" t="inlineStr">
+        <is>
+          <t>Esto define donde la losa aporta ala comprimida:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="59" t="inlineStr"/>
+      <c r="B39" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="59" t="inlineStr"/>
+      <c r="B40" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="59" t="inlineStr"/>
+      <c r="B41" s="60" t="inlineStr">
+        <is>
+          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="inlineStr"/>
+      <c r="B42" s="60" t="inlineStr">
+        <is>
+          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="59" t="inlineStr"/>
+      <c r="B43" s="60" t="inlineStr">
+        <is>
+          <t>PENDIENTE: una viga invertida de borde recibe la reaccion de la losa excentrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="59" t="inlineStr"/>
+      <c r="B44" s="60" t="inlineStr">
+        <is>
+          <t>respecto de su eje y queda sometida a TORSION. Esta planilla no la verifica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="59" t="inlineStr"/>
+      <c r="B45" s="60" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="59" t="inlineStr">
+        <is>
+          <t>7. RESULTADO</t>
+        </is>
+      </c>
+      <c r="B46" s="59" t="inlineStr">
+        <is>
+          <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="inlineStr"/>
+      <c r="B47" s="60" t="inlineStr">
+        <is>
+          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="inlineStr"/>
+      <c r="B48" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="59" t="inlineStr"/>
+      <c r="B49" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="59" t="inlineStr"/>
+      <c r="B50" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="inlineStr"/>
+      <c r="B51" s="60" t="inlineStr">
+        <is>
+          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="59" t="inlineStr"/>
+      <c r="B52" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="59" t="inlineStr"/>
+      <c r="B53" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="59" t="inlineStr"/>
+      <c r="B54" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="59" t="inlineStr"/>
+      <c r="B55" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="59" t="inlineStr"/>
+      <c r="B56" s="60" t="inlineStr">
+        <is>
+          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="59" t="inlineStr"/>
+      <c r="B57" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="59" t="inlineStr"/>
+      <c r="B58" s="60" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="inlineStr">
+        <is>
+          <t>8. ALCANCE</t>
+        </is>
+      </c>
+      <c r="B59" s="60" t="inlineStr">
+        <is>
+          <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="59" t="inlineStr"/>
+      <c r="B60" s="60" t="inlineStr">
+        <is>
+          <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="59" t="inlineStr"/>
+      <c r="B61" s="60" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="59" t="inlineStr">
+        <is>
+          <t>LIMITACIONES</t>
+        </is>
+      </c>
+      <c r="B62" s="59" t="inlineStr">
+        <is>
+          <t>El ancho tributario B esta relevado solo en</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="59" t="inlineStr"/>
+      <c r="B63" s="60" t="inlineStr">
+        <is>
+          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="59" t="inlineStr"/>
+      <c r="B64" s="60" t="inlineStr">
+        <is>
+          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="59" t="inlineStr"/>
+      <c r="B65" s="60" t="inlineStr">
+        <is>
+          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="59" t="inlineStr"/>
+      <c r="B66" s="60" t="inlineStr">
+        <is>
+          <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2671,368 +3952,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - LOSAS</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr"/>
+      <c r="B1" s="59" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr"/>
-      <c r="B2" s="59" t="inlineStr"/>
+      <c r="A2" s="59" t="inlineStr"/>
+      <c r="B2" s="60" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>METODO</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>Tensiones admisibles, igual criterio que la planilla modelo de la catedra.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr"/>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr"/>
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>Se verifico contra la fila de ejemplo: momentos y reacciones coinciden exactamente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). Tension admisible 2400 kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>h = altura util | d = espesor total. Recubrimiento 1,5 cm.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr"/>
-      <c r="B7" s="59" t="inlineStr"/>
+      <c r="A7" s="59" t="inlineStr"/>
+      <c r="B7" s="60" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q      (cargas de servicio, sin mayorar)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr"/>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr"/>
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>Peso propio = 2400 x d / 100, calculado con el espesor propio de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>Terminaciones 242 kg/m2 (contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr"/>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr"/>
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>Terminaciones 252 kg/m2 (contrapiso pendiente 140 + carpeta 42 + aislacion 50 +</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr"/>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr"/>
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>cielorraso 20).  q = 100 kg/m2 (azotea no accesible)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr"/>
-      <c r="B14" s="59" t="inlineStr"/>
+      <c r="A14" s="59" t="inlineStr"/>
+      <c r="B14" s="60" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>M = coeficiente x p x L2, segun el grado de empotramiento:</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr"/>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr"/>
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">  1/8 simplemente apoyada    1/10 y 1/14 continua    1/12 biempotrada    1/2 voladizo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr"/>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr"/>
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>R = coeficiente x p x L. En voladizo Rx = p x L y Ry no corresponde.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr"/>
-      <c r="B18" s="59" t="inlineStr"/>
+      <c r="A18" s="59" t="inlineStr"/>
+      <c r="B18" s="60" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="58" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B19" s="58" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>As = M x 100 / (2400 x 0,9 x h)        [cm2/m]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="inlineStr"/>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="A20" s="59" t="inlineStr"/>
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>separacion = 100 x area de la barra / As, redondeada, con maximo 20 cm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr"/>
-      <c r="B21" s="59" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr"/>
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>Armadura de reparticion = As / 5, con un minimo de 0,30 cm2/m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr"/>
-      <c r="B22" s="59" t="inlineStr"/>
+      <c r="A22" s="59" t="inlineStr"/>
+      <c r="B22" s="60" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr">
         <is>
           <t>4. ESPESORES</t>
         </is>
       </c>
-      <c r="B23" s="58" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>Los espesores d se leyeron del plano: estan escritos debajo del rotulo de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="inlineStr"/>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="A24" s="59" t="inlineStr"/>
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>S/PB:  L01 11 | L02 9 | L03 13 | L04 11 | L05 11 | L06 8 | L07 12 | L08 10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="inlineStr"/>
-      <c r="B25" s="59" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr"/>
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>S/PA:  L09 13 | L10 12</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="inlineStr"/>
-      <c r="B26" s="59" t="inlineStr"/>
+      <c r="A26" s="59" t="inlineStr"/>
+      <c r="B26" s="60" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="inlineStr">
+      <c r="A27" s="59" t="inlineStr">
         <is>
           <t>5. LUCES</t>
         </is>
       </c>
-      <c r="B27" s="58" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>Relevadas en obra y aportadas por el proyectista. Dos losas son voladizo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr"/>
-      <c r="B28" s="59" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr"/>
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>(L02 de 0,80 m y L08 de 0,75 m) y se calculan con M = p L2 / 2.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="inlineStr"/>
-      <c r="B29" s="59" t="inlineStr"/>
+      <c r="A29" s="59" t="inlineStr"/>
+      <c r="B29" s="60" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="inlineStr">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>6. LOSAS CRUZADAS</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>L07 (4,85 x 5,60) y L10 (4,85 x 6,00) apoyan en los cuatro bordes y su relacion</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="58" t="inlineStr"/>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="A31" s="59" t="inlineStr"/>
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>de lados es menor que 2, por lo que trabajan en las dos direcciones.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr"/>
-      <c r="B32" s="59" t="inlineStr">
+      <c r="A32" s="59" t="inlineStr"/>
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>Se reparte la carga por el metodo de Marcus:   kx = ly4 / (lx4 + ly4)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="58" t="inlineStr"/>
-      <c r="B33" s="59" t="inlineStr">
+      <c r="A33" s="59" t="inlineStr"/>
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">  L07: ly/lx = 1,15  -&gt;  64% en la direccion corta, 36% en la larga</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="inlineStr"/>
-      <c r="B34" s="59" t="inlineStr">
+      <c r="A34" s="59" t="inlineStr"/>
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">  L10: ly/lx = 1,24  -&gt;  70% en la direccion corta, 30% en la larga</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="58" t="inlineStr"/>
-      <c r="B35" s="59" t="inlineStr">
+      <c r="A35" s="59" t="inlineStr"/>
+      <c r="B35" s="60" t="inlineStr">
         <is>
           <t>Cada una ocupa dos renglones, uno por direccion, con la fraccion de carga que</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="inlineStr"/>
-      <c r="B36" s="59" t="inlineStr">
+      <c r="A36" s="59" t="inlineStr"/>
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t>le toca ya aplicada en la columna CARGAS. Las dos armaduras se cruzan en obra:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="58" t="inlineStr"/>
-      <c r="B37" s="59" t="inlineStr">
+      <c r="A37" s="59" t="inlineStr"/>
+      <c r="B37" s="60" t="inlineStr">
         <is>
           <t>la de la direccion corta va abajo, la de la larga arriba de aquella.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="inlineStr"/>
-      <c r="B38" s="59" t="inlineStr">
+      <c r="A38" s="59" t="inlineStr"/>
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t>La columna auxiliar luz transv. es la que dispara el reparto: si se borra, la</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="58" t="inlineStr"/>
-      <c r="B39" s="59" t="inlineStr">
+      <c r="A39" s="59" t="inlineStr"/>
+      <c r="B39" s="60" t="inlineStr">
         <is>
           <t>fila vuelve a calcularse como losa armada en una direccion.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="inlineStr"/>
-      <c r="B40" s="59" t="inlineStr"/>
+      <c r="A40" s="59" t="inlineStr"/>
+      <c r="B40" s="60" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="58" t="inlineStr">
+      <c r="A41" s="59" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B41" s="58" t="inlineStr">
+      <c r="B41" s="59" t="inlineStr">
         <is>
           <t>El grado de empotramiento esta cargado en 1/8 salvo los dos voladizos (1/2). Si</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="inlineStr"/>
-      <c r="B42" s="59" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr"/>
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>alguna losa es continua sobre una viga corresponde 1/10 o 1/14: corregir en la columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="58" t="inlineStr"/>
-      <c r="B43" s="59" t="inlineStr">
+      <c r="A43" s="59" t="inlineStr"/>
+      <c r="B43" s="60" t="inlineStr">
         <is>
           <t>El diagrama de cargas es una imagen fija: si cambias el grado, cambialo a mano.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="inlineStr"/>
-      <c r="B44" s="59" t="inlineStr">
+      <c r="A44" s="59" t="inlineStr"/>
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -3043,7 +4324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3057,368 +4338,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - COLUMNAS</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr"/>
+      <c r="B1" s="59" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr"/>
-      <c r="B2" s="59" t="inlineStr"/>
+      <c r="A2" s="59" t="inlineStr"/>
+      <c r="B2" s="60" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). phi compresion 0,65.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr"/>
-      <c r="B4" s="59" t="inlineStr"/>
+      <c r="A4" s="59" t="inlineStr"/>
+      <c r="B4" s="60" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>1. RELEVAMIENTO</t>
         </is>
       </c>
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>Las columnas se identificaron en el plano cruzando el rotulo COL con un rectangulo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>de la misma seccion a menos de 26 pt. Resultaron 9 en PB y 4 en PA.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr"/>
-      <c r="B7" s="59" t="inlineStr">
+      <c r="A7" s="59" t="inlineStr"/>
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>Las 4 de PA caen exactamente sobre C6, C7, C8 y C9 de PB, y ademas tienen la misma</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr"/>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr"/>
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>seccion, lo que confirma que la correspondencia entre plantas es correcta.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr"/>
-      <c r="B9" s="59" t="inlineStr">
+      <c r="A9" s="59" t="inlineStr"/>
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>La planilla modelo de la catedra tiene 10 columnas en PB: puede faltar una que no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr"/>
-      <c r="B10" s="59" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr"/>
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>haya podido resolverse por rotulo. Conviene contarlas en el plano.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr"/>
-      <c r="B11" s="59" t="inlineStr"/>
+      <c r="A11" s="59" t="inlineStr"/>
+      <c r="B11" s="60" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>2. ALTURAS</t>
         </is>
       </c>
-      <c r="B12" s="58" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>PB 3,15 m y PA 3,22 m, los mismos valores de la planilla de la catedra, coherentes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr"/>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr"/>
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>con los niveles del plano (N.F.L +3,50 del entrepiso y +6,80 del techo).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr"/>
-      <c r="B14" s="59" t="inlineStr"/>
+      <c r="A14" s="59" t="inlineStr"/>
+      <c r="B14" s="60" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>As = 0,008 x area (cuantia minima, el mismo criterio de la planilla modelo).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr"/>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr"/>
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>Se adoptan 4 barras del 12 en todas: 4,52 cm2, que cubre la minima en toda seccion.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr"/>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr"/>
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. long. ; 48 x diam. estribo ; lado menor),</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr"/>
-      <c r="B18" s="59" t="inlineStr">
+      <c r="A18" s="59" t="inlineStr"/>
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>redondeada hacia abajo a multiplo de 5. Para 4d12 con estribo d6 da 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="58" t="inlineStr"/>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr"/>
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>La planilla de la catedra adopta 20 cm: ese valor supera el limite reglamentario.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="inlineStr"/>
-      <c r="B20" s="59" t="inlineStr"/>
+      <c r="A20" s="59" t="inlineStr"/>
+      <c r="B20" s="60" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>4. CAPACIDAD</t>
         </is>
       </c>
-      <c r="B21" s="58" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]     (columna zunchada con estribos)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr"/>
-      <c r="B22" s="59" t="inlineStr">
+      <c r="A22" s="59" t="inlineStr"/>
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">  15x30 con 4d12 -&gt; 51,2 t        20x20 con 4d12 -&gt; 46,6 t</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="inlineStr"/>
-      <c r="B23" s="59" t="inlineStr"/>
+      <c r="A23" s="59" t="inlineStr"/>
+      <c r="B23" s="60" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="58" t="inlineStr">
+      <c r="A24" s="59" t="inlineStr">
         <is>
           <t>5. CARGAS</t>
         </is>
       </c>
-      <c r="B24" s="58" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>La columna CARGA (t) viene cargada con una bajada automatica: suma de las</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="58" t="inlineStr"/>
-      <c r="B25" s="59" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr"/>
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>reacciones de las vigas que apoyan en cada columna (tomadas de la planilla de</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="58" t="inlineStr"/>
-      <c r="B26" s="59" t="inlineStr">
+      <c r="A26" s="59" t="inlineStr"/>
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>vigas), mas el peso propio, mas lo que baja de la columna del nivel superior.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="58" t="inlineStr"/>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="A27" s="59" t="inlineStr"/>
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>ES UNA CARGA PROVISORIA Y ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr"/>
-      <c r="B28" s="59" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr"/>
+      <c r="B28" s="60" t="inlineStr">
         <is>
           <t>de viga no pudieron asignarse a ninguna columna porque apoyan en otra viga, en</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="58" t="inlineStr"/>
-      <c r="B29" s="59" t="inlineStr">
+      <c r="A29" s="59" t="inlineStr"/>
+      <c r="B29" s="60" t="inlineStr">
         <is>
           <t>un tabique o en la medianera, y esas reacciones no estan sumadas.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="58" t="inlineStr"/>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="A30" s="59" t="inlineStr"/>
+      <c r="B30" s="60" t="inlineStr">
         <is>
           <t>Para cerrarla hay que indicar, para cada uno de esos 20 extremos, en que apoya.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="58" t="inlineStr"/>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="A31" s="59" t="inlineStr"/>
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>Mientras tanto la columna es editable: al corregir un valor todo recalcula.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="58" t="inlineStr"/>
-      <c r="B32" s="59" t="inlineStr">
+      <c r="A32" s="59" t="inlineStr"/>
+      <c r="B32" s="60" t="inlineStr">
         <is>
           <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="58" t="inlineStr"/>
-      <c r="B33" s="59" t="inlineStr">
+      <c r="A33" s="59" t="inlineStr"/>
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="58" t="inlineStr"/>
-      <c r="B34" s="59" t="inlineStr"/>
+      <c r="A34" s="59" t="inlineStr"/>
+      <c r="B34" s="60" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="58" t="inlineStr">
+      <c r="A35" s="59" t="inlineStr">
         <is>
           <t>6. ESBELTEZ</t>
         </is>
       </c>
-      <c r="B35" s="58" t="inlineStr">
+      <c r="B35" s="59" t="inlineStr">
         <is>
           <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="58" t="inlineStr"/>
-      <c r="B36" s="59" t="inlineStr">
+      <c r="A36" s="59" t="inlineStr"/>
+      <c r="B36" s="60" t="inlineStr">
         <is>
           <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="58" t="inlineStr"/>
-      <c r="B37" s="59" t="inlineStr">
+      <c r="A37" s="59" t="inlineStr"/>
+      <c r="B37" s="60" t="inlineStr">
         <is>
           <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="58" t="inlineStr"/>
-      <c r="B38" s="59" t="inlineStr">
+      <c r="A38" s="59" t="inlineStr"/>
+      <c r="B38" s="60" t="inlineStr">
         <is>
           <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="58" t="inlineStr"/>
-      <c r="B39" s="59" t="inlineStr"/>
+      <c r="A39" s="59" t="inlineStr"/>
+      <c r="B39" s="60" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="58" t="inlineStr">
+      <c r="A40" s="59" t="inlineStr">
         <is>
           <t>7. C4, A REVISAR</t>
         </is>
       </c>
-      <c r="B40" s="58" t="inlineStr">
+      <c r="B40" s="59" t="inlineStr">
         <is>
           <t>C4 figura en el plano como 10x10 y recibe el extremo de VI 01a, con 17 t de</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="58" t="inlineStr"/>
-      <c r="B41" s="59" t="inlineStr">
+      <c r="A41" s="59" t="inlineStr"/>
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t>reaccion. Una columna de 10x10 no toma esa carga. VI 01a corre sobre la medianera,</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="58" t="inlineStr"/>
-      <c r="B42" s="59" t="inlineStr">
+      <c r="A42" s="59" t="inlineStr"/>
+      <c r="B42" s="60" t="inlineStr">
         <is>
           <t>asi que lo mas probable es que apoye en el muro y ese 10x10 no sea una columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="58" t="inlineStr"/>
-      <c r="B43" s="59" t="inlineStr"/>
+      <c r="A43" s="59" t="inlineStr"/>
+      <c r="B43" s="60" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="58" t="inlineStr">
+      <c r="A44" s="59" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B44" s="58" t="inlineStr">
+      <c r="B44" s="59" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="inlineStr"/>
-      <c r="B45" s="59" t="inlineStr">
+      <c r="A45" s="59" t="inlineStr"/>
+      <c r="B45" s="60" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="58" t="inlineStr"/>
-      <c r="B46" s="59" t="inlineStr">
+      <c r="A46" s="59" t="inlineStr"/>
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>
@@ -3429,7 +4710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3446,7 +4727,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION - inventario. Calculo pendiente: va despues de columnas.</t>
         </is>
@@ -3588,7 +4869,7 @@
       <c r="D9" s="11" t="n">
         <v>533</v>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="62" t="inlineStr">
         <is>
           <t>Ancho cortado en el PDF: confirmar 20 o 22 cm</t>
         </is>
@@ -3654,7 +4935,7 @@
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="61" t="inlineStr">
+      <c r="E13" s="62" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -3669,7 +4950,7 @@
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="61" t="inlineStr">
+      <c r="E14" s="62" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -3871,7 +5152,7 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="61" t="inlineStr">
+      <c r="E26" s="62" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -4021,7 +5302,7 @@
       <c r="E35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>Cabezales: CBZ 01 70x70x65   |   CBZ 02 129x70x70   |   CBZ 03 144x70x70</t>
         </is>
@@ -9984,6 +11265,3068 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Z34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="7" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>VIGAS DE FUNDACION  H°A°        H-21        ACERO 42/50</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>LUZ (m)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>CARGAS (kg/m)</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>REACCIONES</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>MOMENTO TRAMO (kgm)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MOMENTO APOYO (kgm)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>ARMADURA TRAMO</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>ARMADURA APOYO</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="n"/>
+      <c r="R2" s="4" t="n"/>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>T (kg/cm2)</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>ESTRIBOS</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICACION</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>DATOS AUXILIARES</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>esquema</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>diagrama</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>SEPAR</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n"/>
+      <c r="X3" s="4" t="n"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>h muro</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>rec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>VF01 (1)</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D4" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J4*L4/10000+Datos_vigas!$B$16*Y4)</f>
+        <v/>
+      </c>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="24">
+        <f>VLOOKUP(C4,Datos_vigas!$A$19:$E$23,4,0)*D4*B4</f>
+        <v/>
+      </c>
+      <c r="G4" s="24">
+        <f>F4</f>
+        <v/>
+      </c>
+      <c r="H4" s="24">
+        <f>VLOOKUP(C4,Datos_vigas!$A$19:$E$23,2,0)*D4*B4^2</f>
+        <v/>
+      </c>
+      <c r="I4" s="24">
+        <f>IF(VLOOKUP(C4,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C4,Datos_vigas!$A$19:$E$23,3,0)*D4*B4^2)</f>
+        <v/>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" s="11">
+        <f>L4-Z4</f>
+        <v/>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M4" s="25">
+        <f>IF(NOT(ISNUMBER(H4)),"---",IF(H4&lt;=0,"---",IF(H4*100/(Datos_vigas!$B$8*J4*K4^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H4*100/(Datos_vigas!$B$8*J4*K4^2*Datos_vigas!$B$5)))*J4*K4*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J4*K4))))</f>
+        <v/>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" s="25">
+        <f>IF(NOT(ISNUMBER(I4)),"---",IF(I4&lt;=0,"---",IF(I4*100/(Datos_vigas!$B$8*J4*K4^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I4*100/(Datos_vigas!$B$8*J4*K4^2*Datos_vigas!$B$5)))*J4*K4*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J4*K4))))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S4" s="25">
+        <f>F4/(J4*0.85*K4)</f>
+        <v/>
+      </c>
+      <c r="T4" s="25">
+        <f>G4/(J4*0.85*K4)</f>
+        <v/>
+      </c>
+      <c r="U4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V4" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W4" s="11">
+        <f>IF(OR(M4="REVISAR",P4="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M4&lt;&gt;"REVISAR",P4&lt;&gt;"REVISAR",IF(ISNUMBER(M4),N4*PI()*(O4/10)^2/4&gt;=M4,TRUE),IF(ISNUMBER(P4),Q4*PI()*(R4/10)^2/4&gt;=P4,TRUE),IF(ISNUMBER(M4),M4&lt;=0.0163*J4*K4,TRUE),IF(ISNUMBER(P4),P4&lt;=0.0163*J4*K4,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F4&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J4*K4+2*PI()*(U4/10)^2/4*Datos_vigas!$B$6*K4/V4)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X4" s="11" t="n"/>
+      <c r="Y4" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z4" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>VF01 (2)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D5" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J5*L5/10000+Datos_vigas!$B$16*Y5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="24">
+        <f>VLOOKUP(C5,Datos_vigas!$A$19:$E$23,4,0)*D5*B5</f>
+        <v/>
+      </c>
+      <c r="G5" s="24">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="24">
+        <f>VLOOKUP(C5,Datos_vigas!$A$19:$E$23,2,0)*D5*B5^2</f>
+        <v/>
+      </c>
+      <c r="I5" s="24">
+        <f>IF(VLOOKUP(C5,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C5,Datos_vigas!$A$19:$E$23,3,0)*D5*B5^2)</f>
+        <v/>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K5" s="11">
+        <f>L5-Z5</f>
+        <v/>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M5" s="25">
+        <f>IF(NOT(ISNUMBER(H5)),"---",IF(H5&lt;=0,"---",IF(H5*100/(Datos_vigas!$B$8*J5*K5^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H5*100/(Datos_vigas!$B$8*J5*K5^2*Datos_vigas!$B$5)))*J5*K5*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J5*K5))))</f>
+        <v/>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" s="25">
+        <f>IF(NOT(ISNUMBER(I5)),"---",IF(I5&lt;=0,"---",IF(I5*100/(Datos_vigas!$B$8*J5*K5^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I5*100/(Datos_vigas!$B$8*J5*K5^2*Datos_vigas!$B$5)))*J5*K5*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J5*K5))))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S5" s="25">
+        <f>F5/(J5*0.85*K5)</f>
+        <v/>
+      </c>
+      <c r="T5" s="25">
+        <f>G5/(J5*0.85*K5)</f>
+        <v/>
+      </c>
+      <c r="U5" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W5" s="11">
+        <f>IF(OR(M5="REVISAR",P5="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M5&lt;&gt;"REVISAR",P5&lt;&gt;"REVISAR",IF(ISNUMBER(M5),N5*PI()*(O5/10)^2/4&gt;=M5,TRUE),IF(ISNUMBER(P5),Q5*PI()*(R5/10)^2/4&gt;=P5,TRUE),IF(ISNUMBER(M5),M5&lt;=0.0163*J5*K5,TRUE),IF(ISNUMBER(P5),P5&lt;=0.0163*J5*K5,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F5&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J5*K5+2*PI()*(U5/10)^2/4*Datos_vigas!$B$6*K5/V5)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X5" s="11" t="n"/>
+      <c r="Y5" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>VF01 (3)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D6" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J6*L6/10000+Datos_vigas!$B$16*Y6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="24">
+        <f>VLOOKUP(C6,Datos_vigas!$A$19:$E$23,4,0)*D6*B6</f>
+        <v/>
+      </c>
+      <c r="G6" s="24">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="24">
+        <f>VLOOKUP(C6,Datos_vigas!$A$19:$E$23,2,0)*D6*B6^2</f>
+        <v/>
+      </c>
+      <c r="I6" s="24">
+        <f>IF(VLOOKUP(C6,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C6,Datos_vigas!$A$19:$E$23,3,0)*D6*B6^2)</f>
+        <v/>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="11">
+        <f>L6-Z6</f>
+        <v/>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M6" s="25">
+        <f>IF(NOT(ISNUMBER(H6)),"---",IF(H6&lt;=0,"---",IF(H6*100/(Datos_vigas!$B$8*J6*K6^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H6*100/(Datos_vigas!$B$8*J6*K6^2*Datos_vigas!$B$5)))*J6*K6*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J6*K6))))</f>
+        <v/>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="25">
+        <f>IF(NOT(ISNUMBER(I6)),"---",IF(I6&lt;=0,"---",IF(I6*100/(Datos_vigas!$B$8*J6*K6^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I6*100/(Datos_vigas!$B$8*J6*K6^2*Datos_vigas!$B$5)))*J6*K6*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J6*K6))))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S6" s="25">
+        <f>F6/(J6*0.85*K6)</f>
+        <v/>
+      </c>
+      <c r="T6" s="25">
+        <f>G6/(J6*0.85*K6)</f>
+        <v/>
+      </c>
+      <c r="U6" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W6" s="11">
+        <f>IF(OR(M6="REVISAR",P6="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M6&lt;&gt;"REVISAR",P6&lt;&gt;"REVISAR",IF(ISNUMBER(M6),N6*PI()*(O6/10)^2/4&gt;=M6,TRUE),IF(ISNUMBER(P6),Q6*PI()*(R6/10)^2/4&gt;=P6,TRUE),IF(ISNUMBER(M6),M6&lt;=0.0163*J6*K6,TRUE),IF(ISNUMBER(P6),P6&lt;=0.0163*J6*K6,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F6&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J6*K6+2*PI()*(U6/10)^2/4*Datos_vigas!$B$6*K6/V6)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X6" s="11" t="n"/>
+      <c r="Y6" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>VF02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D7" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J7*L7/10000+Datos_vigas!$B$16*Y7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="24">
+        <f>VLOOKUP(C7,Datos_vigas!$A$19:$E$23,4,0)*D7*B7</f>
+        <v/>
+      </c>
+      <c r="G7" s="24">
+        <f>F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="24">
+        <f>VLOOKUP(C7,Datos_vigas!$A$19:$E$23,2,0)*D7*B7^2</f>
+        <v/>
+      </c>
+      <c r="I7" s="24">
+        <f>IF(VLOOKUP(C7,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C7,Datos_vigas!$A$19:$E$23,3,0)*D7*B7^2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" s="11">
+        <f>L7-Z7</f>
+        <v/>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M7" s="25">
+        <f>IF(NOT(ISNUMBER(H7)),"---",IF(H7&lt;=0,"---",IF(H7*100/(Datos_vigas!$B$8*J7*K7^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H7*100/(Datos_vigas!$B$8*J7*K7^2*Datos_vigas!$B$5)))*J7*K7*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J7*K7))))</f>
+        <v/>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" s="25">
+        <f>IF(NOT(ISNUMBER(I7)),"---",IF(I7&lt;=0,"---",IF(I7*100/(Datos_vigas!$B$8*J7*K7^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I7*100/(Datos_vigas!$B$8*J7*K7^2*Datos_vigas!$B$5)))*J7*K7*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J7*K7))))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S7" s="25">
+        <f>F7/(J7*0.85*K7)</f>
+        <v/>
+      </c>
+      <c r="T7" s="25">
+        <f>G7/(J7*0.85*K7)</f>
+        <v/>
+      </c>
+      <c r="U7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W7" s="11">
+        <f>IF(OR(M7="REVISAR",P7="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M7&lt;&gt;"REVISAR",P7&lt;&gt;"REVISAR",IF(ISNUMBER(M7),N7*PI()*(O7/10)^2/4&gt;=M7,TRUE),IF(ISNUMBER(P7),Q7*PI()*(R7/10)^2/4&gt;=P7,TRUE),IF(ISNUMBER(M7),M7&lt;=0.0163*J7*K7,TRUE),IF(ISNUMBER(P7),P7&lt;=0.0163*J7*K7,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F7&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J7*K7+2*PI()*(U7/10)^2/4*Datos_vigas!$B$6*K7/V7)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X7" s="11" t="n"/>
+      <c r="Y7" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>VF03</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D8" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J8*L8/10000+Datos_vigas!$B$16*Y8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="24">
+        <f>VLOOKUP(C8,Datos_vigas!$A$19:$E$23,4,0)*D8*B8</f>
+        <v/>
+      </c>
+      <c r="G8" s="24">
+        <f>F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="24">
+        <f>VLOOKUP(C8,Datos_vigas!$A$19:$E$23,2,0)*D8*B8^2</f>
+        <v/>
+      </c>
+      <c r="I8" s="24">
+        <f>IF(VLOOKUP(C8,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C8,Datos_vigas!$A$19:$E$23,3,0)*D8*B8^2)</f>
+        <v/>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="K8" s="11">
+        <f>L8-Z8</f>
+        <v/>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M8" s="25">
+        <f>IF(NOT(ISNUMBER(H8)),"---",IF(H8&lt;=0,"---",IF(H8*100/(Datos_vigas!$B$8*J8*K8^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H8*100/(Datos_vigas!$B$8*J8*K8^2*Datos_vigas!$B$5)))*J8*K8*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J8*K8))))</f>
+        <v/>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="P8" s="25">
+        <f>IF(NOT(ISNUMBER(I8)),"---",IF(I8&lt;=0,"---",IF(I8*100/(Datos_vigas!$B$8*J8*K8^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I8*100/(Datos_vigas!$B$8*J8*K8^2*Datos_vigas!$B$5)))*J8*K8*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J8*K8))))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S8" s="25">
+        <f>F8/(J8*0.85*K8)</f>
+        <v/>
+      </c>
+      <c r="T8" s="25">
+        <f>G8/(J8*0.85*K8)</f>
+        <v/>
+      </c>
+      <c r="U8" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W8" s="11">
+        <f>IF(OR(M8="REVISAR",P8="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M8&lt;&gt;"REVISAR",P8&lt;&gt;"REVISAR",IF(ISNUMBER(M8),N8*PI()*(O8/10)^2/4&gt;=M8,TRUE),IF(ISNUMBER(P8),Q8*PI()*(R8/10)^2/4&gt;=P8,TRUE),IF(ISNUMBER(M8),M8&lt;=0.0163*J8*K8,TRUE),IF(ISNUMBER(P8),P8&lt;=0.0163*J8*K8,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F8&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J8*K8+2*PI()*(U8/10)^2/4*Datos_vigas!$B$6*K8/V8)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X8" s="13" t="inlineStr">
+        <is>
+          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+        </is>
+      </c>
+      <c r="Y8" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z8" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>VF04a</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D9" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J9*L9/10000+Datos_vigas!$B$16*Y9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="24">
+        <f>VLOOKUP(C9,Datos_vigas!$A$19:$E$23,4,0)*D9*B9</f>
+        <v/>
+      </c>
+      <c r="G9" s="24">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="24">
+        <f>VLOOKUP(C9,Datos_vigas!$A$19:$E$23,2,0)*D9*B9^2</f>
+        <v/>
+      </c>
+      <c r="I9" s="24">
+        <f>IF(VLOOKUP(C9,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C9,Datos_vigas!$A$19:$E$23,3,0)*D9*B9^2)</f>
+        <v/>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" s="11">
+        <f>L9-Z9</f>
+        <v/>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M9" s="25">
+        <f>IF(NOT(ISNUMBER(H9)),"---",IF(H9&lt;=0,"---",IF(H9*100/(Datos_vigas!$B$8*J9*K9^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H9*100/(Datos_vigas!$B$8*J9*K9^2*Datos_vigas!$B$5)))*J9*K9*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J9*K9))))</f>
+        <v/>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P9" s="25">
+        <f>IF(NOT(ISNUMBER(I9)),"---",IF(I9&lt;=0,"---",IF(I9*100/(Datos_vigas!$B$8*J9*K9^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I9*100/(Datos_vigas!$B$8*J9*K9^2*Datos_vigas!$B$5)))*J9*K9*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J9*K9))))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" s="25">
+        <f>F9/(J9*0.85*K9)</f>
+        <v/>
+      </c>
+      <c r="T9" s="25">
+        <f>G9/(J9*0.85*K9)</f>
+        <v/>
+      </c>
+      <c r="U9" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W9" s="11">
+        <f>IF(OR(M9="REVISAR",P9="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M9&lt;&gt;"REVISAR",P9&lt;&gt;"REVISAR",IF(ISNUMBER(M9),N9*PI()*(O9/10)^2/4&gt;=M9,TRUE),IF(ISNUMBER(P9),Q9*PI()*(R9/10)^2/4&gt;=P9,TRUE),IF(ISNUMBER(M9),M9&lt;=0.0163*J9*K9,TRUE),IF(ISNUMBER(P9),P9&lt;=0.0163*J9*K9,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F9&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J9*K9+2*PI()*(U9/10)^2/4*Datos_vigas!$B$6*K9/V9)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X9" s="13" t="inlineStr">
+        <is>
+          <t>El ancho quedo cortado en el PDF: se adopta 20 cm. Confirmar si es 20 o 22.</t>
+        </is>
+      </c>
+      <c r="Y9" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z9" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>VF04b</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D10" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J10*L10/10000+Datos_vigas!$B$16*Y10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="24">
+        <f>VLOOKUP(C10,Datos_vigas!$A$19:$E$23,4,0)*D10*B10</f>
+        <v/>
+      </c>
+      <c r="G10" s="24">
+        <f>F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="24">
+        <f>VLOOKUP(C10,Datos_vigas!$A$19:$E$23,2,0)*D10*B10^2</f>
+        <v/>
+      </c>
+      <c r="I10" s="24">
+        <f>IF(VLOOKUP(C10,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C10,Datos_vigas!$A$19:$E$23,3,0)*D10*B10^2)</f>
+        <v/>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" s="11">
+        <f>L10-Z10</f>
+        <v/>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" s="25">
+        <f>IF(NOT(ISNUMBER(H10)),"---",IF(H10&lt;=0,"---",IF(H10*100/(Datos_vigas!$B$8*J10*K10^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H10*100/(Datos_vigas!$B$8*J10*K10^2*Datos_vigas!$B$5)))*J10*K10*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J10*K10))))</f>
+        <v/>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" s="25">
+        <f>IF(NOT(ISNUMBER(I10)),"---",IF(I10&lt;=0,"---",IF(I10*100/(Datos_vigas!$B$8*J10*K10^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I10*100/(Datos_vigas!$B$8*J10*K10^2*Datos_vigas!$B$5)))*J10*K10*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J10*K10))))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" s="25">
+        <f>F10/(J10*0.85*K10)</f>
+        <v/>
+      </c>
+      <c r="T10" s="25">
+        <f>G10/(J10*0.85*K10)</f>
+        <v/>
+      </c>
+      <c r="U10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" s="11">
+        <f>IF(OR(M10="REVISAR",P10="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M10&lt;&gt;"REVISAR",P10&lt;&gt;"REVISAR",IF(ISNUMBER(M10),N10*PI()*(O10/10)^2/4&gt;=M10,TRUE),IF(ISNUMBER(P10),Q10*PI()*(R10/10)^2/4&gt;=P10,TRUE),IF(ISNUMBER(M10),M10&lt;=0.0163*J10*K10,TRUE),IF(ISNUMBER(P10),P10&lt;=0.0163*J10*K10,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F10&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J10*K10+2*PI()*(U10/10)^2/4*Datos_vigas!$B$6*K10/V10)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X10" s="11" t="n"/>
+      <c r="Y10" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z10" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>VF04c</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D11" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J11*L11/10000+Datos_vigas!$B$16*Y11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="24">
+        <f>VLOOKUP(C11,Datos_vigas!$A$19:$E$23,4,0)*D11*B11</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="24">
+        <f>VLOOKUP(C11,Datos_vigas!$A$19:$E$23,2,0)*D11*B11^2</f>
+        <v/>
+      </c>
+      <c r="I11" s="24">
+        <f>IF(VLOOKUP(C11,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C11,Datos_vigas!$A$19:$E$23,3,0)*D11*B11^2)</f>
+        <v/>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" s="11">
+        <f>L11-Z11</f>
+        <v/>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M11" s="25">
+        <f>IF(NOT(ISNUMBER(H11)),"---",IF(H11&lt;=0,"---",IF(H11*100/(Datos_vigas!$B$8*J11*K11^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H11*100/(Datos_vigas!$B$8*J11*K11^2*Datos_vigas!$B$5)))*J11*K11*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J11*K11))))</f>
+        <v/>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" s="25">
+        <f>IF(NOT(ISNUMBER(I11)),"---",IF(I11&lt;=0,"---",IF(I11*100/(Datos_vigas!$B$8*J11*K11^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I11*100/(Datos_vigas!$B$8*J11*K11^2*Datos_vigas!$B$5)))*J11*K11*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J11*K11))))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" s="25">
+        <f>F11/(J11*0.85*K11)</f>
+        <v/>
+      </c>
+      <c r="T11" s="25">
+        <f>G11/(J11*0.85*K11)</f>
+        <v/>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W11" s="11">
+        <f>IF(OR(M11="REVISAR",P11="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M11&lt;&gt;"REVISAR",P11&lt;&gt;"REVISAR",IF(ISNUMBER(M11),N11*PI()*(O11/10)^2/4&gt;=M11,TRUE),IF(ISNUMBER(P11),Q11*PI()*(R11/10)^2/4&gt;=P11,TRUE),IF(ISNUMBER(M11),M11&lt;=0.0163*J11*K11,TRUE),IF(ISNUMBER(P11),P11&lt;=0.0163*J11*K11,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F11&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J11*K11+2*PI()*(U11/10)^2/4*Datos_vigas!$B$6*K11/V11)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X11" s="11" t="n"/>
+      <c r="Y11" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>VF05</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D12" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J12*L12/10000+Datos_vigas!$B$16*Y12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="24">
+        <f>VLOOKUP(C12,Datos_vigas!$A$19:$E$23,4,0)*D12*B12</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="24">
+        <f>VLOOKUP(C12,Datos_vigas!$A$19:$E$23,2,0)*D12*B12^2</f>
+        <v/>
+      </c>
+      <c r="I12" s="24">
+        <f>IF(VLOOKUP(C12,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C12,Datos_vigas!$A$19:$E$23,3,0)*D12*B12^2)</f>
+        <v/>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="11">
+        <f>L12-Z12</f>
+        <v/>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" s="25">
+        <f>IF(NOT(ISNUMBER(H12)),"---",IF(H12&lt;=0,"---",IF(H12*100/(Datos_vigas!$B$8*J12*K12^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H12*100/(Datos_vigas!$B$8*J12*K12^2*Datos_vigas!$B$5)))*J12*K12*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J12*K12))))</f>
+        <v/>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" s="25">
+        <f>IF(NOT(ISNUMBER(I12)),"---",IF(I12&lt;=0,"---",IF(I12*100/(Datos_vigas!$B$8*J12*K12^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I12*100/(Datos_vigas!$B$8*J12*K12^2*Datos_vigas!$B$5)))*J12*K12*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J12*K12))))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S12" s="25">
+        <f>F12/(J12*0.85*K12)</f>
+        <v/>
+      </c>
+      <c r="T12" s="25">
+        <f>G12/(J12*0.85*K12)</f>
+        <v/>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W12" s="11">
+        <f>IF(OR(M12="REVISAR",P12="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M12&lt;&gt;"REVISAR",P12&lt;&gt;"REVISAR",IF(ISNUMBER(M12),N12*PI()*(O12/10)^2/4&gt;=M12,TRUE),IF(ISNUMBER(P12),Q12*PI()*(R12/10)^2/4&gt;=P12,TRUE),IF(ISNUMBER(M12),M12&lt;=0.0163*J12*K12,TRUE),IF(ISNUMBER(P12),P12&lt;=0.0163*J12*K12,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F12&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J12*K12+2*PI()*(U12/10)^2/4*Datos_vigas!$B$6*K12/V12)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X12" s="11" t="n"/>
+      <c r="Y12" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z12" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>VF06a</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="n"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="37" t="n"/>
+      <c r="M13" s="25" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="25" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="25" t="n"/>
+      <c r="T13" s="25" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>FALTA SECCION</t>
+        </is>
+      </c>
+      <c r="X13" s="13" t="inlineStr">
+        <is>
+          <t>El rotulo figura en el plano pero la cota no resulto legible. Completar b, d y la luz y la fila calcula sola.</t>
+        </is>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z13" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>VF06b</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="n"/>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="37" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="37" t="n"/>
+      <c r="M14" s="25" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="25" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="25" t="n"/>
+      <c r="T14" s="25" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n"/>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>FALTA SECCION</t>
+        </is>
+      </c>
+      <c r="X14" s="13" t="inlineStr">
+        <is>
+          <t>El rotulo figura en el plano pero la cota no resulto legible. Completar b, d y la luz y la fila calcula sola.</t>
+        </is>
+      </c>
+      <c r="Y14" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z14" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>VF06c</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D15" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J15*L15/10000+Datos_vigas!$B$16*Y15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="24">
+        <f>VLOOKUP(C15,Datos_vigas!$A$19:$E$23,4,0)*D15*B15</f>
+        <v/>
+      </c>
+      <c r="G15" s="24">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="24">
+        <f>VLOOKUP(C15,Datos_vigas!$A$19:$E$23,2,0)*D15*B15^2</f>
+        <v/>
+      </c>
+      <c r="I15" s="24">
+        <f>IF(VLOOKUP(C15,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C15,Datos_vigas!$A$19:$E$23,3,0)*D15*B15^2)</f>
+        <v/>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" s="11">
+        <f>L15-Z15</f>
+        <v/>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M15" s="25">
+        <f>IF(NOT(ISNUMBER(H15)),"---",IF(H15&lt;=0,"---",IF(H15*100/(Datos_vigas!$B$8*J15*K15^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H15*100/(Datos_vigas!$B$8*J15*K15^2*Datos_vigas!$B$5)))*J15*K15*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J15*K15))))</f>
+        <v/>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" s="25">
+        <f>IF(NOT(ISNUMBER(I15)),"---",IF(I15&lt;=0,"---",IF(I15*100/(Datos_vigas!$B$8*J15*K15^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I15*100/(Datos_vigas!$B$8*J15*K15^2*Datos_vigas!$B$5)))*J15*K15*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J15*K15))))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" s="25">
+        <f>F15/(J15*0.85*K15)</f>
+        <v/>
+      </c>
+      <c r="T15" s="25">
+        <f>G15/(J15*0.85*K15)</f>
+        <v/>
+      </c>
+      <c r="U15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V15" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W15" s="11">
+        <f>IF(OR(M15="REVISAR",P15="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M15&lt;&gt;"REVISAR",P15&lt;&gt;"REVISAR",IF(ISNUMBER(M15),N15*PI()*(O15/10)^2/4&gt;=M15,TRUE),IF(ISNUMBER(P15),Q15*PI()*(R15/10)^2/4&gt;=P15,TRUE),IF(ISNUMBER(M15),M15&lt;=0.0163*J15*K15,TRUE),IF(ISNUMBER(P15),P15&lt;=0.0163*J15*K15,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F15&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J15*K15+2*PI()*(U15/10)^2/4*Datos_vigas!$B$6*K15/V15)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X15" s="11" t="n"/>
+      <c r="Y15" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z15" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>VF06d</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D16" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J16*L16/10000+Datos_vigas!$B$16*Y16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="24">
+        <f>VLOOKUP(C16,Datos_vigas!$A$19:$E$23,4,0)*D16*B16</f>
+        <v/>
+      </c>
+      <c r="G16" s="24">
+        <f>F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="24">
+        <f>VLOOKUP(C16,Datos_vigas!$A$19:$E$23,2,0)*D16*B16^2</f>
+        <v/>
+      </c>
+      <c r="I16" s="24">
+        <f>IF(VLOOKUP(C16,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C16,Datos_vigas!$A$19:$E$23,3,0)*D16*B16^2)</f>
+        <v/>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="K16" s="11">
+        <f>L16-Z16</f>
+        <v/>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M16" s="25">
+        <f>IF(NOT(ISNUMBER(H16)),"---",IF(H16&lt;=0,"---",IF(H16*100/(Datos_vigas!$B$8*J16*K16^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H16*100/(Datos_vigas!$B$8*J16*K16^2*Datos_vigas!$B$5)))*J16*K16*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J16*K16))))</f>
+        <v/>
+      </c>
+      <c r="N16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" s="25">
+        <f>IF(NOT(ISNUMBER(I16)),"---",IF(I16&lt;=0,"---",IF(I16*100/(Datos_vigas!$B$8*J16*K16^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I16*100/(Datos_vigas!$B$8*J16*K16^2*Datos_vigas!$B$5)))*J16*K16*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J16*K16))))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" s="25">
+        <f>F16/(J16*0.85*K16)</f>
+        <v/>
+      </c>
+      <c r="T16" s="25">
+        <f>G16/(J16*0.85*K16)</f>
+        <v/>
+      </c>
+      <c r="U16" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V16" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" s="11">
+        <f>IF(OR(M16="REVISAR",P16="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M16&lt;&gt;"REVISAR",P16&lt;&gt;"REVISAR",IF(ISNUMBER(M16),N16*PI()*(O16/10)^2/4&gt;=M16,TRUE),IF(ISNUMBER(P16),Q16*PI()*(R16/10)^2/4&gt;=P16,TRUE),IF(ISNUMBER(M16),M16&lt;=0.0163*J16*K16,TRUE),IF(ISNUMBER(P16),P16&lt;=0.0163*J16*K16,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F16&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J16*K16+2*PI()*(U16/10)^2/4*Datos_vigas!$B$6*K16/V16)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X16" s="11" t="n"/>
+      <c r="Y16" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z16" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>VF07</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D17" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J17*L17/10000+Datos_vigas!$B$16*Y17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="24">
+        <f>VLOOKUP(C17,Datos_vigas!$A$19:$E$23,4,0)*D17*B17</f>
+        <v/>
+      </c>
+      <c r="G17" s="24">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="24">
+        <f>VLOOKUP(C17,Datos_vigas!$A$19:$E$23,2,0)*D17*B17^2</f>
+        <v/>
+      </c>
+      <c r="I17" s="24">
+        <f>IF(VLOOKUP(C17,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C17,Datos_vigas!$A$19:$E$23,3,0)*D17*B17^2)</f>
+        <v/>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" s="11">
+        <f>L17-Z17</f>
+        <v/>
+      </c>
+      <c r="L17" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M17" s="25">
+        <f>IF(NOT(ISNUMBER(H17)),"---",IF(H17&lt;=0,"---",IF(H17*100/(Datos_vigas!$B$8*J17*K17^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H17*100/(Datos_vigas!$B$8*J17*K17^2*Datos_vigas!$B$5)))*J17*K17*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J17*K17))))</f>
+        <v/>
+      </c>
+      <c r="N17" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P17" s="25">
+        <f>IF(NOT(ISNUMBER(I17)),"---",IF(I17&lt;=0,"---",IF(I17*100/(Datos_vigas!$B$8*J17*K17^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I17*100/(Datos_vigas!$B$8*J17*K17^2*Datos_vigas!$B$5)))*J17*K17*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J17*K17))))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S17" s="25">
+        <f>F17/(J17*0.85*K17)</f>
+        <v/>
+      </c>
+      <c r="T17" s="25">
+        <f>G17/(J17*0.85*K17)</f>
+        <v/>
+      </c>
+      <c r="U17" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" s="11">
+        <f>IF(OR(M17="REVISAR",P17="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M17&lt;&gt;"REVISAR",P17&lt;&gt;"REVISAR",IF(ISNUMBER(M17),N17*PI()*(O17/10)^2/4&gt;=M17,TRUE),IF(ISNUMBER(P17),Q17*PI()*(R17/10)^2/4&gt;=P17,TRUE),IF(ISNUMBER(M17),M17&lt;=0.0163*J17*K17,TRUE),IF(ISNUMBER(P17),P17&lt;=0.0163*J17*K17,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F17&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J17*K17+2*PI()*(U17/10)^2/4*Datos_vigas!$B$6*K17/V17)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X17" s="11" t="n"/>
+      <c r="Y17" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z17" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>VF08</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D18" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J18*L18/10000+Datos_vigas!$B$16*Y18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="24">
+        <f>VLOOKUP(C18,Datos_vigas!$A$19:$E$23,4,0)*D18*B18</f>
+        <v/>
+      </c>
+      <c r="G18" s="24">
+        <f>F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="24">
+        <f>VLOOKUP(C18,Datos_vigas!$A$19:$E$23,2,0)*D18*B18^2</f>
+        <v/>
+      </c>
+      <c r="I18" s="24">
+        <f>IF(VLOOKUP(C18,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C18,Datos_vigas!$A$19:$E$23,3,0)*D18*B18^2)</f>
+        <v/>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K18" s="11">
+        <f>L18-Z18</f>
+        <v/>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M18" s="25">
+        <f>IF(NOT(ISNUMBER(H18)),"---",IF(H18&lt;=0,"---",IF(H18*100/(Datos_vigas!$B$8*J18*K18^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H18*100/(Datos_vigas!$B$8*J18*K18^2*Datos_vigas!$B$5)))*J18*K18*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J18*K18))))</f>
+        <v/>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" s="25">
+        <f>IF(NOT(ISNUMBER(I18)),"---",IF(I18&lt;=0,"---",IF(I18*100/(Datos_vigas!$B$8*J18*K18^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I18*100/(Datos_vigas!$B$8*J18*K18^2*Datos_vigas!$B$5)))*J18*K18*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J18*K18))))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S18" s="25">
+        <f>F18/(J18*0.85*K18)</f>
+        <v/>
+      </c>
+      <c r="T18" s="25">
+        <f>G18/(J18*0.85*K18)</f>
+        <v/>
+      </c>
+      <c r="U18" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V18" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W18" s="11">
+        <f>IF(OR(M18="REVISAR",P18="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M18&lt;&gt;"REVISAR",P18&lt;&gt;"REVISAR",IF(ISNUMBER(M18),N18*PI()*(O18/10)^2/4&gt;=M18,TRUE),IF(ISNUMBER(P18),Q18*PI()*(R18/10)^2/4&gt;=P18,TRUE),IF(ISNUMBER(M18),M18&lt;=0.0163*J18*K18,TRUE),IF(ISNUMBER(P18),P18&lt;=0.0163*J18*K18,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F18&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J18*K18+2*PI()*(U18/10)^2/4*Datos_vigas!$B$6*K18/V18)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X18" s="11" t="n"/>
+      <c r="Y18" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z18" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>VF09 (1)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D19" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J19*L19/10000+Datos_vigas!$B$16*Y19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="24">
+        <f>VLOOKUP(C19,Datos_vigas!$A$19:$E$23,4,0)*D19*B19</f>
+        <v/>
+      </c>
+      <c r="G19" s="24">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="24">
+        <f>VLOOKUP(C19,Datos_vigas!$A$19:$E$23,2,0)*D19*B19^2</f>
+        <v/>
+      </c>
+      <c r="I19" s="24">
+        <f>IF(VLOOKUP(C19,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C19,Datos_vigas!$A$19:$E$23,3,0)*D19*B19^2)</f>
+        <v/>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" s="11">
+        <f>L19-Z19</f>
+        <v/>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M19" s="25">
+        <f>IF(NOT(ISNUMBER(H19)),"---",IF(H19&lt;=0,"---",IF(H19*100/(Datos_vigas!$B$8*J19*K19^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H19*100/(Datos_vigas!$B$8*J19*K19^2*Datos_vigas!$B$5)))*J19*K19*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J19*K19))))</f>
+        <v/>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P19" s="25">
+        <f>IF(NOT(ISNUMBER(I19)),"---",IF(I19&lt;=0,"---",IF(I19*100/(Datos_vigas!$B$8*J19*K19^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I19*100/(Datos_vigas!$B$8*J19*K19^2*Datos_vigas!$B$5)))*J19*K19*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J19*K19))))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S19" s="25">
+        <f>F19/(J19*0.85*K19)</f>
+        <v/>
+      </c>
+      <c r="T19" s="25">
+        <f>G19/(J19*0.85*K19)</f>
+        <v/>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V19" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W19" s="11">
+        <f>IF(OR(M19="REVISAR",P19="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M19&lt;&gt;"REVISAR",P19&lt;&gt;"REVISAR",IF(ISNUMBER(M19),N19*PI()*(O19/10)^2/4&gt;=M19,TRUE),IF(ISNUMBER(P19),Q19*PI()*(R19/10)^2/4&gt;=P19,TRUE),IF(ISNUMBER(M19),M19&lt;=0.0163*J19*K19,TRUE),IF(ISNUMBER(P19),P19&lt;=0.0163*J19*K19,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F19&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J19*K19+2*PI()*(U19/10)^2/4*Datos_vigas!$B$6*K19/V19)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X19" s="11" t="n"/>
+      <c r="Y19" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z19" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>VF09 (2)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D20" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J20*L20/10000+Datos_vigas!$B$16*Y20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="24">
+        <f>VLOOKUP(C20,Datos_vigas!$A$19:$E$23,4,0)*D20*B20</f>
+        <v/>
+      </c>
+      <c r="G20" s="24">
+        <f>F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="24">
+        <f>VLOOKUP(C20,Datos_vigas!$A$19:$E$23,2,0)*D20*B20^2</f>
+        <v/>
+      </c>
+      <c r="I20" s="24">
+        <f>IF(VLOOKUP(C20,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C20,Datos_vigas!$A$19:$E$23,3,0)*D20*B20^2)</f>
+        <v/>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K20" s="11">
+        <f>L20-Z20</f>
+        <v/>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M20" s="25">
+        <f>IF(NOT(ISNUMBER(H20)),"---",IF(H20&lt;=0,"---",IF(H20*100/(Datos_vigas!$B$8*J20*K20^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H20*100/(Datos_vigas!$B$8*J20*K20^2*Datos_vigas!$B$5)))*J20*K20*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J20*K20))))</f>
+        <v/>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P20" s="25">
+        <f>IF(NOT(ISNUMBER(I20)),"---",IF(I20&lt;=0,"---",IF(I20*100/(Datos_vigas!$B$8*J20*K20^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I20*100/(Datos_vigas!$B$8*J20*K20^2*Datos_vigas!$B$5)))*J20*K20*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J20*K20))))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S20" s="25">
+        <f>F20/(J20*0.85*K20)</f>
+        <v/>
+      </c>
+      <c r="T20" s="25">
+        <f>G20/(J20*0.85*K20)</f>
+        <v/>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W20" s="11">
+        <f>IF(OR(M20="REVISAR",P20="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M20&lt;&gt;"REVISAR",P20&lt;&gt;"REVISAR",IF(ISNUMBER(M20),N20*PI()*(O20/10)^2/4&gt;=M20,TRUE),IF(ISNUMBER(P20),Q20*PI()*(R20/10)^2/4&gt;=P20,TRUE),IF(ISNUMBER(M20),M20&lt;=0.0163*J20*K20,TRUE),IF(ISNUMBER(P20),P20&lt;=0.0163*J20*K20,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F20&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J20*K20+2*PI()*(U20/10)^2/4*Datos_vigas!$B$6*K20/V20)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X20" s="11" t="n"/>
+      <c r="Y20" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z20" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>VF10a</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D21" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J21*L21/10000+Datos_vigas!$B$16*Y21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="24">
+        <f>VLOOKUP(C21,Datos_vigas!$A$19:$E$23,4,0)*D21*B21</f>
+        <v/>
+      </c>
+      <c r="G21" s="24">
+        <f>F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="24">
+        <f>VLOOKUP(C21,Datos_vigas!$A$19:$E$23,2,0)*D21*B21^2</f>
+        <v/>
+      </c>
+      <c r="I21" s="24">
+        <f>IF(VLOOKUP(C21,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C21,Datos_vigas!$A$19:$E$23,3,0)*D21*B21^2)</f>
+        <v/>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" s="11">
+        <f>L21-Z21</f>
+        <v/>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M21" s="25">
+        <f>IF(NOT(ISNUMBER(H21)),"---",IF(H21&lt;=0,"---",IF(H21*100/(Datos_vigas!$B$8*J21*K21^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H21*100/(Datos_vigas!$B$8*J21*K21^2*Datos_vigas!$B$5)))*J21*K21*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J21*K21))))</f>
+        <v/>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P21" s="25">
+        <f>IF(NOT(ISNUMBER(I21)),"---",IF(I21&lt;=0,"---",IF(I21*100/(Datos_vigas!$B$8*J21*K21^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I21*100/(Datos_vigas!$B$8*J21*K21^2*Datos_vigas!$B$5)))*J21*K21*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J21*K21))))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S21" s="25">
+        <f>F21/(J21*0.85*K21)</f>
+        <v/>
+      </c>
+      <c r="T21" s="25">
+        <f>G21/(J21*0.85*K21)</f>
+        <v/>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V21" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W21" s="11">
+        <f>IF(OR(M21="REVISAR",P21="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M21&lt;&gt;"REVISAR",P21&lt;&gt;"REVISAR",IF(ISNUMBER(M21),N21*PI()*(O21/10)^2/4&gt;=M21,TRUE),IF(ISNUMBER(P21),Q21*PI()*(R21/10)^2/4&gt;=P21,TRUE),IF(ISNUMBER(M21),M21&lt;=0.0163*J21*K21,TRUE),IF(ISNUMBER(P21),P21&lt;=0.0163*J21*K21,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F21&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J21*K21+2*PI()*(U21/10)^2/4*Datos_vigas!$B$6*K21/V21)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X21" s="11" t="n"/>
+      <c r="Y21" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z21" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>VF10b</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D22" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J22*L22/10000+Datos_vigas!$B$16*Y22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="24">
+        <f>VLOOKUP(C22,Datos_vigas!$A$19:$E$23,4,0)*D22*B22</f>
+        <v/>
+      </c>
+      <c r="G22" s="24">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="24">
+        <f>VLOOKUP(C22,Datos_vigas!$A$19:$E$23,2,0)*D22*B22^2</f>
+        <v/>
+      </c>
+      <c r="I22" s="24">
+        <f>IF(VLOOKUP(C22,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C22,Datos_vigas!$A$19:$E$23,3,0)*D22*B22^2)</f>
+        <v/>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="K22" s="11">
+        <f>L22-Z22</f>
+        <v/>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M22" s="25">
+        <f>IF(NOT(ISNUMBER(H22)),"---",IF(H22&lt;=0,"---",IF(H22*100/(Datos_vigas!$B$8*J22*K22^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H22*100/(Datos_vigas!$B$8*J22*K22^2*Datos_vigas!$B$5)))*J22*K22*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J22*K22))))</f>
+        <v/>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" s="25">
+        <f>IF(NOT(ISNUMBER(I22)),"---",IF(I22&lt;=0,"---",IF(I22*100/(Datos_vigas!$B$8*J22*K22^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I22*100/(Datos_vigas!$B$8*J22*K22^2*Datos_vigas!$B$5)))*J22*K22*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J22*K22))))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S22" s="25">
+        <f>F22/(J22*0.85*K22)</f>
+        <v/>
+      </c>
+      <c r="T22" s="25">
+        <f>G22/(J22*0.85*K22)</f>
+        <v/>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W22" s="11">
+        <f>IF(OR(M22="REVISAR",P22="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M22&lt;&gt;"REVISAR",P22&lt;&gt;"REVISAR",IF(ISNUMBER(M22),N22*PI()*(O22/10)^2/4&gt;=M22,TRUE),IF(ISNUMBER(P22),Q22*PI()*(R22/10)^2/4&gt;=P22,TRUE),IF(ISNUMBER(M22),M22&lt;=0.0163*J22*K22,TRUE),IF(ISNUMBER(P22),P22&lt;=0.0163*J22*K22,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F22&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J22*K22+2*PI()*(U22/10)^2/4*Datos_vigas!$B$6*K22/V22)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X22" s="11" t="n"/>
+      <c r="Y22" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z22" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>VF10c</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D23" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J23*L23/10000+Datos_vigas!$B$16*Y23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="24">
+        <f>VLOOKUP(C23,Datos_vigas!$A$19:$E$23,4,0)*D23*B23</f>
+        <v/>
+      </c>
+      <c r="G23" s="24">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="24">
+        <f>VLOOKUP(C23,Datos_vigas!$A$19:$E$23,2,0)*D23*B23^2</f>
+        <v/>
+      </c>
+      <c r="I23" s="24">
+        <f>IF(VLOOKUP(C23,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C23,Datos_vigas!$A$19:$E$23,3,0)*D23*B23^2)</f>
+        <v/>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" s="11">
+        <f>L23-Z23</f>
+        <v/>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M23" s="25">
+        <f>IF(NOT(ISNUMBER(H23)),"---",IF(H23&lt;=0,"---",IF(H23*100/(Datos_vigas!$B$8*J23*K23^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H23*100/(Datos_vigas!$B$8*J23*K23^2*Datos_vigas!$B$5)))*J23*K23*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J23*K23))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P23" s="25">
+        <f>IF(NOT(ISNUMBER(I23)),"---",IF(I23&lt;=0,"---",IF(I23*100/(Datos_vigas!$B$8*J23*K23^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I23*100/(Datos_vigas!$B$8*J23*K23^2*Datos_vigas!$B$5)))*J23*K23*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J23*K23))))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="S23" s="25">
+        <f>F23/(J23*0.85*K23)</f>
+        <v/>
+      </c>
+      <c r="T23" s="25">
+        <f>G23/(J23*0.85*K23)</f>
+        <v/>
+      </c>
+      <c r="U23" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V23" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W23" s="11">
+        <f>IF(OR(M23="REVISAR",P23="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M23&lt;&gt;"REVISAR",P23&lt;&gt;"REVISAR",IF(ISNUMBER(M23),N23*PI()*(O23/10)^2/4&gt;=M23,TRUE),IF(ISNUMBER(P23),Q23*PI()*(R23/10)^2/4&gt;=P23,TRUE),IF(ISNUMBER(M23),M23&lt;=0.0163*J23*K23,TRUE),IF(ISNUMBER(P23),P23&lt;=0.0163*J23*K23,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F23&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J23*K23+2*PI()*(U23/10)^2/4*Datos_vigas!$B$6*K23/V23)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X23" s="13" t="inlineStr">
+        <is>
+          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+        </is>
+      </c>
+      <c r="Y23" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z23" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>VF11</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D24" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*Y24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="24">
+        <f>VLOOKUP(C24,Datos_vigas!$A$19:$E$23,4,0)*D24*B24</f>
+        <v/>
+      </c>
+      <c r="G24" s="24">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="24">
+        <f>VLOOKUP(C24,Datos_vigas!$A$19:$E$23,2,0)*D24*B24^2</f>
+        <v/>
+      </c>
+      <c r="I24" s="24">
+        <f>IF(VLOOKUP(C24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C24,Datos_vigas!$A$19:$E$23,3,0)*D24*B24^2)</f>
+        <v/>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" s="11">
+        <f>L24-Z24</f>
+        <v/>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M24" s="25">
+        <f>IF(NOT(ISNUMBER(H24)),"---",IF(H24&lt;=0,"---",IF(H24*100/(Datos_vigas!$B$8*J24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H24*100/(Datos_vigas!$B$8*J24*K24^2*Datos_vigas!$B$5)))*J24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" s="25">
+        <f>IF(NOT(ISNUMBER(I24)),"---",IF(I24&lt;=0,"---",IF(I24*100/(Datos_vigas!$B$8*J24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I24*100/(Datos_vigas!$B$8*J24*K24^2*Datos_vigas!$B$5)))*J24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S24" s="25">
+        <f>F24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="T24" s="25">
+        <f>G24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W24" s="11">
+        <f>IF(OR(M24="REVISAR",P24="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M24&lt;&gt;"REVISAR",P24&lt;&gt;"REVISAR",IF(ISNUMBER(M24),N24*PI()*(O24/10)^2/4&gt;=M24,TRUE),IF(ISNUMBER(P24),Q24*PI()*(R24/10)^2/4&gt;=P24,TRUE),IF(ISNUMBER(M24),M24&lt;=0.0163*J24*K24,TRUE),IF(ISNUMBER(P24),P24&lt;=0.0163*J24*K24,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F24&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J24*K24+2*PI()*(U24/10)^2/4*Datos_vigas!$B$6*K24/V24)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X24" s="13" t="inlineStr">
+        <is>
+          <t>Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+        </is>
+      </c>
+      <c r="Y24" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z24" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>VF12</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D25" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*Y25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="24">
+        <f>VLOOKUP(C25,Datos_vigas!$A$19:$E$23,4,0)*D25*B25</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="24">
+        <f>VLOOKUP(C25,Datos_vigas!$A$19:$E$23,2,0)*D25*B25^2</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
+        <f>IF(VLOOKUP(C25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C25,Datos_vigas!$A$19:$E$23,3,0)*D25*B25^2)</f>
+        <v/>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K25" s="11">
+        <f>L25-Z25</f>
+        <v/>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M25" s="25">
+        <f>IF(NOT(ISNUMBER(H25)),"---",IF(H25&lt;=0,"---",IF(H25*100/(Datos_vigas!$B$8*J25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H25*100/(Datos_vigas!$B$8*J25*K25^2*Datos_vigas!$B$5)))*J25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P25" s="25">
+        <f>IF(NOT(ISNUMBER(I25)),"---",IF(I25&lt;=0,"---",IF(I25*100/(Datos_vigas!$B$8*J25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I25*100/(Datos_vigas!$B$8*J25*K25^2*Datos_vigas!$B$5)))*J25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S25" s="25">
+        <f>F25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="T25" s="25">
+        <f>G25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V25" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" s="11">
+        <f>IF(OR(M25="REVISAR",P25="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M25&lt;&gt;"REVISAR",P25&lt;&gt;"REVISAR",IF(ISNUMBER(M25),N25*PI()*(O25/10)^2/4&gt;=M25,TRUE),IF(ISNUMBER(P25),Q25*PI()*(R25/10)^2/4&gt;=P25,TRUE),IF(ISNUMBER(M25),M25&lt;=0.0163*J25*K25,TRUE),IF(ISNUMBER(P25),P25&lt;=0.0163*J25*K25,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F25&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J25*K25+2*PI()*(U25/10)^2/4*Datos_vigas!$B$6*K25/V25)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z25" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>VF13</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="n"/>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="37" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="37" t="n"/>
+      <c r="M26" s="25" t="n"/>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="25" t="n"/>
+      <c r="Q26" s="10" t="n"/>
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="25" t="n"/>
+      <c r="T26" s="25" t="n"/>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>FALTA SECCION</t>
+        </is>
+      </c>
+      <c r="X26" s="13" t="inlineStr">
+        <is>
+          <t>El rotulo figura en el plano pero la cota no resulto legible. Completar b, d y la luz y la fila calcula sola.</t>
+        </is>
+      </c>
+      <c r="Y26" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z26" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>VF14</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D27" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*Y27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="24">
+        <f>VLOOKUP(C27,Datos_vigas!$A$19:$E$23,4,0)*D27*B27</f>
+        <v/>
+      </c>
+      <c r="G27" s="24">
+        <f>F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="24">
+        <f>VLOOKUP(C27,Datos_vigas!$A$19:$E$23,2,0)*D27*B27^2</f>
+        <v/>
+      </c>
+      <c r="I27" s="24">
+        <f>IF(VLOOKUP(C27,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C27,Datos_vigas!$A$19:$E$23,3,0)*D27*B27^2)</f>
+        <v/>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K27" s="11">
+        <f>L27-Z27</f>
+        <v/>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="M27" s="25">
+        <f>IF(NOT(ISNUMBER(H27)),"---",IF(H27&lt;=0,"---",IF(H27*100/(Datos_vigas!$B$8*J27*K27^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H27*100/(Datos_vigas!$B$8*J27*K27^2*Datos_vigas!$B$5)))*J27*K27*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J27*K27))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P27" s="25">
+        <f>IF(NOT(ISNUMBER(I27)),"---",IF(I27&lt;=0,"---",IF(I27*100/(Datos_vigas!$B$8*J27*K27^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I27*100/(Datos_vigas!$B$8*J27*K27^2*Datos_vigas!$B$5)))*J27*K27*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J27*K27))))</f>
+        <v/>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="25">
+        <f>F27/(J27*0.85*K27)</f>
+        <v/>
+      </c>
+      <c r="T27" s="25">
+        <f>G27/(J27*0.85*K27)</f>
+        <v/>
+      </c>
+      <c r="U27" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V27" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W27" s="11">
+        <f>IF(OR(M27="REVISAR",P27="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M27&lt;&gt;"REVISAR",P27&lt;&gt;"REVISAR",IF(ISNUMBER(M27),N27*PI()*(O27/10)^2/4&gt;=M27,TRUE),IF(ISNUMBER(P27),Q27*PI()*(R27/10)^2/4&gt;=P27,TRUE),IF(ISNUMBER(M27),M27&lt;=0.0163*J27*K27,TRUE),IF(ISNUMBER(P27),P27&lt;=0.0163*J27*K27,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F27&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J27*K27+2*PI()*(U27/10)^2/4*Datos_vigas!$B$6*K27/V27)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X27" s="13" t="inlineStr">
+        <is>
+          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+        </is>
+      </c>
+      <c r="Y27" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z27" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>VF15</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D28" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*Y28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="24">
+        <f>VLOOKUP(C28,Datos_vigas!$A$19:$E$23,4,0)*D28*B28</f>
+        <v/>
+      </c>
+      <c r="G28" s="24">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="24">
+        <f>VLOOKUP(C28,Datos_vigas!$A$19:$E$23,2,0)*D28*B28^2</f>
+        <v/>
+      </c>
+      <c r="I28" s="24">
+        <f>IF(VLOOKUP(C28,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C28,Datos_vigas!$A$19:$E$23,3,0)*D28*B28^2)</f>
+        <v/>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K28" s="11">
+        <f>L28-Z28</f>
+        <v/>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M28" s="25">
+        <f>IF(NOT(ISNUMBER(H28)),"---",IF(H28&lt;=0,"---",IF(H28*100/(Datos_vigas!$B$8*J28*K28^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H28*100/(Datos_vigas!$B$8*J28*K28^2*Datos_vigas!$B$5)))*J28*K28*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J28*K28))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P28" s="25">
+        <f>IF(NOT(ISNUMBER(I28)),"---",IF(I28&lt;=0,"---",IF(I28*100/(Datos_vigas!$B$8*J28*K28^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I28*100/(Datos_vigas!$B$8*J28*K28^2*Datos_vigas!$B$5)))*J28*K28*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J28*K28))))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R28" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S28" s="25">
+        <f>F28/(J28*0.85*K28)</f>
+        <v/>
+      </c>
+      <c r="T28" s="25">
+        <f>G28/(J28*0.85*K28)</f>
+        <v/>
+      </c>
+      <c r="U28" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V28" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W28" s="11">
+        <f>IF(OR(M28="REVISAR",P28="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M28&lt;&gt;"REVISAR",P28&lt;&gt;"REVISAR",IF(ISNUMBER(M28),N28*PI()*(O28/10)^2/4&gt;=M28,TRUE),IF(ISNUMBER(P28),Q28*PI()*(R28/10)^2/4&gt;=P28,TRUE),IF(ISNUMBER(M28),M28&lt;=0.0163*J28*K28,TRUE),IF(ISNUMBER(P28),P28&lt;=0.0163*J28*K28,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F28&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J28*K28+2*PI()*(U28/10)^2/4*Datos_vigas!$B$6*K28/V28)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X28" s="11" t="n"/>
+      <c r="Y28" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z28" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>VF16a</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D29" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*Y29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="24">
+        <f>VLOOKUP(C29,Datos_vigas!$A$19:$E$23,4,0)*D29*B29</f>
+        <v/>
+      </c>
+      <c r="G29" s="24">
+        <f>F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="24">
+        <f>VLOOKUP(C29,Datos_vigas!$A$19:$E$23,2,0)*D29*B29^2</f>
+        <v/>
+      </c>
+      <c r="I29" s="24">
+        <f>IF(VLOOKUP(C29,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C29,Datos_vigas!$A$19:$E$23,3,0)*D29*B29^2)</f>
+        <v/>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="11">
+        <f>L29-Z29</f>
+        <v/>
+      </c>
+      <c r="L29" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M29" s="25">
+        <f>IF(NOT(ISNUMBER(H29)),"---",IF(H29&lt;=0,"---",IF(H29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)))*J29*K29*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J29*K29))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P29" s="25">
+        <f>IF(NOT(ISNUMBER(I29)),"---",IF(I29&lt;=0,"---",IF(I29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)))*J29*K29*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J29*K29))))</f>
+        <v/>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="S29" s="25">
+        <f>F29/(J29*0.85*K29)</f>
+        <v/>
+      </c>
+      <c r="T29" s="25">
+        <f>G29/(J29*0.85*K29)</f>
+        <v/>
+      </c>
+      <c r="U29" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V29" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W29" s="11">
+        <f>IF(OR(M29="REVISAR",P29="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M29&lt;&gt;"REVISAR",P29&lt;&gt;"REVISAR",IF(ISNUMBER(M29),N29*PI()*(O29/10)^2/4&gt;=M29,TRUE),IF(ISNUMBER(P29),Q29*PI()*(R29/10)^2/4&gt;=P29,TRUE),IF(ISNUMBER(M29),M29&lt;=0.0163*J29*K29,TRUE),IF(ISNUMBER(P29),P29&lt;=0.0163*J29*K29,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F29&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J29*K29+2*PI()*(U29/10)^2/4*Datos_vigas!$B$6*K29/V29)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X29" s="13" t="inlineStr">
+        <is>
+          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ.</t>
+        </is>
+      </c>
+      <c r="Y29" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z29" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>VF16b</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D30" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*Y30)</f>
+        <v/>
+      </c>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="24">
+        <f>VLOOKUP(C30,Datos_vigas!$A$19:$E$23,4,0)*D30*B30</f>
+        <v/>
+      </c>
+      <c r="G30" s="24">
+        <f>F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="24">
+        <f>VLOOKUP(C30,Datos_vigas!$A$19:$E$23,2,0)*D30*B30^2</f>
+        <v/>
+      </c>
+      <c r="I30" s="24">
+        <f>IF(VLOOKUP(C30,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C30,Datos_vigas!$A$19:$E$23,3,0)*D30*B30^2)</f>
+        <v/>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K30" s="11">
+        <f>L30-Z30</f>
+        <v/>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M30" s="25">
+        <f>IF(NOT(ISNUMBER(H30)),"---",IF(H30&lt;=0,"---",IF(H30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)))*J30*K30*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J30*K30))))</f>
+        <v/>
+      </c>
+      <c r="N30" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O30" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" s="25">
+        <f>IF(NOT(ISNUMBER(I30)),"---",IF(I30&lt;=0,"---",IF(I30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)))*J30*K30*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J30*K30))))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S30" s="25">
+        <f>F30/(J30*0.85*K30)</f>
+        <v/>
+      </c>
+      <c r="T30" s="25">
+        <f>G30/(J30*0.85*K30)</f>
+        <v/>
+      </c>
+      <c r="U30" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W30" s="11">
+        <f>IF(OR(M30="REVISAR",P30="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M30&lt;&gt;"REVISAR",P30&lt;&gt;"REVISAR",IF(ISNUMBER(M30),N30*PI()*(O30/10)^2/4&gt;=M30,TRUE),IF(ISNUMBER(P30),Q30*PI()*(R30/10)^2/4&gt;=P30,TRUE),IF(ISNUMBER(M30),M30&lt;=0.0163*J30*K30,TRUE),IF(ISNUMBER(P30),P30&lt;=0.0163*J30*K30,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F30&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J30*K30+2*PI()*(U30/10)^2/4*Datos_vigas!$B$6*K30/V30)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X30" s="11" t="n"/>
+      <c r="Y30" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z30" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>VF17</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D31" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*Y31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="24">
+        <f>VLOOKUP(C31,Datos_vigas!$A$19:$E$23,4,0)*D31*B31</f>
+        <v/>
+      </c>
+      <c r="G31" s="24">
+        <f>F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="24">
+        <f>VLOOKUP(C31,Datos_vigas!$A$19:$E$23,2,0)*D31*B31^2</f>
+        <v/>
+      </c>
+      <c r="I31" s="24">
+        <f>IF(VLOOKUP(C31,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C31,Datos_vigas!$A$19:$E$23,3,0)*D31*B31^2)</f>
+        <v/>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K31" s="11">
+        <f>L31-Z31</f>
+        <v/>
+      </c>
+      <c r="L31" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M31" s="25">
+        <f>IF(NOT(ISNUMBER(H31)),"---",IF(H31&lt;=0,"---",IF(H31*100/(Datos_vigas!$B$8*J31*K31^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H31*100/(Datos_vigas!$B$8*J31*K31^2*Datos_vigas!$B$5)))*J31*K31*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J31*K31))))</f>
+        <v/>
+      </c>
+      <c r="N31" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" s="25">
+        <f>IF(NOT(ISNUMBER(I31)),"---",IF(I31&lt;=0,"---",IF(I31*100/(Datos_vigas!$B$8*J31*K31^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I31*100/(Datos_vigas!$B$8*J31*K31^2*Datos_vigas!$B$5)))*J31*K31*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J31*K31))))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S31" s="25">
+        <f>F31/(J31*0.85*K31)</f>
+        <v/>
+      </c>
+      <c r="T31" s="25">
+        <f>G31/(J31*0.85*K31)</f>
+        <v/>
+      </c>
+      <c r="U31" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V31" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W31" s="11">
+        <f>IF(OR(M31="REVISAR",P31="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M31&lt;&gt;"REVISAR",P31&lt;&gt;"REVISAR",IF(ISNUMBER(M31),N31*PI()*(O31/10)^2/4&gt;=M31,TRUE),IF(ISNUMBER(P31),Q31*PI()*(R31/10)^2/4&gt;=P31,TRUE),IF(ISNUMBER(M31),M31&lt;=0.0163*J31*K31,TRUE),IF(ISNUMBER(P31),P31&lt;=0.0163*J31*K31,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F31&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J31*K31+2*PI()*(U31/10)^2/4*Datos_vigas!$B$6*K31/V31)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z31" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" ht="46" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>VF18a</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D32" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*Y32)</f>
+        <v/>
+      </c>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="24">
+        <f>VLOOKUP(C32,Datos_vigas!$A$19:$E$23,4,0)*D32*B32</f>
+        <v/>
+      </c>
+      <c r="G32" s="24">
+        <f>F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="24">
+        <f>VLOOKUP(C32,Datos_vigas!$A$19:$E$23,2,0)*D32*B32^2</f>
+        <v/>
+      </c>
+      <c r="I32" s="24">
+        <f>IF(VLOOKUP(C32,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C32,Datos_vigas!$A$19:$E$23,3,0)*D32*B32^2)</f>
+        <v/>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K32" s="11">
+        <f>L32-Z32</f>
+        <v/>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="M32" s="25">
+        <f>IF(NOT(ISNUMBER(H32)),"---",IF(H32&lt;=0,"---",IF(H32*100/(Datos_vigas!$B$8*J32*K32^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H32*100/(Datos_vigas!$B$8*J32*K32^2*Datos_vigas!$B$5)))*J32*K32*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J32*K32))))</f>
+        <v/>
+      </c>
+      <c r="N32" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P32" s="25">
+        <f>IF(NOT(ISNUMBER(I32)),"---",IF(I32&lt;=0,"---",IF(I32*100/(Datos_vigas!$B$8*J32*K32^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I32*100/(Datos_vigas!$B$8*J32*K32^2*Datos_vigas!$B$5)))*J32*K32*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J32*K32))))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="S32" s="25">
+        <f>F32/(J32*0.85*K32)</f>
+        <v/>
+      </c>
+      <c r="T32" s="25">
+        <f>G32/(J32*0.85*K32)</f>
+        <v/>
+      </c>
+      <c r="U32" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W32" s="11">
+        <f>IF(OR(M32="REVISAR",P32="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M32&lt;&gt;"REVISAR",P32&lt;&gt;"REVISAR",IF(ISNUMBER(M32),N32*PI()*(O32/10)^2/4&gt;=M32,TRUE),IF(ISNUMBER(P32),Q32*PI()*(R32/10)^2/4&gt;=P32,TRUE),IF(ISNUMBER(M32),M32&lt;=0.0163*J32*K32,TRUE),IF(ISNUMBER(P32),P32&lt;=0.0163*J32*K32,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F32&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J32*K32+2*PI()*(U32/10)^2/4*Datos_vigas!$B$6*K32/V32)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X32" s="13" t="inlineStr">
+        <is>
+          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+        </is>
+      </c>
+      <c r="Y32" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z32" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>VF18b</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D33" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*Y33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="24">
+        <f>VLOOKUP(C33,Datos_vigas!$A$19:$E$23,4,0)*D33*B33</f>
+        <v/>
+      </c>
+      <c r="G33" s="24">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="24">
+        <f>VLOOKUP(C33,Datos_vigas!$A$19:$E$23,2,0)*D33*B33^2</f>
+        <v/>
+      </c>
+      <c r="I33" s="24">
+        <f>IF(VLOOKUP(C33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C33,Datos_vigas!$A$19:$E$23,3,0)*D33*B33^2)</f>
+        <v/>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K33" s="11">
+        <f>L33-Z33</f>
+        <v/>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M33" s="25">
+        <f>IF(NOT(ISNUMBER(H33)),"---",IF(H33&lt;=0,"---",IF(H33*100/(Datos_vigas!$B$8*J33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H33*100/(Datos_vigas!$B$8*J33*K33^2*Datos_vigas!$B$5)))*J33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P33" s="25">
+        <f>IF(NOT(ISNUMBER(I33)),"---",IF(I33&lt;=0,"---",IF(I33*100/(Datos_vigas!$B$8*J33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I33*100/(Datos_vigas!$B$8*J33*K33^2*Datos_vigas!$B$5)))*J33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S33" s="25">
+        <f>F33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="T33" s="25">
+        <f>G33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="U33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W33" s="11">
+        <f>IF(OR(M33="REVISAR",P33="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M33&lt;&gt;"REVISAR",P33&lt;&gt;"REVISAR",IF(ISNUMBER(M33),N33*PI()*(O33/10)^2/4&gt;=M33,TRUE),IF(ISNUMBER(P33),Q33*PI()*(R33/10)^2/4&gt;=P33,TRUE),IF(ISNUMBER(M33),M33&lt;=0.0163*J33*K33,TRUE),IF(ISNUMBER(P33),P33&lt;=0.0163*J33*K33,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F33&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J33*K33+2*PI()*(U33/10)^2/4*Datos_vigas!$B$6*K33/V33)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z33" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>VF18c</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="D34" s="29">
+        <f>1.2*(Datos_vigas!$B$7*J34*L34/10000+Datos_vigas!$B$16*Y34)</f>
+        <v/>
+      </c>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="29">
+        <f>VLOOKUP(C34,Datos_vigas!$A$19:$E$23,4,0)*D34*B34</f>
+        <v/>
+      </c>
+      <c r="G34" s="29">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="29">
+        <f>VLOOKUP(C34,Datos_vigas!$A$19:$E$23,2,0)*D34*B34^2</f>
+        <v/>
+      </c>
+      <c r="I34" s="29">
+        <f>IF(VLOOKUP(C34,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C34,Datos_vigas!$A$19:$E$23,3,0)*D34*B34^2)</f>
+        <v/>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" s="18">
+        <f>L34-Z34</f>
+        <v/>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="M34" s="30">
+        <f>IF(NOT(ISNUMBER(H34)),"---",IF(H34&lt;=0,"---",IF(H34*100/(Datos_vigas!$B$8*J34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H34*100/(Datos_vigas!$B$8*J34*K34^2*Datos_vigas!$B$5)))*J34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="P34" s="30">
+        <f>IF(NOT(ISNUMBER(I34)),"---",IF(I34&lt;=0,"---",IF(I34*100/(Datos_vigas!$B$8*J34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I34*100/(Datos_vigas!$B$8*J34*K34^2*Datos_vigas!$B$5)))*J34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="S34" s="30">
+        <f>F34/(J34*0.85*K34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="30">
+        <f>G34/(J34*0.85*K34)</f>
+        <v/>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="W34" s="18">
+        <f>IF(OR(M34="REVISAR",P34="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M34&lt;&gt;"REVISAR",P34&lt;&gt;"REVISAR",IF(ISNUMBER(M34),N34*PI()*(O34/10)^2/4&gt;=M34,TRUE),IF(ISNUMBER(P34),Q34*PI()*(R34/10)^2/4&gt;=P34,TRUE),IF(ISNUMBER(M34),M34&lt;=0.0163*J34*K34,TRUE),IF(ISNUMBER(P34),P34&lt;=0.0163*J34*K34,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F34&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J34*K34+2*PI()*(U34/10)^2/4*Datos_vigas!$B$6*K34/V34)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X34" s="18" t="n"/>
+      <c r="Y34" s="19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Z34" s="19" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="S2:U2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="V2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="W2:W3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="W4:W34">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"VERIFICA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"NO VERIFICA FLEX."</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"NO VERIF. CORTE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+      <formula>"SECCION INSUF."</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"FALTA SECCION"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C4:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Datos_vigas!$A$19:$A$23</formula1>
+    </dataValidation>
+    <dataValidation sqref="O4:O34 R4:R34 U4:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"6,8,10,12,16,20,25"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F25"/>
@@ -9998,7 +14341,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - HIPOTESIS DE CALCULO</t>
         </is>
@@ -10010,7 +14353,7 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
         </is>
@@ -10030,17 +14373,17 @@
       <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -10050,12 +14393,12 @@
       <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="47" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -10068,12 +14411,12 @@
       <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="47" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -10086,12 +14429,12 @@
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -10104,12 +14447,12 @@
       <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>phi flexion</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -10122,12 +14465,12 @@
       <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>phi corte</t>
         </is>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="47" t="n">
         <v>0.75</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -10140,12 +14483,12 @@
       <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Coef. mayoracion permanente</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="47" t="n">
         <v>1.2</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -10158,12 +14501,12 @@
       <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Coef. mayoracion sobrecarga</t>
         </is>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="47" t="n">
         <v>1.6</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -10184,7 +14527,7 @@
       <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>PAQUETES DE CARGA</t>
         </is>
@@ -10216,21 +14559,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="inlineStr">
+      <c r="A14" s="48" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B14" s="48" t="n">
+      <c r="B14" s="49" t="n">
         <v>550</v>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="D14" s="49" t="n">
+      <c r="D14" s="50" t="n">
         <v>2.6</v>
       </c>
-      <c r="E14" s="49" t="n">
+      <c r="E14" s="50" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="32" t="inlineStr">
@@ -10240,21 +14583,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>TECHO</t>
         </is>
       </c>
-      <c r="B15" s="48" t="n">
+      <c r="B15" s="49" t="n">
         <v>560</v>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="49" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="49" t="n">
+      <c r="D15" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="49" t="n">
+      <c r="E15" s="50" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="32" t="inlineStr">
@@ -10264,12 +14607,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>Mamposteria sobre viga</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="47" t="n">
         <v>250</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -10279,7 +14622,7 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="50" t="inlineStr">
+      <c r="F16" s="51" t="inlineStr">
         <is>
           <t>Ladrillo hueco 18 cm + revoque en ambas caras</t>
         </is>
@@ -10294,7 +14637,7 @@
       <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>COEFICIENTES SEGUN ESQUEMA</t>
         </is>
@@ -10322,101 +14665,101 @@
       <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="B19" s="51" t="n">
+      <c r="B19" s="52" t="n">
         <v>0.125</v>
       </c>
-      <c r="C19" s="51" t="n">
+      <c r="C19" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="51" t="n">
+      <c r="D19" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E19" s="53" t="n">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n">
+      <c r="B20" s="52" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="C20" s="51" t="n">
+      <c r="C20" s="52" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="51" t="n">
+      <c r="D20" s="52" t="n">
         <v>0.575</v>
       </c>
-      <c r="E20" s="52" t="n">
+      <c r="E20" s="53" t="n">
         <v>21</v>
       </c>
       <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Empotrada-apoyada</t>
         </is>
       </c>
-      <c r="B21" s="51" t="n">
+      <c r="B21" s="52" t="n">
         <v>0.07031</v>
       </c>
-      <c r="C21" s="51" t="n">
+      <c r="C21" s="52" t="n">
         <v>0.125</v>
       </c>
-      <c r="D21" s="51" t="n">
+      <c r="D21" s="52" t="n">
         <v>0.625</v>
       </c>
-      <c r="E21" s="52" t="n">
+      <c r="E21" s="53" t="n">
         <v>18.5</v>
       </c>
       <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t>Biempotrada</t>
         </is>
       </c>
-      <c r="B22" s="51" t="n">
+      <c r="B22" s="52" t="n">
         <v>0.04167</v>
       </c>
-      <c r="C22" s="51" t="n">
+      <c r="C22" s="52" t="n">
         <v>0.08333</v>
       </c>
-      <c r="D22" s="51" t="n">
+      <c r="D22" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="52" t="n">
+      <c r="E22" s="53" t="n">
         <v>21</v>
       </c>
       <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="A23" s="46" t="inlineStr">
         <is>
           <t>Voladizo</t>
         </is>
       </c>
-      <c r="B23" s="51" t="n">
+      <c r="B23" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="51" t="n">
+      <c r="C23" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="D23" s="51" t="n">
+      <c r="D23" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="52" t="n">
+      <c r="E23" s="53" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -10430,7 +14773,7 @@
       <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="inlineStr">
+      <c r="A25" s="54" t="inlineStr">
         <is>
           <t>p = 1,2 g + 1,6 q    |    M = coef x p x L2    |    R = coef x p x L</t>
         </is>
@@ -10446,7 +14789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10464,7 +14807,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - LOSAS</t>
         </is>
@@ -10474,7 +14817,7 @@
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
         </is>
@@ -10490,17 +14833,17 @@
       <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>MATERIALES Y METODO</t>
         </is>
       </c>
-      <c r="B4" s="44" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -10508,12 +14851,12 @@
       <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="47" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -10524,12 +14867,12 @@
       <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="47" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -10540,12 +14883,12 @@
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Tension admisible del acero</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -10556,12 +14899,12 @@
       <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Brazo elastico  z / h</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -10572,12 +14915,12 @@
       <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -10588,12 +14931,12 @@
       <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Recubrimiento</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="47" t="n">
         <v>1.5</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -10604,12 +14947,12 @@
       <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Separacion maxima</t>
         </is>
       </c>
-      <c r="B11" s="46" t="n">
+      <c r="B11" s="47" t="n">
         <v>20</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -10620,12 +14963,12 @@
       <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Armadura de reparticion</t>
         </is>
       </c>
-      <c r="B12" s="46" t="n">
+      <c r="B12" s="47" t="n">
         <v>0.2</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -10636,12 +14979,12 @@
       <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>Reparticion minima</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n">
+      <c r="B13" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -10658,7 +15001,7 @@
       <c r="D14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>CARGAS POR NIVEL</t>
         </is>
@@ -10680,15 +15023,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B16" s="46" t="n">
+      <c r="B16" s="47" t="n">
         <v>242</v>
       </c>
-      <c r="C16" s="46" t="n">
+      <c r="C16" s="47" t="n">
         <v>200</v>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -10698,15 +15041,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B17" s="46" t="n">
+      <c r="B17" s="47" t="n">
         <v>252</v>
       </c>
-      <c r="C17" s="46" t="n">
+      <c r="C17" s="47" t="n">
         <v>100</v>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -10716,7 +15059,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>El peso propio se suma aparte: 2400 x d / 100</t>
         </is>
@@ -10732,7 +15075,7 @@
       <c r="D19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>GRADO DE EMPOTRAMIENTO</t>
         </is>
@@ -10754,90 +15097,90 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="54" t="inlineStr">
+      <c r="A21" s="55" t="inlineStr">
         <is>
           <t>1/8</t>
         </is>
       </c>
-      <c r="B21" s="51" t="n">
+      <c r="B21" s="52" t="n">
         <v>0.125</v>
       </c>
-      <c r="C21" s="55" t="n">
+      <c r="C21" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="D21" s="56" t="inlineStr">
+      <c r="D21" s="57" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="inlineStr">
+      <c r="A22" s="55" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="B22" s="51" t="n">
+      <c r="B22" s="52" t="n">
         <v>0.1</v>
       </c>
-      <c r="C22" s="55" t="n">
+      <c r="C22" s="56" t="n">
         <v>0.55</v>
       </c>
-      <c r="D22" s="56" t="inlineStr">
+      <c r="D22" s="57" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="54" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>1/12</t>
         </is>
       </c>
-      <c r="B23" s="51" t="n">
+      <c r="B23" s="52" t="n">
         <v>0.0833</v>
       </c>
-      <c r="C23" s="55" t="n">
+      <c r="C23" s="56" t="n">
         <v>0.5</v>
       </c>
-      <c r="D23" s="56" t="inlineStr">
+      <c r="D23" s="57" t="inlineStr">
         <is>
           <t>Biempotrada</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>1/14</t>
         </is>
       </c>
-      <c r="B24" s="51" t="n">
+      <c r="B24" s="52" t="n">
         <v>0.07140000000000001</v>
       </c>
-      <c r="C24" s="55" t="n">
+      <c r="C24" s="56" t="n">
         <v>0.575</v>
       </c>
-      <c r="D24" s="56" t="inlineStr">
+      <c r="D24" s="57" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="B25" s="51" t="n">
+      <c r="B25" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C25" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="56" t="inlineStr">
+      <c r="D25" s="57" t="inlineStr">
         <is>
           <t>Voladizo</t>
         </is>
@@ -10850,7 +15193,7 @@
       <c r="D26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="inlineStr">
+      <c r="A27" s="54" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q   (cargas de servicio)</t>
         </is>
@@ -10860,7 +15203,7 @@
       <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="53" t="inlineStr">
+      <c r="A28" s="54" t="inlineStr">
         <is>
           <t>M = coef x p x L2        R = coef x p x L        As = M x 100 / (2400 x 0,9 x h)        rep. = As / 5</t>
         </is>
@@ -10874,7 +15217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10890,7 +15233,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - COLUMNAS</t>
         </is>
@@ -10904,29 +15247,29 @@
       <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>MATERIALES Y CRITERIOS</t>
         </is>
       </c>
-      <c r="B3" s="44" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C3" s="44" t="inlineStr">
+      <c r="C3" s="45" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B4" s="46" t="n">
+      <c r="B4" s="47" t="n">
         <v>210</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -10936,12 +15279,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n">
+      <c r="B5" s="47" t="n">
         <v>4200</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -10951,12 +15294,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n">
+      <c r="B6" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -10966,12 +15309,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>phi compresion (estribos)</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="47" t="n">
         <v>0.65</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -10981,12 +15324,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Cuantia minima</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.008</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -10996,12 +15339,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Altura PB</t>
         </is>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="47" t="n">
         <v>3.15</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -11011,12 +15354,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Altura PA</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="47" t="n">
         <v>3.22</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -11031,7 +15374,7 @@
       <c r="C11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="53" t="inlineStr">
+      <c r="A12" s="54" t="inlineStr">
         <is>
           <t>As = cuantia minima x area        phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]</t>
         </is>
@@ -11040,7 +15383,7 @@
       <c r="C12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="54" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. longitudinal ; 48 x diam. estribo ; lado menor)</t>
         </is>
@@ -11053,7 +15396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11067,752 +15410,182 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>MEMORIA - ILUMINACION Y VENTILACION</t>
         </is>
       </c>
-      <c r="B1" s="58" t="inlineStr"/>
+      <c r="B1" s="59" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="58" t="inlineStr"/>
-      <c r="B2" s="59" t="inlineStr"/>
+      <c r="A2" s="59" t="inlineStr"/>
+      <c r="B2" s="60" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>CRITERIO</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>Area de iluminacion requerida = superficie del local / 9</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="58" t="inlineStr"/>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr"/>
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>Area de ventilacion requerida = un tercio de la de iluminacion = superficie / 27</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="58" t="inlineStr"/>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr"/>
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>Area proyectada: la vidriada de la carpinteria para iluminacion, y la parte que</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="58" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr"/>
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>realmente abre para ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58" t="inlineStr"/>
-      <c r="B7" s="59" t="inlineStr"/>
+      <c r="A7" s="59" t="inlineStr"/>
+      <c r="B7" s="60" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="59" t="inlineStr">
         <is>
           <t>RESULTADO</t>
         </is>
       </c>
-      <c r="B8" s="58" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Los trece locales cumplen holgadamente iluminacion y ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="58" t="inlineStr"/>
-      <c r="B9" s="59" t="inlineStr"/>
+      <c r="A9" s="59" t="inlineStr"/>
+      <c r="B9" s="60" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="59" t="inlineStr">
         <is>
           <t>CORRECCION</t>
         </is>
       </c>
-      <c r="B10" s="58" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Local 07, Hall / ingreso: la planilla original traia 0,66 y 0,22, que son los</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr"/>
-      <c r="B11" s="59" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr"/>
+      <c r="B11" s="60" t="inlineStr">
         <is>
           <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="58" t="inlineStr"/>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="A12" s="59" t="inlineStr"/>
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="58" t="inlineStr"/>
-      <c r="B13" s="59" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr"/>
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>declarada y un verificador lo puede observar.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr"/>
-      <c r="B14" s="59" t="inlineStr"/>
+      <c r="A14" s="59" t="inlineStr"/>
+      <c r="B14" s="60" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="59" t="inlineStr">
         <is>
           <t>A REVISAR</t>
         </is>
       </c>
-      <c r="B15" s="58" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>Local 14, Estar / Playroom: declara 5,00 m2 de ventilacion sobre 5,00 m2 de</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="58" t="inlineStr"/>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="A16" s="59" t="inlineStr"/>
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>iluminacion, es decir una carpinteria enteramente abrible. En los demas locales</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="58" t="inlineStr"/>
-      <c r="B17" s="59" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr"/>
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>la relacion es del 50 por ciento. Conviene verificar la carpinteria real.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="58" t="inlineStr"/>
-      <c r="B18" s="59" t="inlineStr"/>
+      <c r="A18" s="59" t="inlineStr"/>
+      <c r="B18" s="60" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="58" t="inlineStr"/>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="A19" s="59" t="inlineStr"/>
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Local 02, Deposito: figura sin exigencia por no ser habitable. Son 11,8 m2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="58" t="inlineStr"/>
-      <c r="B20" s="59" t="inlineStr">
+      <c r="A20" s="59" t="inlineStr"/>
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>cerrados: si se lo considera habitable hay que preverle conducto.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="58" t="inlineStr"/>
-      <c r="B21" s="59" t="inlineStr"/>
+      <c r="A21" s="59" t="inlineStr"/>
+      <c r="B21" s="60" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="58" t="inlineStr">
+      <c r="A22" s="59" t="inlineStr">
         <is>
           <t>REDONDEOS</t>
         </is>
       </c>
-      <c r="B22" s="58" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>Diferencias menores que no afectan: local 03 da 5,95 m2 y figura 6,0;</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="58" t="inlineStr"/>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="A23" s="59" t="inlineStr"/>
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>local 09 da 12,25 y figura 12,3.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B66"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="98" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="57" t="inlineStr">
-        <is>
-          <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
-        </is>
-      </c>
-      <c r="B1" s="58" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="58" t="inlineStr"/>
-      <c r="B2" s="59" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="58" t="inlineStr">
-        <is>
-          <t>NORMATIVA</t>
-        </is>
-      </c>
-      <c r="B3" s="58" t="inlineStr">
-        <is>
-          <t>CIRSOC 201. Hormigon H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200 kg/cm2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="58" t="inlineStr">
-        <is>
-          <t>UNIDADES</t>
-        </is>
-      </c>
-      <c r="B4" s="58" t="inlineStr">
-        <is>
-          <t>Longitudes en m y cm. Cargas en kg/m. Momentos en kgm. Tensiones en kg/cm2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="58" t="inlineStr">
-        <is>
-          <t>DIMENSIONES</t>
-        </is>
-      </c>
-      <c r="B5" s="58" t="inlineStr">
-        <is>
-          <t>b = ancho | h = altura util | d = altura total (igual criterio que la planilla de catedra).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="58" t="inlineStr"/>
-      <c r="B6" s="59" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="58" t="inlineStr">
-        <is>
-          <t>1. CARGAS</t>
-        </is>
-      </c>
-      <c r="B7" s="58" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="58" t="inlineStr">
-        <is>
-          <t>Entrepiso PA</t>
-        </is>
-      </c>
-      <c r="B8" s="59" t="inlineStr">
-        <is>
-          <t>Losa maciza 12 cm 300 + contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="58" t="inlineStr"/>
-      <c r="B9" s="59" t="inlineStr">
-        <is>
-          <t>g = 550 kg/m2       q = 200 kg/m2 (vivienda)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="58" t="inlineStr">
-        <is>
-          <t>Azotea</t>
-        </is>
-      </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Losa 300 + contrapiso de pendiente 140 + carpeta 42 + aislacion y membrana 50 + cielorraso 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="58" t="inlineStr"/>
-      <c r="B11" s="59" t="inlineStr">
-        <is>
-          <t>g = 560 kg/m2       q = 100 kg/m2 (cubierta no accesible)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="58" t="inlineStr">
-        <is>
-          <t>Mamposteria</t>
-        </is>
-      </c>
-      <c r="B12" s="59" t="inlineStr">
-        <is>
-          <t>250 kg/m2. Altura 2,60 m en PA y 1,00 m de parapeto en azotea.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="58" t="inlineStr">
-        <is>
-          <t>Peso propio</t>
-        </is>
-      </c>
-      <c r="B13" s="59" t="inlineStr">
-        <is>
-          <t>2400 kg/m3 x b x d, viga por viga.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="58" t="inlineStr">
-        <is>
-          <t>Carga de calculo</t>
-        </is>
-      </c>
-      <c r="B14" s="59" t="inlineStr">
-        <is>
-          <t>p = 1,2 (g x B + peso propio + muro) + 1,6 (q x B)        B = ancho tributario</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="58" t="inlineStr"/>
-      <c r="B15" s="59" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="58" t="inlineStr">
-        <is>
-          <t>2. SOLICITACIONES</t>
-        </is>
-      </c>
-      <c r="B16" s="58" t="inlineStr">
-        <is>
-          <t>Coeficientes segun esquema (tabla en hoja Datos):</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="58" t="inlineStr"/>
-      <c r="B17" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Simplemente apoyada   M = pL2/8                    R = 0,500 pL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="58" t="inlineStr"/>
-      <c r="B18" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Continua              M = pL2/14   Mapoyo = pL2/10  R = 0,575 pL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="58" t="inlineStr"/>
-      <c r="B19" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Empotrada-apoyada     M = 9pL2/128 Mapoyo = pL2/8   R = 0,625 pL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="58" t="inlineStr"/>
-      <c r="B20" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Biempotrada           M = pL2/24   Mapoyo = pL2/12  R = 0,500 pL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="58" t="inlineStr"/>
-      <c r="B21" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Voladizo                           Mapoyo = pL2/2   R = 1,000 pL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="58" t="inlineStr"/>
-      <c r="B22" s="59" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="58" t="inlineStr">
-        <is>
-          <t>3. FLEXION</t>
-        </is>
-      </c>
-      <c r="B23" s="58" t="inlineStr">
-        <is>
-          <t>k = M / (phi b h2 f'c)      w = 1 - RAIZ(1 - 2k)      As = w b h f'c / fy</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="58" t="inlineStr"/>
-      <c r="B24" s="59" t="inlineStr">
-        <is>
-          <t>As min = 0,0033 b h       As max = 0,0163 b h (0,75 de la cuantia balanceada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="58" t="inlineStr"/>
-      <c r="B25" s="59" t="inlineStr">
-        <is>
-          <t>Si la armadura no entra en una capa se disponen dos y el recubrimiento pasa a 6 cm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="58" t="inlineStr"/>
-      <c r="B26" s="59" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="58" t="inlineStr">
-        <is>
-          <t>4. CORTE</t>
-        </is>
-      </c>
-      <c r="B27" s="58" t="inlineStr">
-        <is>
-          <t>T = R / (b x 0,85 h)       tension tangencial en el apoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="58" t="inlineStr"/>
-      <c r="B28" s="59" t="inlineStr">
-        <is>
-          <t>Vc = 0,53 RAIZ(f'c) b h        phi Vn = 0,75 (Vc + Av fy h / s)  &gt;=  R</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="58" t="inlineStr"/>
-      <c r="B29" s="59" t="inlineStr">
-        <is>
-          <t>Av = 2 ramas. Se aumenta el diametro antes que cerrar la separacion por debajo de 10 cm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="58" t="inlineStr"/>
-      <c r="B30" s="59" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="58" t="inlineStr">
-        <is>
-          <t>5. FLECHA</t>
-        </is>
-      </c>
-      <c r="B31" s="58" t="inlineStr">
-        <is>
-          <t>Altura minima: simplemente apoyada L/16, un extremo continuo L/18,5,</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="58" t="inlineStr"/>
-      <c r="B32" s="59" t="inlineStr">
-        <is>
-          <t>ambos extremos continuos L/21, voladizo L/8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="58" t="inlineStr"/>
-      <c r="B33" s="59" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="58" t="inlineStr">
-        <is>
-          <t>6. VIGAS INVERTIDAS</t>
-        </is>
-      </c>
-      <c r="B34" s="58" t="inlineStr">
-        <is>
-          <t>Las vigas de BORDE son invertidas: sobresalen 70 cm por encima del fondo de</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="58" t="inlineStr"/>
-      <c r="B35" s="59" t="inlineStr">
-        <is>
-          <t>losa (cotas N.F.L +3,50 / N.S.V +4,20 y N.F.L +6,80 / N.S.V +7,50 del plano).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="58" t="inlineStr"/>
-      <c r="B36" s="59" t="inlineStr">
-        <is>
-          <t>Son VI 01a, VI 01b, VI 07a, VI 07b, VI 07c, VI 11a, VI 11b, VI 11c, VI 15a y VI 15b,</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="58" t="inlineStr"/>
-      <c r="B37" s="59" t="inlineStr">
-        <is>
-          <t>identificadas por coincidir su eje con el contorno del edificio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="58" t="inlineStr"/>
-      <c r="B38" s="59" t="inlineStr">
-        <is>
-          <t>Esto define donde la losa aporta ala comprimida:</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="58" t="inlineStr"/>
-      <c r="B39" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="58" t="inlineStr"/>
-      <c r="B40" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="58" t="inlineStr"/>
-      <c r="B41" s="59" t="inlineStr">
-        <is>
-          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="58" t="inlineStr"/>
-      <c r="B42" s="59" t="inlineStr">
-        <is>
-          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="58" t="inlineStr"/>
-      <c r="B43" s="59" t="inlineStr">
-        <is>
-          <t>PENDIENTE: una viga invertida de borde recibe la reaccion de la losa excentrica</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="58" t="inlineStr"/>
-      <c r="B44" s="59" t="inlineStr">
-        <is>
-          <t>respecto de su eje y queda sometida a TORSION. Esta planilla no la verifica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="58" t="inlineStr"/>
-      <c r="B45" s="59" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="58" t="inlineStr">
-        <is>
-          <t>7. RESULTADO</t>
-        </is>
-      </c>
-      <c r="B46" s="58" t="inlineStr">
-        <is>
-          <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="58" t="inlineStr"/>
-      <c r="B47" s="59" t="inlineStr">
-        <is>
-          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="58" t="inlineStr"/>
-      <c r="B48" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="58" t="inlineStr"/>
-      <c r="B49" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="58" t="inlineStr"/>
-      <c r="B50" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="58" t="inlineStr"/>
-      <c r="B51" s="59" t="inlineStr">
-        <is>
-          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="58" t="inlineStr"/>
-      <c r="B52" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="58" t="inlineStr"/>
-      <c r="B53" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="58" t="inlineStr"/>
-      <c r="B54" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="58" t="inlineStr"/>
-      <c r="B55" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="58" t="inlineStr"/>
-      <c r="B56" s="59" t="inlineStr">
-        <is>
-          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="58" t="inlineStr"/>
-      <c r="B57" s="59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="58" t="inlineStr"/>
-      <c r="B58" s="59" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="58" t="inlineStr">
-        <is>
-          <t>8. ALCANCE</t>
-        </is>
-      </c>
-      <c r="B59" s="59" t="inlineStr">
-        <is>
-          <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="58" t="inlineStr"/>
-      <c r="B60" s="59" t="inlineStr">
-        <is>
-          <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="58" t="inlineStr"/>
-      <c r="B61" s="59" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="58" t="inlineStr">
-        <is>
-          <t>LIMITACIONES</t>
-        </is>
-      </c>
-      <c r="B62" s="58" t="inlineStr">
-        <is>
-          <t>El ancho tributario B esta relevado solo en</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="58" t="inlineStr"/>
-      <c r="B63" s="59" t="inlineStr">
-        <is>
-          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="58" t="inlineStr"/>
-      <c r="B64" s="59" t="inlineStr">
-        <is>
-          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="58" t="inlineStr"/>
-      <c r="B65" s="59" t="inlineStr">
-        <is>
-          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="58" t="inlineStr"/>
-      <c r="B66" s="59" t="inlineStr">
-        <is>
-          <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
       </c>
     </row>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
@@ -11882,7 +11882,11 @@
         <f>IF(OR(M7="REVISAR",P7="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M7&lt;&gt;"REVISAR",P7&lt;&gt;"REVISAR",IF(ISNUMBER(M7),N7*PI()*(O7/10)^2/4&gt;=M7,TRUE),IF(ISNUMBER(P7),Q7*PI()*(R7/10)^2/4&gt;=P7,TRUE),IF(ISNUMBER(M7),M7&lt;=0.0163*J7*K7,TRUE),IF(ISNUMBER(P7),P7&lt;=0.0163*J7*K7,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F7&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J7*K7+2*PI()*(U7/10)^2/4*Datos_vigas!$B$6*K7/V7)),"NO VERIF. CORTE","VERIFICA")))</f>
         <v/>
       </c>
-      <c r="X7" s="11" t="n"/>
+      <c r="X7" s="13" t="inlineStr">
+        <is>
+          <t>Longitud total 3.28 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
+        </is>
+      </c>
       <c r="Y7" s="12" t="n">
         <v>3.15</v>
       </c>
@@ -11897,7 +11901,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>9.279999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
@@ -11940,20 +11944,20 @@
         <v/>
       </c>
       <c r="N8" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P8" s="25">
         <f>IF(NOT(ISNUMBER(I8)),"---",IF(I8&lt;=0,"---",IF(I8*100/(Datos_vigas!$B$8*J8*K8^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I8*100/(Datos_vigas!$B$8*J8*K8^2*Datos_vigas!$B$5)))*J8*K8*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J8*K8))))</f>
         <v/>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S8" s="25">
         <f>F8/(J8*0.85*K8)</f>
@@ -11964,10 +11968,10 @@
         <v/>
       </c>
       <c r="U8" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W8" s="11">
         <f>IF(OR(M8="REVISAR",P8="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M8&lt;&gt;"REVISAR",P8&lt;&gt;"REVISAR",IF(ISNUMBER(M8),N8*PI()*(O8/10)^2/4&gt;=M8,TRUE),IF(ISNUMBER(P8),Q8*PI()*(R8/10)^2/4&gt;=P8,TRUE),IF(ISNUMBER(M8),M8&lt;=0.0163*J8*K8,TRUE),IF(ISNUMBER(P8),P8&lt;=0.0163*J8*K8,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F8&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J8*K8+2*PI()*(U8/10)^2/4*Datos_vigas!$B$6*K8/V8)),"NO VERIF. CORTE","VERIFICA")))</f>
@@ -11975,14 +11979,14 @@
       </c>
       <c r="X8" s="13" t="inlineStr">
         <is>
-          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+          <t>Longitud total 9.28 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano. No se detectaron pilotes intermedios en este tramo. Verificar: puede estar apoyada directamente sobre el terreno, en cuyo caso no flexiona como viga de luz libre. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
         </is>
       </c>
       <c r="Y8" s="12" t="n">
         <v>3.15</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
@@ -11992,7 +11996,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>5.33</v>
+        <v>3.8</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
@@ -12045,10 +12049,10 @@
         <v/>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S9" s="25">
         <f>F9/(J9*0.85*K9)</f>
@@ -12070,7 +12074,7 @@
       </c>
       <c r="X9" s="13" t="inlineStr">
         <is>
-          <t>El ancho quedo cortado en el PDF: se adopta 20 cm. Confirmar si es 20 o 22.</t>
+          <t>El ancho quedo cortado en el PDF: se adopta 20 cm. Confirmar si es 20 o 22. Longitud total 5.33 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
         </is>
       </c>
       <c r="Y9" s="12" t="n">
@@ -12737,7 +12741,7 @@
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>3.5</v>
+        <v>2.04</v>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
@@ -12817,7 +12821,11 @@
         <f>IF(OR(M18="REVISAR",P18="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M18&lt;&gt;"REVISAR",P18&lt;&gt;"REVISAR",IF(ISNUMBER(M18),N18*PI()*(O18/10)^2/4&gt;=M18,TRUE),IF(ISNUMBER(P18),Q18*PI()*(R18/10)^2/4&gt;=P18,TRUE),IF(ISNUMBER(M18),M18&lt;=0.0163*J18*K18,TRUE),IF(ISNUMBER(P18),P18&lt;=0.0163*J18*K18,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F18&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J18*K18+2*PI()*(U18/10)^2/4*Datos_vigas!$B$6*K18/V18)),"NO VERIF. CORTE","VERIFICA")))</f>
         <v/>
       </c>
-      <c r="X18" s="11" t="n"/>
+      <c r="X18" s="13" t="inlineStr">
+        <is>
+          <t>Longitud total 3.50 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
+        </is>
+      </c>
       <c r="Y18" s="12" t="n">
         <v>3.15</v>
       </c>
@@ -13014,7 +13022,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>3.36</v>
+        <v>2.74</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
@@ -13090,7 +13098,11 @@
         <f>IF(OR(M21="REVISAR",P21="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M21&lt;&gt;"REVISAR",P21&lt;&gt;"REVISAR",IF(ISNUMBER(M21),N21*PI()*(O21/10)^2/4&gt;=M21,TRUE),IF(ISNUMBER(P21),Q21*PI()*(R21/10)^2/4&gt;=P21,TRUE),IF(ISNUMBER(M21),M21&lt;=0.0163*J21*K21,TRUE),IF(ISNUMBER(P21),P21&lt;=0.0163*J21*K21,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F21&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J21*K21+2*PI()*(U21/10)^2/4*Datos_vigas!$B$6*K21/V21)),"NO VERIF. CORTE","VERIFICA")))</f>
         <v/>
       </c>
-      <c r="X21" s="11" t="n"/>
+      <c r="X21" s="13" t="inlineStr">
+        <is>
+          <t>Longitud total 3.36 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
+        </is>
+      </c>
       <c r="Y21" s="12" t="n">
         <v>3.15</v>
       </c>
@@ -13196,7 +13208,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>8.029999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
@@ -13239,20 +13251,20 @@
         <v/>
       </c>
       <c r="N23" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P23" s="25">
         <f>IF(NOT(ISNUMBER(I23)),"---",IF(I23&lt;=0,"---",IF(I23*100/(Datos_vigas!$B$8*J23*K23^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I23*100/(Datos_vigas!$B$8*J23*K23^2*Datos_vigas!$B$5)))*J23*K23*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J23*K23))))</f>
         <v/>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S23" s="25">
         <f>F23/(J23*0.85*K23)</f>
@@ -13274,7 +13286,7 @@
       </c>
       <c r="X23" s="13" t="inlineStr">
         <is>
-          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+          <t>Longitud total 8.03 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
         </is>
       </c>
       <c r="Y23" s="12" t="n">
@@ -13533,11 +13545,11 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>8.75</v>
+        <v>3.09</v>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Simplemente apoyada</t>
         </is>
       </c>
       <c r="D27" s="24">
@@ -13576,20 +13588,24 @@
         <v/>
       </c>
       <c r="N27" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P27" s="25">
         <f>IF(NOT(ISNUMBER(I27)),"---",IF(I27&lt;=0,"---",IF(I27*100/(Datos_vigas!$B$8*J27*K27^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I27*100/(Datos_vigas!$B$8*J27*K27^2*Datos_vigas!$B$5)))*J27*K27*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J27*K27))))</f>
         <v/>
       </c>
-      <c r="Q27" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" s="10" t="n">
-        <v>16</v>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
       </c>
       <c r="S27" s="25">
         <f>F27/(J27*0.85*K27)</f>
@@ -13611,7 +13627,7 @@
       </c>
       <c r="X27" s="13" t="inlineStr">
         <is>
-          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+          <t>Longitud total 8.75 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
         </is>
       </c>
       <c r="Y27" s="12" t="n">
@@ -13723,7 +13739,7 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>6.96</v>
+        <v>4.47</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -13769,17 +13785,17 @@
         <v>2</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P29" s="25">
         <f>IF(NOT(ISNUMBER(I29)),"---",IF(I29&lt;=0,"---",IF(I29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)))*J29*K29*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J29*K29))))</f>
         <v/>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="S29" s="25">
         <f>F29/(J29*0.85*K29)</f>
@@ -13801,7 +13817,7 @@
       </c>
       <c r="X29" s="13" t="inlineStr">
         <is>
-          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ.</t>
+          <t>Longitud total 6.96 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
         </is>
       </c>
       <c r="Y29" s="12" t="n">
@@ -14004,7 +14020,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>7.48</v>
+        <v>5.5</v>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
@@ -14047,20 +14063,20 @@
         <v/>
       </c>
       <c r="N32" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P32" s="25">
         <f>IF(NOT(ISNUMBER(I32)),"---",IF(I32&lt;=0,"---",IF(I32*100/(Datos_vigas!$B$8*J32*K32^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I32*100/(Datos_vigas!$B$8*J32*K32^2*Datos_vigas!$B$5)))*J32*K32*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J32*K32))))</f>
         <v/>
       </c>
       <c r="Q32" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R32" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S32" s="25">
         <f>F32/(J32*0.85*K32)</f>
@@ -14082,7 +14098,7 @@
       </c>
       <c r="X32" s="13" t="inlineStr">
         <is>
-          <t>Luz tomada como la longitud total rotulada. Si hay pilotes intermedios la luz de calculo es menor y los esfuerzos bajan mucho: corregir la columna LUZ. Relacion luz/altura alta. En una viga de fundacion enterrada la flecha no suele gobernar, por eso no se la incluye en la verificacion.</t>
+          <t>Longitud total 7.48 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
         </is>
       </c>
       <c r="Y32" s="12" t="n">
@@ -14190,7 +14206,7 @@
         </is>
       </c>
       <c r="B34" s="15" t="n">
-        <v>4.82</v>
+        <v>4.26</v>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
@@ -14243,10 +14259,10 @@
         <v/>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R34" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S34" s="30">
         <f>F34/(J34*0.85*K34)</f>
@@ -14266,7 +14282,11 @@
         <f>IF(OR(M34="REVISAR",P34="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M34&lt;&gt;"REVISAR",P34&lt;&gt;"REVISAR",IF(ISNUMBER(M34),N34*PI()*(O34/10)^2/4&gt;=M34,TRUE),IF(ISNUMBER(P34),Q34*PI()*(R34/10)^2/4&gt;=P34,TRUE),IF(ISNUMBER(M34),M34&lt;=0.0163*J34*K34,TRUE),IF(ISNUMBER(P34),P34&lt;=0.0163*J34*K34,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F34&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J34*K34+2*PI()*(U34/10)^2/4*Datos_vigas!$B$6*K34/V34)),"NO VERIF. CORTE","VERIFICA")))</f>
         <v/>
       </c>
-      <c r="X34" s="18" t="n"/>
+      <c r="X34" s="20" t="inlineStr">
+        <is>
+          <t>Longitud total 4.82 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
+        </is>
+      </c>
       <c r="Y34" s="19" t="n">
         <v>3.15</v>
       </c>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -12,14 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilla losas" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilla columnas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vigas de fundacion" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_vigas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_losas" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_columnas" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria ilum. y vent." sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria vigas" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria losas" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria columnas" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundacion (inventario)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilotes y cabezales" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_vigas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_losas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_columnas" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_pilotes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria ilum. y vent." sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria vigas" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria losas" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria columnas" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundacion (inventario)" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
@@ -31,6 +33,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Planilla columnas'!$A$1:$N$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Vigas de fundacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Vigas de fundacion'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Pilotes y cabezales'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -248,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -365,6 +368,7 @@
     <xf numFmtId="2" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -389,7 +393,6 @@
     <xf numFmtId="165" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -397,6 +400,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3374,6 +3378,506 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>DATOS DE PARTIDA - PILOTES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="45" t="inlineStr">
+        <is>
+          <t>PARAMETRO</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="C3" s="46" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+      <c r="D3" s="45" t="inlineStr">
+        <is>
+          <t>origen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="47" t="inlineStr">
+        <is>
+          <t>Carga admisible por pilote</t>
+        </is>
+      </c>
+      <c r="B4" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>ESTIMADA. Falta el estudio de suelos: cambiar aca y recalcula todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>Tension admisible del terreno</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>kg/cm2</t>
+        </is>
+      </c>
+      <c r="D5" s="52" t="inlineStr">
+        <is>
+          <t>Dato real, tomado del encabezado del calculo de bases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>Diametro del pilote</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>Nota del plano: todos los pilotes son O30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>Profundidad</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>Nota del plano: h = -4,50 m desde la cota +-0,00 de vereda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>Coef. de mayoracion adoptado</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>Para pasar de carga mayorada a carga de servicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="58" t="inlineStr">
+        <is>
+          <t>COMO SE ESTIMO LA CARGA ADMISIBLE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>Pilote O30 de 4,50 m: area de punta 0,0707 m2, area lateral 4,24 m2.</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>Punta  0,0707 x 20 t/m2 = 1,4 t.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>Friccion lateral  4,24 x adherencia:  1,5 t/m2 -&gt; 6,4 t   |   3,0 t/m2 -&gt; 12,7 t.</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>Total segun adherencia: entre 7,8 y 14,1 t. Se adopta 12 t como valor de trabajo.</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>LECTURA INVERSA, que es la util mientras no haya estudio de suelos:</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>con las cargas de esta planilla, para que el esquema funcione cada pilote</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>tiene que admitir del orden de 20 t. Si el estudio de suelos da menos,</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>faltan pilotes; si da mas, el diseno esta holgado.</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="59" t="inlineStr">
+        <is>
+          <t>MEMORIA - ILUMINACION Y VENTILACION</t>
+        </is>
+      </c>
+      <c r="B1" s="60" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="60" t="inlineStr">
+        <is>
+          <t>CRITERIO</t>
+        </is>
+      </c>
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t>Area de iluminacion requerida = superficie del local / 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="60" t="inlineStr"/>
+      <c r="B4" s="61" t="inlineStr">
+        <is>
+          <t>Area de ventilacion requerida = un tercio de la de iluminacion = superficie / 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr"/>
+      <c r="B5" s="61" t="inlineStr">
+        <is>
+          <t>Area proyectada: la vidriada de la carpinteria para iluminacion, y la parte que</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr">
+        <is>
+          <t>realmente abre para ventilacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="60" t="inlineStr"/>
+      <c r="B7" s="61" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>RESULTADO</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>Los trece locales cumplen holgadamente iluminacion y ventilacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>CORRECCION</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Local 07, Hall / ingreso: la planilla original traia 0,66 y 0,22, que son los</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr">
+        <is>
+          <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="inlineStr"/>
+      <c r="B12" s="61" t="inlineStr">
+        <is>
+          <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="inlineStr"/>
+      <c r="B13" s="61" t="inlineStr">
+        <is>
+          <t>declarada y un verificador lo puede observar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="60" t="inlineStr"/>
+      <c r="B14" s="61" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>A REVISAR</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t>Local 14, Estar / Playroom: declara 5,00 m2 de ventilacion sobre 5,00 m2 de</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="60" t="inlineStr"/>
+      <c r="B16" s="61" t="inlineStr">
+        <is>
+          <t>iluminacion, es decir una carpinteria enteramente abrible. En los demas locales</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
+        <is>
+          <t>la relacion es del 50 por ciento. Conviene verificar la carpinteria real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="60" t="inlineStr"/>
+      <c r="B19" s="61" t="inlineStr">
+        <is>
+          <t>Local 02, Deposito: figura sin exigencia por no ser habitable. Son 11,8 m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr">
+        <is>
+          <t>cerrados: si se lo considera habitable hay que preverle conducto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="60" t="inlineStr"/>
+      <c r="B21" s="61" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="60" t="inlineStr">
+        <is>
+          <t>REDONDEOS</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>Diferencias menores que no afectan: local 03 da 5,95 m2 y figura 6,0;</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="60" t="inlineStr"/>
+      <c r="B23" s="61" t="inlineStr">
+        <is>
+          <t>local 09 da 12,25 y figura 12,3.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3382,552 +3886,552 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr"/>
+      <c r="B1" s="60" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="59" t="inlineStr"/>
-      <c r="B2" s="60" t="inlineStr"/>
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>NORMATIVA</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>CIRSOC 201. Hormigon H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200 kg/cm2).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>UNIDADES</t>
         </is>
       </c>
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>Longitudes en m y cm. Cargas en kg/m. Momentos en kgm. Tensiones en kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>b = ancho | h = altura util | d = altura total (igual criterio que la planilla de catedra).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="60" t="inlineStr"/>
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="59" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B7" s="59" t="inlineStr"/>
+      <c r="B7" s="60" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>Entrepiso PA</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>Losa maciza 12 cm 300 + contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="59" t="inlineStr"/>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>g = 550 kg/m2       q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>Azotea</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Losa 300 + contrapiso de pendiente 140 + carpeta 42 + aislacion y membrana 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr"/>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>g = 560 kg/m2       q = 100 kg/m2 (cubierta no accesible)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>Mamposteria</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>250 kg/m2. Altura 2,60 m en PA y 1,00 m de parapeto en azotea.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="59" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>Peso propio</t>
         </is>
       </c>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>2400 kg/m3 x b x d, viga por viga.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="59" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>Carga de calculo</t>
         </is>
       </c>
-      <c r="B14" s="60" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>p = 1,2 (g x B + peso propio + muro) + 1,6 (q x B)        B = ancho tributario</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="59" t="inlineStr"/>
-      <c r="B15" s="60" t="inlineStr"/>
+      <c r="A15" s="60" t="inlineStr"/>
+      <c r="B15" s="61" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="59" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B16" s="59" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>Coeficientes segun esquema (tabla en hoja Datos):</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="59" t="inlineStr"/>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Simplemente apoyada   M = pL2/8                    R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="inlineStr"/>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Continua              M = pL2/14   Mapoyo = pL2/10  R = 0,575 pL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="59" t="inlineStr"/>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr"/>
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Empotrada-apoyada     M = 9pL2/128 Mapoyo = pL2/8   R = 0,625 pL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="59" t="inlineStr"/>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Biempotrada           M = pL2/24   Mapoyo = pL2/12  R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="59" t="inlineStr"/>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr"/>
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Voladizo                           Mapoyo = pL2/2   R = 1,000 pL</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="59" t="inlineStr"/>
-      <c r="B22" s="60" t="inlineStr"/>
+      <c r="A22" s="60" t="inlineStr"/>
+      <c r="B22" s="61" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="59" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>3. FLEXION</t>
         </is>
       </c>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>k = M / (phi b h2 f'c)      w = 1 - RAIZ(1 - 2k)      As = w b h f'c / fy</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="59" t="inlineStr"/>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr"/>
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>As min = 0,0033 b h       As max = 0,0163 b h (0,75 de la cuantia balanceada)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="59" t="inlineStr"/>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr"/>
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>Si la armadura no entra en una capa se disponen dos y el recubrimiento pasa a 6 cm.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="59" t="inlineStr"/>
-      <c r="B26" s="60" t="inlineStr"/>
+      <c r="A26" s="60" t="inlineStr"/>
+      <c r="B26" s="61" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>4. CORTE</t>
         </is>
       </c>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>T = R / (b x 0,85 h)       tension tangencial en el apoyo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="59" t="inlineStr"/>
-      <c r="B28" s="60" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr"/>
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>Vc = 0,53 RAIZ(f'c) b h        phi Vn = 0,75 (Vc + Av fy h / s)  &gt;=  R</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="59" t="inlineStr"/>
-      <c r="B29" s="60" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr"/>
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>Av = 2 ramas. Se aumenta el diametro antes que cerrar la separacion por debajo de 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="59" t="inlineStr"/>
-      <c r="B30" s="60" t="inlineStr"/>
+      <c r="A30" s="60" t="inlineStr"/>
+      <c r="B30" s="61" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="59" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>5. FLECHA</t>
         </is>
       </c>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>Altura minima: simplemente apoyada L/16, un extremo continuo L/18,5,</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="59" t="inlineStr"/>
-      <c r="B32" s="60" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr"/>
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>ambos extremos continuos L/21, voladizo L/8.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="59" t="inlineStr"/>
-      <c r="B33" s="60" t="inlineStr"/>
+      <c r="A33" s="60" t="inlineStr"/>
+      <c r="B33" s="61" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="59" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>6. VIGAS INVERTIDAS</t>
         </is>
       </c>
-      <c r="B34" s="59" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t>Las vigas de BORDE son invertidas: sobresalen 70 cm por encima del fondo de</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="59" t="inlineStr"/>
-      <c r="B35" s="60" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr"/>
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>losa (cotas N.F.L +3,50 / N.S.V +4,20 y N.F.L +6,80 / N.S.V +7,50 del plano).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="59" t="inlineStr"/>
-      <c r="B36" s="60" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr"/>
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>Son VI 01a, VI 01b, VI 07a, VI 07b, VI 07c, VI 11a, VI 11b, VI 11c, VI 15a y VI 15b,</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="59" t="inlineStr"/>
-      <c r="B37" s="60" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr"/>
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>identificadas por coincidir su eje con el contorno del edificio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="59" t="inlineStr"/>
-      <c r="B38" s="60" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr"/>
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="59" t="inlineStr"/>
-      <c r="B39" s="60" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr"/>
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="59" t="inlineStr"/>
-      <c r="B40" s="60" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr"/>
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="59" t="inlineStr"/>
-      <c r="B41" s="60" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr"/>
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="59" t="inlineStr"/>
-      <c r="B42" s="60" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr"/>
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="59" t="inlineStr"/>
-      <c r="B43" s="60" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr"/>
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>PENDIENTE: una viga invertida de borde recibe la reaccion de la losa excentrica</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="59" t="inlineStr"/>
-      <c r="B44" s="60" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr"/>
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>respecto de su eje y queda sometida a TORSION. Esta planilla no la verifica.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="59" t="inlineStr"/>
-      <c r="B45" s="60" t="inlineStr"/>
+      <c r="A45" s="60" t="inlineStr"/>
+      <c r="B45" s="61" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="59" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>7. RESULTADO</t>
         </is>
       </c>
-      <c r="B46" s="59" t="inlineStr">
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="59" t="inlineStr"/>
-      <c r="B47" s="60" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr"/>
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="59" t="inlineStr"/>
-      <c r="B48" s="60" t="inlineStr">
+      <c r="A48" s="60" t="inlineStr"/>
+      <c r="B48" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="59" t="inlineStr"/>
-      <c r="B49" s="60" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr"/>
+      <c r="B49" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="59" t="inlineStr"/>
-      <c r="B50" s="60" t="inlineStr">
+      <c r="A50" s="60" t="inlineStr"/>
+      <c r="B50" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="59" t="inlineStr"/>
-      <c r="B51" s="60" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr"/>
+      <c r="B51" s="61" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="59" t="inlineStr"/>
-      <c r="B52" s="60" t="inlineStr">
+      <c r="A52" s="60" t="inlineStr"/>
+      <c r="B52" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="59" t="inlineStr"/>
-      <c r="B53" s="60" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr"/>
+      <c r="B53" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="59" t="inlineStr"/>
-      <c r="B54" s="60" t="inlineStr">
+      <c r="A54" s="60" t="inlineStr"/>
+      <c r="B54" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="59" t="inlineStr"/>
-      <c r="B55" s="60" t="inlineStr">
+      <c r="A55" s="60" t="inlineStr"/>
+      <c r="B55" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="59" t="inlineStr"/>
-      <c r="B56" s="60" t="inlineStr">
+      <c r="A56" s="60" t="inlineStr"/>
+      <c r="B56" s="61" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="59" t="inlineStr"/>
-      <c r="B57" s="60" t="inlineStr">
+      <c r="A57" s="60" t="inlineStr"/>
+      <c r="B57" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="59" t="inlineStr"/>
-      <c r="B58" s="60" t="inlineStr"/>
+      <c r="A58" s="60" t="inlineStr"/>
+      <c r="B58" s="61" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="59" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr">
         <is>
           <t>8. ALCANCE</t>
         </is>
       </c>
-      <c r="B59" s="60" t="inlineStr">
+      <c r="B59" s="61" t="inlineStr">
         <is>
           <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="59" t="inlineStr"/>
-      <c r="B60" s="60" t="inlineStr">
+      <c r="A60" s="60" t="inlineStr"/>
+      <c r="B60" s="61" t="inlineStr">
         <is>
           <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="59" t="inlineStr"/>
-      <c r="B61" s="60" t="inlineStr"/>
+      <c r="A61" s="60" t="inlineStr"/>
+      <c r="B61" s="61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="59" t="inlineStr">
+      <c r="A62" s="60" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B62" s="59" t="inlineStr">
+      <c r="B62" s="60" t="inlineStr">
         <is>
           <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="59" t="inlineStr"/>
-      <c r="B63" s="60" t="inlineStr">
+      <c r="A63" s="60" t="inlineStr"/>
+      <c r="B63" s="61" t="inlineStr">
         <is>
           <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="59" t="inlineStr"/>
-      <c r="B64" s="60" t="inlineStr">
+      <c r="A64" s="60" t="inlineStr"/>
+      <c r="B64" s="61" t="inlineStr">
         <is>
           <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="59" t="inlineStr"/>
-      <c r="B65" s="60" t="inlineStr">
+      <c r="A65" s="60" t="inlineStr"/>
+      <c r="B65" s="61" t="inlineStr">
         <is>
           <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="59" t="inlineStr"/>
-      <c r="B66" s="60" t="inlineStr">
+      <c r="A66" s="60" t="inlineStr"/>
+      <c r="B66" s="61" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -3938,7 +4442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3952,368 +4456,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - LOSAS</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr"/>
+      <c r="B1" s="60" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="59" t="inlineStr"/>
-      <c r="B2" s="60" t="inlineStr"/>
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>METODO</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>Tensiones admisibles, igual criterio que la planilla modelo de la catedra.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="inlineStr"/>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr"/>
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>Se verifico contra la fila de ejemplo: momentos y reacciones coinciden exactamente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). Tension admisible 2400 kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B6" s="59" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>h = altura util | d = espesor total. Recubrimiento 1,5 cm.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="59" t="inlineStr"/>
-      <c r="B7" s="60" t="inlineStr"/>
+      <c r="A7" s="60" t="inlineStr"/>
+      <c r="B7" s="61" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B8" s="59" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q      (cargas de servicio, sin mayorar)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="59" t="inlineStr"/>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>Peso propio = 2400 x d / 100, calculado con el espesor propio de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Terminaciones 242 kg/m2 (contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr"/>
-      <c r="B11" s="60" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>Terminaciones 252 kg/m2 (contrapiso pendiente 140 + carpeta 42 + aislacion 50 +</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="59" t="inlineStr"/>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr"/>
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>cielorraso 20).  q = 100 kg/m2 (azotea no accesible)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="59" t="inlineStr"/>
-      <c r="B14" s="60" t="inlineStr"/>
+      <c r="A14" s="60" t="inlineStr"/>
+      <c r="B14" s="61" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>M = coeficiente x p x L2, segun el grado de empotramiento:</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="59" t="inlineStr"/>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr"/>
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  1/8 simplemente apoyada    1/10 y 1/14 continua    1/12 biempotrada    1/2 voladizo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="59" t="inlineStr"/>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>R = coeficiente x p x L. En voladizo Rx = p x L y Ry no corresponde.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="inlineStr"/>
-      <c r="B18" s="60" t="inlineStr"/>
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="59" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B19" s="59" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>As = M x 100 / (2400 x 0,9 x h)        [cm2/m]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="59" t="inlineStr"/>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>separacion = 100 x area de la barra / As, redondeada, con maximo 20 cm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="59" t="inlineStr"/>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr"/>
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>Armadura de reparticion = As / 5, con un minimo de 0,30 cm2/m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="59" t="inlineStr"/>
-      <c r="B22" s="60" t="inlineStr"/>
+      <c r="A22" s="60" t="inlineStr"/>
+      <c r="B22" s="61" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="59" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>4. ESPESORES</t>
         </is>
       </c>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>Los espesores d se leyeron del plano: estan escritos debajo del rotulo de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="59" t="inlineStr"/>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr"/>
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>S/PB:  L01 11 | L02 9 | L03 13 | L04 11 | L05 11 | L06 8 | L07 12 | L08 10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="59" t="inlineStr"/>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr"/>
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>S/PA:  L09 13 | L10 12</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="59" t="inlineStr"/>
-      <c r="B26" s="60" t="inlineStr"/>
+      <c r="A26" s="60" t="inlineStr"/>
+      <c r="B26" s="61" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>5. LUCES</t>
         </is>
       </c>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>Relevadas en obra y aportadas por el proyectista. Dos losas son voladizo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="59" t="inlineStr"/>
-      <c r="B28" s="60" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr"/>
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>(L02 de 0,80 m y L08 de 0,75 m) y se calculan con M = p L2 / 2.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="59" t="inlineStr"/>
-      <c r="B29" s="60" t="inlineStr"/>
+      <c r="A29" s="60" t="inlineStr"/>
+      <c r="B29" s="61" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="59" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>6. LOSAS CRUZADAS</t>
         </is>
       </c>
-      <c r="B30" s="60" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>L07 (4,85 x 5,60) y L10 (4,85 x 6,00) apoyan en los cuatro bordes y su relacion</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="59" t="inlineStr"/>
-      <c r="B31" s="60" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr"/>
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>de lados es menor que 2, por lo que trabajan en las dos direcciones.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="59" t="inlineStr"/>
-      <c r="B32" s="60" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr"/>
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>Se reparte la carga por el metodo de Marcus:   kx = ly4 / (lx4 + ly4)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="59" t="inlineStr"/>
-      <c r="B33" s="60" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr"/>
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  L07: ly/lx = 1,15  -&gt;  64% en la direccion corta, 36% en la larga</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="59" t="inlineStr"/>
-      <c r="B34" s="60" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr"/>
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  L10: ly/lx = 1,24  -&gt;  70% en la direccion corta, 30% en la larga</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="59" t="inlineStr"/>
-      <c r="B35" s="60" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr"/>
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>Cada una ocupa dos renglones, uno por direccion, con la fraccion de carga que</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="59" t="inlineStr"/>
-      <c r="B36" s="60" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr"/>
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>le toca ya aplicada en la columna CARGAS. Las dos armaduras se cruzan en obra:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="59" t="inlineStr"/>
-      <c r="B37" s="60" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr"/>
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>la de la direccion corta va abajo, la de la larga arriba de aquella.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="59" t="inlineStr"/>
-      <c r="B38" s="60" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr"/>
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>La columna auxiliar luz transv. es la que dispara el reparto: si se borra, la</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="59" t="inlineStr"/>
-      <c r="B39" s="60" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr"/>
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>fila vuelve a calcularse como losa armada en una direccion.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="59" t="inlineStr"/>
-      <c r="B40" s="60" t="inlineStr"/>
+      <c r="A40" s="60" t="inlineStr"/>
+      <c r="B40" s="61" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="59" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B41" s="59" t="inlineStr">
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t>El grado de empotramiento esta cargado en 1/8 salvo los dos voladizos (1/2). Si</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="59" t="inlineStr"/>
-      <c r="B42" s="60" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr"/>
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>alguna losa es continua sobre una viga corresponde 1/10 o 1/14: corregir en la columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="59" t="inlineStr"/>
-      <c r="B43" s="60" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr"/>
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>El diagrama de cargas es una imagen fija: si cambias el grado, cambialo a mano.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="59" t="inlineStr"/>
-      <c r="B44" s="60" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr"/>
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -4324,7 +4828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4338,368 +4842,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - COLUMNAS</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr"/>
+      <c r="B1" s="60" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="59" t="inlineStr"/>
-      <c r="B2" s="60" t="inlineStr"/>
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B3" s="59" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). phi compresion 0,65.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="59" t="inlineStr"/>
-      <c r="B4" s="60" t="inlineStr"/>
+      <c r="A4" s="60" t="inlineStr"/>
+      <c r="B4" s="61" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="59" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>1. RELEVAMIENTO</t>
         </is>
       </c>
-      <c r="B5" s="59" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>Las columnas se identificaron en el plano cruzando el rotulo COL con un rectangulo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>de la misma seccion a menos de 26 pt. Resultaron 9 en PB y 4 en PA.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="59" t="inlineStr"/>
-      <c r="B7" s="60" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr"/>
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>Las 4 de PA caen exactamente sobre C6, C7, C8 y C9 de PB, y ademas tienen la misma</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59" t="inlineStr"/>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr"/>
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>seccion, lo que confirma que la correspondencia entre plantas es correcta.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="59" t="inlineStr"/>
-      <c r="B9" s="60" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>La planilla modelo de la catedra tiene 10 columnas en PB: puede faltar una que no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr"/>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr"/>
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>haya podido resolverse por rotulo. Conviene contarlas en el plano.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr"/>
-      <c r="B11" s="60" t="inlineStr"/>
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>2. ALTURAS</t>
         </is>
       </c>
-      <c r="B12" s="59" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>PB 3,15 m y PA 3,22 m, los mismos valores de la planilla de la catedra, coherentes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="59" t="inlineStr"/>
-      <c r="B13" s="60" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr"/>
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>con los niveles del plano (N.F.L +3,50 del entrepiso y +6,80 del techo).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="59" t="inlineStr"/>
-      <c r="B14" s="60" t="inlineStr"/>
+      <c r="A14" s="60" t="inlineStr"/>
+      <c r="B14" s="61" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="59" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>As = 0,008 x area (cuantia minima, el mismo criterio de la planilla modelo).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="59" t="inlineStr"/>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr"/>
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>Se adoptan 4 barras del 12 en todas: 4,52 cm2, que cubre la minima en toda seccion.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="59" t="inlineStr"/>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. long. ; 48 x diam. estribo ; lado menor),</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="inlineStr"/>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>redondeada hacia abajo a multiplo de 5. Para 4d12 con estribo d6 da 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="59" t="inlineStr"/>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr"/>
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>La planilla de la catedra adopta 20 cm: ese valor supera el limite reglamentario.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="59" t="inlineStr"/>
-      <c r="B20" s="60" t="inlineStr"/>
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="59" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>4. CAPACIDAD</t>
         </is>
       </c>
-      <c r="B21" s="59" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]     (columna zunchada con estribos)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="59" t="inlineStr"/>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr"/>
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  15x30 con 4d12 -&gt; 51,2 t        20x20 con 4d12 -&gt; 46,6 t</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="59" t="inlineStr"/>
-      <c r="B23" s="60" t="inlineStr"/>
+      <c r="A23" s="60" t="inlineStr"/>
+      <c r="B23" s="61" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="59" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>5. CARGAS</t>
         </is>
       </c>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>La columna CARGA (t) viene cargada con una bajada automatica: suma de las</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="59" t="inlineStr"/>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr"/>
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>reacciones de las vigas que apoyan en cada columna (tomadas de la planilla de</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="59" t="inlineStr"/>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr"/>
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>vigas), mas el peso propio, mas lo que baja de la columna del nivel superior.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr"/>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr"/>
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>ES UNA CARGA PROVISORIA Y ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="59" t="inlineStr"/>
-      <c r="B28" s="60" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr"/>
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>de viga no pudieron asignarse a ninguna columna porque apoyan en otra viga, en</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="59" t="inlineStr"/>
-      <c r="B29" s="60" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr"/>
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>un tabique o en la medianera, y esas reacciones no estan sumadas.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="59" t="inlineStr"/>
-      <c r="B30" s="60" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr"/>
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>Para cerrarla hay que indicar, para cada uno de esos 20 extremos, en que apoya.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="59" t="inlineStr"/>
-      <c r="B31" s="60" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr"/>
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>Mientras tanto la columna es editable: al corregir un valor todo recalcula.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="59" t="inlineStr"/>
-      <c r="B32" s="60" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr"/>
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="59" t="inlineStr"/>
-      <c r="B33" s="60" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr"/>
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="59" t="inlineStr"/>
-      <c r="B34" s="60" t="inlineStr"/>
+      <c r="A34" s="60" t="inlineStr"/>
+      <c r="B34" s="61" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="59" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>6. ESBELTEZ</t>
         </is>
       </c>
-      <c r="B35" s="59" t="inlineStr">
+      <c r="B35" s="60" t="inlineStr">
         <is>
           <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="59" t="inlineStr"/>
-      <c r="B36" s="60" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr"/>
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="59" t="inlineStr"/>
-      <c r="B37" s="60" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr"/>
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="59" t="inlineStr"/>
-      <c r="B38" s="60" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr"/>
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="59" t="inlineStr"/>
-      <c r="B39" s="60" t="inlineStr"/>
+      <c r="A39" s="60" t="inlineStr"/>
+      <c r="B39" s="61" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="59" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>7. C4, A REVISAR</t>
         </is>
       </c>
-      <c r="B40" s="59" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t>C4 figura en el plano como 10x10 y recibe el extremo de VI 01a, con 17 t de</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="59" t="inlineStr"/>
-      <c r="B41" s="60" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr"/>
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>reaccion. Una columna de 10x10 no toma esa carga. VI 01a corre sobre la medianera,</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="59" t="inlineStr"/>
-      <c r="B42" s="60" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr"/>
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>asi que lo mas probable es que apoye en el muro y ese 10x10 no sea una columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="59" t="inlineStr"/>
-      <c r="B43" s="60" t="inlineStr"/>
+      <c r="A43" s="60" t="inlineStr"/>
+      <c r="B43" s="61" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="59" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B44" s="59" t="inlineStr">
+      <c r="B44" s="60" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="59" t="inlineStr"/>
-      <c r="B45" s="60" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr"/>
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="59" t="inlineStr"/>
-      <c r="B46" s="60" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr"/>
+      <c r="B46" s="61" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>
@@ -4710,7 +5214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4727,7 +5231,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION - inventario. Calculo pendiente: va despues de columnas.</t>
         </is>
@@ -4869,7 +5373,7 @@
       <c r="D9" s="11" t="n">
         <v>533</v>
       </c>
-      <c r="E9" s="62" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>Ancho cortado en el PDF: confirmar 20 o 22 cm</t>
         </is>
@@ -4935,7 +5439,7 @@
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="62" t="inlineStr">
+      <c r="E13" s="63" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -4950,7 +5454,7 @@
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="62" t="inlineStr">
+      <c r="E14" s="63" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -5152,7 +5656,7 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="62" t="inlineStr">
+      <c r="E26" s="63" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -5302,7 +5806,7 @@
       <c r="E35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="54" t="inlineStr">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>Cabezales: CBZ 01 70x70x65   |   CBZ 02 129x70x70   |   CBZ 03 144x70x70</t>
         </is>
@@ -14347,6 +14851,756 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>PILOTES Y CABEZALES  H°A°        H-21        ACERO 42/50        TODOS LOS PILOTES Ø30  h = -4,50 m</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>COLUMNA</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>CABEZAL (cm)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>CARGA</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>PILOTES</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICACION</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>mayorada (t)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>servicio (t)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>cantidad</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>o (cm)</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>long. (m)</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>carga c/u (t)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>admisible (t)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>CB1</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>C1 (15x30)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 01</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H4" s="25">
+        <f>IF(G4="","",G4/1.4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L4" s="25">
+        <f>IF(H4="","",H4/I4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N4" s="11">
+        <f>IF(L4="","FALTA CARGA",IF(L4&lt;=M4,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>CB2</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>C2 (15x30)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 01</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="H5" s="25">
+        <f>IF(G5="","",G5/1.4)</f>
+        <v/>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L5" s="25">
+        <f>IF(H5="","",H5/I5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N5" s="11">
+        <f>IF(L5="","FALTA CARGA",IF(L5&lt;=M5,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>CB3</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>C5 (15x30)</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 01</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H6" s="25">
+        <f>IF(G6="","",G6/1.4)</f>
+        <v/>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L6" s="25">
+        <f>IF(H6="","",H6/I6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N6" s="11">
+        <f>IF(L6="","FALTA CARGA",IF(L6&lt;=M6,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>CB4</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>C3 (30x15)</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 01</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H7" s="25">
+        <f>IF(G7="","",G7/1.4)</f>
+        <v/>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" s="25">
+        <f>IF(H7="","",H7/I7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N7" s="11">
+        <f>IF(L7="","FALTA CARGA",IF(L7&lt;=M7,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O7" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>CB5</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>C4 (10x10)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 01</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="H8" s="25">
+        <f>IF(G8="","",G8/1.4)</f>
+        <v/>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L8" s="25">
+        <f>IF(H8="","",H8/I8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N8" s="11">
+        <f>IF(L8="","FALTA CARGA",IF(L8&lt;=M8,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>CB6</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>C6 (20x20)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 03</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H9" s="25">
+        <f>IF(G9="","",G9/1.4)</f>
+        <v/>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" s="25">
+        <f>IF(H9="","",H9/I9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N9" s="11">
+        <f>IF(L9="","FALTA CARGA",IF(L9&lt;=M9,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 144x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>CB7</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>C7 (30x15)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 02</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="H10" s="25">
+        <f>IF(G10="","",G10/1.4)</f>
+        <v/>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" s="25">
+        <f>IF(H10="","",H10/I10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N10" s="11">
+        <f>IF(L10="","FALTA CARGA",IF(L10&lt;=M10,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 129x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>CB8</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>C9 (15x30)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>CBZ 03</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="H11" s="25">
+        <f>IF(G11="","",G11/1.4)</f>
+        <v/>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L11" s="25">
+        <f>IF(H11="","",H11/I11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="8">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N11" s="11">
+        <f>IF(L11="","FALTA CARGA",IF(L11&lt;=M11,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 144x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>CB9</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>C8 (15x30)</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>CBZ 02</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="H12" s="30">
+        <f>IF(G12="","",G12/1.4)</f>
+        <v/>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L12" s="30">
+        <f>IF(H12="","",H12/I12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="15">
+        <f>Datos_pilotes!$B$4</f>
+        <v/>
+      </c>
+      <c r="N12" s="18">
+        <f>IF(L12="","FALTA CARGA",IF(L12&lt;=M12,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 129x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>Los 33 pilotes del plano: 13 bajo cabezales de columna (los de esta tabla) y 20 repartidos bajo las vigas de fundacion.</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="N4:N12">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"VERIFICA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"NO VERIFICA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"FALTA CARGA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F25"/>
@@ -14361,7 +15615,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - HIPOTESIS DE CALCULO</t>
         </is>
@@ -14373,7 +15627,7 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
         </is>
@@ -14393,17 +15647,17 @@
       <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -14413,12 +15667,12 @@
       <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="48" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -14431,12 +15685,12 @@
       <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="48" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -14449,12 +15703,12 @@
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="48" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -14467,12 +15721,12 @@
       <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>phi flexion</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="48" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -14485,12 +15739,12 @@
       <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>phi corte</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="48" t="n">
         <v>0.75</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -14503,12 +15757,12 @@
       <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Coef. mayoracion permanente</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="48" t="n">
         <v>1.2</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -14521,12 +15775,12 @@
       <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>Coef. mayoracion sobrecarga</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="48" t="n">
         <v>1.6</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -14547,7 +15801,7 @@
       <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>PAQUETES DE CARGA</t>
         </is>
@@ -14579,21 +15833,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B14" s="49" t="n">
+      <c r="B14" s="50" t="n">
         <v>550</v>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="50" t="n">
         <v>200</v>
       </c>
-      <c r="D14" s="50" t="n">
+      <c r="D14" s="51" t="n">
         <v>2.6</v>
       </c>
-      <c r="E14" s="50" t="n">
+      <c r="E14" s="51" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="32" t="inlineStr">
@@ -14603,21 +15857,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>TECHO</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n">
+      <c r="B15" s="50" t="n">
         <v>560</v>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="50" t="n">
+      <c r="D15" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="50" t="n">
+      <c r="E15" s="51" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="32" t="inlineStr">
@@ -14627,12 +15881,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="46" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>Mamposteria sobre viga</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="48" t="n">
         <v>250</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -14642,7 +15896,7 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="51" t="inlineStr">
+      <c r="F16" s="52" t="inlineStr">
         <is>
           <t>Ladrillo hueco 18 cm + revoque en ambas caras</t>
         </is>
@@ -14657,7 +15911,7 @@
       <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t>COEFICIENTES SEGUN ESQUEMA</t>
         </is>
@@ -14685,101 +15939,101 @@
       <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="B19" s="52" t="n">
+      <c r="B19" s="53" t="n">
         <v>0.125</v>
       </c>
-      <c r="C19" s="52" t="n">
+      <c r="C19" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="52" t="n">
+      <c r="D19" s="53" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" s="53" t="n">
+      <c r="E19" s="54" t="n">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
-      <c r="B20" s="52" t="n">
+      <c r="B20" s="53" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="C20" s="52" t="n">
+      <c r="C20" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="52" t="n">
+      <c r="D20" s="53" t="n">
         <v>0.575</v>
       </c>
-      <c r="E20" s="53" t="n">
+      <c r="E20" s="54" t="n">
         <v>21</v>
       </c>
       <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>Empotrada-apoyada</t>
         </is>
       </c>
-      <c r="B21" s="52" t="n">
+      <c r="B21" s="53" t="n">
         <v>0.07031</v>
       </c>
-      <c r="C21" s="52" t="n">
+      <c r="C21" s="53" t="n">
         <v>0.125</v>
       </c>
-      <c r="D21" s="52" t="n">
+      <c r="D21" s="53" t="n">
         <v>0.625</v>
       </c>
-      <c r="E21" s="53" t="n">
+      <c r="E21" s="54" t="n">
         <v>18.5</v>
       </c>
       <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="46" t="inlineStr">
+      <c r="A22" s="47" t="inlineStr">
         <is>
           <t>Biempotrada</t>
         </is>
       </c>
-      <c r="B22" s="52" t="n">
+      <c r="B22" s="53" t="n">
         <v>0.04167</v>
       </c>
-      <c r="C22" s="52" t="n">
+      <c r="C22" s="53" t="n">
         <v>0.08333</v>
       </c>
-      <c r="D22" s="52" t="n">
+      <c r="D22" s="53" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="53" t="n">
+      <c r="E22" s="54" t="n">
         <v>21</v>
       </c>
       <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="47" t="inlineStr">
         <is>
           <t>Voladizo</t>
         </is>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="53" t="n">
         <v>0.5</v>
       </c>
-      <c r="D23" s="52" t="n">
+      <c r="D23" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="53" t="n">
+      <c r="E23" s="54" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -14793,7 +16047,7 @@
       <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>p = 1,2 g + 1,6 q    |    M = coef x p x L2    |    R = coef x p x L</t>
         </is>
@@ -14809,7 +16063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14827,7 +16081,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - LOSAS</t>
         </is>
@@ -14837,7 +16091,7 @@
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
         </is>
@@ -14853,17 +16107,17 @@
       <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>MATERIALES Y METODO</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -14871,12 +16125,12 @@
       <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="48" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -14887,12 +16141,12 @@
       <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="48" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -14903,12 +16157,12 @@
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Tension admisible del acero</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="48" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -14919,12 +16173,12 @@
       <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Brazo elastico  z / h</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="48" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -14935,12 +16189,12 @@
       <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="48" t="n">
         <v>2400</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -14951,12 +16205,12 @@
       <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Recubrimiento</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="48" t="n">
         <v>1.5</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -14967,12 +16221,12 @@
       <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>Separacion maxima</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="48" t="n">
         <v>20</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -14983,12 +16237,12 @@
       <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="47" t="inlineStr">
         <is>
           <t>Armadura de reparticion</t>
         </is>
       </c>
-      <c r="B12" s="47" t="n">
+      <c r="B12" s="48" t="n">
         <v>0.2</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -14999,12 +16253,12 @@
       <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>Reparticion minima</t>
         </is>
       </c>
-      <c r="B13" s="47" t="n">
+      <c r="B13" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -15021,7 +16275,7 @@
       <c r="D14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>CARGAS POR NIVEL</t>
         </is>
@@ -15043,15 +16297,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B16" s="47" t="n">
+      <c r="B16" s="48" t="n">
         <v>242</v>
       </c>
-      <c r="C16" s="47" t="n">
+      <c r="C16" s="48" t="n">
         <v>200</v>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -15061,15 +16315,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B17" s="47" t="n">
+      <c r="B17" s="48" t="n">
         <v>252</v>
       </c>
-      <c r="C17" s="47" t="n">
+      <c r="C17" s="48" t="n">
         <v>100</v>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -15079,7 +16333,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>El peso propio se suma aparte: 2400 x d / 100</t>
         </is>
@@ -15095,7 +16349,7 @@
       <c r="D19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>GRADO DE EMPOTRAMIENTO</t>
         </is>
@@ -15122,7 +16376,7 @@
           <t>1/8</t>
         </is>
       </c>
-      <c r="B21" s="52" t="n">
+      <c r="B21" s="53" t="n">
         <v>0.125</v>
       </c>
       <c r="C21" s="56" t="n">
@@ -15140,7 +16394,7 @@
           <t>1/10</t>
         </is>
       </c>
-      <c r="B22" s="52" t="n">
+      <c r="B22" s="53" t="n">
         <v>0.1</v>
       </c>
       <c r="C22" s="56" t="n">
@@ -15158,7 +16412,7 @@
           <t>1/12</t>
         </is>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="53" t="n">
         <v>0.0833</v>
       </c>
       <c r="C23" s="56" t="n">
@@ -15176,7 +16430,7 @@
           <t>1/14</t>
         </is>
       </c>
-      <c r="B24" s="52" t="n">
+      <c r="B24" s="53" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="C24" s="56" t="n">
@@ -15194,7 +16448,7 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="B25" s="52" t="n">
+      <c r="B25" s="53" t="n">
         <v>0.5</v>
       </c>
       <c r="C25" s="56" t="n">
@@ -15213,7 +16467,7 @@
       <c r="D26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="54" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q   (cargas de servicio)</t>
         </is>
@@ -15223,7 +16477,7 @@
       <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="54" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>M = coef x p x L2        R = coef x p x L        As = M x 100 / (2400 x 0,9 x h)        rep. = As / 5</t>
         </is>
@@ -15237,7 +16491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15253,7 +16507,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - COLUMNAS</t>
         </is>
@@ -15267,29 +16521,29 @@
       <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>MATERIALES Y CRITERIOS</t>
         </is>
       </c>
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="46" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C3" s="45" t="inlineStr">
+      <c r="C3" s="46" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B4" s="47" t="n">
+      <c r="B4" s="48" t="n">
         <v>210</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -15299,12 +16553,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="48" t="n">
         <v>4200</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -15314,12 +16568,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="48" t="n">
         <v>2400</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -15329,12 +16583,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>phi compresion (estribos)</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="48" t="n">
         <v>0.65</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -15344,12 +16598,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Cuantia minima</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="48" t="n">
         <v>0.008</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -15359,12 +16613,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Altura PB</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="48" t="n">
         <v>3.15</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -15374,12 +16628,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Altura PA</t>
         </is>
       </c>
-      <c r="B10" s="47" t="n">
+      <c r="B10" s="48" t="n">
         <v>3.22</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -15394,7 +16648,7 @@
       <c r="C11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>As = cuantia minima x area        phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]</t>
         </is>
@@ -15403,211 +16657,13 @@
       <c r="C12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="54" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. longitudinal ; 48 x diam. estribo ; lado menor)</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="58" t="inlineStr">
-        <is>
-          <t>MEMORIA - ILUMINACION Y VENTILACION</t>
-        </is>
-      </c>
-      <c r="B1" s="59" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="59" t="inlineStr"/>
-      <c r="B2" s="60" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="59" t="inlineStr">
-        <is>
-          <t>CRITERIO</t>
-        </is>
-      </c>
-      <c r="B3" s="59" t="inlineStr">
-        <is>
-          <t>Area de iluminacion requerida = superficie del local / 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="59" t="inlineStr"/>
-      <c r="B4" s="60" t="inlineStr">
-        <is>
-          <t>Area de ventilacion requerida = un tercio de la de iluminacion = superficie / 27</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="59" t="inlineStr"/>
-      <c r="B5" s="60" t="inlineStr">
-        <is>
-          <t>Area proyectada: la vidriada de la carpinteria para iluminacion, y la parte que</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="59" t="inlineStr"/>
-      <c r="B6" s="60" t="inlineStr">
-        <is>
-          <t>realmente abre para ventilacion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="59" t="inlineStr"/>
-      <c r="B7" s="60" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="59" t="inlineStr">
-        <is>
-          <t>RESULTADO</t>
-        </is>
-      </c>
-      <c r="B8" s="59" t="inlineStr">
-        <is>
-          <t>Los trece locales cumplen holgadamente iluminacion y ventilacion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="59" t="inlineStr"/>
-      <c r="B9" s="60" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="59" t="inlineStr">
-        <is>
-          <t>CORRECCION</t>
-        </is>
-      </c>
-      <c r="B10" s="59" t="inlineStr">
-        <is>
-          <t>Local 07, Hall / ingreso: la planilla original traia 0,66 y 0,22, que son los</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="59" t="inlineStr"/>
-      <c r="B11" s="60" t="inlineStr">
-        <is>
-          <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="59" t="inlineStr"/>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="59" t="inlineStr"/>
-      <c r="B13" s="60" t="inlineStr">
-        <is>
-          <t>declarada y un verificador lo puede observar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="59" t="inlineStr"/>
-      <c r="B14" s="60" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="59" t="inlineStr">
-        <is>
-          <t>A REVISAR</t>
-        </is>
-      </c>
-      <c r="B15" s="59" t="inlineStr">
-        <is>
-          <t>Local 14, Estar / Playroom: declara 5,00 m2 de ventilacion sobre 5,00 m2 de</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="59" t="inlineStr"/>
-      <c r="B16" s="60" t="inlineStr">
-        <is>
-          <t>iluminacion, es decir una carpinteria enteramente abrible. En los demas locales</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="59" t="inlineStr"/>
-      <c r="B17" s="60" t="inlineStr">
-        <is>
-          <t>la relacion es del 50 por ciento. Conviene verificar la carpinteria real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="59" t="inlineStr"/>
-      <c r="B18" s="60" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="59" t="inlineStr"/>
-      <c r="B19" s="60" t="inlineStr">
-        <is>
-          <t>Local 02, Deposito: figura sin exigencia por no ser habitable. Son 11,8 m2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="59" t="inlineStr"/>
-      <c r="B20" s="60" t="inlineStr">
-        <is>
-          <t>cerrados: si se lo considera habitable hay que preverle conducto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="59" t="inlineStr"/>
-      <c r="B21" s="60" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="59" t="inlineStr">
-        <is>
-          <t>REDONDEOS</t>
-        </is>
-      </c>
-      <c r="B22" s="59" t="inlineStr">
-        <is>
-          <t>Diferencias menores que no afectan: local 03 da 5,95 m2 y figura 6,0;</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="59" t="inlineStr"/>
-      <c r="B23" s="60" t="inlineStr">
-        <is>
-          <t>local 09 da 12,25 y figura 12,3.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -13,27 +13,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Planilla columnas" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vigas de fundacion" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pilotes y cabezales" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_vigas" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_losas" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_columnas" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_pilotes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria ilum. y vent." sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria vigas" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria losas" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria columnas" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundacion (inventario)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabiques" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_vigas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_losas" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_columnas" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_pilotes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria ilum. y vent." sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria vigas" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria losas" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria columnas" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundacion (inventario)" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Planilla vigas'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla vigas'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla vigas'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla losas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla losas'!$A$1:$R$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla columnas'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Planilla columnas'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Planilla columnas'!$A$1:$N$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Vigas de fundacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Vigas de fundacion'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Pilotes y cabezales'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Tabiques'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -251,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -365,12 +367,15 @@
     <xf numFmtId="1" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1268,6 +1273,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1807,7 +1837,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -1832,7 +1862,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -1857,7 +1887,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -1882,7 +1912,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -1907,7 +1937,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -1932,7 +1962,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -1957,7 +1987,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -1982,7 +2012,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2007,7 +2037,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2032,7 +2062,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2057,7 +2087,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2082,7 +2112,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2107,7 +2137,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2132,7 +2162,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2157,7 +2187,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2182,7 +2212,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2207,7 +2237,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2232,7 +2262,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2257,7 +2287,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2095500" cy="571500"/>
@@ -2268,6 +2298,81 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3378,6 +3483,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>DATOS DE PARTIDA - COLUMNAS</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>MATERIALES Y CRITERIOS</t>
+        </is>
+      </c>
+      <c r="B3" s="47" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="C3" s="47" t="inlineStr">
+        <is>
+          <t>unidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="48" t="inlineStr">
+        <is>
+          <t>Hormigon H-21   f'c</t>
+        </is>
+      </c>
+      <c r="B4" s="49" t="n">
+        <v>210</v>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>kg/cm2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>Acero 42/50   fy</t>
+        </is>
+      </c>
+      <c r="B5" s="49" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>kg/cm2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t>Peso especifico H.A.</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>kg/m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>phi compresion (estribos)</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t>Cuantia minima</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>de la seccion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t>Altura PB</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="inlineStr">
+        <is>
+          <t>Altura PA</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>As = cuantia minima x area        phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>Separacion de estribos = min(12 x diam. longitudinal ; 48 x diam. estribo ; lado menor)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3388,7 +3672,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - PILOTES</t>
         </is>
@@ -3404,34 +3688,34 @@
       <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>PARAMETRO</t>
         </is>
       </c>
-      <c r="B3" s="46" t="inlineStr">
+      <c r="B3" s="47" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C3" s="46" t="inlineStr">
+      <c r="C3" s="47" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
       </c>
-      <c r="D3" s="45" t="inlineStr">
+      <c r="D3" s="46" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Carga admisible por pilote</t>
         </is>
       </c>
-      <c r="B4" s="48" t="n">
+      <c r="B4" s="49" t="n">
         <v>12</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -3439,19 +3723,19 @@
           <t>t</t>
         </is>
       </c>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>ESTIMADA. Falta el estudio de suelos: cambiar aca y recalcula todo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>Tension admisible del terreno</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="49" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -3459,19 +3743,19 @@
           <t>kg/cm2</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>Dato real, tomado del encabezado del calculo de bases.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>Diametro del pilote</t>
         </is>
       </c>
-      <c r="B6" s="48" t="n">
+      <c r="B6" s="49" t="n">
         <v>30</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -3479,19 +3763,19 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>Nota del plano: todos los pilotes son O30.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>Profundidad</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="49" t="n">
         <v>-4.5</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -3499,19 +3783,19 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>Nota del plano: h = -4,50 m desde la cota +-0,00 de vereda.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>Coef. de mayoracion adoptado</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="49" t="n">
         <v>1.4</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -3519,7 +3803,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>Para pasar de carga mayorada a carga de servicio.</t>
         </is>
@@ -3538,7 +3822,7 @@
       <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>COMO SE ESTIMO LA CARGA ADMISIBLE</t>
         </is>
@@ -3594,7 +3878,7 @@
       <c r="D16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>LECTURA INVERSA, que es la util mientras no haya estudio de suelos:</t>
         </is>
@@ -3674,7 +3958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3688,180 +3972,180 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>MEMORIA - ILUMINACION Y VENTILACION</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr"/>
+      <c r="B1" s="61" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="inlineStr"/>
-      <c r="B2" s="61" t="inlineStr"/>
+      <c r="A2" s="61" t="inlineStr"/>
+      <c r="B2" s="62" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>CRITERIO</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>Area de iluminacion requerida = superficie del local / 9</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr"/>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr"/>
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Area de ventilacion requerida = un tercio de la de iluminacion = superficie / 27</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr"/>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr"/>
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>Area proyectada: la vidriada de la carpinteria para iluminacion, y la parte que</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>realmente abre para ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr"/>
-      <c r="B7" s="61" t="inlineStr"/>
+      <c r="A7" s="61" t="inlineStr"/>
+      <c r="B7" s="62" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>RESULTADO</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>Los trece locales cumplen holgadamente iluminacion y ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr"/>
-      <c r="B9" s="61" t="inlineStr"/>
+      <c r="A9" s="61" t="inlineStr"/>
+      <c r="B9" s="62" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>CORRECCION</t>
         </is>
       </c>
-      <c r="B10" s="60" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Local 07, Hall / ingreso: la planilla original traia 0,66 y 0,22, que son los</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr"/>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr"/>
+      <c r="B11" s="62" t="inlineStr">
         <is>
           <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr"/>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr"/>
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr"/>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr"/>
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>declarada y un verificador lo puede observar.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="60" t="inlineStr"/>
-      <c r="B14" s="61" t="inlineStr"/>
+      <c r="A14" s="61" t="inlineStr"/>
+      <c r="B14" s="62" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>A REVISAR</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>Local 14, Estar / Playroom: declara 5,00 m2 de ventilacion sobre 5,00 m2 de</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="60" t="inlineStr"/>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr"/>
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>iluminacion, es decir una carpinteria enteramente abrible. En los demas locales</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr"/>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr"/>
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>la relacion es del 50 por ciento. Conviene verificar la carpinteria real.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="60" t="inlineStr"/>
-      <c r="B18" s="61" t="inlineStr"/>
+      <c r="A18" s="61" t="inlineStr"/>
+      <c r="B18" s="62" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr"/>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr"/>
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>Local 02, Deposito: figura sin exigencia por no ser habitable. Son 11,8 m2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="60" t="inlineStr"/>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr"/>
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t>cerrados: si se lo considera habitable hay que preverle conducto.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr"/>
-      <c r="B21" s="61" t="inlineStr"/>
+      <c r="A21" s="61" t="inlineStr"/>
+      <c r="B21" s="62" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr">
         <is>
           <t>REDONDEOS</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>Diferencias menores que no afectan: local 03 da 5,95 m2 y figura 6,0;</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr"/>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr"/>
+      <c r="B23" s="62" t="inlineStr">
         <is>
           <t>local 09 da 12,25 y figura 12,3.</t>
         </is>
@@ -3872,7 +4156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3886,552 +4170,552 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr"/>
+      <c r="B1" s="61" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="inlineStr"/>
-      <c r="B2" s="61" t="inlineStr"/>
+      <c r="A2" s="61" t="inlineStr"/>
+      <c r="B2" s="62" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>NORMATIVA</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>CIRSOC 201. Hormigon H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200 kg/cm2).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr">
         <is>
           <t>UNIDADES</t>
         </is>
       </c>
-      <c r="B4" s="60" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>Longitudes en m y cm. Cargas en kg/m. Momentos en kgm. Tensiones en kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>b = ancho | h = altura util | d = altura total (igual criterio que la planilla de catedra).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr"/>
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="62" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B7" s="60" t="inlineStr"/>
+      <c r="B7" s="61" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>Entrepiso PA</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>Losa maciza 12 cm 300 + contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr"/>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr"/>
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>g = 550 kg/m2       q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>Azotea</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>Losa 300 + contrapiso de pendiente 140 + carpeta 42 + aislacion y membrana 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr"/>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr"/>
+      <c r="B11" s="62" t="inlineStr">
         <is>
           <t>g = 560 kg/m2       q = 100 kg/m2 (cubierta no accesible)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>Mamposteria</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>250 kg/m2. Altura 2,60 m en PA y 1,00 m de parapeto en azotea.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>Peso propio</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>2400 kg/m3 x b x d, viga por viga.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>Carga de calculo</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="62" t="inlineStr">
         <is>
           <t>p = 1,2 (g x B + peso propio + muro) + 1,6 (q x B)        B = ancho tributario</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr"/>
-      <c r="B15" s="61" t="inlineStr"/>
+      <c r="A15" s="61" t="inlineStr"/>
+      <c r="B15" s="62" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>Coeficientes segun esquema (tabla en hoja Datos):</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr"/>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr"/>
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  Simplemente apoyada   M = pL2/8                    R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="60" t="inlineStr"/>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr"/>
+      <c r="B18" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  Continua              M = pL2/14   Mapoyo = pL2/10  R = 0,575 pL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr"/>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr"/>
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  Empotrada-apoyada     M = 9pL2/128 Mapoyo = pL2/8   R = 0,625 pL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="60" t="inlineStr"/>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr"/>
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  Biempotrada           M = pL2/24   Mapoyo = pL2/12  R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr"/>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr"/>
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  Voladizo                           Mapoyo = pL2/2   R = 1,000 pL</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="inlineStr"/>
-      <c r="B22" s="61" t="inlineStr"/>
+      <c r="A22" s="61" t="inlineStr"/>
+      <c r="B22" s="62" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>3. FLEXION</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>k = M / (phi b h2 f'c)      w = 1 - RAIZ(1 - 2k)      As = w b h f'c / fy</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="60" t="inlineStr"/>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr"/>
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>As min = 0,0033 b h       As max = 0,0163 b h (0,75 de la cuantia balanceada)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="60" t="inlineStr"/>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="A25" s="61" t="inlineStr"/>
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>Si la armadura no entra en una capa se disponen dos y el recubrimiento pasa a 6 cm.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="60" t="inlineStr"/>
-      <c r="B26" s="61" t="inlineStr"/>
+      <c r="A26" s="61" t="inlineStr"/>
+      <c r="B26" s="62" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="61" t="inlineStr">
         <is>
           <t>4. CORTE</t>
         </is>
       </c>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>T = R / (b x 0,85 h)       tension tangencial en el apoyo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="inlineStr"/>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr"/>
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>Vc = 0,53 RAIZ(f'c) b h        phi Vn = 0,75 (Vc + Av fy h / s)  &gt;=  R</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="inlineStr"/>
-      <c r="B29" s="61" t="inlineStr">
+      <c r="A29" s="61" t="inlineStr"/>
+      <c r="B29" s="62" t="inlineStr">
         <is>
           <t>Av = 2 ramas. Se aumenta el diametro antes que cerrar la separacion por debajo de 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="inlineStr"/>
-      <c r="B30" s="61" t="inlineStr"/>
+      <c r="A30" s="61" t="inlineStr"/>
+      <c r="B30" s="62" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr">
         <is>
           <t>5. FLECHA</t>
         </is>
       </c>
-      <c r="B31" s="60" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>Altura minima: simplemente apoyada L/16, un extremo continuo L/18,5,</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="inlineStr"/>
-      <c r="B32" s="61" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr"/>
+      <c r="B32" s="62" t="inlineStr">
         <is>
           <t>ambos extremos continuos L/21, voladizo L/8.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr"/>
-      <c r="B33" s="61" t="inlineStr"/>
+      <c r="A33" s="61" t="inlineStr"/>
+      <c r="B33" s="62" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>6. VIGAS INVERTIDAS</t>
         </is>
       </c>
-      <c r="B34" s="60" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>Las vigas de BORDE son invertidas: sobresalen 70 cm por encima del fondo de</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr"/>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr"/>
+      <c r="B35" s="62" t="inlineStr">
         <is>
           <t>losa (cotas N.F.L +3,50 / N.S.V +4,20 y N.F.L +6,80 / N.S.V +7,50 del plano).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr"/>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr"/>
+      <c r="B36" s="62" t="inlineStr">
         <is>
           <t>Son VI 01a, VI 01b, VI 07a, VI 07b, VI 07c, VI 11a, VI 11b, VI 11c, VI 15a y VI 15b,</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr"/>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="A37" s="61" t="inlineStr"/>
+      <c r="B37" s="62" t="inlineStr">
         <is>
           <t>identificadas por coincidir su eje con el contorno del edificio.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="60" t="inlineStr"/>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="A38" s="61" t="inlineStr"/>
+      <c r="B38" s="62" t="inlineStr">
         <is>
           <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="inlineStr"/>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="A39" s="61" t="inlineStr"/>
+      <c r="B39" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="inlineStr"/>
-      <c r="B40" s="61" t="inlineStr">
+      <c r="A40" s="61" t="inlineStr"/>
+      <c r="B40" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="inlineStr"/>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="A41" s="61" t="inlineStr"/>
+      <c r="B41" s="62" t="inlineStr">
         <is>
           <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="60" t="inlineStr"/>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="A42" s="61" t="inlineStr"/>
+      <c r="B42" s="62" t="inlineStr">
         <is>
           <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="inlineStr"/>
-      <c r="B43" s="61" t="inlineStr">
+      <c r="A43" s="61" t="inlineStr"/>
+      <c r="B43" s="62" t="inlineStr">
         <is>
           <t>PENDIENTE: una viga invertida de borde recibe la reaccion de la losa excentrica</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="60" t="inlineStr"/>
-      <c r="B44" s="61" t="inlineStr">
+      <c r="A44" s="61" t="inlineStr"/>
+      <c r="B44" s="62" t="inlineStr">
         <is>
           <t>respecto de su eje y queda sometida a TORSION. Esta planilla no la verifica.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="60" t="inlineStr"/>
-      <c r="B45" s="61" t="inlineStr"/>
+      <c r="A45" s="61" t="inlineStr"/>
+      <c r="B45" s="62" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="inlineStr">
+      <c r="A46" s="61" t="inlineStr">
         <is>
           <t>7. RESULTADO</t>
         </is>
       </c>
-      <c r="B46" s="60" t="inlineStr">
+      <c r="B46" s="61" t="inlineStr">
         <is>
           <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="60" t="inlineStr"/>
-      <c r="B47" s="61" t="inlineStr">
+      <c r="A47" s="61" t="inlineStr"/>
+      <c r="B47" s="62" t="inlineStr">
         <is>
           <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="60" t="inlineStr"/>
-      <c r="B48" s="61" t="inlineStr">
+      <c r="A48" s="61" t="inlineStr"/>
+      <c r="B48" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="60" t="inlineStr"/>
-      <c r="B49" s="61" t="inlineStr">
+      <c r="A49" s="61" t="inlineStr"/>
+      <c r="B49" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="60" t="inlineStr"/>
-      <c r="B50" s="61" t="inlineStr">
+      <c r="A50" s="61" t="inlineStr"/>
+      <c r="B50" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="60" t="inlineStr"/>
-      <c r="B51" s="61" t="inlineStr">
+      <c r="A51" s="61" t="inlineStr"/>
+      <c r="B51" s="62" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="60" t="inlineStr"/>
-      <c r="B52" s="61" t="inlineStr">
+      <c r="A52" s="61" t="inlineStr"/>
+      <c r="B52" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="60" t="inlineStr"/>
-      <c r="B53" s="61" t="inlineStr">
+      <c r="A53" s="61" t="inlineStr"/>
+      <c r="B53" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="60" t="inlineStr"/>
-      <c r="B54" s="61" t="inlineStr">
+      <c r="A54" s="61" t="inlineStr"/>
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="60" t="inlineStr"/>
-      <c r="B55" s="61" t="inlineStr">
+      <c r="A55" s="61" t="inlineStr"/>
+      <c r="B55" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="60" t="inlineStr"/>
-      <c r="B56" s="61" t="inlineStr">
+      <c r="A56" s="61" t="inlineStr"/>
+      <c r="B56" s="62" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="60" t="inlineStr"/>
-      <c r="B57" s="61" t="inlineStr">
+      <c r="A57" s="61" t="inlineStr"/>
+      <c r="B57" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="60" t="inlineStr"/>
-      <c r="B58" s="61" t="inlineStr"/>
+      <c r="A58" s="61" t="inlineStr"/>
+      <c r="B58" s="62" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="60" t="inlineStr">
+      <c r="A59" s="61" t="inlineStr">
         <is>
           <t>8. ALCANCE</t>
         </is>
       </c>
-      <c r="B59" s="61" t="inlineStr">
+      <c r="B59" s="62" t="inlineStr">
         <is>
           <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="60" t="inlineStr"/>
-      <c r="B60" s="61" t="inlineStr">
+      <c r="A60" s="61" t="inlineStr"/>
+      <c r="B60" s="62" t="inlineStr">
         <is>
           <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="60" t="inlineStr"/>
-      <c r="B61" s="61" t="inlineStr"/>
+      <c r="A61" s="61" t="inlineStr"/>
+      <c r="B61" s="62" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="60" t="inlineStr">
+      <c r="A62" s="61" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B62" s="60" t="inlineStr">
+      <c r="B62" s="61" t="inlineStr">
         <is>
           <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="60" t="inlineStr"/>
-      <c r="B63" s="61" t="inlineStr">
+      <c r="A63" s="61" t="inlineStr"/>
+      <c r="B63" s="62" t="inlineStr">
         <is>
           <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="60" t="inlineStr"/>
-      <c r="B64" s="61" t="inlineStr">
+      <c r="A64" s="61" t="inlineStr"/>
+      <c r="B64" s="62" t="inlineStr">
         <is>
           <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="60" t="inlineStr"/>
-      <c r="B65" s="61" t="inlineStr">
+      <c r="A65" s="61" t="inlineStr"/>
+      <c r="B65" s="62" t="inlineStr">
         <is>
           <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="60" t="inlineStr"/>
-      <c r="B66" s="61" t="inlineStr">
+      <c r="A66" s="61" t="inlineStr"/>
+      <c r="B66" s="62" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -4442,7 +4726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4456,368 +4740,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - LOSAS</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr"/>
+      <c r="B1" s="61" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="inlineStr"/>
-      <c r="B2" s="61" t="inlineStr"/>
+      <c r="A2" s="61" t="inlineStr"/>
+      <c r="B2" s="62" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>METODO</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>Tensiones admisibles, igual criterio que la planilla modelo de la catedra.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr"/>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="A4" s="61" t="inlineStr"/>
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Se verifico contra la fila de ejemplo: momentos y reacciones coinciden exactamente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). Tension admisible 2400 kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B6" s="60" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>h = altura util | d = espesor total. Recubrimiento 1,5 cm.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr"/>
-      <c r="B7" s="61" t="inlineStr"/>
+      <c r="A7" s="61" t="inlineStr"/>
+      <c r="B7" s="62" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B8" s="60" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q      (cargas de servicio, sin mayorar)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr"/>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr"/>
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>Peso propio = 2400 x d / 100, calculado con el espesor propio de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>Terminaciones 242 kg/m2 (contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr"/>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr"/>
+      <c r="B11" s="62" t="inlineStr">
         <is>
           <t>q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>Terminaciones 252 kg/m2 (contrapiso pendiente 140 + carpeta 42 + aislacion 50 +</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr"/>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr"/>
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>cielorraso 20).  q = 100 kg/m2 (azotea no accesible)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="60" t="inlineStr"/>
-      <c r="B14" s="61" t="inlineStr"/>
+      <c r="A14" s="61" t="inlineStr"/>
+      <c r="B14" s="62" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>M = coeficiente x p x L2, segun el grado de empotramiento:</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="60" t="inlineStr"/>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr"/>
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  1/8 simplemente apoyada    1/10 y 1/14 continua    1/12 biempotrada    1/2 voladizo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr"/>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr"/>
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>R = coeficiente x p x L. En voladizo Rx = p x L y Ry no corresponde.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="60" t="inlineStr"/>
-      <c r="B18" s="61" t="inlineStr"/>
+      <c r="A18" s="61" t="inlineStr"/>
+      <c r="B18" s="62" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>As = M x 100 / (2400 x 0,9 x h)        [cm2/m]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="60" t="inlineStr"/>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="A20" s="61" t="inlineStr"/>
+      <c r="B20" s="62" t="inlineStr">
         <is>
           <t>separacion = 100 x area de la barra / As, redondeada, con maximo 20 cm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr"/>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr"/>
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t>Armadura de reparticion = As / 5, con un minimo de 0,30 cm2/m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="inlineStr"/>
-      <c r="B22" s="61" t="inlineStr"/>
+      <c r="A22" s="61" t="inlineStr"/>
+      <c r="B22" s="62" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="61" t="inlineStr">
         <is>
           <t>4. ESPESORES</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>Los espesores d se leyeron del plano: estan escritos debajo del rotulo de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="60" t="inlineStr"/>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr"/>
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>S/PB:  L01 11 | L02 9 | L03 13 | L04 11 | L05 11 | L06 8 | L07 12 | L08 10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="60" t="inlineStr"/>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="A25" s="61" t="inlineStr"/>
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>S/PA:  L09 13 | L10 12</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="60" t="inlineStr"/>
-      <c r="B26" s="61" t="inlineStr"/>
+      <c r="A26" s="61" t="inlineStr"/>
+      <c r="B26" s="62" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="61" t="inlineStr">
         <is>
           <t>5. LUCES</t>
         </is>
       </c>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>Relevadas en obra y aportadas por el proyectista. Dos losas son voladizo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="inlineStr"/>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr"/>
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>(L02 de 0,80 m y L08 de 0,75 m) y se calculan con M = p L2 / 2.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="inlineStr"/>
-      <c r="B29" s="61" t="inlineStr"/>
+      <c r="A29" s="61" t="inlineStr"/>
+      <c r="B29" s="62" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="61" t="inlineStr">
         <is>
           <t>6. LOSAS CRUZADAS</t>
         </is>
       </c>
-      <c r="B30" s="61" t="inlineStr">
+      <c r="B30" s="62" t="inlineStr">
         <is>
           <t>L07 (4,85 x 5,60) y L10 (4,85 x 6,00) apoyan en los cuatro bordes y su relacion</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr"/>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr"/>
+      <c r="B31" s="62" t="inlineStr">
         <is>
           <t>de lados es menor que 2, por lo que trabajan en las dos direcciones.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="inlineStr"/>
-      <c r="B32" s="61" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr"/>
+      <c r="B32" s="62" t="inlineStr">
         <is>
           <t>Se reparte la carga por el metodo de Marcus:   kx = ly4 / (lx4 + ly4)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr"/>
-      <c r="B33" s="61" t="inlineStr">
+      <c r="A33" s="61" t="inlineStr"/>
+      <c r="B33" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  L07: ly/lx = 1,15  -&gt;  64% en la direccion corta, 36% en la larga</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr"/>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="A34" s="61" t="inlineStr"/>
+      <c r="B34" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  L10: ly/lx = 1,24  -&gt;  70% en la direccion corta, 30% en la larga</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr"/>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr"/>
+      <c r="B35" s="62" t="inlineStr">
         <is>
           <t>Cada una ocupa dos renglones, uno por direccion, con la fraccion de carga que</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr"/>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr"/>
+      <c r="B36" s="62" t="inlineStr">
         <is>
           <t>le toca ya aplicada en la columna CARGAS. Las dos armaduras se cruzan en obra:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr"/>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="A37" s="61" t="inlineStr"/>
+      <c r="B37" s="62" t="inlineStr">
         <is>
           <t>la de la direccion corta va abajo, la de la larga arriba de aquella.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="60" t="inlineStr"/>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="A38" s="61" t="inlineStr"/>
+      <c r="B38" s="62" t="inlineStr">
         <is>
           <t>La columna auxiliar luz transv. es la que dispara el reparto: si se borra, la</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="inlineStr"/>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="A39" s="61" t="inlineStr"/>
+      <c r="B39" s="62" t="inlineStr">
         <is>
           <t>fila vuelve a calcularse como losa armada en una direccion.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="inlineStr"/>
-      <c r="B40" s="61" t="inlineStr"/>
+      <c r="A40" s="61" t="inlineStr"/>
+      <c r="B40" s="62" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A41" s="61" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B41" s="60" t="inlineStr">
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>El grado de empotramiento esta cargado en 1/8 salvo los dos voladizos (1/2). Si</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="60" t="inlineStr"/>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="A42" s="61" t="inlineStr"/>
+      <c r="B42" s="62" t="inlineStr">
         <is>
           <t>alguna losa es continua sobre una viga corresponde 1/10 o 1/14: corregir en la columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="inlineStr"/>
-      <c r="B43" s="61" t="inlineStr">
+      <c r="A43" s="61" t="inlineStr"/>
+      <c r="B43" s="62" t="inlineStr">
         <is>
           <t>El diagrama de cargas es una imagen fija: si cambias el grado, cambialo a mano.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="60" t="inlineStr"/>
-      <c r="B44" s="61" t="inlineStr">
+      <c r="A44" s="61" t="inlineStr"/>
+      <c r="B44" s="62" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -4828,7 +5112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4842,368 +5126,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="59" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - COLUMNAS</t>
         </is>
       </c>
-      <c r="B1" s="60" t="inlineStr"/>
+      <c r="B1" s="61" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="60" t="inlineStr"/>
-      <c r="B2" s="61" t="inlineStr"/>
+      <c r="A2" s="61" t="inlineStr"/>
+      <c r="B2" s="62" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). phi compresion 0,65.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="60" t="inlineStr"/>
-      <c r="B4" s="61" t="inlineStr"/>
+      <c r="A4" s="61" t="inlineStr"/>
+      <c r="B4" s="62" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="61" t="inlineStr">
         <is>
           <t>1. RELEVAMIENTO</t>
         </is>
       </c>
-      <c r="B5" s="60" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>Las columnas se identificaron en el plano cruzando el rotulo COL con un rectangulo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="60" t="inlineStr"/>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="A6" s="61" t="inlineStr"/>
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>de la misma seccion a menos de 26 pt. Resultaron 9 en PB y 4 en PA.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="60" t="inlineStr"/>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="A7" s="61" t="inlineStr"/>
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>Las 4 de PA caen exactamente sobre C6, C7, C8 y C9 de PB, y ademas tienen la misma</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="60" t="inlineStr"/>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr"/>
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>seccion, lo que confirma que la correspondencia entre plantas es correcta.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60" t="inlineStr"/>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="A9" s="61" t="inlineStr"/>
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>La planilla modelo de la catedra tiene 10 columnas en PB: puede faltar una que no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="60" t="inlineStr"/>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr"/>
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>haya podido resolverse por rotulo. Conviene contarlas en el plano.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="60" t="inlineStr"/>
-      <c r="B11" s="61" t="inlineStr"/>
+      <c r="A11" s="61" t="inlineStr"/>
+      <c r="B11" s="62" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>2. ALTURAS</t>
         </is>
       </c>
-      <c r="B12" s="60" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>PB 3,15 m y PA 3,22 m, los mismos valores de la planilla de la catedra, coherentes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr"/>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr"/>
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>con los niveles del plano (N.F.L +3,50 del entrepiso y +6,80 del techo).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="60" t="inlineStr"/>
-      <c r="B14" s="61" t="inlineStr"/>
+      <c r="A14" s="61" t="inlineStr"/>
+      <c r="B14" s="62" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="61" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B15" s="60" t="inlineStr">
+      <c r="B15" s="61" t="inlineStr">
         <is>
           <t>As = 0,008 x area (cuantia minima, el mismo criterio de la planilla modelo).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="60" t="inlineStr"/>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="A16" s="61" t="inlineStr"/>
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>Se adoptan 4 barras del 12 en todas: 4,52 cm2, que cubre la minima en toda seccion.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="60" t="inlineStr"/>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="A17" s="61" t="inlineStr"/>
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. long. ; 48 x diam. estribo ; lado menor),</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="60" t="inlineStr"/>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="A18" s="61" t="inlineStr"/>
+      <c r="B18" s="62" t="inlineStr">
         <is>
           <t>redondeada hacia abajo a multiplo de 5. Para 4d12 con estribo d6 da 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="60" t="inlineStr"/>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="A19" s="61" t="inlineStr"/>
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>La planilla de la catedra adopta 20 cm: ese valor supera el limite reglamentario.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="60" t="inlineStr"/>
-      <c r="B20" s="61" t="inlineStr"/>
+      <c r="A20" s="61" t="inlineStr"/>
+      <c r="B20" s="62" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="61" t="inlineStr">
         <is>
           <t>4. CAPACIDAD</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]     (columna zunchada con estribos)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="60" t="inlineStr"/>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="A22" s="61" t="inlineStr"/>
+      <c r="B22" s="62" t="inlineStr">
         <is>
           <t xml:space="preserve">  15x30 con 4d12 -&gt; 51,2 t        20x20 con 4d12 -&gt; 46,6 t</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="60" t="inlineStr"/>
-      <c r="B23" s="61" t="inlineStr"/>
+      <c r="A23" s="61" t="inlineStr"/>
+      <c r="B23" s="62" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="61" t="inlineStr">
         <is>
           <t>5. CARGAS</t>
         </is>
       </c>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>La columna CARGA (t) viene cargada con una bajada automatica: suma de las</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="60" t="inlineStr"/>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="A25" s="61" t="inlineStr"/>
+      <c r="B25" s="62" t="inlineStr">
         <is>
           <t>reacciones de las vigas que apoyan en cada columna (tomadas de la planilla de</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="60" t="inlineStr"/>
-      <c r="B26" s="61" t="inlineStr">
+      <c r="A26" s="61" t="inlineStr"/>
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>vigas), mas el peso propio, mas lo que baja de la columna del nivel superior.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="60" t="inlineStr"/>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="A27" s="61" t="inlineStr"/>
+      <c r="B27" s="62" t="inlineStr">
         <is>
           <t>ES UNA CARGA PROVISORIA Y ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="60" t="inlineStr"/>
-      <c r="B28" s="61" t="inlineStr">
+      <c r="A28" s="61" t="inlineStr"/>
+      <c r="B28" s="62" t="inlineStr">
         <is>
           <t>de viga no pudieron asignarse a ninguna columna porque apoyan en otra viga, en</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="60" t="inlineStr"/>
-      <c r="B29" s="61" t="inlineStr">
+      <c r="A29" s="61" t="inlineStr"/>
+      <c r="B29" s="62" t="inlineStr">
         <is>
           <t>un tabique o en la medianera, y esas reacciones no estan sumadas.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="60" t="inlineStr"/>
-      <c r="B30" s="61" t="inlineStr">
+      <c r="A30" s="61" t="inlineStr"/>
+      <c r="B30" s="62" t="inlineStr">
         <is>
           <t>Para cerrarla hay que indicar, para cada uno de esos 20 extremos, en que apoya.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="60" t="inlineStr"/>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="A31" s="61" t="inlineStr"/>
+      <c r="B31" s="62" t="inlineStr">
         <is>
           <t>Mientras tanto la columna es editable: al corregir un valor todo recalcula.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="60" t="inlineStr"/>
-      <c r="B32" s="61" t="inlineStr">
+      <c r="A32" s="61" t="inlineStr"/>
+      <c r="B32" s="62" t="inlineStr">
         <is>
           <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr"/>
-      <c r="B33" s="61" t="inlineStr">
+      <c r="A33" s="61" t="inlineStr"/>
+      <c r="B33" s="62" t="inlineStr">
         <is>
           <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr"/>
-      <c r="B34" s="61" t="inlineStr"/>
+      <c r="A34" s="61" t="inlineStr"/>
+      <c r="B34" s="62" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="61" t="inlineStr">
         <is>
           <t>6. ESBELTEZ</t>
         </is>
       </c>
-      <c r="B35" s="60" t="inlineStr">
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr"/>
-      <c r="B36" s="61" t="inlineStr">
+      <c r="A36" s="61" t="inlineStr"/>
+      <c r="B36" s="62" t="inlineStr">
         <is>
           <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr"/>
-      <c r="B37" s="61" t="inlineStr">
+      <c r="A37" s="61" t="inlineStr"/>
+      <c r="B37" s="62" t="inlineStr">
         <is>
           <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="60" t="inlineStr"/>
-      <c r="B38" s="61" t="inlineStr">
+      <c r="A38" s="61" t="inlineStr"/>
+      <c r="B38" s="62" t="inlineStr">
         <is>
           <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="inlineStr"/>
-      <c r="B39" s="61" t="inlineStr"/>
+      <c r="A39" s="61" t="inlineStr"/>
+      <c r="B39" s="62" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="A40" s="61" t="inlineStr">
         <is>
           <t>7. C4, A REVISAR</t>
         </is>
       </c>
-      <c r="B40" s="60" t="inlineStr">
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t>C4 figura en el plano como 10x10 y recibe el extremo de VI 01a, con 17 t de</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="inlineStr"/>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="A41" s="61" t="inlineStr"/>
+      <c r="B41" s="62" t="inlineStr">
         <is>
           <t>reaccion. Una columna de 10x10 no toma esa carga. VI 01a corre sobre la medianera,</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="60" t="inlineStr"/>
-      <c r="B42" s="61" t="inlineStr">
+      <c r="A42" s="61" t="inlineStr"/>
+      <c r="B42" s="62" t="inlineStr">
         <is>
           <t>asi que lo mas probable es que apoye en el muro y ese 10x10 no sea una columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="60" t="inlineStr"/>
-      <c r="B43" s="61" t="inlineStr"/>
+      <c r="A43" s="61" t="inlineStr"/>
+      <c r="B43" s="62" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A44" s="61" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B44" s="60" t="inlineStr">
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="60" t="inlineStr"/>
-      <c r="B45" s="61" t="inlineStr">
+      <c r="A45" s="61" t="inlineStr"/>
+      <c r="B45" s="62" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="inlineStr"/>
-      <c r="B46" s="61" t="inlineStr">
+      <c r="A46" s="61" t="inlineStr"/>
+      <c r="B46" s="62" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>
@@ -5214,7 +5498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5231,7 +5515,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="63" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION - inventario. Calculo pendiente: va despues de columnas.</t>
         </is>
@@ -5373,7 +5657,7 @@
       <c r="D9" s="11" t="n">
         <v>533</v>
       </c>
-      <c r="E9" s="63" t="inlineStr">
+      <c r="E9" s="64" t="inlineStr">
         <is>
           <t>Ancho cortado en el PDF: confirmar 20 o 22 cm</t>
         </is>
@@ -5439,7 +5723,7 @@
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="63" t="inlineStr">
+      <c r="E13" s="64" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -5454,7 +5738,7 @@
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="63" t="inlineStr">
+      <c r="E14" s="64" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -5656,7 +5940,7 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="63" t="inlineStr">
+      <c r="E26" s="64" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -5806,7 +6090,7 @@
       <c r="E35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="inlineStr">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>Cabezales: CBZ 01 70x70x65   |   CBZ 02 129x70x70   |   CBZ 03 144x70x70</t>
         </is>
@@ -5827,7 +6111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF33"/>
+  <dimension ref="A1:AF34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6403,31 +6687,27 @@
         <v/>
       </c>
       <c r="L6" s="10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M6" s="25">
         <f>IF(NOT(ISNUMBER(H6)),"---",IF(H6&lt;=0,"---",IF(H6*100/(Datos_vigas!$B$8*AB6*K6^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H6*100/(Datos_vigas!$B$8*AB6*K6^2*Datos_vigas!$B$5)))*AB6*K6*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J6*K6))))</f>
         <v/>
       </c>
       <c r="N6" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P6" s="25">
         <f>IF(NOT(ISNUMBER(I6)),"---",IF(I6&lt;=0,"---",IF(I6*100/(Datos_vigas!$B$8*AC6*K6^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I6*100/(Datos_vigas!$B$8*AC6*K6^2*Datos_vigas!$B$5)))*AC6*K6*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J6*K6))))</f>
         <v/>
       </c>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="R6" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
+      <c r="Q6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="10" t="n">
+        <v>25</v>
       </c>
       <c r="S6" s="25">
         <f>F6/(J6*0.85*K6)</f>
@@ -6474,7 +6754,7 @@
         <v/>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>2.664</v>
+        <v>2.689</v>
       </c>
       <c r="AE6" s="10" t="n">
         <v>2.6</v>
@@ -6585,7 +6865,7 @@
         <v/>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>2.075</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" s="10" t="n">
         <v>2.6</v>
@@ -6807,7 +7087,7 @@
         <v/>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>1.552</v>
+        <v>1.549</v>
       </c>
       <c r="AE9" s="10" t="n">
         <v>2.6</v>
@@ -6820,11 +7100,11 @@
       <c r="A10" s="26" t="n"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>VI 07a</t>
+          <t>VI 06</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.37</v>
+        <v>14</v>
       </c>
       <c r="D10" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD10+Datos_vigas!$B$7*J10*L10/10000+Datos_vigas!$B$16*AE10)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD10)</f>
@@ -6862,20 +7142,24 @@
         <v/>
       </c>
       <c r="N10" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="P10" s="25">
         <f>IF(NOT(ISNUMBER(I10)),"---",IF(I10&lt;=0,"---",IF(I10*100/(Datos_vigas!$B$8*AC10*K10^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I10*100/(Datos_vigas!$B$8*AC10*K10^2*Datos_vigas!$B$5)))*AC10*K10*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J10*K10))))</f>
         <v/>
       </c>
-      <c r="Q10" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" s="10" t="n">
-        <v>12</v>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
       </c>
       <c r="S10" s="25">
         <f>F10/(J10*0.85*K10)</f>
@@ -6886,10 +7170,10 @@
         <v/>
       </c>
       <c r="U10" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W10" s="11">
         <f>IF(OR(M10="REVISAR",P10="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M10&lt;&gt;"REVISAR",P10&lt;&gt;"REVISAR",IF(ISNUMBER(M10),N10*PI()*(O10/10)^2/4&gt;=M10,TRUE),IF(ISNUMBER(P10),Q10*PI()*(R10/10)^2/4&gt;=P10,TRUE),IF(ISNUMBER(M10),M10&lt;=0.0163*AB10*K10,TRUE),IF(ISNUMBER(P10),P10&lt;=0.0163*AC10*K10,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F10&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J10*K10+2*PI()*(U10/10)^2/4*Datos_vigas!$B$6*K10/V10)),"NO VERIF. CORTE",IF(NOT(L10&gt;=C10*100/VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -6897,7 +7181,7 @@
       </c>
       <c r="X10" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Armadura en 2 capas (rec. 6 cm).</t>
         </is>
       </c>
       <c r="Y10" s="10" t="inlineStr">
@@ -6907,7 +7191,7 @@
       </c>
       <c r="Z10" s="10" t="inlineStr">
         <is>
-          <t>Invertida</t>
+          <t>Colgante</t>
         </is>
       </c>
       <c r="AA10" s="10" t="n">
@@ -6922,24 +7206,24 @@
         <v/>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>0.75</v>
+        <v>1.549</v>
       </c>
       <c r="AE10" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF10" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="26" t="n"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>VI 07b</t>
+          <t>VI 07a</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>4.03</v>
+        <v>3.37</v>
       </c>
       <c r="D11" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD11+Datos_vigas!$B$7*J11*L11/10000+Datos_vigas!$B$16*AE11)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD11)</f>
@@ -7037,7 +7321,7 @@
         <v/>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AE11" s="10" t="n">
         <v>2.6</v>
@@ -7050,11 +7334,11 @@
       <c r="A12" s="26" t="n"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>VI 07c</t>
+          <t>VI 07b</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>8.6</v>
+        <v>4.03</v>
       </c>
       <c r="D12" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD12+Datos_vigas!$B$7*J12*L12/10000+Datos_vigas!$B$16*AE12)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD12)</f>
@@ -7092,20 +7376,20 @@
         <v/>
       </c>
       <c r="N12" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P12" s="25">
         <f>IF(NOT(ISNUMBER(I12)),"---",IF(I12&lt;=0,"---",IF(I12*100/(Datos_vigas!$B$8*AC12*K12^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I12*100/(Datos_vigas!$B$8*AC12*K12^2*Datos_vigas!$B$5)))*AC12*K12*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J12*K12))))</f>
         <v/>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S12" s="25">
         <f>F12/(J12*0.85*K12)</f>
@@ -7116,10 +7400,10 @@
         <v/>
       </c>
       <c r="U12" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W12" s="11">
         <f>IF(OR(M12="REVISAR",P12="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M12&lt;&gt;"REVISAR",P12&lt;&gt;"REVISAR",IF(ISNUMBER(M12),N12*PI()*(O12/10)^2/4&gt;=M12,TRUE),IF(ISNUMBER(P12),Q12*PI()*(R12/10)^2/4&gt;=P12,TRUE),IF(ISNUMBER(M12),M12&lt;=0.0163*AB12*K12,TRUE),IF(ISNUMBER(P12),P12&lt;=0.0163*AC12*K12,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F12&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J12*K12+2*PI()*(U12/10)^2/4*Datos_vigas!$B$6*K12/V12)),"NO VERIF. CORTE",IF(NOT(L12&gt;=C12*100/VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -7127,12 +7411,12 @@
       </c>
       <c r="X12" s="13" t="inlineStr">
         <is>
-          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
         </is>
       </c>
       <c r="Y12" s="10" t="inlineStr">
         <is>
-          <t>Empotrada-apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z12" s="10" t="inlineStr">
@@ -7152,24 +7436,24 @@
         <v/>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="26" t="n"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>VI 08a</t>
+          <t>VI 07c</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="D13" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD13+Datos_vigas!$B$7*J13*L13/10000+Datos_vigas!$B$16*AE13)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD13)</f>
@@ -7207,20 +7491,20 @@
         <v/>
       </c>
       <c r="N13" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P13" s="25">
         <f>IF(NOT(ISNUMBER(I13)),"---",IF(I13&lt;=0,"---",IF(I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)))*AC13*K13*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J13*K13))))</f>
         <v/>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S13" s="25">
         <f>F13/(J13*0.85*K13)</f>
@@ -7231,24 +7515,28 @@
         <v/>
       </c>
       <c r="U13" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W13" s="11">
         <f>IF(OR(M13="REVISAR",P13="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M13&lt;&gt;"REVISAR",P13&lt;&gt;"REVISAR",IF(ISNUMBER(M13),N13*PI()*(O13/10)^2/4&gt;=M13,TRUE),IF(ISNUMBER(P13),Q13*PI()*(R13/10)^2/4&gt;=P13,TRUE),IF(ISNUMBER(M13),M13&lt;=0.0163*AB13*K13,TRUE),IF(ISNUMBER(P13),P13&lt;=0.0163*AC13*K13,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F13&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J13*K13+2*PI()*(U13/10)^2/4*Datos_vigas!$B$6*K13/V13)),"NO VERIF. CORTE",IF(NOT(L13&gt;=C13*100/VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X13" s="11" t="n"/>
+      <c r="X13" s="13" t="inlineStr">
+        <is>
+          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+        </is>
+      </c>
       <c r="Y13" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Empotrada-apoyada</t>
         </is>
       </c>
       <c r="Z13" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA13" s="10" t="n">
@@ -7263,24 +7551,24 @@
         <v/>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>1.075</v>
+        <v>3.71</v>
       </c>
       <c r="AE13" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="26" t="n"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>VI 08b</t>
+          <t>VI 08a</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4.85</v>
+        <v>3.65</v>
       </c>
       <c r="D14" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD14+Datos_vigas!$B$7*J14*L14/10000+Datos_vigas!$B$16*AE14)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD14)</f>
@@ -7374,7 +7662,7 @@
         <v/>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>1.075</v>
+        <v>1.065</v>
       </c>
       <c r="AE14" s="10" t="n">
         <v>2.6</v>
@@ -7387,11 +7675,11 @@
       <c r="A15" s="26" t="n"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>VI 09</t>
+          <t>VI 08b</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>4.85</v>
+        <v>4.87</v>
       </c>
       <c r="D15" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD15+Datos_vigas!$B$7*J15*L15/10000+Datos_vigas!$B$16*AE15)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD15)</f>
@@ -7438,15 +7726,11 @@
         <f>IF(NOT(ISNUMBER(I15)),"---",IF(I15&lt;=0,"---",IF(I15*100/(Datos_vigas!$B$8*AC15*K15^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I15*100/(Datos_vigas!$B$8*AC15*K15^2*Datos_vigas!$B$5)))*AC15*K15*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J15*K15))))</f>
         <v/>
       </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="R15" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
+      <c r="Q15" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="S15" s="25">
         <f>F15/(J15*0.85*K15)</f>
@@ -7469,7 +7753,7 @@
       <c r="X15" s="11" t="n"/>
       <c r="Y15" s="10" t="inlineStr">
         <is>
-          <t>Simplemente apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z15" s="10" t="inlineStr">
@@ -7489,7 +7773,7 @@
         <v/>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>1.552</v>
+        <v>1.065</v>
       </c>
       <c r="AE15" s="10" t="n">
         <v>2.6</v>
@@ -7502,11 +7786,11 @@
       <c r="A16" s="26" t="n"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>VI 10a</t>
+          <t>VI 09</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2.55</v>
+        <v>4.87</v>
       </c>
       <c r="D16" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD16+Datos_vigas!$B$7*J16*L16/10000+Datos_vigas!$B$16*AE16)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD16)</f>
@@ -7553,11 +7837,15 @@
         <f>IF(NOT(ISNUMBER(I16)),"---",IF(I16&lt;=0,"---",IF(I16*100/(Datos_vigas!$B$8*AC16*K16^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I16*100/(Datos_vigas!$B$8*AC16*K16^2*Datos_vigas!$B$5)))*AC16*K16*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J16*K16))))</f>
         <v/>
       </c>
-      <c r="Q16" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" s="10" t="n">
-        <v>12</v>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
       </c>
       <c r="S16" s="25">
         <f>F16/(J16*0.85*K16)</f>
@@ -7580,7 +7868,7 @@
       <c r="X16" s="11" t="n"/>
       <c r="Y16" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Simplemente apoyada</t>
         </is>
       </c>
       <c r="Z16" s="10" t="inlineStr">
@@ -7600,7 +7888,7 @@
         <v/>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>0</v>
+        <v>1.549</v>
       </c>
       <c r="AE16" s="10" t="n">
         <v>2.6</v>
@@ -7613,11 +7901,11 @@
       <c r="A17" s="26" t="n"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>VI 10b</t>
+          <t>VI 10a</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="D17" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD17+Datos_vigas!$B$7*J17*L17/10000+Datos_vigas!$B$16*AE17)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD17)</f>
@@ -7711,7 +7999,7 @@
         <v/>
       </c>
       <c r="AD17" s="10" t="n">
-        <v>1.825</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="10" t="n">
         <v>2.6</v>
@@ -7724,11 +8012,11 @@
       <c r="A18" s="26" t="n"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>VI 10c</t>
+          <t>VI 10b</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD18+Datos_vigas!$B$7*J18*L18/10000+Datos_vigas!$B$16*AE18)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD18)</f>
@@ -7822,7 +8110,7 @@
         <v/>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>0</v>
+        <v>1.825</v>
       </c>
       <c r="AE18" s="10" t="n">
         <v>2.6</v>
@@ -7835,11 +8123,11 @@
       <c r="A19" s="26" t="n"/>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>VI 11a</t>
+          <t>VI 10c</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>7.68</v>
+        <v>3.6</v>
       </c>
       <c r="D19" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD19+Datos_vigas!$B$7*J19*L19/10000+Datos_vigas!$B$16*AE19)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD19)</f>
@@ -7877,20 +8165,20 @@
         <v/>
       </c>
       <c r="N19" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P19" s="25">
         <f>IF(NOT(ISNUMBER(I19)),"---",IF(I19&lt;=0,"---",IF(I19*100/(Datos_vigas!$B$8*AC19*K19^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I19*100/(Datos_vigas!$B$8*AC19*K19^2*Datos_vigas!$B$5)))*AC19*K19*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J19*K19))))</f>
         <v/>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S19" s="25">
         <f>F19/(J19*0.85*K19)</f>
@@ -7904,25 +8192,21 @@
         <v>6</v>
       </c>
       <c r="V19" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W19" s="11">
         <f>IF(OR(M19="REVISAR",P19="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M19&lt;&gt;"REVISAR",P19&lt;&gt;"REVISAR",IF(ISNUMBER(M19),N19*PI()*(O19/10)^2/4&gt;=M19,TRUE),IF(ISNUMBER(P19),Q19*PI()*(R19/10)^2/4&gt;=P19,TRUE),IF(ISNUMBER(M19),M19&lt;=0.0163*AB19*K19,TRUE),IF(ISNUMBER(P19),P19&lt;=0.0163*AC19*K19,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F19&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J19*K19+2*PI()*(U19/10)^2/4*Datos_vigas!$B$6*K19/V19)),"NO VERIF. CORTE",IF(NOT(L19&gt;=C19*100/VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X19" s="13" t="inlineStr">
-        <is>
-          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
-        </is>
-      </c>
+      <c r="X19" s="11" t="n"/>
       <c r="Y19" s="10" t="inlineStr">
         <is>
-          <t>Empotrada-apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z19" s="10" t="inlineStr">
         <is>
-          <t>Invertida</t>
+          <t>Colgante</t>
         </is>
       </c>
       <c r="AA19" s="10" t="n">
@@ -7937,7 +8221,7 @@
         <v/>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>1.825</v>
+        <v>0</v>
       </c>
       <c r="AE19" s="10" t="n">
         <v>2.6</v>
@@ -7950,11 +8234,11 @@
       <c r="A20" s="26" t="n"/>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>VI 11b</t>
+          <t>VI 11a</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3.45</v>
+        <v>7.68</v>
       </c>
       <c r="D20" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD20+Datos_vigas!$B$7*J20*L20/10000+Datos_vigas!$B$16*AE20)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD20)</f>
@@ -7992,20 +8276,20 @@
         <v/>
       </c>
       <c r="N20" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P20" s="25">
         <f>IF(NOT(ISNUMBER(I20)),"---",IF(I20&lt;=0,"---",IF(I20*100/(Datos_vigas!$B$8*AC20*K20^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I20*100/(Datos_vigas!$B$8*AC20*K20^2*Datos_vigas!$B$5)))*AC20*K20*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J20*K20))))</f>
         <v/>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S20" s="25">
         <f>F20/(J20*0.85*K20)</f>
@@ -8019,7 +8303,7 @@
         <v>6</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W20" s="11">
         <f>IF(OR(M20="REVISAR",P20="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M20&lt;&gt;"REVISAR",P20&lt;&gt;"REVISAR",IF(ISNUMBER(M20),N20*PI()*(O20/10)^2/4&gt;=M20,TRUE),IF(ISNUMBER(P20),Q20*PI()*(R20/10)^2/4&gt;=P20,TRUE),IF(ISNUMBER(M20),M20&lt;=0.0163*AB20*K20,TRUE),IF(ISNUMBER(P20),P20&lt;=0.0163*AC20*K20,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F20&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J20*K20+2*PI()*(U20/10)^2/4*Datos_vigas!$B$6*K20/V20)),"NO VERIF. CORTE",IF(NOT(L20&gt;=C20*100/VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -8027,12 +8311,12 @@
       </c>
       <c r="X20" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
         </is>
       </c>
       <c r="Y20" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Empotrada-apoyada</t>
         </is>
       </c>
       <c r="Z20" s="10" t="inlineStr">
@@ -8052,7 +8336,7 @@
         <v/>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>0</v>
+        <v>1.825</v>
       </c>
       <c r="AE20" s="10" t="n">
         <v>2.6</v>
@@ -8065,11 +8349,11 @@
       <c r="A21" s="26" t="n"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>VI 11c</t>
+          <t>VI 11b</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>5.02</v>
+        <v>3.45</v>
       </c>
       <c r="D21" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD21+Datos_vigas!$B$7*J21*L21/10000+Datos_vigas!$B$16*AE21)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD21)</f>
@@ -8167,7 +8451,7 @@
         <v/>
       </c>
       <c r="AD21" s="10" t="n">
-        <v>1.552</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="10" t="n">
         <v>2.6</v>
@@ -8180,11 +8464,11 @@
       <c r="A22" s="26" t="n"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>VCH 03a</t>
+          <t>VI 11c</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3.83</v>
+        <v>5.02</v>
       </c>
       <c r="D22" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD22+Datos_vigas!$B$7*J22*L22/10000+Datos_vigas!$B$16*AE22)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD22)</f>
@@ -8208,14 +8492,14 @@
         <v/>
       </c>
       <c r="J22" s="10" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="K22" s="11">
         <f>L22-AF22</f>
         <v/>
       </c>
       <c r="L22" s="10" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="M22" s="25">
         <f>IF(NOT(ISNUMBER(H22)),"---",IF(H22&lt;=0,"---",IF(H22*100/(Datos_vigas!$B$8*AB22*K22^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H22*100/(Datos_vigas!$B$8*AB22*K22^2*Datos_vigas!$B$5)))*AB22*K22*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J22*K22))))</f>
@@ -8225,17 +8509,17 @@
         <v>3</v>
       </c>
       <c r="O22" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P22" s="25">
         <f>IF(NOT(ISNUMBER(I22)),"---",IF(I22&lt;=0,"---",IF(I22*100/(Datos_vigas!$B$8*AC22*K22^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I22*100/(Datos_vigas!$B$8*AC22*K22^2*Datos_vigas!$B$5)))*AC22*K22*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J22*K22))))</f>
         <v/>
       </c>
       <c r="Q22" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S22" s="25">
         <f>F22/(J22*0.85*K22)</f>
@@ -8246,10 +8530,10 @@
         <v/>
       </c>
       <c r="U22" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="W22" s="11">
         <f>IF(OR(M22="REVISAR",P22="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M22&lt;&gt;"REVISAR",P22&lt;&gt;"REVISAR",IF(ISNUMBER(M22),N22*PI()*(O22/10)^2/4&gt;=M22,TRUE),IF(ISNUMBER(P22),Q22*PI()*(R22/10)^2/4&gt;=P22,TRUE),IF(ISNUMBER(M22),M22&lt;=0.0163*AB22*K22,TRUE),IF(ISNUMBER(P22),P22&lt;=0.0163*AC22*K22,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F22&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J22*K22+2*PI()*(U22/10)^2/4*Datos_vigas!$B$6*K22/V22)),"NO VERIF. CORTE",IF(NOT(L22&gt;=C22*100/VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -8257,7 +8541,7 @@
       </c>
       <c r="X22" s="13" t="inlineStr">
         <is>
-          <t>Excede cuantia maxima y no llega a la altura minima por flecha. Revisar el ancho tributario real. Separacion de estribos menor a 10 cm: revisar constructividad.</t>
+          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
         </is>
       </c>
       <c r="Y22" s="10" t="inlineStr">
@@ -8267,7 +8551,7 @@
       </c>
       <c r="Z22" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA22" s="10" t="n">
@@ -8282,7 +8566,7 @@
         <v/>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>2.075</v>
+        <v>1.549</v>
       </c>
       <c r="AE22" s="10" t="n">
         <v>2.6</v>
@@ -8295,11 +8579,11 @@
       <c r="A23" s="26" t="n"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>VCH 03b</t>
+          <t>VCH 03a</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2.15</v>
+        <v>3.71</v>
       </c>
       <c r="D23" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD23+Datos_vigas!$B$7*J23*L23/10000+Datos_vigas!$B$16*AE23)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD23)</f>
@@ -8337,20 +8621,20 @@
         <v/>
       </c>
       <c r="N23" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P23" s="25">
         <f>IF(NOT(ISNUMBER(I23)),"---",IF(I23&lt;=0,"---",IF(I23*100/(Datos_vigas!$B$8*AC23*K23^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I23*100/(Datos_vigas!$B$8*AC23*K23^2*Datos_vigas!$B$5)))*AC23*K23*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J23*K23))))</f>
         <v/>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S23" s="25">
         <f>F23/(J23*0.85*K23)</f>
@@ -8372,7 +8656,7 @@
       </c>
       <c r="X23" s="13" t="inlineStr">
         <is>
-          <t>Separacion de estribos menor a 10 cm: revisar constructividad.</t>
+          <t>Excede cuantia maxima y no llega a la altura minima por flecha. Revisar el ancho tributario real. Separacion de estribos menor a 10 cm: revisar constructividad.</t>
         </is>
       </c>
       <c r="Y23" s="10" t="inlineStr">
@@ -8397,7 +8681,7 @@
         <v/>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>2.075</v>
+        <v>2.1</v>
       </c>
       <c r="AE23" s="10" t="n">
         <v>2.6</v>
@@ -8407,251 +8691,251 @@
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="27" t="n"/>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>VCH 03b</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D24" s="24">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD24+Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*AE24)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="24">
+        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,4,0)*D24*C24</f>
+        <v/>
+      </c>
+      <c r="G24" s="24">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="24">
+        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,2,0)*D24*C24^2</f>
+        <v/>
+      </c>
+      <c r="I24" s="24">
+        <f>IF(VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)*D24*C24^2)</f>
+        <v/>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K24" s="11">
+        <f>L24-AF24</f>
+        <v/>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="M24" s="25">
+        <f>IF(NOT(ISNUMBER(H24)),"---",IF(H24&lt;=0,"---",IF(H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)))*AB24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" s="25">
+        <f>IF(NOT(ISNUMBER(I24)),"---",IF(I24&lt;=0,"---",IF(I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)))*AC24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S24" s="25">
+        <f>F24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="T24" s="25">
+        <f>G24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="V24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W24" s="11">
+        <f>IF(OR(M24="REVISAR",P24="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M24&lt;&gt;"REVISAR",P24&lt;&gt;"REVISAR",IF(ISNUMBER(M24),N24*PI()*(O24/10)^2/4&gt;=M24,TRUE),IF(ISNUMBER(P24),Q24*PI()*(R24/10)^2/4&gt;=P24,TRUE),IF(ISNUMBER(M24),M24&lt;=0.0163*AB24*K24,TRUE),IF(ISNUMBER(P24),P24&lt;=0.0163*AC24*K24,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F24&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J24*K24+2*PI()*(U24/10)^2/4*Datos_vigas!$B$6*K24/V24)),"NO VERIF. CORTE",IF(NOT(L24&gt;=C24*100/VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X24" s="13" t="inlineStr">
+        <is>
+          <t>Separacion de estribos menor a 10 cm: revisar constructividad.</t>
+        </is>
+      </c>
+      <c r="Y24" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="Z24" s="10" t="inlineStr">
+        <is>
+          <t>Colgante</t>
+        </is>
+      </c>
+      <c r="AA24" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB24" s="11">
+        <f>IF(Z24="Colgante",MIN(C24*100/4,J24+16*AA24),J24)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="11">
+        <f>IF(Z24="Invertida",MIN(C24*100/4,J24+16*AA24),J24)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE24" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF24" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>VCH 05</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C25" s="15" t="n">
         <v>3.71</v>
       </c>
-      <c r="D24" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD24+Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*AE24)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD24)</f>
-        <v/>
-      </c>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="29">
-        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,4,0)*D24*C24</f>
-        <v/>
-      </c>
-      <c r="G24" s="29">
-        <f>F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="29">
-        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,2,0)*D24*C24^2</f>
-        <v/>
-      </c>
-      <c r="I24" s="29">
-        <f>IF(VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)*D24*C24^2)</f>
-        <v/>
-      </c>
-      <c r="J24" s="17" t="n">
+      <c r="D25" s="29">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AE25)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="29">
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="29">
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2</f>
+        <v/>
+      </c>
+      <c r="I25" s="29">
+        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2)</f>
+        <v/>
+      </c>
+      <c r="J25" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="K24" s="18">
-        <f>L24-AF24</f>
-        <v/>
-      </c>
-      <c r="L24" s="17" t="n">
+      <c r="K25" s="18">
+        <f>L25-AF25</f>
+        <v/>
+      </c>
+      <c r="L25" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="M24" s="30">
-        <f>IF(NOT(ISNUMBER(H24)),"---",IF(H24&lt;=0,"---",IF(H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)))*AB24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
-        <v/>
-      </c>
-      <c r="N24" s="17" t="n">
+      <c r="M25" s="30">
+        <f>IF(NOT(ISNUMBER(H25)),"---",IF(H25&lt;=0,"---",IF(H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)))*AB25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="17" t="n">
+      <c r="O25" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="P24" s="30">
-        <f>IF(NOT(ISNUMBER(I24)),"---",IF(I24&lt;=0,"---",IF(I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)))*AC24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="17" t="inlineStr">
+      <c r="P25" s="30">
+        <f>IF(NOT(ISNUMBER(I25)),"---",IF(I25&lt;=0,"---",IF(I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)))*AC25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="R24" s="17" t="inlineStr">
+      <c r="R25" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="S24" s="30">
-        <f>F24/(J24*0.85*K24)</f>
-        <v/>
-      </c>
-      <c r="T24" s="30">
-        <f>G24/(J24*0.85*K24)</f>
-        <v/>
-      </c>
-      <c r="U24" s="17" t="n">
+      <c r="S25" s="30">
+        <f>F25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="T25" s="30">
+        <f>G25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="V24" s="17" t="n">
+      <c r="V25" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="W24" s="18">
-        <f>IF(OR(M24="REVISAR",P24="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M24&lt;&gt;"REVISAR",P24&lt;&gt;"REVISAR",IF(ISNUMBER(M24),N24*PI()*(O24/10)^2/4&gt;=M24,TRUE),IF(ISNUMBER(P24),Q24*PI()*(R24/10)^2/4&gt;=P24,TRUE),IF(ISNUMBER(M24),M24&lt;=0.0163*AB24*K24,TRUE),IF(ISNUMBER(P24),P24&lt;=0.0163*AC24*K24,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F24&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J24*K24+2*PI()*(U24/10)^2/4*Datos_vigas!$B$6*K24/V24)),"NO VERIF. CORTE",IF(NOT(L24&gt;=C24*100/VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X24" s="18" t="n"/>
-      <c r="Y24" s="17" t="inlineStr">
+      <c r="W25" s="18">
+        <f>IF(OR(M25="REVISAR",P25="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M25&lt;&gt;"REVISAR",P25&lt;&gt;"REVISAR",IF(ISNUMBER(M25),N25*PI()*(O25/10)^2/4&gt;=M25,TRUE),IF(ISNUMBER(P25),Q25*PI()*(R25/10)^2/4&gt;=P25,TRUE),IF(ISNUMBER(M25),M25&lt;=0.0163*AB25*K25,TRUE),IF(ISNUMBER(P25),P25&lt;=0.0163*AC25*K25,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F25&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J25*K25+2*PI()*(U25/10)^2/4*Datos_vigas!$B$6*K25/V25)),"NO VERIF. CORTE",IF(NOT(L25&gt;=C25*100/VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X25" s="18" t="n"/>
+      <c r="Y25" s="17" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="Z24" s="17" t="inlineStr">
+      <c r="Z25" s="17" t="inlineStr">
         <is>
           <t>Colgante</t>
         </is>
       </c>
-      <c r="AA24" s="17" t="n">
+      <c r="AA25" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="AB24" s="18">
-        <f>IF(Z24="Colgante",MIN(C24*100/4,J24+16*AA24),J24)</f>
-        <v/>
-      </c>
-      <c r="AC24" s="18">
-        <f>IF(Z24="Invertida",MIN(C24*100/4,J24+16*AA24),J24)</f>
-        <v/>
-      </c>
-      <c r="AD24" s="17" t="n">
+      <c r="AB25" s="18">
+        <f>IF(Z25="Colgante",MIN(C25*100/4,J25+16*AA25),J25)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="18">
+        <f>IF(Z25="Invertida",MIN(C25*100/4,J25+16*AA25),J25)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" s="17" t="n">
+      <c r="AE25" s="17" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF24" s="17" t="n">
+      <c r="AF25" s="17" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>TECHO</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>VI 12</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C26" s="8" t="n">
         <v>9.9</v>
       </c>
-      <c r="D25" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AE25)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD25)</f>
-        <v/>
-      </c>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="24">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="24">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2</f>
-        <v/>
-      </c>
-      <c r="I25" s="24">
-        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2)</f>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K25" s="11">
-        <f>L25-AF25</f>
-        <v/>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="M25" s="25">
-        <f>IF(NOT(ISNUMBER(H25)),"---",IF(H25&lt;=0,"---",IF(H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)))*AB25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
-        <v/>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="P25" s="25">
-        <f>IF(NOT(ISNUMBER(I25)),"---",IF(I25&lt;=0,"---",IF(I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)))*AC25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="S25" s="25">
-        <f>F25/(J25*0.85*K25)</f>
-        <v/>
-      </c>
-      <c r="T25" s="25">
-        <f>G25/(J25*0.85*K25)</f>
-        <v/>
-      </c>
-      <c r="U25" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="V25" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" s="11">
-        <f>IF(OR(M25="REVISAR",P25="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M25&lt;&gt;"REVISAR",P25&lt;&gt;"REVISAR",IF(ISNUMBER(M25),N25*PI()*(O25/10)^2/4&gt;=M25,TRUE),IF(ISNUMBER(P25),Q25*PI()*(R25/10)^2/4&gt;=P25,TRUE),IF(ISNUMBER(M25),M25&lt;=0.0163*AB25*K25,TRUE),IF(ISNUMBER(P25),P25&lt;=0.0163*AC25*K25,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F25&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J25*K25+2*PI()*(U25/10)^2/4*Datos_vigas!$B$6*K25/V25)),"NO VERIF. CORTE",IF(NOT(L25&gt;=C25*100/VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X25" s="13" t="inlineStr">
-        <is>
-          <t>Armadura en 2 capas (rec. 6 cm).</t>
-        </is>
-      </c>
-      <c r="Y25" s="10" t="inlineStr">
-        <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="Z25" s="10" t="inlineStr">
-        <is>
-          <t>Colgante</t>
-        </is>
-      </c>
-      <c r="AA25" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB25" s="11">
-        <f>IF(Z25="Colgante",MIN(C25*100/4,J25+16*AA25),J25)</f>
-        <v/>
-      </c>
-      <c r="AC25" s="11">
-        <f>IF(Z25="Invertida",MIN(C25*100/4,J25+16*AA25),J25)</f>
-        <v/>
-      </c>
-      <c r="AD25" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="10" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="26" t="n"/>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>VI 13a</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="D26" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AE26)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD26)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AE26)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD26)</f>
         <v/>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -8679,7 +8963,7 @@
         <v/>
       </c>
       <c r="L26" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M26" s="25">
         <f>IF(NOT(ISNUMBER(H26)),"---",IF(H26&lt;=0,"---",IF(H26*100/(Datos_vigas!$B$8*AB26*K26^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H26*100/(Datos_vigas!$B$8*AB26*K26^2*Datos_vigas!$B$5)))*AB26*K26*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J26*K26))))</f>
@@ -8689,17 +8973,17 @@
         <v>2</v>
       </c>
       <c r="O26" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P26" s="25">
         <f>IF(NOT(ISNUMBER(I26)),"---",IF(I26&lt;=0,"---",IF(I26*100/(Datos_vigas!$B$8*AC26*K26^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I26*100/(Datos_vigas!$B$8*AC26*K26^2*Datos_vigas!$B$5)))*AC26*K26*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J26*K26))))</f>
         <v/>
       </c>
       <c r="Q26" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R26" s="10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S26" s="25">
         <f>F26/(J26*0.85*K26)</f>
@@ -8710,7 +8994,7 @@
         <v/>
       </c>
       <c r="U26" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V26" s="10" t="n">
         <v>10</v>
@@ -8719,7 +9003,11 @@
         <f>IF(OR(M26="REVISAR",P26="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M26&lt;&gt;"REVISAR",P26&lt;&gt;"REVISAR",IF(ISNUMBER(M26),N26*PI()*(O26/10)^2/4&gt;=M26,TRUE),IF(ISNUMBER(P26),Q26*PI()*(R26/10)^2/4&gt;=P26,TRUE),IF(ISNUMBER(M26),M26&lt;=0.0163*AB26*K26,TRUE),IF(ISNUMBER(P26),P26&lt;=0.0163*AC26*K26,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F26&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J26*K26+2*PI()*(U26/10)^2/4*Datos_vigas!$B$6*K26/V26)),"NO VERIF. CORTE",IF(NOT(L26&gt;=C26*100/VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X26" s="11" t="n"/>
+      <c r="X26" s="13" t="inlineStr">
+        <is>
+          <t>Armadura en 2 capas (rec. 6 cm).</t>
+        </is>
+      </c>
       <c r="Y26" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -8742,27 +9030,27 @@
         <v/>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>3.799</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AF26" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="26" t="n"/>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>VI 13b</t>
+          <t>VI 13a</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="D27" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AE27)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD27)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AE27)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD27)</f>
         <v/>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -8790,27 +9078,27 @@
         <v/>
       </c>
       <c r="L27" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M27" s="25">
         <f>IF(NOT(ISNUMBER(H27)),"---",IF(H27&lt;=0,"---",IF(H27*100/(Datos_vigas!$B$8*AB27*K27^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H27*100/(Datos_vigas!$B$8*AB27*K27^2*Datos_vigas!$B$5)))*AB27*K27*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J27*K27))))</f>
         <v/>
       </c>
       <c r="N27" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P27" s="25">
         <f>IF(NOT(ISNUMBER(I27)),"---",IF(I27&lt;=0,"---",IF(I27*100/(Datos_vigas!$B$8*AC27*K27^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I27*100/(Datos_vigas!$B$8*AC27*K27^2*Datos_vigas!$B$5)))*AC27*K27*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J27*K27))))</f>
         <v/>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="S27" s="25">
         <f>F27/(J27*0.85*K27)</f>
@@ -8824,7 +9112,7 @@
         <v>6</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="W27" s="11">
         <f>IF(OR(M27="REVISAR",P27="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M27&lt;&gt;"REVISAR",P27&lt;&gt;"REVISAR",IF(ISNUMBER(M27),N27*PI()*(O27/10)^2/4&gt;=M27,TRUE),IF(ISNUMBER(P27),Q27*PI()*(R27/10)^2/4&gt;=P27,TRUE),IF(ISNUMBER(M27),M27&lt;=0.0163*AB27*K27,TRUE),IF(ISNUMBER(P27),P27&lt;=0.0163*AC27*K27,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F27&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J27*K27+2*PI()*(U27/10)^2/4*Datos_vigas!$B$6*K27/V27)),"NO VERIF. CORTE",IF(NOT(L27&gt;=C27*100/VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -8853,7 +9141,7 @@
         <v/>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>2.1</v>
+        <v>3.799</v>
       </c>
       <c r="AE27" s="10" t="n">
         <v>1</v>
@@ -8866,14 +9154,14 @@
       <c r="A28" s="26" t="n"/>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>VI 14</t>
+          <t>VI 13b</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="D28" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AE28)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD28)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AE28)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD28)</f>
         <v/>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -8964,7 +9252,7 @@
         <v/>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>1.699</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" s="10" t="n">
         <v>1</v>
@@ -8977,14 +9265,14 @@
       <c r="A29" s="26" t="n"/>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>VI 15a</t>
+          <t>VI 14</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>4.03</v>
+        <v>6</v>
       </c>
       <c r="D29" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AE29)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD29)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AE29)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD29)</f>
         <v/>
       </c>
       <c r="E29" s="11" t="n"/>
@@ -9052,11 +9340,7 @@
         <f>IF(OR(M29="REVISAR",P29="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M29&lt;&gt;"REVISAR",P29&lt;&gt;"REVISAR",IF(ISNUMBER(M29),N29*PI()*(O29/10)^2/4&gt;=M29,TRUE),IF(ISNUMBER(P29),Q29*PI()*(R29/10)^2/4&gt;=P29,TRUE),IF(ISNUMBER(M29),M29&lt;=0.0163*AB29*K29,TRUE),IF(ISNUMBER(P29),P29&lt;=0.0163*AC29*K29,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F29&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J29*K29+2*PI()*(U29/10)^2/4*Datos_vigas!$B$6*K29/V29)),"NO VERIF. CORTE",IF(NOT(L29&gt;=C29*100/VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X29" s="13" t="inlineStr">
-        <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
-        </is>
-      </c>
+      <c r="X29" s="11" t="n"/>
       <c r="Y29" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -9064,7 +9348,7 @@
       </c>
       <c r="Z29" s="10" t="inlineStr">
         <is>
-          <t>Invertida</t>
+          <t>Colgante</t>
         </is>
       </c>
       <c r="AA29" s="10" t="n">
@@ -9079,7 +9363,7 @@
         <v/>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0</v>
+        <v>1.699</v>
       </c>
       <c r="AE29" s="10" t="n">
         <v>1</v>
@@ -9092,14 +9376,14 @@
       <c r="A30" s="26" t="n"/>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>VI 15b</t>
+          <t>VI 15a</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4.85</v>
+        <v>4.03</v>
       </c>
       <c r="D30" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AE30)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD30)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AE30)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD30)</f>
         <v/>
       </c>
       <c r="E30" s="11" t="n"/>
@@ -9194,7 +9478,7 @@
         <v/>
       </c>
       <c r="AD30" s="10" t="n">
-        <v>1.699</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="10" t="n">
         <v>1</v>
@@ -9207,14 +9491,14 @@
       <c r="A31" s="26" t="n"/>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>VI 16a</t>
+          <t>VI 15b</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>3.58</v>
+        <v>4.85</v>
       </c>
       <c r="D31" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AE31)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD31)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AE31)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD31)</f>
         <v/>
       </c>
       <c r="E31" s="11" t="n"/>
@@ -9282,7 +9566,11 @@
         <f>IF(OR(M31="REVISAR",P31="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M31&lt;&gt;"REVISAR",P31&lt;&gt;"REVISAR",IF(ISNUMBER(M31),N31*PI()*(O31/10)^2/4&gt;=M31,TRUE),IF(ISNUMBER(P31),Q31*PI()*(R31/10)^2/4&gt;=P31,TRUE),IF(ISNUMBER(M31),M31&lt;=0.0163*AB31*K31,TRUE),IF(ISNUMBER(P31),P31&lt;=0.0163*AC31*K31,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F31&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J31*K31+2*PI()*(U31/10)^2/4*Datos_vigas!$B$6*K31/V31)),"NO VERIF. CORTE",IF(NOT(L31&gt;=C31*100/VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X31" s="11" t="n"/>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+        </is>
+      </c>
       <c r="Y31" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -9290,7 +9578,7 @@
       </c>
       <c r="Z31" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA31" s="10" t="n">
@@ -9318,14 +9606,14 @@
       <c r="A32" s="26" t="n"/>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>VI 16b</t>
+          <t>VI 16a</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>1.12</v>
+        <v>3.58</v>
       </c>
       <c r="D32" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AE32)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD32)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AE32)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD32)</f>
         <v/>
       </c>
       <c r="E32" s="11" t="n"/>
@@ -9426,130 +9714,241 @@
       </c>
     </row>
     <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="A33" s="26" t="n"/>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>VI 16b</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D33" s="24">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AE33)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="24">
+        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,4,0)*D33*C33</f>
+        <v/>
+      </c>
+      <c r="G33" s="24">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="24">
+        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,2,0)*D33*C33^2</f>
+        <v/>
+      </c>
+      <c r="I33" s="24">
+        <f>IF(VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)*D33*C33^2)</f>
+        <v/>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" s="11">
+        <f>L33-AF33</f>
+        <v/>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="M33" s="25">
+        <f>IF(NOT(ISNUMBER(H33)),"---",IF(H33&lt;=0,"---",IF(H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)))*AB33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P33" s="25">
+        <f>IF(NOT(ISNUMBER(I33)),"---",IF(I33&lt;=0,"---",IF(I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)))*AC33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S33" s="25">
+        <f>F33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="T33" s="25">
+        <f>G33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="U33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="W33" s="11">
+        <f>IF(OR(M33="REVISAR",P33="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M33&lt;&gt;"REVISAR",P33&lt;&gt;"REVISAR",IF(ISNUMBER(M33),N33*PI()*(O33/10)^2/4&gt;=M33,TRUE),IF(ISNUMBER(P33),Q33*PI()*(R33/10)^2/4&gt;=P33,TRUE),IF(ISNUMBER(M33),M33&lt;=0.0163*AB33*K33,TRUE),IF(ISNUMBER(P33),P33&lt;=0.0163*AC33*K33,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F33&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J33*K33+2*PI()*(U33/10)^2/4*Datos_vigas!$B$6*K33/V33)),"NO VERIF. CORTE",IF(NOT(L33&gt;=C33*100/VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="Z33" s="10" t="inlineStr">
+        <is>
+          <t>Colgante</t>
+        </is>
+      </c>
+      <c r="AA33" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB33" s="11">
+        <f>IF(Z33="Colgante",MIN(C33*100/4,J33+16*AA33),J33)</f>
+        <v/>
+      </c>
+      <c r="AC33" s="11">
+        <f>IF(Z33="Invertida",MIN(C33*100/4,J33+16*AA33),J33)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="10" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="AE33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="27" t="n"/>
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>VI 17</t>
         </is>
       </c>
-      <c r="C33" s="15" t="n">
+      <c r="C34" s="15" t="n">
         <v>4.35</v>
       </c>
-      <c r="D33" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AE33)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD33)</f>
-        <v/>
-      </c>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="29">
-        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,4,0)*D33*C33</f>
-        <v/>
-      </c>
-      <c r="G33" s="29">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H33" s="29">
-        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,2,0)*D33*C33^2</f>
-        <v/>
-      </c>
-      <c r="I33" s="29">
-        <f>IF(VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)*D33*C33^2)</f>
-        <v/>
-      </c>
-      <c r="J33" s="17" t="n">
+      <c r="D34" s="29">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD34+Datos_vigas!$B$7*J34*L34/10000+Datos_vigas!$B$16*AE34)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD34)</f>
+        <v/>
+      </c>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="29">
+        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,4,0)*D34*C34</f>
+        <v/>
+      </c>
+      <c r="G34" s="29">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="29">
+        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,2,0)*D34*C34^2</f>
+        <v/>
+      </c>
+      <c r="I34" s="29">
+        <f>IF(VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)*D34*C34^2)</f>
+        <v/>
+      </c>
+      <c r="J34" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="K33" s="18">
-        <f>L33-AF33</f>
-        <v/>
-      </c>
-      <c r="L33" s="17" t="n">
+      <c r="K34" s="18">
+        <f>L34-AF34</f>
+        <v/>
+      </c>
+      <c r="L34" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="M33" s="30">
-        <f>IF(NOT(ISNUMBER(H33)),"---",IF(H33&lt;=0,"---",IF(H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)))*AB33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
-        <v/>
-      </c>
-      <c r="N33" s="17" t="n">
+      <c r="M34" s="30">
+        <f>IF(NOT(ISNUMBER(H34)),"---",IF(H34&lt;=0,"---",IF(H34*100/(Datos_vigas!$B$8*AB34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H34*100/(Datos_vigas!$B$8*AB34*K34^2*Datos_vigas!$B$5)))*AB34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="O33" s="17" t="n">
+      <c r="O34" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="P33" s="30">
-        <f>IF(NOT(ISNUMBER(I33)),"---",IF(I33&lt;=0,"---",IF(I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)))*AC33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
-        <v/>
-      </c>
-      <c r="Q33" s="17" t="inlineStr">
+      <c r="P34" s="30">
+        <f>IF(NOT(ISNUMBER(I34)),"---",IF(I34&lt;=0,"---",IF(I34*100/(Datos_vigas!$B$8*AC34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I34*100/(Datos_vigas!$B$8*AC34*K34^2*Datos_vigas!$B$5)))*AC34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="R33" s="17" t="inlineStr">
+      <c r="R34" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="S33" s="30">
-        <f>F33/(J33*0.85*K33)</f>
-        <v/>
-      </c>
-      <c r="T33" s="30">
-        <f>G33/(J33*0.85*K33)</f>
-        <v/>
-      </c>
-      <c r="U33" s="17" t="n">
+      <c r="S34" s="30">
+        <f>F34/(J34*0.85*K34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="30">
+        <f>G34/(J34*0.85*K34)</f>
+        <v/>
+      </c>
+      <c r="U34" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="V33" s="17" t="n">
+      <c r="V34" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="W33" s="18">
-        <f>IF(OR(M33="REVISAR",P33="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M33&lt;&gt;"REVISAR",P33&lt;&gt;"REVISAR",IF(ISNUMBER(M33),N33*PI()*(O33/10)^2/4&gt;=M33,TRUE),IF(ISNUMBER(P33),Q33*PI()*(R33/10)^2/4&gt;=P33,TRUE),IF(ISNUMBER(M33),M33&lt;=0.0163*AB33*K33,TRUE),IF(ISNUMBER(P33),P33&lt;=0.0163*AC33*K33,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F33&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J33*K33+2*PI()*(U33/10)^2/4*Datos_vigas!$B$6*K33/V33)),"NO VERIF. CORTE",IF(NOT(L33&gt;=C33*100/VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X33" s="18" t="n"/>
-      <c r="Y33" s="17" t="inlineStr">
+      <c r="W34" s="18">
+        <f>IF(OR(M34="REVISAR",P34="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M34&lt;&gt;"REVISAR",P34&lt;&gt;"REVISAR",IF(ISNUMBER(M34),N34*PI()*(O34/10)^2/4&gt;=M34,TRUE),IF(ISNUMBER(P34),Q34*PI()*(R34/10)^2/4&gt;=P34,TRUE),IF(ISNUMBER(M34),M34&lt;=0.0163*AB34*K34,TRUE),IF(ISNUMBER(P34),P34&lt;=0.0163*AC34*K34,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F34&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J34*K34+2*PI()*(U34/10)^2/4*Datos_vigas!$B$6*K34/V34)),"NO VERIF. CORTE",IF(NOT(L34&gt;=C34*100/VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X34" s="18" t="n"/>
+      <c r="Y34" s="17" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="Z33" s="17" t="inlineStr">
+      <c r="Z34" s="17" t="inlineStr">
         <is>
           <t>Colgante</t>
         </is>
       </c>
-      <c r="AA33" s="17" t="n">
+      <c r="AA34" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="AB33" s="18">
-        <f>IF(Z33="Colgante",MIN(C33*100/4,J33+16*AA33),J33)</f>
-        <v/>
-      </c>
-      <c r="AC33" s="18">
-        <f>IF(Z33="Invertida",MIN(C33*100/4,J33+16*AA33),J33)</f>
-        <v/>
-      </c>
-      <c r="AD33" s="17" t="n">
+      <c r="AB34" s="18">
+        <f>IF(Z34="Colgante",MIN(C34*100/4,J34+16*AA34),J34)</f>
+        <v/>
+      </c>
+      <c r="AC34" s="18">
+        <f>IF(Z34="Invertida",MIN(C34*100/4,J34+16*AA34),J34)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AE33" s="17" t="n">
+      <c r="AE34" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="AF33" s="17" t="n">
+      <c r="AF34" s="17" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A4:A24"/>
     <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A25"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A25:A33"/>
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="S2:U2"/>
+    <mergeCell ref="A26:A34"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="V2"/>
     <mergeCell ref="B2:B3"/>
@@ -9561,7 +9960,7 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="W2:W3"/>
   </mergeCells>
-  <conditionalFormatting sqref="W4:W33">
+  <conditionalFormatting sqref="W4:W34">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"VERIFICA"</formula>
     </cfRule>
@@ -9576,13 +9975,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="Y4:Y33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y4:Y34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_vigas!$A$19:$A$23</formula1>
     </dataValidation>
-    <dataValidation sqref="Z4:Z33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Z4:Z34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Invertida,Colgante"</formula1>
     </dataValidation>
-    <dataValidation sqref="O4:O33 R4:R33 U4:U33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O4:O34 R4:R34 U4:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"6,8,10,12,16,20,25"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10691,7 +11090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10946,7 +11345,7 @@
         <v>3.22</v>
       </c>
       <c r="D5" s="37" t="n">
-        <v>22.06</v>
+        <v>22.55</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>30</v>
@@ -10997,7 +11396,7 @@
         <v/>
       </c>
       <c r="R5" s="9" t="n">
-        <v>22.06</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -11076,7 +11475,7 @@
         <v>3.22</v>
       </c>
       <c r="D7" s="39" t="n">
-        <v>20.05</v>
+        <v>20.35</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>15</v>
@@ -11127,7 +11526,7 @@
         <v/>
       </c>
       <c r="R7" s="16" t="n">
-        <v>20.05</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -11210,7 +11609,7 @@
         <v>3.15</v>
       </c>
       <c r="D9" s="37" t="n">
-        <v>29.47</v>
+        <v>29.46</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>15</v>
@@ -11261,7 +11660,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>29.47</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -11340,13 +11739,13 @@
         <v>3.15</v>
       </c>
       <c r="D11" s="37" t="n">
-        <v>10.28</v>
+        <v>15.96</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G11" s="11">
         <f>E11*F11</f>
@@ -11375,7 +11774,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>COL 01 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5). ATENCION: seccion 10x10 leida del plano. Recibe VI 01a (17 t): una columna de 10x10 no puede tomar esa carga. Probablemente VI 01a apoye en la medianera y esto no sea columna.</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O11" s="9">
@@ -11391,7 +11790,7 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>10.28</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -11405,13 +11804,13 @@
         <v>3.15</v>
       </c>
       <c r="D12" s="37" t="n">
-        <v>15.9</v>
+        <v>19.38</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G12" s="11">
         <f>E12*F12</f>
@@ -11440,7 +11839,7 @@
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+          <t>COL 04 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O12" s="9">
@@ -11456,7 +11855,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>15.9</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -11470,13 +11869,13 @@
         <v>3.15</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>32.1</v>
+        <v>27.95</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G13" s="11">
         <f>E13*F13</f>
@@ -11505,7 +11904,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>COL 04 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+          <t>COL 03 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O13" s="9">
@@ -11521,7 +11920,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>32.1</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -11535,13 +11934,13 @@
         <v>3.15</v>
       </c>
       <c r="D14" s="37" t="n">
-        <v>37.27</v>
+        <v>50.09</v>
       </c>
       <c r="E14" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>30</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>15</v>
       </c>
       <c r="G14" s="11">
         <f>E14*F14</f>
@@ -11570,7 +11969,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>COL 03 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O14" s="9">
@@ -11586,145 +11985,80 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>37.27</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="26" t="n"/>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="A15" s="27" t="n"/>
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="15" t="n">
         <v>3.15</v>
       </c>
-      <c r="D15" s="37" t="n">
-        <v>42.22</v>
-      </c>
-      <c r="E15" s="10" t="n">
+      <c r="D15" s="39" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E15" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="18">
         <f>E15*F15</f>
         <v/>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="30">
         <f>Datos_columnas!$B$8*G15</f>
         <v/>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I15" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="K15" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="18">
         <f>FLOOR(MIN(12*J15/10,48*K15/10,MIN(E15,F15)),5)</f>
         <v/>
       </c>
-      <c r="M15" s="11">
+      <c r="M15" s="18">
         <f>IF(D15="","FALTA CARGA",IF(O15&lt;H15,"ARM. INSUFIC.",IF(D15&gt;P15,"NO VERIFICA",IF(D15&gt;0.85*P15,"AL LIMITE",IF(Q15&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
-      <c r="N15" s="13" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="16">
         <f>I15*PI()*(J15/10)^2/4</f>
         <v/>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="16">
         <f>Datos_columnas!$B$7*0.8*(0.85*Datos_columnas!$B$4*(G15-O15)+Datos_columnas!$B$5*O15)/1000</f>
         <v/>
       </c>
-      <c r="Q15" s="38">
+      <c r="Q15" s="40">
         <f>100*C15/(0.3*MIN(E15,F15))</f>
         <v/>
       </c>
-      <c r="R15" s="9" t="n">
-        <v>42.22</v>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="27" t="n"/>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="D16" s="39" t="n">
-        <v>54.89</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="G16" s="18">
-        <f>E16*F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="30">
-        <f>Datos_columnas!$B$8*G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="L16" s="18">
-        <f>FLOOR(MIN(12*J16/10,48*K16/10,MIN(E16,F16)),5)</f>
-        <v/>
-      </c>
-      <c r="M16" s="18">
-        <f>IF(D16="","FALTA CARGA",IF(O16&lt;H16,"ARM. INSUFIC.",IF(D16&gt;P16,"NO VERIFICA",IF(D16&gt;0.85*P16,"AL LIMITE",IF(Q16&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
-        <v/>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
-        </is>
-      </c>
-      <c r="O16" s="16">
-        <f>I16*PI()*(J16/10)^2/4</f>
-        <v/>
-      </c>
-      <c r="P16" s="16">
-        <f>Datos_columnas!$B$7*0.8*(0.85*Datos_columnas!$B$4*(G16-O16)+Datos_columnas!$B$5*O16)/1000</f>
-        <v/>
-      </c>
-      <c r="Q16" s="40">
-        <f>100*C16/(0.3*MIN(E16,F16))</f>
-        <v/>
-      </c>
-      <c r="R16" s="16" t="n">
-        <v>54.89</v>
+      <c r="R15" s="16" t="n">
+        <v>49.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A8:A15"/>
     <mergeCell ref="N2:N3"/>
-    <mergeCell ref="A8:A16"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="H2:J2"/>
@@ -11735,7 +12069,7 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="O2:R2"/>
   </mergeCells>
-  <conditionalFormatting sqref="M4:M16">
+  <conditionalFormatting sqref="M4:M15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"VERIFICA"</formula>
     </cfRule>
@@ -11756,7 +12090,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J16 K4:K16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J15 K4:K15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"6,8,10,12,16,20,25"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12529,7 +12863,7 @@
         <v/>
       </c>
       <c r="J9" s="10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K9" s="11">
         <f>L9-Z9</f>
@@ -12871,41 +13205,84 @@
           <t>VF06a</t>
         </is>
       </c>
-      <c r="B13" s="41" t="n"/>
+      <c r="B13" s="8" t="n">
+        <v>0.23</v>
+      </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n"/>
+      <c r="D13" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J13*L13/10000+Datos_vigas!$B$16*Y13)</f>
+        <v/>
+      </c>
       <c r="E13" s="11" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
-      <c r="J13" s="37" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="37" t="n"/>
-      <c r="M13" s="25" t="n"/>
-      <c r="N13" s="10" t="n"/>
-      <c r="O13" s="10" t="n"/>
-      <c r="P13" s="25" t="n"/>
-      <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="10" t="n"/>
-      <c r="S13" s="25" t="n"/>
-      <c r="T13" s="25" t="n"/>
-      <c r="U13" s="10" t="n"/>
-      <c r="V13" s="10" t="n"/>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>FALTA SECCION</t>
-        </is>
-      </c>
-      <c r="X13" s="13" t="inlineStr">
-        <is>
-          <t>El rotulo figura en el plano pero la cota no resulto legible. Completar b, d y la luz y la fila calcula sola.</t>
-        </is>
-      </c>
+      <c r="F13" s="24">
+        <f>VLOOKUP(C13,Datos_vigas!$A$19:$E$23,4,0)*D13*B13</f>
+        <v/>
+      </c>
+      <c r="G13" s="24">
+        <f>F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>VLOOKUP(C13,Datos_vigas!$A$19:$E$23,2,0)*D13*B13^2</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
+        <f>IF(VLOOKUP(C13,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C13,Datos_vigas!$A$19:$E$23,3,0)*D13*B13^2)</f>
+        <v/>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="11">
+        <f>L13-Z13</f>
+        <v/>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M13" s="25">
+        <f>IF(NOT(ISNUMBER(H13)),"---",IF(H13&lt;=0,"---",IF(H13*100/(Datos_vigas!$B$8*J13*K13^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H13*100/(Datos_vigas!$B$8*J13*K13^2*Datos_vigas!$B$5)))*J13*K13*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J13*K13))))</f>
+        <v/>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" s="25">
+        <f>IF(NOT(ISNUMBER(I13)),"---",IF(I13&lt;=0,"---",IF(I13*100/(Datos_vigas!$B$8*J13*K13^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I13*100/(Datos_vigas!$B$8*J13*K13^2*Datos_vigas!$B$5)))*J13*K13*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J13*K13))))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" s="25">
+        <f>F13/(J13*0.85*K13)</f>
+        <v/>
+      </c>
+      <c r="T13" s="25">
+        <f>G13/(J13*0.85*K13)</f>
+        <v/>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W13" s="11">
+        <f>IF(OR(M13="REVISAR",P13="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M13&lt;&gt;"REVISAR",P13&lt;&gt;"REVISAR",IF(ISNUMBER(M13),N13*PI()*(O13/10)^2/4&gt;=M13,TRUE),IF(ISNUMBER(P13),Q13*PI()*(R13/10)^2/4&gt;=P13,TRUE),IF(ISNUMBER(M13),M13&lt;=0.0163*J13*K13,TRUE),IF(ISNUMBER(P13),P13&lt;=0.0163*J13*K13,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F13&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J13*K13+2*PI()*(U13/10)^2/4*Datos_vigas!$B$6*K13/V13)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X13" s="11" t="n"/>
       <c r="Y13" s="12" t="n">
         <v>3.15</v>
       </c>
@@ -12919,41 +13296,84 @@
           <t>VF06b</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n"/>
+      <c r="B14" s="8" t="n">
+        <v>1.83</v>
+      </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
-      <c r="D14" s="24" t="n"/>
+      <c r="D14" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J14*L14/10000+Datos_vigas!$B$16*Y14)</f>
+        <v/>
+      </c>
       <c r="E14" s="11" t="n"/>
-      <c r="F14" s="24" t="n"/>
-      <c r="G14" s="24" t="n"/>
-      <c r="H14" s="24" t="n"/>
-      <c r="I14" s="24" t="n"/>
-      <c r="J14" s="37" t="n"/>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="37" t="n"/>
-      <c r="M14" s="25" t="n"/>
-      <c r="N14" s="10" t="n"/>
-      <c r="O14" s="10" t="n"/>
-      <c r="P14" s="25" t="n"/>
-      <c r="Q14" s="10" t="n"/>
-      <c r="R14" s="10" t="n"/>
-      <c r="S14" s="25" t="n"/>
-      <c r="T14" s="25" t="n"/>
-      <c r="U14" s="10" t="n"/>
-      <c r="V14" s="10" t="n"/>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>FALTA SECCION</t>
-        </is>
-      </c>
-      <c r="X14" s="13" t="inlineStr">
-        <is>
-          <t>El rotulo figura en el plano pero la cota no resulto legible. Completar b, d y la luz y la fila calcula sola.</t>
-        </is>
-      </c>
+      <c r="F14" s="24">
+        <f>VLOOKUP(C14,Datos_vigas!$A$19:$E$23,4,0)*D14*B14</f>
+        <v/>
+      </c>
+      <c r="G14" s="24">
+        <f>F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="24">
+        <f>VLOOKUP(C14,Datos_vigas!$A$19:$E$23,2,0)*D14*B14^2</f>
+        <v/>
+      </c>
+      <c r="I14" s="24">
+        <f>IF(VLOOKUP(C14,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C14,Datos_vigas!$A$19:$E$23,3,0)*D14*B14^2)</f>
+        <v/>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="11">
+        <f>L14-Z14</f>
+        <v/>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M14" s="25">
+        <f>IF(NOT(ISNUMBER(H14)),"---",IF(H14&lt;=0,"---",IF(H14*100/(Datos_vigas!$B$8*J14*K14^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H14*100/(Datos_vigas!$B$8*J14*K14^2*Datos_vigas!$B$5)))*J14*K14*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J14*K14))))</f>
+        <v/>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" s="25">
+        <f>IF(NOT(ISNUMBER(I14)),"---",IF(I14&lt;=0,"---",IF(I14*100/(Datos_vigas!$B$8*J14*K14^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I14*100/(Datos_vigas!$B$8*J14*K14^2*Datos_vigas!$B$5)))*J14*K14*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J14*K14))))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S14" s="25">
+        <f>F14/(J14*0.85*K14)</f>
+        <v/>
+      </c>
+      <c r="T14" s="25">
+        <f>G14/(J14*0.85*K14)</f>
+        <v/>
+      </c>
+      <c r="U14" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V14" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W14" s="11">
+        <f>IF(OR(M14="REVISAR",P14="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M14&lt;&gt;"REVISAR",P14&lt;&gt;"REVISAR",IF(ISNUMBER(M14),N14*PI()*(O14/10)^2/4&gt;=M14,TRUE),IF(ISNUMBER(P14),Q14*PI()*(R14/10)^2/4&gt;=P14,TRUE),IF(ISNUMBER(M14),M14&lt;=0.0163*J14*K14,TRUE),IF(ISNUMBER(P14),P14&lt;=0.0163*J14*K14,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F14&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J14*K14+2*PI()*(U14/10)^2/4*Datos_vigas!$B$6*K14/V14)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X14" s="11" t="n"/>
       <c r="Y14" s="12" t="n">
         <v>3.15</v>
       </c>
@@ -13373,7 +13793,7 @@
         <v/>
       </c>
       <c r="J19" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K19" s="11">
         <f>L19-Z19</f>
@@ -13387,20 +13807,20 @@
         <v/>
       </c>
       <c r="N19" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P19" s="25">
         <f>IF(NOT(ISNUMBER(I19)),"---",IF(I19&lt;=0,"---",IF(I19*100/(Datos_vigas!$B$8*J19*K19^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I19*100/(Datos_vigas!$B$8*J19*K19^2*Datos_vigas!$B$5)))*J19*K19*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J19*K19))))</f>
         <v/>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S19" s="25">
         <f>F19/(J19*0.85*K19)</f>
@@ -13464,7 +13884,7 @@
         <v/>
       </c>
       <c r="J20" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K20" s="11">
         <f>L20-Z20</f>
@@ -13478,20 +13898,20 @@
         <v/>
       </c>
       <c r="N20" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P20" s="25">
         <f>IF(NOT(ISNUMBER(I20)),"---",IF(I20&lt;=0,"---",IF(I20*100/(Datos_vigas!$B$8*J20*K20^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I20*100/(Datos_vigas!$B$8*J20*K20^2*Datos_vigas!$B$5)))*J20*K20*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J20*K20))))</f>
         <v/>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S20" s="25">
         <f>F20/(J20*0.85*K20)</f>
@@ -13697,7 +14117,11 @@
         <f>IF(OR(M22="REVISAR",P22="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M22&lt;&gt;"REVISAR",P22&lt;&gt;"REVISAR",IF(ISNUMBER(M22),N22*PI()*(O22/10)^2/4&gt;=M22,TRUE),IF(ISNUMBER(P22),Q22*PI()*(R22/10)^2/4&gt;=P22,TRUE),IF(ISNUMBER(M22),M22&lt;=0.0163*J22*K22,TRUE),IF(ISNUMBER(P22),P22&lt;=0.0163*J22*K22,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F22&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J22*K22+2*PI()*(U22/10)^2/4*Datos_vigas!$B$6*K22/V22)),"NO VERIF. CORTE","VERIFICA")))</f>
         <v/>
       </c>
-      <c r="X22" s="11" t="n"/>
+      <c r="X22" s="13" t="inlineStr">
+        <is>
+          <t>Longitud total 3.26 m. La luz de calculo es la mayor entre pilotes, deducida de la posicion de los pilotes dibujados en el plano.</t>
+        </is>
+      </c>
       <c r="Y22" s="12" t="n">
         <v>3.15</v>
       </c>
@@ -14000,41 +14424,88 @@
           <t>VF13</t>
         </is>
       </c>
-      <c r="B26" s="41" t="n"/>
+      <c r="B26" s="8" t="n">
+        <v>2.28</v>
+      </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="D26" s="24" t="n"/>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="D26" s="24">
+        <f>1.2*(Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*Y26)</f>
+        <v/>
+      </c>
       <c r="E26" s="11" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="24" t="n"/>
-      <c r="I26" s="24" t="n"/>
-      <c r="J26" s="37" t="n"/>
-      <c r="K26" s="11" t="n"/>
-      <c r="L26" s="37" t="n"/>
-      <c r="M26" s="25" t="n"/>
-      <c r="N26" s="10" t="n"/>
-      <c r="O26" s="10" t="n"/>
-      <c r="P26" s="25" t="n"/>
-      <c r="Q26" s="10" t="n"/>
-      <c r="R26" s="10" t="n"/>
-      <c r="S26" s="25" t="n"/>
-      <c r="T26" s="25" t="n"/>
-      <c r="U26" s="10" t="n"/>
-      <c r="V26" s="10" t="n"/>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>FALTA SECCION</t>
-        </is>
-      </c>
-      <c r="X26" s="13" t="inlineStr">
-        <is>
-          <t>El rotulo figura en el plano pero la cota no resulto legible. Completar b, d y la luz y la fila calcula sola.</t>
-        </is>
-      </c>
+      <c r="F26" s="24">
+        <f>VLOOKUP(C26,Datos_vigas!$A$19:$E$23,4,0)*D26*B26</f>
+        <v/>
+      </c>
+      <c r="G26" s="24">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="24">
+        <f>VLOOKUP(C26,Datos_vigas!$A$19:$E$23,2,0)*D26*B26^2</f>
+        <v/>
+      </c>
+      <c r="I26" s="24">
+        <f>IF(VLOOKUP(C26,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(C26,Datos_vigas!$A$19:$E$23,3,0)*D26*B26^2)</f>
+        <v/>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K26" s="11">
+        <f>L26-Z26</f>
+        <v/>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M26" s="25">
+        <f>IF(NOT(ISNUMBER(H26)),"---",IF(H26&lt;=0,"---",IF(H26*100/(Datos_vigas!$B$8*J26*K26^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H26*100/(Datos_vigas!$B$8*J26*K26^2*Datos_vigas!$B$5)))*J26*K26*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J26*K26))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P26" s="25">
+        <f>IF(NOT(ISNUMBER(I26)),"---",IF(I26&lt;=0,"---",IF(I26*100/(Datos_vigas!$B$8*J26*K26^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I26*100/(Datos_vigas!$B$8*J26*K26^2*Datos_vigas!$B$5)))*J26*K26*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J26*K26))))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S26" s="25">
+        <f>F26/(J26*0.85*K26)</f>
+        <v/>
+      </c>
+      <c r="T26" s="25">
+        <f>G26/(J26*0.85*K26)</f>
+        <v/>
+      </c>
+      <c r="U26" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V26" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W26" s="11">
+        <f>IF(OR(M26="REVISAR",P26="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M26&lt;&gt;"REVISAR",P26&lt;&gt;"REVISAR",IF(ISNUMBER(M26),N26*PI()*(O26/10)^2/4&gt;=M26,TRUE),IF(ISNUMBER(P26),Q26*PI()*(R26/10)^2/4&gt;=P26,TRUE),IF(ISNUMBER(M26),M26&lt;=0.0163*J26*K26,TRUE),IF(ISNUMBER(P26),P26&lt;=0.0163*J26*K26,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F26&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J26*K26+2*PI()*(U26/10)^2/4*Datos_vigas!$B$6*K26/V26)),"NO VERIF. CORTE","VERIFICA")))</f>
+        <v/>
+      </c>
+      <c r="X26" s="11" t="n"/>
       <c r="Y26" s="12" t="n">
         <v>3.15</v>
       </c>
@@ -14279,27 +14750,27 @@
         <v/>
       </c>
       <c r="L29" s="10" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M29" s="25">
         <f>IF(NOT(ISNUMBER(H29)),"---",IF(H29&lt;=0,"---",IF(H29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)))*J29*K29*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J29*K29))))</f>
         <v/>
       </c>
       <c r="N29" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P29" s="25">
         <f>IF(NOT(ISNUMBER(I29)),"---",IF(I29&lt;=0,"---",IF(I29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I29*100/(Datos_vigas!$B$8*J29*K29^2*Datos_vigas!$B$5)))*J29*K29*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J29*K29))))</f>
         <v/>
       </c>
       <c r="Q29" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R29" s="10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S29" s="25">
         <f>F29/(J29*0.85*K29)</f>
@@ -14313,7 +14784,7 @@
         <v>6</v>
       </c>
       <c r="V29" s="10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="W29" s="11">
         <f>IF(OR(M29="REVISAR",P29="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M29&lt;&gt;"REVISAR",P29&lt;&gt;"REVISAR",IF(ISNUMBER(M29),N29*PI()*(O29/10)^2/4&gt;=M29,TRUE),IF(ISNUMBER(P29),Q29*PI()*(R29/10)^2/4&gt;=P29,TRUE),IF(ISNUMBER(M29),M29&lt;=0.0163*J29*K29,TRUE),IF(ISNUMBER(P29),P29&lt;=0.0163*J29*K29,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F29&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J29*K29+2*PI()*(U29/10)^2/4*Datos_vigas!$B$6*K29/V29)),"NO VERIF. CORTE","VERIFICA")))</f>
@@ -14374,27 +14845,27 @@
         <v/>
       </c>
       <c r="L30" s="10" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M30" s="25">
         <f>IF(NOT(ISNUMBER(H30)),"---",IF(H30&lt;=0,"---",IF(H30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)))*J30*K30*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J30*K30))))</f>
         <v/>
       </c>
       <c r="N30" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P30" s="25">
         <f>IF(NOT(ISNUMBER(I30)),"---",IF(I30&lt;=0,"---",IF(I30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I30*100/(Datos_vigas!$B$8*J30*K30^2*Datos_vigas!$B$5)))*J30*K30*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J30*K30))))</f>
         <v/>
       </c>
       <c r="Q30" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S30" s="25">
         <f>F30/(J30*0.85*K30)</f>
@@ -14408,7 +14879,7 @@
         <v>6</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W30" s="11">
         <f>IF(OR(M30="REVISAR",P30="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M30&lt;&gt;"REVISAR",P30&lt;&gt;"REVISAR",IF(ISNUMBER(M30),N30*PI()*(O30/10)^2/4&gt;=M30,TRUE),IF(ISNUMBER(P30),Q30*PI()*(R30/10)^2/4&gt;=P30,TRUE),IF(ISNUMBER(M30),M30&lt;=0.0163*J30*K30,TRUE),IF(ISNUMBER(P30),P30&lt;=0.0163*J30*K30,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F30&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J30*K30+2*PI()*(U30/10)^2/4*Datos_vigas!$B$6*K30/V30)),"NO VERIF. CORTE","VERIFICA")))</f>
@@ -14648,7 +15119,7 @@
         <v/>
       </c>
       <c r="J33" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K33" s="11">
         <f>L33-Z33</f>
@@ -14662,20 +15133,20 @@
         <v/>
       </c>
       <c r="N33" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O33" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P33" s="25">
         <f>IF(NOT(ISNUMBER(I33)),"---",IF(I33&lt;=0,"---",IF(I33*100/(Datos_vigas!$B$8*J33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I33*100/(Datos_vigas!$B$8*J33*K33^2*Datos_vigas!$B$5)))*J33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
         <v/>
       </c>
       <c r="Q33" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R33" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S33" s="25">
         <f>F33/(J33*0.85*K33)</f>
@@ -15549,7 +16020,7 @@
       <c r="O13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Los 33 pilotes del plano: 13 bajo cabezales de columna (los de esta tabla) y 20 repartidos bajo las vigas de fundacion.</t>
         </is>
@@ -15601,6 +16072,1072 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>TABIQUES DE H°A°        H-21        ACERO 42/50        espesor 12 cm</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>NIVEL</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>CARGA (t)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>N por metro (t/m)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>CAPACIDAD</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICACION</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>espesor (cm)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>largo (m)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>alto (m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>esbeltez</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>reduccion</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>fi Pn (t/m)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>PB   (altura de entrepiso)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>T01a</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="G5" s="25">
+        <f>IF(F5="","",F5/D5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="38">
+        <f>E5*100/C5</f>
+        <v/>
+      </c>
+      <c r="I5" s="33">
+        <f>MAX(0,1-(E5*100/(32*C5))^2)</f>
+        <v/>
+      </c>
+      <c r="J5" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C5)*I5/1000</f>
+        <v/>
+      </c>
+      <c r="K5" s="11">
+        <f>IF(G5="","FALTA CARGA",IF(G5&lt;=J5,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>Recibe el extremo de VI 01a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>T01b</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F6" s="42" t="n"/>
+      <c r="G6" s="25">
+        <f>IF(F6="","",F6/D6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="38">
+        <f>E6*100/C6</f>
+        <v/>
+      </c>
+      <c r="I6" s="33">
+        <f>MAX(0,1-(E6*100/(32*C6))^2)</f>
+        <v/>
+      </c>
+      <c r="J6" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C6)*I6/1000</f>
+        <v/>
+      </c>
+      <c r="K6" s="11">
+        <f>IF(G6="","FALTA CARGA",IF(G6&lt;=J6,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="25">
+        <f>IF(F7="","",F7/D7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="38">
+        <f>E7*100/C7</f>
+        <v/>
+      </c>
+      <c r="I7" s="33">
+        <f>MAX(0,1-(E7*100/(32*C7))^2)</f>
+        <v/>
+      </c>
+      <c r="J7" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C7)*I7/1000</f>
+        <v/>
+      </c>
+      <c r="K7" s="11">
+        <f>IF(G7="","FALTA CARGA",IF(G7&lt;=J7,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F8" s="42" t="n"/>
+      <c r="G8" s="25">
+        <f>IF(F8="","",F8/D8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="38">
+        <f>E8*100/C8</f>
+        <v/>
+      </c>
+      <c r="I8" s="33">
+        <f>MAX(0,1-(E8*100/(32*C8))^2)</f>
+        <v/>
+      </c>
+      <c r="J8" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C8)*I8/1000</f>
+        <v/>
+      </c>
+      <c r="K8" s="11">
+        <f>IF(G8="","FALTA CARGA",IF(G8&lt;=J8,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>No se habia detectado en el plano: aparece en el computo. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>T04a</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F9" s="42" t="n"/>
+      <c r="G9" s="25">
+        <f>IF(F9="","",F9/D9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="38">
+        <f>E9*100/C9</f>
+        <v/>
+      </c>
+      <c r="I9" s="33">
+        <f>MAX(0,1-(E9*100/(32*C9))^2)</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C9)*I9/1000</f>
+        <v/>
+      </c>
+      <c r="K9" s="11">
+        <f>IF(G9="","FALTA CARGA",IF(G9&lt;=J9,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>T04b</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F10" s="42" t="n"/>
+      <c r="G10" s="25">
+        <f>IF(F10="","",F10/D10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>E10*100/C10</f>
+        <v/>
+      </c>
+      <c r="I10" s="33">
+        <f>MAX(0,1-(E10*100/(32*C10))^2)</f>
+        <v/>
+      </c>
+      <c r="J10" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C10)*I10/1000</f>
+        <v/>
+      </c>
+      <c r="K10" s="11">
+        <f>IF(G10="","FALTA CARGA",IF(G10&lt;=J10,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>En el plano solo figura en la planta de fundacion. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>T05a</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F11" s="42" t="n"/>
+      <c r="G11" s="25">
+        <f>IF(F11="","",F11/D11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="38">
+        <f>E11*100/C11</f>
+        <v/>
+      </c>
+      <c r="I11" s="33">
+        <f>MAX(0,1-(E11*100/(32*C11))^2)</f>
+        <v/>
+      </c>
+      <c r="J11" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C11)*I11/1000</f>
+        <v/>
+      </c>
+      <c r="K11" s="11">
+        <f>IF(G11="","FALTA CARGA",IF(G11&lt;=J11,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>T05b</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="G12" s="25">
+        <f>IF(F12="","",F12/D12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="38">
+        <f>E12*100/C12</f>
+        <v/>
+      </c>
+      <c r="I12" s="33">
+        <f>MAX(0,1-(E12*100/(32*C12))^2)</f>
+        <v/>
+      </c>
+      <c r="J12" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C12)*I12/1000</f>
+        <v/>
+      </c>
+      <c r="K12" s="11">
+        <f>IF(G12="","FALTA CARGA",IF(G12&lt;=J12,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>Recibe el extremo de VI 07c.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>T06a</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="25">
+        <f>IF(F13="","",F13/D13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>E13*100/C13</f>
+        <v/>
+      </c>
+      <c r="I13" s="33">
+        <f>MAX(0,1-(E13*100/(32*C13))^2)</f>
+        <v/>
+      </c>
+      <c r="J13" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C13)*I13/1000</f>
+        <v/>
+      </c>
+      <c r="K13" s="11">
+        <f>IF(G13="","FALTA CARGA",IF(G13&lt;=J13,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>T06b</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F14" s="42" t="n"/>
+      <c r="G14" s="25">
+        <f>IF(F14="","",F14/D14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="38">
+        <f>E14*100/C14</f>
+        <v/>
+      </c>
+      <c r="I14" s="33">
+        <f>MAX(0,1-(E14*100/(32*C14))^2)</f>
+        <v/>
+      </c>
+      <c r="J14" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C14)*I14/1000</f>
+        <v/>
+      </c>
+      <c r="K14" s="11">
+        <f>IF(G14="","FALTA CARGA",IF(G14&lt;=J14,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>Perpendicular a las vigas chatas, en la union de VCH 03a con VCH 03b. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>T06c</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="25">
+        <f>IF(F15="","",F15/D15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="38">
+        <f>E15*100/C15</f>
+        <v/>
+      </c>
+      <c r="I15" s="33">
+        <f>MAX(0,1-(E15*100/(32*C15))^2)</f>
+        <v/>
+      </c>
+      <c r="J15" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C15)*I15/1000</f>
+        <v/>
+      </c>
+      <c r="K15" s="11">
+        <f>IF(G15="","FALTA CARGA",IF(G15&lt;=J15,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="G16" s="25">
+        <f>IF(F16="","",F16/D16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="38">
+        <f>E16*100/C16</f>
+        <v/>
+      </c>
+      <c r="I16" s="33">
+        <f>MAX(0,1-(E16*100/(32*C16))^2)</f>
+        <v/>
+      </c>
+      <c r="J16" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C16)*I16/1000</f>
+        <v/>
+      </c>
+      <c r="K16" s="11">
+        <f>IF(G16="","FALTA CARGA",IF(G16&lt;=J16,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>Recibe el extremo de VI 02, perpendicular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>T08a</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G17" s="25">
+        <f>IF(F17="","",F17/D17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="38">
+        <f>E17*100/C17</f>
+        <v/>
+      </c>
+      <c r="I17" s="33">
+        <f>MAX(0,1-(E17*100/(32*C17))^2)</f>
+        <v/>
+      </c>
+      <c r="J17" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C17)*I17/1000</f>
+        <v/>
+      </c>
+      <c r="K17" s="11">
+        <f>IF(G17="","FALTA CARGA",IF(G17&lt;=J17,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>Recibe el extremo de VI 11a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>T08b</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="30">
+        <f>IF(F18="","",F18/D18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="40">
+        <f>E18*100/C18</f>
+        <v/>
+      </c>
+      <c r="I18" s="35">
+        <f>MAX(0,1-(E18*100/(32*C18))^2)</f>
+        <v/>
+      </c>
+      <c r="J18" s="16">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C18)*I18/1000</f>
+        <v/>
+      </c>
+      <c r="K18" s="18">
+        <f>IF(G18="","FALTA CARGA",IF(G18&lt;=J18,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>PA   (altura de entrepiso)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="25">
+        <f>IF(F20="","",F20/D20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="38">
+        <f>E20*100/C20</f>
+        <v/>
+      </c>
+      <c r="I20" s="33">
+        <f>MAX(0,1-(E20*100/(32*C20))^2)</f>
+        <v/>
+      </c>
+      <c r="J20" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C20)*I20/1000</f>
+        <v/>
+      </c>
+      <c r="K20" s="11">
+        <f>IF(G20="","FALTA CARGA",IF(G20&lt;=J20,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F21" s="42" t="n"/>
+      <c r="G21" s="25">
+        <f>IF(F21="","",F21/D21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="38">
+        <f>E21*100/C21</f>
+        <v/>
+      </c>
+      <c r="I21" s="33">
+        <f>MAX(0,1-(E21*100/(32*C21))^2)</f>
+        <v/>
+      </c>
+      <c r="J21" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C21)*I21/1000</f>
+        <v/>
+      </c>
+      <c r="K21" s="11">
+        <f>IF(G21="","FALTA CARGA",IF(G21&lt;=J21,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F22" s="42" t="n"/>
+      <c r="G22" s="25">
+        <f>IF(F22="","",F22/D22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="38">
+        <f>E22*100/C22</f>
+        <v/>
+      </c>
+      <c r="I22" s="33">
+        <f>MAX(0,1-(E22*100/(32*C22))^2)</f>
+        <v/>
+      </c>
+      <c r="J22" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C22)*I22/1000</f>
+        <v/>
+      </c>
+      <c r="K22" s="11">
+        <f>IF(G22="","FALTA CARGA",IF(G22&lt;=J22,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>Longitud muy corta: verificar si es un tabique o el machon de una abertura. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="25">
+        <f>IF(F23="","",F23/D23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="38">
+        <f>E23*100/C23</f>
+        <v/>
+      </c>
+      <c r="I23" s="33">
+        <f>MAX(0,1-(E23*100/(32*C23))^2)</f>
+        <v/>
+      </c>
+      <c r="J23" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C23)*I23/1000</f>
+        <v/>
+      </c>
+      <c r="K23" s="11">
+        <f>IF(G23="","FALTA CARGA",IF(G23&lt;=J23,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>Longitud muy corta: verificar si es un tabique o el machon de una abertura. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="30">
+        <f>IF(F24="","",F24/D24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="40">
+        <f>E24*100/C24</f>
+        <v/>
+      </c>
+      <c r="I24" s="35">
+        <f>MAX(0,1-(E24*100/(32*C24))^2)</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>0.55*0.65*Datos_vigas!$B$5*(100*C24)*I24/1000</f>
+        <v/>
+      </c>
+      <c r="K24" s="18">
+        <f>IF(G24="","FALTA CARGA",IF(G24&lt;=J24,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>fi Pn = 0,55 x 0,65 x f'c x Ag x [1 - (alto / 32 espesor)^2]    muro portante de hormigon armado, con reduccion por esbeltez.</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>Longitudes tomadas del computo metrico (planilla N 3, item 4.1.10).</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="L2:L3"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K4:K24">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"VERIFICA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"NO VERIFICA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
+      <formula>"FALTA CARGA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F25"/>
@@ -15615,7 +17152,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - HIPOTESIS DE CALCULO</t>
         </is>
@@ -15647,17 +17184,17 @@
       <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -15667,12 +17204,12 @@
       <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="49" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -15685,12 +17222,12 @@
       <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="48" t="n">
+      <c r="B6" s="49" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -15703,12 +17240,12 @@
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="49" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -15721,12 +17258,12 @@
       <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>phi flexion</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="49" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -15739,12 +17276,12 @@
       <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>phi corte</t>
         </is>
       </c>
-      <c r="B9" s="48" t="n">
+      <c r="B9" s="49" t="n">
         <v>0.75</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -15757,12 +17294,12 @@
       <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="48" t="inlineStr">
         <is>
           <t>Coef. mayoracion permanente</t>
         </is>
       </c>
-      <c r="B10" s="48" t="n">
+      <c r="B10" s="49" t="n">
         <v>1.2</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -15775,12 +17312,12 @@
       <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>Coef. mayoracion sobrecarga</t>
         </is>
       </c>
-      <c r="B11" s="48" t="n">
+      <c r="B11" s="49" t="n">
         <v>1.6</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -15801,7 +17338,7 @@
       <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>PAQUETES DE CARGA</t>
         </is>
@@ -15833,21 +17370,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="49" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B14" s="50" t="n">
+      <c r="B14" s="51" t="n">
         <v>550</v>
       </c>
-      <c r="C14" s="50" t="n">
+      <c r="C14" s="51" t="n">
         <v>200</v>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="52" t="n">
         <v>2.6</v>
       </c>
-      <c r="E14" s="51" t="n">
+      <c r="E14" s="52" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="32" t="inlineStr">
@@ -15857,21 +17394,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>TECHO</t>
         </is>
       </c>
-      <c r="B15" s="50" t="n">
+      <c r="B15" s="51" t="n">
         <v>560</v>
       </c>
-      <c r="C15" s="50" t="n">
+      <c r="C15" s="51" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="51" t="n">
+      <c r="D15" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="51" t="n">
+      <c r="E15" s="52" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="32" t="inlineStr">
@@ -15881,12 +17418,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>Mamposteria sobre viga</t>
         </is>
       </c>
-      <c r="B16" s="48" t="n">
+      <c r="B16" s="49" t="n">
         <v>250</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -15896,7 +17433,7 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="52" t="inlineStr">
+      <c r="F16" s="53" t="inlineStr">
         <is>
           <t>Ladrillo hueco 18 cm + revoque en ambas caras</t>
         </is>
@@ -15911,7 +17448,7 @@
       <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="46" t="inlineStr">
         <is>
           <t>COEFICIENTES SEGUN ESQUEMA</t>
         </is>
@@ -15939,101 +17476,101 @@
       <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="47" t="inlineStr">
+      <c r="A19" s="48" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="B19" s="53" t="n">
+      <c r="B19" s="54" t="n">
         <v>0.125</v>
       </c>
-      <c r="C19" s="53" t="n">
+      <c r="C19" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="53" t="n">
+      <c r="D19" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" s="54" t="n">
+      <c r="E19" s="55" t="n">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="47" t="inlineStr">
+      <c r="A20" s="48" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
-      <c r="B20" s="53" t="n">
+      <c r="B20" s="54" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="C20" s="53" t="n">
+      <c r="C20" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="53" t="n">
+      <c r="D20" s="54" t="n">
         <v>0.575</v>
       </c>
-      <c r="E20" s="54" t="n">
+      <c r="E20" s="55" t="n">
         <v>21</v>
       </c>
       <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="47" t="inlineStr">
+      <c r="A21" s="48" t="inlineStr">
         <is>
           <t>Empotrada-apoyada</t>
         </is>
       </c>
-      <c r="B21" s="53" t="n">
+      <c r="B21" s="54" t="n">
         <v>0.07031</v>
       </c>
-      <c r="C21" s="53" t="n">
+      <c r="C21" s="54" t="n">
         <v>0.125</v>
       </c>
-      <c r="D21" s="53" t="n">
+      <c r="D21" s="54" t="n">
         <v>0.625</v>
       </c>
-      <c r="E21" s="54" t="n">
+      <c r="E21" s="55" t="n">
         <v>18.5</v>
       </c>
       <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="47" t="inlineStr">
+      <c r="A22" s="48" t="inlineStr">
         <is>
           <t>Biempotrada</t>
         </is>
       </c>
-      <c r="B22" s="53" t="n">
+      <c r="B22" s="54" t="n">
         <v>0.04167</v>
       </c>
-      <c r="C22" s="53" t="n">
+      <c r="C22" s="54" t="n">
         <v>0.08333</v>
       </c>
-      <c r="D22" s="53" t="n">
+      <c r="D22" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="54" t="n">
+      <c r="E22" s="55" t="n">
         <v>21</v>
       </c>
       <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="47" t="inlineStr">
+      <c r="A23" s="48" t="inlineStr">
         <is>
           <t>Voladizo</t>
         </is>
       </c>
-      <c r="B23" s="53" t="n">
+      <c r="B23" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="53" t="n">
+      <c r="C23" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="D23" s="53" t="n">
+      <c r="D23" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="54" t="n">
+      <c r="E23" s="55" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -16047,7 +17584,7 @@
       <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="inlineStr">
+      <c r="A25" s="41" t="inlineStr">
         <is>
           <t>p = 1,2 g + 1,6 q    |    M = coef x p x L2    |    R = coef x p x L</t>
         </is>
@@ -16063,7 +17600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16081,7 +17618,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - LOSAS</t>
         </is>
@@ -16107,17 +17644,17 @@
       <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>MATERIALES Y METODO</t>
         </is>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -16125,12 +17662,12 @@
       <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="47" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="48" t="n">
+      <c r="B5" s="49" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -16141,12 +17678,12 @@
       <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="48" t="n">
+      <c r="B6" s="49" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -16157,12 +17694,12 @@
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>Tension admisible del acero</t>
         </is>
       </c>
-      <c r="B7" s="48" t="n">
+      <c r="B7" s="49" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -16173,12 +17710,12 @@
       <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>Brazo elastico  z / h</t>
         </is>
       </c>
-      <c r="B8" s="48" t="n">
+      <c r="B8" s="49" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -16189,12 +17726,12 @@
       <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B9" s="48" t="n">
+      <c r="B9" s="49" t="n">
         <v>2400</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -16205,12 +17742,12 @@
       <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="48" t="inlineStr">
         <is>
           <t>Recubrimiento</t>
         </is>
       </c>
-      <c r="B10" s="48" t="n">
+      <c r="B10" s="49" t="n">
         <v>1.5</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -16221,12 +17758,12 @@
       <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="48" t="inlineStr">
         <is>
           <t>Separacion maxima</t>
         </is>
       </c>
-      <c r="B11" s="48" t="n">
+      <c r="B11" s="49" t="n">
         <v>20</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -16237,12 +17774,12 @@
       <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>Armadura de reparticion</t>
         </is>
       </c>
-      <c r="B12" s="48" t="n">
+      <c r="B12" s="49" t="n">
         <v>0.2</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -16253,12 +17790,12 @@
       <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="inlineStr">
+      <c r="A13" s="48" t="inlineStr">
         <is>
           <t>Reparticion minima</t>
         </is>
       </c>
-      <c r="B13" s="48" t="n">
+      <c r="B13" s="49" t="n">
         <v>0.3</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -16275,7 +17812,7 @@
       <c r="D14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>CARGAS POR NIVEL</t>
         </is>
@@ -16297,15 +17834,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="49" t="inlineStr">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B16" s="48" t="n">
+      <c r="B16" s="49" t="n">
         <v>242</v>
       </c>
-      <c r="C16" s="48" t="n">
+      <c r="C16" s="49" t="n">
         <v>200</v>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -16315,15 +17852,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="50" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B17" s="48" t="n">
+      <c r="B17" s="49" t="n">
         <v>252</v>
       </c>
-      <c r="C17" s="48" t="n">
+      <c r="C17" s="49" t="n">
         <v>100</v>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -16333,7 +17870,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>El peso propio se suma aparte: 2400 x d / 100</t>
         </is>
@@ -16349,7 +17886,7 @@
       <c r="D19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>GRADO DE EMPOTRAMIENTO</t>
         </is>
@@ -16371,90 +17908,90 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>1/8</t>
         </is>
       </c>
-      <c r="B21" s="53" t="n">
+      <c r="B21" s="54" t="n">
         <v>0.125</v>
       </c>
-      <c r="C21" s="56" t="n">
+      <c r="C21" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="D21" s="57" t="inlineStr">
+      <c r="D21" s="58" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="B22" s="53" t="n">
+      <c r="B22" s="54" t="n">
         <v>0.1</v>
       </c>
-      <c r="C22" s="56" t="n">
+      <c r="C22" s="57" t="n">
         <v>0.55</v>
       </c>
-      <c r="D22" s="57" t="inlineStr">
+      <c r="D22" s="58" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="A23" s="56" t="inlineStr">
         <is>
           <t>1/12</t>
         </is>
       </c>
-      <c r="B23" s="53" t="n">
+      <c r="B23" s="54" t="n">
         <v>0.0833</v>
       </c>
-      <c r="C23" s="56" t="n">
+      <c r="C23" s="57" t="n">
         <v>0.5</v>
       </c>
-      <c r="D23" s="57" t="inlineStr">
+      <c r="D23" s="58" t="inlineStr">
         <is>
           <t>Biempotrada</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>1/14</t>
         </is>
       </c>
-      <c r="B24" s="53" t="n">
+      <c r="B24" s="54" t="n">
         <v>0.07140000000000001</v>
       </c>
-      <c r="C24" s="56" t="n">
+      <c r="C24" s="57" t="n">
         <v>0.575</v>
       </c>
-      <c r="D24" s="57" t="inlineStr">
+      <c r="D24" s="58" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="B25" s="53" t="n">
+      <c r="B25" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="C25" s="56" t="n">
+      <c r="C25" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="57" t="inlineStr">
+      <c r="D25" s="58" t="inlineStr">
         <is>
           <t>Voladizo</t>
         </is>
@@ -16467,7 +18004,7 @@
       <c r="D26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="42" t="inlineStr">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q   (cargas de servicio)</t>
         </is>
@@ -16477,7 +18014,7 @@
       <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="A28" s="41" t="inlineStr">
         <is>
           <t>M = coef x p x L2        R = coef x p x L        As = M x 100 / (2400 x 0,9 x h)        rep. = As / 5</t>
         </is>
@@ -16485,185 +18022,6 @@
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="43" t="inlineStr">
-        <is>
-          <t>DATOS DE PARTIDA - COLUMNAS</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="45" t="inlineStr">
-        <is>
-          <t>MATERIALES Y CRITERIOS</t>
-        </is>
-      </c>
-      <c r="B3" s="46" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="C3" s="46" t="inlineStr">
-        <is>
-          <t>unidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="47" t="inlineStr">
-        <is>
-          <t>Hormigon H-21   f'c</t>
-        </is>
-      </c>
-      <c r="B4" s="48" t="n">
-        <v>210</v>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>kg/cm2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="47" t="inlineStr">
-        <is>
-          <t>Acero 42/50   fy</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>kg/cm2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="47" t="inlineStr">
-        <is>
-          <t>Peso especifico H.A.</t>
-        </is>
-      </c>
-      <c r="B6" s="48" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>kg/m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>phi compresion (estribos)</t>
-        </is>
-      </c>
-      <c r="B7" s="48" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="47" t="inlineStr">
-        <is>
-          <t>Cuantia minima</t>
-        </is>
-      </c>
-      <c r="B8" s="48" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>de la seccion</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>Altura PB</t>
-        </is>
-      </c>
-      <c r="B9" s="48" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="47" t="inlineStr">
-        <is>
-          <t>Altura PA</t>
-        </is>
-      </c>
-      <c r="B10" s="48" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>As = cuantia minima x area        phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>Separacion de estribos = min(12 x diam. longitudinal ; 48 x diam. estribo ; lado menor)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -4162,7 +4162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4477,7 +4477,7 @@
       <c r="A36" s="61" t="inlineStr"/>
       <c r="B36" s="62" t="inlineStr">
         <is>
-          <t>Son VI 01a, VI 01b, VI 07a, VI 07b, VI 07c, VI 11a, VI 11b, VI 11c, VI 15a y VI 15b,</t>
+          <t>losa. Lo confirman las cotas del plano y el hecho de que el cielorraso sea de</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       <c r="A37" s="61" t="inlineStr"/>
       <c r="B37" s="62" t="inlineStr">
         <is>
-          <t>identificadas por coincidir su eje con el contorno del edificio.</t>
+          <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       <c r="A38" s="61" t="inlineStr"/>
       <c r="B38" s="62" t="inlineStr">
         <is>
-          <t>Esto define donde la losa aporta ala comprimida:</t>
+          <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       <c r="A39" s="61" t="inlineStr"/>
       <c r="B39" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
+          <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       <c r="A40" s="61" t="inlineStr"/>
       <c r="B40" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
+          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       <c r="A41" s="61" t="inlineStr"/>
       <c r="B41" s="62" t="inlineStr">
         <is>
-          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
+          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       <c r="A42" s="61" t="inlineStr"/>
       <c r="B42" s="62" t="inlineStr">
         <is>
-          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
+          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       <c r="A43" s="61" t="inlineStr"/>
       <c r="B43" s="62" t="inlineStr">
         <is>
-          <t>PENDIENTE: una viga invertida de borde recibe la reaccion de la losa excentrica</t>
+          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
@@ -4541,39 +4541,39 @@
       <c r="A44" s="61" t="inlineStr"/>
       <c r="B44" s="62" t="inlineStr">
         <is>
-          <t>respecto de su eje y queda sometida a TORSION. Esta planilla no la verifica.</t>
+          <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="61" t="inlineStr"/>
-      <c r="B45" s="62" t="inlineStr"/>
+      <c r="B45" s="62" t="inlineStr">
+        <is>
+          <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="61" t="inlineStr">
-        <is>
-          <t>7. RESULTADO</t>
-        </is>
-      </c>
-      <c r="B46" s="61" t="inlineStr">
-        <is>
-          <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
+      <c r="A46" s="61" t="inlineStr"/>
+      <c r="B46" s="62" t="inlineStr">
+        <is>
+          <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="61" t="inlineStr"/>
-      <c r="B47" s="62" t="inlineStr">
-        <is>
-          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
-        </is>
-      </c>
+      <c r="B47" s="62" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="61" t="inlineStr"/>
-      <c r="B48" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>7. RESULTADO</t>
+        </is>
+      </c>
+      <c r="B48" s="61" t="inlineStr">
+        <is>
+          <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       <c r="A49" s="61" t="inlineStr"/>
       <c r="B49" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
+          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       <c r="A50" s="61" t="inlineStr"/>
       <c r="B50" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
+          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       <c r="A51" s="61" t="inlineStr"/>
       <c r="B51" s="62" t="inlineStr">
         <is>
-          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
+          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       <c r="A52" s="61" t="inlineStr"/>
       <c r="B52" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
+          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4613,7 @@
       <c r="A53" s="61" t="inlineStr"/>
       <c r="B53" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
+          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
       <c r="A54" s="61" t="inlineStr"/>
       <c r="B54" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
+          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       <c r="A55" s="61" t="inlineStr"/>
       <c r="B55" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
+          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       <c r="A56" s="61" t="inlineStr"/>
       <c r="B56" s="62" t="inlineStr">
         <is>
-          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
+          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
@@ -4645,63 +4645,63 @@
       <c r="A57" s="61" t="inlineStr"/>
       <c r="B57" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
+          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="61" t="inlineStr"/>
-      <c r="B58" s="62" t="inlineStr"/>
+      <c r="B58" s="62" t="inlineStr">
+        <is>
+          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="61" t="inlineStr">
-        <is>
-          <t>8. ALCANCE</t>
-        </is>
-      </c>
+      <c r="A59" s="61" t="inlineStr"/>
       <c r="B59" s="62" t="inlineStr">
         <is>
-          <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
+          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="61" t="inlineStr"/>
-      <c r="B60" s="62" t="inlineStr">
+      <c r="B60" s="62" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="61" t="inlineStr">
+        <is>
+          <t>8. ALCANCE</t>
+        </is>
+      </c>
+      <c r="B61" s="62" t="inlineStr">
+        <is>
+          <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="61" t="inlineStr"/>
+      <c r="B62" s="62" t="inlineStr">
         <is>
           <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="61" t="inlineStr"/>
-      <c r="B61" s="62" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="61" t="inlineStr">
-        <is>
-          <t>LIMITACIONES</t>
-        </is>
-      </c>
-      <c r="B62" s="61" t="inlineStr">
-        <is>
-          <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="61" t="inlineStr"/>
-      <c r="B63" s="62" t="inlineStr">
-        <is>
-          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
-        </is>
-      </c>
+      <c r="B63" s="62" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="61" t="inlineStr"/>
-      <c r="B64" s="62" t="inlineStr">
-        <is>
-          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
+      <c r="A64" s="61" t="inlineStr">
+        <is>
+          <t>LIMITACIONES</t>
+        </is>
+      </c>
+      <c r="B64" s="61" t="inlineStr">
+        <is>
+          <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
@@ -4709,13 +4709,29 @@
       <c r="A65" s="61" t="inlineStr"/>
       <c r="B65" s="62" t="inlineStr">
         <is>
-          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
+          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="61" t="inlineStr"/>
       <c r="B66" s="62" t="inlineStr">
+        <is>
+          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="61" t="inlineStr"/>
+      <c r="B67" s="62" t="inlineStr">
+        <is>
+          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="61" t="inlineStr"/>
+      <c r="B68" s="62" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -6499,7 +6515,7 @@
       </c>
       <c r="X4" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde sobre la medianera: NO recibe losa. Solo peso propio y mamposteria. Apoya en el tabique T01a y en la columna COL 01 de 10x10. Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde sobre la medianera: NO recibe losa. Solo peso propio y mamposteria. Apoya en el tabique T01a y en la columna COL 01 de 10x10. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y4" s="10" t="inlineStr">
@@ -6614,7 +6630,7 @@
       </c>
       <c r="X5" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y5" s="10" t="inlineStr">
@@ -6729,7 +6745,7 @@
       </c>
       <c r="X6" s="13" t="inlineStr">
         <is>
-          <t>Armadura en 2 capas (rec. 6 cm). NO VERIFICA. Recibe L03 (2,08 m) y el alero L02, computado como 0,59 m equivalentes por tener menor carga que un entrepiso. Con 9,88 m de luz y 15x60 la armadura de apoyo necesaria (25,5 cm2) supera la cuantia maxima (13,2). Apoyos confirmados en obra: tabique T07 perpendicular en el extremo superior y COL 02 en el inferior, sin apoyo intermedio. Para esta carga harian falta 15x75 (As 16,2 cm2). Verificar la seccion real construida.</t>
+          <t>Armadura en 2 capas (rec. 6 cm). NO USAR TEXTO VIEJO. Recibe L03 (2,08 m) y el alero L02, computado como 0,59 m equivalentes por tener menor carga que un entrepiso. Con 9,88 m de luz y 15x60 la armadura de apoyo necesaria (25,5 cm2) supera la cuantia maxima (13,2). Apoyos confirmados en obra: tabique T07 perpendicular en el extremo superior y COL 02 en el inferior, sin apoyo intermedio. Para esta carga harian falta 15x75 (As 16,2 cm2). Verificar la seccion real construida.</t>
         </is>
       </c>
       <c r="Y6" s="10" t="inlineStr">
@@ -6739,7 +6755,7 @@
       </c>
       <c r="Z6" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA6" s="10" t="n">
@@ -6850,7 +6866,7 @@
       </c>
       <c r="Z7" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA7" s="10" t="n">
@@ -6961,7 +6977,7 @@
       </c>
       <c r="Z8" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA8" s="10" t="n">
@@ -7072,7 +7088,7 @@
       </c>
       <c r="Z9" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA9" s="10" t="n">
@@ -7191,7 +7207,7 @@
       </c>
       <c r="Z10" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA10" s="10" t="n">
@@ -7296,7 +7312,7 @@
       </c>
       <c r="X11" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y11" s="10" t="inlineStr">
@@ -7411,7 +7427,7 @@
       </c>
       <c r="X12" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y12" s="10" t="inlineStr">
@@ -7526,7 +7542,7 @@
       </c>
       <c r="X13" s="13" t="inlineStr">
         <is>
-          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y13" s="10" t="inlineStr">
@@ -7647,7 +7663,7 @@
       </c>
       <c r="Z14" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA14" s="10" t="n">
@@ -7758,7 +7774,7 @@
       </c>
       <c r="Z15" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA15" s="10" t="n">
@@ -7873,7 +7889,7 @@
       </c>
       <c r="Z16" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA16" s="10" t="n">
@@ -7984,7 +8000,7 @@
       </c>
       <c r="Z17" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA17" s="10" t="n">
@@ -8095,7 +8111,7 @@
       </c>
       <c r="Z18" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA18" s="10" t="n">
@@ -8206,7 +8222,7 @@
       </c>
       <c r="Z19" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA19" s="10" t="n">
@@ -8311,7 +8327,7 @@
       </c>
       <c r="X20" s="13" t="inlineStr">
         <is>
-          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y20" s="10" t="inlineStr">
@@ -8426,7 +8442,7 @@
       </c>
       <c r="X21" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y21" s="10" t="inlineStr">
@@ -8541,7 +8557,7 @@
       </c>
       <c r="X22" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y22" s="10" t="inlineStr">
@@ -8980,10 +8996,10 @@
         <v/>
       </c>
       <c r="Q26" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R26" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S26" s="25">
         <f>F26/(J26*0.85*K26)</f>
@@ -8997,17 +9013,13 @@
         <v>6</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W26" s="11">
         <f>IF(OR(M26="REVISAR",P26="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M26&lt;&gt;"REVISAR",P26&lt;&gt;"REVISAR",IF(ISNUMBER(M26),N26*PI()*(O26/10)^2/4&gt;=M26,TRUE),IF(ISNUMBER(P26),Q26*PI()*(R26/10)^2/4&gt;=P26,TRUE),IF(ISNUMBER(M26),M26&lt;=0.0163*AB26*K26,TRUE),IF(ISNUMBER(P26),P26&lt;=0.0163*AC26*K26,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F26&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J26*K26+2*PI()*(U26/10)^2/4*Datos_vigas!$B$6*K26/V26)),"NO VERIF. CORTE",IF(NOT(L26&gt;=C26*100/VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X26" s="13" t="inlineStr">
-        <is>
-          <t>Armadura en 2 capas (rec. 6 cm).</t>
-        </is>
-      </c>
+      <c r="X26" s="11" t="n"/>
       <c r="Y26" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -9015,7 +9027,7 @@
       </c>
       <c r="Z26" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA26" s="10" t="n">
@@ -9036,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="AF26" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
@@ -9126,7 +9138,7 @@
       </c>
       <c r="Z27" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA27" s="10" t="n">
@@ -9237,7 +9249,7 @@
       </c>
       <c r="Z28" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA28" s="10" t="n">
@@ -9348,7 +9360,7 @@
       </c>
       <c r="Z29" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA29" s="10" t="n">
@@ -9453,7 +9465,7 @@
       </c>
       <c r="X30" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y30" s="10" t="inlineStr">
@@ -9568,7 +9580,7 @@
       </c>
       <c r="X31" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde INVERTIDA: sobresale 70 cm sobre el fondo de losa. Verificar torsion, no incluida en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y31" s="10" t="inlineStr">
@@ -9689,7 +9701,7 @@
       </c>
       <c r="Z32" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA32" s="10" t="n">
@@ -9800,7 +9812,7 @@
       </c>
       <c r="Z33" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA33" s="10" t="n">
@@ -9915,7 +9927,7 @@
       </c>
       <c r="Z34" s="17" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA34" s="17" t="n">
@@ -15556,7 +15568,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>29.47</v>
+        <v>29.46</v>
       </c>
       <c r="H5" s="25">
         <f>IF(G5="","",G5/1.4)</f>
@@ -15597,7 +15609,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>C5 (15x30)</t>
+          <t>C4 (15x30)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -15615,7 +15627,7 @@
         <v>65</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>15.9</v>
+        <v>15.96</v>
       </c>
       <c r="H6" s="25">
         <f>IF(G6="","",G6/1.4)</f>
@@ -15715,7 +15727,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>C4 (10x10)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -15732,9 +15744,7 @@
       <c r="F8" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>10.28</v>
-      </c>
+      <c r="G8" s="8" t="n"/>
       <c r="H8" s="25">
         <f>IF(G8="","",G8/1.4)</f>
         <v/>
@@ -15762,7 +15772,7 @@
       </c>
       <c r="O8" s="13" t="inlineStr">
         <is>
-          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm.</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15784,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>C6 (20x20)</t>
+          <t>C5 (20x20)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -15792,7 +15802,7 @@
         <v>70</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>32.1</v>
+        <v>19.38</v>
       </c>
       <c r="H9" s="25">
         <f>IF(G9="","",G9/1.4)</f>
@@ -15833,7 +15843,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>C7 (30x15)</t>
+          <t>C6 (30x15)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -15851,7 +15861,7 @@
         <v>70</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>37.27</v>
+        <v>27.95</v>
       </c>
       <c r="H10" s="25">
         <f>IF(G10="","",G10/1.4)</f>
@@ -15880,7 +15890,7 @@
       </c>
       <c r="O10" s="13" t="inlineStr">
         <is>
-          <t>Cantidad de pilotes deducida de la dimension del cabezal: 129x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 129x70 cm. El computo metrico declara un solo CBZ02 y en el plano aparecen dos rotulos. Verificar cual corresponde. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15902,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>C9 (15x30)</t>
+          <t>C8 (15x30)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -15910,7 +15920,7 @@
         <v>70</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>54.89</v>
+        <v>49.7</v>
       </c>
       <c r="H11" s="25">
         <f>IF(G11="","",G11/1.4)</f>
@@ -15951,7 +15961,7 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>C8 (15x30)</t>
+          <t>C7 (15x30)</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -15969,7 +15979,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>42.22</v>
+        <v>50.09</v>
       </c>
       <c r="H12" s="30">
         <f>IF(G12="","",G12/1.4)</f>
@@ -15998,7 +16008,7 @@
       </c>
       <c r="O12" s="20" t="inlineStr">
         <is>
-          <t>Cantidad de pilotes deducida de la dimension del cabezal: 129x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 129x70 cm. El computo metrico declara un solo CBZ02 y en el plano aparecen dos rotulos. Verificar cual corresponde. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
         </is>
       </c>
     </row>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Planilla vigas'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla vigas'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla vigas'!$A$1:$X$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla losas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla losas'!$A$1:$R$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla columnas'!$1:$3</definedName>
@@ -1263,31 +1263,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>33</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2095500" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4162,7 +4137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4485,7 +4460,7 @@
       <c r="A37" s="61" t="inlineStr"/>
       <c r="B37" s="62" t="inlineStr">
         <is>
-          <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
+          <t>NOTA: el computo metrico lista una VI 06 de 15x70x14,00 que no existe en obra;</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4468,7 @@
       <c r="A38" s="61" t="inlineStr"/>
       <c r="B38" s="62" t="inlineStr">
         <is>
-          <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
+          <t>por eso no figura en esta planilla. La cuarta cara de L07 apoya en otro elemento.</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4476,7 @@
       <c r="A39" s="61" t="inlineStr"/>
       <c r="B39" s="62" t="inlineStr">
         <is>
-          <t>Esto define donde la losa aporta ala comprimida:</t>
+          <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4484,7 @@
       <c r="A40" s="61" t="inlineStr"/>
       <c r="B40" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
+          <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4492,7 @@
       <c r="A41" s="61" t="inlineStr"/>
       <c r="B41" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
+          <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4500,7 @@
       <c r="A42" s="61" t="inlineStr"/>
       <c r="B42" s="62" t="inlineStr">
         <is>
-          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
+          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4508,7 @@
       <c r="A43" s="61" t="inlineStr"/>
       <c r="B43" s="62" t="inlineStr">
         <is>
-          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
+          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4516,7 @@
       <c r="A44" s="61" t="inlineStr"/>
       <c r="B44" s="62" t="inlineStr">
         <is>
-          <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
+          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4524,7 @@
       <c r="A45" s="61" t="inlineStr"/>
       <c r="B45" s="62" t="inlineStr">
         <is>
-          <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
+          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
@@ -4557,39 +4532,39 @@
       <c r="A46" s="61" t="inlineStr"/>
       <c r="B46" s="62" t="inlineStr">
         <is>
-          <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
+          <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="61" t="inlineStr"/>
-      <c r="B47" s="62" t="inlineStr"/>
+      <c r="B47" s="62" t="inlineStr">
+        <is>
+          <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="61" t="inlineStr">
-        <is>
-          <t>7. RESULTADO</t>
-        </is>
-      </c>
-      <c r="B48" s="61" t="inlineStr">
-        <is>
-          <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
+      <c r="A48" s="61" t="inlineStr"/>
+      <c r="B48" s="62" t="inlineStr">
+        <is>
+          <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="61" t="inlineStr"/>
-      <c r="B49" s="62" t="inlineStr">
-        <is>
-          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
-        </is>
-      </c>
+      <c r="B49" s="62" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="61" t="inlineStr"/>
-      <c r="B50" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>7. RESULTADO</t>
+        </is>
+      </c>
+      <c r="B50" s="61" t="inlineStr">
+        <is>
+          <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4572,7 @@
       <c r="A51" s="61" t="inlineStr"/>
       <c r="B51" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
+          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4580,7 @@
       <c r="A52" s="61" t="inlineStr"/>
       <c r="B52" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
+          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
@@ -4613,7 +4588,7 @@
       <c r="A53" s="61" t="inlineStr"/>
       <c r="B53" s="62" t="inlineStr">
         <is>
-          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
+          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4596,7 @@
       <c r="A54" s="61" t="inlineStr"/>
       <c r="B54" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
+          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4604,7 @@
       <c r="A55" s="61" t="inlineStr"/>
       <c r="B55" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
+          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4612,7 @@
       <c r="A56" s="61" t="inlineStr"/>
       <c r="B56" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
+          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4620,7 @@
       <c r="A57" s="61" t="inlineStr"/>
       <c r="B57" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
+          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4628,7 @@
       <c r="A58" s="61" t="inlineStr"/>
       <c r="B58" s="62" t="inlineStr">
         <is>
-          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
+          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
@@ -4661,63 +4636,63 @@
       <c r="A59" s="61" t="inlineStr"/>
       <c r="B59" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
+          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="61" t="inlineStr"/>
-      <c r="B60" s="62" t="inlineStr"/>
+      <c r="B60" s="62" t="inlineStr">
+        <is>
+          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="61" t="inlineStr">
-        <is>
-          <t>8. ALCANCE</t>
-        </is>
-      </c>
+      <c r="A61" s="61" t="inlineStr"/>
       <c r="B61" s="62" t="inlineStr">
         <is>
-          <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
+          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="61" t="inlineStr"/>
-      <c r="B62" s="62" t="inlineStr">
+      <c r="B62" s="62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="61" t="inlineStr">
+        <is>
+          <t>8. ALCANCE</t>
+        </is>
+      </c>
+      <c r="B63" s="62" t="inlineStr">
+        <is>
+          <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="61" t="inlineStr"/>
+      <c r="B64" s="62" t="inlineStr">
         <is>
           <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="61" t="inlineStr"/>
-      <c r="B63" s="62" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="61" t="inlineStr">
-        <is>
-          <t>LIMITACIONES</t>
-        </is>
-      </c>
-      <c r="B64" s="61" t="inlineStr">
-        <is>
-          <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="61" t="inlineStr"/>
-      <c r="B65" s="62" t="inlineStr">
-        <is>
-          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
-        </is>
-      </c>
+      <c r="B65" s="62" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="61" t="inlineStr"/>
-      <c r="B66" s="62" t="inlineStr">
-        <is>
-          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
+      <c r="A66" s="61" t="inlineStr">
+        <is>
+          <t>LIMITACIONES</t>
+        </is>
+      </c>
+      <c r="B66" s="61" t="inlineStr">
+        <is>
+          <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
@@ -4725,13 +4700,29 @@
       <c r="A67" s="61" t="inlineStr"/>
       <c r="B67" s="62" t="inlineStr">
         <is>
-          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
+          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="61" t="inlineStr"/>
       <c r="B68" s="62" t="inlineStr">
+        <is>
+          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="61" t="inlineStr"/>
+      <c r="B69" s="62" t="inlineStr">
+        <is>
+          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="61" t="inlineStr"/>
+      <c r="B70" s="62" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -6127,7 +6118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF34"/>
+  <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7116,11 +7107,11 @@
       <c r="A10" s="26" t="n"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>VI 06</t>
+          <t>VI 07a</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>14</v>
+        <v>3.37</v>
       </c>
       <c r="D10" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD10+Datos_vigas!$B$7*J10*L10/10000+Datos_vigas!$B$16*AE10)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD10)</f>
@@ -7158,24 +7149,20 @@
         <v/>
       </c>
       <c r="N10" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="P10" s="25">
         <f>IF(NOT(ISNUMBER(I10)),"---",IF(I10&lt;=0,"---",IF(I10*100/(Datos_vigas!$B$8*AC10*K10^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I10*100/(Datos_vigas!$B$8*AC10*K10^2*Datos_vigas!$B$5)))*AC10*K10*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J10*K10))))</f>
         <v/>
       </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="R10" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
+      <c r="Q10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="S10" s="25">
         <f>F10/(J10*0.85*K10)</f>
@@ -7186,10 +7173,10 @@
         <v/>
       </c>
       <c r="U10" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W10" s="11">
         <f>IF(OR(M10="REVISAR",P10="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M10&lt;&gt;"REVISAR",P10&lt;&gt;"REVISAR",IF(ISNUMBER(M10),N10*PI()*(O10/10)^2/4&gt;=M10,TRUE),IF(ISNUMBER(P10),Q10*PI()*(R10/10)^2/4&gt;=P10,TRUE),IF(ISNUMBER(M10),M10&lt;=0.0163*AB10*K10,TRUE),IF(ISNUMBER(P10),P10&lt;=0.0163*AC10*K10,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F10&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J10*K10+2*PI()*(U10/10)^2/4*Datos_vigas!$B$6*K10/V10)),"NO VERIF. CORTE",IF(NOT(L10&gt;=C10*100/VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -7197,7 +7184,7 @@
       </c>
       <c r="X10" s="13" t="inlineStr">
         <is>
-          <t>Armadura en 2 capas (rec. 6 cm).</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y10" s="10" t="inlineStr">
@@ -7222,24 +7209,24 @@
         <v/>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>1.549</v>
+        <v>0.78</v>
       </c>
       <c r="AE10" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF10" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="26" t="n"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>VI 07a</t>
+          <t>VI 07b</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>3.37</v>
+        <v>4.03</v>
       </c>
       <c r="D11" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD11+Datos_vigas!$B$7*J11*L11/10000+Datos_vigas!$B$16*AE11)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD11)</f>
@@ -7337,7 +7324,7 @@
         <v/>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="10" t="n">
         <v>2.6</v>
@@ -7350,11 +7337,11 @@
       <c r="A12" s="26" t="n"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>VI 07b</t>
+          <t>VI 07c</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.03</v>
+        <v>8.6</v>
       </c>
       <c r="D12" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD12+Datos_vigas!$B$7*J12*L12/10000+Datos_vigas!$B$16*AE12)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD12)</f>
@@ -7392,20 +7379,20 @@
         <v/>
       </c>
       <c r="N12" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P12" s="25">
         <f>IF(NOT(ISNUMBER(I12)),"---",IF(I12&lt;=0,"---",IF(I12*100/(Datos_vigas!$B$8*AC12*K12^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I12*100/(Datos_vigas!$B$8*AC12*K12^2*Datos_vigas!$B$5)))*AC12*K12*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J12*K12))))</f>
         <v/>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S12" s="25">
         <f>F12/(J12*0.85*K12)</f>
@@ -7416,10 +7403,10 @@
         <v/>
       </c>
       <c r="U12" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W12" s="11">
         <f>IF(OR(M12="REVISAR",P12="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M12&lt;&gt;"REVISAR",P12&lt;&gt;"REVISAR",IF(ISNUMBER(M12),N12*PI()*(O12/10)^2/4&gt;=M12,TRUE),IF(ISNUMBER(P12),Q12*PI()*(R12/10)^2/4&gt;=P12,TRUE),IF(ISNUMBER(M12),M12&lt;=0.0163*AB12*K12,TRUE),IF(ISNUMBER(P12),P12&lt;=0.0163*AC12*K12,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F12&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J12*K12+2*PI()*(U12/10)^2/4*Datos_vigas!$B$6*K12/V12)),"NO VERIF. CORTE",IF(NOT(L12&gt;=C12*100/VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -7427,12 +7414,12 @@
       </c>
       <c r="X12" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y12" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Empotrada-apoyada</t>
         </is>
       </c>
       <c r="Z12" s="10" t="inlineStr">
@@ -7452,24 +7439,24 @@
         <v/>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AE12" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="26" t="n"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>VI 07c</t>
+          <t>VI 08a</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="D13" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD13+Datos_vigas!$B$7*J13*L13/10000+Datos_vigas!$B$16*AE13)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD13)</f>
@@ -7507,20 +7494,20 @@
         <v/>
       </c>
       <c r="N13" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P13" s="25">
         <f>IF(NOT(ISNUMBER(I13)),"---",IF(I13&lt;=0,"---",IF(I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)))*AC13*K13*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J13*K13))))</f>
         <v/>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S13" s="25">
         <f>F13/(J13*0.85*K13)</f>
@@ -7531,23 +7518,19 @@
         <v/>
       </c>
       <c r="U13" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W13" s="11">
         <f>IF(OR(M13="REVISAR",P13="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M13&lt;&gt;"REVISAR",P13&lt;&gt;"REVISAR",IF(ISNUMBER(M13),N13*PI()*(O13/10)^2/4&gt;=M13,TRUE),IF(ISNUMBER(P13),Q13*PI()*(R13/10)^2/4&gt;=P13,TRUE),IF(ISNUMBER(M13),M13&lt;=0.0163*AB13*K13,TRUE),IF(ISNUMBER(P13),P13&lt;=0.0163*AC13*K13,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F13&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J13*K13+2*PI()*(U13/10)^2/4*Datos_vigas!$B$6*K13/V13)),"NO VERIF. CORTE",IF(NOT(L13&gt;=C13*100/VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X13" s="13" t="inlineStr">
-        <is>
-          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
-        </is>
-      </c>
+      <c r="X13" s="11" t="n"/>
       <c r="Y13" s="10" t="inlineStr">
         <is>
-          <t>Empotrada-apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z13" s="10" t="inlineStr">
@@ -7567,24 +7550,24 @@
         <v/>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>3.71</v>
+        <v>1.065</v>
       </c>
       <c r="AE13" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="26" t="n"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>VI 08a</t>
+          <t>VI 08b</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>3.65</v>
+        <v>4.87</v>
       </c>
       <c r="D14" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD14+Datos_vigas!$B$7*J14*L14/10000+Datos_vigas!$B$16*AE14)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD14)</f>
@@ -7691,7 +7674,7 @@
       <c r="A15" s="26" t="n"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>VI 08b</t>
+          <t>VI 09</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -7742,11 +7725,15 @@
         <f>IF(NOT(ISNUMBER(I15)),"---",IF(I15&lt;=0,"---",IF(I15*100/(Datos_vigas!$B$8*AC15*K15^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I15*100/(Datos_vigas!$B$8*AC15*K15^2*Datos_vigas!$B$5)))*AC15*K15*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J15*K15))))</f>
         <v/>
       </c>
-      <c r="Q15" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" s="10" t="n">
-        <v>12</v>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
       </c>
       <c r="S15" s="25">
         <f>F15/(J15*0.85*K15)</f>
@@ -7769,7 +7756,7 @@
       <c r="X15" s="11" t="n"/>
       <c r="Y15" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Simplemente apoyada</t>
         </is>
       </c>
       <c r="Z15" s="10" t="inlineStr">
@@ -7789,7 +7776,7 @@
         <v/>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>1.065</v>
+        <v>1.549</v>
       </c>
       <c r="AE15" s="10" t="n">
         <v>2.6</v>
@@ -7802,11 +7789,11 @@
       <c r="A16" s="26" t="n"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>VI 09</t>
+          <t>VI 10a</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>4.87</v>
+        <v>2.55</v>
       </c>
       <c r="D16" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD16+Datos_vigas!$B$7*J16*L16/10000+Datos_vigas!$B$16*AE16)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD16)</f>
@@ -7853,15 +7840,11 @@
         <f>IF(NOT(ISNUMBER(I16)),"---",IF(I16&lt;=0,"---",IF(I16*100/(Datos_vigas!$B$8*AC16*K16^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I16*100/(Datos_vigas!$B$8*AC16*K16^2*Datos_vigas!$B$5)))*AC16*K16*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J16*K16))))</f>
         <v/>
       </c>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="R16" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
+      <c r="Q16" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="S16" s="25">
         <f>F16/(J16*0.85*K16)</f>
@@ -7884,7 +7867,7 @@
       <c r="X16" s="11" t="n"/>
       <c r="Y16" s="10" t="inlineStr">
         <is>
-          <t>Simplemente apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z16" s="10" t="inlineStr">
@@ -7904,7 +7887,7 @@
         <v/>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>1.549</v>
+        <v>0</v>
       </c>
       <c r="AE16" s="10" t="n">
         <v>2.6</v>
@@ -7917,11 +7900,11 @@
       <c r="A17" s="26" t="n"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>VI 10a</t>
+          <t>VI 10b</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="D17" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD17+Datos_vigas!$B$7*J17*L17/10000+Datos_vigas!$B$16*AE17)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD17)</f>
@@ -8015,7 +7998,7 @@
         <v/>
       </c>
       <c r="AD17" s="10" t="n">
-        <v>0</v>
+        <v>1.825</v>
       </c>
       <c r="AE17" s="10" t="n">
         <v>2.6</v>
@@ -8028,11 +8011,11 @@
       <c r="A18" s="26" t="n"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>VI 10b</t>
+          <t>VI 10c</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D18" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD18+Datos_vigas!$B$7*J18*L18/10000+Datos_vigas!$B$16*AE18)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD18)</f>
@@ -8126,7 +8109,7 @@
         <v/>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>1.825</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="10" t="n">
         <v>2.6</v>
@@ -8139,11 +8122,11 @@
       <c r="A19" s="26" t="n"/>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>VI 10c</t>
+          <t>VI 11a</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>3.6</v>
+        <v>7.68</v>
       </c>
       <c r="D19" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD19+Datos_vigas!$B$7*J19*L19/10000+Datos_vigas!$B$16*AE19)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD19)</f>
@@ -8181,20 +8164,20 @@
         <v/>
       </c>
       <c r="N19" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P19" s="25">
         <f>IF(NOT(ISNUMBER(I19)),"---",IF(I19&lt;=0,"---",IF(I19*100/(Datos_vigas!$B$8*AC19*K19^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I19*100/(Datos_vigas!$B$8*AC19*K19^2*Datos_vigas!$B$5)))*AC19*K19*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J19*K19))))</f>
         <v/>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S19" s="25">
         <f>F19/(J19*0.85*K19)</f>
@@ -8208,16 +8191,20 @@
         <v>6</v>
       </c>
       <c r="V19" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W19" s="11">
         <f>IF(OR(M19="REVISAR",P19="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M19&lt;&gt;"REVISAR",P19&lt;&gt;"REVISAR",IF(ISNUMBER(M19),N19*PI()*(O19/10)^2/4&gt;=M19,TRUE),IF(ISNUMBER(P19),Q19*PI()*(R19/10)^2/4&gt;=P19,TRUE),IF(ISNUMBER(M19),M19&lt;=0.0163*AB19*K19,TRUE),IF(ISNUMBER(P19),P19&lt;=0.0163*AC19*K19,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F19&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J19*K19+2*PI()*(U19/10)^2/4*Datos_vigas!$B$6*K19/V19)),"NO VERIF. CORTE",IF(NOT(L19&gt;=C19*100/VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X19" s="11" t="n"/>
+      <c r="X19" s="13" t="inlineStr">
+        <is>
+          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+        </is>
+      </c>
       <c r="Y19" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Empotrada-apoyada</t>
         </is>
       </c>
       <c r="Z19" s="10" t="inlineStr">
@@ -8237,7 +8224,7 @@
         <v/>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>0</v>
+        <v>1.825</v>
       </c>
       <c r="AE19" s="10" t="n">
         <v>2.6</v>
@@ -8250,11 +8237,11 @@
       <c r="A20" s="26" t="n"/>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>VI 11a</t>
+          <t>VI 11b</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>7.68</v>
+        <v>3.45</v>
       </c>
       <c r="D20" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD20+Datos_vigas!$B$7*J20*L20/10000+Datos_vigas!$B$16*AE20)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD20)</f>
@@ -8292,20 +8279,20 @@
         <v/>
       </c>
       <c r="N20" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P20" s="25">
         <f>IF(NOT(ISNUMBER(I20)),"---",IF(I20&lt;=0,"---",IF(I20*100/(Datos_vigas!$B$8*AC20*K20^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I20*100/(Datos_vigas!$B$8*AC20*K20^2*Datos_vigas!$B$5)))*AC20*K20*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J20*K20))))</f>
         <v/>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S20" s="25">
         <f>F20/(J20*0.85*K20)</f>
@@ -8319,7 +8306,7 @@
         <v>6</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W20" s="11">
         <f>IF(OR(M20="REVISAR",P20="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M20&lt;&gt;"REVISAR",P20&lt;&gt;"REVISAR",IF(ISNUMBER(M20),N20*PI()*(O20/10)^2/4&gt;=M20,TRUE),IF(ISNUMBER(P20),Q20*PI()*(R20/10)^2/4&gt;=P20,TRUE),IF(ISNUMBER(M20),M20&lt;=0.0163*AB20*K20,TRUE),IF(ISNUMBER(P20),P20&lt;=0.0163*AC20*K20,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F20&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J20*K20+2*PI()*(U20/10)^2/4*Datos_vigas!$B$6*K20/V20)),"NO VERIF. CORTE",IF(NOT(L20&gt;=C20*100/VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -8327,12 +8314,12 @@
       </c>
       <c r="X20" s="13" t="inlineStr">
         <is>
-          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y20" s="10" t="inlineStr">
         <is>
-          <t>Empotrada-apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z20" s="10" t="inlineStr">
@@ -8352,7 +8339,7 @@
         <v/>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>1.825</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="10" t="n">
         <v>2.6</v>
@@ -8365,11 +8352,11 @@
       <c r="A21" s="26" t="n"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>VI 11b</t>
+          <t>VI 11c</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>3.45</v>
+        <v>5.02</v>
       </c>
       <c r="D21" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD21+Datos_vigas!$B$7*J21*L21/10000+Datos_vigas!$B$16*AE21)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD21)</f>
@@ -8467,7 +8454,7 @@
         <v/>
       </c>
       <c r="AD21" s="10" t="n">
-        <v>0</v>
+        <v>1.549</v>
       </c>
       <c r="AE21" s="10" t="n">
         <v>2.6</v>
@@ -8480,11 +8467,11 @@
       <c r="A22" s="26" t="n"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>VI 11c</t>
+          <t>VCH 03a</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>5.02</v>
+        <v>3.71</v>
       </c>
       <c r="D22" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD22+Datos_vigas!$B$7*J22*L22/10000+Datos_vigas!$B$16*AE22)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD22)</f>
@@ -8508,21 +8495,21 @@
         <v/>
       </c>
       <c r="J22" s="10" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="K22" s="11">
         <f>L22-AF22</f>
         <v/>
       </c>
       <c r="L22" s="10" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="M22" s="25">
         <f>IF(NOT(ISNUMBER(H22)),"---",IF(H22&lt;=0,"---",IF(H22*100/(Datos_vigas!$B$8*AB22*K22^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H22*100/(Datos_vigas!$B$8*AB22*K22^2*Datos_vigas!$B$5)))*AB22*K22*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J22*K22))))</f>
         <v/>
       </c>
       <c r="N22" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O22" s="10" t="n">
         <v>12</v>
@@ -8532,10 +8519,10 @@
         <v/>
       </c>
       <c r="Q22" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S22" s="25">
         <f>F22/(J22*0.85*K22)</f>
@@ -8546,10 +8533,10 @@
         <v/>
       </c>
       <c r="U22" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="W22" s="11">
         <f>IF(OR(M22="REVISAR",P22="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M22&lt;&gt;"REVISAR",P22&lt;&gt;"REVISAR",IF(ISNUMBER(M22),N22*PI()*(O22/10)^2/4&gt;=M22,TRUE),IF(ISNUMBER(P22),Q22*PI()*(R22/10)^2/4&gt;=P22,TRUE),IF(ISNUMBER(M22),M22&lt;=0.0163*AB22*K22,TRUE),IF(ISNUMBER(P22),P22&lt;=0.0163*AC22*K22,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F22&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J22*K22+2*PI()*(U22/10)^2/4*Datos_vigas!$B$6*K22/V22)),"NO VERIF. CORTE",IF(NOT(L22&gt;=C22*100/VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -8557,7 +8544,7 @@
       </c>
       <c r="X22" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+          <t>Excede cuantia maxima y no llega a la altura minima por flecha. Revisar el ancho tributario real. Separacion de estribos menor a 10 cm: revisar constructividad.</t>
         </is>
       </c>
       <c r="Y22" s="10" t="inlineStr">
@@ -8567,7 +8554,7 @@
       </c>
       <c r="Z22" s="10" t="inlineStr">
         <is>
-          <t>Invertida</t>
+          <t>Colgante</t>
         </is>
       </c>
       <c r="AA22" s="10" t="n">
@@ -8582,7 +8569,7 @@
         <v/>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>1.549</v>
+        <v>2.1</v>
       </c>
       <c r="AE22" s="10" t="n">
         <v>2.6</v>
@@ -8595,11 +8582,11 @@
       <c r="A23" s="26" t="n"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>VCH 03a</t>
+          <t>VCH 03b</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>3.71</v>
+        <v>2.13</v>
       </c>
       <c r="D23" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD23+Datos_vigas!$B$7*J23*L23/10000+Datos_vigas!$B$16*AE23)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD23)</f>
@@ -8637,20 +8624,20 @@
         <v/>
       </c>
       <c r="N23" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P23" s="25">
         <f>IF(NOT(ISNUMBER(I23)),"---",IF(I23&lt;=0,"---",IF(I23*100/(Datos_vigas!$B$8*AC23*K23^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I23*100/(Datos_vigas!$B$8*AC23*K23^2*Datos_vigas!$B$5)))*AC23*K23*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J23*K23))))</f>
         <v/>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S23" s="25">
         <f>F23/(J23*0.85*K23)</f>
@@ -8672,7 +8659,7 @@
       </c>
       <c r="X23" s="13" t="inlineStr">
         <is>
-          <t>Excede cuantia maxima y no llega a la altura minima por flecha. Revisar el ancho tributario real. Separacion de estribos menor a 10 cm: revisar constructividad.</t>
+          <t>Separacion de estribos menor a 10 cm: revisar constructividad.</t>
         </is>
       </c>
       <c r="Y23" s="10" t="inlineStr">
@@ -8707,251 +8694,247 @@
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="26" t="n"/>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>VCH 03b</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="D24" s="24">
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>VCH 05</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="D24" s="29">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD24+Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*AE24)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD24)</f>
         <v/>
       </c>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="24">
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="29">
         <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,4,0)*D24*C24</f>
         <v/>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="29">
         <f>F24</f>
         <v/>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="29">
         <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,2,0)*D24*C24^2</f>
         <v/>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="29">
         <f>IF(VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)*D24*C24^2)</f>
         <v/>
       </c>
-      <c r="J24" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="K24" s="11">
+      <c r="J24" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K24" s="18">
         <f>L24-AF24</f>
         <v/>
       </c>
-      <c r="L24" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="M24" s="25">
+      <c r="L24" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="M24" s="30">
         <f>IF(NOT(ISNUMBER(H24)),"---",IF(H24&lt;=0,"---",IF(H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)))*AB24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
         <v/>
       </c>
-      <c r="N24" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="O24" s="10" t="n">
+      <c r="N24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="P24" s="30">
+        <f>IF(NOT(ISNUMBER(I24)),"---",IF(I24&lt;=0,"---",IF(I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)))*AC24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R24" s="17" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S24" s="30">
+        <f>F24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="T24" s="30">
+        <f>G24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="P24" s="25">
-        <f>IF(NOT(ISNUMBER(I24)),"---",IF(I24&lt;=0,"---",IF(I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)))*AC24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R24" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="S24" s="25">
-        <f>F24/(J24*0.85*K24)</f>
-        <v/>
-      </c>
-      <c r="T24" s="25">
-        <f>G24/(J24*0.85*K24)</f>
-        <v/>
-      </c>
-      <c r="U24" s="10" t="n">
+      <c r="V24" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="W24" s="18">
+        <f>IF(OR(M24="REVISAR",P24="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M24&lt;&gt;"REVISAR",P24&lt;&gt;"REVISAR",IF(ISNUMBER(M24),N24*PI()*(O24/10)^2/4&gt;=M24,TRUE),IF(ISNUMBER(P24),Q24*PI()*(R24/10)^2/4&gt;=P24,TRUE),IF(ISNUMBER(M24),M24&lt;=0.0163*AB24*K24,TRUE),IF(ISNUMBER(P24),P24&lt;=0.0163*AC24*K24,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F24&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J24*K24+2*PI()*(U24/10)^2/4*Datos_vigas!$B$6*K24/V24)),"NO VERIF. CORTE",IF(NOT(L24&gt;=C24*100/VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X24" s="18" t="n"/>
+      <c r="Y24" s="17" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="Z24" s="17" t="inlineStr">
+        <is>
+          <t>Colgante</t>
+        </is>
+      </c>
+      <c r="AA24" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="V24" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W24" s="11">
-        <f>IF(OR(M24="REVISAR",P24="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M24&lt;&gt;"REVISAR",P24&lt;&gt;"REVISAR",IF(ISNUMBER(M24),N24*PI()*(O24/10)^2/4&gt;=M24,TRUE),IF(ISNUMBER(P24),Q24*PI()*(R24/10)^2/4&gt;=P24,TRUE),IF(ISNUMBER(M24),M24&lt;=0.0163*AB24*K24,TRUE),IF(ISNUMBER(P24),P24&lt;=0.0163*AC24*K24,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F24&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J24*K24+2*PI()*(U24/10)^2/4*Datos_vigas!$B$6*K24/V24)),"NO VERIF. CORTE",IF(NOT(L24&gt;=C24*100/VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X24" s="13" t="inlineStr">
-        <is>
-          <t>Separacion de estribos menor a 10 cm: revisar constructividad.</t>
-        </is>
-      </c>
-      <c r="Y24" s="10" t="inlineStr">
+      <c r="AB24" s="18">
+        <f>IF(Z24="Colgante",MIN(C24*100/4,J24+16*AA24),J24)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="18">
+        <f>IF(Z24="Invertida",MIN(C24*100/4,J24+16*AA24),J24)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF24" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>TECHO</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>VI 12</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D25" s="24">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AE25)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="24">
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="24">
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
+        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2)</f>
+        <v/>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K25" s="11">
+        <f>L25-AF25</f>
+        <v/>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="M25" s="25">
+        <f>IF(NOT(ISNUMBER(H25)),"---",IF(H25&lt;=0,"---",IF(H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)))*AB25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="P25" s="25">
+        <f>IF(NOT(ISNUMBER(I25)),"---",IF(I25&lt;=0,"---",IF(I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)))*AC25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="S25" s="25">
+        <f>F25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="T25" s="25">
+        <f>G25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V25" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="W25" s="11">
+        <f>IF(OR(M25="REVISAR",P25="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M25&lt;&gt;"REVISAR",P25&lt;&gt;"REVISAR",IF(ISNUMBER(M25),N25*PI()*(O25/10)^2/4&gt;=M25,TRUE),IF(ISNUMBER(P25),Q25*PI()*(R25/10)^2/4&gt;=P25,TRUE),IF(ISNUMBER(M25),M25&lt;=0.0163*AB25*K25,TRUE),IF(ISNUMBER(P25),P25&lt;=0.0163*AC25*K25,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F25&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J25*K25+2*PI()*(U25/10)^2/4*Datos_vigas!$B$6*K25/V25)),"NO VERIF. CORTE",IF(NOT(L25&gt;=C25*100/VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
-      <c r="Z24" s="10" t="inlineStr">
-        <is>
-          <t>Colgante</t>
-        </is>
-      </c>
-      <c r="AA24" s="10" t="n">
+      <c r="Z25" s="10" t="inlineStr">
+        <is>
+          <t>Invertida</t>
+        </is>
+      </c>
+      <c r="AA25" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="AB24" s="11">
-        <f>IF(Z24="Colgante",MIN(C24*100/4,J24+16*AA24),J24)</f>
-        <v/>
-      </c>
-      <c r="AC24" s="11">
-        <f>IF(Z24="Invertida",MIN(C24*100/4,J24+16*AA24),J24)</f>
-        <v/>
-      </c>
-      <c r="AD24" s="10" t="n">
+      <c r="AB25" s="11">
+        <f>IF(Z25="Colgante",MIN(C25*100/4,J25+16*AA25),J25)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="11">
+        <f>IF(Z25="Invertida",MIN(C25*100/4,J25+16*AA25),J25)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE24" s="10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF24" s="10" t="n">
+      <c r="AE25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="10" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="27" t="n"/>
-      <c r="B25" s="28" t="inlineStr">
-        <is>
-          <t>VCH 05</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="D25" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AE25)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD25)</f>
-        <v/>
-      </c>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="29">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25</f>
-        <v/>
-      </c>
-      <c r="G25" s="29">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="29">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2</f>
-        <v/>
-      </c>
-      <c r="I25" s="29">
-        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2)</f>
-        <v/>
-      </c>
-      <c r="J25" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K25" s="18">
-        <f>L25-AF25</f>
-        <v/>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="M25" s="30">
-        <f>IF(NOT(ISNUMBER(H25)),"---",IF(H25&lt;=0,"---",IF(H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)))*AB25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
-        <v/>
-      </c>
-      <c r="N25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="P25" s="30">
-        <f>IF(NOT(ISNUMBER(I25)),"---",IF(I25&lt;=0,"---",IF(I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)))*AC25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="17" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="R25" s="17" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="S25" s="30">
-        <f>F25/(J25*0.85*K25)</f>
-        <v/>
-      </c>
-      <c r="T25" s="30">
-        <f>G25/(J25*0.85*K25)</f>
-        <v/>
-      </c>
-      <c r="U25" s="17" t="n">
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>VI 13a</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="V25" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="W25" s="18">
-        <f>IF(OR(M25="REVISAR",P25="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M25&lt;&gt;"REVISAR",P25&lt;&gt;"REVISAR",IF(ISNUMBER(M25),N25*PI()*(O25/10)^2/4&gt;=M25,TRUE),IF(ISNUMBER(P25),Q25*PI()*(R25/10)^2/4&gt;=P25,TRUE),IF(ISNUMBER(M25),M25&lt;=0.0163*AB25*K25,TRUE),IF(ISNUMBER(P25),P25&lt;=0.0163*AC25*K25,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F25&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J25*K25+2*PI()*(U25/10)^2/4*Datos_vigas!$B$6*K25/V25)),"NO VERIF. CORTE",IF(NOT(L25&gt;=C25*100/VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X25" s="18" t="n"/>
-      <c r="Y25" s="17" t="inlineStr">
-        <is>
-          <t>Simplemente apoyada</t>
-        </is>
-      </c>
-      <c r="Z25" s="17" t="inlineStr">
-        <is>
-          <t>Colgante</t>
-        </is>
-      </c>
-      <c r="AA25" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB25" s="18">
-        <f>IF(Z25="Colgante",MIN(C25*100/4,J25+16*AA25),J25)</f>
-        <v/>
-      </c>
-      <c r="AC25" s="18">
-        <f>IF(Z25="Invertida",MIN(C25*100/4,J25+16*AA25),J25)</f>
-        <v/>
-      </c>
-      <c r="AD25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF25" s="17" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>TECHO</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>VI 12</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>9.9</v>
-      </c>
       <c r="D26" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AE26)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD26)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AE26)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD26)</f>
         <v/>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -8989,7 +8972,7 @@
         <v>2</v>
       </c>
       <c r="O26" s="10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="P26" s="25">
         <f>IF(NOT(ISNUMBER(I26)),"---",IF(I26&lt;=0,"---",IF(I26*100/(Datos_vigas!$B$8*AC26*K26^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I26*100/(Datos_vigas!$B$8*AC26*K26^2*Datos_vigas!$B$5)))*AC26*K26*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J26*K26))))</f>
@@ -8999,7 +8982,7 @@
         <v>2</v>
       </c>
       <c r="R26" s="10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S26" s="25">
         <f>F26/(J26*0.85*K26)</f>
@@ -9042,7 +9025,7 @@
         <v/>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>2.1</v>
+        <v>3.799</v>
       </c>
       <c r="AE26" s="10" t="n">
         <v>1</v>
@@ -9055,14 +9038,14 @@
       <c r="A27" s="26" t="n"/>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>VI 13a</t>
+          <t>VI 13b</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="D27" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AE27)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD27)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AE27)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD27)</f>
         <v/>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -9097,20 +9080,20 @@
         <v/>
       </c>
       <c r="N27" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P27" s="25">
         <f>IF(NOT(ISNUMBER(I27)),"---",IF(I27&lt;=0,"---",IF(I27*100/(Datos_vigas!$B$8*AC27*K27^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I27*100/(Datos_vigas!$B$8*AC27*K27^2*Datos_vigas!$B$5)))*AC27*K27*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J27*K27))))</f>
         <v/>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S27" s="25">
         <f>F27/(J27*0.85*K27)</f>
@@ -9124,7 +9107,7 @@
         <v>6</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="W27" s="11">
         <f>IF(OR(M27="REVISAR",P27="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M27&lt;&gt;"REVISAR",P27&lt;&gt;"REVISAR",IF(ISNUMBER(M27),N27*PI()*(O27/10)^2/4&gt;=M27,TRUE),IF(ISNUMBER(P27),Q27*PI()*(R27/10)^2/4&gt;=P27,TRUE),IF(ISNUMBER(M27),M27&lt;=0.0163*AB27*K27,TRUE),IF(ISNUMBER(P27),P27&lt;=0.0163*AC27*K27,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F27&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J27*K27+2*PI()*(U27/10)^2/4*Datos_vigas!$B$6*K27/V27)),"NO VERIF. CORTE",IF(NOT(L27&gt;=C27*100/VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -9153,7 +9136,7 @@
         <v/>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>3.799</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" s="10" t="n">
         <v>1</v>
@@ -9166,14 +9149,14 @@
       <c r="A28" s="26" t="n"/>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>VI 13b</t>
+          <t>VI 14</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="D28" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AE28)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD28)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AE28)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD28)</f>
         <v/>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -9264,7 +9247,7 @@
         <v/>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>2.1</v>
+        <v>1.699</v>
       </c>
       <c r="AE28" s="10" t="n">
         <v>1</v>
@@ -9277,14 +9260,14 @@
       <c r="A29" s="26" t="n"/>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>VI 14</t>
+          <t>VI 15a</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>6</v>
+        <v>4.03</v>
       </c>
       <c r="D29" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AE29)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD29)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AE29)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD29)</f>
         <v/>
       </c>
       <c r="E29" s="11" t="n"/>
@@ -9352,7 +9335,11 @@
         <f>IF(OR(M29="REVISAR",P29="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M29&lt;&gt;"REVISAR",P29&lt;&gt;"REVISAR",IF(ISNUMBER(M29),N29*PI()*(O29/10)^2/4&gt;=M29,TRUE),IF(ISNUMBER(P29),Q29*PI()*(R29/10)^2/4&gt;=P29,TRUE),IF(ISNUMBER(M29),M29&lt;=0.0163*AB29*K29,TRUE),IF(ISNUMBER(P29),P29&lt;=0.0163*AC29*K29,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F29&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J29*K29+2*PI()*(U29/10)^2/4*Datos_vigas!$B$6*K29/V29)),"NO VERIF. CORTE",IF(NOT(L29&gt;=C29*100/VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X29" s="11" t="n"/>
+      <c r="X29" s="13" t="inlineStr">
+        <is>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+        </is>
+      </c>
       <c r="Y29" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -9375,7 +9362,7 @@
         <v/>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>1.699</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="10" t="n">
         <v>1</v>
@@ -9388,14 +9375,14 @@
       <c r="A30" s="26" t="n"/>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>VI 15a</t>
+          <t>VI 15b</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4.03</v>
+        <v>4.85</v>
       </c>
       <c r="D30" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AE30)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD30)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AE30)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD30)</f>
         <v/>
       </c>
       <c r="E30" s="11" t="n"/>
@@ -9490,7 +9477,7 @@
         <v/>
       </c>
       <c r="AD30" s="10" t="n">
-        <v>0</v>
+        <v>1.699</v>
       </c>
       <c r="AE30" s="10" t="n">
         <v>1</v>
@@ -9503,14 +9490,14 @@
       <c r="A31" s="26" t="n"/>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>VI 15b</t>
+          <t>VI 16a</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>4.85</v>
+        <v>3.58</v>
       </c>
       <c r="D31" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AE31)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD31)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AE31)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD31)</f>
         <v/>
       </c>
       <c r="E31" s="11" t="n"/>
@@ -9578,11 +9565,7 @@
         <f>IF(OR(M31="REVISAR",P31="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M31&lt;&gt;"REVISAR",P31&lt;&gt;"REVISAR",IF(ISNUMBER(M31),N31*PI()*(O31/10)^2/4&gt;=M31,TRUE),IF(ISNUMBER(P31),Q31*PI()*(R31/10)^2/4&gt;=P31,TRUE),IF(ISNUMBER(M31),M31&lt;=0.0163*AB31*K31,TRUE),IF(ISNUMBER(P31),P31&lt;=0.0163*AC31*K31,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F31&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J31*K31+2*PI()*(U31/10)^2/4*Datos_vigas!$B$6*K31/V31)),"NO VERIF. CORTE",IF(NOT(L31&gt;=C31*100/VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X31" s="13" t="inlineStr">
-        <is>
-          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
-        </is>
-      </c>
+      <c r="X31" s="11" t="n"/>
       <c r="Y31" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -9618,14 +9601,14 @@
       <c r="A32" s="26" t="n"/>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>VI 16a</t>
+          <t>VI 16b</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>3.58</v>
+        <v>1.12</v>
       </c>
       <c r="D32" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AE32)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD32)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AE32)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD32)</f>
         <v/>
       </c>
       <c r="E32" s="11" t="n"/>
@@ -9726,241 +9709,130 @@
       </c>
     </row>
     <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="26" t="n"/>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>VI 16b</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="D33" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AE33)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD33)</f>
-        <v/>
-      </c>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="24">
+      <c r="A33" s="27" t="n"/>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>VI 17</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="D33" s="29">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AE33)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="29">
         <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,4,0)*D33*C33</f>
         <v/>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="29">
         <f>F33</f>
         <v/>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="29">
         <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,2,0)*D33*C33^2</f>
         <v/>
       </c>
-      <c r="I33" s="24">
+      <c r="I33" s="29">
         <f>IF(VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)*D33*C33^2)</f>
         <v/>
       </c>
-      <c r="J33" s="10" t="n">
+      <c r="J33" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="K33" s="11">
+      <c r="K33" s="18">
         <f>L33-AF33</f>
         <v/>
       </c>
-      <c r="L33" s="10" t="n">
+      <c r="L33" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="M33" s="25">
+      <c r="M33" s="30">
         <f>IF(NOT(ISNUMBER(H33)),"---",IF(H33&lt;=0,"---",IF(H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)))*AB33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
         <v/>
       </c>
-      <c r="N33" s="10" t="n">
+      <c r="N33" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="O33" s="10" t="n">
+      <c r="O33" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="P33" s="25">
+      <c r="P33" s="30">
         <f>IF(NOT(ISNUMBER(I33)),"---",IF(I33&lt;=0,"---",IF(I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)))*AC33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
         <v/>
       </c>
-      <c r="Q33" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R33" s="10" t="n">
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="S33" s="30">
+        <f>F33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="T33" s="30">
+        <f>G33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="W33" s="18">
+        <f>IF(OR(M33="REVISAR",P33="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M33&lt;&gt;"REVISAR",P33&lt;&gt;"REVISAR",IF(ISNUMBER(M33),N33*PI()*(O33/10)^2/4&gt;=M33,TRUE),IF(ISNUMBER(P33),Q33*PI()*(R33/10)^2/4&gt;=P33,TRUE),IF(ISNUMBER(M33),M33&lt;=0.0163*AB33*K33,TRUE),IF(ISNUMBER(P33),P33&lt;=0.0163*AC33*K33,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F33&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J33*K33+2*PI()*(U33/10)^2/4*Datos_vigas!$B$6*K33/V33)),"NO VERIF. CORTE",IF(NOT(L33&gt;=C33*100/VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X33" s="18" t="n"/>
+      <c r="Y33" s="17" t="inlineStr">
+        <is>
+          <t>Simplemente apoyada</t>
+        </is>
+      </c>
+      <c r="Z33" s="17" t="inlineStr">
+        <is>
+          <t>Invertida</t>
+        </is>
+      </c>
+      <c r="AA33" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="S33" s="25">
-        <f>F33/(J33*0.85*K33)</f>
-        <v/>
-      </c>
-      <c r="T33" s="25">
-        <f>G33/(J33*0.85*K33)</f>
-        <v/>
-      </c>
-      <c r="U33" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="V33" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="W33" s="11">
-        <f>IF(OR(M33="REVISAR",P33="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M33&lt;&gt;"REVISAR",P33&lt;&gt;"REVISAR",IF(ISNUMBER(M33),N33*PI()*(O33/10)^2/4&gt;=M33,TRUE),IF(ISNUMBER(P33),Q33*PI()*(R33/10)^2/4&gt;=P33,TRUE),IF(ISNUMBER(M33),M33&lt;=0.0163*AB33*K33,TRUE),IF(ISNUMBER(P33),P33&lt;=0.0163*AC33*K33,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F33&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J33*K33+2*PI()*(U33/10)^2/4*Datos_vigas!$B$6*K33/V33)),"NO VERIF. CORTE",IF(NOT(L33&gt;=C33*100/VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="10" t="inlineStr">
-        <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="Z33" s="10" t="inlineStr">
-        <is>
-          <t>Invertida</t>
-        </is>
-      </c>
-      <c r="AA33" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB33" s="11">
+      <c r="AB33" s="18">
         <f>IF(Z33="Colgante",MIN(C33*100/4,J33+16*AA33),J33)</f>
         <v/>
       </c>
-      <c r="AC33" s="11">
+      <c r="AC33" s="18">
         <f>IF(Z33="Invertida",MIN(C33*100/4,J33+16*AA33),J33)</f>
         <v/>
       </c>
-      <c r="AD33" s="10" t="n">
-        <v>1.699</v>
-      </c>
-      <c r="AE33" s="10" t="n">
+      <c r="AD33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="AF33" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" ht="46" customHeight="1">
-      <c r="A34" s="27" t="n"/>
-      <c r="B34" s="28" t="inlineStr">
-        <is>
-          <t>VI 17</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="D34" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD34+Datos_vigas!$B$7*J34*L34/10000+Datos_vigas!$B$16*AE34)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD34)</f>
-        <v/>
-      </c>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="29">
-        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,4,0)*D34*C34</f>
-        <v/>
-      </c>
-      <c r="G34" s="29">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="H34" s="29">
-        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,2,0)*D34*C34^2</f>
-        <v/>
-      </c>
-      <c r="I34" s="29">
-        <f>IF(VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)*D34*C34^2)</f>
-        <v/>
-      </c>
-      <c r="J34" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K34" s="18">
-        <f>L34-AF34</f>
-        <v/>
-      </c>
-      <c r="L34" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="M34" s="30">
-        <f>IF(NOT(ISNUMBER(H34)),"---",IF(H34&lt;=0,"---",IF(H34*100/(Datos_vigas!$B$8*AB34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H34*100/(Datos_vigas!$B$8*AB34*K34^2*Datos_vigas!$B$5)))*AB34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
-        <v/>
-      </c>
-      <c r="N34" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="P34" s="30">
-        <f>IF(NOT(ISNUMBER(I34)),"---",IF(I34&lt;=0,"---",IF(I34*100/(Datos_vigas!$B$8*AC34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I34*100/(Datos_vigas!$B$8*AC34*K34^2*Datos_vigas!$B$5)))*AC34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
-        <v/>
-      </c>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="R34" s="17" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="S34" s="30">
-        <f>F34/(J34*0.85*K34)</f>
-        <v/>
-      </c>
-      <c r="T34" s="30">
-        <f>G34/(J34*0.85*K34)</f>
-        <v/>
-      </c>
-      <c r="U34" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="V34" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="W34" s="18">
-        <f>IF(OR(M34="REVISAR",P34="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M34&lt;&gt;"REVISAR",P34&lt;&gt;"REVISAR",IF(ISNUMBER(M34),N34*PI()*(O34/10)^2/4&gt;=M34,TRUE),IF(ISNUMBER(P34),Q34*PI()*(R34/10)^2/4&gt;=P34,TRUE),IF(ISNUMBER(M34),M34&lt;=0.0163*AB34*K34,TRUE),IF(ISNUMBER(P34),P34&lt;=0.0163*AC34*K34,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F34&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J34*K34+2*PI()*(U34/10)^2/4*Datos_vigas!$B$6*K34/V34)),"NO VERIF. CORTE",IF(NOT(L34&gt;=C34*100/VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X34" s="18" t="n"/>
-      <c r="Y34" s="17" t="inlineStr">
-        <is>
-          <t>Simplemente apoyada</t>
-        </is>
-      </c>
-      <c r="Z34" s="17" t="inlineStr">
-        <is>
-          <t>Invertida</t>
-        </is>
-      </c>
-      <c r="AA34" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB34" s="18">
-        <f>IF(Z34="Colgante",MIN(C34*100/4,J34+16*AA34),J34)</f>
-        <v/>
-      </c>
-      <c r="AC34" s="18">
-        <f>IF(Z34="Invertida",MIN(C34*100/4,J34+16*AA34),J34)</f>
-        <v/>
-      </c>
-      <c r="AD34" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="17" t="n">
+      <c r="AF33" s="17" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A4:A24"/>
     <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A25"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A25:A33"/>
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="S2:U2"/>
-    <mergeCell ref="A26:A34"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="V2"/>
     <mergeCell ref="B2:B3"/>
@@ -9972,7 +9844,7 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="W2:W3"/>
   </mergeCells>
-  <conditionalFormatting sqref="W4:W34">
+  <conditionalFormatting sqref="W4:W33">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"VERIFICA"</formula>
     </cfRule>
@@ -9987,13 +9859,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="Y4:Y34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y4:Y33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_vigas!$A$19:$A$23</formula1>
     </dataValidation>
-    <dataValidation sqref="Z4:Z34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Z4:Z33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Invertida,Colgante"</formula1>
     </dataValidation>
-    <dataValidation sqref="O4:O34 R4:R34 U4:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O4:O33 R4:R33 U4:U33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"6,8,10,12,16,20,25"</formula1>
     </dataValidation>
   </dataValidations>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla losas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla losas'!$A$1:$R$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla columnas'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Planilla columnas'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Planilla columnas'!$A$1:$N$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Vigas de fundacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Vigas de fundacion'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Pilotes y cabezales'!$1:$3</definedName>
@@ -5125,7 +5125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5200,7 +5200,7 @@
       <c r="A9" s="61" t="inlineStr"/>
       <c r="B9" s="62" t="inlineStr">
         <is>
-          <t>La planilla modelo de la catedra tiene 10 columnas en PB: puede faltar una que no</t>
+          <t>La C01 de 10x10 esta confirmada por el proyectista aunque el computo metrico no</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="A10" s="61" t="inlineStr"/>
       <c r="B10" s="62" t="inlineStr">
         <is>
-          <t>haya podido resolverse por rotulo. Conviene contarlas en el plano.</t>
+          <t>la incluya en su item 4.1.3: ese computo esta incompleto en ese punto.</t>
         </is>
       </c>
     </row>
@@ -5443,12 +5443,12 @@
     <row r="40">
       <c r="A40" s="61" t="inlineStr">
         <is>
-          <t>7. C4, A REVISAR</t>
+          <t>7. LA DE 10x10</t>
         </is>
       </c>
       <c r="B40" s="61" t="inlineStr">
         <is>
-          <t>C4 figura en el plano como 10x10 y recibe el extremo de VI 01a, con 17 t de</t>
+          <t>Existe, confirmada por el proyectista, y el computo metrico la omite. Con 10 cm</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       <c r="A41" s="61" t="inlineStr"/>
       <c r="B41" s="62" t="inlineStr">
         <is>
-          <t>reaccion. Una columna de 10x10 no toma esa carga. VI 01a corre sobre la medianera,</t>
+          <t>de lado y 3,15 m de altura su esbeltez es k lu / r = 105, tres veces el limite</t>
         </is>
       </c>
     </row>
@@ -5464,37 +5464,53 @@
       <c r="A42" s="61" t="inlineStr"/>
       <c r="B42" s="62" t="inlineStr">
         <is>
-          <t>asi que lo mas probable es que apoye en el muro y ese 10x10 no sea una columna.</t>
+          <t>por debajo del cual se puede despreciar el pandeo, y su capacidad es de 18,7 t</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="61" t="inlineStr"/>
-      <c r="B43" s="62" t="inlineStr"/>
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>contra los 51 de una 15x30. Es el punto mas delicado del conjunto: conviene</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="61" t="inlineStr">
-        <is>
-          <t>LIMITACIONES</t>
-        </is>
-      </c>
-      <c r="B44" s="61" t="inlineStr">
-        <is>
-          <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
+      <c r="A44" s="61" t="inlineStr"/>
+      <c r="B44" s="62" t="inlineStr">
+        <is>
+          <t>verificarla a segundo orden en serio, no con la formula de compresion simple.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="61" t="inlineStr"/>
-      <c r="B45" s="62" t="inlineStr">
+      <c r="B45" s="62" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="61" t="inlineStr">
+        <is>
+          <t>LIMITACIONES</t>
+        </is>
+      </c>
+      <c r="B46" s="61" t="inlineStr">
+        <is>
+          <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="61" t="inlineStr"/>
+      <c r="B47" s="62" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="61" t="inlineStr"/>
-      <c r="B46" s="62" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="61" t="inlineStr"/>
+      <c r="B48" s="62" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>
@@ -10974,7 +10990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11623,13 +11639,13 @@
         <v>3.15</v>
       </c>
       <c r="D11" s="37" t="n">
-        <v>15.96</v>
+        <v>10.28</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G11" s="11">
         <f>E11*F11</f>
@@ -11658,7 +11674,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+          <t>COL 01 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5). Columna de 10x10, confirmada por el proyectista. El computo metrico la omite: ese computo esta incompleto en el item 4.1.3. Esbeltez muy alta (k lu / r = 105) y capacidad de solo 18,7 t: es la columna mas comprometida del conjunto.</t>
         </is>
       </c>
       <c r="O11" s="9">
@@ -11674,7 +11690,7 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>15.96</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
@@ -11688,13 +11704,13 @@
         <v>3.15</v>
       </c>
       <c r="D12" s="37" t="n">
-        <v>19.38</v>
+        <v>15.96</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G12" s="11">
         <f>E12*F12</f>
@@ -11723,7 +11739,7 @@
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>COL 04 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O12" s="9">
@@ -11739,7 +11755,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>19.38</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -11753,13 +11769,13 @@
         <v>3.15</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>27.95</v>
+        <v>32.1</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G13" s="11">
         <f>E13*F13</f>
@@ -11788,7 +11804,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>COL 03 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+          <t>COL 04 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O13" s="9">
@@ -11804,7 +11820,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>27.95</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -11818,13 +11834,13 @@
         <v>3.15</v>
       </c>
       <c r="D14" s="37" t="n">
-        <v>50.09</v>
+        <v>37.78</v>
       </c>
       <c r="E14" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>15</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>30</v>
       </c>
       <c r="G14" s="11">
         <f>E14*F14</f>
@@ -11853,7 +11869,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+          <t>COL 03 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
       <c r="O14" s="9">
@@ -11869,80 +11885,145 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>50.09</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="27" t="n"/>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="A15" s="26" t="n"/>
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>C8</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="8" t="n">
         <v>3.15</v>
       </c>
-      <c r="D15" s="39" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="E15" s="17" t="n">
+      <c r="D15" s="37" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="11">
         <f>E15*F15</f>
         <v/>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="25">
         <f>Datos_columnas!$B$8*G15</f>
         <v/>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="K15" s="17" t="n">
+      <c r="K15" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="11">
         <f>FLOOR(MIN(12*J15/10,48*K15/10,MIN(E15,F15)),5)</f>
         <v/>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="11">
         <f>IF(D15="","FALTA CARGA",IF(O15&lt;H15,"ARM. INSUFIC.",IF(D15&gt;P15,"NO VERIFICA",IF(D15&gt;0.85*P15,"AL LIMITE",IF(Q15&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
         <v/>
       </c>
-      <c r="N15" s="20" t="inlineStr">
+      <c r="N15" s="13" t="inlineStr">
         <is>
           <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
         </is>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="9">
         <f>I15*PI()*(J15/10)^2/4</f>
         <v/>
       </c>
-      <c r="P15" s="16">
+      <c r="P15" s="9">
         <f>Datos_columnas!$B$7*0.8*(0.85*Datos_columnas!$B$4*(G15-O15)+Datos_columnas!$B$5*O15)/1000</f>
         <v/>
       </c>
-      <c r="Q15" s="40">
+      <c r="Q15" s="38">
         <f>100*C15/(0.3*MIN(E15,F15))</f>
         <v/>
       </c>
-      <c r="R15" s="16" t="n">
-        <v>49.7</v>
+      <c r="R15" s="9" t="n">
+        <v>42.67</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D16" s="39" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="18">
+        <f>E16*F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="30">
+        <f>Datos_columnas!$B$8*G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" s="18">
+        <f>FLOOR(MIN(12*J16/10,48*K16/10,MIN(E16,F16)),5)</f>
+        <v/>
+      </c>
+      <c r="M16" s="18">
+        <f>IF(D16="","FALTA CARGA",IF(O16&lt;H16,"ARM. INSUFIC.",IF(D16&gt;P16,"NO VERIFICA",IF(D16&gt;0.85*P16,"AL LIMITE",IF(Q16&gt;34,"VERIF. ESBELTEZ","VERIFICA")))))</f>
+        <v/>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>COL 02 del plano. Carga PROVISORIA por bajada automatica; es un piso, la real es mayor (ver Memoria, punto 5).</t>
+        </is>
+      </c>
+      <c r="O16" s="16">
+        <f>I16*PI()*(J16/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="P16" s="16">
+        <f>Datos_columnas!$B$7*0.8*(0.85*Datos_columnas!$B$4*(G16-O16)+Datos_columnas!$B$5*O16)/1000</f>
+        <v/>
+      </c>
+      <c r="Q16" s="40">
+        <f>100*C16/(0.3*MIN(E16,F16))</f>
+        <v/>
+      </c>
+      <c r="R16" s="16" t="n">
+        <v>54.93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="E2:G2"/>
-    <mergeCell ref="A8:A15"/>
     <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A8:A16"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="H2:J2"/>
@@ -11953,7 +12034,7 @@
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="O2:R2"/>
   </mergeCells>
-  <conditionalFormatting sqref="M4:M15">
+  <conditionalFormatting sqref="M4:M16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"VERIFICA"</formula>
     </cfRule>
@@ -11974,7 +12055,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J15 K4:K15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J16 K4:K16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"6,8,10,12,16,20,25"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15481,7 +15562,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>C4 (15x30)</t>
+          <t>C5 (15x30)</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -15599,7 +15680,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C4 (10x10)</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -15616,7 +15697,9 @@
       <c r="F8" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="G8" s="8" t="n"/>
+      <c r="G8" s="8" t="n">
+        <v>10.28</v>
+      </c>
       <c r="H8" s="25">
         <f>IF(G8="","",G8/1.4)</f>
         <v/>
@@ -15644,7 +15727,7 @@
       </c>
       <c r="O8" s="13" t="inlineStr">
         <is>
-          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm.</t>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 70x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15739,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>C5 (20x20)</t>
+          <t>C6 (20x20)</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -15674,7 +15757,7 @@
         <v>70</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>19.38</v>
+        <v>32.1</v>
       </c>
       <c r="H9" s="25">
         <f>IF(G9="","",G9/1.4)</f>
@@ -15715,7 +15798,7 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>C6 (30x15)</t>
+          <t>C7 (30x15)</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -15733,7 +15816,7 @@
         <v>70</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>27.95</v>
+        <v>37.78</v>
       </c>
       <c r="H10" s="25">
         <f>IF(G10="","",G10/1.4)</f>
@@ -15774,7 +15857,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>C8 (15x30)</t>
+          <t>C9 (15x30)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -15792,7 +15875,7 @@
         <v>70</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>49.7</v>
+        <v>54.93</v>
       </c>
       <c r="H11" s="25">
         <f>IF(G11="","",G11/1.4)</f>
@@ -15833,7 +15916,7 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>C7 (15x30)</t>
+          <t>C8 (15x30)</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -15851,7 +15934,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>50.09</v>
+        <v>42.67</v>
       </c>
       <c r="H12" s="30">
         <f>IF(G12="","",G12/1.4)</f>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Planilla vigas'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla vigas'!$A$1:$X$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla vigas'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla losas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla losas'!$A$1:$R$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla columnas'!$1:$3</definedName>
@@ -1263,6 +1263,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2095500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4137,7 +4162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4460,7 +4485,7 @@
       <c r="A37" s="61" t="inlineStr"/>
       <c r="B37" s="62" t="inlineStr">
         <is>
-          <t>NOTA: el computo metrico lista una VI 06 de 15x70x14,00 que no existe en obra;</t>
+          <t>VI 06 mide 14,00 m en total y es el cuarto borde de L07. Sobre su eje hay cuatro</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4493,7 @@
       <c r="A38" s="61" t="inlineStr"/>
       <c r="B38" s="62" t="inlineStr">
         <is>
-          <t>por eso no figura en esta planilla. La cuarta cara de L07 apoya en otro elemento.</t>
+          <t>columnas, de modo que trabaja como viga continua de tres tramos de 4,10, 4,32 y</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4501,7 @@
       <c r="A39" s="61" t="inlineStr"/>
       <c r="B39" s="62" t="inlineStr">
         <is>
-          <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
+          <t>6,53 m. Se calcula con el mayor, 6,53 m, que es el que gobierna.</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4509,7 @@
       <c r="A40" s="61" t="inlineStr"/>
       <c r="B40" s="62" t="inlineStr">
         <is>
-          <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
+          <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4517,7 @@
       <c r="A41" s="61" t="inlineStr"/>
       <c r="B41" s="62" t="inlineStr">
         <is>
-          <t>Esto define donde la losa aporta ala comprimida:</t>
+          <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4525,7 @@
       <c r="A42" s="61" t="inlineStr"/>
       <c r="B42" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
+          <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4533,7 @@
       <c r="A43" s="61" t="inlineStr"/>
       <c r="B43" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
+          <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4541,7 @@
       <c r="A44" s="61" t="inlineStr"/>
       <c r="B44" s="62" t="inlineStr">
         <is>
-          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
+          <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4549,7 @@
       <c r="A45" s="61" t="inlineStr"/>
       <c r="B45" s="62" t="inlineStr">
         <is>
-          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
+          <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4557,7 @@
       <c r="A46" s="61" t="inlineStr"/>
       <c r="B46" s="62" t="inlineStr">
         <is>
-          <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
+          <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4565,7 @@
       <c r="A47" s="61" t="inlineStr"/>
       <c r="B47" s="62" t="inlineStr">
         <is>
-          <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
+          <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
         </is>
       </c>
     </row>
@@ -4548,31 +4573,31 @@
       <c r="A48" s="61" t="inlineStr"/>
       <c r="B48" s="62" t="inlineStr">
         <is>
-          <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
+          <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="61" t="inlineStr"/>
-      <c r="B49" s="62" t="inlineStr"/>
+      <c r="B49" s="62" t="inlineStr">
+        <is>
+          <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="61" t="inlineStr">
+      <c r="A50" s="61" t="inlineStr"/>
+      <c r="B50" s="62" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="61" t="inlineStr">
         <is>
           <t>7. RESULTADO</t>
         </is>
       </c>
-      <c r="B50" s="61" t="inlineStr">
+      <c r="B51" s="61" t="inlineStr">
         <is>
           <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="61" t="inlineStr"/>
-      <c r="B51" s="62" t="inlineStr">
-        <is>
-          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4605,7 @@
       <c r="A52" s="61" t="inlineStr"/>
       <c r="B52" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
+          <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4613,7 @@
       <c r="A53" s="61" t="inlineStr"/>
       <c r="B53" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
+          <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4621,7 @@
       <c r="A54" s="61" t="inlineStr"/>
       <c r="B54" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
+          <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4629,7 @@
       <c r="A55" s="61" t="inlineStr"/>
       <c r="B55" s="62" t="inlineStr">
         <is>
-          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
+          <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4637,7 @@
       <c r="A56" s="61" t="inlineStr"/>
       <c r="B56" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
+          <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4645,7 @@
       <c r="A57" s="61" t="inlineStr"/>
       <c r="B57" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
+          <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4653,7 @@
       <c r="A58" s="61" t="inlineStr"/>
       <c r="B58" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
+          <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4661,7 @@
       <c r="A59" s="61" t="inlineStr"/>
       <c r="B59" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
+          <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4669,7 @@
       <c r="A60" s="61" t="inlineStr"/>
       <c r="B60" s="62" t="inlineStr">
         <is>
-          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
+          <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
@@ -4652,55 +4677,55 @@
       <c r="A61" s="61" t="inlineStr"/>
       <c r="B61" s="62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
+          <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="61" t="inlineStr"/>
-      <c r="B62" s="62" t="inlineStr"/>
+      <c r="B62" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="61" t="inlineStr">
+      <c r="A63" s="61" t="inlineStr"/>
+      <c r="B63" s="62" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="61" t="inlineStr">
         <is>
           <t>8. ALCANCE</t>
         </is>
       </c>
-      <c r="B63" s="62" t="inlineStr">
+      <c r="B64" s="62" t="inlineStr">
         <is>
           <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="61" t="inlineStr"/>
-      <c r="B64" s="62" t="inlineStr">
-        <is>
-          <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="61" t="inlineStr"/>
-      <c r="B65" s="62" t="inlineStr"/>
+      <c r="B65" s="62" t="inlineStr">
+        <is>
+          <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="61" t="inlineStr">
+      <c r="A66" s="61" t="inlineStr"/>
+      <c r="B66" s="62" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="61" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B66" s="61" t="inlineStr">
+      <c r="B67" s="61" t="inlineStr">
         <is>
           <t>El ancho tributario B esta relevado solo en</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="61" t="inlineStr"/>
-      <c r="B67" s="62" t="inlineStr">
-        <is>
-          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4733,7 @@
       <c r="A68" s="61" t="inlineStr"/>
       <c r="B68" s="62" t="inlineStr">
         <is>
-          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
+          <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
@@ -4716,13 +4741,21 @@
       <c r="A69" s="61" t="inlineStr"/>
       <c r="B69" s="62" t="inlineStr">
         <is>
-          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
+          <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="61" t="inlineStr"/>
       <c r="B70" s="62" t="inlineStr">
+        <is>
+          <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="61" t="inlineStr"/>
+      <c r="B71" s="62" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -6134,7 +6167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF33"/>
+  <dimension ref="A1:AF34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7123,11 +7156,11 @@
       <c r="A10" s="26" t="n"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>VI 07a</t>
+          <t>VI 06</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.37</v>
+        <v>6.53</v>
       </c>
       <c r="D10" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD10+Datos_vigas!$B$7*J10*L10/10000+Datos_vigas!$B$16*AE10)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD10)</f>
@@ -7175,10 +7208,10 @@
         <v/>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S10" s="25">
         <f>F10/(J10*0.85*K10)</f>
@@ -7200,7 +7233,7 @@
       </c>
       <c r="X10" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+          <t>Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07.</t>
         </is>
       </c>
       <c r="Y10" s="10" t="inlineStr">
@@ -7225,7 +7258,7 @@
         <v/>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>0.78</v>
+        <v>1.549</v>
       </c>
       <c r="AE10" s="10" t="n">
         <v>2.6</v>
@@ -7238,11 +7271,11 @@
       <c r="A11" s="26" t="n"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>VI 07b</t>
+          <t>VI 07a</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>4.03</v>
+        <v>3.37</v>
       </c>
       <c r="D11" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD11+Datos_vigas!$B$7*J11*L11/10000+Datos_vigas!$B$16*AE11)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD11)</f>
@@ -7340,7 +7373,7 @@
         <v/>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AE11" s="10" t="n">
         <v>2.6</v>
@@ -7353,11 +7386,11 @@
       <c r="A12" s="26" t="n"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>VI 07c</t>
+          <t>VI 07b</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>8.6</v>
+        <v>4.03</v>
       </c>
       <c r="D12" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD12+Datos_vigas!$B$7*J12*L12/10000+Datos_vigas!$B$16*AE12)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD12)</f>
@@ -7395,20 +7428,20 @@
         <v/>
       </c>
       <c r="N12" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P12" s="25">
         <f>IF(NOT(ISNUMBER(I12)),"---",IF(I12&lt;=0,"---",IF(I12*100/(Datos_vigas!$B$8*AC12*K12^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I12*100/(Datos_vigas!$B$8*AC12*K12^2*Datos_vigas!$B$5)))*AC12*K12*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J12*K12))))</f>
         <v/>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S12" s="25">
         <f>F12/(J12*0.85*K12)</f>
@@ -7419,10 +7452,10 @@
         <v/>
       </c>
       <c r="U12" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W12" s="11">
         <f>IF(OR(M12="REVISAR",P12="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M12&lt;&gt;"REVISAR",P12&lt;&gt;"REVISAR",IF(ISNUMBER(M12),N12*PI()*(O12/10)^2/4&gt;=M12,TRUE),IF(ISNUMBER(P12),Q12*PI()*(R12/10)^2/4&gt;=P12,TRUE),IF(ISNUMBER(M12),M12&lt;=0.0163*AB12*K12,TRUE),IF(ISNUMBER(P12),P12&lt;=0.0163*AC12*K12,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F12&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J12*K12+2*PI()*(U12/10)^2/4*Datos_vigas!$B$6*K12/V12)),"NO VERIF. CORTE",IF(NOT(L12&gt;=C12*100/VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -7430,12 +7463,12 @@
       </c>
       <c r="X12" s="13" t="inlineStr">
         <is>
-          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y12" s="10" t="inlineStr">
         <is>
-          <t>Empotrada-apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z12" s="10" t="inlineStr">
@@ -7455,24 +7488,24 @@
         <v/>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="26" t="n"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>VI 08a</t>
+          <t>VI 07c</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="D13" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD13+Datos_vigas!$B$7*J13*L13/10000+Datos_vigas!$B$16*AE13)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD13)</f>
@@ -7510,20 +7543,20 @@
         <v/>
       </c>
       <c r="N13" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P13" s="25">
         <f>IF(NOT(ISNUMBER(I13)),"---",IF(I13&lt;=0,"---",IF(I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)))*AC13*K13*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J13*K13))))</f>
         <v/>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S13" s="25">
         <f>F13/(J13*0.85*K13)</f>
@@ -7534,19 +7567,23 @@
         <v/>
       </c>
       <c r="U13" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W13" s="11">
         <f>IF(OR(M13="REVISAR",P13="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M13&lt;&gt;"REVISAR",P13&lt;&gt;"REVISAR",IF(ISNUMBER(M13),N13*PI()*(O13/10)^2/4&gt;=M13,TRUE),IF(ISNUMBER(P13),Q13*PI()*(R13/10)^2/4&gt;=P13,TRUE),IF(ISNUMBER(M13),M13&lt;=0.0163*AB13*K13,TRUE),IF(ISNUMBER(P13),P13&lt;=0.0163*AC13*K13,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F13&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J13*K13+2*PI()*(U13/10)^2/4*Datos_vigas!$B$6*K13/V13)),"NO VERIF. CORTE",IF(NOT(L13&gt;=C13*100/VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X13" s="11" t="n"/>
+      <c r="X13" s="13" t="inlineStr">
+        <is>
+          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+        </is>
+      </c>
       <c r="Y13" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Empotrada-apoyada</t>
         </is>
       </c>
       <c r="Z13" s="10" t="inlineStr">
@@ -7566,24 +7603,24 @@
         <v/>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>1.065</v>
+        <v>3.71</v>
       </c>
       <c r="AE13" s="10" t="n">
         <v>2.6</v>
       </c>
       <c r="AF13" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="26" t="n"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>VI 08b</t>
+          <t>VI 08a</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4.87</v>
+        <v>3.65</v>
       </c>
       <c r="D14" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD14+Datos_vigas!$B$7*J14*L14/10000+Datos_vigas!$B$16*AE14)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD14)</f>
@@ -7690,7 +7727,7 @@
       <c r="A15" s="26" t="n"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>VI 09</t>
+          <t>VI 08b</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -7741,15 +7778,11 @@
         <f>IF(NOT(ISNUMBER(I15)),"---",IF(I15&lt;=0,"---",IF(I15*100/(Datos_vigas!$B$8*AC15*K15^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I15*100/(Datos_vigas!$B$8*AC15*K15^2*Datos_vigas!$B$5)))*AC15*K15*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J15*K15))))</f>
         <v/>
       </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="R15" s="10" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
+      <c r="Q15" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="S15" s="25">
         <f>F15/(J15*0.85*K15)</f>
@@ -7772,7 +7805,7 @@
       <c r="X15" s="11" t="n"/>
       <c r="Y15" s="10" t="inlineStr">
         <is>
-          <t>Simplemente apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z15" s="10" t="inlineStr">
@@ -7792,7 +7825,7 @@
         <v/>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>1.549</v>
+        <v>1.065</v>
       </c>
       <c r="AE15" s="10" t="n">
         <v>2.6</v>
@@ -7805,11 +7838,11 @@
       <c r="A16" s="26" t="n"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>VI 10a</t>
+          <t>VI 09</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2.55</v>
+        <v>4.87</v>
       </c>
       <c r="D16" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD16+Datos_vigas!$B$7*J16*L16/10000+Datos_vigas!$B$16*AE16)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD16)</f>
@@ -7856,11 +7889,15 @@
         <f>IF(NOT(ISNUMBER(I16)),"---",IF(I16&lt;=0,"---",IF(I16*100/(Datos_vigas!$B$8*AC16*K16^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I16*100/(Datos_vigas!$B$8*AC16*K16^2*Datos_vigas!$B$5)))*AC16*K16*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J16*K16))))</f>
         <v/>
       </c>
-      <c r="Q16" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" s="10" t="n">
-        <v>12</v>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
       </c>
       <c r="S16" s="25">
         <f>F16/(J16*0.85*K16)</f>
@@ -7883,7 +7920,7 @@
       <c r="X16" s="11" t="n"/>
       <c r="Y16" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Simplemente apoyada</t>
         </is>
       </c>
       <c r="Z16" s="10" t="inlineStr">
@@ -7903,7 +7940,7 @@
         <v/>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>0</v>
+        <v>1.549</v>
       </c>
       <c r="AE16" s="10" t="n">
         <v>2.6</v>
@@ -7916,11 +7953,11 @@
       <c r="A17" s="26" t="n"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>VI 10b</t>
+          <t>VI 10a</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="D17" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD17+Datos_vigas!$B$7*J17*L17/10000+Datos_vigas!$B$16*AE17)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD17)</f>
@@ -8014,7 +8051,7 @@
         <v/>
       </c>
       <c r="AD17" s="10" t="n">
-        <v>1.825</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="10" t="n">
         <v>2.6</v>
@@ -8027,11 +8064,11 @@
       <c r="A18" s="26" t="n"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>VI 10c</t>
+          <t>VI 10b</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D18" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD18+Datos_vigas!$B$7*J18*L18/10000+Datos_vigas!$B$16*AE18)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD18)</f>
@@ -8125,7 +8162,7 @@
         <v/>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>0</v>
+        <v>1.825</v>
       </c>
       <c r="AE18" s="10" t="n">
         <v>2.6</v>
@@ -8138,11 +8175,11 @@
       <c r="A19" s="26" t="n"/>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>VI 11a</t>
+          <t>VI 10c</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>7.68</v>
+        <v>3.6</v>
       </c>
       <c r="D19" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD19+Datos_vigas!$B$7*J19*L19/10000+Datos_vigas!$B$16*AE19)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD19)</f>
@@ -8180,20 +8217,20 @@
         <v/>
       </c>
       <c r="N19" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="10" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P19" s="25">
         <f>IF(NOT(ISNUMBER(I19)),"---",IF(I19&lt;=0,"---",IF(I19*100/(Datos_vigas!$B$8*AC19*K19^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I19*100/(Datos_vigas!$B$8*AC19*K19^2*Datos_vigas!$B$5)))*AC19*K19*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J19*K19))))</f>
         <v/>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S19" s="25">
         <f>F19/(J19*0.85*K19)</f>
@@ -8207,20 +8244,16 @@
         <v>6</v>
       </c>
       <c r="V19" s="10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="W19" s="11">
         <f>IF(OR(M19="REVISAR",P19="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M19&lt;&gt;"REVISAR",P19&lt;&gt;"REVISAR",IF(ISNUMBER(M19),N19*PI()*(O19/10)^2/4&gt;=M19,TRUE),IF(ISNUMBER(P19),Q19*PI()*(R19/10)^2/4&gt;=P19,TRUE),IF(ISNUMBER(M19),M19&lt;=0.0163*AB19*K19,TRUE),IF(ISNUMBER(P19),P19&lt;=0.0163*AC19*K19,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F19&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J19*K19+2*PI()*(U19/10)^2/4*Datos_vigas!$B$6*K19/V19)),"NO VERIF. CORTE",IF(NOT(L19&gt;=C19*100/VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X19" s="13" t="inlineStr">
-        <is>
-          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
-        </is>
-      </c>
+      <c r="X19" s="11" t="n"/>
       <c r="Y19" s="10" t="inlineStr">
         <is>
-          <t>Empotrada-apoyada</t>
+          <t>Continua</t>
         </is>
       </c>
       <c r="Z19" s="10" t="inlineStr">
@@ -8240,7 +8273,7 @@
         <v/>
       </c>
       <c r="AD19" s="10" t="n">
-        <v>1.825</v>
+        <v>0</v>
       </c>
       <c r="AE19" s="10" t="n">
         <v>2.6</v>
@@ -8253,11 +8286,11 @@
       <c r="A20" s="26" t="n"/>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>VI 11b</t>
+          <t>VI 11a</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3.45</v>
+        <v>7.68</v>
       </c>
       <c r="D20" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD20+Datos_vigas!$B$7*J20*L20/10000+Datos_vigas!$B$16*AE20)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD20)</f>
@@ -8295,20 +8328,20 @@
         <v/>
       </c>
       <c r="N20" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P20" s="25">
         <f>IF(NOT(ISNUMBER(I20)),"---",IF(I20&lt;=0,"---",IF(I20*100/(Datos_vigas!$B$8*AC20*K20^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I20*100/(Datos_vigas!$B$8*AC20*K20^2*Datos_vigas!$B$5)))*AC20*K20*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J20*K20))))</f>
         <v/>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="S20" s="25">
         <f>F20/(J20*0.85*K20)</f>
@@ -8322,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="V20" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W20" s="11">
         <f>IF(OR(M20="REVISAR",P20="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M20&lt;&gt;"REVISAR",P20&lt;&gt;"REVISAR",IF(ISNUMBER(M20),N20*PI()*(O20/10)^2/4&gt;=M20,TRUE),IF(ISNUMBER(P20),Q20*PI()*(R20/10)^2/4&gt;=P20,TRUE),IF(ISNUMBER(M20),M20&lt;=0.0163*AB20*K20,TRUE),IF(ISNUMBER(P20),P20&lt;=0.0163*AC20*K20,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F20&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J20*K20+2*PI()*(U20/10)^2/4*Datos_vigas!$B$6*K20/V20)),"NO VERIF. CORTE",IF(NOT(L20&gt;=C20*100/VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -8330,12 +8363,12 @@
       </c>
       <c r="X20" s="13" t="inlineStr">
         <is>
-          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+          <t>El plano rotula 'VI 111'; se interpreta 11a por el orden a-b-c. Sin apoyo intermedio, empotrada en tabiques. Apoya en columna COL 02 de 15x30 y en el tabique T08a. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y20" s="10" t="inlineStr">
         <is>
-          <t>Continua</t>
+          <t>Empotrada-apoyada</t>
         </is>
       </c>
       <c r="Z20" s="10" t="inlineStr">
@@ -8355,7 +8388,7 @@
         <v/>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>0</v>
+        <v>1.825</v>
       </c>
       <c r="AE20" s="10" t="n">
         <v>2.6</v>
@@ -8368,11 +8401,11 @@
       <c r="A21" s="26" t="n"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>VI 11c</t>
+          <t>VI 11b</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>5.02</v>
+        <v>3.45</v>
       </c>
       <c r="D21" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD21+Datos_vigas!$B$7*J21*L21/10000+Datos_vigas!$B$16*AE21)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD21)</f>
@@ -8470,7 +8503,7 @@
         <v/>
       </c>
       <c r="AD21" s="10" t="n">
-        <v>1.549</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="10" t="n">
         <v>2.6</v>
@@ -8483,11 +8516,11 @@
       <c r="A22" s="26" t="n"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>VCH 03a</t>
+          <t>VI 11c</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3.71</v>
+        <v>5.02</v>
       </c>
       <c r="D22" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD22+Datos_vigas!$B$7*J22*L22/10000+Datos_vigas!$B$16*AE22)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD22)</f>
@@ -8511,21 +8544,21 @@
         <v/>
       </c>
       <c r="J22" s="10" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="K22" s="11">
         <f>L22-AF22</f>
         <v/>
       </c>
       <c r="L22" s="10" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="M22" s="25">
         <f>IF(NOT(ISNUMBER(H22)),"---",IF(H22&lt;=0,"---",IF(H22*100/(Datos_vigas!$B$8*AB22*K22^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H22*100/(Datos_vigas!$B$8*AB22*K22^2*Datos_vigas!$B$5)))*AB22*K22*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J22*K22))))</f>
         <v/>
       </c>
       <c r="N22" s="10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O22" s="10" t="n">
         <v>12</v>
@@ -8535,10 +8568,10 @@
         <v/>
       </c>
       <c r="Q22" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R22" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S22" s="25">
         <f>F22/(J22*0.85*K22)</f>
@@ -8549,10 +8582,10 @@
         <v/>
       </c>
       <c r="U22" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="V22" s="10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="W22" s="11">
         <f>IF(OR(M22="REVISAR",P22="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M22&lt;&gt;"REVISAR",P22&lt;&gt;"REVISAR",IF(ISNUMBER(M22),N22*PI()*(O22/10)^2/4&gt;=M22,TRUE),IF(ISNUMBER(P22),Q22*PI()*(R22/10)^2/4&gt;=P22,TRUE),IF(ISNUMBER(M22),M22&lt;=0.0163*AB22*K22,TRUE),IF(ISNUMBER(P22),P22&lt;=0.0163*AC22*K22,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F22&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J22*K22+2*PI()*(U22/10)^2/4*Datos_vigas!$B$6*K22/V22)),"NO VERIF. CORTE",IF(NOT(L22&gt;=C22*100/VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -8560,7 +8593,7 @@
       </c>
       <c r="X22" s="13" t="inlineStr">
         <is>
-          <t>Excede cuantia maxima y no llega a la altura minima por flecha. Revisar el ancho tributario real. Separacion de estribos menor a 10 cm: revisar constructividad.</t>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y22" s="10" t="inlineStr">
@@ -8570,7 +8603,7 @@
       </c>
       <c r="Z22" s="10" t="inlineStr">
         <is>
-          <t>Colgante</t>
+          <t>Invertida</t>
         </is>
       </c>
       <c r="AA22" s="10" t="n">
@@ -8585,7 +8618,7 @@
         <v/>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>2.1</v>
+        <v>1.549</v>
       </c>
       <c r="AE22" s="10" t="n">
         <v>2.6</v>
@@ -8598,11 +8631,11 @@
       <c r="A23" s="26" t="n"/>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>VCH 03b</t>
+          <t>VCH 03a</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>2.13</v>
+        <v>3.71</v>
       </c>
       <c r="D23" s="24">
         <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD23+Datos_vigas!$B$7*J23*L23/10000+Datos_vigas!$B$16*AE23)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD23)</f>
@@ -8640,20 +8673,20 @@
         <v/>
       </c>
       <c r="N23" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P23" s="25">
         <f>IF(NOT(ISNUMBER(I23)),"---",IF(I23&lt;=0,"---",IF(I23*100/(Datos_vigas!$B$8*AC23*K23^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I23*100/(Datos_vigas!$B$8*AC23*K23^2*Datos_vigas!$B$5)))*AC23*K23*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J23*K23))))</f>
         <v/>
       </c>
       <c r="Q23" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R23" s="10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S23" s="25">
         <f>F23/(J23*0.85*K23)</f>
@@ -8675,7 +8708,7 @@
       </c>
       <c r="X23" s="13" t="inlineStr">
         <is>
-          <t>Separacion de estribos menor a 10 cm: revisar constructividad.</t>
+          <t>Excede cuantia maxima y no llega a la altura minima por flecha. Revisar el ancho tributario real. Separacion de estribos menor a 10 cm: revisar constructividad.</t>
         </is>
       </c>
       <c r="Y23" s="10" t="inlineStr">
@@ -8710,247 +8743,251 @@
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="27" t="n"/>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>VCH 03b</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D24" s="24">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD24+Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*AE24)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="24">
+        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,4,0)*D24*C24</f>
+        <v/>
+      </c>
+      <c r="G24" s="24">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="24">
+        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,2,0)*D24*C24^2</f>
+        <v/>
+      </c>
+      <c r="I24" s="24">
+        <f>IF(VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)*D24*C24^2)</f>
+        <v/>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K24" s="11">
+        <f>L24-AF24</f>
+        <v/>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="M24" s="25">
+        <f>IF(NOT(ISNUMBER(H24)),"---",IF(H24&lt;=0,"---",IF(H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)))*AB24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" s="25">
+        <f>IF(NOT(ISNUMBER(I24)),"---",IF(I24&lt;=0,"---",IF(I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)))*AC24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="S24" s="25">
+        <f>F24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="T24" s="25">
+        <f>G24/(J24*0.85*K24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="V24" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W24" s="11">
+        <f>IF(OR(M24="REVISAR",P24="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M24&lt;&gt;"REVISAR",P24&lt;&gt;"REVISAR",IF(ISNUMBER(M24),N24*PI()*(O24/10)^2/4&gt;=M24,TRUE),IF(ISNUMBER(P24),Q24*PI()*(R24/10)^2/4&gt;=P24,TRUE),IF(ISNUMBER(M24),M24&lt;=0.0163*AB24*K24,TRUE),IF(ISNUMBER(P24),P24&lt;=0.0163*AC24*K24,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F24&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J24*K24+2*PI()*(U24/10)^2/4*Datos_vigas!$B$6*K24/V24)),"NO VERIF. CORTE",IF(NOT(L24&gt;=C24*100/VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X24" s="13" t="inlineStr">
+        <is>
+          <t>Separacion de estribos menor a 10 cm: revisar constructividad.</t>
+        </is>
+      </c>
+      <c r="Y24" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="Z24" s="10" t="inlineStr">
+        <is>
+          <t>Colgante</t>
+        </is>
+      </c>
+      <c r="AA24" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB24" s="11">
+        <f>IF(Z24="Colgante",MIN(C24*100/4,J24+16*AA24),J24)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="11">
+        <f>IF(Z24="Invertida",MIN(C24*100/4,J24+16*AA24),J24)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE24" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF24" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>VCH 05</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C25" s="15" t="n">
         <v>3.71</v>
       </c>
-      <c r="D24" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD24+Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*AE24)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD24)</f>
-        <v/>
-      </c>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="29">
-        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,4,0)*D24*C24</f>
-        <v/>
-      </c>
-      <c r="G24" s="29">
-        <f>F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="29">
-        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,2,0)*D24*C24^2</f>
-        <v/>
-      </c>
-      <c r="I24" s="29">
-        <f>IF(VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)*D24*C24^2)</f>
-        <v/>
-      </c>
-      <c r="J24" s="17" t="n">
+      <c r="D25" s="29">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AE25)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="29">
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="29">
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2</f>
+        <v/>
+      </c>
+      <c r="I25" s="29">
+        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2)</f>
+        <v/>
+      </c>
+      <c r="J25" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="K24" s="18">
-        <f>L24-AF24</f>
-        <v/>
-      </c>
-      <c r="L24" s="17" t="n">
+      <c r="K25" s="18">
+        <f>L25-AF25</f>
+        <v/>
+      </c>
+      <c r="L25" s="17" t="n">
         <v>45</v>
       </c>
-      <c r="M24" s="30">
-        <f>IF(NOT(ISNUMBER(H24)),"---",IF(H24&lt;=0,"---",IF(H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H24*100/(Datos_vigas!$B$8*AB24*K24^2*Datos_vigas!$B$5)))*AB24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
-        <v/>
-      </c>
-      <c r="N24" s="17" t="n">
+      <c r="M25" s="30">
+        <f>IF(NOT(ISNUMBER(H25)),"---",IF(H25&lt;=0,"---",IF(H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)))*AB25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="17" t="n">
+      <c r="O25" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="P24" s="30">
-        <f>IF(NOT(ISNUMBER(I24)),"---",IF(I24&lt;=0,"---",IF(I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I24*100/(Datos_vigas!$B$8*AC24*K24^2*Datos_vigas!$B$5)))*AC24*K24*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J24*K24))))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="17" t="inlineStr">
+      <c r="P25" s="30">
+        <f>IF(NOT(ISNUMBER(I25)),"---",IF(I25&lt;=0,"---",IF(I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)))*AC25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="R24" s="17" t="inlineStr">
+      <c r="R25" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="S24" s="30">
-        <f>F24/(J24*0.85*K24)</f>
-        <v/>
-      </c>
-      <c r="T24" s="30">
-        <f>G24/(J24*0.85*K24)</f>
-        <v/>
-      </c>
-      <c r="U24" s="17" t="n">
+      <c r="S25" s="30">
+        <f>F25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="T25" s="30">
+        <f>G25/(J25*0.85*K25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="V24" s="17" t="n">
+      <c r="V25" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="W24" s="18">
-        <f>IF(OR(M24="REVISAR",P24="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M24&lt;&gt;"REVISAR",P24&lt;&gt;"REVISAR",IF(ISNUMBER(M24),N24*PI()*(O24/10)^2/4&gt;=M24,TRUE),IF(ISNUMBER(P24),Q24*PI()*(R24/10)^2/4&gt;=P24,TRUE),IF(ISNUMBER(M24),M24&lt;=0.0163*AB24*K24,TRUE),IF(ISNUMBER(P24),P24&lt;=0.0163*AC24*K24,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F24&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J24*K24+2*PI()*(U24/10)^2/4*Datos_vigas!$B$6*K24/V24)),"NO VERIF. CORTE",IF(NOT(L24&gt;=C24*100/VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X24" s="18" t="n"/>
-      <c r="Y24" s="17" t="inlineStr">
+      <c r="W25" s="18">
+        <f>IF(OR(M25="REVISAR",P25="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M25&lt;&gt;"REVISAR",P25&lt;&gt;"REVISAR",IF(ISNUMBER(M25),N25*PI()*(O25/10)^2/4&gt;=M25,TRUE),IF(ISNUMBER(P25),Q25*PI()*(R25/10)^2/4&gt;=P25,TRUE),IF(ISNUMBER(M25),M25&lt;=0.0163*AB25*K25,TRUE),IF(ISNUMBER(P25),P25&lt;=0.0163*AC25*K25,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F25&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J25*K25+2*PI()*(U25/10)^2/4*Datos_vigas!$B$6*K25/V25)),"NO VERIF. CORTE",IF(NOT(L25&gt;=C25*100/VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X25" s="18" t="n"/>
+      <c r="Y25" s="17" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="Z24" s="17" t="inlineStr">
+      <c r="Z25" s="17" t="inlineStr">
         <is>
           <t>Colgante</t>
         </is>
       </c>
-      <c r="AA24" s="17" t="n">
+      <c r="AA25" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="AB24" s="18">
-        <f>IF(Z24="Colgante",MIN(C24*100/4,J24+16*AA24),J24)</f>
-        <v/>
-      </c>
-      <c r="AC24" s="18">
-        <f>IF(Z24="Invertida",MIN(C24*100/4,J24+16*AA24),J24)</f>
-        <v/>
-      </c>
-      <c r="AD24" s="17" t="n">
+      <c r="AB25" s="18">
+        <f>IF(Z25="Colgante",MIN(C25*100/4,J25+16*AA25),J25)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="18">
+        <f>IF(Z25="Invertida",MIN(C25*100/4,J25+16*AA25),J25)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" s="17" t="n">
+      <c r="AE25" s="17" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF24" s="17" t="n">
+      <c r="AF25" s="17" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>TECHO</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>VI 12</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C26" s="8" t="n">
         <v>9.9</v>
       </c>
-      <c r="D25" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AE25)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD25)</f>
-        <v/>
-      </c>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="24">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
-        <f>F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="24">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2</f>
-        <v/>
-      </c>
-      <c r="I25" s="24">
-        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2)</f>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="K25" s="11">
-        <f>L25-AF25</f>
-        <v/>
-      </c>
-      <c r="L25" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="M25" s="25">
-        <f>IF(NOT(ISNUMBER(H25)),"---",IF(H25&lt;=0,"---",IF(H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H25*100/(Datos_vigas!$B$8*AB25*K25^2*Datos_vigas!$B$5)))*AB25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
-        <v/>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="P25" s="25">
-        <f>IF(NOT(ISNUMBER(I25)),"---",IF(I25&lt;=0,"---",IF(I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I25*100/(Datos_vigas!$B$8*AC25*K25^2*Datos_vigas!$B$5)))*AC25*K25*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J25*K25))))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="S25" s="25">
-        <f>F25/(J25*0.85*K25)</f>
-        <v/>
-      </c>
-      <c r="T25" s="25">
-        <f>G25/(J25*0.85*K25)</f>
-        <v/>
-      </c>
-      <c r="U25" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="V25" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="W25" s="11">
-        <f>IF(OR(M25="REVISAR",P25="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M25&lt;&gt;"REVISAR",P25&lt;&gt;"REVISAR",IF(ISNUMBER(M25),N25*PI()*(O25/10)^2/4&gt;=M25,TRUE),IF(ISNUMBER(P25),Q25*PI()*(R25/10)^2/4&gt;=P25,TRUE),IF(ISNUMBER(M25),M25&lt;=0.0163*AB25*K25,TRUE),IF(ISNUMBER(P25),P25&lt;=0.0163*AC25*K25,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F25&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J25*K25+2*PI()*(U25/10)^2/4*Datos_vigas!$B$6*K25/V25)),"NO VERIF. CORTE",IF(NOT(L25&gt;=C25*100/VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X25" s="11" t="n"/>
-      <c r="Y25" s="10" t="inlineStr">
-        <is>
-          <t>Continua</t>
-        </is>
-      </c>
-      <c r="Z25" s="10" t="inlineStr">
-        <is>
-          <t>Invertida</t>
-        </is>
-      </c>
-      <c r="AA25" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB25" s="11">
-        <f>IF(Z25="Colgante",MIN(C25*100/4,J25+16*AA25),J25)</f>
-        <v/>
-      </c>
-      <c r="AC25" s="11">
-        <f>IF(Z25="Invertida",MIN(C25*100/4,J25+16*AA25),J25)</f>
-        <v/>
-      </c>
-      <c r="AD25" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="26" t="n"/>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>VI 13a</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="D26" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AE26)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD26)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AE26)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD26)</f>
         <v/>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -8988,7 +9025,7 @@
         <v>2</v>
       </c>
       <c r="O26" s="10" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="P26" s="25">
         <f>IF(NOT(ISNUMBER(I26)),"---",IF(I26&lt;=0,"---",IF(I26*100/(Datos_vigas!$B$8*AC26*K26^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I26*100/(Datos_vigas!$B$8*AC26*K26^2*Datos_vigas!$B$5)))*AC26*K26*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J26*K26))))</f>
@@ -8998,7 +9035,7 @@
         <v>2</v>
       </c>
       <c r="R26" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S26" s="25">
         <f>F26/(J26*0.85*K26)</f>
@@ -9041,7 +9078,7 @@
         <v/>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>3.799</v>
+        <v>2.1</v>
       </c>
       <c r="AE26" s="10" t="n">
         <v>1</v>
@@ -9054,14 +9091,14 @@
       <c r="A27" s="26" t="n"/>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>VI 13b</t>
+          <t>VI 13a</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="D27" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AE27)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD27)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AE27)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD27)</f>
         <v/>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -9096,20 +9133,20 @@
         <v/>
       </c>
       <c r="N27" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P27" s="25">
         <f>IF(NOT(ISNUMBER(I27)),"---",IF(I27&lt;=0,"---",IF(I27*100/(Datos_vigas!$B$8*AC27*K27^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I27*100/(Datos_vigas!$B$8*AC27*K27^2*Datos_vigas!$B$5)))*AC27*K27*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J27*K27))))</f>
         <v/>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S27" s="25">
         <f>F27/(J27*0.85*K27)</f>
@@ -9123,7 +9160,7 @@
         <v>6</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="W27" s="11">
         <f>IF(OR(M27="REVISAR",P27="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M27&lt;&gt;"REVISAR",P27&lt;&gt;"REVISAR",IF(ISNUMBER(M27),N27*PI()*(O27/10)^2/4&gt;=M27,TRUE),IF(ISNUMBER(P27),Q27*PI()*(R27/10)^2/4&gt;=P27,TRUE),IF(ISNUMBER(M27),M27&lt;=0.0163*AB27*K27,TRUE),IF(ISNUMBER(P27),P27&lt;=0.0163*AC27*K27,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F27&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J27*K27+2*PI()*(U27/10)^2/4*Datos_vigas!$B$6*K27/V27)),"NO VERIF. CORTE",IF(NOT(L27&gt;=C27*100/VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -9152,7 +9189,7 @@
         <v/>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>2.1</v>
+        <v>3.799</v>
       </c>
       <c r="AE27" s="10" t="n">
         <v>1</v>
@@ -9165,14 +9202,14 @@
       <c r="A28" s="26" t="n"/>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>VI 14</t>
+          <t>VI 13b</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="D28" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AE28)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD28)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AE28)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD28)</f>
         <v/>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -9263,7 +9300,7 @@
         <v/>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>1.699</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" s="10" t="n">
         <v>1</v>
@@ -9276,14 +9313,14 @@
       <c r="A29" s="26" t="n"/>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>VI 15a</t>
+          <t>VI 14</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>4.03</v>
+        <v>6</v>
       </c>
       <c r="D29" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AE29)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD29)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AE29)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD29)</f>
         <v/>
       </c>
       <c r="E29" s="11" t="n"/>
@@ -9351,11 +9388,7 @@
         <f>IF(OR(M29="REVISAR",P29="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M29&lt;&gt;"REVISAR",P29&lt;&gt;"REVISAR",IF(ISNUMBER(M29),N29*PI()*(O29/10)^2/4&gt;=M29,TRUE),IF(ISNUMBER(P29),Q29*PI()*(R29/10)^2/4&gt;=P29,TRUE),IF(ISNUMBER(M29),M29&lt;=0.0163*AB29*K29,TRUE),IF(ISNUMBER(P29),P29&lt;=0.0163*AC29*K29,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F29&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J29*K29+2*PI()*(U29/10)^2/4*Datos_vigas!$B$6*K29/V29)),"NO VERIF. CORTE",IF(NOT(L29&gt;=C29*100/VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X29" s="13" t="inlineStr">
-        <is>
-          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
-        </is>
-      </c>
+      <c r="X29" s="11" t="n"/>
       <c r="Y29" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -9378,7 +9411,7 @@
         <v/>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>0</v>
+        <v>1.699</v>
       </c>
       <c r="AE29" s="10" t="n">
         <v>1</v>
@@ -9391,14 +9424,14 @@
       <c r="A30" s="26" t="n"/>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>VI 15b</t>
+          <t>VI 15a</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>4.85</v>
+        <v>4.03</v>
       </c>
       <c r="D30" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AE30)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD30)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AE30)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD30)</f>
         <v/>
       </c>
       <c r="E30" s="11" t="n"/>
@@ -9493,7 +9526,7 @@
         <v/>
       </c>
       <c r="AD30" s="10" t="n">
-        <v>1.699</v>
+        <v>0</v>
       </c>
       <c r="AE30" s="10" t="n">
         <v>1</v>
@@ -9506,14 +9539,14 @@
       <c r="A31" s="26" t="n"/>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>VI 16a</t>
+          <t>VI 15b</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>3.58</v>
+        <v>4.85</v>
       </c>
       <c r="D31" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AE31)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD31)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AE31)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD31)</f>
         <v/>
       </c>
       <c r="E31" s="11" t="n"/>
@@ -9581,7 +9614,11 @@
         <f>IF(OR(M31="REVISAR",P31="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M31&lt;&gt;"REVISAR",P31&lt;&gt;"REVISAR",IF(ISNUMBER(M31),N31*PI()*(O31/10)^2/4&gt;=M31,TRUE),IF(ISNUMBER(P31),Q31*PI()*(R31/10)^2/4&gt;=P31,TRUE),IF(ISNUMBER(M31),M31&lt;=0.0163*AB31*K31,TRUE),IF(ISNUMBER(P31),P31&lt;=0.0163*AC31*K31,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F31&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J31*K31+2*PI()*(U31/10)^2/4*Datos_vigas!$B$6*K31/V31)),"NO VERIF. CORTE",IF(NOT(L31&gt;=C31*100/VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X31" s="11" t="n"/>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t>Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+        </is>
+      </c>
       <c r="Y31" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -9617,14 +9654,14 @@
       <c r="A32" s="26" t="n"/>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>VI 16b</t>
+          <t>VI 16a</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>1.12</v>
+        <v>3.58</v>
       </c>
       <c r="D32" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AE32)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD32)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AE32)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD32)</f>
         <v/>
       </c>
       <c r="E32" s="11" t="n"/>
@@ -9725,130 +9762,241 @@
       </c>
     </row>
     <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="A33" s="26" t="n"/>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>VI 16b</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D33" s="24">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AE33)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD33)</f>
+        <v/>
+      </c>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="24">
+        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,4,0)*D33*C33</f>
+        <v/>
+      </c>
+      <c r="G33" s="24">
+        <f>F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="24">
+        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,2,0)*D33*C33^2</f>
+        <v/>
+      </c>
+      <c r="I33" s="24">
+        <f>IF(VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)*D33*C33^2)</f>
+        <v/>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K33" s="11">
+        <f>L33-AF33</f>
+        <v/>
+      </c>
+      <c r="L33" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="M33" s="25">
+        <f>IF(NOT(ISNUMBER(H33)),"---",IF(H33&lt;=0,"---",IF(H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)))*AB33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P33" s="25">
+        <f>IF(NOT(ISNUMBER(I33)),"---",IF(I33&lt;=0,"---",IF(I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)))*AC33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="S33" s="25">
+        <f>F33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="T33" s="25">
+        <f>G33/(J33*0.85*K33)</f>
+        <v/>
+      </c>
+      <c r="U33" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="W33" s="11">
+        <f>IF(OR(M33="REVISAR",P33="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M33&lt;&gt;"REVISAR",P33&lt;&gt;"REVISAR",IF(ISNUMBER(M33),N33*PI()*(O33/10)^2/4&gt;=M33,TRUE),IF(ISNUMBER(P33),Q33*PI()*(R33/10)^2/4&gt;=P33,TRUE),IF(ISNUMBER(M33),M33&lt;=0.0163*AB33*K33,TRUE),IF(ISNUMBER(P33),P33&lt;=0.0163*AC33*K33,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F33&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J33*K33+2*PI()*(U33/10)^2/4*Datos_vigas!$B$6*K33/V33)),"NO VERIF. CORTE",IF(NOT(L33&gt;=C33*100/VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="10" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="Z33" s="10" t="inlineStr">
+        <is>
+          <t>Invertida</t>
+        </is>
+      </c>
+      <c r="AA33" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB33" s="11">
+        <f>IF(Z33="Colgante",MIN(C33*100/4,J33+16*AA33),J33)</f>
+        <v/>
+      </c>
+      <c r="AC33" s="11">
+        <f>IF(Z33="Invertida",MIN(C33*100/4,J33+16*AA33),J33)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="10" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="AE33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="27" t="n"/>
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>VI 17</t>
         </is>
       </c>
-      <c r="C33" s="15" t="n">
+      <c r="C34" s="15" t="n">
         <v>4.35</v>
       </c>
-      <c r="D33" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,2,0)*AD33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AE33)+Datos_vigas!$B$11*VLOOKUP($A$25,Datos_vigas!$A$14:$E$15,3,0)*AD33)</f>
-        <v/>
-      </c>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="29">
-        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,4,0)*D33*C33</f>
-        <v/>
-      </c>
-      <c r="G33" s="29">
-        <f>F33</f>
-        <v/>
-      </c>
-      <c r="H33" s="29">
-        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,2,0)*D33*C33^2</f>
-        <v/>
-      </c>
-      <c r="I33" s="29">
-        <f>IF(VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)*D33*C33^2)</f>
-        <v/>
-      </c>
-      <c r="J33" s="17" t="n">
+      <c r="D34" s="29">
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD34+Datos_vigas!$B$7*J34*L34/10000+Datos_vigas!$B$16*AE34)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD34)</f>
+        <v/>
+      </c>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="29">
+        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,4,0)*D34*C34</f>
+        <v/>
+      </c>
+      <c r="G34" s="29">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="29">
+        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,2,0)*D34*C34^2</f>
+        <v/>
+      </c>
+      <c r="I34" s="29">
+        <f>IF(VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)*D34*C34^2)</f>
+        <v/>
+      </c>
+      <c r="J34" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="K33" s="18">
-        <f>L33-AF33</f>
-        <v/>
-      </c>
-      <c r="L33" s="17" t="n">
+      <c r="K34" s="18">
+        <f>L34-AF34</f>
+        <v/>
+      </c>
+      <c r="L34" s="17" t="n">
         <v>70</v>
       </c>
-      <c r="M33" s="30">
-        <f>IF(NOT(ISNUMBER(H33)),"---",IF(H33&lt;=0,"---",IF(H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H33*100/(Datos_vigas!$B$8*AB33*K33^2*Datos_vigas!$B$5)))*AB33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
-        <v/>
-      </c>
-      <c r="N33" s="17" t="n">
+      <c r="M34" s="30">
+        <f>IF(NOT(ISNUMBER(H34)),"---",IF(H34&lt;=0,"---",IF(H34*100/(Datos_vigas!$B$8*AB34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*H34*100/(Datos_vigas!$B$8*AB34*K34^2*Datos_vigas!$B$5)))*AB34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="O33" s="17" t="n">
+      <c r="O34" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="P33" s="30">
-        <f>IF(NOT(ISNUMBER(I33)),"---",IF(I33&lt;=0,"---",IF(I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I33*100/(Datos_vigas!$B$8*AC33*K33^2*Datos_vigas!$B$5)))*AC33*K33*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J33*K33))))</f>
-        <v/>
-      </c>
-      <c r="Q33" s="17" t="inlineStr">
+      <c r="P34" s="30">
+        <f>IF(NOT(ISNUMBER(I34)),"---",IF(I34&lt;=0,"---",IF(I34*100/(Datos_vigas!$B$8*AC34*K34^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I34*100/(Datos_vigas!$B$8*AC34*K34^2*Datos_vigas!$B$5)))*AC34*K34*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J34*K34))))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="R33" s="17" t="inlineStr">
+      <c r="R34" s="17" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="S33" s="30">
-        <f>F33/(J33*0.85*K33)</f>
-        <v/>
-      </c>
-      <c r="T33" s="30">
-        <f>G33/(J33*0.85*K33)</f>
-        <v/>
-      </c>
-      <c r="U33" s="17" t="n">
+      <c r="S34" s="30">
+        <f>F34/(J34*0.85*K34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="30">
+        <f>G34/(J34*0.85*K34)</f>
+        <v/>
+      </c>
+      <c r="U34" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="V33" s="17" t="n">
+      <c r="V34" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="W33" s="18">
-        <f>IF(OR(M33="REVISAR",P33="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M33&lt;&gt;"REVISAR",P33&lt;&gt;"REVISAR",IF(ISNUMBER(M33),N33*PI()*(O33/10)^2/4&gt;=M33,TRUE),IF(ISNUMBER(P33),Q33*PI()*(R33/10)^2/4&gt;=P33,TRUE),IF(ISNUMBER(M33),M33&lt;=0.0163*AB33*K33,TRUE),IF(ISNUMBER(P33),P33&lt;=0.0163*AC33*K33,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F33&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J33*K33+2*PI()*(U33/10)^2/4*Datos_vigas!$B$6*K33/V33)),"NO VERIF. CORTE",IF(NOT(L33&gt;=C33*100/VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
-        <v/>
-      </c>
-      <c r="X33" s="18" t="n"/>
-      <c r="Y33" s="17" t="inlineStr">
+      <c r="W34" s="18">
+        <f>IF(OR(M34="REVISAR",P34="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M34&lt;&gt;"REVISAR",P34&lt;&gt;"REVISAR",IF(ISNUMBER(M34),N34*PI()*(O34/10)^2/4&gt;=M34,TRUE),IF(ISNUMBER(P34),Q34*PI()*(R34/10)^2/4&gt;=P34,TRUE),IF(ISNUMBER(M34),M34&lt;=0.0163*AB34*K34,TRUE),IF(ISNUMBER(P34),P34&lt;=0.0163*AC34*K34,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F34&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J34*K34+2*PI()*(U34/10)^2/4*Datos_vigas!$B$6*K34/V34)),"NO VERIF. CORTE",IF(NOT(L34&gt;=C34*100/VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
+        <v/>
+      </c>
+      <c r="X34" s="18" t="n"/>
+      <c r="Y34" s="17" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="Z33" s="17" t="inlineStr">
+      <c r="Z34" s="17" t="inlineStr">
         <is>
           <t>Invertida</t>
         </is>
       </c>
-      <c r="AA33" s="17" t="n">
+      <c r="AA34" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="AB33" s="18">
-        <f>IF(Z33="Colgante",MIN(C33*100/4,J33+16*AA33),J33)</f>
-        <v/>
-      </c>
-      <c r="AC33" s="18">
-        <f>IF(Z33="Invertida",MIN(C33*100/4,J33+16*AA33),J33)</f>
-        <v/>
-      </c>
-      <c r="AD33" s="17" t="n">
+      <c r="AB34" s="18">
+        <f>IF(Z34="Colgante",MIN(C34*100/4,J34+16*AA34),J34)</f>
+        <v/>
+      </c>
+      <c r="AC34" s="18">
+        <f>IF(Z34="Invertida",MIN(C34*100/4,J34+16*AA34),J34)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AE33" s="17" t="n">
+      <c r="AE34" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="AF33" s="17" t="n">
+      <c r="AF34" s="17" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A4:A24"/>
     <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A25"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A25:A33"/>
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="S2:U2"/>
+    <mergeCell ref="A26:A34"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="V2"/>
     <mergeCell ref="B2:B3"/>
@@ -9860,7 +10008,7 @@
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="W2:W3"/>
   </mergeCells>
-  <conditionalFormatting sqref="W4:W33">
+  <conditionalFormatting sqref="W4:W34">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"VERIFICA"</formula>
     </cfRule>
@@ -9875,13 +10023,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="Y4:Y33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Y4:Y34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_vigas!$A$19:$A$23</formula1>
     </dataValidation>
-    <dataValidation sqref="Z4:Z33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Z4:Z34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Invertida,Colgante"</formula1>
     </dataValidation>
-    <dataValidation sqref="O4:O33 R4:R33 U4:U33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O4:O34 R4:R34 U4:U34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"6,8,10,12,16,20,25"</formula1>
     </dataValidation>
   </dataValidations>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -16187,27 +16187,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>TABIQUES DE H°A°        H-21        ACERO 42/50        espesor 12 cm</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TABIQUES  H°A°        H-21        ACERO III        espesor 12 cm</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -16221,6 +16226,11 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -16235,34 +16245,43 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>DIMENSIONES</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
           <t>CARGA (t)</t>
         </is>
       </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>ALTURA (m)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (cm)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>N por metro (t/m)</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>CAPACIDAD</t>
-        </is>
-      </c>
+          <t>ARMADURA VERTICAL</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>ARMADURA HORIZONTAL</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>VERIFICACION</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
@@ -16271,967 +16290,995 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>espesor (cm)</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>largo (m)</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>alto (m)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>esbeltez</t>
+          <t>o</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>reduccion</t>
+          <t>separacion</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>fi Pn (t/m)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>PB   (altura de entrepiso)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>separacion</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>area (cm2)</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>sigma (kg/cm2)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>fi Pn (t)</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>resultado</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>365</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="G4" s="25">
+        <f>2*(100/I4)*PI()*(H4/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" s="25">
+        <f>(100/L4)*PI()*(K4/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M4" s="38">
+        <f>IF(F4&lt;=12,E4*F4,(E4+F4-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N4" s="9">
+        <f>IF(C4="","",C4*1000/M4)</f>
+        <v/>
+      </c>
+      <c r="O4" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M4*MAX(0,1-(D4*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P4" s="11">
+        <f>IF(C4="","FALTA CARGA",IF(C4&lt;=O4,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="11" t="n"/>
+      <c r="A5" s="26" t="n"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>T01a</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n">
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G5" s="25">
+        <f>2*(100/I5)*PI()*(H5/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" s="25">
+        <f>(100/L5)*PI()*(K5/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M5" s="38">
+        <f>IF(F5&lt;=12,E5*F5,(E5+F5-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N5" s="9">
+        <f>IF(C5="","",C5*1000/M5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M5*MAX(0,1-(D5*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P5" s="11">
+        <f>IF(C5="","FALTA CARGA",IF(C5&lt;=O5,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="11" t="inlineStr"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="26" t="n"/>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="G6" s="25">
+        <f>2*(100/I6)*PI()*(H6/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" s="25">
+        <f>(100/L6)*PI()*(K6/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" s="38">
+        <f>IF(F6&lt;=12,E6*F6,(E6+F6-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(C6="","",C6*1000/M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M6*MAX(0,1-(D6*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P6" s="11">
+        <f>IF(C6="","FALTA CARGA",IF(C6&lt;=O6,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="13" t="inlineStr">
+        <is>
+          <t>Tabique recto: B = 12 cm es el espesor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="26" t="n"/>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>3.15</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="G5" s="25">
-        <f>IF(F5="","",F5/D5)</f>
-        <v/>
-      </c>
-      <c r="H5" s="38">
-        <f>E5*100/C5</f>
-        <v/>
-      </c>
-      <c r="I5" s="33">
-        <f>MAX(0,1-(E5*100/(32*C5))^2)</f>
-        <v/>
-      </c>
-      <c r="J5" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C5)*I5/1000</f>
-        <v/>
-      </c>
-      <c r="K5" s="11">
-        <f>IF(G5="","FALTA CARGA",IF(G5&lt;=J5,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>Recibe el extremo de VI 01a.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>T01b</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
+      <c r="E7" s="10" t="n">
+        <v>355</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E6" s="8" t="n">
+      <c r="G7" s="25">
+        <f>2*(100/I7)*PI()*(H7/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" s="25">
+        <f>(100/L7)*PI()*(K7/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M7" s="38">
+        <f>IF(F7&lt;=12,E7*F7,(E7+F7-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N7" s="9">
+        <f>IF(C7="","",C7*1000/M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M7*MAX(0,1-(D7*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P7" s="11">
+        <f>IF(C7="","FALTA CARGA",IF(C7&lt;=O7,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t>Tabique recto: B = 12 cm es el espesor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="26" t="n"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>3.15</v>
       </c>
-      <c r="F6" s="42" t="n"/>
-      <c r="G6" s="25">
-        <f>IF(F6="","",F6/D6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="38">
-        <f>E6*100/C6</f>
-        <v/>
-      </c>
-      <c r="I6" s="33">
-        <f>MAX(0,1-(E6*100/(32*C6))^2)</f>
-        <v/>
-      </c>
-      <c r="J6" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C6)*I6/1000</f>
-        <v/>
-      </c>
-      <c r="K6" s="11">
-        <f>IF(G6="","FALTA CARGA",IF(G6&lt;=J6,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
+      <c r="E8" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="25">
+        <f>2*(100/I8)*PI()*(H8/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" s="25">
+        <f>(100/L8)*PI()*(K8/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M8" s="38">
+        <f>IF(F8&lt;=12,E8*F8,(E8+F8-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(C8="","",C8*1000/M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M8*MAX(0,1-(D8*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P8" s="11">
+        <f>IF(C8="","FALTA CARGA",IF(C8&lt;=O8,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t>El mas cargado del conjunto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="26" t="n"/>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G9" s="25">
+        <f>2*(100/I9)*PI()*(H9/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" s="25">
+        <f>(100/L9)*PI()*(K9/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M9" s="38">
+        <f>IF(F9&lt;=12,E9*F9,(E9+F9-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N9" s="9">
+        <f>IF(C9="","",C9*1000/M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M9*MAX(0,1-(D9*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P9" s="11">
+        <f>IF(C9="","FALTA CARGA",IF(C9&lt;=O9,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="G10" s="25">
+        <f>2*(100/I10)*PI()*(H10/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" s="25">
+        <f>(100/L10)*PI()*(K10/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" s="38">
+        <f>IF(F10&lt;=12,E10*F10,(E10+F10-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(C10="","",C10*1000/M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M10*MAX(0,1-(D10*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P10" s="11">
+        <f>IF(C10="","FALTA CARGA",IF(C10&lt;=O10,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="13" t="inlineStr">
+        <is>
+          <t>Recibe el extremo de VI 02. Carga estimada por la bajada de vigas: 21,1 t. Falta la carga: no figura en la planilla de la catedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="n"/>
+      <c r="D11" s="15" t="n">
         <v>3.15</v>
       </c>
-      <c r="F7" s="42" t="n"/>
-      <c r="G7" s="25">
-        <f>IF(F7="","",F7/D7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="38">
-        <f>E7*100/C7</f>
-        <v/>
-      </c>
-      <c r="I7" s="33">
-        <f>MAX(0,1-(E7*100/(32*C7))^2)</f>
-        <v/>
-      </c>
-      <c r="J7" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C7)*I7/1000</f>
-        <v/>
-      </c>
-      <c r="K7" s="11">
-        <f>IF(G7="","FALTA CARGA",IF(G7&lt;=J7,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>T03</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
+      <c r="E11" s="17" t="n">
+        <v>290</v>
+      </c>
+      <c r="F11" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F8" s="42" t="n"/>
-      <c r="G8" s="25">
-        <f>IF(F8="","",F8/D8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="38">
-        <f>E8*100/C8</f>
-        <v/>
-      </c>
-      <c r="I8" s="33">
-        <f>MAX(0,1-(E8*100/(32*C8))^2)</f>
-        <v/>
-      </c>
-      <c r="J8" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C8)*I8/1000</f>
-        <v/>
-      </c>
-      <c r="K8" s="11">
-        <f>IF(G8="","FALTA CARGA",IF(G8&lt;=J8,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>No se habia detectado en el plano: aparece en el computo. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>T04a</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n">
+      <c r="G11" s="30">
+        <f>2*(100/I11)*PI()*(H11/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" s="30">
+        <f>(100/L11)*PI()*(K11/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M11" s="40">
+        <f>IF(F11&lt;=12,E11*F11,(E11+F11-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N11" s="16">
+        <f>IF(C11="","",C11*1000/M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="16">
+        <f>0.55*0.65*Datos_vigas!$B$5*M11*MAX(0,1-(D11*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P11" s="18">
+        <f>IF(C11="","FALTA CARGA",IF(C11&lt;=O11,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="20" t="inlineStr">
+        <is>
+          <t>Recibe el extremo de VI 11a. Carga estimada por la bajada de vigas: 14,6 t. Falta la carga: no figura en la planilla de la catedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="n"/>
+      <c r="D12" s="8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>375</v>
+      </c>
+      <c r="F12" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F9" s="42" t="n"/>
-      <c r="G9" s="25">
-        <f>IF(F9="","",F9/D9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="38">
-        <f>E9*100/C9</f>
-        <v/>
-      </c>
-      <c r="I9" s="33">
-        <f>MAX(0,1-(E9*100/(32*C9))^2)</f>
-        <v/>
-      </c>
-      <c r="J9" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C9)*I9/1000</f>
-        <v/>
-      </c>
-      <c r="K9" s="11">
-        <f>IF(G9="","FALTA CARGA",IF(G9&lt;=J9,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>T04b</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
+      <c r="G12" s="25">
+        <f>2*(100/I12)*PI()*(H12/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" s="25">
+        <f>(100/L12)*PI()*(K12/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M12" s="38">
+        <f>IF(F12&lt;=12,E12*F12,(E12+F12-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="9">
+        <f>IF(C12="","",C12*1000/M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M12*MAX(0,1-(D12*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P12" s="11">
+        <f>IF(C12="","FALTA CARGA",IF(C12&lt;=O12,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga: no figura en la planilla de la catedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="26" t="n"/>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C13" s="42" t="n"/>
+      <c r="D13" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="F13" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F10" s="42" t="n"/>
-      <c r="G10" s="25">
-        <f>IF(F10="","",F10/D10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="38">
-        <f>E10*100/C10</f>
-        <v/>
-      </c>
-      <c r="I10" s="33">
-        <f>MAX(0,1-(E10*100/(32*C10))^2)</f>
-        <v/>
-      </c>
-      <c r="J10" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C10)*I10/1000</f>
-        <v/>
-      </c>
-      <c r="K10" s="11">
-        <f>IF(G10="","FALTA CARGA",IF(G10&lt;=J10,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>En el plano solo figura en la planta de fundacion. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>T05a</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
+      <c r="G13" s="25">
+        <f>2*(100/I13)*PI()*(H13/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" s="25">
+        <f>(100/L13)*PI()*(K13/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" s="38">
+        <f>IF(F13&lt;=12,E13*F13,(E13+F13-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N13" s="9">
+        <f>IF(C13="","",C13*1000/M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M13*MAX(0,1-(D13*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P13" s="11">
+        <f>IF(C13="","FALTA CARGA",IF(C13&lt;=O13,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>Falta la carga: no figura en la planilla de la catedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="26" t="n"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="n"/>
+      <c r="D14" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="F14" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F11" s="42" t="n"/>
-      <c r="G11" s="25">
-        <f>IF(F11="","",F11/D11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="38">
-        <f>E11*100/C11</f>
-        <v/>
-      </c>
-      <c r="I11" s="33">
-        <f>MAX(0,1-(E11*100/(32*C11))^2)</f>
-        <v/>
-      </c>
-      <c r="J11" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C11)*I11/1000</f>
-        <v/>
-      </c>
-      <c r="K11" s="11">
-        <f>IF(G11="","FALTA CARGA",IF(G11&lt;=J11,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>T05b</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
+      <c r="G14" s="25">
+        <f>2*(100/I14)*PI()*(H14/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" s="25">
+        <f>(100/L14)*PI()*(K14/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" s="38">
+        <f>IF(F14&lt;=12,E14*F14,(E14+F14-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N14" s="9">
+        <f>IF(C14="","",C14*1000/M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M14*MAX(0,1-(D14*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P14" s="11">
+        <f>IF(C14="","FALTA CARGA",IF(C14&lt;=O14,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="13" t="inlineStr">
+        <is>
+          <t>Longitud muy corta: verificar si es tabique o el machon de una abertura. Falta la carga: no figura en la planilla de la catedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="26" t="n"/>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="F15" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>25.47</v>
-      </c>
-      <c r="G12" s="25">
-        <f>IF(F12="","",F12/D12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="38">
-        <f>E12*100/C12</f>
-        <v/>
-      </c>
-      <c r="I12" s="33">
-        <f>MAX(0,1-(E12*100/(32*C12))^2)</f>
-        <v/>
-      </c>
-      <c r="J12" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C12)*I12/1000</f>
-        <v/>
-      </c>
-      <c r="K12" s="11">
-        <f>IF(G12="","FALTA CARGA",IF(G12&lt;=J12,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>Recibe el extremo de VI 07c.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>T06a</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
+      <c r="G15" s="25">
+        <f>2*(100/I15)*PI()*(H15/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J15" s="25">
+        <f>(100/L15)*PI()*(K15/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M15" s="38">
+        <f>IF(F15&lt;=12,E15*F15,(E15+F15-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N15" s="9">
+        <f>IF(C15="","",C15*1000/M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="9">
+        <f>0.55*0.65*Datos_vigas!$B$5*M15*MAX(0,1-(D15*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P15" s="11">
+        <f>IF(C15="","FALTA CARGA",IF(C15&lt;=O15,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>Longitud muy corta: verificar si es tabique o el machon de una abertura. Falta la carga: no figura en la planilla de la catedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="n"/>
+      <c r="D16" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="F16" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F13" s="42" t="n"/>
-      <c r="G13" s="25">
-        <f>IF(F13="","",F13/D13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="38">
-        <f>E13*100/C13</f>
-        <v/>
-      </c>
-      <c r="I13" s="33">
-        <f>MAX(0,1-(E13*100/(32*C13))^2)</f>
-        <v/>
-      </c>
-      <c r="J13" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C13)*I13/1000</f>
-        <v/>
-      </c>
-      <c r="K13" s="11">
-        <f>IF(G13="","FALTA CARGA",IF(G13&lt;=J13,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>T06b</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F14" s="42" t="n"/>
-      <c r="G14" s="25">
-        <f>IF(F14="","",F14/D14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="38">
-        <f>E14*100/C14</f>
-        <v/>
-      </c>
-      <c r="I14" s="33">
-        <f>MAX(0,1-(E14*100/(32*C14))^2)</f>
-        <v/>
-      </c>
-      <c r="J14" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C14)*I14/1000</f>
-        <v/>
-      </c>
-      <c r="K14" s="11">
-        <f>IF(G14="","FALTA CARGA",IF(G14&lt;=J14,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L14" s="13" t="inlineStr">
-        <is>
-          <t>Perpendicular a las vigas chatas, en la union de VCH 03a con VCH 03b. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>T06c</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F15" s="42" t="n"/>
-      <c r="G15" s="25">
-        <f>IF(F15="","",F15/D15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="38">
-        <f>E15*100/C15</f>
-        <v/>
-      </c>
-      <c r="I15" s="33">
-        <f>MAX(0,1-(E15*100/(32*C15))^2)</f>
-        <v/>
-      </c>
-      <c r="J15" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C15)*I15/1000</f>
-        <v/>
-      </c>
-      <c r="K15" s="11">
-        <f>IF(G15="","FALTA CARGA",IF(G15&lt;=J15,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L15" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="G16" s="25">
-        <f>IF(F16="","",F16/D16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="38">
-        <f>E16*100/C16</f>
-        <v/>
-      </c>
-      <c r="I16" s="33">
-        <f>MAX(0,1-(E16*100/(32*C16))^2)</f>
-        <v/>
-      </c>
-      <c r="J16" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C16)*I16/1000</f>
-        <v/>
-      </c>
-      <c r="K16" s="11">
-        <f>IF(G16="","FALTA CARGA",IF(G16&lt;=J16,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>Recibe el extremo de VI 02, perpendicular.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>T08a</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D17" s="8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="G17" s="25">
-        <f>IF(F17="","",F17/D17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="38">
-        <f>E17*100/C17</f>
-        <v/>
-      </c>
-      <c r="I17" s="33">
-        <f>MAX(0,1-(E17*100/(32*C17))^2)</f>
-        <v/>
-      </c>
-      <c r="J17" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C17)*I17/1000</f>
-        <v/>
-      </c>
-      <c r="K17" s="11">
-        <f>IF(G17="","FALTA CARGA",IF(G17&lt;=J17,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>Recibe el extremo de VI 11a.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="18" t="n"/>
-      <c r="B18" s="28" t="inlineStr">
-        <is>
-          <t>T08b</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="30">
-        <f>IF(F18="","",F18/D18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="40">
-        <f>E18*100/C18</f>
-        <v/>
-      </c>
-      <c r="I18" s="35">
-        <f>MAX(0,1-(E18*100/(32*C18))^2)</f>
-        <v/>
-      </c>
-      <c r="J18" s="16">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C18)*I18/1000</f>
-        <v/>
-      </c>
-      <c r="K18" s="18">
-        <f>IF(G18="","FALTA CARGA",IF(G18&lt;=J18,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
+      <c r="G16" s="30">
+        <f>2*(100/I16)*PI()*(H16/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" s="30">
+        <f>(100/L16)*PI()*(K16/10)^2/4</f>
+        <v/>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M16" s="40">
+        <f>IF(F16&lt;=12,E16*F16,(E16+F16-12)*12)</f>
+        <v/>
+      </c>
+      <c r="N16" s="16">
+        <f>IF(C16="","",C16*1000/M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="16">
+        <f>0.55*0.65*Datos_vigas!$B$5*M16*MAX(0,1-(D16*100/(32*12))^2)/1000</f>
+        <v/>
+      </c>
+      <c r="P16" s="18">
+        <f>IF(C16="","FALTA CARGA",IF(C16&lt;=O16,"VERIFICA","NO VERIFICA"))</f>
+        <v/>
+      </c>
+      <c r="Q16" s="20" t="inlineStr">
+        <is>
+          <t>Falta la carga: no figura en la planilla de la catedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>T1 a T6: cargas y dimensiones tomadas de la planilla de la catedra.</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>PA   (altura de entrepiso)</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>T09</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F20" s="42" t="n"/>
-      <c r="G20" s="25">
-        <f>IF(F20="","",F20/D20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="38">
-        <f>E20*100/C20</f>
-        <v/>
-      </c>
-      <c r="I20" s="33">
-        <f>MAX(0,1-(E20*100/(32*C20))^2)</f>
-        <v/>
-      </c>
-      <c r="J20" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C20)*I20/1000</f>
-        <v/>
-      </c>
-      <c r="K20" s="11">
-        <f>IF(G20="","FALTA CARGA",IF(G20&lt;=J20,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F21" s="42" t="n"/>
-      <c r="G21" s="25">
-        <f>IF(F21="","",F21/D21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="38">
-        <f>E21*100/C21</f>
-        <v/>
-      </c>
-      <c r="I21" s="33">
-        <f>MAX(0,1-(E21*100/(32*C21))^2)</f>
-        <v/>
-      </c>
-      <c r="J21" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C21)*I21/1000</f>
-        <v/>
-      </c>
-      <c r="K21" s="11">
-        <f>IF(G21="","FALTA CARGA",IF(G21&lt;=J21,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F22" s="42" t="n"/>
-      <c r="G22" s="25">
-        <f>IF(F22="","",F22/D22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="38">
-        <f>E22*100/C22</f>
-        <v/>
-      </c>
-      <c r="I22" s="33">
-        <f>MAX(0,1-(E22*100/(32*C22))^2)</f>
-        <v/>
-      </c>
-      <c r="J22" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C22)*I22/1000</f>
-        <v/>
-      </c>
-      <c r="K22" s="11">
-        <f>IF(G22="","FALTA CARGA",IF(G22&lt;=J22,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>Longitud muy corta: verificar si es un tabique o el machon de una abertura. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F23" s="42" t="n"/>
-      <c r="G23" s="25">
-        <f>IF(F23="","",F23/D23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="38">
-        <f>E23*100/C23</f>
-        <v/>
-      </c>
-      <c r="I23" s="33">
-        <f>MAX(0,1-(E23*100/(32*C23))^2)</f>
-        <v/>
-      </c>
-      <c r="J23" s="9">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C23)*I23/1000</f>
-        <v/>
-      </c>
-      <c r="K23" s="11">
-        <f>IF(G23="","FALTA CARGA",IF(G23&lt;=J23,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>Longitud muy corta: verificar si es un tabique o el machon de una abertura. Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="18" t="n"/>
-      <c r="B24" s="28" t="inlineStr">
-        <is>
-          <t>T13</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F24" s="43" t="n"/>
-      <c r="G24" s="30">
-        <f>IF(F24="","",F24/D24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="40">
-        <f>E24*100/C24</f>
-        <v/>
-      </c>
-      <c r="I24" s="35">
-        <f>MAX(0,1-(E24*100/(32*C24))^2)</f>
-        <v/>
-      </c>
-      <c r="J24" s="16">
-        <f>0.55*0.65*Datos_vigas!$B$5*(100*C24)*I24/1000</f>
-        <v/>
-      </c>
-      <c r="K24" s="18">
-        <f>IF(G24="","FALTA CARGA",IF(G24&lt;=J24,"VERIFICA","NO VERIFICA"))</f>
-        <v/>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>Falta la carga que recibe. Mientras tanto no se puede verificar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="41" t="inlineStr">
-        <is>
-          <t>fi Pn = 0,55 x 0,65 x f'c x Ag x [1 - (alto / 32 espesor)^2]    muro portante de hormigon armado, con reduccion por esbeltez.</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="44" t="inlineStr">
-        <is>
-          <t>Longitudes tomadas del computo metrico (planilla N 3, item 4.1.10).</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>T7 a T13: dimensiones del computo metrico; la carga todavia no esta definida.</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>Area: si B es menor o igual al espesor el tabique es recto y el area es A x B; si no, es un tabique en L y el area es (A + B - espesor) x espesor.</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>fi Pn = 0,55 x 0,65 x f'c x area x [1 - (altura / 32 espesor)^2]   muro portante de hormigon armado con reduccion por esbeltez.</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>Armadura vertical en doble malla y horizontal en malla simple, ambas o8 c/20, iguales a las de la planilla de la catedra.</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A4:L4"/>
+  <mergeCells count="12">
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A11"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K4:K24">
+  <conditionalFormatting sqref="P4:P16">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"VERIFICA"</formula>
     </cfRule>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -16187,7 +16187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16651,7 +16651,7 @@
       </c>
       <c r="Q8" s="13" t="inlineStr">
         <is>
-          <t>El mas cargado del conjunto.</t>
+          <t>Si corresponde al T05b del plano, recibe el extremo de VI 07c, cuya reaccion da 18,1 t de servicio en mi bajada contra los 11 t de la catedra. Verificar.</t>
         </is>
       </c>
     </row>
@@ -16719,7 +16719,9 @@
           <t>T7</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n"/>
+      <c r="C10" s="8" t="n">
+        <v>21.12</v>
+      </c>
       <c r="D10" s="8" t="n">
         <v>3.15</v>
       </c>
@@ -16767,7 +16769,7 @@
       </c>
       <c r="Q10" s="13" t="inlineStr">
         <is>
-          <t>Recibe el extremo de VI 02. Carga estimada por la bajada de vigas: 21,1 t. Falta la carga: no figura en la planilla de la catedra.</t>
+          <t>Carga tomada de la reaccion de VI 02 en la planilla de vigas, MAYORADA. No es comparable sin mas con las de T1 a T6.</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16780,9 @@
           <t>T8</t>
         </is>
       </c>
-      <c r="C11" s="43" t="n"/>
+      <c r="C11" s="15" t="n">
+        <v>13.78</v>
+      </c>
       <c r="D11" s="15" t="n">
         <v>3.15</v>
       </c>
@@ -16826,7 +16830,7 @@
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
-          <t>Recibe el extremo de VI 11a. Carga estimada por la bajada de vigas: 14,6 t. Falta la carga: no figura en la planilla de la catedra.</t>
+          <t>Carga tomada de la reaccion de VI 11a en la planilla de vigas, MAYORADA.</t>
         </is>
       </c>
     </row>
@@ -17151,7 +17155,7 @@
     <row r="18">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>T1 a T6: cargas y dimensiones tomadas de la planilla de la catedra.</t>
+          <t>T1 a T6: cargas y dimensiones tomadas de la planilla de la catedra. Probablemente sean cargas de servicio; compararlas contra fi Pn, que es resistencia ultima, queda del lado inseguro en torno a un 40 por ciento. Con utilizaciones del 10 al 20 por ciento no cambia ningun veredicto, pero conviene saberlo.</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
@@ -17174,7 +17178,7 @@
     <row r="19">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>T7 a T13: dimensiones del computo metrico; la carga todavia no esta definida.</t>
+          <t>T7 y T8: carga tomada de la reaccion de VI 02 y VI 11a en la planilla de vigas, que son MAYORADAS. El criterio no es el mismo que en T1 a T6.</t>
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
@@ -17197,7 +17201,7 @@
     <row r="20">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>Area: si B es menor o igual al espesor el tabique es recto y el area es A x B; si no, es un tabique en L y el area es (A + B - espesor) x espesor.</t>
+          <t>T9 a T13: dimensiones del computo metrico; la carga todavia no esta definida.</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -17220,7 +17224,7 @@
     <row r="21">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>fi Pn = 0,55 x 0,65 x f'c x area x [1 - (altura / 32 espesor)^2]   muro portante de hormigon armado con reduccion por esbeltez.</t>
+          <t>Area: si B es menor o igual al espesor el tabique es recto y el area es A x B; si no, es un tabique en L y el area es (A + B - espesor) x espesor.</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -17243,7 +17247,7 @@
     <row r="22">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>Armadura vertical en doble malla y horizontal en malla simple, ambas o8 c/20, iguales a las de la planilla de la catedra.</t>
+          <t>fi Pn = 0,55 x 0,65 x f'c x area x [1 - (altura / 32 espesor)^2]   muro portante de hormigon armado con reduccion por esbeltez.</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -17262,6 +17266,29 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>Armadura vertical en doble malla y horizontal en malla simple, ambas o8 c/20, iguales a las de la planilla de la catedra.</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -253,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -406,6 +406,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3662,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3680,12 +3683,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
@@ -3708,6 +3713,7 @@
           <t>origen</t>
         </is>
       </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
@@ -3728,6 +3734,7 @@
           <t>ESTIMADA. Falta el estudio de suelos: cambiar aca y recalcula todo.</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
@@ -3748,6 +3755,7 @@
           <t>Dato real, tomado del encabezado del calculo de bases.</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="48" t="inlineStr">
@@ -3768,6 +3776,7 @@
           <t>Nota del plano: todos los pilotes son O30.</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="48" t="inlineStr">
@@ -3788,6 +3797,7 @@
           <t>Nota del plano: h = -4,50 m desde la cota +-0,00 de vereda.</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="48" t="inlineStr">
@@ -3808,150 +3818,350 @@
           <t>Para pasar de carga mayorada a carga de servicio.</t>
         </is>
       </c>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>TIPOS DE PILOTE  (nota general del plano: CANTIDAD 33 PILOTES)</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="inlineStr">
-        <is>
-          <t>COMO SE ESTIMO LA CARGA ADMISIBLE</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>cantidad</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>cota fundacion</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>nivel llenado</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="inlineStr">
+        <is>
+          <t>long. hormigon</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>Pilote O30 de 4,50 m: area de punta 0,0707 m2, area lateral 4,24 m2.</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t>Pilote tipo "A"</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="60" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="D12" s="60" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E12" s="60" t="n">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>Punta  0,0707 x 20 t/m2 = 1,4 t.</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t>Pilote tipo "B"</t>
+        </is>
+      </c>
+      <c r="B13" s="60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="60" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="D13" s="60" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="E13" s="60" t="n">
+        <v>4.15</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>Friccion lateral  4,24 x adherencia:  1,5 t/m2 -&gt; 6,4 t   |   3,0 t/m2 -&gt; 12,7 t.</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>Pilote tipo "C"</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" s="60" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="D14" s="60" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E14" s="60" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>Total segun adherencia: entre 7,8 y 14,1 t. Se adopta 12 t como valor de trabajo.</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>Pilote tipo "D"</t>
+        </is>
+      </c>
+      <c r="B15" s="60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="60" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="D15" s="60" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E15" s="60" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="44" t="inlineStr"/>
+      <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
-        <is>
-          <t>LECTURA INVERSA, que es la util mientras no haya estudio de suelos:</t>
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>Los cuatro tipos se funden a -4,50 m; se diferencian en el nivel de llenado de hormigon, o sea en la longitud real del fuste.</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>con las cargas de esta planilla, para que el esquema funcione cada pilote</t>
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>El computo metrico declara 32 pilotes: le falta uno. La nota del plano dice 33, que es la cantidad que se detecta en el dibujo.</t>
         </is>
       </c>
       <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>tiene que admitir del orden de 20 t. Si el estudio de suelos da menos,</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>faltan pilotes; si da mas, el diseno esta holgado.</t>
+      <c r="A20" s="59" t="inlineStr">
+        <is>
+          <t>COMO SE ESTIMO LA CARGA ADMISIBLE</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="44" t="inlineStr"/>
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>Pilote O30: area de punta 0,0707 m2. Punta  0,0707 x 20 t/m2 = 1,4 t.</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
+          <t>Area lateral segun el tipo: 3,86 m2 el A, 3,91 el B, 4,19 el C y 4,15 el D.</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
+          <t>Con una adherencia de 2,5 t/m2 la capacidad va de 11,1 t el tipo A a 11,9 t el C:</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
+          <t>la diferencia entre tipos es menor al 8 por ciento, por eso se adopta un unico</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>valor de 12 t para todos, en lugar de uno por tipo.</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>LECTURA INVERSA, que es la util mientras no haya estudio de suelos:</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>con las cargas de esta planilla, para que el esquema funcione cada pilote</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>tiene que admitir del orden de 20 t. Si el estudio de suelos da menos,</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>faltan pilotes; si da mas, el diseno esta holgado.</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>FALTA: la nota del plano remite a las planillas de cada tipo de pilote, que</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>traen la armadura y quiza la carga. Si aparecen, se cierra este punto.</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3972,180 +4182,180 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>MEMORIA - ILUMINACION Y VENTILACION</t>
         </is>
       </c>
-      <c r="B1" s="61" t="inlineStr"/>
+      <c r="B1" s="62" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr"/>
-      <c r="B2" s="62" t="inlineStr"/>
+      <c r="A2" s="62" t="inlineStr"/>
+      <c r="B2" s="63" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>CRITERIO</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>Area de iluminacion requerida = superficie del local / 9</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr"/>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr"/>
+      <c r="B4" s="63" t="inlineStr">
         <is>
           <t>Area de ventilacion requerida = un tercio de la de iluminacion = superficie / 27</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr"/>
-      <c r="B5" s="62" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr"/>
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>Area proyectada: la vidriada de la carpinteria para iluminacion, y la parte que</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="62" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr"/>
+      <c r="B6" s="63" t="inlineStr">
         <is>
           <t>realmente abre para ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="inlineStr"/>
-      <c r="B7" s="62" t="inlineStr"/>
+      <c r="A7" s="62" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>RESULTADO</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>Los trece locales cumplen holgadamente iluminacion y ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="61" t="inlineStr"/>
-      <c r="B9" s="62" t="inlineStr"/>
+      <c r="A9" s="62" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>CORRECCION</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="62" t="inlineStr">
         <is>
           <t>Local 07, Hall / ingreso: la planilla original traia 0,66 y 0,22, que son los</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr"/>
-      <c r="B11" s="62" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr"/>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr"/>
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="inlineStr"/>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>declarada y un verificador lo puede observar.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="inlineStr"/>
-      <c r="B14" s="62" t="inlineStr"/>
+      <c r="A14" s="62" t="inlineStr"/>
+      <c r="B14" s="63" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>A REVISAR</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>Local 14, Estar / Playroom: declara 5,00 m2 de ventilacion sobre 5,00 m2 de</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="61" t="inlineStr"/>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr"/>
+      <c r="B16" s="63" t="inlineStr">
         <is>
           <t>iluminacion, es decir una carpinteria enteramente abrible. En los demas locales</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="61" t="inlineStr"/>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr"/>
+      <c r="B17" s="63" t="inlineStr">
         <is>
           <t>la relacion es del 50 por ciento. Conviene verificar la carpinteria real.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="61" t="inlineStr"/>
-      <c r="B18" s="62" t="inlineStr"/>
+      <c r="A18" s="62" t="inlineStr"/>
+      <c r="B18" s="63" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="inlineStr"/>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr"/>
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>Local 02, Deposito: figura sin exigencia por no ser habitable. Son 11,8 m2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr"/>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr"/>
+      <c r="B20" s="63" t="inlineStr">
         <is>
           <t>cerrados: si se lo considera habitable hay que preverle conducto.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="inlineStr"/>
-      <c r="B21" s="62" t="inlineStr"/>
+      <c r="A21" s="62" t="inlineStr"/>
+      <c r="B21" s="63" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr">
+      <c r="A22" s="62" t="inlineStr">
         <is>
           <t>REDONDEOS</t>
         </is>
       </c>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B22" s="62" t="inlineStr">
         <is>
           <t>Diferencias menores que no afectan: local 03 da 5,95 m2 y figura 6,0;</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr"/>
-      <c r="B23" s="62" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr"/>
+      <c r="B23" s="63" t="inlineStr">
         <is>
           <t>local 09 da 12,25 y figura 12,3.</t>
         </is>
@@ -4170,592 +4380,592 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
         </is>
       </c>
-      <c r="B1" s="61" t="inlineStr"/>
+      <c r="B1" s="62" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr"/>
-      <c r="B2" s="62" t="inlineStr"/>
+      <c r="A2" s="62" t="inlineStr"/>
+      <c r="B2" s="63" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>NORMATIVA</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>CIRSOC 201. Hormigon H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200 kg/cm2).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>UNIDADES</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Longitudes en m y cm. Cargas en kg/m. Momentos en kgm. Tensiones en kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>b = ancho | h = altura util | d = altura total (igual criterio que la planilla de catedra).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="62" t="inlineStr"/>
+      <c r="A6" s="62" t="inlineStr"/>
+      <c r="B6" s="63" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr"/>
+      <c r="B7" s="62" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>Entrepiso PA</t>
         </is>
       </c>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="63" t="inlineStr">
         <is>
           <t>Losa maciza 12 cm 300 + contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="61" t="inlineStr"/>
-      <c r="B9" s="62" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>g = 550 kg/m2       q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>Azotea</t>
         </is>
       </c>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="63" t="inlineStr">
         <is>
           <t>Losa 300 + contrapiso de pendiente 140 + carpeta 42 + aislacion y membrana 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr"/>
-      <c r="B11" s="62" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>g = 560 kg/m2       q = 100 kg/m2 (cubierta no accesible)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>Mamposteria</t>
         </is>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>250 kg/m2. Altura 2,60 m en PA y 1,00 m de parapeto en azotea.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
         <is>
           <t>Peso propio</t>
         </is>
       </c>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>2400 kg/m3 x b x d, viga por viga.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="62" t="inlineStr">
         <is>
           <t>Carga de calculo</t>
         </is>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="63" t="inlineStr">
         <is>
           <t>p = 1,2 (g x B + peso propio + muro) + 1,6 (q x B)        B = ancho tributario</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="61" t="inlineStr"/>
-      <c r="B15" s="62" t="inlineStr"/>
+      <c r="A15" s="62" t="inlineStr"/>
+      <c r="B15" s="63" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="61" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B16" s="61" t="inlineStr">
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>Coeficientes segun esquema (tabla en hoja Datos):</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="61" t="inlineStr"/>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr"/>
+      <c r="B17" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  Simplemente apoyada   M = pL2/8                    R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="61" t="inlineStr"/>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="A18" s="62" t="inlineStr"/>
+      <c r="B18" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  Continua              M = pL2/14   Mapoyo = pL2/10  R = 0,575 pL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="inlineStr"/>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr"/>
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  Empotrada-apoyada     M = 9pL2/128 Mapoyo = pL2/8   R = 0,625 pL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr"/>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr"/>
+      <c r="B20" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  Biempotrada           M = pL2/24   Mapoyo = pL2/12  R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="inlineStr"/>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="A21" s="62" t="inlineStr"/>
+      <c r="B21" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  Voladizo                           Mapoyo = pL2/2   R = 1,000 pL</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr"/>
-      <c r="B22" s="62" t="inlineStr"/>
+      <c r="A22" s="62" t="inlineStr"/>
+      <c r="B22" s="63" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t>3. FLEXION</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="62" t="inlineStr">
         <is>
           <t>k = M / (phi b h2 f'c)      w = 1 - RAIZ(1 - 2k)      As = w b h f'c / fy</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="61" t="inlineStr"/>
-      <c r="B24" s="62" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr"/>
+      <c r="B24" s="63" t="inlineStr">
         <is>
           <t>As min = 0,0033 b h       As max = 0,0163 b h (0,75 de la cuantia balanceada)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="61" t="inlineStr"/>
-      <c r="B25" s="62" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr"/>
+      <c r="B25" s="63" t="inlineStr">
         <is>
           <t>Si la armadura no entra en una capa se disponen dos y el recubrimiento pasa a 6 cm.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="61" t="inlineStr"/>
-      <c r="B26" s="62" t="inlineStr"/>
+      <c r="A26" s="62" t="inlineStr"/>
+      <c r="B26" s="63" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>4. CORTE</t>
         </is>
       </c>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="B27" s="62" t="inlineStr">
         <is>
           <t>T = R / (b x 0,85 h)       tension tangencial en el apoyo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="61" t="inlineStr"/>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="A28" s="62" t="inlineStr"/>
+      <c r="B28" s="63" t="inlineStr">
         <is>
           <t>Vc = 0,53 RAIZ(f'c) b h        phi Vn = 0,75 (Vc + Av fy h / s)  &gt;=  R</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="61" t="inlineStr"/>
-      <c r="B29" s="62" t="inlineStr">
+      <c r="A29" s="62" t="inlineStr"/>
+      <c r="B29" s="63" t="inlineStr">
         <is>
           <t>Av = 2 ramas. Se aumenta el diametro antes que cerrar la separacion por debajo de 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="61" t="inlineStr"/>
-      <c r="B30" s="62" t="inlineStr"/>
+      <c r="A30" s="62" t="inlineStr"/>
+      <c r="B30" s="63" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="61" t="inlineStr">
+      <c r="A31" s="62" t="inlineStr">
         <is>
           <t>5. FLECHA</t>
         </is>
       </c>
-      <c r="B31" s="61" t="inlineStr">
+      <c r="B31" s="62" t="inlineStr">
         <is>
           <t>Altura minima: simplemente apoyada L/16, un extremo continuo L/18,5,</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="61" t="inlineStr"/>
-      <c r="B32" s="62" t="inlineStr">
+      <c r="A32" s="62" t="inlineStr"/>
+      <c r="B32" s="63" t="inlineStr">
         <is>
           <t>ambos extremos continuos L/21, voladizo L/8.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="61" t="inlineStr"/>
-      <c r="B33" s="62" t="inlineStr"/>
+      <c r="A33" s="62" t="inlineStr"/>
+      <c r="B33" s="63" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="61" t="inlineStr">
+      <c r="A34" s="62" t="inlineStr">
         <is>
           <t>6. VIGAS INVERTIDAS</t>
         </is>
       </c>
-      <c r="B34" s="61" t="inlineStr">
+      <c r="B34" s="62" t="inlineStr">
         <is>
           <t>Las vigas de BORDE son invertidas: sobresalen 70 cm por encima del fondo de</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="61" t="inlineStr"/>
-      <c r="B35" s="62" t="inlineStr">
+      <c r="A35" s="62" t="inlineStr"/>
+      <c r="B35" s="63" t="inlineStr">
         <is>
           <t>losa (cotas N.F.L +3,50 / N.S.V +4,20 y N.F.L +6,80 / N.S.V +7,50 del plano).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="61" t="inlineStr"/>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr"/>
+      <c r="B36" s="63" t="inlineStr">
         <is>
           <t>losa. Lo confirman las cotas del plano y el hecho de que el cielorraso sea de</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="61" t="inlineStr"/>
-      <c r="B37" s="62" t="inlineStr">
+      <c r="A37" s="62" t="inlineStr"/>
+      <c r="B37" s="63" t="inlineStr">
         <is>
           <t>VI 06 mide 14,00 m en total y es el cuarto borde de L07. Sobre su eje hay cuatro</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="61" t="inlineStr"/>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="A38" s="62" t="inlineStr"/>
+      <c r="B38" s="63" t="inlineStr">
         <is>
           <t>columnas, de modo que trabaja como viga continua de tres tramos de 4,10, 4,32 y</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="61" t="inlineStr"/>
-      <c r="B39" s="62" t="inlineStr">
+      <c r="A39" s="62" t="inlineStr"/>
+      <c r="B39" s="63" t="inlineStr">
         <is>
           <t>6,53 m. Se calcula con el mayor, 6,53 m, que es el que gobierna.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="61" t="inlineStr"/>
-      <c r="B40" s="62" t="inlineStr">
+      <c r="A40" s="62" t="inlineStr"/>
+      <c r="B40" s="63" t="inlineStr">
         <is>
           <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="61" t="inlineStr"/>
-      <c r="B41" s="62" t="inlineStr">
+      <c r="A41" s="62" t="inlineStr"/>
+      <c r="B41" s="63" t="inlineStr">
         <is>
           <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="61" t="inlineStr"/>
-      <c r="B42" s="62" t="inlineStr">
+      <c r="A42" s="62" t="inlineStr"/>
+      <c r="B42" s="63" t="inlineStr">
         <is>
           <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="61" t="inlineStr"/>
-      <c r="B43" s="62" t="inlineStr">
+      <c r="A43" s="62" t="inlineStr"/>
+      <c r="B43" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="61" t="inlineStr"/>
-      <c r="B44" s="62" t="inlineStr">
+      <c r="A44" s="62" t="inlineStr"/>
+      <c r="B44" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="61" t="inlineStr"/>
-      <c r="B45" s="62" t="inlineStr">
+      <c r="A45" s="62" t="inlineStr"/>
+      <c r="B45" s="63" t="inlineStr">
         <is>
           <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="61" t="inlineStr"/>
-      <c r="B46" s="62" t="inlineStr">
+      <c r="A46" s="62" t="inlineStr"/>
+      <c r="B46" s="63" t="inlineStr">
         <is>
           <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="61" t="inlineStr"/>
-      <c r="B47" s="62" t="inlineStr">
+      <c r="A47" s="62" t="inlineStr"/>
+      <c r="B47" s="63" t="inlineStr">
         <is>
           <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="61" t="inlineStr"/>
-      <c r="B48" s="62" t="inlineStr">
+      <c r="A48" s="62" t="inlineStr"/>
+      <c r="B48" s="63" t="inlineStr">
         <is>
           <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="61" t="inlineStr"/>
-      <c r="B49" s="62" t="inlineStr">
+      <c r="A49" s="62" t="inlineStr"/>
+      <c r="B49" s="63" t="inlineStr">
         <is>
           <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="61" t="inlineStr"/>
-      <c r="B50" s="62" t="inlineStr"/>
+      <c r="A50" s="62" t="inlineStr"/>
+      <c r="B50" s="63" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="61" t="inlineStr">
+      <c r="A51" s="62" t="inlineStr">
         <is>
           <t>7. RESULTADO</t>
         </is>
       </c>
-      <c r="B51" s="61" t="inlineStr">
+      <c r="B51" s="62" t="inlineStr">
         <is>
           <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="61" t="inlineStr"/>
-      <c r="B52" s="62" t="inlineStr">
+      <c r="A52" s="62" t="inlineStr"/>
+      <c r="B52" s="63" t="inlineStr">
         <is>
           <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="61" t="inlineStr"/>
-      <c r="B53" s="62" t="inlineStr">
+      <c r="A53" s="62" t="inlineStr"/>
+      <c r="B53" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="61" t="inlineStr"/>
-      <c r="B54" s="62" t="inlineStr">
+      <c r="A54" s="62" t="inlineStr"/>
+      <c r="B54" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="61" t="inlineStr"/>
-      <c r="B55" s="62" t="inlineStr">
+      <c r="A55" s="62" t="inlineStr"/>
+      <c r="B55" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="61" t="inlineStr"/>
-      <c r="B56" s="62" t="inlineStr">
+      <c r="A56" s="62" t="inlineStr"/>
+      <c r="B56" s="63" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="61" t="inlineStr"/>
-      <c r="B57" s="62" t="inlineStr">
+      <c r="A57" s="62" t="inlineStr"/>
+      <c r="B57" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="61" t="inlineStr"/>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="A58" s="62" t="inlineStr"/>
+      <c r="B58" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="61" t="inlineStr"/>
-      <c r="B59" s="62" t="inlineStr">
+      <c r="A59" s="62" t="inlineStr"/>
+      <c r="B59" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="61" t="inlineStr"/>
-      <c r="B60" s="62" t="inlineStr">
+      <c r="A60" s="62" t="inlineStr"/>
+      <c r="B60" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="61" t="inlineStr"/>
-      <c r="B61" s="62" t="inlineStr">
+      <c r="A61" s="62" t="inlineStr"/>
+      <c r="B61" s="63" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="61" t="inlineStr"/>
-      <c r="B62" s="62" t="inlineStr">
+      <c r="A62" s="62" t="inlineStr"/>
+      <c r="B62" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="61" t="inlineStr"/>
-      <c r="B63" s="62" t="inlineStr"/>
+      <c r="A63" s="62" t="inlineStr"/>
+      <c r="B63" s="63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="61" t="inlineStr">
+      <c r="A64" s="62" t="inlineStr">
         <is>
           <t>8. ALCANCE</t>
         </is>
       </c>
-      <c r="B64" s="62" t="inlineStr">
+      <c r="B64" s="63" t="inlineStr">
         <is>
           <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="61" t="inlineStr"/>
-      <c r="B65" s="62" t="inlineStr">
+      <c r="A65" s="62" t="inlineStr"/>
+      <c r="B65" s="63" t="inlineStr">
         <is>
           <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="61" t="inlineStr"/>
-      <c r="B66" s="62" t="inlineStr"/>
+      <c r="A66" s="62" t="inlineStr"/>
+      <c r="B66" s="63" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="61" t="inlineStr">
+      <c r="A67" s="62" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B67" s="61" t="inlineStr">
+      <c r="B67" s="62" t="inlineStr">
         <is>
           <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="61" t="inlineStr"/>
-      <c r="B68" s="62" t="inlineStr">
+      <c r="A68" s="62" t="inlineStr"/>
+      <c r="B68" s="63" t="inlineStr">
         <is>
           <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="61" t="inlineStr"/>
-      <c r="B69" s="62" t="inlineStr">
+      <c r="A69" s="62" t="inlineStr"/>
+      <c r="B69" s="63" t="inlineStr">
         <is>
           <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="61" t="inlineStr"/>
-      <c r="B70" s="62" t="inlineStr">
+      <c r="A70" s="62" t="inlineStr"/>
+      <c r="B70" s="63" t="inlineStr">
         <is>
           <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="61" t="inlineStr"/>
-      <c r="B71" s="62" t="inlineStr">
+      <c r="A71" s="62" t="inlineStr"/>
+      <c r="B71" s="63" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -4780,368 +4990,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - LOSAS</t>
         </is>
       </c>
-      <c r="B1" s="61" t="inlineStr"/>
+      <c r="B1" s="62" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr"/>
-      <c r="B2" s="62" t="inlineStr"/>
+      <c r="A2" s="62" t="inlineStr"/>
+      <c r="B2" s="63" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>METODO</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>Tensiones admisibles, igual criterio que la planilla modelo de la catedra.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr"/>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="A4" s="62" t="inlineStr"/>
+      <c r="B4" s="63" t="inlineStr">
         <is>
           <t>Se verifico contra la fila de ejemplo: momentos y reacciones coinciden exactamente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). Tension admisible 2400 kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="62" t="inlineStr">
         <is>
           <t>h = altura util | d = espesor total. Recubrimiento 1,5 cm.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="inlineStr"/>
-      <c r="B7" s="62" t="inlineStr"/>
+      <c r="A7" s="62" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="62" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q      (cargas de servicio, sin mayorar)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="61" t="inlineStr"/>
-      <c r="B9" s="62" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>Peso propio = 2400 x d / 100, calculado con el espesor propio de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="63" t="inlineStr">
         <is>
           <t>Terminaciones 242 kg/m2 (contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr"/>
-      <c r="B11" s="62" t="inlineStr">
+      <c r="A11" s="62" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr">
         <is>
           <t>q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>Terminaciones 252 kg/m2 (contrapiso pendiente 140 + carpeta 42 + aislacion 50 +</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="inlineStr"/>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>cielorraso 20).  q = 100 kg/m2 (azotea no accesible)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="inlineStr"/>
-      <c r="B14" s="62" t="inlineStr"/>
+      <c r="A14" s="62" t="inlineStr"/>
+      <c r="B14" s="63" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>M = coeficiente x p x L2, segun el grado de empotramiento:</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="61" t="inlineStr"/>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr"/>
+      <c r="B16" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  1/8 simplemente apoyada    1/10 y 1/14 continua    1/12 biempotrada    1/2 voladizo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="61" t="inlineStr"/>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr"/>
+      <c r="B17" s="63" t="inlineStr">
         <is>
           <t>R = coeficiente x p x L. En voladizo Rx = p x L y Ry no corresponde.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="61" t="inlineStr"/>
-      <c r="B18" s="62" t="inlineStr"/>
+      <c r="A18" s="62" t="inlineStr"/>
+      <c r="B18" s="63" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>As = M x 100 / (2400 x 0,9 x h)        [cm2/m]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr"/>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="A20" s="62" t="inlineStr"/>
+      <c r="B20" s="63" t="inlineStr">
         <is>
           <t>separacion = 100 x area de la barra / As, redondeada, con maximo 20 cm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="inlineStr"/>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="A21" s="62" t="inlineStr"/>
+      <c r="B21" s="63" t="inlineStr">
         <is>
           <t>Armadura de reparticion = As / 5, con un minimo de 0,30 cm2/m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr"/>
-      <c r="B22" s="62" t="inlineStr"/>
+      <c r="A22" s="62" t="inlineStr"/>
+      <c r="B22" s="63" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t>4. ESPESORES</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="62" t="inlineStr">
         <is>
           <t>Los espesores d se leyeron del plano: estan escritos debajo del rotulo de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="61" t="inlineStr"/>
-      <c r="B24" s="62" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr"/>
+      <c r="B24" s="63" t="inlineStr">
         <is>
           <t>S/PB:  L01 11 | L02 9 | L03 13 | L04 11 | L05 11 | L06 8 | L07 12 | L08 10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="61" t="inlineStr"/>
-      <c r="B25" s="62" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr"/>
+      <c r="B25" s="63" t="inlineStr">
         <is>
           <t>S/PA:  L09 13 | L10 12</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="61" t="inlineStr"/>
-      <c r="B26" s="62" t="inlineStr"/>
+      <c r="A26" s="62" t="inlineStr"/>
+      <c r="B26" s="63" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="61" t="inlineStr">
+      <c r="A27" s="62" t="inlineStr">
         <is>
           <t>5. LUCES</t>
         </is>
       </c>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="B27" s="62" t="inlineStr">
         <is>
           <t>Relevadas en obra y aportadas por el proyectista. Dos losas son voladizo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="61" t="inlineStr"/>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="A28" s="62" t="inlineStr"/>
+      <c r="B28" s="63" t="inlineStr">
         <is>
           <t>(L02 de 0,80 m y L08 de 0,75 m) y se calculan con M = p L2 / 2.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="61" t="inlineStr"/>
-      <c r="B29" s="62" t="inlineStr"/>
+      <c r="A29" s="62" t="inlineStr"/>
+      <c r="B29" s="63" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="61" t="inlineStr">
+      <c r="A30" s="62" t="inlineStr">
         <is>
           <t>6. LOSAS CRUZADAS</t>
         </is>
       </c>
-      <c r="B30" s="62" t="inlineStr">
+      <c r="B30" s="63" t="inlineStr">
         <is>
           <t>L07 (4,85 x 5,60) y L10 (4,85 x 6,00) apoyan en los cuatro bordes y su relacion</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="61" t="inlineStr"/>
-      <c r="B31" s="62" t="inlineStr">
+      <c r="A31" s="62" t="inlineStr"/>
+      <c r="B31" s="63" t="inlineStr">
         <is>
           <t>de lados es menor que 2, por lo que trabajan en las dos direcciones.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="61" t="inlineStr"/>
-      <c r="B32" s="62" t="inlineStr">
+      <c r="A32" s="62" t="inlineStr"/>
+      <c r="B32" s="63" t="inlineStr">
         <is>
           <t>Se reparte la carga por el metodo de Marcus:   kx = ly4 / (lx4 + ly4)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="61" t="inlineStr"/>
-      <c r="B33" s="62" t="inlineStr">
+      <c r="A33" s="62" t="inlineStr"/>
+      <c r="B33" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  L07: ly/lx = 1,15  -&gt;  64% en la direccion corta, 36% en la larga</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="61" t="inlineStr"/>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="A34" s="62" t="inlineStr"/>
+      <c r="B34" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  L10: ly/lx = 1,24  -&gt;  70% en la direccion corta, 30% en la larga</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="61" t="inlineStr"/>
-      <c r="B35" s="62" t="inlineStr">
+      <c r="A35" s="62" t="inlineStr"/>
+      <c r="B35" s="63" t="inlineStr">
         <is>
           <t>Cada una ocupa dos renglones, uno por direccion, con la fraccion de carga que</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="61" t="inlineStr"/>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr"/>
+      <c r="B36" s="63" t="inlineStr">
         <is>
           <t>le toca ya aplicada en la columna CARGAS. Las dos armaduras se cruzan en obra:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="61" t="inlineStr"/>
-      <c r="B37" s="62" t="inlineStr">
+      <c r="A37" s="62" t="inlineStr"/>
+      <c r="B37" s="63" t="inlineStr">
         <is>
           <t>la de la direccion corta va abajo, la de la larga arriba de aquella.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="61" t="inlineStr"/>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="A38" s="62" t="inlineStr"/>
+      <c r="B38" s="63" t="inlineStr">
         <is>
           <t>La columna auxiliar luz transv. es la que dispara el reparto: si se borra, la</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="61" t="inlineStr"/>
-      <c r="B39" s="62" t="inlineStr">
+      <c r="A39" s="62" t="inlineStr"/>
+      <c r="B39" s="63" t="inlineStr">
         <is>
           <t>fila vuelve a calcularse como losa armada en una direccion.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="61" t="inlineStr"/>
-      <c r="B40" s="62" t="inlineStr"/>
+      <c r="A40" s="62" t="inlineStr"/>
+      <c r="B40" s="63" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="61" t="inlineStr">
+      <c r="A41" s="62" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B41" s="62" t="inlineStr">
         <is>
           <t>El grado de empotramiento esta cargado en 1/8 salvo los dos voladizos (1/2). Si</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="61" t="inlineStr"/>
-      <c r="B42" s="62" t="inlineStr">
+      <c r="A42" s="62" t="inlineStr"/>
+      <c r="B42" s="63" t="inlineStr">
         <is>
           <t>alguna losa es continua sobre una viga corresponde 1/10 o 1/14: corregir en la columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="61" t="inlineStr"/>
-      <c r="B43" s="62" t="inlineStr">
+      <c r="A43" s="62" t="inlineStr"/>
+      <c r="B43" s="63" t="inlineStr">
         <is>
           <t>El diagrama de cargas es una imagen fija: si cambias el grado, cambialo a mano.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="61" t="inlineStr"/>
-      <c r="B44" s="62" t="inlineStr">
+      <c r="A44" s="62" t="inlineStr"/>
+      <c r="B44" s="63" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -5166,384 +5376,384 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - COLUMNAS</t>
         </is>
       </c>
-      <c r="B1" s="61" t="inlineStr"/>
+      <c r="B1" s="62" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="inlineStr"/>
-      <c r="B2" s="62" t="inlineStr"/>
+      <c r="A2" s="62" t="inlineStr"/>
+      <c r="B2" s="63" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B3" s="61" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). phi compresion 0,65.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="inlineStr"/>
-      <c r="B4" s="62" t="inlineStr"/>
+      <c r="A4" s="62" t="inlineStr"/>
+      <c r="B4" s="63" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="inlineStr">
+      <c r="A5" s="62" t="inlineStr">
         <is>
           <t>1. RELEVAMIENTO</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>Las columnas se identificaron en el plano cruzando el rotulo COL con un rectangulo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="inlineStr"/>
-      <c r="B6" s="62" t="inlineStr">
+      <c r="A6" s="62" t="inlineStr"/>
+      <c r="B6" s="63" t="inlineStr">
         <is>
           <t>de la misma seccion a menos de 26 pt. Resultaron 9 en PB y 4 en PA.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="61" t="inlineStr"/>
-      <c r="B7" s="62" t="inlineStr">
+      <c r="A7" s="62" t="inlineStr"/>
+      <c r="B7" s="63" t="inlineStr">
         <is>
           <t>Las 4 de PA caen exactamente sobre C6, C7, C8 y C9 de PB, y ademas tienen la misma</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr"/>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="A8" s="62" t="inlineStr"/>
+      <c r="B8" s="63" t="inlineStr">
         <is>
           <t>seccion, lo que confirma que la correspondencia entre plantas es correcta.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="61" t="inlineStr"/>
-      <c r="B9" s="62" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr"/>
+      <c r="B9" s="63" t="inlineStr">
         <is>
           <t>La C01 de 10x10 esta confirmada por el proyectista aunque el computo metrico no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr"/>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="A10" s="62" t="inlineStr"/>
+      <c r="B10" s="63" t="inlineStr">
         <is>
           <t>la incluya en su item 4.1.3: ese computo esta incompleto en ese punto.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr"/>
-      <c r="B11" s="62" t="inlineStr"/>
+      <c r="A11" s="62" t="inlineStr"/>
+      <c r="B11" s="63" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="62" t="inlineStr">
         <is>
           <t>2. ALTURAS</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>PB 3,15 m y PA 3,22 m, los mismos valores de la planilla de la catedra, coherentes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="61" t="inlineStr"/>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr"/>
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>con los niveles del plano (N.F.L +3,50 del entrepiso y +6,80 del techo).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="inlineStr"/>
-      <c r="B14" s="62" t="inlineStr"/>
+      <c r="A14" s="62" t="inlineStr"/>
+      <c r="B14" s="63" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="61" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B15" s="61" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>As = 0,008 x area (cuantia minima, el mismo criterio de la planilla modelo).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="61" t="inlineStr"/>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="A16" s="62" t="inlineStr"/>
+      <c r="B16" s="63" t="inlineStr">
         <is>
           <t>Se adoptan 4 barras del 12 en todas: 4,52 cm2, que cubre la minima en toda seccion.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="61" t="inlineStr"/>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr"/>
+      <c r="B17" s="63" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. long. ; 48 x diam. estribo ; lado menor),</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="61" t="inlineStr"/>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="A18" s="62" t="inlineStr"/>
+      <c r="B18" s="63" t="inlineStr">
         <is>
           <t>redondeada hacia abajo a multiplo de 5. Para 4d12 con estribo d6 da 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="inlineStr"/>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr"/>
+      <c r="B19" s="63" t="inlineStr">
         <is>
           <t>La planilla de la catedra adopta 20 cm: ese valor supera el limite reglamentario.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr"/>
-      <c r="B20" s="62" t="inlineStr"/>
+      <c r="A20" s="62" t="inlineStr"/>
+      <c r="B20" s="63" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="61" t="inlineStr">
+      <c r="A21" s="62" t="inlineStr">
         <is>
           <t>4. CAPACIDAD</t>
         </is>
       </c>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="B21" s="62" t="inlineStr">
         <is>
           <t>phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]     (columna zunchada con estribos)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr"/>
-      <c r="B22" s="62" t="inlineStr">
+      <c r="A22" s="62" t="inlineStr"/>
+      <c r="B22" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  15x30 con 4d12 -&gt; 51,2 t        20x20 con 4d12 -&gt; 46,6 t</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="61" t="inlineStr"/>
-      <c r="B23" s="62" t="inlineStr"/>
+      <c r="A23" s="62" t="inlineStr"/>
+      <c r="B23" s="63" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="61" t="inlineStr">
+      <c r="A24" s="62" t="inlineStr">
         <is>
           <t>5. CARGAS</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B24" s="62" t="inlineStr">
         <is>
           <t>La columna CARGA (t) viene cargada con una bajada automatica: suma de las</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="61" t="inlineStr"/>
-      <c r="B25" s="62" t="inlineStr">
+      <c r="A25" s="62" t="inlineStr"/>
+      <c r="B25" s="63" t="inlineStr">
         <is>
           <t>reacciones de las vigas que apoyan en cada columna (tomadas de la planilla de</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="61" t="inlineStr"/>
-      <c r="B26" s="62" t="inlineStr">
+      <c r="A26" s="62" t="inlineStr"/>
+      <c r="B26" s="63" t="inlineStr">
         <is>
           <t>vigas), mas el peso propio, mas lo que baja de la columna del nivel superior.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="61" t="inlineStr"/>
-      <c r="B27" s="62" t="inlineStr">
+      <c r="A27" s="62" t="inlineStr"/>
+      <c r="B27" s="63" t="inlineStr">
         <is>
           <t>ES UNA CARGA PROVISORIA Y ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="61" t="inlineStr"/>
-      <c r="B28" s="62" t="inlineStr">
+      <c r="A28" s="62" t="inlineStr"/>
+      <c r="B28" s="63" t="inlineStr">
         <is>
           <t>de viga no pudieron asignarse a ninguna columna porque apoyan en otra viga, en</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="61" t="inlineStr"/>
-      <c r="B29" s="62" t="inlineStr">
+      <c r="A29" s="62" t="inlineStr"/>
+      <c r="B29" s="63" t="inlineStr">
         <is>
           <t>un tabique o en la medianera, y esas reacciones no estan sumadas.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="61" t="inlineStr"/>
-      <c r="B30" s="62" t="inlineStr">
+      <c r="A30" s="62" t="inlineStr"/>
+      <c r="B30" s="63" t="inlineStr">
         <is>
           <t>Para cerrarla hay que indicar, para cada uno de esos 20 extremos, en que apoya.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="61" t="inlineStr"/>
-      <c r="B31" s="62" t="inlineStr">
+      <c r="A31" s="62" t="inlineStr"/>
+      <c r="B31" s="63" t="inlineStr">
         <is>
           <t>Mientras tanto la columna es editable: al corregir un valor todo recalcula.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="61" t="inlineStr"/>
-      <c r="B32" s="62" t="inlineStr">
+      <c r="A32" s="62" t="inlineStr"/>
+      <c r="B32" s="63" t="inlineStr">
         <is>
           <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="61" t="inlineStr"/>
-      <c r="B33" s="62" t="inlineStr">
+      <c r="A33" s="62" t="inlineStr"/>
+      <c r="B33" s="63" t="inlineStr">
         <is>
           <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="61" t="inlineStr"/>
-      <c r="B34" s="62" t="inlineStr"/>
+      <c r="A34" s="62" t="inlineStr"/>
+      <c r="B34" s="63" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="61" t="inlineStr">
+      <c r="A35" s="62" t="inlineStr">
         <is>
           <t>6. ESBELTEZ</t>
         </is>
       </c>
-      <c r="B35" s="61" t="inlineStr">
+      <c r="B35" s="62" t="inlineStr">
         <is>
           <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="61" t="inlineStr"/>
-      <c r="B36" s="62" t="inlineStr">
+      <c r="A36" s="62" t="inlineStr"/>
+      <c r="B36" s="63" t="inlineStr">
         <is>
           <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="61" t="inlineStr"/>
-      <c r="B37" s="62" t="inlineStr">
+      <c r="A37" s="62" t="inlineStr"/>
+      <c r="B37" s="63" t="inlineStr">
         <is>
           <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="61" t="inlineStr"/>
-      <c r="B38" s="62" t="inlineStr">
+      <c r="A38" s="62" t="inlineStr"/>
+      <c r="B38" s="63" t="inlineStr">
         <is>
           <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="61" t="inlineStr"/>
-      <c r="B39" s="62" t="inlineStr"/>
+      <c r="A39" s="62" t="inlineStr"/>
+      <c r="B39" s="63" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="61" t="inlineStr">
+      <c r="A40" s="62" t="inlineStr">
         <is>
           <t>7. LA DE 10x10</t>
         </is>
       </c>
-      <c r="B40" s="61" t="inlineStr">
+      <c r="B40" s="62" t="inlineStr">
         <is>
           <t>Existe, confirmada por el proyectista, y el computo metrico la omite. Con 10 cm</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="61" t="inlineStr"/>
-      <c r="B41" s="62" t="inlineStr">
+      <c r="A41" s="62" t="inlineStr"/>
+      <c r="B41" s="63" t="inlineStr">
         <is>
           <t>de lado y 3,15 m de altura su esbeltez es k lu / r = 105, tres veces el limite</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="61" t="inlineStr"/>
-      <c r="B42" s="62" t="inlineStr">
+      <c r="A42" s="62" t="inlineStr"/>
+      <c r="B42" s="63" t="inlineStr">
         <is>
           <t>por debajo del cual se puede despreciar el pandeo, y su capacidad es de 18,7 t</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="61" t="inlineStr"/>
-      <c r="B43" s="62" t="inlineStr">
+      <c r="A43" s="62" t="inlineStr"/>
+      <c r="B43" s="63" t="inlineStr">
         <is>
           <t>contra los 51 de una 15x30. Es el punto mas delicado del conjunto: conviene</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="61" t="inlineStr"/>
-      <c r="B44" s="62" t="inlineStr">
+      <c r="A44" s="62" t="inlineStr"/>
+      <c r="B44" s="63" t="inlineStr">
         <is>
           <t>verificarla a segundo orden en serio, no con la formula de compresion simple.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="61" t="inlineStr"/>
-      <c r="B45" s="62" t="inlineStr"/>
+      <c r="A45" s="62" t="inlineStr"/>
+      <c r="B45" s="63" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="61" t="inlineStr">
+      <c r="A46" s="62" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B46" s="61" t="inlineStr">
+      <c r="B46" s="62" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="61" t="inlineStr"/>
-      <c r="B47" s="62" t="inlineStr">
+      <c r="A47" s="62" t="inlineStr"/>
+      <c r="B47" s="63" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="61" t="inlineStr"/>
-      <c r="B48" s="62" t="inlineStr">
+      <c r="A48" s="62" t="inlineStr"/>
+      <c r="B48" s="63" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>
@@ -5571,7 +5781,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="63" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION - inventario. Calculo pendiente: va despues de columnas.</t>
         </is>
@@ -5713,7 +5923,7 @@
       <c r="D9" s="11" t="n">
         <v>533</v>
       </c>
-      <c r="E9" s="64" t="inlineStr">
+      <c r="E9" s="65" t="inlineStr">
         <is>
           <t>Ancho cortado en el PDF: confirmar 20 o 22 cm</t>
         </is>
@@ -5779,7 +5989,7 @@
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="64" t="inlineStr">
+      <c r="E13" s="65" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -5794,7 +6004,7 @@
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="64" t="inlineStr">
+      <c r="E14" s="65" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -5996,7 +6206,7 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="64" t="inlineStr">
+      <c r="E26" s="65" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -253,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -368,12 +368,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3496,7 +3490,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - COLUMNAS</t>
         </is>
@@ -3510,29 +3504,29 @@
       <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>MATERIALES Y CRITERIOS</t>
         </is>
       </c>
-      <c r="B3" s="47" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C3" s="47" t="inlineStr">
+      <c r="C3" s="45" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B4" s="49" t="n">
+      <c r="B4" s="47" t="n">
         <v>210</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -3542,12 +3536,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="47" t="n">
         <v>4200</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -3557,12 +3551,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -3572,12 +3566,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>phi compresion (estribos)</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="47" t="n">
         <v>0.65</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -3587,12 +3581,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Cuantia minima</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.008</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -3602,12 +3596,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Altura PB</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="47" t="n">
         <v>3.15</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -3617,12 +3611,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Altura PA</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="47" t="n">
         <v>3.22</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -3675,7 +3669,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - PILOTES</t>
         </is>
@@ -3693,22 +3687,22 @@
       <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>PARAMETRO</t>
         </is>
       </c>
-      <c r="B3" s="47" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C3" s="47" t="inlineStr">
+      <c r="C3" s="45" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
       </c>
-      <c r="D3" s="46" t="inlineStr">
+      <c r="D3" s="44" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
@@ -3716,12 +3710,12 @@
       <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Carga admisible por pilote</t>
         </is>
       </c>
-      <c r="B4" s="49" t="n">
+      <c r="B4" s="47" t="n">
         <v>12</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -3729,7 +3723,7 @@
           <t>t</t>
         </is>
       </c>
-      <c r="D4" s="53" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>ESTIMADA. Falta el estudio de suelos: cambiar aca y recalcula todo.</t>
         </is>
@@ -3737,12 +3731,12 @@
       <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Tension admisible del terreno</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="47" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -3750,7 +3744,7 @@
           <t>kg/cm2</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Dato real, tomado del encabezado del calculo de bases.</t>
         </is>
@@ -3758,12 +3752,12 @@
       <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Diametro del pilote</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="47" t="n">
         <v>30</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -3771,7 +3765,7 @@
           <t>cm</t>
         </is>
       </c>
-      <c r="D6" s="53" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>Nota del plano: todos los pilotes son O30.</t>
         </is>
@@ -3779,12 +3773,12 @@
       <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Profundidad</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="47" t="n">
         <v>-4.5</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -3792,7 +3786,7 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="51" t="inlineStr">
         <is>
           <t>Nota del plano: h = -4,50 m desde la cota +-0,00 de vereda.</t>
         </is>
@@ -3800,12 +3794,12 @@
       <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Coef. de mayoracion adoptado</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="47" t="n">
         <v>1.4</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -3813,7 +3807,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="51" t="inlineStr">
         <is>
           <t>Para pasar de carga mayorada a carga de servicio.</t>
         </is>
@@ -3828,7 +3822,7 @@
       <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="59" t="inlineStr">
+      <c r="A10" s="57" t="inlineStr">
         <is>
           <t>TIPOS DE PILOTE  (nota general del plano: CANTIDAD 33 PILOTES)</t>
         </is>
@@ -3839,105 +3833,105 @@
       <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="47" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>cantidad</t>
         </is>
       </c>
-      <c r="C11" s="47" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>cota fundacion</t>
         </is>
       </c>
-      <c r="D11" s="47" t="inlineStr">
+      <c r="D11" s="45" t="inlineStr">
         <is>
           <t>nivel llenado</t>
         </is>
       </c>
-      <c r="E11" s="47" t="inlineStr">
+      <c r="E11" s="45" t="inlineStr">
         <is>
           <t>long. hormigon</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Pilote tipo "A"</t>
         </is>
       </c>
-      <c r="B12" s="60" t="n">
+      <c r="B12" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="60" t="n">
+      <c r="C12" s="58" t="n">
         <v>-4.5</v>
       </c>
-      <c r="D12" s="60" t="n">
+      <c r="D12" s="58" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E12" s="60" t="n">
+      <c r="E12" s="58" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>Pilote tipo "B"</t>
         </is>
       </c>
-      <c r="B13" s="60" t="n">
+      <c r="B13" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="60" t="n">
+      <c r="C13" s="58" t="n">
         <v>-4.5</v>
       </c>
-      <c r="D13" s="60" t="n">
+      <c r="D13" s="58" t="n">
         <v>-0.35</v>
       </c>
-      <c r="E13" s="60" t="n">
+      <c r="E13" s="58" t="n">
         <v>4.15</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>Pilote tipo "C"</t>
         </is>
       </c>
-      <c r="B14" s="60" t="n">
+      <c r="B14" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="C14" s="60" t="n">
+      <c r="C14" s="58" t="n">
         <v>-4.5</v>
       </c>
-      <c r="D14" s="60" t="n">
+      <c r="D14" s="58" t="n">
         <v>-0.05</v>
       </c>
-      <c r="E14" s="60" t="n">
+      <c r="E14" s="58" t="n">
         <v>4.45</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>Pilote tipo "D"</t>
         </is>
       </c>
-      <c r="B15" s="60" t="n">
+      <c r="B15" s="58" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="60" t="n">
+      <c r="C15" s="58" t="n">
         <v>-4.5</v>
       </c>
-      <c r="D15" s="60" t="n">
+      <c r="D15" s="58" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E15" s="60" t="n">
+      <c r="E15" s="58" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -3949,7 +3943,7 @@
       <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="44" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>Los cuatro tipos se funden a -4,50 m; se diferencian en el nivel de llenado de hormigon, o sea en la longitud real del fuste.</t>
         </is>
@@ -3978,7 +3972,7 @@
       <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="57" t="inlineStr">
         <is>
           <t>COMO SE ESTIMO LA CARGA ADMISIBLE</t>
         </is>
@@ -3989,7 +3983,7 @@
       <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>Pilote O30: area de punta 0,0707 m2. Punta  0,0707 x 20 t/m2 = 1,4 t.</t>
         </is>
@@ -4000,7 +3994,7 @@
       <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>Area lateral segun el tipo: 3,86 m2 el A, 3,91 el B, 4,19 el C y 4,15 el D.</t>
         </is>
@@ -4011,7 +4005,7 @@
       <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>Con una adherencia de 2,5 t/m2 la capacidad va de 11,1 t el tipo A a 11,9 t el C:</t>
         </is>
@@ -4022,7 +4016,7 @@
       <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>la diferencia entre tipos es menor al 8 por ciento, por eso se adopta un unico</t>
         </is>
@@ -4033,7 +4027,7 @@
       <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>valor de 12 t para todos, en lugar de uno por tipo.</t>
         </is>
@@ -4044,7 +4038,7 @@
       <c r="E25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="44" t="inlineStr"/>
+      <c r="A26" s="42" t="inlineStr"/>
       <c r="B26" s="2" t="n"/>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
@@ -4062,7 +4056,7 @@
       <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="44" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>con las cargas de esta planilla, para que el esquema funcione cada pilote</t>
         </is>
@@ -4073,7 +4067,7 @@
       <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="44" t="inlineStr">
+      <c r="A29" s="42" t="inlineStr">
         <is>
           <t>tiene que admitir del orden de 20 t. Si el estudio de suelos da menos,</t>
         </is>
@@ -4084,7 +4078,7 @@
       <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="44" t="inlineStr">
+      <c r="A30" s="42" t="inlineStr">
         <is>
           <t>faltan pilotes; si da mas, el diseno esta holgado.</t>
         </is>
@@ -4095,14 +4089,14 @@
       <c r="E30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="44" t="inlineStr"/>
+      <c r="A31" s="42" t="inlineStr"/>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="44" t="inlineStr">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>FALTA: la nota del plano remite a las planillas de cada tipo de pilote, que</t>
         </is>
@@ -4113,7 +4107,7 @@
       <c r="E32" s="2" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="44" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>traen la armadura y quiza la carga. Si aparecen, se cierra este punto.</t>
         </is>
@@ -4124,14 +4118,14 @@
       <c r="E33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="44" t="inlineStr"/>
+      <c r="A34" s="42" t="inlineStr"/>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="44" t="inlineStr">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
         </is>
@@ -4142,7 +4136,7 @@
       <c r="E35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="44" t="inlineStr">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
         </is>
@@ -4153,7 +4147,7 @@
       <c r="E36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="44" t="inlineStr">
+      <c r="A37" s="42" t="inlineStr">
         <is>
           <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
         </is>
@@ -4182,180 +4176,180 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>MEMORIA - ILUMINACION Y VENTILACION</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr"/>
+      <c r="B1" s="60" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr"/>
-      <c r="B2" s="63" t="inlineStr"/>
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>CRITERIO</t>
         </is>
       </c>
-      <c r="B3" s="62" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>Area de iluminacion requerida = superficie del local / 9</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr"/>
-      <c r="B4" s="63" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr"/>
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>Area de ventilacion requerida = un tercio de la de iluminacion = superficie / 27</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="inlineStr"/>
-      <c r="B5" s="63" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr"/>
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>Area proyectada: la vidriada de la carpinteria para iluminacion, y la parte que</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="inlineStr"/>
-      <c r="B6" s="63" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>realmente abre para ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="62" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
+      <c r="A7" s="60" t="inlineStr"/>
+      <c r="B7" s="61" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>RESULTADO</t>
         </is>
       </c>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>Los trece locales cumplen holgadamente iluminacion y ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="62" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr"/>
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="62" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>CORRECCION</t>
         </is>
       </c>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B10" s="60" t="inlineStr">
         <is>
           <t>Local 07, Hall / ingreso: la planilla original traia 0,66 y 0,22, que son los</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="62" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="62" t="inlineStr"/>
-      <c r="B12" s="63" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr"/>
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="62" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr"/>
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>declarada y un verificador lo puede observar.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="62" t="inlineStr"/>
-      <c r="B14" s="63" t="inlineStr"/>
+      <c r="A14" s="60" t="inlineStr"/>
+      <c r="B14" s="61" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="62" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>A REVISAR</t>
         </is>
       </c>
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>Local 14, Estar / Playroom: declara 5,00 m2 de ventilacion sobre 5,00 m2 de</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr"/>
-      <c r="B16" s="63" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr"/>
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>iluminacion, es decir una carpinteria enteramente abrible. En los demas locales</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="62" t="inlineStr"/>
-      <c r="B17" s="63" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>la relacion es del 50 por ciento. Conviene verificar la carpinteria real.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="62" t="inlineStr"/>
-      <c r="B18" s="63" t="inlineStr"/>
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="inlineStr"/>
-      <c r="B19" s="63" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr"/>
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>Local 02, Deposito: figura sin exigencia por no ser habitable. Son 11,8 m2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr"/>
-      <c r="B20" s="63" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>cerrados: si se lo considera habitable hay que preverle conducto.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="62" t="inlineStr"/>
-      <c r="B21" s="63" t="inlineStr"/>
+      <c r="A21" s="60" t="inlineStr"/>
+      <c r="B21" s="61" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>REDONDEOS</t>
         </is>
       </c>
-      <c r="B22" s="62" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>Diferencias menores que no afectan: local 03 da 5,95 m2 y figura 6,0;</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="inlineStr"/>
-      <c r="B23" s="63" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr"/>
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>local 09 da 12,25 y figura 12,3.</t>
         </is>
@@ -4380,592 +4374,592 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr"/>
+      <c r="B1" s="60" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr"/>
-      <c r="B2" s="63" t="inlineStr"/>
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>NORMATIVA</t>
         </is>
       </c>
-      <c r="B3" s="62" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>CIRSOC 201. Hormigon H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200 kg/cm2).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>UNIDADES</t>
         </is>
       </c>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="B4" s="60" t="inlineStr">
         <is>
           <t>Longitudes en m y cm. Cargas en kg/m. Momentos en kgm. Tensiones en kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B5" s="62" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>b = ancho | h = altura util | d = altura total (igual criterio que la planilla de catedra).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="inlineStr"/>
-      <c r="B6" s="63" t="inlineStr"/>
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="62" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B7" s="62" t="inlineStr"/>
+      <c r="B7" s="60" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>Entrepiso PA</t>
         </is>
       </c>
-      <c r="B8" s="63" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>Losa maciza 12 cm 300 + contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="62" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>g = 550 kg/m2       q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="62" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>Azotea</t>
         </is>
       </c>
-      <c r="B10" s="63" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Losa 300 + contrapiso de pendiente 140 + carpeta 42 + aislacion y membrana 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="62" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>g = 560 kg/m2       q = 100 kg/m2 (cubierta no accesible)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>Mamposteria</t>
         </is>
       </c>
-      <c r="B12" s="63" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>250 kg/m2. Altura 2,60 m en PA y 1,00 m de parapeto en azotea.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="62" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>Peso propio</t>
         </is>
       </c>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>2400 kg/m3 x b x d, viga por viga.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="62" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>Carga de calculo</t>
         </is>
       </c>
-      <c r="B14" s="63" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>p = 1,2 (g x B + peso propio + muro) + 1,6 (q x B)        B = ancho tributario</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="62" t="inlineStr"/>
-      <c r="B15" s="63" t="inlineStr"/>
+      <c r="A15" s="60" t="inlineStr"/>
+      <c r="B15" s="61" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>Coeficientes segun esquema (tabla en hoja Datos):</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="62" t="inlineStr"/>
-      <c r="B17" s="63" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Simplemente apoyada   M = pL2/8                    R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="62" t="inlineStr"/>
-      <c r="B18" s="63" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Continua              M = pL2/14   Mapoyo = pL2/10  R = 0,575 pL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="inlineStr"/>
-      <c r="B19" s="63" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr"/>
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Empotrada-apoyada     M = 9pL2/128 Mapoyo = pL2/8   R = 0,625 pL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr"/>
-      <c r="B20" s="63" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Biempotrada           M = pL2/24   Mapoyo = pL2/12  R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="62" t="inlineStr"/>
-      <c r="B21" s="63" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr"/>
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  Voladizo                           Mapoyo = pL2/2   R = 1,000 pL</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="inlineStr"/>
-      <c r="B22" s="63" t="inlineStr"/>
+      <c r="A22" s="60" t="inlineStr"/>
+      <c r="B22" s="61" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>3. FLEXION</t>
         </is>
       </c>
-      <c r="B23" s="62" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>k = M / (phi b h2 f'c)      w = 1 - RAIZ(1 - 2k)      As = w b h f'c / fy</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr"/>
-      <c r="B24" s="63" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr"/>
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>As min = 0,0033 b h       As max = 0,0163 b h (0,75 de la cuantia balanceada)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr"/>
-      <c r="B25" s="63" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr"/>
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>Si la armadura no entra en una capa se disponen dos y el recubrimiento pasa a 6 cm.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="inlineStr"/>
-      <c r="B26" s="63" t="inlineStr"/>
+      <c r="A26" s="60" t="inlineStr"/>
+      <c r="B26" s="61" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="62" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>4. CORTE</t>
         </is>
       </c>
-      <c r="B27" s="62" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>T = R / (b x 0,85 h)       tension tangencial en el apoyo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="inlineStr"/>
-      <c r="B28" s="63" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr"/>
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>Vc = 0,53 RAIZ(f'c) b h        phi Vn = 0,75 (Vc + Av fy h / s)  &gt;=  R</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="62" t="inlineStr"/>
-      <c r="B29" s="63" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr"/>
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>Av = 2 ramas. Se aumenta el diametro antes que cerrar la separacion por debajo de 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="inlineStr"/>
-      <c r="B30" s="63" t="inlineStr"/>
+      <c r="A30" s="60" t="inlineStr"/>
+      <c r="B30" s="61" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="62" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>5. FLECHA</t>
         </is>
       </c>
-      <c r="B31" s="62" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>Altura minima: simplemente apoyada L/16, un extremo continuo L/18,5,</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="inlineStr"/>
-      <c r="B32" s="63" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr"/>
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>ambos extremos continuos L/21, voladizo L/8.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="62" t="inlineStr"/>
-      <c r="B33" s="63" t="inlineStr"/>
+      <c r="A33" s="60" t="inlineStr"/>
+      <c r="B33" s="61" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="62" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>6. VIGAS INVERTIDAS</t>
         </is>
       </c>
-      <c r="B34" s="62" t="inlineStr">
+      <c r="B34" s="60" t="inlineStr">
         <is>
           <t>Las vigas de BORDE son invertidas: sobresalen 70 cm por encima del fondo de</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="62" t="inlineStr"/>
-      <c r="B35" s="63" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr"/>
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>losa (cotas N.F.L +3,50 / N.S.V +4,20 y N.F.L +6,80 / N.S.V +7,50 del plano).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="62" t="inlineStr"/>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr"/>
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>losa. Lo confirman las cotas del plano y el hecho de que el cielorraso sea de</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="62" t="inlineStr"/>
-      <c r="B37" s="63" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr"/>
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>VI 06 mide 14,00 m en total y es el cuarto borde de L07. Sobre su eje hay cuatro</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="62" t="inlineStr"/>
-      <c r="B38" s="63" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr"/>
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>columnas, de modo que trabaja como viga continua de tres tramos de 4,10, 4,32 y</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="62" t="inlineStr"/>
-      <c r="B39" s="63" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr"/>
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>6,53 m. Se calcula con el mayor, 6,53 m, que es el que gobierna.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="62" t="inlineStr"/>
-      <c r="B40" s="63" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr"/>
+      <c r="B40" s="61" t="inlineStr">
         <is>
           <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="62" t="inlineStr"/>
-      <c r="B41" s="63" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr"/>
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="62" t="inlineStr"/>
-      <c r="B42" s="63" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr"/>
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="62" t="inlineStr"/>
-      <c r="B43" s="63" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr"/>
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="62" t="inlineStr"/>
-      <c r="B44" s="63" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr"/>
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="62" t="inlineStr"/>
-      <c r="B45" s="63" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr"/>
+      <c r="B45" s="61" t="inlineStr">
         <is>
           <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="62" t="inlineStr"/>
-      <c r="B46" s="63" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr"/>
+      <c r="B46" s="61" t="inlineStr">
         <is>
           <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="62" t="inlineStr"/>
-      <c r="B47" s="63" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr"/>
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="62" t="inlineStr"/>
-      <c r="B48" s="63" t="inlineStr">
+      <c r="A48" s="60" t="inlineStr"/>
+      <c r="B48" s="61" t="inlineStr">
         <is>
           <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="62" t="inlineStr"/>
-      <c r="B49" s="63" t="inlineStr">
+      <c r="A49" s="60" t="inlineStr"/>
+      <c r="B49" s="61" t="inlineStr">
         <is>
           <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="62" t="inlineStr"/>
-      <c r="B50" s="63" t="inlineStr"/>
+      <c r="A50" s="60" t="inlineStr"/>
+      <c r="B50" s="61" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="62" t="inlineStr">
+      <c r="A51" s="60" t="inlineStr">
         <is>
           <t>7. RESULTADO</t>
         </is>
       </c>
-      <c r="B51" s="62" t="inlineStr">
+      <c r="B51" s="60" t="inlineStr">
         <is>
           <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="62" t="inlineStr"/>
-      <c r="B52" s="63" t="inlineStr">
+      <c r="A52" s="60" t="inlineStr"/>
+      <c r="B52" s="61" t="inlineStr">
         <is>
           <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="62" t="inlineStr"/>
-      <c r="B53" s="63" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr"/>
+      <c r="B53" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="62" t="inlineStr"/>
-      <c r="B54" s="63" t="inlineStr">
+      <c r="A54" s="60" t="inlineStr"/>
+      <c r="B54" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="62" t="inlineStr"/>
-      <c r="B55" s="63" t="inlineStr">
+      <c r="A55" s="60" t="inlineStr"/>
+      <c r="B55" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="62" t="inlineStr"/>
-      <c r="B56" s="63" t="inlineStr">
+      <c r="A56" s="60" t="inlineStr"/>
+      <c r="B56" s="61" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="62" t="inlineStr"/>
-      <c r="B57" s="63" t="inlineStr">
+      <c r="A57" s="60" t="inlineStr"/>
+      <c r="B57" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="62" t="inlineStr"/>
-      <c r="B58" s="63" t="inlineStr">
+      <c r="A58" s="60" t="inlineStr"/>
+      <c r="B58" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="62" t="inlineStr"/>
-      <c r="B59" s="63" t="inlineStr">
+      <c r="A59" s="60" t="inlineStr"/>
+      <c r="B59" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="62" t="inlineStr"/>
-      <c r="B60" s="63" t="inlineStr">
+      <c r="A60" s="60" t="inlineStr"/>
+      <c r="B60" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="62" t="inlineStr"/>
-      <c r="B61" s="63" t="inlineStr">
+      <c r="A61" s="60" t="inlineStr"/>
+      <c r="B61" s="61" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="62" t="inlineStr"/>
-      <c r="B62" s="63" t="inlineStr">
+      <c r="A62" s="60" t="inlineStr"/>
+      <c r="B62" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="62" t="inlineStr"/>
-      <c r="B63" s="63" t="inlineStr"/>
+      <c r="A63" s="60" t="inlineStr"/>
+      <c r="B63" s="61" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="62" t="inlineStr">
+      <c r="A64" s="60" t="inlineStr">
         <is>
           <t>8. ALCANCE</t>
         </is>
       </c>
-      <c r="B64" s="63" t="inlineStr">
+      <c r="B64" s="61" t="inlineStr">
         <is>
           <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="62" t="inlineStr"/>
-      <c r="B65" s="63" t="inlineStr">
+      <c r="A65" s="60" t="inlineStr"/>
+      <c r="B65" s="61" t="inlineStr">
         <is>
           <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="62" t="inlineStr"/>
-      <c r="B66" s="63" t="inlineStr"/>
+      <c r="A66" s="60" t="inlineStr"/>
+      <c r="B66" s="61" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="62" t="inlineStr">
+      <c r="A67" s="60" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B67" s="62" t="inlineStr">
+      <c r="B67" s="60" t="inlineStr">
         <is>
           <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="62" t="inlineStr"/>
-      <c r="B68" s="63" t="inlineStr">
+      <c r="A68" s="60" t="inlineStr"/>
+      <c r="B68" s="61" t="inlineStr">
         <is>
           <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="62" t="inlineStr"/>
-      <c r="B69" s="63" t="inlineStr">
+      <c r="A69" s="60" t="inlineStr"/>
+      <c r="B69" s="61" t="inlineStr">
         <is>
           <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="62" t="inlineStr"/>
-      <c r="B70" s="63" t="inlineStr">
+      <c r="A70" s="60" t="inlineStr"/>
+      <c r="B70" s="61" t="inlineStr">
         <is>
           <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="62" t="inlineStr"/>
-      <c r="B71" s="63" t="inlineStr">
+      <c r="A71" s="60" t="inlineStr"/>
+      <c r="B71" s="61" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -4990,368 +4984,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - LOSAS</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr"/>
+      <c r="B1" s="60" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr"/>
-      <c r="B2" s="63" t="inlineStr"/>
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>METODO</t>
         </is>
       </c>
-      <c r="B3" s="62" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>Tensiones admisibles, igual criterio que la planilla modelo de la catedra.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr"/>
-      <c r="B4" s="63" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr"/>
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>Se verifico contra la fila de ejemplo: momentos y reacciones coinciden exactamente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B5" s="62" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). Tension admisible 2400 kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B6" s="62" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>h = altura util | d = espesor total. Recubrimiento 1,5 cm.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="62" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr"/>
+      <c r="A7" s="60" t="inlineStr"/>
+      <c r="B7" s="61" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q      (cargas de servicio, sin mayorar)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="62" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>Peso propio = 2400 x d / 100, calculado con el espesor propio de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="62" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B10" s="63" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>Terminaciones 242 kg/m2 (contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="62" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B12" s="63" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>Terminaciones 252 kg/m2 (contrapiso pendiente 140 + carpeta 42 + aislacion 50 +</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="62" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr"/>
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>cielorraso 20).  q = 100 kg/m2 (azotea no accesible)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="62" t="inlineStr"/>
-      <c r="B14" s="63" t="inlineStr"/>
+      <c r="A14" s="60" t="inlineStr"/>
+      <c r="B14" s="61" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="62" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>M = coeficiente x p x L2, segun el grado de empotramiento:</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr"/>
-      <c r="B16" s="63" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr"/>
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  1/8 simplemente apoyada    1/10 y 1/14 continua    1/12 biempotrada    1/2 voladizo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="62" t="inlineStr"/>
-      <c r="B17" s="63" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>R = coeficiente x p x L. En voladizo Rx = p x L y Ry no corresponde.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="62" t="inlineStr"/>
-      <c r="B18" s="63" t="inlineStr"/>
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>As = M x 100 / (2400 x 0,9 x h)        [cm2/m]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr"/>
-      <c r="B20" s="63" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>separacion = 100 x area de la barra / As, redondeada, con maximo 20 cm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="62" t="inlineStr"/>
-      <c r="B21" s="63" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr"/>
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>Armadura de reparticion = As / 5, con un minimo de 0,30 cm2/m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="inlineStr"/>
-      <c r="B22" s="63" t="inlineStr"/>
+      <c r="A22" s="60" t="inlineStr"/>
+      <c r="B22" s="61" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>4. ESPESORES</t>
         </is>
       </c>
-      <c r="B23" s="62" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>Los espesores d se leyeron del plano: estan escritos debajo del rotulo de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr"/>
-      <c r="B24" s="63" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr"/>
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>S/PB:  L01 11 | L02 9 | L03 13 | L04 11 | L05 11 | L06 8 | L07 12 | L08 10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr"/>
-      <c r="B25" s="63" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr"/>
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>S/PA:  L09 13 | L10 12</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="inlineStr"/>
-      <c r="B26" s="63" t="inlineStr"/>
+      <c r="A26" s="60" t="inlineStr"/>
+      <c r="B26" s="61" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="62" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>5. LUCES</t>
         </is>
       </c>
-      <c r="B27" s="62" t="inlineStr">
+      <c r="B27" s="60" t="inlineStr">
         <is>
           <t>Relevadas en obra y aportadas por el proyectista. Dos losas son voladizo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="inlineStr"/>
-      <c r="B28" s="63" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr"/>
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>(L02 de 0,80 m y L08 de 0,75 m) y se calculan con M = p L2 / 2.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="62" t="inlineStr"/>
-      <c r="B29" s="63" t="inlineStr"/>
+      <c r="A29" s="60" t="inlineStr"/>
+      <c r="B29" s="61" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>6. LOSAS CRUZADAS</t>
         </is>
       </c>
-      <c r="B30" s="63" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>L07 (4,85 x 5,60) y L10 (4,85 x 6,00) apoyan en los cuatro bordes y su relacion</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="62" t="inlineStr"/>
-      <c r="B31" s="63" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr"/>
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>de lados es menor que 2, por lo que trabajan en las dos direcciones.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="inlineStr"/>
-      <c r="B32" s="63" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr"/>
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>Se reparte la carga por el metodo de Marcus:   kx = ly4 / (lx4 + ly4)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="62" t="inlineStr"/>
-      <c r="B33" s="63" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr"/>
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  L07: ly/lx = 1,15  -&gt;  64% en la direccion corta, 36% en la larga</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="62" t="inlineStr"/>
-      <c r="B34" s="63" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr"/>
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  L10: ly/lx = 1,24  -&gt;  70% en la direccion corta, 30% en la larga</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="62" t="inlineStr"/>
-      <c r="B35" s="63" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr"/>
+      <c r="B35" s="61" t="inlineStr">
         <is>
           <t>Cada una ocupa dos renglones, uno por direccion, con la fraccion de carga que</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="62" t="inlineStr"/>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr"/>
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>le toca ya aplicada en la columna CARGAS. Las dos armaduras se cruzan en obra:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="62" t="inlineStr"/>
-      <c r="B37" s="63" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr"/>
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>la de la direccion corta va abajo, la de la larga arriba de aquella.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="62" t="inlineStr"/>
-      <c r="B38" s="63" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr"/>
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>La columna auxiliar luz transv. es la que dispara el reparto: si se borra, la</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="62" t="inlineStr"/>
-      <c r="B39" s="63" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr"/>
+      <c r="B39" s="61" t="inlineStr">
         <is>
           <t>fila vuelve a calcularse como losa armada en una direccion.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="62" t="inlineStr"/>
-      <c r="B40" s="63" t="inlineStr"/>
+      <c r="A40" s="60" t="inlineStr"/>
+      <c r="B40" s="61" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="62" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B41" s="62" t="inlineStr">
+      <c r="B41" s="60" t="inlineStr">
         <is>
           <t>El grado de empotramiento esta cargado en 1/8 salvo los dos voladizos (1/2). Si</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="62" t="inlineStr"/>
-      <c r="B42" s="63" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr"/>
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>alguna losa es continua sobre una viga corresponde 1/10 o 1/14: corregir en la columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="62" t="inlineStr"/>
-      <c r="B43" s="63" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr"/>
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>El diagrama de cargas es una imagen fija: si cambias el grado, cambialo a mano.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="62" t="inlineStr"/>
-      <c r="B44" s="63" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr"/>
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -5376,384 +5370,384 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="inlineStr">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - COLUMNAS</t>
         </is>
       </c>
-      <c r="B1" s="62" t="inlineStr"/>
+      <c r="B1" s="60" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="inlineStr"/>
-      <c r="B2" s="63" t="inlineStr"/>
+      <c r="A2" s="60" t="inlineStr"/>
+      <c r="B2" s="61" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B3" s="62" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). phi compresion 0,65.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="inlineStr"/>
-      <c r="B4" s="63" t="inlineStr"/>
+      <c r="A4" s="60" t="inlineStr"/>
+      <c r="B4" s="61" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>1. RELEVAMIENTO</t>
         </is>
       </c>
-      <c r="B5" s="62" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>Las columnas se identificaron en el plano cruzando el rotulo COL con un rectangulo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="inlineStr"/>
-      <c r="B6" s="63" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr"/>
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>de la misma seccion a menos de 26 pt. Resultaron 9 en PB y 4 en PA.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="62" t="inlineStr"/>
-      <c r="B7" s="63" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr"/>
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>Las 4 de PA caen exactamente sobre C6, C7, C8 y C9 de PB, y ademas tienen la misma</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="62" t="inlineStr"/>
-      <c r="B8" s="63" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr"/>
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>seccion, lo que confirma que la correspondencia entre plantas es correcta.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="62" t="inlineStr"/>
-      <c r="B9" s="63" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr"/>
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>La C01 de 10x10 esta confirmada por el proyectista aunque el computo metrico no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="62" t="inlineStr"/>
-      <c r="B10" s="63" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr"/>
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>la incluya en su item 4.1.3: ese computo esta incompleto en ese punto.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="62" t="inlineStr"/>
-      <c r="B11" s="63" t="inlineStr"/>
+      <c r="A11" s="60" t="inlineStr"/>
+      <c r="B11" s="61" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="62" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>2. ALTURAS</t>
         </is>
       </c>
-      <c r="B12" s="62" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>PB 3,15 m y PA 3,22 m, los mismos valores de la planilla de la catedra, coherentes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="62" t="inlineStr"/>
-      <c r="B13" s="63" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr"/>
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>con los niveles del plano (N.F.L +3,50 del entrepiso y +6,80 del techo).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="62" t="inlineStr"/>
-      <c r="B14" s="63" t="inlineStr"/>
+      <c r="A14" s="60" t="inlineStr"/>
+      <c r="B14" s="61" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="62" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
         <is>
           <t>As = 0,008 x area (cuantia minima, el mismo criterio de la planilla modelo).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="62" t="inlineStr"/>
-      <c r="B16" s="63" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr"/>
+      <c r="B16" s="61" t="inlineStr">
         <is>
           <t>Se adoptan 4 barras del 12 en todas: 4,52 cm2, que cubre la minima en toda seccion.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="62" t="inlineStr"/>
-      <c r="B17" s="63" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr"/>
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. long. ; 48 x diam. estribo ; lado menor),</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="62" t="inlineStr"/>
-      <c r="B18" s="63" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr"/>
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>redondeada hacia abajo a multiplo de 5. Para 4d12 con estribo d6 da 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="62" t="inlineStr"/>
-      <c r="B19" s="63" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr"/>
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>La planilla de la catedra adopta 20 cm: ese valor supera el limite reglamentario.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="62" t="inlineStr"/>
-      <c r="B20" s="63" t="inlineStr"/>
+      <c r="A20" s="60" t="inlineStr"/>
+      <c r="B20" s="61" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="62" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>4. CAPACIDAD</t>
         </is>
       </c>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]     (columna zunchada con estribos)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="62" t="inlineStr"/>
-      <c r="B22" s="63" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr"/>
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  15x30 con 4d12 -&gt; 51,2 t        20x20 con 4d12 -&gt; 46,6 t</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="inlineStr"/>
-      <c r="B23" s="63" t="inlineStr"/>
+      <c r="A23" s="60" t="inlineStr"/>
+      <c r="B23" s="61" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="62" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>5. CARGAS</t>
         </is>
       </c>
-      <c r="B24" s="62" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>La columna CARGA (t) viene cargada con una bajada automatica: suma de las</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="62" t="inlineStr"/>
-      <c r="B25" s="63" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr"/>
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>reacciones de las vigas que apoyan en cada columna (tomadas de la planilla de</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="62" t="inlineStr"/>
-      <c r="B26" s="63" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr"/>
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>vigas), mas el peso propio, mas lo que baja de la columna del nivel superior.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="62" t="inlineStr"/>
-      <c r="B27" s="63" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr"/>
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>ES UNA CARGA PROVISORIA Y ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="62" t="inlineStr"/>
-      <c r="B28" s="63" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr"/>
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>de viga no pudieron asignarse a ninguna columna porque apoyan en otra viga, en</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="62" t="inlineStr"/>
-      <c r="B29" s="63" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr"/>
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>un tabique o en la medianera, y esas reacciones no estan sumadas.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="62" t="inlineStr"/>
-      <c r="B30" s="63" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr"/>
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>Para cerrarla hay que indicar, para cada uno de esos 20 extremos, en que apoya.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="62" t="inlineStr"/>
-      <c r="B31" s="63" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr"/>
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>Mientras tanto la columna es editable: al corregir un valor todo recalcula.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="62" t="inlineStr"/>
-      <c r="B32" s="63" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr"/>
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="62" t="inlineStr"/>
-      <c r="B33" s="63" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr"/>
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="62" t="inlineStr"/>
-      <c r="B34" s="63" t="inlineStr"/>
+      <c r="A34" s="60" t="inlineStr"/>
+      <c r="B34" s="61" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="62" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>6. ESBELTEZ</t>
         </is>
       </c>
-      <c r="B35" s="62" t="inlineStr">
+      <c r="B35" s="60" t="inlineStr">
         <is>
           <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="62" t="inlineStr"/>
-      <c r="B36" s="63" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr"/>
+      <c r="B36" s="61" t="inlineStr">
         <is>
           <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="62" t="inlineStr"/>
-      <c r="B37" s="63" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr"/>
+      <c r="B37" s="61" t="inlineStr">
         <is>
           <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="62" t="inlineStr"/>
-      <c r="B38" s="63" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr"/>
+      <c r="B38" s="61" t="inlineStr">
         <is>
           <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="62" t="inlineStr"/>
-      <c r="B39" s="63" t="inlineStr"/>
+      <c r="A39" s="60" t="inlineStr"/>
+      <c r="B39" s="61" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="62" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>7. LA DE 10x10</t>
         </is>
       </c>
-      <c r="B40" s="62" t="inlineStr">
+      <c r="B40" s="60" t="inlineStr">
         <is>
           <t>Existe, confirmada por el proyectista, y el computo metrico la omite. Con 10 cm</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="62" t="inlineStr"/>
-      <c r="B41" s="63" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr"/>
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>de lado y 3,15 m de altura su esbeltez es k lu / r = 105, tres veces el limite</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="62" t="inlineStr"/>
-      <c r="B42" s="63" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr"/>
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>por debajo del cual se puede despreciar el pandeo, y su capacidad es de 18,7 t</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="62" t="inlineStr"/>
-      <c r="B43" s="63" t="inlineStr">
+      <c r="A43" s="60" t="inlineStr"/>
+      <c r="B43" s="61" t="inlineStr">
         <is>
           <t>contra los 51 de una 15x30. Es el punto mas delicado del conjunto: conviene</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="62" t="inlineStr"/>
-      <c r="B44" s="63" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr"/>
+      <c r="B44" s="61" t="inlineStr">
         <is>
           <t>verificarla a segundo orden en serio, no con la formula de compresion simple.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="62" t="inlineStr"/>
-      <c r="B45" s="63" t="inlineStr"/>
+      <c r="A45" s="60" t="inlineStr"/>
+      <c r="B45" s="61" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="62" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B46" s="62" t="inlineStr">
+      <c r="B46" s="60" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="62" t="inlineStr"/>
-      <c r="B47" s="63" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr"/>
+      <c r="B47" s="61" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="62" t="inlineStr"/>
-      <c r="B48" s="63" t="inlineStr">
+      <c r="A48" s="60" t="inlineStr"/>
+      <c r="B48" s="61" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>
@@ -5781,7 +5775,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION - inventario. Calculo pendiente: va despues de columnas.</t>
         </is>
@@ -5923,7 +5917,7 @@
       <c r="D9" s="11" t="n">
         <v>533</v>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>Ancho cortado en el PDF: confirmar 20 o 22 cm</t>
         </is>
@@ -5989,7 +5983,7 @@
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="65" t="inlineStr">
+      <c r="E13" s="63" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -6004,7 +5998,7 @@
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="65" t="inlineStr">
+      <c r="E14" s="63" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -6206,7 +6200,7 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="65" t="inlineStr">
+      <c r="E26" s="63" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -17055,7 +17049,9 @@
           <t>T9</t>
         </is>
       </c>
-      <c r="C12" s="42" t="n"/>
+      <c r="C12" s="8" t="n">
+        <v>6.96</v>
+      </c>
       <c r="D12" s="8" t="n">
         <v>3.2</v>
       </c>
@@ -17103,7 +17099,7 @@
       </c>
       <c r="Q12" s="13" t="inlineStr">
         <is>
-          <t>Falta la carga: no figura en la planilla de la catedra.</t>
+          <t>Recibe el extremo de VI 14. Carga mayorada.</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17110,9 @@
           <t>T10</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n"/>
+      <c r="C13" s="8" t="n">
+        <v>13.38</v>
+      </c>
       <c r="D13" s="8" t="n">
         <v>2.6</v>
       </c>
@@ -17162,7 +17160,7 @@
       </c>
       <c r="Q13" s="13" t="inlineStr">
         <is>
-          <t>Falta la carga: no figura en la planilla de la catedra.</t>
+          <t>Recibe el extremo de VI 12. Carga mayorada.</t>
         </is>
       </c>
     </row>
@@ -17173,7 +17171,9 @@
           <t>T11</t>
         </is>
       </c>
-      <c r="C14" s="42" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>5.07</v>
+      </c>
       <c r="D14" s="8" t="n">
         <v>2.6</v>
       </c>
@@ -17221,7 +17221,7 @@
       </c>
       <c r="Q14" s="13" t="inlineStr">
         <is>
-          <t>Longitud muy corta: verificar si es tabique o el machon de una abertura. Falta la carga: no figura en la planilla de la catedra.</t>
+          <t>Recibe el extremo de VI 13b sobre solo 28 cm de largo: es el tabique con mayor tension del conjunto.</t>
         </is>
       </c>
     </row>
@@ -17232,7 +17232,9 @@
           <t>T12</t>
         </is>
       </c>
-      <c r="C15" s="42" t="n"/>
+      <c r="C15" s="8" t="n">
+        <v>6.93</v>
+      </c>
       <c r="D15" s="8" t="n">
         <v>2.6</v>
       </c>
@@ -17280,7 +17282,7 @@
       </c>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>Longitud muy corta: verificar si es tabique o el machon de una abertura. Falta la carga: no figura en la planilla de la catedra.</t>
+          <t>Recibe los extremos de VI 17 (1,31 t) y VI 15b (5,62 t) sobre 32 cm de largo.</t>
         </is>
       </c>
     </row>
@@ -17291,7 +17293,9 @@
           <t>T13</t>
         </is>
       </c>
-      <c r="C16" s="43" t="n"/>
+      <c r="C16" s="15" t="n">
+        <v>1.22</v>
+      </c>
       <c r="D16" s="15" t="n">
         <v>3.2</v>
       </c>
@@ -17339,7 +17343,7 @@
       </c>
       <c r="Q16" s="20" t="inlineStr">
         <is>
-          <t>Falta la carga: no figura en la planilla de la catedra.</t>
+          <t>No recibe vigas: es la continuidad del tabique T06c de planta baja. La carga indicada es solo su peso propio; lo que baje de arriba se suma a T06c.</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17367,7 @@
       <c r="Q17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>T1 a T6: cargas y dimensiones tomadas de la planilla de la catedra. Probablemente sean cargas de servicio; compararlas contra fi Pn, que es resistencia ultima, queda del lado inseguro en torno a un 40 por ciento. Con utilizaciones del 10 al 20 por ciento no cambia ningun veredicto, pero conviene saberlo.</t>
         </is>
@@ -17386,7 +17390,7 @@
       <c r="Q18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="A19" s="42" t="inlineStr">
         <is>
           <t>T7 y T8: carga tomada de la reaccion de VI 02 y VI 11a en la planilla de vigas, que son MAYORADAS. El criterio no es el mismo que en T1 a T6.</t>
         </is>
@@ -17409,9 +17413,9 @@
       <c r="Q19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>T9 a T13: dimensiones del computo metrico; la carga todavia no esta definida.</t>
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>T9 a T13: dimensiones del computo metrico. Las cargas son las reacciones de las vigas de techo que apoyan en cada uno, aportadas por el proyectista: T9 recibe VI 14, T10 recibe VI 12, T11 recibe VI 13b y T12 recibe VI 17 mas VI 15b. T13 no recibe vigas: continua el tabique T06c de planta baja.</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -17432,7 +17436,7 @@
       <c r="Q20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>Area: si B es menor o igual al espesor el tabique es recto y el area es A x B; si no, es un tabique en L y el area es (A + B - espesor) x espesor.</t>
         </is>
@@ -17455,7 +17459,7 @@
       <c r="Q21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="42" t="inlineStr">
         <is>
           <t>fi Pn = 0,55 x 0,65 x f'c x area x [1 - (altura / 32 espesor)^2]   muro portante de hormigon armado con reduccion por esbeltez.</t>
         </is>
@@ -17478,7 +17482,7 @@
       <c r="Q22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="A23" s="42" t="inlineStr">
         <is>
           <t>Armadura vertical en doble malla y horizontal en malla simple, ambas o8 c/20, iguales a las de la planilla de la catedra.</t>
         </is>
@@ -17549,7 +17553,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - HIPOTESIS DE CALCULO</t>
         </is>
@@ -17561,7 +17565,7 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
         </is>
@@ -17581,17 +17585,17 @@
       <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -17601,12 +17605,12 @@
       <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="47" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -17619,12 +17623,12 @@
       <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="47" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -17637,12 +17641,12 @@
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -17655,12 +17659,12 @@
       <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>phi flexion</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -17673,12 +17677,12 @@
       <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>phi corte</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="47" t="n">
         <v>0.75</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -17691,12 +17695,12 @@
       <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Coef. mayoracion permanente</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="47" t="n">
         <v>1.2</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -17709,12 +17713,12 @@
       <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Coef. mayoracion sobrecarga</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="47" t="n">
         <v>1.6</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -17735,7 +17739,7 @@
       <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>PAQUETES DE CARGA</t>
         </is>
@@ -17767,21 +17771,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="48" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B14" s="51" t="n">
+      <c r="B14" s="49" t="n">
         <v>550</v>
       </c>
-      <c r="C14" s="51" t="n">
+      <c r="C14" s="49" t="n">
         <v>200</v>
       </c>
-      <c r="D14" s="52" t="n">
+      <c r="D14" s="50" t="n">
         <v>2.6</v>
       </c>
-      <c r="E14" s="52" t="n">
+      <c r="E14" s="50" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="32" t="inlineStr">
@@ -17791,21 +17795,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="48" t="inlineStr">
         <is>
           <t>TECHO</t>
         </is>
       </c>
-      <c r="B15" s="51" t="n">
+      <c r="B15" s="49" t="n">
         <v>560</v>
       </c>
-      <c r="C15" s="51" t="n">
+      <c r="C15" s="49" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="52" t="n">
+      <c r="D15" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="52" t="n">
+      <c r="E15" s="50" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="32" t="inlineStr">
@@ -17815,12 +17819,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="48" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>Mamposteria sobre viga</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="47" t="n">
         <v>250</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -17830,7 +17834,7 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="53" t="inlineStr">
+      <c r="F16" s="51" t="inlineStr">
         <is>
           <t>Ladrillo hueco 18 cm + revoque en ambas caras</t>
         </is>
@@ -17845,7 +17849,7 @@
       <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>COEFICIENTES SEGUN ESQUEMA</t>
         </is>
@@ -17873,101 +17877,101 @@
       <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="48" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
-      <c r="B19" s="54" t="n">
+      <c r="B19" s="52" t="n">
         <v>0.125</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="54" t="n">
+      <c r="D19" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" s="55" t="n">
+      <c r="E19" s="53" t="n">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="48" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
-      <c r="B20" s="54" t="n">
+      <c r="B20" s="52" t="n">
         <v>0.07142999999999999</v>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="52" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="54" t="n">
+      <c r="D20" s="52" t="n">
         <v>0.575</v>
       </c>
-      <c r="E20" s="55" t="n">
+      <c r="E20" s="53" t="n">
         <v>21</v>
       </c>
       <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Empotrada-apoyada</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n">
+      <c r="B21" s="52" t="n">
         <v>0.07031</v>
       </c>
-      <c r="C21" s="54" t="n">
+      <c r="C21" s="52" t="n">
         <v>0.125</v>
       </c>
-      <c r="D21" s="54" t="n">
+      <c r="D21" s="52" t="n">
         <v>0.625</v>
       </c>
-      <c r="E21" s="55" t="n">
+      <c r="E21" s="53" t="n">
         <v>18.5</v>
       </c>
       <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="46" t="inlineStr">
         <is>
           <t>Biempotrada</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n">
+      <c r="B22" s="52" t="n">
         <v>0.04167</v>
       </c>
-      <c r="C22" s="54" t="n">
+      <c r="C22" s="52" t="n">
         <v>0.08333</v>
       </c>
-      <c r="D22" s="54" t="n">
+      <c r="D22" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="E22" s="55" t="n">
+      <c r="E22" s="53" t="n">
         <v>21</v>
       </c>
       <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="48" t="inlineStr">
+      <c r="A23" s="46" t="inlineStr">
         <is>
           <t>Voladizo</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n">
+      <c r="B23" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="54" t="n">
+      <c r="C23" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="D23" s="54" t="n">
+      <c r="D23" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="55" t="n">
+      <c r="E23" s="53" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -18015,7 +18019,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - LOSAS</t>
         </is>
@@ -18025,7 +18029,7 @@
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="44" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
         </is>
@@ -18041,17 +18045,17 @@
       <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>MATERIALES Y METODO</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>unidad</t>
         </is>
@@ -18059,12 +18063,12 @@
       <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n">
+      <c r="B5" s="47" t="n">
         <v>210</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -18075,12 +18079,12 @@
       <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
         </is>
       </c>
-      <c r="B6" s="49" t="n">
+      <c r="B6" s="47" t="n">
         <v>4200</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -18091,12 +18095,12 @@
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Tension admisible del acero</t>
         </is>
       </c>
-      <c r="B7" s="49" t="n">
+      <c r="B7" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -18107,12 +18111,12 @@
       <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Brazo elastico  z / h</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="47" t="n">
         <v>0.9</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -18123,12 +18127,12 @@
       <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
         </is>
       </c>
-      <c r="B9" s="49" t="n">
+      <c r="B9" s="47" t="n">
         <v>2400</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -18139,12 +18143,12 @@
       <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Recubrimiento</t>
         </is>
       </c>
-      <c r="B10" s="49" t="n">
+      <c r="B10" s="47" t="n">
         <v>1.5</v>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -18155,12 +18159,12 @@
       <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Separacion maxima</t>
         </is>
       </c>
-      <c r="B11" s="49" t="n">
+      <c r="B11" s="47" t="n">
         <v>20</v>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -18171,12 +18175,12 @@
       <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Armadura de reparticion</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="47" t="n">
         <v>0.2</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -18187,12 +18191,12 @@
       <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="46" t="inlineStr">
         <is>
           <t>Reparticion minima</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -18209,7 +18213,7 @@
       <c r="D14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>CARGAS POR NIVEL</t>
         </is>
@@ -18231,15 +18235,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
+      <c r="A16" s="48" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="47" t="n">
         <v>242</v>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="47" t="n">
         <v>200</v>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -18249,15 +18253,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="inlineStr">
+      <c r="A17" s="48" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B17" s="49" t="n">
+      <c r="B17" s="47" t="n">
         <v>252</v>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="47" t="n">
         <v>100</v>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -18283,7 +18287,7 @@
       <c r="D19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>GRADO DE EMPOTRAMIENTO</t>
         </is>
@@ -18305,90 +18309,90 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="56" t="inlineStr">
+      <c r="A21" s="54" t="inlineStr">
         <is>
           <t>1/8</t>
         </is>
       </c>
-      <c r="B21" s="54" t="n">
+      <c r="B21" s="52" t="n">
         <v>0.125</v>
       </c>
-      <c r="C21" s="57" t="n">
+      <c r="C21" s="55" t="n">
         <v>0.5</v>
       </c>
-      <c r="D21" s="58" t="inlineStr">
+      <c r="D21" s="56" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="56" t="inlineStr">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="B22" s="54" t="n">
+      <c r="B22" s="52" t="n">
         <v>0.1</v>
       </c>
-      <c r="C22" s="57" t="n">
+      <c r="C22" s="55" t="n">
         <v>0.55</v>
       </c>
-      <c r="D22" s="58" t="inlineStr">
+      <c r="D22" s="56" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="56" t="inlineStr">
+      <c r="A23" s="54" t="inlineStr">
         <is>
           <t>1/12</t>
         </is>
       </c>
-      <c r="B23" s="54" t="n">
+      <c r="B23" s="52" t="n">
         <v>0.0833</v>
       </c>
-      <c r="C23" s="57" t="n">
+      <c r="C23" s="55" t="n">
         <v>0.5</v>
       </c>
-      <c r="D23" s="58" t="inlineStr">
+      <c r="D23" s="56" t="inlineStr">
         <is>
           <t>Biempotrada</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="56" t="inlineStr">
+      <c r="A24" s="54" t="inlineStr">
         <is>
           <t>1/14</t>
         </is>
       </c>
-      <c r="B24" s="54" t="n">
+      <c r="B24" s="52" t="n">
         <v>0.07140000000000001</v>
       </c>
-      <c r="C24" s="57" t="n">
+      <c r="C24" s="55" t="n">
         <v>0.575</v>
       </c>
-      <c r="D24" s="58" t="inlineStr">
+      <c r="D24" s="56" t="inlineStr">
         <is>
           <t>Continua</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="56" t="inlineStr">
+      <c r="A25" s="54" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
-      <c r="B25" s="54" t="n">
+      <c r="B25" s="52" t="n">
         <v>0.5</v>
       </c>
-      <c r="C25" s="57" t="n">
+      <c r="C25" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="58" t="inlineStr">
+      <c r="D25" s="56" t="inlineStr">
         <is>
           <t>Voladizo</t>
         </is>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>21.12</v>
+        <v>22.43</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3.15</v>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="Q10" s="13" t="inlineStr">
         <is>
-          <t>Carga tomada de la reaccion de VI 02 en la planilla de vigas, MAYORADA. No es comparable sin mas con las de T1 a T6.</t>
+          <t>Recibe los extremos de VI 02 (21,12 t) y de VI 17 (1,31 t). Cargas MAYORADAS, no comparables sin mas con las de T1 a T6. Es el tabique mas exigido del conjunto.</t>
         </is>
       </c>
     </row>
@@ -17233,7 +17233,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>6.93</v>
+        <v>5.62</v>
       </c>
       <c r="D15" s="8" t="n">
         <v>2.6</v>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>Recibe los extremos de VI 17 (1,31 t) y VI 15b (5,62 t) sobre 32 cm de largo.</t>
+          <t>A REVISAR. Se le deja solo VI 15b. El proyectista indica que VI 17 no descarga aqui sino en T07, y que T12 acompana a VI 17 en toda su longitud, o sea que va encima de la viga y no debajo. Falta definir si lo mismo vale para T9, T10, T11 y T13.</t>
         </is>
       </c>
     </row>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -16391,7 +16391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -17282,7 +17282,7 @@
       </c>
       <c r="Q15" s="13" t="inlineStr">
         <is>
-          <t>A REVISAR. Se le deja solo VI 15b. El proyectista indica que VI 17 no descarga aqui sino en T07, y que T12 acompana a VI 17 en toda su longitud, o sea que va encima de la viga y no debajo. Falta definir si lo mismo vale para T9, T10, T11 y T13.</t>
+          <t>Recibe el extremo de VI 15b. VI 17 no descarga aqui sino en T07. T12 acompana a VI 17 en toda su longitud por debajo, de modo que esa viga esta mas sostenida de lo que supone el calculo: queda del lado seguro.</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17415,7 @@
     <row r="20">
       <c r="A20" s="42" t="inlineStr">
         <is>
-          <t>T9 a T13: dimensiones del computo metrico. Las cargas son las reacciones de las vigas de techo que apoyan en cada uno, aportadas por el proyectista: T9 recibe VI 14, T10 recibe VI 12, T11 recibe VI 13b y T12 recibe VI 17 mas VI 15b. T13 no recibe vigas: continua el tabique T06c de planta baja.</t>
+          <t>Direccion de la carga: como todas las vigas son invertidas, sobresalen 70 cm por encima del fondo de losa, mientras que los tabiques de planta alta llegan desde el piso hasta ese fondo. El tabique queda debajo y sostiene a la viga, no al reves.</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -17438,7 +17438,7 @@
     <row r="21">
       <c r="A21" s="42" t="inlineStr">
         <is>
-          <t>Area: si B es menor o igual al espesor el tabique es recto y el area es A x B; si no, es un tabique en L y el area es (A + B - espesor) x espesor.</t>
+          <t>T9 a T13: dimensiones del computo metrico. Las cargas son las reacciones de las vigas de techo que apoyan en cada uno, aportadas por el proyectista: T9 recibe VI 14, T10 recibe VI 12, T11 recibe VI 13b y T12 recibe VI 17 mas VI 15b. T13 no recibe vigas: continua el tabique T06c de planta baja.</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -17461,7 +17461,7 @@
     <row r="22">
       <c r="A22" s="42" t="inlineStr">
         <is>
-          <t>fi Pn = 0,55 x 0,65 x f'c x area x [1 - (altura / 32 espesor)^2]   muro portante de hormigon armado con reduccion por esbeltez.</t>
+          <t>Area: si B es menor o igual al espesor el tabique es recto y el area es A x B; si no, es un tabique en L y el area es (A + B - espesor) x espesor.</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
@@ -17484,7 +17484,7 @@
     <row r="23">
       <c r="A23" s="42" t="inlineStr">
         <is>
-          <t>Armadura vertical en doble malla y horizontal en malla simple, ambas o8 c/20, iguales a las de la planilla de la catedra.</t>
+          <t>fi Pn = 0,55 x 0,65 x f'c x area x [1 - (altura / 32 espesor)^2]   muro portante de hormigon armado con reduccion por esbeltez.</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
@@ -17503,6 +17503,29 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Armadura vertical en doble malla y horizontal en malla simple, ambas o8 c/20, iguales a las de la planilla de la catedra.</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -6371,7 +6371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF34"/>
+  <dimension ref="A1:AH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6403,9 +6403,11 @@
     <col width="8" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
+    <col width="7" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6445,6 +6447,8 @@
       <c r="AD1" s="2" t="n"/>
       <c r="AE1" s="2" t="n"/>
       <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -6539,6 +6543,8 @@
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n"/>
+      <c r="AG2" s="4" t="n"/>
+      <c r="AH2" s="4" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="4" t="n"/>
@@ -6660,15 +6666,25 @@
       </c>
       <c r="AD3" s="5" t="inlineStr">
         <is>
+          <t>P punt. (kg)</t>
+        </is>
+      </c>
+      <c r="AE3" s="5" t="inlineStr">
+        <is>
+          <t>a (m)</t>
+        </is>
+      </c>
+      <c r="AF3" s="5" t="inlineStr">
+        <is>
           <t>B trib.</t>
         </is>
       </c>
-      <c r="AE3" s="5" t="inlineStr">
+      <c r="AG3" s="5" t="inlineStr">
         <is>
           <t>h muro</t>
         </is>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
+      <c r="AH3" s="5" t="inlineStr">
         <is>
           <t>rec.</t>
         </is>
@@ -6689,12 +6705,12 @@
         <v>9.9</v>
       </c>
       <c r="D4" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD4+Datos_vigas!$B$7*J4*L4/10000+Datos_vigas!$B$16*AE4)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD4)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF4+Datos_vigas!$B$7*J4*L4/10000+Datos_vigas!$B$16*AG4)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF4)</f>
         <v/>
       </c>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="24">
-        <f>VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,4,0)*D4*C4</f>
+        <f>VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,4,0)*D4*C4+IF(OR(AD4="",AE4=""),0,AD4*MAX(AE4,C4-AE4)/C4)</f>
         <v/>
       </c>
       <c r="G4" s="24">
@@ -6702,18 +6718,18 @@
         <v/>
       </c>
       <c r="H4" s="24">
-        <f>VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,2,0)*D4*C4^2</f>
+        <f>VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,2,0)*D4*C4^2+0.75*1000*IF(OR(AD4="",AE4=""),0,AD4*AE4*(C4-AE4)/C4/1000)</f>
         <v/>
       </c>
       <c r="I4" s="24">
-        <f>IF(VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,3,0)*D4*C4^2)</f>
+        <f>IF(VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y4,Datos_vigas!$A$19:$E$23,3,0)*D4*C4^2+0.50*1000*IF(OR(AD4="",AE4=""),0,AD4*AE4*(C4-AE4)/C4/1000))</f>
         <v/>
       </c>
       <c r="J4" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K4" s="11">
-        <f>L4-AF4</f>
+        <f>L4-AH4</f>
         <v/>
       </c>
       <c r="L4" s="10" t="n">
@@ -6783,13 +6799,15 @@
         <f>IF(Z4="Invertida",MIN(C4*100/4,J4+16*AA4),J4)</f>
         <v/>
       </c>
-      <c r="AD4" s="10" t="n">
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" s="10" t="n">
+      <c r="AG4" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF4" s="10" t="n">
+      <c r="AH4" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6804,12 +6822,12 @@
         <v>3.95</v>
       </c>
       <c r="D5" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD5+Datos_vigas!$B$7*J5*L5/10000+Datos_vigas!$B$16*AE5)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD5)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF5+Datos_vigas!$B$7*J5*L5/10000+Datos_vigas!$B$16*AG5)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF5)</f>
         <v/>
       </c>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="24">
-        <f>VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,4,0)*D5*C5</f>
+        <f>VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,4,0)*D5*C5+IF(OR(AD5="",AE5=""),0,AD5*MAX(AE5,C5-AE5)/C5)</f>
         <v/>
       </c>
       <c r="G5" s="24">
@@ -6817,18 +6835,18 @@
         <v/>
       </c>
       <c r="H5" s="24">
-        <f>VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,2,0)*D5*C5^2</f>
+        <f>VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,2,0)*D5*C5^2+0.75*1000*IF(OR(AD5="",AE5=""),0,AD5*AE5*(C5-AE5)/C5/1000)</f>
         <v/>
       </c>
       <c r="I5" s="24">
-        <f>IF(VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,3,0)*D5*C5^2)</f>
+        <f>IF(VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y5,Datos_vigas!$A$19:$E$23,3,0)*D5*C5^2+0.50*1000*IF(OR(AD5="",AE5=""),0,AD5*AE5*(C5-AE5)/C5/1000))</f>
         <v/>
       </c>
       <c r="J5" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K5" s="11">
-        <f>L5-AF5</f>
+        <f>L5-AH5</f>
         <v/>
       </c>
       <c r="L5" s="10" t="n">
@@ -6898,13 +6916,15 @@
         <f>IF(Z5="Invertida",MIN(C5*100/4,J5+16*AA5),J5)</f>
         <v/>
       </c>
-      <c r="AD5" s="10" t="n">
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n"/>
+      <c r="AF5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE5" s="10" t="n">
+      <c r="AG5" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF5" s="10" t="n">
+      <c r="AH5" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6919,12 +6939,12 @@
         <v>9.880000000000001</v>
       </c>
       <c r="D6" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD6+Datos_vigas!$B$7*J6*L6/10000+Datos_vigas!$B$16*AE6)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD6)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF6+Datos_vigas!$B$7*J6*L6/10000+Datos_vigas!$B$16*AG6)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF6)</f>
         <v/>
       </c>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="24">
-        <f>VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,4,0)*D6*C6</f>
+        <f>VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,4,0)*D6*C6+IF(OR(AD6="",AE6=""),0,AD6*MAX(AE6,C6-AE6)/C6)</f>
         <v/>
       </c>
       <c r="G6" s="24">
@@ -6932,18 +6952,18 @@
         <v/>
       </c>
       <c r="H6" s="24">
-        <f>VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,2,0)*D6*C6^2</f>
+        <f>VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,2,0)*D6*C6^2+0.75*1000*IF(OR(AD6="",AE6=""),0,AD6*AE6*(C6-AE6)/C6/1000)</f>
         <v/>
       </c>
       <c r="I6" s="24">
-        <f>IF(VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,3,0)*D6*C6^2)</f>
+        <f>IF(VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y6,Datos_vigas!$A$19:$E$23,3,0)*D6*C6^2+0.50*1000*IF(OR(AD6="",AE6=""),0,AD6*AE6*(C6-AE6)/C6/1000))</f>
         <v/>
       </c>
       <c r="J6" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K6" s="11">
-        <f>L6-AF6</f>
+        <f>L6-AH6</f>
         <v/>
       </c>
       <c r="L6" s="10" t="n">
@@ -7013,13 +7033,15 @@
         <f>IF(Z6="Invertida",MIN(C6*100/4,J6+16*AA6),J6)</f>
         <v/>
       </c>
-      <c r="AD6" s="10" t="n">
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n">
         <v>2.689</v>
       </c>
-      <c r="AE6" s="10" t="n">
+      <c r="AG6" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF6" s="10" t="n">
+      <c r="AH6" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7034,12 +7056,12 @@
         <v>3.75</v>
       </c>
       <c r="D7" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD7+Datos_vigas!$B$7*J7*L7/10000+Datos_vigas!$B$16*AE7)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD7)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF7+Datos_vigas!$B$7*J7*L7/10000+Datos_vigas!$B$16*AG7)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF7)</f>
         <v/>
       </c>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="24">
-        <f>VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,4,0)*D7*C7</f>
+        <f>VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,4,0)*D7*C7+IF(OR(AD7="",AE7=""),0,AD7*MAX(AE7,C7-AE7)/C7)</f>
         <v/>
       </c>
       <c r="G7" s="24">
@@ -7047,18 +7069,18 @@
         <v/>
       </c>
       <c r="H7" s="24">
-        <f>VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,2,0)*D7*C7^2</f>
+        <f>VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,2,0)*D7*C7^2+0.75*1000*IF(OR(AD7="",AE7=""),0,AD7*AE7*(C7-AE7)/C7/1000)</f>
         <v/>
       </c>
       <c r="I7" s="24">
-        <f>IF(VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,3,0)*D7*C7^2)</f>
+        <f>IF(VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y7,Datos_vigas!$A$19:$E$23,3,0)*D7*C7^2+0.50*1000*IF(OR(AD7="",AE7=""),0,AD7*AE7*(C7-AE7)/C7/1000))</f>
         <v/>
       </c>
       <c r="J7" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K7" s="11">
-        <f>L7-AF7</f>
+        <f>L7-AH7</f>
         <v/>
       </c>
       <c r="L7" s="10" t="n">
@@ -7124,13 +7146,15 @@
         <f>IF(Z7="Invertida",MIN(C7*100/4,J7+16*AA7),J7)</f>
         <v/>
       </c>
-      <c r="AD7" s="10" t="n">
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE7" s="10" t="n">
+      <c r="AG7" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF7" s="10" t="n">
+      <c r="AH7" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7145,12 +7169,12 @@
         <v>3.75</v>
       </c>
       <c r="D8" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD8+Datos_vigas!$B$7*J8*L8/10000+Datos_vigas!$B$16*AE8)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD8)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF8+Datos_vigas!$B$7*J8*L8/10000+Datos_vigas!$B$16*AG8)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF8)</f>
         <v/>
       </c>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="24">
-        <f>VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,4,0)*D8*C8</f>
+        <f>VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,4,0)*D8*C8+IF(OR(AD8="",AE8=""),0,AD8*MAX(AE8,C8-AE8)/C8)</f>
         <v/>
       </c>
       <c r="G8" s="24">
@@ -7158,18 +7182,18 @@
         <v/>
       </c>
       <c r="H8" s="24">
-        <f>VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,2,0)*D8*C8^2</f>
+        <f>VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,2,0)*D8*C8^2+0.75*1000*IF(OR(AD8="",AE8=""),0,AD8*AE8*(C8-AE8)/C8/1000)</f>
         <v/>
       </c>
       <c r="I8" s="24">
-        <f>IF(VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,3,0)*D8*C8^2)</f>
+        <f>IF(VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,3,0)*D8*C8^2+0.50*1000*IF(OR(AD8="",AE8=""),0,AD8*AE8*(C8-AE8)/C8/1000))</f>
         <v/>
       </c>
       <c r="J8" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K8" s="11">
-        <f>L8-AF8</f>
+        <f>L8-AH8</f>
         <v/>
       </c>
       <c r="L8" s="10" t="n">
@@ -7235,13 +7259,15 @@
         <f>IF(Z8="Invertida",MIN(C8*100/4,J8+16*AA8),J8)</f>
         <v/>
       </c>
-      <c r="AD8" s="10" t="n">
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" s="10" t="n">
+      <c r="AG8" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF8" s="10" t="n">
+      <c r="AH8" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7256,12 +7282,12 @@
         <v>3.8</v>
       </c>
       <c r="D9" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD9+Datos_vigas!$B$7*J9*L9/10000+Datos_vigas!$B$16*AE9)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD9)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF9+Datos_vigas!$B$7*J9*L9/10000+Datos_vigas!$B$16*AG9)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF9)</f>
         <v/>
       </c>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="24">
-        <f>VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,4,0)*D9*C9</f>
+        <f>VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,4,0)*D9*C9+IF(OR(AD9="",AE9=""),0,AD9*MAX(AE9,C9-AE9)/C9)</f>
         <v/>
       </c>
       <c r="G9" s="24">
@@ -7269,18 +7295,18 @@
         <v/>
       </c>
       <c r="H9" s="24">
-        <f>VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,2,0)*D9*C9^2</f>
+        <f>VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,2,0)*D9*C9^2+0.75*1000*IF(OR(AD9="",AE9=""),0,AD9*AE9*(C9-AE9)/C9/1000)</f>
         <v/>
       </c>
       <c r="I9" s="24">
-        <f>IF(VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,3,0)*D9*C9^2)</f>
+        <f>IF(VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y9,Datos_vigas!$A$19:$E$23,3,0)*D9*C9^2+0.50*1000*IF(OR(AD9="",AE9=""),0,AD9*AE9*(C9-AE9)/C9/1000))</f>
         <v/>
       </c>
       <c r="J9" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K9" s="11">
-        <f>L9-AF9</f>
+        <f>L9-AH9</f>
         <v/>
       </c>
       <c r="L9" s="10" t="n">
@@ -7346,13 +7372,15 @@
         <f>IF(Z9="Invertida",MIN(C9*100/4,J9+16*AA9),J9)</f>
         <v/>
       </c>
-      <c r="AD9" s="10" t="n">
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n">
         <v>1.549</v>
       </c>
-      <c r="AE9" s="10" t="n">
+      <c r="AG9" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF9" s="10" t="n">
+      <c r="AH9" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7367,12 +7395,12 @@
         <v>6.53</v>
       </c>
       <c r="D10" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD10+Datos_vigas!$B$7*J10*L10/10000+Datos_vigas!$B$16*AE10)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD10)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF10+Datos_vigas!$B$7*J10*L10/10000+Datos_vigas!$B$16*AG10)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF10)</f>
         <v/>
       </c>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="24">
-        <f>VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,4,0)*D10*C10</f>
+        <f>VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,4,0)*D10*C10+IF(OR(AD10="",AE10=""),0,AD10*MAX(AE10,C10-AE10)/C10)</f>
         <v/>
       </c>
       <c r="G10" s="24">
@@ -7380,18 +7408,18 @@
         <v/>
       </c>
       <c r="H10" s="24">
-        <f>VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,2,0)*D10*C10^2</f>
+        <f>VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,2,0)*D10*C10^2+0.75*1000*IF(OR(AD10="",AE10=""),0,AD10*AE10*(C10-AE10)/C10/1000)</f>
         <v/>
       </c>
       <c r="I10" s="24">
-        <f>IF(VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,3,0)*D10*C10^2)</f>
+        <f>IF(VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,3,0)*D10*C10^2+0.50*1000*IF(OR(AD10="",AE10=""),0,AD10*AE10*(C10-AE10)/C10/1000))</f>
         <v/>
       </c>
       <c r="J10" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K10" s="11">
-        <f>L10-AF10</f>
+        <f>L10-AH10</f>
         <v/>
       </c>
       <c r="L10" s="10" t="n">
@@ -7461,13 +7489,15 @@
         <f>IF(Z10="Invertida",MIN(C10*100/4,J10+16*AA10),J10)</f>
         <v/>
       </c>
-      <c r="AD10" s="10" t="n">
+      <c r="AD10" s="10" t="n"/>
+      <c r="AE10" s="10" t="n"/>
+      <c r="AF10" s="10" t="n">
         <v>1.549</v>
       </c>
-      <c r="AE10" s="10" t="n">
+      <c r="AG10" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF10" s="10" t="n">
+      <c r="AH10" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7482,12 +7512,12 @@
         <v>3.37</v>
       </c>
       <c r="D11" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD11+Datos_vigas!$B$7*J11*L11/10000+Datos_vigas!$B$16*AE11)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD11)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF11+Datos_vigas!$B$7*J11*L11/10000+Datos_vigas!$B$16*AG11)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF11)</f>
         <v/>
       </c>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="24">
-        <f>VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,4,0)*D11*C11</f>
+        <f>VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,4,0)*D11*C11+IF(OR(AD11="",AE11=""),0,AD11*MAX(AE11,C11-AE11)/C11)</f>
         <v/>
       </c>
       <c r="G11" s="24">
@@ -7495,18 +7525,18 @@
         <v/>
       </c>
       <c r="H11" s="24">
-        <f>VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,2,0)*D11*C11^2</f>
+        <f>VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,2,0)*D11*C11^2+0.75*1000*IF(OR(AD11="",AE11=""),0,AD11*AE11*(C11-AE11)/C11/1000)</f>
         <v/>
       </c>
       <c r="I11" s="24">
-        <f>IF(VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,3,0)*D11*C11^2)</f>
+        <f>IF(VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y11,Datos_vigas!$A$19:$E$23,3,0)*D11*C11^2+0.50*1000*IF(OR(AD11="",AE11=""),0,AD11*AE11*(C11-AE11)/C11/1000))</f>
         <v/>
       </c>
       <c r="J11" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K11" s="11">
-        <f>L11-AF11</f>
+        <f>L11-AH11</f>
         <v/>
       </c>
       <c r="L11" s="10" t="n">
@@ -7576,13 +7606,15 @@
         <f>IF(Z11="Invertida",MIN(C11*100/4,J11+16*AA11),J11)</f>
         <v/>
       </c>
-      <c r="AD11" s="10" t="n">
+      <c r="AD11" s="10" t="n"/>
+      <c r="AE11" s="10" t="n"/>
+      <c r="AF11" s="10" t="n">
         <v>0.78</v>
       </c>
-      <c r="AE11" s="10" t="n">
+      <c r="AG11" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF11" s="10" t="n">
+      <c r="AH11" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7597,12 +7629,12 @@
         <v>4.03</v>
       </c>
       <c r="D12" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD12+Datos_vigas!$B$7*J12*L12/10000+Datos_vigas!$B$16*AE12)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD12)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF12+Datos_vigas!$B$7*J12*L12/10000+Datos_vigas!$B$16*AG12)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF12)</f>
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="24">
-        <f>VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,4,0)*D12*C12</f>
+        <f>VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,4,0)*D12*C12+IF(OR(AD12="",AE12=""),0,AD12*MAX(AE12,C12-AE12)/C12)</f>
         <v/>
       </c>
       <c r="G12" s="24">
@@ -7610,18 +7642,18 @@
         <v/>
       </c>
       <c r="H12" s="24">
-        <f>VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,2,0)*D12*C12^2</f>
+        <f>VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,2,0)*D12*C12^2+0.75*1000*IF(OR(AD12="",AE12=""),0,AD12*AE12*(C12-AE12)/C12/1000)</f>
         <v/>
       </c>
       <c r="I12" s="24">
-        <f>IF(VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,3,0)*D12*C12^2)</f>
+        <f>IF(VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y12,Datos_vigas!$A$19:$E$23,3,0)*D12*C12^2+0.50*1000*IF(OR(AD12="",AE12=""),0,AD12*AE12*(C12-AE12)/C12/1000))</f>
         <v/>
       </c>
       <c r="J12" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K12" s="11">
-        <f>L12-AF12</f>
+        <f>L12-AH12</f>
         <v/>
       </c>
       <c r="L12" s="10" t="n">
@@ -7691,13 +7723,15 @@
         <f>IF(Z12="Invertida",MIN(C12*100/4,J12+16*AA12),J12)</f>
         <v/>
       </c>
-      <c r="AD12" s="10" t="n">
+      <c r="AD12" s="10" t="n"/>
+      <c r="AE12" s="10" t="n"/>
+      <c r="AF12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE12" s="10" t="n">
+      <c r="AG12" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF12" s="10" t="n">
+      <c r="AH12" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7712,12 +7746,12 @@
         <v>8.6</v>
       </c>
       <c r="D13" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD13+Datos_vigas!$B$7*J13*L13/10000+Datos_vigas!$B$16*AE13)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD13)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF13+Datos_vigas!$B$7*J13*L13/10000+Datos_vigas!$B$16*AG13)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF13)</f>
         <v/>
       </c>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="24">
-        <f>VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,4,0)*D13*C13</f>
+        <f>VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,4,0)*D13*C13+IF(OR(AD13="",AE13=""),0,AD13*MAX(AE13,C13-AE13)/C13)</f>
         <v/>
       </c>
       <c r="G13" s="24">
@@ -7725,18 +7759,18 @@
         <v/>
       </c>
       <c r="H13" s="24">
-        <f>VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,2,0)*D13*C13^2</f>
+        <f>VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,2,0)*D13*C13^2+0.75*1000*IF(OR(AD13="",AE13=""),0,AD13*AE13*(C13-AE13)/C13/1000)</f>
         <v/>
       </c>
       <c r="I13" s="24">
-        <f>IF(VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,3,0)*D13*C13^2)</f>
+        <f>IF(VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,3,0)*D13*C13^2+0.50*1000*IF(OR(AD13="",AE13=""),0,AD13*AE13*(C13-AE13)/C13/1000))</f>
         <v/>
       </c>
       <c r="J13" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="11">
-        <f>L13-AF13</f>
+        <f>L13-AH13</f>
         <v/>
       </c>
       <c r="L13" s="10" t="n">
@@ -7747,10 +7781,10 @@
         <v/>
       </c>
       <c r="N13" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P13" s="25">
         <f>IF(NOT(ISNUMBER(I13)),"---",IF(I13&lt;=0,"---",IF(I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I13*100/(Datos_vigas!$B$8*AC13*K13^2*Datos_vigas!$B$5)))*AC13*K13*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J13*K13))))</f>
@@ -7771,10 +7805,10 @@
         <v/>
       </c>
       <c r="U13" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W13" s="11">
         <f>IF(OR(M13="REVISAR",P13="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M13&lt;&gt;"REVISAR",P13&lt;&gt;"REVISAR",IF(ISNUMBER(M13),N13*PI()*(O13/10)^2/4&gt;=M13,TRUE),IF(ISNUMBER(P13),Q13*PI()*(R13/10)^2/4&gt;=P13,TRUE),IF(ISNUMBER(M13),M13&lt;=0.0163*AB13*K13,TRUE),IF(ISNUMBER(P13),P13&lt;=0.0163*AC13*K13,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F13&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J13*K13+2*PI()*(U13/10)^2/4*Datos_vigas!$B$6*K13/V13)),"NO VERIF. CORTE",IF(NOT(L13&gt;=C13*100/VLOOKUP(Y13,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -7782,7 +7816,7 @@
       </c>
       <c r="X13" s="13" t="inlineStr">
         <is>
-          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
+          <t>Armadura en 2 capas (rec. 6 cm). Apoya en columna COL 02 de 15x30 y en el tabique T05b. La viga chata VCH 05 le descarga 1.735 kg a 3,60 m del apoyo. Se superpone el momento isostatico P a b / L repartido 0,75 al tramo y 0,50 al apoyo, y la reaccion isostatica al corte. Viga de borde: recibe la reaccion de la losa excentrica y queda sometida a TORSION, no verificada en esta planilla.</t>
         </is>
       </c>
       <c r="Y13" s="10" t="inlineStr">
@@ -7807,12 +7841,18 @@
         <v/>
       </c>
       <c r="AD13" s="10" t="n">
+        <v>1735</v>
+      </c>
+      <c r="AE13" s="10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AF13" s="10" t="n">
         <v>3.71</v>
       </c>
-      <c r="AE13" s="10" t="n">
+      <c r="AG13" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF13" s="10" t="n">
+      <c r="AH13" s="10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7827,12 +7867,12 @@
         <v>3.65</v>
       </c>
       <c r="D14" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD14+Datos_vigas!$B$7*J14*L14/10000+Datos_vigas!$B$16*AE14)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD14)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF14+Datos_vigas!$B$7*J14*L14/10000+Datos_vigas!$B$16*AG14)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF14)</f>
         <v/>
       </c>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="24">
-        <f>VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,4,0)*D14*C14</f>
+        <f>VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,4,0)*D14*C14+IF(OR(AD14="",AE14=""),0,AD14*MAX(AE14,C14-AE14)/C14)</f>
         <v/>
       </c>
       <c r="G14" s="24">
@@ -7840,18 +7880,18 @@
         <v/>
       </c>
       <c r="H14" s="24">
-        <f>VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,2,0)*D14*C14^2</f>
+        <f>VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,2,0)*D14*C14^2+0.75*1000*IF(OR(AD14="",AE14=""),0,AD14*AE14*(C14-AE14)/C14/1000)</f>
         <v/>
       </c>
       <c r="I14" s="24">
-        <f>IF(VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,3,0)*D14*C14^2)</f>
+        <f>IF(VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y14,Datos_vigas!$A$19:$E$23,3,0)*D14*C14^2+0.50*1000*IF(OR(AD14="",AE14=""),0,AD14*AE14*(C14-AE14)/C14/1000))</f>
         <v/>
       </c>
       <c r="J14" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K14" s="11">
-        <f>L14-AF14</f>
+        <f>L14-AH14</f>
         <v/>
       </c>
       <c r="L14" s="10" t="n">
@@ -7917,13 +7957,15 @@
         <f>IF(Z14="Invertida",MIN(C14*100/4,J14+16*AA14),J14)</f>
         <v/>
       </c>
-      <c r="AD14" s="10" t="n">
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n">
         <v>1.065</v>
       </c>
-      <c r="AE14" s="10" t="n">
+      <c r="AG14" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF14" s="10" t="n">
+      <c r="AH14" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7938,12 +7980,12 @@
         <v>4.87</v>
       </c>
       <c r="D15" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD15+Datos_vigas!$B$7*J15*L15/10000+Datos_vigas!$B$16*AE15)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD15)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF15+Datos_vigas!$B$7*J15*L15/10000+Datos_vigas!$B$16*AG15)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF15)</f>
         <v/>
       </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="24">
-        <f>VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,4,0)*D15*C15</f>
+        <f>VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,4,0)*D15*C15+IF(OR(AD15="",AE15=""),0,AD15*MAX(AE15,C15-AE15)/C15)</f>
         <v/>
       </c>
       <c r="G15" s="24">
@@ -7951,18 +7993,18 @@
         <v/>
       </c>
       <c r="H15" s="24">
-        <f>VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,2,0)*D15*C15^2</f>
+        <f>VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,2,0)*D15*C15^2+0.75*1000*IF(OR(AD15="",AE15=""),0,AD15*AE15*(C15-AE15)/C15/1000)</f>
         <v/>
       </c>
       <c r="I15" s="24">
-        <f>IF(VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,3,0)*D15*C15^2)</f>
+        <f>IF(VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,3,0)*D15*C15^2+0.50*1000*IF(OR(AD15="",AE15=""),0,AD15*AE15*(C15-AE15)/C15/1000))</f>
         <v/>
       </c>
       <c r="J15" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K15" s="11">
-        <f>L15-AF15</f>
+        <f>L15-AH15</f>
         <v/>
       </c>
       <c r="L15" s="10" t="n">
@@ -8028,13 +8070,15 @@
         <f>IF(Z15="Invertida",MIN(C15*100/4,J15+16*AA15),J15)</f>
         <v/>
       </c>
-      <c r="AD15" s="10" t="n">
+      <c r="AD15" s="10" t="n"/>
+      <c r="AE15" s="10" t="n"/>
+      <c r="AF15" s="10" t="n">
         <v>1.065</v>
       </c>
-      <c r="AE15" s="10" t="n">
+      <c r="AG15" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF15" s="10" t="n">
+      <c r="AH15" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8049,12 +8093,12 @@
         <v>4.87</v>
       </c>
       <c r="D16" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD16+Datos_vigas!$B$7*J16*L16/10000+Datos_vigas!$B$16*AE16)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD16)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF16+Datos_vigas!$B$7*J16*L16/10000+Datos_vigas!$B$16*AG16)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF16)</f>
         <v/>
       </c>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="24">
-        <f>VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,4,0)*D16*C16</f>
+        <f>VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,4,0)*D16*C16+IF(OR(AD16="",AE16=""),0,AD16*MAX(AE16,C16-AE16)/C16)</f>
         <v/>
       </c>
       <c r="G16" s="24">
@@ -8062,18 +8106,18 @@
         <v/>
       </c>
       <c r="H16" s="24">
-        <f>VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,2,0)*D16*C16^2</f>
+        <f>VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,2,0)*D16*C16^2+0.75*1000*IF(OR(AD16="",AE16=""),0,AD16*AE16*(C16-AE16)/C16/1000)</f>
         <v/>
       </c>
       <c r="I16" s="24">
-        <f>IF(VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,3,0)*D16*C16^2)</f>
+        <f>IF(VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,3,0)*D16*C16^2+0.50*1000*IF(OR(AD16="",AE16=""),0,AD16*AE16*(C16-AE16)/C16/1000))</f>
         <v/>
       </c>
       <c r="J16" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="11">
-        <f>L16-AF16</f>
+        <f>L16-AH16</f>
         <v/>
       </c>
       <c r="L16" s="10" t="n">
@@ -8143,13 +8187,15 @@
         <f>IF(Z16="Invertida",MIN(C16*100/4,J16+16*AA16),J16)</f>
         <v/>
       </c>
-      <c r="AD16" s="10" t="n">
+      <c r="AD16" s="10" t="n"/>
+      <c r="AE16" s="10" t="n"/>
+      <c r="AF16" s="10" t="n">
         <v>1.549</v>
       </c>
-      <c r="AE16" s="10" t="n">
+      <c r="AG16" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF16" s="10" t="n">
+      <c r="AH16" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8164,12 +8210,12 @@
         <v>2.55</v>
       </c>
       <c r="D17" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD17+Datos_vigas!$B$7*J17*L17/10000+Datos_vigas!$B$16*AE17)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD17)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF17+Datos_vigas!$B$7*J17*L17/10000+Datos_vigas!$B$16*AG17)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF17)</f>
         <v/>
       </c>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="24">
-        <f>VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,4,0)*D17*C17</f>
+        <f>VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,4,0)*D17*C17+IF(OR(AD17="",AE17=""),0,AD17*MAX(AE17,C17-AE17)/C17)</f>
         <v/>
       </c>
       <c r="G17" s="24">
@@ -8177,18 +8223,18 @@
         <v/>
       </c>
       <c r="H17" s="24">
-        <f>VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,2,0)*D17*C17^2</f>
+        <f>VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,2,0)*D17*C17^2+0.75*1000*IF(OR(AD17="",AE17=""),0,AD17*AE17*(C17-AE17)/C17/1000)</f>
         <v/>
       </c>
       <c r="I17" s="24">
-        <f>IF(VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,3,0)*D17*C17^2)</f>
+        <f>IF(VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y17,Datos_vigas!$A$19:$E$23,3,0)*D17*C17^2+0.50*1000*IF(OR(AD17="",AE17=""),0,AD17*AE17*(C17-AE17)/C17/1000))</f>
         <v/>
       </c>
       <c r="J17" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K17" s="11">
-        <f>L17-AF17</f>
+        <f>L17-AH17</f>
         <v/>
       </c>
       <c r="L17" s="10" t="n">
@@ -8254,13 +8300,15 @@
         <f>IF(Z17="Invertida",MIN(C17*100/4,J17+16*AA17),J17)</f>
         <v/>
       </c>
-      <c r="AD17" s="10" t="n">
+      <c r="AD17" s="10" t="n"/>
+      <c r="AE17" s="10" t="n"/>
+      <c r="AF17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE17" s="10" t="n">
+      <c r="AG17" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF17" s="10" t="n">
+      <c r="AH17" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8275,12 +8323,12 @@
         <v>4</v>
       </c>
       <c r="D18" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD18+Datos_vigas!$B$7*J18*L18/10000+Datos_vigas!$B$16*AE18)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD18)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF18+Datos_vigas!$B$7*J18*L18/10000+Datos_vigas!$B$16*AG18)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF18)</f>
         <v/>
       </c>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="24">
-        <f>VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,4,0)*D18*C18</f>
+        <f>VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,4,0)*D18*C18+IF(OR(AD18="",AE18=""),0,AD18*MAX(AE18,C18-AE18)/C18)</f>
         <v/>
       </c>
       <c r="G18" s="24">
@@ -8288,18 +8336,18 @@
         <v/>
       </c>
       <c r="H18" s="24">
-        <f>VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,2,0)*D18*C18^2</f>
+        <f>VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,2,0)*D18*C18^2+0.75*1000*IF(OR(AD18="",AE18=""),0,AD18*AE18*(C18-AE18)/C18/1000)</f>
         <v/>
       </c>
       <c r="I18" s="24">
-        <f>IF(VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,3,0)*D18*C18^2)</f>
+        <f>IF(VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y18,Datos_vigas!$A$19:$E$23,3,0)*D18*C18^2+0.50*1000*IF(OR(AD18="",AE18=""),0,AD18*AE18*(C18-AE18)/C18/1000))</f>
         <v/>
       </c>
       <c r="J18" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K18" s="11">
-        <f>L18-AF18</f>
+        <f>L18-AH18</f>
         <v/>
       </c>
       <c r="L18" s="10" t="n">
@@ -8365,13 +8413,15 @@
         <f>IF(Z18="Invertida",MIN(C18*100/4,J18+16*AA18),J18)</f>
         <v/>
       </c>
-      <c r="AD18" s="10" t="n">
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n">
         <v>1.825</v>
       </c>
-      <c r="AE18" s="10" t="n">
+      <c r="AG18" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF18" s="10" t="n">
+      <c r="AH18" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8386,12 +8436,12 @@
         <v>3.6</v>
       </c>
       <c r="D19" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD19+Datos_vigas!$B$7*J19*L19/10000+Datos_vigas!$B$16*AE19)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD19)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF19+Datos_vigas!$B$7*J19*L19/10000+Datos_vigas!$B$16*AG19)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF19)</f>
         <v/>
       </c>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="24">
-        <f>VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,4,0)*D19*C19</f>
+        <f>VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,4,0)*D19*C19+IF(OR(AD19="",AE19=""),0,AD19*MAX(AE19,C19-AE19)/C19)</f>
         <v/>
       </c>
       <c r="G19" s="24">
@@ -8399,18 +8449,18 @@
         <v/>
       </c>
       <c r="H19" s="24">
-        <f>VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,2,0)*D19*C19^2</f>
+        <f>VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,2,0)*D19*C19^2+0.75*1000*IF(OR(AD19="",AE19=""),0,AD19*AE19*(C19-AE19)/C19/1000)</f>
         <v/>
       </c>
       <c r="I19" s="24">
-        <f>IF(VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,3,0)*D19*C19^2)</f>
+        <f>IF(VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y19,Datos_vigas!$A$19:$E$23,3,0)*D19*C19^2+0.50*1000*IF(OR(AD19="",AE19=""),0,AD19*AE19*(C19-AE19)/C19/1000))</f>
         <v/>
       </c>
       <c r="J19" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K19" s="11">
-        <f>L19-AF19</f>
+        <f>L19-AH19</f>
         <v/>
       </c>
       <c r="L19" s="10" t="n">
@@ -8476,13 +8526,15 @@
         <f>IF(Z19="Invertida",MIN(C19*100/4,J19+16*AA19),J19)</f>
         <v/>
       </c>
-      <c r="AD19" s="10" t="n">
+      <c r="AD19" s="10" t="n"/>
+      <c r="AE19" s="10" t="n"/>
+      <c r="AF19" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE19" s="10" t="n">
+      <c r="AG19" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF19" s="10" t="n">
+      <c r="AH19" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8497,12 +8549,12 @@
         <v>7.68</v>
       </c>
       <c r="D20" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD20+Datos_vigas!$B$7*J20*L20/10000+Datos_vigas!$B$16*AE20)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD20)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF20+Datos_vigas!$B$7*J20*L20/10000+Datos_vigas!$B$16*AG20)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF20)</f>
         <v/>
       </c>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="24">
-        <f>VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,4,0)*D20*C20</f>
+        <f>VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,4,0)*D20*C20+IF(OR(AD20="",AE20=""),0,AD20*MAX(AE20,C20-AE20)/C20)</f>
         <v/>
       </c>
       <c r="G20" s="24">
@@ -8510,18 +8562,18 @@
         <v/>
       </c>
       <c r="H20" s="24">
-        <f>VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,2,0)*D20*C20^2</f>
+        <f>VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,2,0)*D20*C20^2+0.75*1000*IF(OR(AD20="",AE20=""),0,AD20*AE20*(C20-AE20)/C20/1000)</f>
         <v/>
       </c>
       <c r="I20" s="24">
-        <f>IF(VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,3,0)*D20*C20^2)</f>
+        <f>IF(VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y20,Datos_vigas!$A$19:$E$23,3,0)*D20*C20^2+0.50*1000*IF(OR(AD20="",AE20=""),0,AD20*AE20*(C20-AE20)/C20/1000))</f>
         <v/>
       </c>
       <c r="J20" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K20" s="11">
-        <f>L20-AF20</f>
+        <f>L20-AH20</f>
         <v/>
       </c>
       <c r="L20" s="10" t="n">
@@ -8591,13 +8643,15 @@
         <f>IF(Z20="Invertida",MIN(C20*100/4,J20+16*AA20),J20)</f>
         <v/>
       </c>
-      <c r="AD20" s="10" t="n">
+      <c r="AD20" s="10" t="n"/>
+      <c r="AE20" s="10" t="n"/>
+      <c r="AF20" s="10" t="n">
         <v>1.825</v>
       </c>
-      <c r="AE20" s="10" t="n">
+      <c r="AG20" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF20" s="10" t="n">
+      <c r="AH20" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8612,12 +8666,12 @@
         <v>3.45</v>
       </c>
       <c r="D21" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD21+Datos_vigas!$B$7*J21*L21/10000+Datos_vigas!$B$16*AE21)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD21)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF21+Datos_vigas!$B$7*J21*L21/10000+Datos_vigas!$B$16*AG21)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF21)</f>
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="24">
-        <f>VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,4,0)*D21*C21</f>
+        <f>VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,4,0)*D21*C21+IF(OR(AD21="",AE21=""),0,AD21*MAX(AE21,C21-AE21)/C21)</f>
         <v/>
       </c>
       <c r="G21" s="24">
@@ -8625,18 +8679,18 @@
         <v/>
       </c>
       <c r="H21" s="24">
-        <f>VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,2,0)*D21*C21^2</f>
+        <f>VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,2,0)*D21*C21^2+0.75*1000*IF(OR(AD21="",AE21=""),0,AD21*AE21*(C21-AE21)/C21/1000)</f>
         <v/>
       </c>
       <c r="I21" s="24">
-        <f>IF(VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,3,0)*D21*C21^2)</f>
+        <f>IF(VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y21,Datos_vigas!$A$19:$E$23,3,0)*D21*C21^2+0.50*1000*IF(OR(AD21="",AE21=""),0,AD21*AE21*(C21-AE21)/C21/1000))</f>
         <v/>
       </c>
       <c r="J21" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K21" s="11">
-        <f>L21-AF21</f>
+        <f>L21-AH21</f>
         <v/>
       </c>
       <c r="L21" s="10" t="n">
@@ -8706,13 +8760,15 @@
         <f>IF(Z21="Invertida",MIN(C21*100/4,J21+16*AA21),J21)</f>
         <v/>
       </c>
-      <c r="AD21" s="10" t="n">
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AF21" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE21" s="10" t="n">
+      <c r="AG21" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF21" s="10" t="n">
+      <c r="AH21" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8727,12 +8783,12 @@
         <v>5.02</v>
       </c>
       <c r="D22" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD22+Datos_vigas!$B$7*J22*L22/10000+Datos_vigas!$B$16*AE22)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD22)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF22+Datos_vigas!$B$7*J22*L22/10000+Datos_vigas!$B$16*AG22)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF22)</f>
         <v/>
       </c>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="24">
-        <f>VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,4,0)*D22*C22</f>
+        <f>VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,4,0)*D22*C22+IF(OR(AD22="",AE22=""),0,AD22*MAX(AE22,C22-AE22)/C22)</f>
         <v/>
       </c>
       <c r="G22" s="24">
@@ -8740,18 +8796,18 @@
         <v/>
       </c>
       <c r="H22" s="24">
-        <f>VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,2,0)*D22*C22^2</f>
+        <f>VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,2,0)*D22*C22^2+0.75*1000*IF(OR(AD22="",AE22=""),0,AD22*AE22*(C22-AE22)/C22/1000)</f>
         <v/>
       </c>
       <c r="I22" s="24">
-        <f>IF(VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,3,0)*D22*C22^2)</f>
+        <f>IF(VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y22,Datos_vigas!$A$19:$E$23,3,0)*D22*C22^2+0.50*1000*IF(OR(AD22="",AE22=""),0,AD22*AE22*(C22-AE22)/C22/1000))</f>
         <v/>
       </c>
       <c r="J22" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="11">
-        <f>L22-AF22</f>
+        <f>L22-AH22</f>
         <v/>
       </c>
       <c r="L22" s="10" t="n">
@@ -8821,13 +8877,15 @@
         <f>IF(Z22="Invertida",MIN(C22*100/4,J22+16*AA22),J22)</f>
         <v/>
       </c>
-      <c r="AD22" s="10" t="n">
+      <c r="AD22" s="10" t="n"/>
+      <c r="AE22" s="10" t="n"/>
+      <c r="AF22" s="10" t="n">
         <v>1.549</v>
       </c>
-      <c r="AE22" s="10" t="n">
+      <c r="AG22" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF22" s="10" t="n">
+      <c r="AH22" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8842,12 +8900,12 @@
         <v>3.71</v>
       </c>
       <c r="D23" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD23+Datos_vigas!$B$7*J23*L23/10000+Datos_vigas!$B$16*AE23)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD23)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF23+Datos_vigas!$B$7*J23*L23/10000+Datos_vigas!$B$16*AG23)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF23)</f>
         <v/>
       </c>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="24">
-        <f>VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,4,0)*D23*C23</f>
+        <f>VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,4,0)*D23*C23+IF(OR(AD23="",AE23=""),0,AD23*MAX(AE23,C23-AE23)/C23)</f>
         <v/>
       </c>
       <c r="G23" s="24">
@@ -8855,18 +8913,18 @@
         <v/>
       </c>
       <c r="H23" s="24">
-        <f>VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,2,0)*D23*C23^2</f>
+        <f>VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,2,0)*D23*C23^2+0.75*1000*IF(OR(AD23="",AE23=""),0,AD23*AE23*(C23-AE23)/C23/1000)</f>
         <v/>
       </c>
       <c r="I23" s="24">
-        <f>IF(VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,3,0)*D23*C23^2)</f>
+        <f>IF(VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y23,Datos_vigas!$A$19:$E$23,3,0)*D23*C23^2+0.50*1000*IF(OR(AD23="",AE23=""),0,AD23*AE23*(C23-AE23)/C23/1000))</f>
         <v/>
       </c>
       <c r="J23" s="10" t="n">
         <v>40</v>
       </c>
       <c r="K23" s="11">
-        <f>L23-AF23</f>
+        <f>L23-AH23</f>
         <v/>
       </c>
       <c r="L23" s="10" t="n">
@@ -8936,13 +8994,15 @@
         <f>IF(Z23="Invertida",MIN(C23*100/4,J23+16*AA23),J23)</f>
         <v/>
       </c>
-      <c r="AD23" s="10" t="n">
+      <c r="AD23" s="10" t="n"/>
+      <c r="AE23" s="10" t="n"/>
+      <c r="AF23" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE23" s="10" t="n">
+      <c r="AG23" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF23" s="10" t="n">
+      <c r="AH23" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8957,12 +9017,12 @@
         <v>2.13</v>
       </c>
       <c r="D24" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD24+Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*AE24)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD24)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF24+Datos_vigas!$B$7*J24*L24/10000+Datos_vigas!$B$16*AG24)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF24)</f>
         <v/>
       </c>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="24">
-        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,4,0)*D24*C24</f>
+        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,4,0)*D24*C24+IF(OR(AD24="",AE24=""),0,AD24*MAX(AE24,C24-AE24)/C24)</f>
         <v/>
       </c>
       <c r="G24" s="24">
@@ -8970,18 +9030,18 @@
         <v/>
       </c>
       <c r="H24" s="24">
-        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,2,0)*D24*C24^2</f>
+        <f>VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,2,0)*D24*C24^2+0.75*1000*IF(OR(AD24="",AE24=""),0,AD24*AE24*(C24-AE24)/C24/1000)</f>
         <v/>
       </c>
       <c r="I24" s="24">
-        <f>IF(VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)*D24*C24^2)</f>
+        <f>IF(VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y24,Datos_vigas!$A$19:$E$23,3,0)*D24*C24^2+0.50*1000*IF(OR(AD24="",AE24=""),0,AD24*AE24*(C24-AE24)/C24/1000))</f>
         <v/>
       </c>
       <c r="J24" s="10" t="n">
         <v>40</v>
       </c>
       <c r="K24" s="11">
-        <f>L24-AF24</f>
+        <f>L24-AH24</f>
         <v/>
       </c>
       <c r="L24" s="10" t="n">
@@ -9051,13 +9111,15 @@
         <f>IF(Z24="Invertida",MIN(C24*100/4,J24+16*AA24),J24)</f>
         <v/>
       </c>
-      <c r="AD24" s="10" t="n">
+      <c r="AD24" s="10" t="n"/>
+      <c r="AE24" s="10" t="n"/>
+      <c r="AF24" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE24" s="10" t="n">
+      <c r="AG24" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF24" s="10" t="n">
+      <c r="AH24" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9072,12 +9134,12 @@
         <v>3.71</v>
       </c>
       <c r="D25" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AD25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AE25)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AD25)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,2,0)*AF25+Datos_vigas!$B$7*J25*L25/10000+Datos_vigas!$B$16*AG25)+Datos_vigas!$B$11*VLOOKUP($A$4,Datos_vigas!$A$14:$E$15,3,0)*AF25)</f>
         <v/>
       </c>
       <c r="E25" s="18" t="n"/>
       <c r="F25" s="29">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25</f>
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,4,0)*D25*C25+IF(OR(AD25="",AE25=""),0,AD25*MAX(AE25,C25-AE25)/C25)</f>
         <v/>
       </c>
       <c r="G25" s="29">
@@ -9085,18 +9147,18 @@
         <v/>
       </c>
       <c r="H25" s="29">
-        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2</f>
+        <f>VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,2,0)*D25*C25^2+0.75*1000*IF(OR(AD25="",AE25=""),0,AD25*AE25*(C25-AE25)/C25/1000)</f>
         <v/>
       </c>
       <c r="I25" s="29">
-        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2)</f>
+        <f>IF(VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y25,Datos_vigas!$A$19:$E$23,3,0)*D25*C25^2+0.50*1000*IF(OR(AD25="",AE25=""),0,AD25*AE25*(C25-AE25)/C25/1000))</f>
         <v/>
       </c>
       <c r="J25" s="17" t="n">
         <v>12</v>
       </c>
       <c r="K25" s="18">
-        <f>L25-AF25</f>
+        <f>L25-AH25</f>
         <v/>
       </c>
       <c r="L25" s="17" t="n">
@@ -9166,13 +9228,15 @@
         <f>IF(Z25="Invertida",MIN(C25*100/4,J25+16*AA25),J25)</f>
         <v/>
       </c>
-      <c r="AD25" s="17" t="n">
+      <c r="AD25" s="17" t="n"/>
+      <c r="AE25" s="17" t="n"/>
+      <c r="AF25" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AE25" s="17" t="n">
+      <c r="AG25" s="17" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF25" s="17" t="n">
+      <c r="AH25" s="17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9191,12 +9255,12 @@
         <v>9.9</v>
       </c>
       <c r="D26" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AE26)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD26)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF26+Datos_vigas!$B$7*J26*L26/10000+Datos_vigas!$B$16*AG26)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF26)</f>
         <v/>
       </c>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="24">
-        <f>VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,4,0)*D26*C26</f>
+        <f>VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,4,0)*D26*C26+IF(OR(AD26="",AE26=""),0,AD26*MAX(AE26,C26-AE26)/C26)</f>
         <v/>
       </c>
       <c r="G26" s="24">
@@ -9204,18 +9268,18 @@
         <v/>
       </c>
       <c r="H26" s="24">
-        <f>VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,2,0)*D26*C26^2</f>
+        <f>VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,2,0)*D26*C26^2+0.75*1000*IF(OR(AD26="",AE26=""),0,AD26*AE26*(C26-AE26)/C26/1000)</f>
         <v/>
       </c>
       <c r="I26" s="24">
-        <f>IF(VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,3,0)*D26*C26^2)</f>
+        <f>IF(VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y26,Datos_vigas!$A$19:$E$23,3,0)*D26*C26^2+0.50*1000*IF(OR(AD26="",AE26=""),0,AD26*AE26*(C26-AE26)/C26/1000))</f>
         <v/>
       </c>
       <c r="J26" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K26" s="11">
-        <f>L26-AF26</f>
+        <f>L26-AH26</f>
         <v/>
       </c>
       <c r="L26" s="10" t="n">
@@ -9281,13 +9345,15 @@
         <f>IF(Z26="Invertida",MIN(C26*100/4,J26+16*AA26),J26)</f>
         <v/>
       </c>
-      <c r="AD26" s="10" t="n">
+      <c r="AD26" s="10" t="n"/>
+      <c r="AE26" s="10" t="n"/>
+      <c r="AF26" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE26" s="10" t="n">
+      <c r="AG26" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF26" s="10" t="n">
+      <c r="AH26" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9302,12 +9368,12 @@
         <v>6</v>
       </c>
       <c r="D27" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AE27)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD27)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF27+Datos_vigas!$B$7*J27*L27/10000+Datos_vigas!$B$16*AG27)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF27)</f>
         <v/>
       </c>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="24">
-        <f>VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,4,0)*D27*C27</f>
+        <f>VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,4,0)*D27*C27+IF(OR(AD27="",AE27=""),0,AD27*MAX(AE27,C27-AE27)/C27)</f>
         <v/>
       </c>
       <c r="G27" s="24">
@@ -9315,18 +9381,18 @@
         <v/>
       </c>
       <c r="H27" s="24">
-        <f>VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,2,0)*D27*C27^2</f>
+        <f>VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,2,0)*D27*C27^2+0.75*1000*IF(OR(AD27="",AE27=""),0,AD27*AE27*(C27-AE27)/C27/1000)</f>
         <v/>
       </c>
       <c r="I27" s="24">
-        <f>IF(VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,3,0)*D27*C27^2)</f>
+        <f>IF(VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y27,Datos_vigas!$A$19:$E$23,3,0)*D27*C27^2+0.50*1000*IF(OR(AD27="",AE27=""),0,AD27*AE27*(C27-AE27)/C27/1000))</f>
         <v/>
       </c>
       <c r="J27" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K27" s="11">
-        <f>L27-AF27</f>
+        <f>L27-AH27</f>
         <v/>
       </c>
       <c r="L27" s="10" t="n">
@@ -9392,13 +9458,15 @@
         <f>IF(Z27="Invertida",MIN(C27*100/4,J27+16*AA27),J27)</f>
         <v/>
       </c>
-      <c r="AD27" s="10" t="n">
+      <c r="AD27" s="10" t="n"/>
+      <c r="AE27" s="10" t="n"/>
+      <c r="AF27" s="10" t="n">
         <v>3.799</v>
       </c>
-      <c r="AE27" s="10" t="n">
+      <c r="AG27" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF27" s="10" t="n">
+      <c r="AH27" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9413,12 +9481,12 @@
         <v>3.75</v>
       </c>
       <c r="D28" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AE28)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD28)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF28+Datos_vigas!$B$7*J28*L28/10000+Datos_vigas!$B$16*AG28)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF28)</f>
         <v/>
       </c>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="24">
-        <f>VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,4,0)*D28*C28</f>
+        <f>VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,4,0)*D28*C28+IF(OR(AD28="",AE28=""),0,AD28*MAX(AE28,C28-AE28)/C28)</f>
         <v/>
       </c>
       <c r="G28" s="24">
@@ -9426,18 +9494,18 @@
         <v/>
       </c>
       <c r="H28" s="24">
-        <f>VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,2,0)*D28*C28^2</f>
+        <f>VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,2,0)*D28*C28^2+0.75*1000*IF(OR(AD28="",AE28=""),0,AD28*AE28*(C28-AE28)/C28/1000)</f>
         <v/>
       </c>
       <c r="I28" s="24">
-        <f>IF(VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,3,0)*D28*C28^2)</f>
+        <f>IF(VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y28,Datos_vigas!$A$19:$E$23,3,0)*D28*C28^2+0.50*1000*IF(OR(AD28="",AE28=""),0,AD28*AE28*(C28-AE28)/C28/1000))</f>
         <v/>
       </c>
       <c r="J28" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="11">
-        <f>L28-AF28</f>
+        <f>L28-AH28</f>
         <v/>
       </c>
       <c r="L28" s="10" t="n">
@@ -9503,13 +9571,15 @@
         <f>IF(Z28="Invertida",MIN(C28*100/4,J28+16*AA28),J28)</f>
         <v/>
       </c>
-      <c r="AD28" s="10" t="n">
+      <c r="AD28" s="10" t="n"/>
+      <c r="AE28" s="10" t="n"/>
+      <c r="AF28" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE28" s="10" t="n">
+      <c r="AG28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF28" s="10" t="n">
+      <c r="AH28" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9524,12 +9594,12 @@
         <v>6</v>
       </c>
       <c r="D29" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AE29)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD29)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF29+Datos_vigas!$B$7*J29*L29/10000+Datos_vigas!$B$16*AG29)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF29)</f>
         <v/>
       </c>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="24">
-        <f>VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,4,0)*D29*C29</f>
+        <f>VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,4,0)*D29*C29+IF(OR(AD29="",AE29=""),0,AD29*MAX(AE29,C29-AE29)/C29)</f>
         <v/>
       </c>
       <c r="G29" s="24">
@@ -9537,18 +9607,18 @@
         <v/>
       </c>
       <c r="H29" s="24">
-        <f>VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,2,0)*D29*C29^2</f>
+        <f>VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,2,0)*D29*C29^2+0.75*1000*IF(OR(AD29="",AE29=""),0,AD29*AE29*(C29-AE29)/C29/1000)</f>
         <v/>
       </c>
       <c r="I29" s="24">
-        <f>IF(VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,3,0)*D29*C29^2)</f>
+        <f>IF(VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y29,Datos_vigas!$A$19:$E$23,3,0)*D29*C29^2+0.50*1000*IF(OR(AD29="",AE29=""),0,AD29*AE29*(C29-AE29)/C29/1000))</f>
         <v/>
       </c>
       <c r="J29" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K29" s="11">
-        <f>L29-AF29</f>
+        <f>L29-AH29</f>
         <v/>
       </c>
       <c r="L29" s="10" t="n">
@@ -9614,13 +9684,15 @@
         <f>IF(Z29="Invertida",MIN(C29*100/4,J29+16*AA29),J29)</f>
         <v/>
       </c>
-      <c r="AD29" s="10" t="n">
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="10" t="n"/>
+      <c r="AF29" s="10" t="n">
         <v>1.699</v>
       </c>
-      <c r="AE29" s="10" t="n">
+      <c r="AG29" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF29" s="10" t="n">
+      <c r="AH29" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9635,12 +9707,12 @@
         <v>4.03</v>
       </c>
       <c r="D30" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AE30)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD30)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF30+Datos_vigas!$B$7*J30*L30/10000+Datos_vigas!$B$16*AG30)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF30)</f>
         <v/>
       </c>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="24">
-        <f>VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,4,0)*D30*C30</f>
+        <f>VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,4,0)*D30*C30+IF(OR(AD30="",AE30=""),0,AD30*MAX(AE30,C30-AE30)/C30)</f>
         <v/>
       </c>
       <c r="G30" s="24">
@@ -9648,18 +9720,18 @@
         <v/>
       </c>
       <c r="H30" s="24">
-        <f>VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,2,0)*D30*C30^2</f>
+        <f>VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,2,0)*D30*C30^2+0.75*1000*IF(OR(AD30="",AE30=""),0,AD30*AE30*(C30-AE30)/C30/1000)</f>
         <v/>
       </c>
       <c r="I30" s="24">
-        <f>IF(VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,3,0)*D30*C30^2)</f>
+        <f>IF(VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y30,Datos_vigas!$A$19:$E$23,3,0)*D30*C30^2+0.50*1000*IF(OR(AD30="",AE30=""),0,AD30*AE30*(C30-AE30)/C30/1000))</f>
         <v/>
       </c>
       <c r="J30" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K30" s="11">
-        <f>L30-AF30</f>
+        <f>L30-AH30</f>
         <v/>
       </c>
       <c r="L30" s="10" t="n">
@@ -9729,13 +9801,15 @@
         <f>IF(Z30="Invertida",MIN(C30*100/4,J30+16*AA30),J30)</f>
         <v/>
       </c>
-      <c r="AD30" s="10" t="n">
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="10" t="n"/>
+      <c r="AF30" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AE30" s="10" t="n">
+      <c r="AG30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF30" s="10" t="n">
+      <c r="AH30" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9750,12 +9824,12 @@
         <v>4.85</v>
       </c>
       <c r="D31" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AE31)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD31)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF31+Datos_vigas!$B$7*J31*L31/10000+Datos_vigas!$B$16*AG31)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF31)</f>
         <v/>
       </c>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="24">
-        <f>VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,4,0)*D31*C31</f>
+        <f>VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,4,0)*D31*C31+IF(OR(AD31="",AE31=""),0,AD31*MAX(AE31,C31-AE31)/C31)</f>
         <v/>
       </c>
       <c r="G31" s="24">
@@ -9763,18 +9837,18 @@
         <v/>
       </c>
       <c r="H31" s="24">
-        <f>VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,2,0)*D31*C31^2</f>
+        <f>VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,2,0)*D31*C31^2+0.75*1000*IF(OR(AD31="",AE31=""),0,AD31*AE31*(C31-AE31)/C31/1000)</f>
         <v/>
       </c>
       <c r="I31" s="24">
-        <f>IF(VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,3,0)*D31*C31^2)</f>
+        <f>IF(VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y31,Datos_vigas!$A$19:$E$23,3,0)*D31*C31^2+0.50*1000*IF(OR(AD31="",AE31=""),0,AD31*AE31*(C31-AE31)/C31/1000))</f>
         <v/>
       </c>
       <c r="J31" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="11">
-        <f>L31-AF31</f>
+        <f>L31-AH31</f>
         <v/>
       </c>
       <c r="L31" s="10" t="n">
@@ -9844,13 +9918,15 @@
         <f>IF(Z31="Invertida",MIN(C31*100/4,J31+16*AA31),J31)</f>
         <v/>
       </c>
-      <c r="AD31" s="10" t="n">
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="10" t="n"/>
+      <c r="AF31" s="10" t="n">
         <v>1.699</v>
       </c>
-      <c r="AE31" s="10" t="n">
+      <c r="AG31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF31" s="10" t="n">
+      <c r="AH31" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9865,12 +9941,12 @@
         <v>3.58</v>
       </c>
       <c r="D32" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AE32)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD32)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF32+Datos_vigas!$B$7*J32*L32/10000+Datos_vigas!$B$16*AG32)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF32)</f>
         <v/>
       </c>
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="24">
-        <f>VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,4,0)*D32*C32</f>
+        <f>VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,4,0)*D32*C32+IF(OR(AD32="",AE32=""),0,AD32*MAX(AE32,C32-AE32)/C32)</f>
         <v/>
       </c>
       <c r="G32" s="24">
@@ -9878,18 +9954,18 @@
         <v/>
       </c>
       <c r="H32" s="24">
-        <f>VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,2,0)*D32*C32^2</f>
+        <f>VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,2,0)*D32*C32^2+0.75*1000*IF(OR(AD32="",AE32=""),0,AD32*AE32*(C32-AE32)/C32/1000)</f>
         <v/>
       </c>
       <c r="I32" s="24">
-        <f>IF(VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,3,0)*D32*C32^2)</f>
+        <f>IF(VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y32,Datos_vigas!$A$19:$E$23,3,0)*D32*C32^2+0.50*1000*IF(OR(AD32="",AE32=""),0,AD32*AE32*(C32-AE32)/C32/1000))</f>
         <v/>
       </c>
       <c r="J32" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K32" s="11">
-        <f>L32-AF32</f>
+        <f>L32-AH32</f>
         <v/>
       </c>
       <c r="L32" s="10" t="n">
@@ -9955,13 +10031,15 @@
         <f>IF(Z32="Invertida",MIN(C32*100/4,J32+16*AA32),J32)</f>
         <v/>
       </c>
-      <c r="AD32" s="10" t="n">
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="10" t="n"/>
+      <c r="AF32" s="10" t="n">
         <v>1.699</v>
       </c>
-      <c r="AE32" s="10" t="n">
+      <c r="AG32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF32" s="10" t="n">
+      <c r="AH32" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9976,12 +10054,12 @@
         <v>1.12</v>
       </c>
       <c r="D33" s="24">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AE33)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD33)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF33+Datos_vigas!$B$7*J33*L33/10000+Datos_vigas!$B$16*AG33)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF33)</f>
         <v/>
       </c>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="24">
-        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,4,0)*D33*C33</f>
+        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,4,0)*D33*C33+IF(OR(AD33="",AE33=""),0,AD33*MAX(AE33,C33-AE33)/C33)</f>
         <v/>
       </c>
       <c r="G33" s="24">
@@ -9989,18 +10067,18 @@
         <v/>
       </c>
       <c r="H33" s="24">
-        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,2,0)*D33*C33^2</f>
+        <f>VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,2,0)*D33*C33^2+0.75*1000*IF(OR(AD33="",AE33=""),0,AD33*AE33*(C33-AE33)/C33/1000)</f>
         <v/>
       </c>
       <c r="I33" s="24">
-        <f>IF(VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)*D33*C33^2)</f>
+        <f>IF(VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y33,Datos_vigas!$A$19:$E$23,3,0)*D33*C33^2+0.50*1000*IF(OR(AD33="",AE33=""),0,AD33*AE33*(C33-AE33)/C33/1000))</f>
         <v/>
       </c>
       <c r="J33" s="10" t="n">
         <v>15</v>
       </c>
       <c r="K33" s="11">
-        <f>L33-AF33</f>
+        <f>L33-AH33</f>
         <v/>
       </c>
       <c r="L33" s="10" t="n">
@@ -10066,13 +10144,15 @@
         <f>IF(Z33="Invertida",MIN(C33*100/4,J33+16*AA33),J33)</f>
         <v/>
       </c>
-      <c r="AD33" s="10" t="n">
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="10" t="n"/>
+      <c r="AF33" s="10" t="n">
         <v>1.699</v>
       </c>
-      <c r="AE33" s="10" t="n">
+      <c r="AG33" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AF33" s="10" t="n">
+      <c r="AH33" s="10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10087,12 +10167,12 @@
         <v>4.35</v>
       </c>
       <c r="D34" s="29">
-        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AD34+Datos_vigas!$B$7*J34*L34/10000+Datos_vigas!$B$16*AE34)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AD34)</f>
+        <f>(Datos_vigas!$B$10*(VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,2,0)*AF34+Datos_vigas!$B$7*J34*L34/10000+Datos_vigas!$B$16*AG34)+Datos_vigas!$B$11*VLOOKUP($A$26,Datos_vigas!$A$14:$E$15,3,0)*AF34)</f>
         <v/>
       </c>
       <c r="E34" s="18" t="n"/>
       <c r="F34" s="29">
-        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,4,0)*D34*C34</f>
+        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,4,0)*D34*C34+IF(OR(AD34="",AE34=""),0,AD34*MAX(AE34,C34-AE34)/C34)</f>
         <v/>
       </c>
       <c r="G34" s="29">
@@ -10100,18 +10180,18 @@
         <v/>
       </c>
       <c r="H34" s="29">
-        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,2,0)*D34*C34^2</f>
+        <f>VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,2,0)*D34*C34^2+0.75*1000*IF(OR(AD34="",AE34=""),0,AD34*AE34*(C34-AE34)/C34/1000)</f>
         <v/>
       </c>
       <c r="I34" s="29">
-        <f>IF(VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)*D34*C34^2)</f>
+        <f>IF(VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)=0,"---",VLOOKUP(Y34,Datos_vigas!$A$19:$E$23,3,0)*D34*C34^2+0.50*1000*IF(OR(AD34="",AE34=""),0,AD34*AE34*(C34-AE34)/C34/1000))</f>
         <v/>
       </c>
       <c r="J34" s="17" t="n">
         <v>15</v>
       </c>
       <c r="K34" s="18">
-        <f>L34-AF34</f>
+        <f>L34-AH34</f>
         <v/>
       </c>
       <c r="L34" s="17" t="n">
@@ -10181,13 +10261,15 @@
         <f>IF(Z34="Invertida",MIN(C34*100/4,J34+16*AA34),J34)</f>
         <v/>
       </c>
-      <c r="AD34" s="17" t="n">
+      <c r="AD34" s="17" t="n"/>
+      <c r="AE34" s="17" t="n"/>
+      <c r="AF34" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="AE34" s="17" t="n">
+      <c r="AG34" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="AF34" s="17" t="n">
+      <c r="AH34" s="17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10197,20 +10279,20 @@
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="A4:A25"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A1:AF1"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="S2:U2"/>
     <mergeCell ref="A26:A34"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="V2"/>
+    <mergeCell ref="A1:AH1"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="Y2:AF2"/>
+    <mergeCell ref="V2"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="X2:X3"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="W2:W3"/>
+    <mergeCell ref="Y2:AH2"/>
   </mergeCells>
   <conditionalFormatting sqref="W4:W34">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -12316,7 +12398,7 @@
         <v>3.15</v>
       </c>
       <c r="D16" s="39" t="n">
-        <v>54.93</v>
+        <v>55.94</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>15</v>
@@ -12367,7 +12449,7 @@
         <v/>
       </c>
       <c r="R16" s="16" t="n">
-        <v>54.93</v>
+        <v>55.94</v>
       </c>
     </row>
   </sheetData>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6</v>
+        <v>14.1</v>
       </c>
       <c r="D9" s="8" t="n">
         <v>3.15</v>
@@ -16996,7 +16996,11 @@
         <f>IF(C9="","FALTA CARGA",IF(C9&lt;=O9,"VERIFICA","NO VERIFICA"))</f>
         <v/>
       </c>
-      <c r="Q9" s="11" t="inlineStr"/>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>6,00 t de la planilla de la catedra mas las reacciones de VCH 03a (6,4 t) y VCH 05 (1,7 t), que apoyan en el perpendicularmente. No consta si los 6,00 t ya las incluian; se suman por ser la hipotesis conservadora. Con cualquiera de las dos lecturas el tabique usa entre el 6 y el 14 por ciento de su capacidad.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="26" t="n"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -3659,7 +3659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3678,6 +3678,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -3685,6 +3686,7 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="44" t="inlineStr">
@@ -3708,6 +3710,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="46" t="inlineStr">
@@ -3729,6 +3732,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="46" t="inlineStr">
@@ -3750,6 +3754,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="46" t="inlineStr">
@@ -3771,6 +3776,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="46" t="inlineStr">
@@ -3792,6 +3798,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="46" t="inlineStr">
@@ -3813,13 +3820,23 @@
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>ARMADURA DEL PILOTE  (planilla del Ing. Caggiano, 23-03-22)</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>5 barras del 12 longitudinales, mas espiral o6 c/15 de 20 cm de diametro, 27 vueltas, longitud teorica 16,95 m. SIN BULBO.</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="57" t="inlineStr">
@@ -3831,6 +3848,7 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="45" t="inlineStr">
@@ -3858,6 +3876,7 @@
           <t>long. hormigon</t>
         </is>
       </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="46" t="inlineStr">
@@ -3875,7 +3894,12 @@
         <v>-0.4</v>
       </c>
       <c r="E12" s="58" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>bajo cabezales de 70 cm (CBZ02 y CBZ03)</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -3894,7 +3918,12 @@
         <v>-0.35</v>
       </c>
       <c r="E13" s="58" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>bajo cabezales de 65 cm (CBZ01)</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3913,7 +3942,12 @@
         <v>-0.05</v>
       </c>
       <c r="E14" s="58" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>bajo VF de 25x35 y 20x35</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -3933,6 +3967,11 @@
       </c>
       <c r="E15" s="58" t="n">
         <v>4.4</v>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>bajo VF de 25x40</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3941,6 +3980,7 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="42" t="inlineStr">
@@ -3952,6 +3992,7 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="41" t="inlineStr">
@@ -3963,6 +4004,7 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -3970,6 +4012,7 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="57" t="inlineStr">
@@ -3981,6 +4024,7 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="42" t="inlineStr">
@@ -3992,6 +4036,7 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="42" t="inlineStr">
@@ -4003,6 +4048,7 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="42" t="inlineStr">
@@ -4014,6 +4060,7 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
@@ -4025,6 +4072,7 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="42" t="inlineStr">
@@ -4036,6 +4084,7 @@
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="42" t="inlineStr"/>
@@ -4043,6 +4092,7 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="41" t="inlineStr">
@@ -4054,6 +4104,7 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
@@ -4065,6 +4116,7 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="42" t="inlineStr">
@@ -4076,6 +4128,7 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="42" t="inlineStr">
@@ -4087,6 +4140,7 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="42" t="inlineStr"/>
@@ -4094,28 +4148,31 @@
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="42" t="inlineStr">
         <is>
-          <t>FALTA: la nota del plano remite a las planillas de cada tipo de pilote, que</t>
+          <t>Capacidad ESTRUCTURAL del pilote: con 5d12 (5,65 cm2) en 707 cm2, cuantia 0,8%,</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="42" t="inlineStr">
         <is>
-          <t>traen la armadura y quiza la carga. Si aparecen, se cierra este punto.</t>
+          <t>fi Pn = 77,4 t. La seccion de hormigon no es el limite: manda el suelo.</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="42" t="inlineStr"/>
@@ -4123,39 +4180,75 @@
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="42" t="inlineStr">
         <is>
-          <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
+          <t>FALTA todavia la capacidad geotecnica. Las planillas de armadura de pilotes no</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="42" t="inlineStr">
         <is>
-          <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
+          <t>la traen: son planillas de doblado de hierro. Ese dato esta en el estudio de suelos.</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="inlineStr">
-        <is>
-          <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
-        </is>
-      </c>
+      <c r="A37" s="42" t="inlineStr"/>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16198,7 +16291,7 @@
         <v/>
       </c>
       <c r="I9" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="10" t="n">
         <v>30</v>
@@ -16220,7 +16313,7 @@
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>Cantidad de pilotes deducida de la dimension del cabezal: 144x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 144x70 cm. Tres pilotes, no dos: la planilla de armadura declara 8 pilotes bajo cabezales de 70 cm, que son un CBZ02 y dos CBZ03. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16409,7 @@
         <v/>
       </c>
       <c r="I11" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>30</v>
@@ -16338,7 +16431,7 @@
       </c>
       <c r="O11" s="13" t="inlineStr">
         <is>
-          <t>Cantidad de pilotes deducida de la dimension del cabezal: 144x70 cm. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
+          <t>Cantidad de pilotes deducida de la dimension del cabezal: 144x70 cm. Tres pilotes, no dos: la planilla de armadura declara 8 pilotes bajo cabezales de 70 cm, que son un CBZ02 y dos CBZ03. Carga tomada de la bajada de la planilla de columnas, que esta incompleta: el valor real es mayor.</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16745,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>9</v>
+        <v>18.74</v>
       </c>
       <c r="D4" s="8" t="n">
         <v>3.15</v>
@@ -16699,7 +16792,11 @@
         <f>IF(C4="","FALTA CARGA",IF(C4&lt;=O4,"VERIFICA","NO VERIFICA"))</f>
         <v/>
       </c>
-      <c r="Q4" s="11" t="inlineStr"/>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t>9,00 t de la planilla de la catedra mas las reacciones de VI 01a (6,16 t) y VI 07a (3,58 t), que apoyan aqui. Se suman por la misma razon que en T6.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="26" t="n"/>
@@ -16709,7 +16806,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>3.15</v>
@@ -16756,7 +16853,11 @@
         <f>IF(C5="","FALTA CARGA",IF(C5&lt;=O5,"VERIFICA","NO VERIFICA"))</f>
         <v/>
       </c>
-      <c r="Q5" s="11" t="inlineStr"/>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>6,00 t de la planilla de la catedra mas la reaccion de VI 01b (2,5 t), que apoya aqui y en la COL 01 de 10x10. Se suman por la misma razon que en T6.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="26" t="n"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -7330,7 +7330,11 @@
         <f>IF(OR(M8="REVISAR",P8="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M8&lt;&gt;"REVISAR",P8&lt;&gt;"REVISAR",IF(ISNUMBER(M8),N8*PI()*(O8/10)^2/4&gt;=M8,TRUE),IF(ISNUMBER(P8),Q8*PI()*(R8/10)^2/4&gt;=P8,TRUE),IF(ISNUMBER(M8),M8&lt;=0.0163*AB8*K8,TRUE),IF(ISNUMBER(P8),P8&lt;=0.0163*AC8*K8,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F8&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J8*K8+2*PI()*(U8/10)^2/4*Datos_vigas!$B$6*K8/V8)),"NO VERIF. CORTE",IF(NOT(L8&gt;=C8*100/VLOOKUP(Y8,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X8" s="11" t="n"/>
+      <c r="X8" s="13" t="inlineStr">
+        <is>
+          <t>VI 09 le descarga 6.332 kg a 1,80 m del apoyo, practicamente al medio de sus 3,75 m. Esta viga no recibe losa, de modo que la puntual es casi toda su carga. Se superpone el momento isostatico P a b / L repartido 0,75 al tramo y 0,50 al apoyo, y la reaccion isostatica al corte.</t>
+        </is>
+      </c>
       <c r="Y8" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -7352,8 +7356,12 @@
         <f>IF(Z8="Invertida",MIN(C8*100/4,J8+16*AA8),J8)</f>
         <v/>
       </c>
-      <c r="AD8" s="10" t="n"/>
-      <c r="AE8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n">
+        <v>6332</v>
+      </c>
+      <c r="AE8" s="10" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AF8" s="10" t="n">
         <v>0</v>
       </c>
@@ -7558,7 +7566,7 @@
       </c>
       <c r="X10" s="13" t="inlineStr">
         <is>
-          <t>Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07.</t>
+          <t>Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. PENDIENTE: recibe las puntuales de VI 09 (6,3 t) y VI 08b (6,0 t) y todavia no estan cargadas, porque falta saber en que tramo y a que distancia caen. Con ambas al medio del tramo mayor el momento de tramo pasaria de 7.920 a 22.963 kgm.</t>
         </is>
       </c>
       <c r="Y10" s="10" t="inlineStr">
@@ -8141,7 +8149,11 @@
         <f>IF(OR(M15="REVISAR",P15="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M15&lt;&gt;"REVISAR",P15&lt;&gt;"REVISAR",IF(ISNUMBER(M15),N15*PI()*(O15/10)^2/4&gt;=M15,TRUE),IF(ISNUMBER(P15),Q15*PI()*(R15/10)^2/4&gt;=P15,TRUE),IF(ISNUMBER(M15),M15&lt;=0.0163*AB15*K15,TRUE),IF(ISNUMBER(P15),P15&lt;=0.0163*AC15*K15,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F15&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J15*K15+2*PI()*(U15/10)^2/4*Datos_vigas!$B$6*K15/V15)),"NO VERIF. CORTE",IF(NOT(L15&gt;=C15*100/VLOOKUP(Y15,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X15" s="11" t="n"/>
+      <c r="X15" s="13" t="inlineStr">
+        <is>
+          <t>Descarga en la COL 04 de 20x20 y en VI 06.</t>
+        </is>
+      </c>
       <c r="Y15" s="10" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -8258,7 +8270,11 @@
         <f>IF(OR(M16="REVISAR",P16="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M16&lt;&gt;"REVISAR",P16&lt;&gt;"REVISAR",IF(ISNUMBER(M16),N16*PI()*(O16/10)^2/4&gt;=M16,TRUE),IF(ISNUMBER(P16),Q16*PI()*(R16/10)^2/4&gt;=P16,TRUE),IF(ISNUMBER(M16),M16&lt;=0.0163*AB16*K16,TRUE),IF(ISNUMBER(P16),P16&lt;=0.0163*AC16*K16,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F16&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J16*K16+2*PI()*(U16/10)^2/4*Datos_vigas!$B$6*K16/V16)),"NO VERIF. CORTE",IF(NOT(L16&gt;=C16*100/VLOOKUP(Y16,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
         <v/>
       </c>
-      <c r="X16" s="11" t="n"/>
+      <c r="X16" s="13" t="inlineStr">
+        <is>
+          <t>Viga secundaria: sus dos extremos descargan en otras vigas, VI 04a y VI 06, no en columnas ni tabiques.</t>
+        </is>
+      </c>
       <c r="Y16" s="10" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
@@ -12101,7 +12117,7 @@
         <v>3.15</v>
       </c>
       <c r="D10" s="37" t="n">
-        <v>10.6</v>
+        <v>13.89</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>30</v>
@@ -12152,7 +12168,7 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>10.6</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -12296,7 +12312,7 @@
         <v>3.15</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>32.1</v>
+        <v>35.39</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>20</v>
@@ -12347,7 +12363,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>32.1</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -17127,7 +17127,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>22.43</v>
+        <v>24.03</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3.15</v>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="Q10" s="13" t="inlineStr">
         <is>
-          <t>Recibe los extremos de VI 02 (21,12 t) y de VI 17 (1,31 t). Cargas MAYORADAS, no comparables sin mas con las de T1 a T6. Es el tabique mas exigido del conjunto.</t>
+          <t>Recibe los extremos de VI 02 (21,12 t), VI 17 (1,31 t) y VI 10a (1,60 t), esta ultima alineada con el tabique, que es su continuacion. Cargas MAYORADAS, no comparables sin mas con las de T1 a T6. Es el tabique mas exigido del conjunto: 98 cm de largo tomando 24 t.</t>
         </is>
       </c>
     </row>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -17127,7 +17127,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>24.03</v>
+        <v>30.62</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3.15</v>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="Q10" s="13" t="inlineStr">
         <is>
-          <t>Recibe los extremos de VI 02 (21,12 t), VI 17 (1,31 t) y VI 10a (1,60 t), esta ultima alineada con el tabique, que es su continuacion. Cargas MAYORADAS, no comparables sin mas con las de T1 a T6. Es el tabique mas exigido del conjunto: 98 cm de largo tomando 24 t.</t>
+          <t>NO VERIFICA por poco, al 106 por ciento. Recibe VI 02 (21,12 t), VI 10b (6,60 t), VI 10a (1,59 t) y VI 17 (1,31 t): 98 cm de tabique tomando 30,6 t. La capacidad sale de la formula simplificada de muro portante, cuya reduccion por esbeltez se come dos tercios: con 12 cm y 3,15 m el coeficiente vale 0,327. Un analisis mas fino del arriostramiento real daria mas capacidad. Con 104 cm de largo verificaria.</t>
         </is>
       </c>
     </row>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -16944,7 +16944,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>5</v>
+        <v>12.52</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>3.15</v>
@@ -16993,7 +16993,7 @@
       </c>
       <c r="Q7" s="13" t="inlineStr">
         <is>
-          <t>Tabique recto: B = 12 cm es el espesor.</t>
+          <t>Tabique recto: B = 12 cm es el espesor. 5,00 t de la planilla de la catedra mas la reaccion de VI 11c (7,52 t), que apoya en el T04b del plano y en una COL 02 de 15x30. OJO: el plano distingue T04a y T04b, de 0,73 m cada uno segun el computo, mientras que la catedra tiene un solo T4 de 3,55 m: las dos numeraciones no se corresponden una a una.</t>
         </is>
       </c>
     </row>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -7531,10 +7531,10 @@
         <v/>
       </c>
       <c r="N10" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P10" s="25">
         <f>IF(NOT(ISNUMBER(I10)),"---",IF(I10&lt;=0,"---",IF(I10*100/(Datos_vigas!$B$8*AC10*K10^2*Datos_vigas!$B$5)&gt;=0.5,"REVISAR",MAX((1-SQRT(1-2*I10*100/(Datos_vigas!$B$8*AC10*K10^2*Datos_vigas!$B$5)))*AC10*K10*Datos_vigas!$B$5/Datos_vigas!$B$6,0.0033*J10*K10))))</f>
@@ -7558,7 +7558,7 @@
         <v>6</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="W10" s="11">
         <f>IF(OR(M10="REVISAR",P10="REVISAR"),"SECCION INSUF.",IF(NOT(AND(M10&lt;&gt;"REVISAR",P10&lt;&gt;"REVISAR",IF(ISNUMBER(M10),N10*PI()*(O10/10)^2/4&gt;=M10,TRUE),IF(ISNUMBER(P10),Q10*PI()*(R10/10)^2/4&gt;=P10,TRUE),IF(ISNUMBER(M10),M10&lt;=0.0163*AB10*K10,TRUE),IF(ISNUMBER(P10),P10&lt;=0.0163*AC10*K10,TRUE))),"NO VERIFICA FLEX.",IF(NOT(F10&lt;=Datos_vigas!$B$9*(0.53*SQRT(Datos_vigas!$B$5)*J10*K10+2*PI()*(U10/10)^2/4*Datos_vigas!$B$6*K10/V10)),"NO VERIF. CORTE",IF(NOT(L10&gt;=C10*100/VLOOKUP(Y10,Datos_vigas!$A$19:$E$23,5,0)),"VERIFICAR FLECHA","VERIFICA"))))</f>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="X10" s="13" t="inlineStr">
         <is>
-          <t>Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. PENDIENTE: recibe las puntuales de VI 09 (6,3 t) y VI 08b (6,0 t) y todavia no estan cargadas, porque falta saber en que tramo y a que distancia caen. Con ambas al medio del tramo mayor el momento de tramo pasaria de 7.920 a 22.963 kgm.</t>
+          <t>Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. Longitud total 14,00 m. Sobre su eje hay cuatro columnas: trabaja como viga continua de tres tramos de 4,10, 4,32 y 6,53 m. Se calcula con el mayor. Es el cuarto borde de la losa cruzada L07. VI 08b le descarga 5.954 kg a 6,00 m del extremo inferior, dentro del tramo de 6,53 m y a solo 53 cm del apoyo siguiente: aporta poco momento y mucho corte, por eso la reaccion sube de 9.764 a 15.235 kg. Se superpone el momento isostatico P a b / L repartido 0,75 al tramo y 0,50 al apoyo, y la reaccion isostatica al corte. Viga principal: recibe a VI 08b y a VI 09. VI 09 apoya a 7,95 m del extremo inferior, o sea en el tramo del medio de 4,32 m, que con esa puntual llega a 7.993 kgm y no gobierna. El tramo que gobierna es el de 6,53 m con la puntual de VI 08b.</t>
         </is>
       </c>
       <c r="Y10" s="10" t="inlineStr">
@@ -7590,8 +7590,12 @@
         <f>IF(Z10="Invertida",MIN(C10*100/4,J10+16*AA10),J10)</f>
         <v/>
       </c>
-      <c r="AD10" s="10" t="n"/>
-      <c r="AE10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n">
+        <v>5954</v>
+      </c>
+      <c r="AE10" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="AF10" s="10" t="n">
         <v>1.549</v>
       </c>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -3659,7 +3659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="B4" s="47" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="D4" s="51" t="inlineStr">
         <is>
-          <t>ESTIMADA. Falta el estudio de suelos: cambiar aca y recalcula todo.</t>
+          <t>ADOPTADA del propio diseno, NO verificada. Ver nota abajo. Cambiar aca cuando aparezca el estudio de suelos.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -4065,7 +4065,7 @@
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
         <is>
-          <t>la diferencia entre tipos es menor al 8 por ciento, por eso se adopta un unico</t>
+          <t>la diferencia entre tipos es menor al 8 por ciento, por eso se usa un unico valor</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -4077,7 +4077,7 @@
     <row r="25">
       <c r="A25" s="42" t="inlineStr">
         <is>
-          <t>valor de 12 t para todos, en lugar de uno por tipo.</t>
+          <t>para todos en lugar de uno por tipo.</t>
         </is>
       </c>
       <c r="B25" s="2" t="n"/>
@@ -4095,9 +4095,9 @@
       <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="inlineStr">
-        <is>
-          <t>LECTURA INVERSA, que es la util mientras no haya estudio de suelos:</t>
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>DE DONDE SALEN LOS 22 t QUE SE ADOPTAN, Y QUE VALOR TIENEN:</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -4109,7 +4109,7 @@
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
-          <t>con las cargas de esta planilla, para que el esquema funcione cada pilote</t>
+          <t>El calculista puso UN solo pilote bajo la columna mas cargada, que baja 21,04 t</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
@@ -4121,7 +4121,7 @@
     <row r="29">
       <c r="A29" s="42" t="inlineStr">
         <is>
-          <t>tiene que admitir del orden de 20 t. Si el estudio de suelos da menos,</t>
+          <t>de servicio. Si dimensiono asi, es porque para el ese pilote admite al menos eso.</t>
         </is>
       </c>
       <c r="B29" s="2" t="n"/>
@@ -4133,7 +4133,7 @@
     <row r="30">
       <c r="A30" s="42" t="inlineStr">
         <is>
-          <t>faltan pilotes; si da mas, el diseno esta holgado.</t>
+          <t>Se adopta 22 t, el redondeo por encima de esa solicitacion.</t>
         </is>
       </c>
       <c r="B30" s="2" t="n"/>
@@ -4153,7 +4153,7 @@
     <row r="32">
       <c r="A32" s="42" t="inlineStr">
         <is>
-          <t>Capacidad ESTRUCTURAL del pilote: con 5d12 (5,65 cm2) en 707 cm2, cuantia 0,8%,</t>
+          <t>ESTO NO ES UNA VERIFICACION. Es leer la hipotesis implicita del proyectista y</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
@@ -4165,7 +4165,7 @@
     <row r="33">
       <c r="A33" s="42" t="inlineStr">
         <is>
-          <t>fi Pn = 77,4 t. La seccion de hormigon no es el limite: manda el suelo.</t>
+          <t>adoptarla: por construccion, todos los cabezales dan verde. Sirve para completar</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
@@ -4175,7 +4175,11 @@
       <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="42" t="inlineStr"/>
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>la planilla y para dejar escrito cuanto tiene que resistir el pilote, no para</t>
+        </is>
+      </c>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
@@ -4185,7 +4189,7 @@
     <row r="35">
       <c r="A35" s="42" t="inlineStr">
         <is>
-          <t>FALTA todavia la capacidad geotecnica. Las planillas de armadura de pilotes no</t>
+          <t>afirmar que resiste. La verificacion real necesita el estudio de suelos.</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
@@ -4195,11 +4199,7 @@
       <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="inlineStr">
-        <is>
-          <t>la traen: son planillas de doblado de hierro. Ese dato esta en el estudio de suelos.</t>
-        </is>
-      </c>
+      <c r="A36" s="42" t="inlineStr"/>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n"/>
@@ -4207,7 +4207,11 @@
       <c r="F36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="inlineStr"/>
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>CONTRASTE: para llegar a 21 t con un O30 de 4,50 m hace falta una adherencia</t>
+        </is>
+      </c>
       <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n"/>
@@ -4217,7 +4221,7 @@
     <row r="38">
       <c r="A38" s="42" t="inlineStr">
         <is>
-          <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
+          <t>lateral de 4,5 a 4,8 t/m2. En los limos loessicos de la region de Rosario y Funes</t>
         </is>
       </c>
       <c r="B38" s="2" t="n"/>
@@ -4229,7 +4233,7 @@
     <row r="39">
       <c r="A39" s="42" t="inlineStr">
         <is>
-          <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
+          <t>los valores habituales van de 2 a 3 t/m2, que darian entre 10 y 14 t. O el estudio</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -4241,7 +4245,7 @@
     <row r="40">
       <c r="A40" s="42" t="inlineStr">
         <is>
-          <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
+          <t>dio un suelo mejor del tipico, o las cargas adoptadas en esta planilla estan altas,</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
@@ -4249,6 +4253,126 @@
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>o el pilote esta ajustado. Es un punto a plantear en el trabajo.</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="inlineStr"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>Capacidad ESTRUCTURAL del pilote: con 5d12 (5,65 cm2) en 707 cm2, cuantia 0,8%,</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>fi Pn = 77,4 t. La seccion de hormigon no es el limite: manda el suelo.</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>FALTA todavia la capacidad geotecnica. Las planillas de armadura de pilotes no</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
+        <is>
+          <t>la traen: son planillas de doblado de hierro. Ese dato esta en el estudio de suelos.</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Planilla 3 higrotermica'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla vigas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla vigas'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla losas'!$1:$3</definedName>
@@ -7619,7 +7619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7783,7 +7783,7 @@
     <row r="6">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>Plano: Vista Frente</t>
+          <t>Plano: Fachada Norte</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -7802,19 +7802,19 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>PA01</t>
+          <t>PV02</t>
         </is>
       </c>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="27" t="n">
-        <v>1</v>
+        <v>2.48</v>
       </c>
       <c r="D7" s="28">
         <f>IF(COUNT(B7,C7)&lt;2,"",B7*C7)</f>
         <v/>
       </c>
       <c r="E7" s="29">
-        <f>SUM(D7:D13)</f>
+        <f>SUM(D7:D11)</f>
         <v/>
       </c>
       <c r="F7" s="30">
@@ -7834,7 +7834,11 @@
       <c r="J7" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="K7" s="25" t="n"/>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
       <c r="L7" s="27" t="n"/>
       <c r="M7" s="31">
         <f>IF(OR(D7="",J7=""),"",IF(J7&lt;=G7,"CUMPLE","NO CUMPLE"))</f>
@@ -7844,12 +7848,12 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>PA02</t>
+          <t>PF03</t>
         </is>
       </c>
       <c r="B8" s="26" t="n"/>
       <c r="C8" s="27" t="n">
-        <v>0.75</v>
+        <v>2.88</v>
       </c>
       <c r="D8" s="28">
         <f>IF(COUNT(B8,C8)&lt;2,"",B8*C8)</f>
@@ -7873,7 +7877,11 @@
       <c r="J8" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="K8" s="25" t="n"/>
+      <c r="K8" s="25" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
       <c r="L8" s="27" t="n"/>
       <c r="M8" s="31">
         <f>IF(OR(D8="",J8=""),"",IF(J8&lt;=G8,"CUMPLE","NO CUMPLE"))</f>
@@ -7883,12 +7891,12 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>VA01</t>
+          <t>VA04</t>
         </is>
       </c>
       <c r="B9" s="26" t="n"/>
       <c r="C9" s="27" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="D9" s="28">
         <f>IF(COUNT(B9,C9)&lt;2,"",B9*C9)</f>
@@ -7912,7 +7920,11 @@
       <c r="J9" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="K9" s="25" t="n"/>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
       <c r="L9" s="27" t="n"/>
       <c r="M9" s="31">
         <f>IF(OR(D9="",J9=""),"",IF(J9&lt;=G9,"CUMPLE","NO CUMPLE"))</f>
@@ -7920,15 +7932,9 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>VA02</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="27" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
       <c r="D10" s="28">
         <f>IF(COUNT(B10,C10)&lt;2,"",B10*C10)</f>
         <v/>
@@ -7942,15 +7948,9 @@
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H10" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
+      <c r="H10" s="25" t="n"/>
       <c r="I10" s="25" t="n"/>
-      <c r="J10" s="27" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="J10" s="27" t="n"/>
       <c r="K10" s="25" t="n"/>
       <c r="L10" s="27" t="n"/>
       <c r="M10" s="31">
@@ -7959,215 +7959,190 @@
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>VA03</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="n"/>
-      <c r="C11" s="27" t="n">
+      <c r="A11" s="33" t="n"/>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="35">
+        <f>IF(COUNT(B11,C11)&lt;2,"",B11*C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="37">
+        <f>IF(OR(D11="",$E$7=""),"",D11/$E$7)</f>
+        <v/>
+      </c>
+      <c r="G11" s="35">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H11" s="33" t="n"/>
+      <c r="I11" s="33" t="n"/>
+      <c r="J11" s="34" t="n"/>
+      <c r="K11" s="33" t="n"/>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="38">
+        <f>IF(OR(D11="",J11=""),"",IF(J11&lt;=G11,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Fachada Sur</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>VA01</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="27" t="n">
         <v>0.75</v>
       </c>
-      <c r="D11" s="28">
-        <f>IF(COUNT(B11,C11)&lt;2,"",B11*C11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="30">
-        <f>IF(OR(D11="",$E$7=""),"",D11/$E$7)</f>
-        <v/>
-      </c>
-      <c r="G11" s="28">
+      <c r="D13" s="28">
+        <f>IF(COUNT(B13,C13)&lt;2,"",B13*C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>SUM(D13:D15)</f>
+        <v/>
+      </c>
+      <c r="F13" s="30">
+        <f>IF(OR(D13="",$E$13=""),"",D13/$E$13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H13" s="25" t="inlineStr">
         <is>
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="27" t="n">
+      <c r="I13" s="25" t="n"/>
+      <c r="J13" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="31">
-        <f>IF(OR(D11="",J11=""),"",IF(J11&lt;=G11,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="28">
-        <f>IF(COUNT(B12,C12)&lt;2,"",B12*C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="30">
-        <f>IF(OR(D12="",$E$7=""),"",D12/$E$7)</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="L13" s="27" t="n"/>
+      <c r="M13" s="31">
+        <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="25" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="28">
+        <f>IF(COUNT(B14,C14)&lt;2,"",B14*C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="32" t="n"/>
+      <c r="F14" s="30">
+        <f>IF(OR(D14="",$E$13=""),"",D14/$E$13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="27" t="n"/>
-      <c r="M12" s="31">
-        <f>IF(OR(D12="",J12=""),"",IF(J12&lt;=G12,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="34" t="n"/>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="35">
-        <f>IF(COUNT(B13,C13)&lt;2,"",B13*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="37">
-        <f>IF(OR(D13="",$E$7=""),"",D13/$E$7)</f>
-        <v/>
-      </c>
-      <c r="G13" s="35">
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="27" t="n"/>
+      <c r="M14" s="31">
+        <f>IF(OR(D14="",J14=""),"",IF(J14&lt;=G14,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="33" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="35">
+        <f>IF(COUNT(B15,C15)&lt;2,"",B15*C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="37">
+        <f>IF(OR(D15="",$E$13=""),"",D15/$E$13)</f>
+        <v/>
+      </c>
+      <c r="G15" s="35">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="33" t="n"/>
-      <c r="J13" s="34" t="n"/>
-      <c r="K13" s="33" t="n"/>
-      <c r="L13" s="34" t="n"/>
-      <c r="M13" s="38">
-        <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Vista Contrafachada</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>PF01</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="n"/>
-      <c r="C15" s="27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="D15" s="28">
-        <f>IF(COUNT(B15,C15)&lt;2,"",B15*C15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="29">
-        <f>SUM(D15:D19)</f>
-        <v/>
-      </c>
-      <c r="F15" s="30">
-        <f>IF(OR(D15="",$E$15=""),"",D15/$E$15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="28">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H15" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="31">
+      <c r="H15" s="33" t="n"/>
+      <c r="I15" s="33" t="n"/>
+      <c r="J15" s="34" t="n"/>
+      <c r="K15" s="33" t="n"/>
+      <c r="L15" s="34" t="n"/>
+      <c r="M15" s="38">
         <f>IF(OR(D15="",J15=""),"",IF(J15&lt;=G15,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>PF02</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D16" s="28">
-        <f>IF(COUNT(B16,C16)&lt;2,"",B16*C16)</f>
-        <v/>
-      </c>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="30">
-        <f>IF(OR(D16="",$E$15=""),"",D16/$E$15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="28">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="31">
-        <f>IF(OR(D16="",J16=""),"",IF(J16&lt;=G16,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Fachada Este</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>PF03</t>
+          <t>PA01</t>
         </is>
       </c>
       <c r="B17" s="26" t="n"/>
       <c r="C17" s="27" t="n">
-        <v>2.88</v>
+        <v>1</v>
       </c>
       <c r="D17" s="28">
         <f>IF(COUNT(B17,C17)&lt;2,"",B17*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="32" t="n"/>
+      <c r="E17" s="29">
+        <f>SUM(D17:D22)</f>
+        <v/>
+      </c>
       <c r="F17" s="30">
-        <f>IF(OR(D17="",$E$15=""),"",D17/$E$15)</f>
+        <f>IF(OR(D17="",$E$17=""),"",D17/$E$17)</f>
         <v/>
       </c>
       <c r="G17" s="28">
@@ -8183,7 +8158,11 @@
       <c r="J17" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="K17" s="25" t="n"/>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
       <c r="L17" s="27" t="n"/>
       <c r="M17" s="31">
         <f>IF(OR(D17="",J17=""),"",IF(J17&lt;=G17,"CUMPLE","NO CUMPLE"))</f>
@@ -8191,26 +8170,42 @@
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="27" t="n"/>
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>PF04</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="27" t="n">
+        <v>2.7</v>
+      </c>
       <c r="D18" s="28">
         <f>IF(COUNT(B18,C18)&lt;2,"",B18*C18)</f>
         <v/>
       </c>
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="30">
-        <f>IF(OR(D18="",$E$15=""),"",D18/$E$15)</f>
+        <f>IF(OR(D18="",$E$17=""),"",D18/$E$17)</f>
         <v/>
       </c>
       <c r="G18" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H18" s="25" t="n"/>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
       <c r="I18" s="25" t="n"/>
-      <c r="J18" s="27" t="n"/>
-      <c r="K18" s="25" t="n"/>
+      <c r="J18" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K18" s="25" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
       <c r="L18" s="27" t="n"/>
       <c r="M18" s="31">
         <f>IF(OR(D18="",J18=""),"",IF(J18&lt;=G18,"CUMPLE","NO CUMPLE"))</f>
@@ -8218,86 +8213,111 @@
       </c>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="33" t="n"/>
-      <c r="B19" s="34" t="n"/>
-      <c r="C19" s="34" t="n"/>
-      <c r="D19" s="35">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>VA05</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="n"/>
+      <c r="C19" s="27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D19" s="28">
         <f>IF(COUNT(B19,C19)&lt;2,"",B19*C19)</f>
         <v/>
       </c>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="37">
-        <f>IF(OR(D19="",$E$15=""),"",D19/$E$15)</f>
-        <v/>
-      </c>
-      <c r="G19" s="35">
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="30">
+        <f>IF(OR(D19="",$E$17=""),"",D19/$E$17)</f>
+        <v/>
+      </c>
+      <c r="G19" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="33" t="n"/>
-      <c r="J19" s="34" t="n"/>
-      <c r="K19" s="33" t="n"/>
-      <c r="L19" s="34" t="n"/>
-      <c r="M19" s="38">
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I19" s="25" t="n"/>
+      <c r="J19" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K19" s="25" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="L19" s="27" t="n"/>
+      <c r="M19" s="31">
         <f>IF(OR(D19="",J19=""),"",IF(J19&lt;=G19,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Vista Lateral Izquierda</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>PV04</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D20" s="28">
+        <f>IF(COUNT(B20,C20)&lt;2,"",B20*C20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="30">
+        <f>IF(OR(D20="",$E$17=""),"",D20/$E$17)</f>
+        <v/>
+      </c>
+      <c r="G20" s="28">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K20" s="25" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="L20" s="27" t="n"/>
+      <c r="M20" s="31">
+        <f>IF(OR(D20="",J20=""),"",IF(J20&lt;=G20,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>PF04</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="27" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
       <c r="D21" s="28">
         <f>IF(COUNT(B21,C21)&lt;2,"",B21*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="29">
-        <f>SUM(D21:D26)</f>
-        <v/>
-      </c>
+      <c r="E21" s="32" t="n"/>
       <c r="F21" s="30">
-        <f>IF(OR(D21="",$E$21=""),"",D21/$E$21)</f>
+        <f>IF(OR(D21="",$E$17=""),"",D21/$E$17)</f>
         <v/>
       </c>
       <c r="G21" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H21" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
+      <c r="H21" s="25" t="n"/>
       <c r="I21" s="25" t="n"/>
-      <c r="J21" s="27" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="J21" s="27" t="n"/>
       <c r="K21" s="25" t="n"/>
       <c r="L21" s="27" t="n"/>
       <c r="M21" s="31">
@@ -8306,82 +8326,50 @@
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>PV01</t>
-        </is>
-      </c>
-      <c r="B22" s="26" t="n"/>
-      <c r="C22" s="27" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="D22" s="28">
+      <c r="A22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="35">
         <f>IF(COUNT(B22,C22)&lt;2,"",B22*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="30">
-        <f>IF(OR(D22="",$E$21=""),"",D22/$E$21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="28">
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="37">
+        <f>IF(OR(D22="",$E$17=""),"",D22/$E$17)</f>
+        <v/>
+      </c>
+      <c r="G22" s="35">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H22" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="27" t="n"/>
-      <c r="M22" s="31">
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="33" t="n"/>
+      <c r="J22" s="34" t="n"/>
+      <c r="K22" s="33" t="n"/>
+      <c r="L22" s="34" t="n"/>
+      <c r="M22" s="38">
         <f>IF(OR(D22="",J22=""),"",IF(J22&lt;=G22,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>PV02</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="D23" s="28">
-        <f>IF(COUNT(B23,C23)&lt;2,"",B23*C23)</f>
-        <v/>
-      </c>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="30">
-        <f>IF(OR(D23="",$E$21=""),"",D23/$E$21)</f>
-        <v/>
-      </c>
-      <c r="G23" s="28">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H23" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="31">
-        <f>IF(OR(D23="",J23=""),"",IF(J23&lt;=G23,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Fachada Oeste</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
@@ -8397,9 +8385,12 @@
         <f>IF(COUNT(B24,C24)&lt;2,"",B24*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="32" t="n"/>
+      <c r="E24" s="29">
+        <f>SUM(D24:D30)</f>
+        <v/>
+      </c>
       <c r="F24" s="30">
-        <f>IF(OR(D24="",$E$21=""),"",D24/$E$21)</f>
+        <f>IF(OR(D24="",$E$24=""),"",D24/$E$24)</f>
         <v/>
       </c>
       <c r="G24" s="28">
@@ -8415,7 +8406,11 @@
       <c r="J24" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="K24" s="25" t="n"/>
+      <c r="K24" s="25" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
       <c r="L24" s="27" t="n"/>
       <c r="M24" s="31">
         <f>IF(OR(D24="",J24=""),"",IF(J24&lt;=G24,"CUMPLE","NO CUMPLE"))</f>
@@ -8423,26 +8418,42 @@
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="27" t="n"/>
-      <c r="C25" s="27" t="n"/>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>VA02</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="27" t="n">
+        <v>0.75</v>
+      </c>
       <c r="D25" s="28">
         <f>IF(COUNT(B25,C25)&lt;2,"",B25*C25)</f>
         <v/>
       </c>
       <c r="E25" s="32" t="n"/>
       <c r="F25" s="30">
-        <f>IF(OR(D25="",$E$21=""),"",D25/$E$21)</f>
+        <f>IF(OR(D25="",$E$24=""),"",D25/$E$24)</f>
         <v/>
       </c>
       <c r="G25" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H25" s="25" t="n"/>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
       <c r="I25" s="25" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="25" t="n"/>
+      <c r="J25" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K25" s="25" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
       <c r="L25" s="27" t="n"/>
       <c r="M25" s="31">
         <f>IF(OR(D25="",J25=""),"",IF(J25&lt;=G25,"CUMPLE","NO CUMPLE"))</f>
@@ -8450,71 +8461,108 @@
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="33" t="n"/>
-      <c r="B26" s="34" t="n"/>
-      <c r="C26" s="34" t="n"/>
-      <c r="D26" s="35">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D26" s="28">
         <f>IF(COUNT(B26,C26)&lt;2,"",B26*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="36" t="n"/>
-      <c r="F26" s="37">
-        <f>IF(OR(D26="",$E$21=""),"",D26/$E$21)</f>
-        <v/>
-      </c>
-      <c r="G26" s="35">
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="30">
+        <f>IF(OR(D26="",$E$24=""),"",D26/$E$24)</f>
+        <v/>
+      </c>
+      <c r="G26" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H26" s="33" t="n"/>
-      <c r="I26" s="33" t="n"/>
-      <c r="J26" s="34" t="n"/>
-      <c r="K26" s="33" t="n"/>
-      <c r="L26" s="34" t="n"/>
-      <c r="M26" s="38">
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K26" s="25" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="L26" s="27" t="n"/>
+      <c r="M26" s="31">
         <f>IF(OR(D26="",J26=""),"",IF(J26&lt;=G26,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Vista Lateral Derecha</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>VA03</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D27" s="28">
+        <f>IF(COUNT(B27,C27)&lt;2,"",B27*C27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="30">
+        <f>IF(OR(D27="",$E$24=""),"",D27/$E$24)</f>
+        <v/>
+      </c>
+      <c r="G27" s="28">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I27" s="25" t="n"/>
+      <c r="J27" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K27" s="25" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="L27" s="27" t="n"/>
+      <c r="M27" s="31">
+        <f>IF(OR(D27="",J27=""),"",IF(J27&lt;=G27,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>VA04</t>
+          <t>PF05</t>
         </is>
       </c>
       <c r="B28" s="26" t="n"/>
       <c r="C28" s="27" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="D28" s="28">
         <f>IF(COUNT(B28,C28)&lt;2,"",B28*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="29">
-        <f>SUM(D28:D34)</f>
-        <v/>
-      </c>
+      <c r="E28" s="32" t="n"/>
       <c r="F28" s="30">
-        <f>IF(OR(D28="",$E$28=""),"",D28/$E$28)</f>
+        <f>IF(OR(D28="",$E$24=""),"",D28/$E$24)</f>
         <v/>
       </c>
       <c r="G28" s="28">
@@ -8530,7 +8578,11 @@
       <c r="J28" s="27" t="n">
         <v>2.8</v>
       </c>
-      <c r="K28" s="25" t="n"/>
+      <c r="K28" s="25" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
       <c r="L28" s="27" t="n"/>
       <c r="M28" s="31">
         <f>IF(OR(D28="",J28=""),"",IF(J28&lt;=G28,"CUMPLE","NO CUMPLE"))</f>
@@ -8538,37 +8590,25 @@
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>VA05</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n"/>
-      <c r="C29" s="27" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="A29" s="25" t="n"/>
+      <c r="B29" s="27" t="n"/>
+      <c r="C29" s="27" t="n"/>
       <c r="D29" s="28">
         <f>IF(COUNT(B29,C29)&lt;2,"",B29*C29)</f>
         <v/>
       </c>
       <c r="E29" s="32" t="n"/>
       <c r="F29" s="30">
-        <f>IF(OR(D29="",$E$28=""),"",D29/$E$28)</f>
+        <f>IF(OR(D29="",$E$24=""),"",D29/$E$24)</f>
         <v/>
       </c>
       <c r="G29" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H29" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
+      <c r="H29" s="25" t="n"/>
       <c r="I29" s="25" t="n"/>
-      <c r="J29" s="27" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="J29" s="27" t="n"/>
       <c r="K29" s="25" t="n"/>
       <c r="L29" s="27" t="n"/>
       <c r="M29" s="31">
@@ -8577,100 +8617,71 @@
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>PF05</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D30" s="28">
+      <c r="A30" s="33" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="35">
         <f>IF(COUNT(B30,C30)&lt;2,"",B30*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="30">
-        <f>IF(OR(D30="",$E$28=""),"",D30/$E$28)</f>
-        <v/>
-      </c>
-      <c r="G30" s="28">
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="37">
+        <f>IF(OR(D30="",$E$24=""),"",D30/$E$24)</f>
+        <v/>
+      </c>
+      <c r="G30" s="35">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H30" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K30" s="25" t="n"/>
-      <c r="L30" s="27" t="n"/>
-      <c r="M30" s="31">
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="34" t="n"/>
+      <c r="K30" s="33" t="n"/>
+      <c r="L30" s="34" t="n"/>
+      <c r="M30" s="38">
         <f>IF(OR(D30="",J30=""),"",IF(J30&lt;=G30,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>PV04</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="D31" s="28">
-        <f>IF(COUNT(B31,C31)&lt;2,"",B31*C31)</f>
-        <v/>
-      </c>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="30">
-        <f>IF(OR(D31="",$E$28=""),"",D31/$E$28)</f>
-        <v/>
-      </c>
-      <c r="G31" s="28">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H31" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I31" s="25" t="n"/>
-      <c r="J31" s="27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K31" s="25" t="n"/>
-      <c r="L31" s="27" t="n"/>
-      <c r="M31" s="31">
-        <f>IF(OR(D31="",J31=""),"",IF(J31&lt;=G31,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Patio interno (orientacion a confirmar)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>PV04 (2)</t>
+          <t>PF01</t>
         </is>
       </c>
       <c r="B32" s="26" t="n"/>
       <c r="C32" s="27" t="n">
-        <v>1.5</v>
+        <v>3.55</v>
       </c>
       <c r="D32" s="28">
         <f>IF(COUNT(B32,C32)&lt;2,"",B32*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="32" t="n"/>
+      <c r="E32" s="29">
+        <f>SUM(D32:D37)</f>
+        <v/>
+      </c>
       <c r="F32" s="30">
-        <f>IF(OR(D32="",$E$28=""),"",D32/$E$28)</f>
+        <f>IF(OR(D32="",$E$32=""),"",D32/$E$32)</f>
         <v/>
       </c>
       <c r="G32" s="28">
@@ -8694,25 +8705,37 @@
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="27" t="n"/>
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>PF02</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="27" t="n">
+        <v>3.75</v>
+      </c>
       <c r="D33" s="28">
         <f>IF(COUNT(B33,C33)&lt;2,"",B33*C33)</f>
         <v/>
       </c>
       <c r="E33" s="32" t="n"/>
       <c r="F33" s="30">
-        <f>IF(OR(D33="",$E$28=""),"",D33/$E$28)</f>
+        <f>IF(OR(D33="",$E$32=""),"",D33/$E$32)</f>
         <v/>
       </c>
       <c r="G33" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H33" s="25" t="n"/>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
       <c r="I33" s="25" t="n"/>
-      <c r="J33" s="27" t="n"/>
+      <c r="J33" s="27" t="n">
+        <v>2.8</v>
+      </c>
       <c r="K33" s="25" t="n"/>
       <c r="L33" s="27" t="n"/>
       <c r="M33" s="31">
@@ -8721,91 +8744,139 @@
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="33" t="n"/>
-      <c r="B34" s="34" t="n"/>
-      <c r="C34" s="34" t="n"/>
-      <c r="D34" s="35">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>PV01</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="27" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D34" s="28">
         <f>IF(COUNT(B34,C34)&lt;2,"",B34*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="37">
-        <f>IF(OR(D34="",$E$28=""),"",D34/$E$28)</f>
-        <v/>
-      </c>
-      <c r="G34" s="35">
+      <c r="E34" s="32" t="n"/>
+      <c r="F34" s="30">
+        <f>IF(OR(D34="",$E$32=""),"",D34/$E$32)</f>
+        <v/>
+      </c>
+      <c r="G34" s="28">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="34" t="n"/>
-      <c r="K34" s="33" t="n"/>
-      <c r="L34" s="34" t="n"/>
-      <c r="M34" s="38">
+      <c r="H34" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="27" t="n"/>
+      <c r="M34" s="31">
         <f>IF(OR(D34="",J34=""),"",IF(J34&lt;=G34,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="39" t="inlineStr">
-        <is>
-          <t>COMO SE COMPLETA</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="40" t="inlineStr">
-        <is>
-          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>PV04 (2)</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D35" s="28">
+        <f>IF(COUNT(B35,C35)&lt;2,"",B35*C35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="30">
+        <f>IF(OR(D35="",$E$32=""),"",D35/$E$32)</f>
+        <v/>
+      </c>
+      <c r="G35" s="28">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="n"/>
+      <c r="J35" s="27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K35" s="25" t="n"/>
+      <c r="L35" s="27" t="n"/>
+      <c r="M35" s="31">
+        <f>IF(OR(D35="",J35=""),"",IF(J35&lt;=G35,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="27" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="28">
+        <f>IF(COUNT(B36,C36)&lt;2,"",B36*C36)</f>
+        <v/>
+      </c>
+      <c r="E36" s="32" t="n"/>
+      <c r="F36" s="30">
+        <f>IF(OR(D36="",$E$32=""),"",D36/$E$32)</f>
+        <v/>
+      </c>
+      <c r="G36" s="28">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="27" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="27" t="n"/>
+      <c r="M36" s="31">
+        <f>IF(OR(D36="",J36=""),"",IF(J36&lt;=G36,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="33" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="35">
+        <f>IF(COUNT(B37,C37)&lt;2,"",B37*C37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="36" t="n"/>
+      <c r="F37" s="37">
+        <f>IF(OR(D37="",$E$32=""),"",D37/$E$32)</f>
+        <v/>
+      </c>
+      <c r="G37" s="35">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H37" s="33" t="n"/>
+      <c r="I37" s="33" t="n"/>
+      <c r="J37" s="34" t="n"/>
+      <c r="K37" s="33" t="n"/>
+      <c r="L37" s="34" t="n"/>
+      <c r="M37" s="38">
+        <f>IF(OR(D37="",J37=""),"",IF(J37&lt;=G37,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="40" t="inlineStr">
-        <is>
-          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n"/>
@@ -8820,9 +8891,9 @@
       <c r="M38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="40" t="inlineStr">
-        <is>
-          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>COMO SE COMPLETA</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -8841,7 +8912,7 @@
     <row r="40">
       <c r="A40" s="40" t="inlineStr">
         <is>
-          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
+          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
@@ -8860,7 +8931,7 @@
     <row r="41">
       <c r="A41" s="40" t="inlineStr">
         <is>
-          <t>Orientacion y factor de exposicion solar: el factor depende de la orientacion y de la proteccion.</t>
+          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
         </is>
       </c>
       <c r="B41" s="2" t="n"/>
@@ -8877,7 +8948,11 @@
       <c r="M41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="40" t="inlineStr"/>
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
+        </is>
+      </c>
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n"/>
@@ -8894,7 +8969,7 @@
     <row r="43">
       <c r="A43" s="40" t="inlineStr">
         <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
         </is>
       </c>
       <c r="B43" s="2" t="n"/>
@@ -8913,7 +8988,7 @@
     <row r="44">
       <c r="A44" s="40" t="inlineStr">
         <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+          <t>Orientacion y factor de exposicion solar: el factor depende de la orientacion y de la proteccion.</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
@@ -8947,7 +9022,7 @@
     <row r="46">
       <c r="A46" s="40" t="inlineStr">
         <is>
-          <t>FALTA, y esta marcado en naranja: la ALTURA de cada vano. La planilla de carpinterias acota</t>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -8966,7 +9041,7 @@
     <row r="47">
       <c r="A47" s="40" t="inlineStr">
         <is>
-          <t>el nivel de dintel (2,52 / 2,15 / 2,10) y el cielorraso (3,00), pero no la altura libre del vano,</t>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -8983,11 +9058,7 @@
       <c r="M47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="40" t="inlineStr">
-        <is>
-          <t>asi que no se puede deducir sin el nivel de antepecho de cada abertura.</t>
-        </is>
-      </c>
+      <c r="A48" s="40" t="inlineStr"/>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n"/>
@@ -9002,7 +9073,11 @@
       <c r="M48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="40" t="inlineStr"/>
+      <c r="A49" s="40" t="inlineStr">
+        <is>
+          <t>FALTA, y esta marcado en naranja: la ALTURA de cada vano. La planilla de carpinterias acota</t>
+        </is>
+      </c>
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n"/>
@@ -9019,7 +9094,7 @@
     <row r="50">
       <c r="A50" s="40" t="inlineStr">
         <is>
-          <t>FALTA tambien la ORIENTACION de cada plano: no hay flecha de norte en la documentacion.</t>
+          <t>el nivel de dintel (2,52 / 2,15 / 2,10) y el cielorraso (3,00), pero no la altura libre del vano,</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9038,7 +9113,7 @@
     <row r="51">
       <c r="A51" s="40" t="inlineStr">
         <is>
-          <t>El plano rotula Dormitorio Norte y Dormitorio Sur, pero eso no alcanza para fijar las cuatro vistas.</t>
+          <t>asi que no se puede deducir sin el nivel de antepecho de cada abertura.</t>
         </is>
       </c>
       <c r="B51" s="2" t="n"/>
@@ -9055,11 +9130,7 @@
       <c r="M51" s="2" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="40" t="inlineStr">
-        <is>
-          <t>El agrupamiento por vista que se uso aca es PROVISORIO: se armo por el espacio exterior al que</t>
-        </is>
-      </c>
+      <c r="A52" s="40" t="inlineStr"/>
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n"/>
@@ -9076,7 +9147,7 @@
     <row r="53">
       <c r="A53" s="40" t="inlineStr">
         <is>
-          <t>da cada abertura (Patio / Patio interno). Mover las filas de bloque si corresponde.</t>
+          <t>ORIENTACION: el simbolo de norte del plano de plantas (flecha con arco, arriba a la derecha)</t>
         </is>
       </c>
       <c r="B53" s="2" t="n"/>
@@ -9093,7 +9164,11 @@
       <c r="M53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="40" t="inlineStr"/>
+      <c r="A54" s="40" t="inlineStr">
+        <is>
+          <t>apunta hacia la derecha de la hoja. Entonces: derecha = Norte, izquierda = Sur, abajo = Este,</t>
+        </is>
+      </c>
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n"/>
@@ -9110,7 +9185,7 @@
     <row r="55">
       <c r="A55" s="40" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>arriba = Oeste. Coincide con los rotulos Dormitorio Norte y Dormitorio Sur del plano.</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9127,7 +9202,11 @@
       <c r="M55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="40" t="inlineStr"/>
+      <c r="A56" s="40" t="inlineStr">
+        <is>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta.</t>
+        </is>
+      </c>
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
@@ -9144,7 +9223,7 @@
     <row r="57">
       <c r="A57" s="40" t="inlineStr">
         <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+          <t>Las tres aberturas que dan al patio interno quedan en un bloque aparte: hay que confirmar</t>
         </is>
       </c>
       <c r="B57" s="2" t="n"/>
@@ -9163,7 +9242,7 @@
     <row r="58">
       <c r="A58" s="40" t="inlineStr">
         <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+          <t>a que lado del patio dan antes de asignarles orientacion y factor de exposicion solar.</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9180,11 +9259,7 @@
       <c r="M58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="40" t="inlineStr">
-        <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
-        </is>
-      </c>
+      <c r="A59" s="40" t="inlineStr"/>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n"/>
@@ -9198,22 +9273,115 @@
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
     </row>
+    <row r="60">
+      <c r="A60" s="40" t="inlineStr">
+        <is>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="40" t="inlineStr"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="40" t="inlineStr">
+        <is>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="40" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="40" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A14:M14"/>
+  <mergeCells count="14">
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E32:E37"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A31:M31"/>
     <mergeCell ref="A6:M6"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="E28:E34"/>
+    <mergeCell ref="A12:M12"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="E7:E13"/>
-    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="E24:E30"/>
+    <mergeCell ref="A16:M16"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="M6:M34">
+  <conditionalFormatting sqref="M6:M37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"CUMPLE"</formula>
     </cfRule>
@@ -9222,13 +9390,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H6:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$8:$A$15</formula1>
     </dataValidation>
-    <dataValidation sqref="I6:I34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6:I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$19:$A$25</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Norte,Sur,Este,Oeste,Noreste,Noroeste,Sudeste,Sudoeste,Horizontal"</formula1>
     </dataValidation>
   </dataValidations>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -331,9 +331,6 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -364,6 +361,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7619,7 +7619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7805,23 +7805,25 @@
           <t>PV02</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n"/>
-      <c r="C7" s="27" t="n">
+      <c r="B7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="26" t="n">
         <v>2.48</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="27">
         <f>IF(COUNT(B7,C7)&lt;2,"",B7*C7)</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="28">
         <f>SUM(D7:D11)</f>
         <v/>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <f>IF(OR(D7="",$E$7=""),"",D7/$E$7)</f>
         <v/>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -7831,7 +7833,7 @@
         </is>
       </c>
       <c r="I7" s="25" t="n"/>
-      <c r="J7" s="27" t="n">
+      <c r="J7" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K7" s="25" t="inlineStr">
@@ -7839,8 +7841,8 @@
           <t>Norte</t>
         </is>
       </c>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="31">
+      <c r="L7" s="26" t="n"/>
+      <c r="M7" s="30">
         <f>IF(OR(D7="",J7=""),"",IF(J7&lt;=G7,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -7851,20 +7853,22 @@
           <t>PF03</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n"/>
-      <c r="C8" s="27" t="n">
+      <c r="B8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="26" t="n">
         <v>2.88</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
         <f>IF(COUNT(B8,C8)&lt;2,"",B8*C8)</f>
         <v/>
       </c>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="30">
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="29">
         <f>IF(OR(D8="",$E$7=""),"",D8/$E$7)</f>
         <v/>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -7874,7 +7878,7 @@
         </is>
       </c>
       <c r="I8" s="25" t="n"/>
-      <c r="J8" s="27" t="n">
+      <c r="J8" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K8" s="25" t="inlineStr">
@@ -7882,8 +7886,8 @@
           <t>Norte</t>
         </is>
       </c>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="31">
+      <c r="L8" s="26" t="n"/>
+      <c r="M8" s="30">
         <f>IF(OR(D8="",J8=""),"",IF(J8&lt;=G8,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -7894,20 +7898,22 @@
           <t>VA04</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n"/>
-      <c r="C9" s="27" t="n">
+      <c r="B9" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C9" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <f>IF(COUNT(B9,C9)&lt;2,"",B9*C9)</f>
         <v/>
       </c>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="30">
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="29">
         <f>IF(OR(D9="",$E$7=""),"",D9/$E$7)</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -7917,7 +7923,7 @@
         </is>
       </c>
       <c r="I9" s="25" t="n"/>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K9" s="25" t="inlineStr">
@@ -7925,62 +7931,62 @@
           <t>Norte</t>
         </is>
       </c>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="31">
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="30">
         <f>IF(OR(D9="",J9=""),"",IF(J9&lt;=G9,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="25" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="28">
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="27">
         <f>IF(COUNT(B10,C10)&lt;2,"",B10*C10)</f>
         <v/>
       </c>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="30">
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="29">
         <f>IF(OR(D10="",$E$7=""),"",D10/$E$7)</f>
         <v/>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
       <c r="H10" s="25" t="n"/>
       <c r="I10" s="25" t="n"/>
-      <c r="J10" s="27" t="n"/>
+      <c r="J10" s="26" t="n"/>
       <c r="K10" s="25" t="n"/>
-      <c r="L10" s="27" t="n"/>
-      <c r="M10" s="31">
+      <c r="L10" s="26" t="n"/>
+      <c r="M10" s="30">
         <f>IF(OR(D10="",J10=""),"",IF(J10&lt;=G10,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="34" t="n"/>
-      <c r="C11" s="34" t="n"/>
-      <c r="D11" s="35">
+      <c r="A11" s="32" t="n"/>
+      <c r="B11" s="33" t="n"/>
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="34">
         <f>IF(COUNT(B11,C11)&lt;2,"",B11*C11)</f>
         <v/>
       </c>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="37">
+      <c r="E11" s="35" t="n"/>
+      <c r="F11" s="36">
         <f>IF(OR(D11="",$E$7=""),"",D11/$E$7)</f>
         <v/>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H11" s="33" t="n"/>
-      <c r="I11" s="33" t="n"/>
-      <c r="J11" s="34" t="n"/>
-      <c r="K11" s="33" t="n"/>
-      <c r="L11" s="34" t="n"/>
-      <c r="M11" s="38">
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="33" t="n"/>
+      <c r="K11" s="32" t="n"/>
+      <c r="L11" s="33" t="n"/>
+      <c r="M11" s="37">
         <f>IF(OR(D11="",J11=""),"",IF(J11&lt;=G11,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8010,23 +8016,25 @@
           <t>VA01</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="27" t="n">
+      <c r="B13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <f>IF(COUNT(B13,C13)&lt;2,"",B13*C13)</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="28">
         <f>SUM(D13:D15)</f>
         <v/>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <f>IF(OR(D13="",$E$13=""),"",D13/$E$13)</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8036,7 +8044,7 @@
         </is>
       </c>
       <c r="I13" s="25" t="n"/>
-      <c r="J13" s="27" t="n">
+      <c r="J13" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K13" s="25" t="inlineStr">
@@ -8044,62 +8052,62 @@
           <t>Sur</t>
         </is>
       </c>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="31">
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="30">
         <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="25" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="28">
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="27">
         <f>IF(COUNT(B14,C14)&lt;2,"",B14*C14)</f>
         <v/>
       </c>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="30">
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="29">
         <f>IF(OR(D14="",$E$13=""),"",D14/$E$13)</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
       <c r="H14" s="25" t="n"/>
       <c r="I14" s="25" t="n"/>
-      <c r="J14" s="27" t="n"/>
+      <c r="J14" s="26" t="n"/>
       <c r="K14" s="25" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="31">
+      <c r="L14" s="26" t="n"/>
+      <c r="M14" s="30">
         <f>IF(OR(D14="",J14=""),"",IF(J14&lt;=G14,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="33" t="n"/>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="35">
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="33" t="n"/>
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="34">
         <f>IF(COUNT(B15,C15)&lt;2,"",B15*C15)</f>
         <v/>
       </c>
-      <c r="E15" s="36" t="n"/>
-      <c r="F15" s="37">
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="36">
         <f>IF(OR(D15="",$E$13=""),"",D15/$E$13)</f>
         <v/>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="34" t="n"/>
-      <c r="K15" s="33" t="n"/>
-      <c r="L15" s="34" t="n"/>
-      <c r="M15" s="38">
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="32" t="n"/>
+      <c r="J15" s="33" t="n"/>
+      <c r="K15" s="32" t="n"/>
+      <c r="L15" s="33" t="n"/>
+      <c r="M15" s="37">
         <f>IF(OR(D15="",J15=""),"",IF(J15&lt;=G15,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8129,23 +8137,25 @@
           <t>PA01</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="27" t="n">
+      <c r="B17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>IF(COUNT(B17,C17)&lt;2,"",B17*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="28">
         <f>SUM(D17:D22)</f>
         <v/>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <f>IF(OR(D17="",$E$17=""),"",D17/$E$17)</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8155,7 +8165,7 @@
         </is>
       </c>
       <c r="I17" s="25" t="n"/>
-      <c r="J17" s="27" t="n">
+      <c r="J17" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K17" s="25" t="inlineStr">
@@ -8163,8 +8173,8 @@
           <t>Este</t>
         </is>
       </c>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="31">
+      <c r="L17" s="26" t="n"/>
+      <c r="M17" s="30">
         <f>IF(OR(D17="",J17=""),"",IF(J17&lt;=G17,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8175,20 +8185,20 @@
           <t>PF04</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="27" t="n">
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="26" t="n">
         <v>2.7</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f>IF(COUNT(B18,C18)&lt;2,"",B18*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="30">
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="29">
         <f>IF(OR(D18="",$E$17=""),"",D18/$E$17)</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8198,7 +8208,7 @@
         </is>
       </c>
       <c r="I18" s="25" t="n"/>
-      <c r="J18" s="27" t="n">
+      <c r="J18" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K18" s="25" t="inlineStr">
@@ -8206,8 +8216,8 @@
           <t>Este</t>
         </is>
       </c>
-      <c r="L18" s="27" t="n"/>
-      <c r="M18" s="31">
+      <c r="L18" s="26" t="n"/>
+      <c r="M18" s="30">
         <f>IF(OR(D18="",J18=""),"",IF(J18&lt;=G18,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8218,20 +8228,22 @@
           <t>VA05</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n"/>
-      <c r="C19" s="27" t="n">
+      <c r="B19" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C19" s="26" t="n">
         <v>1.4</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="27">
         <f>IF(COUNT(B19,C19)&lt;2,"",B19*C19)</f>
         <v/>
       </c>
-      <c r="E19" s="32" t="n"/>
-      <c r="F19" s="30">
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="29">
         <f>IF(OR(D19="",$E$17=""),"",D19/$E$17)</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8241,7 +8253,7 @@
         </is>
       </c>
       <c r="I19" s="25" t="n"/>
-      <c r="J19" s="27" t="n">
+      <c r="J19" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K19" s="25" t="inlineStr">
@@ -8249,8 +8261,8 @@
           <t>Este</t>
         </is>
       </c>
-      <c r="L19" s="27" t="n"/>
-      <c r="M19" s="31">
+      <c r="L19" s="26" t="n"/>
+      <c r="M19" s="30">
         <f>IF(OR(D19="",J19=""),"",IF(J19&lt;=G19,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8261,20 +8273,22 @@
           <t>PV04</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="27" t="n">
+      <c r="B20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="26" t="n">
         <v>2.06</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="27">
         <f>IF(COUNT(B20,C20)&lt;2,"",B20*C20)</f>
         <v/>
       </c>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="30">
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="29">
         <f>IF(OR(D20="",$E$17=""),"",D20/$E$17)</f>
         <v/>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8284,7 +8298,7 @@
         </is>
       </c>
       <c r="I20" s="25" t="n"/>
-      <c r="J20" s="27" t="n">
+      <c r="J20" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K20" s="25" t="inlineStr">
@@ -8292,62 +8306,62 @@
           <t>Este</t>
         </is>
       </c>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="31">
+      <c r="L20" s="26" t="n"/>
+      <c r="M20" s="30">
         <f>IF(OR(D20="",J20=""),"",IF(J20&lt;=G20,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="25" t="n"/>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="28">
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="27">
         <f>IF(COUNT(B21,C21)&lt;2,"",B21*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="30">
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="29">
         <f>IF(OR(D21="",$E$17=""),"",D21/$E$17)</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
       <c r="H21" s="25" t="n"/>
       <c r="I21" s="25" t="n"/>
-      <c r="J21" s="27" t="n"/>
+      <c r="J21" s="26" t="n"/>
       <c r="K21" s="25" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="31">
+      <c r="L21" s="26" t="n"/>
+      <c r="M21" s="30">
         <f>IF(OR(D21="",J21=""),"",IF(J21&lt;=G21,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="33" t="n"/>
-      <c r="B22" s="34" t="n"/>
-      <c r="C22" s="34" t="n"/>
-      <c r="D22" s="35">
+      <c r="A22" s="32" t="n"/>
+      <c r="B22" s="33" t="n"/>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="34">
         <f>IF(COUNT(B22,C22)&lt;2,"",B22*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="36" t="n"/>
-      <c r="F22" s="37">
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="36">
         <f>IF(OR(D22="",$E$17=""),"",D22/$E$17)</f>
         <v/>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="33" t="n"/>
-      <c r="J22" s="34" t="n"/>
-      <c r="K22" s="33" t="n"/>
-      <c r="L22" s="34" t="n"/>
-      <c r="M22" s="38">
+      <c r="H22" s="32" t="n"/>
+      <c r="I22" s="32" t="n"/>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="32" t="n"/>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="37">
         <f>IF(OR(D22="",J22=""),"",IF(J22&lt;=G22,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8377,23 +8391,25 @@
           <t>PV03</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="27" t="n">
+      <c r="B24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="26" t="n">
         <v>1.76</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="27">
         <f>IF(COUNT(B24,C24)&lt;2,"",B24*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="28">
         <f>SUM(D24:D30)</f>
         <v/>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="29">
         <f>IF(OR(D24="",$E$24=""),"",D24/$E$24)</f>
         <v/>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8403,7 +8419,7 @@
         </is>
       </c>
       <c r="I24" s="25" t="n"/>
-      <c r="J24" s="27" t="n">
+      <c r="J24" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K24" s="25" t="inlineStr">
@@ -8411,8 +8427,8 @@
           <t>Oeste</t>
         </is>
       </c>
-      <c r="L24" s="27" t="n"/>
-      <c r="M24" s="31">
+      <c r="L24" s="26" t="n"/>
+      <c r="M24" s="30">
         <f>IF(OR(D24="",J24=""),"",IF(J24&lt;=G24,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8423,20 +8439,22 @@
           <t>VA02</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n"/>
-      <c r="C25" s="27" t="n">
+      <c r="B25" s="26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C25" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="27">
         <f>IF(COUNT(B25,C25)&lt;2,"",B25*C25)</f>
         <v/>
       </c>
-      <c r="E25" s="32" t="n"/>
-      <c r="F25" s="30">
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="29">
         <f>IF(OR(D25="",$E$24=""),"",D25/$E$24)</f>
         <v/>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8446,7 +8464,7 @@
         </is>
       </c>
       <c r="I25" s="25" t="n"/>
-      <c r="J25" s="27" t="n">
+      <c r="J25" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K25" s="25" t="inlineStr">
@@ -8454,8 +8472,8 @@
           <t>Oeste</t>
         </is>
       </c>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="31">
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="30">
         <f>IF(OR(D25="",J25=""),"",IF(J25&lt;=G25,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8466,20 +8484,22 @@
           <t>PA02</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="27" t="n">
+      <c r="B26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <f>IF(COUNT(B26,C26)&lt;2,"",B26*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="30">
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="29">
         <f>IF(OR(D26="",$E$24=""),"",D26/$E$24)</f>
         <v/>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8489,7 +8509,7 @@
         </is>
       </c>
       <c r="I26" s="25" t="n"/>
-      <c r="J26" s="27" t="n">
+      <c r="J26" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K26" s="25" t="inlineStr">
@@ -8497,8 +8517,8 @@
           <t>Oeste</t>
         </is>
       </c>
-      <c r="L26" s="27" t="n"/>
-      <c r="M26" s="31">
+      <c r="L26" s="26" t="n"/>
+      <c r="M26" s="30">
         <f>IF(OR(D26="",J26=""),"",IF(J26&lt;=G26,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8509,20 +8529,22 @@
           <t>VA03</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="27" t="n">
+      <c r="B27" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C27" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <f>IF(COUNT(B27,C27)&lt;2,"",B27*C27)</f>
         <v/>
       </c>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="30">
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="29">
         <f>IF(OR(D27="",$E$24=""),"",D27/$E$24)</f>
         <v/>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8532,7 +8554,7 @@
         </is>
       </c>
       <c r="I27" s="25" t="n"/>
-      <c r="J27" s="27" t="n">
+      <c r="J27" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K27" s="25" t="inlineStr">
@@ -8540,8 +8562,8 @@
           <t>Oeste</t>
         </is>
       </c>
-      <c r="L27" s="27" t="n"/>
-      <c r="M27" s="31">
+      <c r="L27" s="26" t="n"/>
+      <c r="M27" s="30">
         <f>IF(OR(D27="",J27=""),"",IF(J27&lt;=G27,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8552,20 +8574,22 @@
           <t>PF05</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n"/>
-      <c r="C28" s="27" t="n">
+      <c r="B28" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C28" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="27">
         <f>IF(COUNT(B28,C28)&lt;2,"",B28*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="30">
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="29">
         <f>IF(OR(D28="",$E$24=""),"",D28/$E$24)</f>
         <v/>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8575,7 +8599,7 @@
         </is>
       </c>
       <c r="I28" s="25" t="n"/>
-      <c r="J28" s="27" t="n">
+      <c r="J28" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K28" s="25" t="inlineStr">
@@ -8583,62 +8607,62 @@
           <t>Oeste</t>
         </is>
       </c>
-      <c r="L28" s="27" t="n"/>
-      <c r="M28" s="31">
+      <c r="L28" s="26" t="n"/>
+      <c r="M28" s="30">
         <f>IF(OR(D28="",J28=""),"",IF(J28&lt;=G28,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="25" t="n"/>
-      <c r="B29" s="27" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="28">
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="27">
         <f>IF(COUNT(B29,C29)&lt;2,"",B29*C29)</f>
         <v/>
       </c>
-      <c r="E29" s="32" t="n"/>
-      <c r="F29" s="30">
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="29">
         <f>IF(OR(D29="",$E$24=""),"",D29/$E$24)</f>
         <v/>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
       <c r="H29" s="25" t="n"/>
       <c r="I29" s="25" t="n"/>
-      <c r="J29" s="27" t="n"/>
+      <c r="J29" s="26" t="n"/>
       <c r="K29" s="25" t="n"/>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="31">
+      <c r="L29" s="26" t="n"/>
+      <c r="M29" s="30">
         <f>IF(OR(D29="",J29=""),"",IF(J29&lt;=G29,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="33" t="n"/>
-      <c r="B30" s="34" t="n"/>
-      <c r="C30" s="34" t="n"/>
-      <c r="D30" s="35">
+      <c r="A30" s="32" t="n"/>
+      <c r="B30" s="33" t="n"/>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="34">
         <f>IF(COUNT(B30,C30)&lt;2,"",B30*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="37">
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="36">
         <f>IF(OR(D30="",$E$24=""),"",D30/$E$24)</f>
         <v/>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="33" t="n"/>
-      <c r="J30" s="34" t="n"/>
-      <c r="K30" s="33" t="n"/>
-      <c r="L30" s="34" t="n"/>
-      <c r="M30" s="38">
+      <c r="H30" s="32" t="n"/>
+      <c r="I30" s="32" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="32" t="n"/>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="37">
         <f>IF(OR(D30="",J30=""),"",IF(J30&lt;=G30,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8668,23 +8692,25 @@
           <t>PF01</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="27" t="n">
+      <c r="B32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="26" t="n">
         <v>3.55</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="27">
         <f>IF(COUNT(B32,C32)&lt;2,"",B32*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="28">
         <f>SUM(D32:D37)</f>
         <v/>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="29">
         <f>IF(OR(D32="",$E$32=""),"",D32/$E$32)</f>
         <v/>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8694,12 +8720,12 @@
         </is>
       </c>
       <c r="I32" s="25" t="n"/>
-      <c r="J32" s="27" t="n">
+      <c r="J32" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K32" s="25" t="n"/>
-      <c r="L32" s="27" t="n"/>
-      <c r="M32" s="31">
+      <c r="L32" s="26" t="n"/>
+      <c r="M32" s="30">
         <f>IF(OR(D32="",J32=""),"",IF(J32&lt;=G32,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8710,20 +8736,22 @@
           <t>PF02</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="27" t="n">
+      <c r="B33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="26" t="n">
         <v>3.75</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <f>IF(COUNT(B33,C33)&lt;2,"",B33*C33)</f>
         <v/>
       </c>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="30">
+      <c r="E33" s="31" t="n"/>
+      <c r="F33" s="29">
         <f>IF(OR(D33="",$E$32=""),"",D33/$E$32)</f>
         <v/>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8733,12 +8761,12 @@
         </is>
       </c>
       <c r="I33" s="25" t="n"/>
-      <c r="J33" s="27" t="n">
+      <c r="J33" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K33" s="25" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="31">
+      <c r="L33" s="26" t="n"/>
+      <c r="M33" s="30">
         <f>IF(OR(D33="",J33=""),"",IF(J33&lt;=G33,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8749,20 +8777,20 @@
           <t>PV01</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="27" t="n">
+      <c r="B34" s="38" t="n"/>
+      <c r="C34" s="26" t="n">
         <v>7.7</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="27">
         <f>IF(COUNT(B34,C34)&lt;2,"",B34*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="32" t="n"/>
-      <c r="F34" s="30">
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="29">
         <f>IF(OR(D34="",$E$32=""),"",D34/$E$32)</f>
         <v/>
       </c>
-      <c r="G34" s="28">
+      <c r="G34" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8772,12 +8800,12 @@
         </is>
       </c>
       <c r="I34" s="25" t="n"/>
-      <c r="J34" s="27" t="n">
+      <c r="J34" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K34" s="25" t="n"/>
-      <c r="L34" s="27" t="n"/>
-      <c r="M34" s="31">
+      <c r="L34" s="26" t="n"/>
+      <c r="M34" s="30">
         <f>IF(OR(D34="",J34=""),"",IF(J34&lt;=G34,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -8788,20 +8816,20 @@
           <t>PV04 (2)</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n"/>
-      <c r="C35" s="27" t="n">
+      <c r="B35" s="38" t="n"/>
+      <c r="C35" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="27">
         <f>IF(COUNT(B35,C35)&lt;2,"",B35*C35)</f>
         <v/>
       </c>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="30">
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="29">
         <f>IF(OR(D35="",$E$32=""),"",D35/$E$32)</f>
         <v/>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
@@ -8811,66 +8839,66 @@
         </is>
       </c>
       <c r="I35" s="25" t="n"/>
-      <c r="J35" s="27" t="n">
+      <c r="J35" s="26" t="n">
         <v>2.8</v>
       </c>
       <c r="K35" s="25" t="n"/>
-      <c r="L35" s="27" t="n"/>
-      <c r="M35" s="31">
+      <c r="L35" s="26" t="n"/>
+      <c r="M35" s="30">
         <f>IF(OR(D35="",J35=""),"",IF(J35&lt;=G35,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="25" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="27" t="n"/>
-      <c r="D36" s="28">
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="27">
         <f>IF(COUNT(B36,C36)&lt;2,"",B36*C36)</f>
         <v/>
       </c>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="30">
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="29">
         <f>IF(OR(D36="",$E$32=""),"",D36/$E$32)</f>
         <v/>
       </c>
-      <c r="G36" s="28">
+      <c r="G36" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
       <c r="H36" s="25" t="n"/>
       <c r="I36" s="25" t="n"/>
-      <c r="J36" s="27" t="n"/>
+      <c r="J36" s="26" t="n"/>
       <c r="K36" s="25" t="n"/>
-      <c r="L36" s="27" t="n"/>
-      <c r="M36" s="31">
+      <c r="L36" s="26" t="n"/>
+      <c r="M36" s="30">
         <f>IF(OR(D36="",J36=""),"",IF(J36&lt;=G36,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="33" t="n"/>
-      <c r="B37" s="34" t="n"/>
-      <c r="C37" s="34" t="n"/>
-      <c r="D37" s="35">
+      <c r="A37" s="32" t="n"/>
+      <c r="B37" s="33" t="n"/>
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="34">
         <f>IF(COUNT(B37,C37)&lt;2,"",B37*C37)</f>
         <v/>
       </c>
-      <c r="E37" s="36" t="n"/>
-      <c r="F37" s="37">
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="36">
         <f>IF(OR(D37="",$E$32=""),"",D37/$E$32)</f>
         <v/>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H37" s="33" t="n"/>
-      <c r="I37" s="33" t="n"/>
-      <c r="J37" s="34" t="n"/>
-      <c r="K37" s="33" t="n"/>
-      <c r="L37" s="34" t="n"/>
-      <c r="M37" s="38">
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="32" t="n"/>
+      <c r="J37" s="33" t="n"/>
+      <c r="K37" s="32" t="n"/>
+      <c r="L37" s="33" t="n"/>
+      <c r="M37" s="37">
         <f>IF(OR(D37="",J37=""),"",IF(J37&lt;=G37,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
@@ -9075,7 +9103,7 @@
     <row r="49">
       <c r="A49" s="40" t="inlineStr">
         <is>
-          <t>FALTA, y esta marcado en naranja: la ALTURA de cada vano. La planilla de carpinterias acota</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -9094,7 +9122,7 @@
     <row r="50">
       <c r="A50" s="40" t="inlineStr">
         <is>
-          <t>el nivel de dintel (2,52 / 2,15 / 2,10) y el cielorraso (3,00), pero no la altura libre del vano,</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9113,7 +9141,7 @@
     <row r="51">
       <c r="A51" s="40" t="inlineStr">
         <is>
-          <t>asi que no se puede deducir sin el nivel de antepecho de cada abertura.</t>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
         </is>
       </c>
       <c r="B51" s="2" t="n"/>
@@ -9130,7 +9158,11 @@
       <c r="M51" s="2" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="40" t="inlineStr"/>
+      <c r="A52" s="40" t="inlineStr">
+        <is>
+          <t>Quedan en naranja las tres que no se pudieron medir: PV01, PV04 (2) y PF04.</t>
+        </is>
+      </c>
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n"/>
@@ -9145,11 +9177,7 @@
       <c r="M52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="40" t="inlineStr">
-        <is>
-          <t>ORIENTACION: el simbolo de norte del plano de plantas (flecha con arco, arriba a la derecha)</t>
-        </is>
-      </c>
+      <c r="A53" s="40" t="inlineStr"/>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n"/>
@@ -9166,7 +9194,7 @@
     <row r="54">
       <c r="A54" s="40" t="inlineStr">
         <is>
-          <t>apunta hacia la derecha de la hoja. Entonces: derecha = Norte, izquierda = Sur, abajo = Este,</t>
+          <t>ORIENTACION: el simbolo de norte del plano de plantas (flecha con arco, arriba a la derecha)</t>
         </is>
       </c>
       <c r="B54" s="2" t="n"/>
@@ -9185,7 +9213,7 @@
     <row r="55">
       <c r="A55" s="40" t="inlineStr">
         <is>
-          <t>arriba = Oeste. Coincide con los rotulos Dormitorio Norte y Dormitorio Sur del plano.</t>
+          <t>apunta hacia la derecha de la hoja. Entonces: derecha = Norte, izquierda = Sur, abajo = Este,</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9204,7 +9232,7 @@
     <row r="56">
       <c r="A56" s="40" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta.</t>
+          <t>arriba = Oeste. Coincide con los rotulos Dormitorio Norte y Dormitorio Sur del plano.</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -9223,7 +9251,7 @@
     <row r="57">
       <c r="A57" s="40" t="inlineStr">
         <is>
-          <t>Las tres aberturas que dan al patio interno quedan en un bloque aparte: hay que confirmar</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta.</t>
         </is>
       </c>
       <c r="B57" s="2" t="n"/>
@@ -9242,7 +9270,7 @@
     <row r="58">
       <c r="A58" s="40" t="inlineStr">
         <is>
-          <t>a que lado del patio dan antes de asignarles orientacion y factor de exposicion solar.</t>
+          <t>Las tres aberturas que dan al patio interno quedan en un bloque aparte: hay que confirmar</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9259,7 +9287,11 @@
       <c r="M58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="40" t="inlineStr"/>
+      <c r="A59" s="40" t="inlineStr">
+        <is>
+          <t>a que lado del patio dan antes de asignarles orientacion y factor de exposicion solar.</t>
+        </is>
+      </c>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n"/>
@@ -9274,11 +9306,7 @@
       <c r="M59" s="2" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="40" t="inlineStr">
-        <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
-        </is>
-      </c>
+      <c r="A60" s="40" t="inlineStr"/>
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n"/>
@@ -9293,7 +9321,11 @@
       <c r="M60" s="2" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="40" t="inlineStr"/>
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+        </is>
+      </c>
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n"/>
@@ -9308,11 +9340,7 @@
       <c r="M61" s="2" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="40" t="inlineStr">
-        <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
-        </is>
-      </c>
+      <c r="A62" s="40" t="inlineStr"/>
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n"/>
@@ -9329,7 +9357,7 @@
     <row r="63">
       <c r="A63" s="40" t="inlineStr">
         <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
@@ -9348,7 +9376,7 @@
     <row r="64">
       <c r="A64" s="40" t="inlineStr">
         <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9363,6 +9391,25 @@
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="40" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -9852,7 +9899,7 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="32" t="n"/>
+      <c r="A5" s="31" t="n"/>
       <c r="B5" s="43" t="inlineStr">
         <is>
           <t>VI 01b</t>
@@ -9969,7 +10016,7 @@
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="32" t="n"/>
+      <c r="A6" s="31" t="n"/>
       <c r="B6" s="43" t="inlineStr">
         <is>
           <t>VI 02</t>
@@ -10086,7 +10133,7 @@
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="32" t="n"/>
+      <c r="A7" s="31" t="n"/>
       <c r="B7" s="43" t="inlineStr">
         <is>
           <t>VI 03c</t>
@@ -10199,7 +10246,7 @@
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="32" t="n"/>
+      <c r="A8" s="31" t="n"/>
       <c r="B8" s="43" t="inlineStr">
         <is>
           <t>VI 04a</t>
@@ -10320,7 +10367,7 @@
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="32" t="n"/>
+      <c r="A9" s="31" t="n"/>
       <c r="B9" s="43" t="inlineStr">
         <is>
           <t>VI 04b</t>
@@ -10433,7 +10480,7 @@
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="32" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="43" t="inlineStr">
         <is>
           <t>VI 06</t>
@@ -10554,7 +10601,7 @@
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="32" t="n"/>
+      <c r="A11" s="31" t="n"/>
       <c r="B11" s="43" t="inlineStr">
         <is>
           <t>VI 07a</t>
@@ -10671,7 +10718,7 @@
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="32" t="n"/>
+      <c r="A12" s="31" t="n"/>
       <c r="B12" s="43" t="inlineStr">
         <is>
           <t>VI 07b</t>
@@ -10788,7 +10835,7 @@
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="32" t="n"/>
+      <c r="A13" s="31" t="n"/>
       <c r="B13" s="43" t="inlineStr">
         <is>
           <t>VI 07c</t>
@@ -10909,7 +10956,7 @@
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="32" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="43" t="inlineStr">
         <is>
           <t>VI 08a</t>
@@ -11022,7 +11069,7 @@
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="32" t="n"/>
+      <c r="A15" s="31" t="n"/>
       <c r="B15" s="43" t="inlineStr">
         <is>
           <t>VI 08b</t>
@@ -11139,7 +11186,7 @@
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="32" t="n"/>
+      <c r="A16" s="31" t="n"/>
       <c r="B16" s="43" t="inlineStr">
         <is>
           <t>VI 09</t>
@@ -11260,7 +11307,7 @@
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
-      <c r="A17" s="32" t="n"/>
+      <c r="A17" s="31" t="n"/>
       <c r="B17" s="43" t="inlineStr">
         <is>
           <t>VI 10a</t>
@@ -11373,7 +11420,7 @@
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="32" t="n"/>
+      <c r="A18" s="31" t="n"/>
       <c r="B18" s="43" t="inlineStr">
         <is>
           <t>VI 10b</t>
@@ -11486,7 +11533,7 @@
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
-      <c r="A19" s="32" t="n"/>
+      <c r="A19" s="31" t="n"/>
       <c r="B19" s="43" t="inlineStr">
         <is>
           <t>VI 10c</t>
@@ -11599,7 +11646,7 @@
       </c>
     </row>
     <row r="20" ht="46" customHeight="1">
-      <c r="A20" s="32" t="n"/>
+      <c r="A20" s="31" t="n"/>
       <c r="B20" s="43" t="inlineStr">
         <is>
           <t>VI 11a</t>
@@ -11716,7 +11763,7 @@
       </c>
     </row>
     <row r="21" ht="46" customHeight="1">
-      <c r="A21" s="32" t="n"/>
+      <c r="A21" s="31" t="n"/>
       <c r="B21" s="43" t="inlineStr">
         <is>
           <t>VI 11b</t>
@@ -11833,7 +11880,7 @@
       </c>
     </row>
     <row r="22" ht="46" customHeight="1">
-      <c r="A22" s="32" t="n"/>
+      <c r="A22" s="31" t="n"/>
       <c r="B22" s="43" t="inlineStr">
         <is>
           <t>VI 11c</t>
@@ -11950,7 +11997,7 @@
       </c>
     </row>
     <row r="23" ht="46" customHeight="1">
-      <c r="A23" s="32" t="n"/>
+      <c r="A23" s="31" t="n"/>
       <c r="B23" s="43" t="inlineStr">
         <is>
           <t>VCH 03a</t>
@@ -12067,7 +12114,7 @@
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="32" t="n"/>
+      <c r="A24" s="31" t="n"/>
       <c r="B24" s="43" t="inlineStr">
         <is>
           <t>VCH 03b</t>
@@ -12184,7 +12231,7 @@
       </c>
     </row>
     <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="36" t="n"/>
+      <c r="A25" s="35" t="n"/>
       <c r="B25" s="46" t="inlineStr">
         <is>
           <t>VCH 05</t>
@@ -12418,7 +12465,7 @@
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="32" t="n"/>
+      <c r="A27" s="31" t="n"/>
       <c r="B27" s="43" t="inlineStr">
         <is>
           <t>VI 13a</t>
@@ -12531,7 +12578,7 @@
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
-      <c r="A28" s="32" t="n"/>
+      <c r="A28" s="31" t="n"/>
       <c r="B28" s="43" t="inlineStr">
         <is>
           <t>VI 13b</t>
@@ -12644,7 +12691,7 @@
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
-      <c r="A29" s="32" t="n"/>
+      <c r="A29" s="31" t="n"/>
       <c r="B29" s="43" t="inlineStr">
         <is>
           <t>VI 14</t>
@@ -12757,7 +12804,7 @@
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
-      <c r="A30" s="32" t="n"/>
+      <c r="A30" s="31" t="n"/>
       <c r="B30" s="43" t="inlineStr">
         <is>
           <t>VI 15a</t>
@@ -12874,7 +12921,7 @@
       </c>
     </row>
     <row r="31" ht="46" customHeight="1">
-      <c r="A31" s="32" t="n"/>
+      <c r="A31" s="31" t="n"/>
       <c r="B31" s="43" t="inlineStr">
         <is>
           <t>VI 15b</t>
@@ -12991,7 +13038,7 @@
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
-      <c r="A32" s="32" t="n"/>
+      <c r="A32" s="31" t="n"/>
       <c r="B32" s="43" t="inlineStr">
         <is>
           <t>VI 16a</t>
@@ -13104,7 +13151,7 @@
       </c>
     </row>
     <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="32" t="n"/>
+      <c r="A33" s="31" t="n"/>
       <c r="B33" s="43" t="inlineStr">
         <is>
           <t>VI 16b</t>
@@ -13217,7 +13264,7 @@
       </c>
     </row>
     <row r="34" ht="46" customHeight="1">
-      <c r="A34" s="36" t="n"/>
+      <c r="A34" s="35" t="n"/>
       <c r="B34" s="46" t="inlineStr">
         <is>
           <t>VI 17</t>
@@ -13663,7 +13710,7 @@
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="32" t="n"/>
+      <c r="A5" s="31" t="n"/>
       <c r="B5" s="43" t="inlineStr">
         <is>
           <t>L02</t>
@@ -13735,7 +13782,7 @@
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="32" t="n"/>
+      <c r="A6" s="31" t="n"/>
       <c r="B6" s="43" t="inlineStr">
         <is>
           <t>L03</t>
@@ -13803,7 +13850,7 @@
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="32" t="n"/>
+      <c r="A7" s="31" t="n"/>
       <c r="B7" s="43" t="inlineStr">
         <is>
           <t>L04</t>
@@ -13871,7 +13918,7 @@
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="32" t="n"/>
+      <c r="A8" s="31" t="n"/>
       <c r="B8" s="43" t="inlineStr">
         <is>
           <t>L05</t>
@@ -13939,7 +13986,7 @@
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="32" t="n"/>
+      <c r="A9" s="31" t="n"/>
       <c r="B9" s="43" t="inlineStr">
         <is>
           <t>L06</t>
@@ -14007,7 +14054,7 @@
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="32" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="43" t="inlineStr">
         <is>
           <t>L07 (x)</t>
@@ -14081,7 +14128,7 @@
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="32" t="n"/>
+      <c r="A11" s="31" t="n"/>
       <c r="B11" s="43" t="inlineStr">
         <is>
           <t>L07 (y)</t>
@@ -14155,7 +14202,7 @@
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="36" t="n"/>
+      <c r="A12" s="35" t="n"/>
       <c r="B12" s="46" t="inlineStr">
         <is>
           <t>L08</t>
@@ -14299,7 +14346,7 @@
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="32" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="43" t="inlineStr">
         <is>
           <t>L10 (x)</t>
@@ -14373,7 +14420,7 @@
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="36" t="n"/>
+      <c r="A15" s="35" t="n"/>
       <c r="B15" s="46" t="inlineStr">
         <is>
           <t>L10 (y)</t>
@@ -14729,7 +14776,7 @@
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="32" t="n"/>
+      <c r="A5" s="31" t="n"/>
       <c r="B5" s="43" t="inlineStr">
         <is>
           <t>C7</t>
@@ -14794,7 +14841,7 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="32" t="n"/>
+      <c r="A6" s="31" t="n"/>
       <c r="B6" s="43" t="inlineStr">
         <is>
           <t>C8</t>
@@ -14859,7 +14906,7 @@
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="36" t="n"/>
+      <c r="A7" s="35" t="n"/>
       <c r="B7" s="46" t="inlineStr">
         <is>
           <t>C9</t>
@@ -14993,7 +15040,7 @@
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="32" t="n"/>
+      <c r="A9" s="31" t="n"/>
       <c r="B9" s="43" t="inlineStr">
         <is>
           <t>C2</t>
@@ -15058,7 +15105,7 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="32" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="43" t="inlineStr">
         <is>
           <t>C3</t>
@@ -15123,7 +15170,7 @@
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="32" t="n"/>
+      <c r="A11" s="31" t="n"/>
       <c r="B11" s="43" t="inlineStr">
         <is>
           <t>C4</t>
@@ -15188,7 +15235,7 @@
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="32" t="n"/>
+      <c r="A12" s="31" t="n"/>
       <c r="B12" s="43" t="inlineStr">
         <is>
           <t>C5</t>
@@ -15253,7 +15300,7 @@
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="32" t="n"/>
+      <c r="A13" s="31" t="n"/>
       <c r="B13" s="43" t="inlineStr">
         <is>
           <t>C6</t>
@@ -15318,7 +15365,7 @@
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="32" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="43" t="inlineStr">
         <is>
           <t>C7</t>
@@ -15383,7 +15430,7 @@
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="32" t="n"/>
+      <c r="A15" s="31" t="n"/>
       <c r="B15" s="43" t="inlineStr">
         <is>
           <t>C8</t>
@@ -15448,7 +15495,7 @@
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="36" t="n"/>
+      <c r="A16" s="35" t="n"/>
       <c r="B16" s="46" t="inlineStr">
         <is>
           <t>C9</t>
@@ -19766,7 +19813,7 @@
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="32" t="n"/>
+      <c r="A5" s="31" t="n"/>
       <c r="B5" s="43" t="inlineStr">
         <is>
           <t>T2</t>
@@ -19827,7 +19874,7 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="32" t="n"/>
+      <c r="A6" s="31" t="n"/>
       <c r="B6" s="43" t="inlineStr">
         <is>
           <t>T3</t>
@@ -19888,7 +19935,7 @@
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="32" t="n"/>
+      <c r="A7" s="31" t="n"/>
       <c r="B7" s="43" t="inlineStr">
         <is>
           <t>T4</t>
@@ -19949,7 +19996,7 @@
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="32" t="n"/>
+      <c r="A8" s="31" t="n"/>
       <c r="B8" s="43" t="inlineStr">
         <is>
           <t>T5</t>
@@ -20010,7 +20057,7 @@
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="32" t="n"/>
+      <c r="A9" s="31" t="n"/>
       <c r="B9" s="43" t="inlineStr">
         <is>
           <t>T6</t>
@@ -20071,7 +20118,7 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="32" t="n"/>
+      <c r="A10" s="31" t="n"/>
       <c r="B10" s="43" t="inlineStr">
         <is>
           <t>T7</t>
@@ -20132,7 +20179,7 @@
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="36" t="n"/>
+      <c r="A11" s="35" t="n"/>
       <c r="B11" s="46" t="inlineStr">
         <is>
           <t>T8</t>
@@ -20258,7 +20305,7 @@
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="32" t="n"/>
+      <c r="A13" s="31" t="n"/>
       <c r="B13" s="43" t="inlineStr">
         <is>
           <t>T10</t>
@@ -20319,7 +20366,7 @@
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="32" t="n"/>
+      <c r="A14" s="31" t="n"/>
       <c r="B14" s="43" t="inlineStr">
         <is>
           <t>T11</t>
@@ -20380,7 +20427,7 @@
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="32" t="n"/>
+      <c r="A15" s="31" t="n"/>
       <c r="B15" s="43" t="inlineStr">
         <is>
           <t>T12</t>
@@ -20441,7 +20488,7 @@
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="36" t="n"/>
+      <c r="A16" s="35" t="n"/>
       <c r="B16" s="46" t="inlineStr">
         <is>
           <t>T13</t>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Planilla 3 higrotermica'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla vigas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla vigas'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla losas'!$1:$3</definedName>
@@ -7616,7 +7616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7780,7 +7780,7 @@
     <row r="6">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>Plano: Fachada Norte</t>
+          <t>Plano: Fachada Noreste (borde derecho del plano)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -7813,7 +7813,7 @@
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>SUM(D7:D11)</f>
+        <f>SUM(D7:D13)</f>
         <v/>
       </c>
       <c r="F7" s="29">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="K7" s="25" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Noreste</t>
         </is>
       </c>
       <c r="L7" s="26" t="n"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="K8" s="25" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Noreste</t>
         </is>
       </c>
       <c r="L8" s="26" t="n"/>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="K9" s="25" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Noreste</t>
         </is>
       </c>
       <c r="L9" s="26" t="n"/>
@@ -7935,9 +7935,17 @@
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="26" t="n"/>
-      <c r="C10" s="26" t="n"/>
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>PV01</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>7.7</v>
+      </c>
       <c r="D10" s="27">
         <f>IF(COUNT(B10,C10)&lt;2,"",B10*C10)</f>
         <v/>
@@ -7951,10 +7959,20 @@
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H10" s="25" t="n"/>
+      <c r="H10" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
       <c r="I10" s="25" t="n"/>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="25" t="n"/>
+      <c r="J10" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
       <c r="L10" s="26" t="n"/>
       <c r="M10" s="30">
         <f>IF(OR(D10="",J10=""),"",IF(J10&lt;=G10,"CUMPLE","NO CUMPLE"))</f>
@@ -7962,214 +7980,237 @@
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="32" t="n"/>
-      <c r="B11" s="33" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="34">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>PF01</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D11" s="27">
         <f>IF(COUNT(B11,C11)&lt;2,"",B11*C11)</f>
         <v/>
       </c>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="36">
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="29">
         <f>IF(OR(D11="",$E$7=""),"",D11/$E$7)</f>
         <v/>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="33" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="37">
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="n"/>
+      <c r="J11" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n"/>
+      <c r="M11" s="30">
         <f>IF(OR(D11="",J11=""),"",IF(J11&lt;=G11,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Fachada Sur</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="27">
+        <f>IF(COUNT(B12,C12)&lt;2,"",B12*C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="29">
+        <f>IF(OR(D12="",$E$7=""),"",D12/$E$7)</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="30">
+        <f>IF(OR(D12="",J12=""),"",IF(J12&lt;=G12,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="32" t="n"/>
+      <c r="B13" s="33" t="n"/>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="34">
+        <f>IF(COUNT(B13,C13)&lt;2,"",B13*C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="36">
+        <f>IF(OR(D13="",$E$7=""),"",D13/$E$7)</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="32" t="n"/>
+      <c r="J13" s="33" t="n"/>
+      <c r="K13" s="32" t="n"/>
+      <c r="L13" s="33" t="n"/>
+      <c r="M13" s="37">
+        <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Fachada Sudoeste (borde izquierdo)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>VA01</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B15" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C15" s="26" t="n">
         <v>0.75</v>
       </c>
-      <c r="D13" s="27">
-        <f>IF(COUNT(B13,C13)&lt;2,"",B13*C13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="28">
-        <f>SUM(D13:D15)</f>
-        <v/>
-      </c>
-      <c r="F13" s="29">
-        <f>IF(OR(D13="",$E$13=""),"",D13/$E$13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="27">
+      <c r="D15" s="27">
+        <f>IF(COUNT(B15,C15)&lt;2,"",B15*C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="28">
+        <f>SUM(D15:D18)</f>
+        <v/>
+      </c>
+      <c r="F15" s="29">
+        <f>IF(OR(D15="",$E$15=""),"",D15/$E$15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="H15" s="25" t="inlineStr">
         <is>
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I13" s="25" t="n"/>
-      <c r="J13" s="26" t="n">
+      <c r="I15" s="25" t="n"/>
+      <c r="J15" s="26" t="n">
         <v>2.8</v>
       </c>
-      <c r="K13" s="25" t="inlineStr">
-        <is>
-          <t>Sur</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="n"/>
-      <c r="M13" s="30">
-        <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="27">
-        <f>IF(COUNT(B14,C14)&lt;2,"",B14*C14)</f>
-        <v/>
-      </c>
-      <c r="E14" s="31" t="n"/>
-      <c r="F14" s="29">
-        <f>IF(OR(D14="",$E$13=""),"",D14/$E$13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="27">
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n"/>
+      <c r="M15" s="30">
+        <f>IF(OR(D15="",J15=""),"",IF(J15&lt;=G15,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>PF01 (2)</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D16" s="27">
+        <f>IF(COUNT(B16,C16)&lt;2,"",B16*C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="29">
+        <f>IF(OR(D16="",$E$15=""),"",D16/$E$15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="26" t="n"/>
-      <c r="M14" s="30">
-        <f>IF(OR(D14="",J14=""),"",IF(J14&lt;=G14,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="32" t="n"/>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="34">
-        <f>IF(COUNT(B15,C15)&lt;2,"",B15*C15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="36">
-        <f>IF(OR(D15="",$E$13=""),"",D15/$E$13)</f>
-        <v/>
-      </c>
-      <c r="G15" s="34">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="33" t="n"/>
-      <c r="K15" s="32" t="n"/>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="37">
-        <f>IF(OR(D15="",J15=""),"",IF(J15&lt;=G15,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Fachada Este</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n"/>
+      <c r="M16" s="30">
+        <f>IF(OR(D16="",J16=""),"",IF(J16&lt;=G16,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>PA01</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" s="26" t="n">
-        <v>1</v>
-      </c>
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
       <c r="D17" s="27">
         <f>IF(COUNT(B17,C17)&lt;2,"",B17*C17)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
-        <f>SUM(D17:D22)</f>
-        <v/>
-      </c>
+      <c r="E17" s="31" t="n"/>
       <c r="F17" s="29">
-        <f>IF(OR(D17="",$E$17=""),"",D17/$E$17)</f>
+        <f>IF(OR(D17="",$E$15=""),"",D17/$E$15)</f>
         <v/>
       </c>
       <c r="G17" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H17" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
+      <c r="H17" s="25" t="n"/>
       <c r="I17" s="25" t="n"/>
-      <c r="J17" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K17" s="25" t="inlineStr">
-        <is>
-          <t>Este</t>
-        </is>
-      </c>
+      <c r="J17" s="26" t="n"/>
+      <c r="K17" s="25" t="n"/>
       <c r="L17" s="26" t="n"/>
       <c r="M17" s="30">
         <f>IF(OR(D17="",J17=""),"",IF(J17&lt;=G17,"CUMPLE","NO CUMPLE"))</f>
@@ -8177,114 +8218,73 @@
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>PF04</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C18" s="26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="D18" s="27">
+      <c r="A18" s="32" t="n"/>
+      <c r="B18" s="33" t="n"/>
+      <c r="C18" s="33" t="n"/>
+      <c r="D18" s="34">
         <f>IF(COUNT(B18,C18)&lt;2,"",B18*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="31" t="n"/>
-      <c r="F18" s="29">
-        <f>IF(OR(D18="",$E$17=""),"",D18/$E$17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="27">
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="36">
+        <f>IF(OR(D18="",$E$15=""),"",D18/$E$15)</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H18" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I18" s="25" t="n"/>
-      <c r="J18" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K18" s="25" t="inlineStr">
-        <is>
-          <t>Este</t>
-        </is>
-      </c>
-      <c r="L18" s="26" t="n"/>
-      <c r="M18" s="30">
+      <c r="H18" s="32" t="n"/>
+      <c r="I18" s="32" t="n"/>
+      <c r="J18" s="33" t="n"/>
+      <c r="K18" s="32" t="n"/>
+      <c r="L18" s="33" t="n"/>
+      <c r="M18" s="37">
         <f>IF(OR(D18="",J18=""),"",IF(J18&lt;=G18,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>VA05</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D19" s="27">
-        <f>IF(COUNT(B19,C19)&lt;2,"",B19*C19)</f>
-        <v/>
-      </c>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="29">
-        <f>IF(OR(D19="",$E$17=""),"",D19/$E$17)</f>
-        <v/>
-      </c>
-      <c r="G19" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H19" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="n"/>
-      <c r="J19" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K19" s="25" t="inlineStr">
-        <is>
-          <t>Este</t>
-        </is>
-      </c>
-      <c r="L19" s="26" t="n"/>
-      <c r="M19" s="30">
-        <f>IF(OR(D19="",J19=""),"",IF(J19&lt;=G19,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Fachada Sudeste (borde inferior)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>PV04</t>
+          <t>PA01</t>
         </is>
       </c>
       <c r="B20" s="26" t="n">
         <v>3</v>
       </c>
       <c r="C20" s="26" t="n">
-        <v>2.06</v>
+        <v>1</v>
       </c>
       <c r="D20" s="27">
         <f>IF(COUNT(B20,C20)&lt;2,"",B20*C20)</f>
         <v/>
       </c>
-      <c r="E20" s="31" t="n"/>
+      <c r="E20" s="28">
+        <f>SUM(D20:D26)</f>
+        <v/>
+      </c>
       <c r="F20" s="29">
-        <f>IF(OR(D20="",$E$17=""),"",D20/$E$17)</f>
+        <f>IF(OR(D20="",$E$20=""),"",D20/$E$20)</f>
         <v/>
       </c>
       <c r="G20" s="27">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="K20" s="25" t="inlineStr">
         <is>
-          <t>Este</t>
+          <t>Sudeste</t>
         </is>
       </c>
       <c r="L20" s="26" t="n"/>
@@ -8312,26 +8312,44 @@
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="25" t="n"/>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="26" t="n"/>
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>PF04</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C21" s="26" t="n">
+        <v>2.7</v>
+      </c>
       <c r="D21" s="27">
         <f>IF(COUNT(B21,C21)&lt;2,"",B21*C21)</f>
         <v/>
       </c>
       <c r="E21" s="31" t="n"/>
       <c r="F21" s="29">
-        <f>IF(OR(D21="",$E$17=""),"",D21/$E$17)</f>
+        <f>IF(OR(D21="",$E$20=""),"",D21/$E$20)</f>
         <v/>
       </c>
       <c r="G21" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H21" s="25" t="n"/>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
       <c r="I21" s="25" t="n"/>
-      <c r="J21" s="26" t="n"/>
-      <c r="K21" s="25" t="n"/>
+      <c r="J21" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K21" s="25" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
       <c r="L21" s="26" t="n"/>
       <c r="M21" s="30">
         <f>IF(OR(D21="",J21=""),"",IF(J21&lt;=G21,"CUMPLE","NO CUMPLE"))</f>
@@ -8339,73 +8357,114 @@
       </c>
     </row>
     <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="32" t="n"/>
-      <c r="B22" s="33" t="n"/>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="34">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>VA05</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D22" s="27">
         <f>IF(COUNT(B22,C22)&lt;2,"",B22*C22)</f>
         <v/>
       </c>
-      <c r="E22" s="35" t="n"/>
-      <c r="F22" s="36">
-        <f>IF(OR(D22="",$E$17=""),"",D22/$E$17)</f>
-        <v/>
-      </c>
-      <c r="G22" s="34">
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="29">
+        <f>IF(OR(D22="",$E$20=""),"",D22/$E$20)</f>
+        <v/>
+      </c>
+      <c r="G22" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H22" s="32" t="n"/>
-      <c r="I22" s="32" t="n"/>
-      <c r="J22" s="33" t="n"/>
-      <c r="K22" s="32" t="n"/>
-      <c r="L22" s="33" t="n"/>
-      <c r="M22" s="37">
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K22" s="25" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n"/>
+      <c r="M22" s="30">
         <f>IF(OR(D22="",J22=""),"",IF(J22&lt;=G22,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Fachada Oeste</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>PV04</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D23" s="27">
+        <f>IF(COUNT(B23,C23)&lt;2,"",B23*C23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="29">
+        <f>IF(OR(D23="",$E$20=""),"",D23/$E$20)</f>
+        <v/>
+      </c>
+      <c r="G23" s="27">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I23" s="25" t="n"/>
+      <c r="J23" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K23" s="25" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n"/>
+      <c r="M23" s="30">
+        <f>IF(OR(D23="",J23=""),"",IF(J23&lt;=G23,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>PV03</t>
+          <t>PF02</t>
         </is>
       </c>
       <c r="B24" s="26" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="26" t="n">
-        <v>1.76</v>
+        <v>3.75</v>
       </c>
       <c r="D24" s="27">
         <f>IF(COUNT(B24,C24)&lt;2,"",B24*C24)</f>
         <v/>
       </c>
-      <c r="E24" s="28">
-        <f>SUM(D24:D30)</f>
-        <v/>
-      </c>
+      <c r="E24" s="31" t="n"/>
       <c r="F24" s="29">
-        <f>IF(OR(D24="",$E$24=""),"",D24/$E$24)</f>
+        <f>IF(OR(D24="",$E$20=""),"",D24/$E$20)</f>
         <v/>
       </c>
       <c r="G24" s="27">
@@ -8423,7 +8482,7 @@
       </c>
       <c r="K24" s="25" t="inlineStr">
         <is>
-          <t>Oeste</t>
+          <t>Sudeste</t>
         </is>
       </c>
       <c r="L24" s="26" t="n"/>
@@ -8433,44 +8492,26 @@
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>VA02</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C25" s="26" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
       <c r="D25" s="27">
         <f>IF(COUNT(B25,C25)&lt;2,"",B25*C25)</f>
         <v/>
       </c>
       <c r="E25" s="31" t="n"/>
       <c r="F25" s="29">
-        <f>IF(OR(D25="",$E$24=""),"",D25/$E$24)</f>
+        <f>IF(OR(D25="",$E$20=""),"",D25/$E$20)</f>
         <v/>
       </c>
       <c r="G25" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H25" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
+      <c r="H25" s="25" t="n"/>
       <c r="I25" s="25" t="n"/>
-      <c r="J25" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K25" s="25" t="inlineStr">
-        <is>
-          <t>Oeste</t>
-        </is>
-      </c>
+      <c r="J25" s="26" t="n"/>
+      <c r="K25" s="25" t="n"/>
       <c r="L25" s="26" t="n"/>
       <c r="M25" s="30">
         <f>IF(OR(D25="",J25=""),"",IF(J25&lt;=G25,"CUMPLE","NO CUMPLE"))</f>
@@ -8478,114 +8519,73 @@
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>PA02</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" s="26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D26" s="27">
+      <c r="A26" s="32" t="n"/>
+      <c r="B26" s="33" t="n"/>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="34">
         <f>IF(COUNT(B26,C26)&lt;2,"",B26*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="29">
-        <f>IF(OR(D26="",$E$24=""),"",D26/$E$24)</f>
-        <v/>
-      </c>
-      <c r="G26" s="27">
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="36">
+        <f>IF(OR(D26="",$E$20=""),"",D26/$E$20)</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H26" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I26" s="25" t="n"/>
-      <c r="J26" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K26" s="25" t="inlineStr">
-        <is>
-          <t>Oeste</t>
-        </is>
-      </c>
-      <c r="L26" s="26" t="n"/>
-      <c r="M26" s="30">
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="32" t="n"/>
+      <c r="L26" s="33" t="n"/>
+      <c r="M26" s="37">
         <f>IF(OR(D26="",J26=""),"",IF(J26&lt;=G26,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>VA03</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="C27" s="26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D27" s="27">
-        <f>IF(COUNT(B27,C27)&lt;2,"",B27*C27)</f>
-        <v/>
-      </c>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="29">
-        <f>IF(OR(D27="",$E$24=""),"",D27/$E$24)</f>
-        <v/>
-      </c>
-      <c r="G27" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H27" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I27" s="25" t="n"/>
-      <c r="J27" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K27" s="25" t="inlineStr">
-        <is>
-          <t>Oeste</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="n"/>
-      <c r="M27" s="30">
-        <f>IF(OR(D27="",J27=""),"",IF(J27&lt;=G27,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Fachada Noroeste (borde superior)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>PF05</t>
+          <t>PV03</t>
         </is>
       </c>
       <c r="B28" s="26" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="C28" s="26" t="n">
-        <v>0.75</v>
+        <v>1.76</v>
       </c>
       <c r="D28" s="27">
         <f>IF(COUNT(B28,C28)&lt;2,"",B28*C28)</f>
         <v/>
       </c>
-      <c r="E28" s="31" t="n"/>
+      <c r="E28" s="28">
+        <f>SUM(D28:D34)</f>
+        <v/>
+      </c>
       <c r="F28" s="29">
-        <f>IF(OR(D28="",$E$24=""),"",D28/$E$24)</f>
+        <f>IF(OR(D28="",$E$28=""),"",D28/$E$28)</f>
         <v/>
       </c>
       <c r="G28" s="27">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="K28" s="25" t="inlineStr">
         <is>
-          <t>Oeste</t>
+          <t>Noroeste</t>
         </is>
       </c>
       <c r="L28" s="26" t="n"/>
@@ -8613,26 +8613,44 @@
       </c>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="25" t="n"/>
-      <c r="B29" s="26" t="n"/>
-      <c r="C29" s="26" t="n"/>
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>VA02</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>0.75</v>
+      </c>
       <c r="D29" s="27">
         <f>IF(COUNT(B29,C29)&lt;2,"",B29*C29)</f>
         <v/>
       </c>
       <c r="E29" s="31" t="n"/>
       <c r="F29" s="29">
-        <f>IF(OR(D29="",$E$24=""),"",D29/$E$24)</f>
+        <f>IF(OR(D29="",$E$28=""),"",D29/$E$28)</f>
         <v/>
       </c>
       <c r="G29" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H29" s="25" t="n"/>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
       <c r="I29" s="25" t="n"/>
-      <c r="J29" s="26" t="n"/>
-      <c r="K29" s="25" t="n"/>
+      <c r="J29" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K29" s="25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
       <c r="L29" s="26" t="n"/>
       <c r="M29" s="30">
         <f>IF(OR(D29="",J29=""),"",IF(J29&lt;=G29,"CUMPLE","NO CUMPLE"))</f>
@@ -8640,73 +8658,114 @@
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="32" t="n"/>
-      <c r="B30" s="33" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="34">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>PA02</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D30" s="27">
         <f>IF(COUNT(B30,C30)&lt;2,"",B30*C30)</f>
         <v/>
       </c>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="36">
-        <f>IF(OR(D30="",$E$24=""),"",D30/$E$24)</f>
-        <v/>
-      </c>
-      <c r="G30" s="34">
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="29">
+        <f>IF(OR(D30="",$E$28=""),"",D30/$E$28)</f>
+        <v/>
+      </c>
+      <c r="G30" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H30" s="32" t="n"/>
-      <c r="I30" s="32" t="n"/>
-      <c r="J30" s="33" t="n"/>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="33" t="n"/>
-      <c r="M30" s="37">
+      <c r="H30" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K30" s="25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n"/>
+      <c r="M30" s="30">
         <f>IF(OR(D30="",J30=""),"",IF(J30&lt;=G30,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Patio interno (orientacion a confirmar)</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>VA03</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D31" s="27">
+        <f>IF(COUNT(B31,C31)&lt;2,"",B31*C31)</f>
+        <v/>
+      </c>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="29">
+        <f>IF(OR(D31="",$E$28=""),"",D31/$E$28)</f>
+        <v/>
+      </c>
+      <c r="G31" s="27">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="n"/>
+      <c r="J31" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K31" s="25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n"/>
+      <c r="M31" s="30">
+        <f>IF(OR(D31="",J31=""),"",IF(J31&lt;=G31,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>PF01</t>
+          <t>PF05</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="C32" s="26" t="n">
-        <v>3.55</v>
+        <v>0.75</v>
       </c>
       <c r="D32" s="27">
         <f>IF(COUNT(B32,C32)&lt;2,"",B32*C32)</f>
         <v/>
       </c>
-      <c r="E32" s="28">
-        <f>SUM(D32:D37)</f>
-        <v/>
-      </c>
+      <c r="E32" s="31" t="n"/>
       <c r="F32" s="29">
-        <f>IF(OR(D32="",$E$32=""),"",D32/$E$32)</f>
+        <f>IF(OR(D32="",$E$28=""),"",D32/$E$28)</f>
         <v/>
       </c>
       <c r="G32" s="27">
@@ -8722,7 +8781,11 @@
       <c r="J32" s="26" t="n">
         <v>2.8</v>
       </c>
-      <c r="K32" s="25" t="n"/>
+      <c r="K32" s="25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
       <c r="L32" s="26" t="n"/>
       <c r="M32" s="30">
         <f>IF(OR(D32="",J32=""),"",IF(J32&lt;=G32,"CUMPLE","NO CUMPLE"))</f>
@@ -8730,39 +8793,25 @@
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>PF02</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="26" t="n">
-        <v>3.75</v>
-      </c>
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
       <c r="D33" s="27">
         <f>IF(COUNT(B33,C33)&lt;2,"",B33*C33)</f>
         <v/>
       </c>
       <c r="E33" s="31" t="n"/>
       <c r="F33" s="29">
-        <f>IF(OR(D33="",$E$32=""),"",D33/$E$32)</f>
+        <f>IF(OR(D33="",$E$28=""),"",D33/$E$28)</f>
         <v/>
       </c>
       <c r="G33" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H33" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
+      <c r="H33" s="25" t="n"/>
       <c r="I33" s="25" t="n"/>
-      <c r="J33" s="26" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="J33" s="26" t="n"/>
       <c r="K33" s="25" t="n"/>
       <c r="L33" s="26" t="n"/>
       <c r="M33" s="30">
@@ -8771,107 +8820,88 @@
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>PV01</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" s="26" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="D34" s="27">
+      <c r="A34" s="32" t="n"/>
+      <c r="B34" s="33" t="n"/>
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="34">
         <f>IF(COUNT(B34,C34)&lt;2,"",B34*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="29">
-        <f>IF(OR(D34="",$E$32=""),"",D34/$E$32)</f>
-        <v/>
-      </c>
-      <c r="G34" s="27">
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="36">
+        <f>IF(OR(D34="",$E$28=""),"",D34/$E$28)</f>
+        <v/>
+      </c>
+      <c r="G34" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H34" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K34" s="25" t="n"/>
-      <c r="L34" s="26" t="n"/>
-      <c r="M34" s="30">
+      <c r="H34" s="32" t="n"/>
+      <c r="I34" s="32" t="n"/>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="32" t="n"/>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="37">
         <f>IF(OR(D34="",J34=""),"",IF(J34&lt;=G34,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Plano: Ubicacion a confirmar</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>PV04 (2)</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B36" s="26" t="n">
         <v>2.95</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C36" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="D35" s="27">
-        <f>IF(COUNT(B35,C35)&lt;2,"",B35*C35)</f>
-        <v/>
-      </c>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="29">
-        <f>IF(OR(D35="",$E$32=""),"",D35/$E$32)</f>
-        <v/>
-      </c>
-      <c r="G35" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H35" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I35" s="25" t="n"/>
-      <c r="J35" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K35" s="25" t="n"/>
-      <c r="L35" s="26" t="n"/>
-      <c r="M35" s="30">
-        <f>IF(OR(D35="",J35=""),"",IF(J35&lt;=G35,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="26" t="n"/>
-      <c r="C36" s="26" t="n"/>
       <c r="D36" s="27">
         <f>IF(COUNT(B36,C36)&lt;2,"",B36*C36)</f>
         <v/>
       </c>
-      <c r="E36" s="31" t="n"/>
+      <c r="E36" s="28">
+        <f>SUM(D36:D38)</f>
+        <v/>
+      </c>
       <c r="F36" s="29">
-        <f>IF(OR(D36="",$E$32=""),"",D36/$E$32)</f>
+        <f>IF(OR(D36="",$E$36=""),"",D36/$E$36)</f>
         <v/>
       </c>
       <c r="G36" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H36" s="25" t="n"/>
+      <c r="H36" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
       <c r="I36" s="25" t="n"/>
-      <c r="J36" s="26" t="n"/>
+      <c r="J36" s="26" t="n">
+        <v>2.8</v>
+      </c>
       <c r="K36" s="25" t="n"/>
       <c r="L36" s="26" t="n"/>
       <c r="M36" s="30">
@@ -8880,53 +8910,61 @@
       </c>
     </row>
     <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="32" t="n"/>
-      <c r="B37" s="33" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="34">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="27">
         <f>IF(COUNT(B37,C37)&lt;2,"",B37*C37)</f>
         <v/>
       </c>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="36">
-        <f>IF(OR(D37="",$E$32=""),"",D37/$E$32)</f>
-        <v/>
-      </c>
-      <c r="G37" s="34">
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="29">
+        <f>IF(OR(D37="",$E$36=""),"",D37/$E$36)</f>
+        <v/>
+      </c>
+      <c r="G37" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H37" s="32" t="n"/>
-      <c r="I37" s="32" t="n"/>
-      <c r="J37" s="33" t="n"/>
-      <c r="K37" s="32" t="n"/>
-      <c r="L37" s="33" t="n"/>
-      <c r="M37" s="37">
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
+      <c r="J37" s="26" t="n"/>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="26" t="n"/>
+      <c r="M37" s="30">
         <f>IF(OR(D37="",J37=""),"",IF(J37&lt;=G37,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="32" t="n"/>
+      <c r="B38" s="33" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="34">
+        <f>IF(COUNT(B38,C38)&lt;2,"",B38*C38)</f>
+        <v/>
+      </c>
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="36">
+        <f>IF(OR(D38="",$E$36=""),"",D38/$E$36)</f>
+        <v/>
+      </c>
+      <c r="G38" s="34">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H38" s="32" t="n"/>
+      <c r="I38" s="32" t="n"/>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="32" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="37">
+        <f>IF(OR(D38="",J38=""),"",IF(J38&lt;=G38,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="inlineStr">
-        <is>
-          <t>COMO SE COMPLETA</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="n"/>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n"/>
@@ -8941,9 +8979,9 @@
       <c r="M39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
-        <is>
-          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>COMO SE COMPLETA</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
@@ -8962,7 +9000,7 @@
     <row r="41">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
+          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
         </is>
       </c>
       <c r="B41" s="2" t="n"/>
@@ -8981,7 +9019,7 @@
     <row r="42">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
+          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>
@@ -9000,7 +9038,7 @@
     <row r="43">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
+          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
         </is>
       </c>
       <c r="B43" s="2" t="n"/>
@@ -9019,7 +9057,7 @@
     <row r="44">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>Orientacion y factor de exposicion solar: el factor depende de la orientacion y de la proteccion.</t>
+          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
@@ -9036,7 +9074,11 @@
       <c r="M44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="39" t="inlineStr"/>
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>Orientacion y factor de exposicion solar: el factor depende de la orientacion y de la proteccion.</t>
+        </is>
+      </c>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n"/>
@@ -9051,11 +9093,7 @@
       <c r="M45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="39" t="inlineStr">
-        <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
-        </is>
-      </c>
+      <c r="A46" s="39" t="inlineStr"/>
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -9072,7 +9110,7 @@
     <row r="47">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -9089,7 +9127,11 @@
       <c r="M47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="39" t="inlineStr"/>
+      <c r="A48" s="39" t="inlineStr">
+        <is>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+        </is>
+      </c>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n"/>
@@ -9104,11 +9146,7 @@
       <c r="M48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
-        </is>
-      </c>
+      <c r="A49" s="39" t="inlineStr"/>
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n"/>
@@ -9125,7 +9163,7 @@
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9144,7 +9182,7 @@
     <row r="51">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B51" s="2" t="n"/>
@@ -9163,7 +9201,7 @@
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9182,7 +9220,7 @@
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
         </is>
       </c>
       <c r="B53" s="2" t="n"/>
@@ -9199,7 +9237,11 @@
       <c r="M53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr"/>
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+        </is>
+      </c>
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n"/>
@@ -9214,11 +9256,7 @@
       <c r="M54" s="2" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="39" t="inlineStr">
-        <is>
-          <t>ORIENTACION: el simbolo de norte del plano de plantas (flecha con arco, arriba a la derecha)</t>
-        </is>
-      </c>
+      <c r="A55" s="39" t="inlineStr"/>
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n"/>
@@ -9235,7 +9273,7 @@
     <row r="56">
       <c r="A56" s="39" t="inlineStr">
         <is>
-          <t>apunta hacia la derecha de la hoja. Entonces: derecha = Norte, izquierda = Sur, abajo = Este,</t>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -9254,7 +9292,7 @@
     <row r="57">
       <c r="A57" s="39" t="inlineStr">
         <is>
-          <t>arriba = Oeste. Coincide con los rotulos Dormitorio Norte y Dormitorio Sur del plano.</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B57" s="2" t="n"/>
@@ -9273,7 +9311,7 @@
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta.</t>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9292,7 +9330,7 @@
     <row r="59">
       <c r="A59" s="39" t="inlineStr">
         <is>
-          <t>Las tres aberturas que dan al patio interno quedan en un bloque aparte: hay que confirmar</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
         </is>
       </c>
       <c r="B59" s="2" t="n"/>
@@ -9311,7 +9349,7 @@
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
         <is>
-          <t>a que lado del patio dan antes de asignarles orientacion y factor de exposicion solar.</t>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
         </is>
       </c>
       <c r="B60" s="2" t="n"/>
@@ -9328,7 +9366,11 @@
       <c r="M60" s="2" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="39" t="inlineStr"/>
+      <c r="A61" s="39" t="inlineStr">
+        <is>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+        </is>
+      </c>
       <c r="B61" s="2" t="n"/>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n"/>
@@ -9345,7 +9387,7 @@
     <row r="62">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B62" s="2" t="n"/>
@@ -9379,7 +9421,7 @@
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9398,7 +9440,7 @@
     <row r="65">
       <c r="A65" s="39" t="inlineStr">
         <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -9415,11 +9457,7 @@
       <c r="M65" s="2" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="39" t="inlineStr">
-        <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
-        </is>
-      </c>
+      <c r="A66" s="39" t="inlineStr"/>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n"/>
@@ -9433,24 +9471,115 @@
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
     </row>
+    <row r="67">
+      <c r="A67" s="39" t="inlineStr">
+        <is>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="39" t="inlineStr"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="39" t="inlineStr">
+        <is>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="39" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E32:E37"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="E20:E26"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="E17:E22"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="E28:E34"/>
     <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A35:M35"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="E24:E30"/>
-    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="E7:E13"/>
+    <mergeCell ref="E15:E18"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="M6:M37">
+  <conditionalFormatting sqref="M6:M38">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"CUMPLE"</formula>
     </cfRule>
@@ -9459,13 +9588,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H6:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$8:$A$15</formula1>
     </dataValidation>
-    <dataValidation sqref="I6:I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6:I38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$19:$A$25</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Norte,Sur,Este,Oeste,Noreste,Noroeste,Sudeste,Sudoeste,Horizontal"</formula1>
     </dataValidation>
   </dataValidations>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -258,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -451,6 +451,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4887,7 +4890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5401,6 +5404,296 @@
       <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="72" t="inlineStr">
+        <is>
+          <t>FACTOR DE EXPOSICION SOLAR MAXIMO ADMITIDO  (Ordenanza 8757/11)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="59" t="inlineStr">
+        <is>
+          <t>orientacion</t>
+        </is>
+      </c>
+      <c r="B45" s="60" t="inlineStr">
+        <is>
+          <t>FES max</t>
+        </is>
+      </c>
+      <c r="C45" s="60" t="inlineStr">
+        <is>
+          <t>cuadrante</t>
+        </is>
+      </c>
+      <c r="D45" s="59" t="inlineStr">
+        <is>
+          <t>observacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="61" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="B46" s="73" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C46" s="74" t="inlineStr">
+        <is>
+          <t>341 a 20 grados</t>
+        </is>
+      </c>
+      <c r="D46" s="66" t="inlineStr">
+        <is>
+          <t>Cuadrante Norte (NNE-NNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>Este</t>
+        </is>
+      </c>
+      <c r="B47" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C47" s="74" t="inlineStr">
+        <is>
+          <t>21 a 160 grados</t>
+        </is>
+      </c>
+      <c r="D47" s="66" t="inlineStr">
+        <is>
+          <t>Modificado a 0,39 por decreto de 2021. Verificar vigencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>Oeste</t>
+        </is>
+      </c>
+      <c r="B48" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C48" s="74" t="inlineStr">
+        <is>
+          <t>201 a 340 grados</t>
+        </is>
+      </c>
+      <c r="D48" s="66" t="inlineStr">
+        <is>
+          <t>Modificado a 0,39 por decreto de 2021. Verificar vigencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="61" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="B49" s="73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C49" s="74" t="inlineStr">
+        <is>
+          <t>161 a 200 grados</t>
+        </is>
+      </c>
+      <c r="D49" s="66" t="inlineStr">
+        <is>
+          <t>Cuadrante Sur (SSE-SSO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
+      <c r="B50" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C50" s="74" t="inlineStr">
+        <is>
+          <t>cae en cuadrante Este</t>
+        </is>
+      </c>
+      <c r="D50" s="66" t="inlineStr">
+        <is>
+          <t>45 grados: entra en el cuadrante Este (21 a 160).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="B51" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C51" s="74" t="inlineStr">
+        <is>
+          <t>cae en cuadrante Este</t>
+        </is>
+      </c>
+      <c r="D51" s="66" t="inlineStr">
+        <is>
+          <t>135 grados: entra en el cuadrante Este (21 a 160).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="61" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
+      <c r="B52" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C52" s="74" t="inlineStr">
+        <is>
+          <t>cae en cuadrante Oeste</t>
+        </is>
+      </c>
+      <c r="D52" s="66" t="inlineStr">
+        <is>
+          <t>225 grados: entra en el cuadrante Oeste (201 a 340).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="61" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="B53" s="73" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C53" s="74" t="inlineStr">
+        <is>
+          <t>cae en cuadrante Oeste</t>
+        </is>
+      </c>
+      <c r="D53" s="66" t="inlineStr">
+        <is>
+          <t>315 grados: entra en el cuadrante Oeste (201 a 340).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="61" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
+        </is>
+      </c>
+      <c r="B54" s="73" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C54" s="74" t="inlineStr">
+        <is>
+          <t>lucernarios</t>
+        </is>
+      </c>
+      <c r="D54" s="66" t="inlineStr">
+        <is>
+          <t>Planos inclinados con angulo menor a 60 grados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="38" t="inlineStr">
+        <is>
+          <t>La casa esta girada 45 grados respecto del norte, asi que NINGUNA de sus cuatro fachadas</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t>cae en el cuadrante Norte ni en el Sur: las cuatro entran en el cuadrante Este/Oeste, que es</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="39" t="inlineStr">
+        <is>
+          <t>el mas exigente (0,30, o 0,39 segun la modificacion de 2021). Conviene confirmarlo en la</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="39" t="inlineStr">
+        <is>
+          <t>Secretaria de Planeamiento antes de presentar: hay versiones distintas dando vueltas.</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="38" t="inlineStr">
+        <is>
+          <t>Si la abertura ocupa menos del 20% del lado expuesto del local, NO hay que verificar el FES</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="39" t="inlineStr">
+        <is>
+          <t>(si la transmitancia). Fuente: preguntas frecuentes de la Secretaria de Planeamiento.</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5421,180 +5714,180 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>MEMORIA - ILUMINACION Y VENTILACION</t>
         </is>
       </c>
-      <c r="B1" s="75" t="inlineStr"/>
+      <c r="B1" s="76" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="75" t="inlineStr"/>
-      <c r="B2" s="76" t="inlineStr"/>
+      <c r="A2" s="76" t="inlineStr"/>
+      <c r="B2" s="77" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>CRITERIO</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>Area de iluminacion requerida = superficie del local / 9</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="75" t="inlineStr"/>
-      <c r="B4" s="76" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr"/>
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>Area de ventilacion requerida = un tercio de la de iluminacion = superficie / 27</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="75" t="inlineStr"/>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr"/>
+      <c r="B5" s="77" t="inlineStr">
         <is>
           <t>Area proyectada: la vidriada de la carpinteria para iluminacion, y la parte que</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="inlineStr"/>
-      <c r="B6" s="76" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr"/>
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>realmente abre para ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="inlineStr"/>
-      <c r="B7" s="76" t="inlineStr"/>
+      <c r="A7" s="76" t="inlineStr"/>
+      <c r="B7" s="77" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>RESULTADO</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>Los trece locales cumplen holgadamente iluminacion y ventilacion.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="inlineStr"/>
-      <c r="B9" s="76" t="inlineStr"/>
+      <c r="A9" s="76" t="inlineStr"/>
+      <c r="B9" s="77" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="75" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>CORRECCION</t>
         </is>
       </c>
-      <c r="B10" s="75" t="inlineStr">
+      <c r="B10" s="76" t="inlineStr">
         <is>
           <t>Local 07, Hall / ingreso: la planilla original traia 0,66 y 0,22, que son los</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="75" t="inlineStr"/>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr"/>
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>valores del local 03 (Lavadero, 6,0 m2). Con sus 3,50 x 2,15 = 7,53 m2 corresponden</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="75" t="inlineStr"/>
-      <c r="B12" s="76" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr"/>
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>0,84 y 0,28. No cambia el resultado, pero el numero no cerraba con la superficie</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="75" t="inlineStr"/>
-      <c r="B13" s="76" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr"/>
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>declarada y un verificador lo puede observar.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="75" t="inlineStr"/>
-      <c r="B14" s="76" t="inlineStr"/>
+      <c r="A14" s="76" t="inlineStr"/>
+      <c r="B14" s="77" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>A REVISAR</t>
         </is>
       </c>
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>Local 14, Estar / Playroom: declara 5,00 m2 de ventilacion sobre 5,00 m2 de</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="75" t="inlineStr"/>
-      <c r="B16" s="76" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr"/>
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>iluminacion, es decir una carpinteria enteramente abrible. En los demas locales</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="75" t="inlineStr"/>
-      <c r="B17" s="76" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr"/>
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>la relacion es del 50 por ciento. Conviene verificar la carpinteria real.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="75" t="inlineStr"/>
-      <c r="B18" s="76" t="inlineStr"/>
+      <c r="A18" s="76" t="inlineStr"/>
+      <c r="B18" s="77" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="75" t="inlineStr"/>
-      <c r="B19" s="76" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr"/>
+      <c r="B19" s="77" t="inlineStr">
         <is>
           <t>Local 02, Deposito: figura sin exigencia por no ser habitable. Son 11,8 m2</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="75" t="inlineStr"/>
-      <c r="B20" s="76" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr"/>
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>cerrados: si se lo considera habitable hay que preverle conducto.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="75" t="inlineStr"/>
-      <c r="B21" s="76" t="inlineStr"/>
+      <c r="A21" s="76" t="inlineStr"/>
+      <c r="B21" s="77" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="75" t="inlineStr">
+      <c r="A22" s="76" t="inlineStr">
         <is>
           <t>REDONDEOS</t>
         </is>
       </c>
-      <c r="B22" s="75" t="inlineStr">
+      <c r="B22" s="76" t="inlineStr">
         <is>
           <t>Diferencias menores que no afectan: local 03 da 5,95 m2 y figura 6,0;</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="75" t="inlineStr"/>
-      <c r="B23" s="76" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr"/>
+      <c r="B23" s="77" t="inlineStr">
         <is>
           <t>local 09 da 12,25 y figura 12,3.</t>
         </is>
@@ -5619,592 +5912,592 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
         </is>
       </c>
-      <c r="B1" s="75" t="inlineStr"/>
+      <c r="B1" s="76" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="75" t="inlineStr"/>
-      <c r="B2" s="76" t="inlineStr"/>
+      <c r="A2" s="76" t="inlineStr"/>
+      <c r="B2" s="77" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>NORMATIVA</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>CIRSOC 201. Hormigon H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200 kg/cm2).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="75" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr">
         <is>
           <t>UNIDADES</t>
         </is>
       </c>
-      <c r="B4" s="75" t="inlineStr">
+      <c r="B4" s="76" t="inlineStr">
         <is>
           <t>Longitudes en m y cm. Cargas en kg/m. Momentos en kgm. Tensiones en kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>b = ancho | h = altura util | d = altura total (igual criterio que la planilla de catedra).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="inlineStr"/>
-      <c r="B6" s="76" t="inlineStr"/>
+      <c r="A6" s="76" t="inlineStr"/>
+      <c r="B6" s="77" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B7" s="75" t="inlineStr"/>
+      <c r="B7" s="76" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>Entrepiso PA</t>
         </is>
       </c>
-      <c r="B8" s="76" t="inlineStr">
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>Losa maciza 12 cm 300 + contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="inlineStr"/>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr"/>
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>g = 550 kg/m2       q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="75" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>Azotea</t>
         </is>
       </c>
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>Losa 300 + contrapiso de pendiente 140 + carpeta 42 + aislacion y membrana 50 + cielorraso 20</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="75" t="inlineStr"/>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr"/>
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>g = 560 kg/m2       q = 100 kg/m2 (cubierta no accesible)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>Mamposteria</t>
         </is>
       </c>
-      <c r="B12" s="76" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>250 kg/m2. Altura 2,60 m en PA y 1,00 m de parapeto en azotea.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="75" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>Peso propio</t>
         </is>
       </c>
-      <c r="B13" s="76" t="inlineStr">
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>2400 kg/m3 x b x d, viga por viga.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="75" t="inlineStr">
+      <c r="A14" s="76" t="inlineStr">
         <is>
           <t>Carga de calculo</t>
         </is>
       </c>
-      <c r="B14" s="76" t="inlineStr">
+      <c r="B14" s="77" t="inlineStr">
         <is>
           <t>p = 1,2 (g x B + peso propio + muro) + 1,6 (q x B)        B = ancho tributario</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="75" t="inlineStr"/>
-      <c r="B15" s="76" t="inlineStr"/>
+      <c r="A15" s="76" t="inlineStr"/>
+      <c r="B15" s="77" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="75" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B16" s="75" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
         <is>
           <t>Coeficientes segun esquema (tabla en hoja Datos):</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="75" t="inlineStr"/>
-      <c r="B17" s="76" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr"/>
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  Simplemente apoyada   M = pL2/8                    R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="75" t="inlineStr"/>
-      <c r="B18" s="76" t="inlineStr">
+      <c r="A18" s="76" t="inlineStr"/>
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  Continua              M = pL2/14   Mapoyo = pL2/10  R = 0,575 pL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="75" t="inlineStr"/>
-      <c r="B19" s="76" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr"/>
+      <c r="B19" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  Empotrada-apoyada     M = 9pL2/128 Mapoyo = pL2/8   R = 0,625 pL</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="75" t="inlineStr"/>
-      <c r="B20" s="76" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr"/>
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  Biempotrada           M = pL2/24   Mapoyo = pL2/12  R = 0,500 pL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="75" t="inlineStr"/>
-      <c r="B21" s="76" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr"/>
+      <c r="B21" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  Voladizo                           Mapoyo = pL2/2   R = 1,000 pL</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="75" t="inlineStr"/>
-      <c r="B22" s="76" t="inlineStr"/>
+      <c r="A22" s="76" t="inlineStr"/>
+      <c r="B22" s="77" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="75" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>3. FLEXION</t>
         </is>
       </c>
-      <c r="B23" s="75" t="inlineStr">
+      <c r="B23" s="76" t="inlineStr">
         <is>
           <t>k = M / (phi b h2 f'c)      w = 1 - RAIZ(1 - 2k)      As = w b h f'c / fy</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="75" t="inlineStr"/>
-      <c r="B24" s="76" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr"/>
+      <c r="B24" s="77" t="inlineStr">
         <is>
           <t>As min = 0,0033 b h       As max = 0,0163 b h (0,75 de la cuantia balanceada)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="75" t="inlineStr"/>
-      <c r="B25" s="76" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr"/>
+      <c r="B25" s="77" t="inlineStr">
         <is>
           <t>Si la armadura no entra en una capa se disponen dos y el recubrimiento pasa a 6 cm.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="75" t="inlineStr"/>
-      <c r="B26" s="76" t="inlineStr"/>
+      <c r="A26" s="76" t="inlineStr"/>
+      <c r="B26" s="77" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="75" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>4. CORTE</t>
         </is>
       </c>
-      <c r="B27" s="75" t="inlineStr">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>T = R / (b x 0,85 h)       tension tangencial en el apoyo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="75" t="inlineStr"/>
-      <c r="B28" s="76" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr"/>
+      <c r="B28" s="77" t="inlineStr">
         <is>
           <t>Vc = 0,53 RAIZ(f'c) b h        phi Vn = 0,75 (Vc + Av fy h / s)  &gt;=  R</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="75" t="inlineStr"/>
-      <c r="B29" s="76" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr"/>
+      <c r="B29" s="77" t="inlineStr">
         <is>
           <t>Av = 2 ramas. Se aumenta el diametro antes que cerrar la separacion por debajo de 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="75" t="inlineStr"/>
-      <c r="B30" s="76" t="inlineStr"/>
+      <c r="A30" s="76" t="inlineStr"/>
+      <c r="B30" s="77" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="75" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr">
         <is>
           <t>5. FLECHA</t>
         </is>
       </c>
-      <c r="B31" s="75" t="inlineStr">
+      <c r="B31" s="76" t="inlineStr">
         <is>
           <t>Altura minima: simplemente apoyada L/16, un extremo continuo L/18,5,</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="75" t="inlineStr"/>
-      <c r="B32" s="76" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr"/>
+      <c r="B32" s="77" t="inlineStr">
         <is>
           <t>ambos extremos continuos L/21, voladizo L/8.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="75" t="inlineStr"/>
-      <c r="B33" s="76" t="inlineStr"/>
+      <c r="A33" s="76" t="inlineStr"/>
+      <c r="B33" s="77" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="75" t="inlineStr">
+      <c r="A34" s="76" t="inlineStr">
         <is>
           <t>6. VIGAS INVERTIDAS</t>
         </is>
       </c>
-      <c r="B34" s="75" t="inlineStr">
+      <c r="B34" s="76" t="inlineStr">
         <is>
           <t>Las vigas de BORDE son invertidas: sobresalen 70 cm por encima del fondo de</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="75" t="inlineStr"/>
-      <c r="B35" s="76" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr"/>
+      <c r="B35" s="77" t="inlineStr">
         <is>
           <t>losa (cotas N.F.L +3,50 / N.S.V +4,20 y N.F.L +6,80 / N.S.V +7,50 del plano).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="75" t="inlineStr"/>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr"/>
+      <c r="B36" s="77" t="inlineStr">
         <is>
           <t>losa. Lo confirman las cotas del plano y el hecho de que el cielorraso sea de</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="75" t="inlineStr"/>
-      <c r="B37" s="76" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr"/>
+      <c r="B37" s="77" t="inlineStr">
         <is>
           <t>VI 06 mide 14,00 m en total y es el cuarto borde de L07. Sobre su eje hay cuatro</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="75" t="inlineStr"/>
-      <c r="B38" s="76" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr"/>
+      <c r="B38" s="77" t="inlineStr">
         <is>
           <t>columnas, de modo que trabaja como viga continua de tres tramos de 4,10, 4,32 y</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="75" t="inlineStr"/>
-      <c r="B39" s="76" t="inlineStr">
+      <c r="A39" s="76" t="inlineStr"/>
+      <c r="B39" s="77" t="inlineStr">
         <is>
           <t>6,53 m. Se calcula con el mayor, 6,53 m, que es el que gobierna.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="75" t="inlineStr"/>
-      <c r="B40" s="76" t="inlineStr">
+      <c r="A40" s="76" t="inlineStr"/>
+      <c r="B40" s="77" t="inlineStr">
         <is>
           <t>hormigon visto: una viga colgante quedaria a la vista. El computo metrico las</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="75" t="inlineStr"/>
-      <c r="B41" s="76" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr"/>
+      <c r="B41" s="77" t="inlineStr">
         <is>
           <t>agrupa a las 28 bajo el rubro Vigas invertidas 15x70.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="75" t="inlineStr"/>
-      <c r="B42" s="76" t="inlineStr">
+      <c r="A42" s="76" t="inlineStr"/>
+      <c r="B42" s="77" t="inlineStr">
         <is>
           <t>Esto define donde la losa aporta ala comprimida:</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="75" t="inlineStr"/>
-      <c r="B43" s="76" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr"/>
+      <c r="B43" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga COLGANTE  -&gt; la losa esta arriba  -&gt; ala util en el TRAMO (momento positivo)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="75" t="inlineStr"/>
-      <c r="B44" s="76" t="inlineStr">
+      <c r="A44" s="76" t="inlineStr"/>
+      <c r="B44" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  viga INVERTIDA -&gt; la losa esta abajo   -&gt; ala util en el APOYO (momento negativo)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="75" t="inlineStr"/>
-      <c r="B45" s="76" t="inlineStr">
+      <c r="A45" s="76" t="inlineStr"/>
+      <c r="B45" s="77" t="inlineStr">
         <is>
           <t>En la zona con ala se adopta b efectivo = min(L/4 ; b + 16 hf); en la otra, la</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="75" t="inlineStr"/>
-      <c r="B46" s="76" t="inlineStr">
+      <c r="A46" s="76" t="inlineStr"/>
+      <c r="B46" s="77" t="inlineStr">
         <is>
           <t>seccion es rectangular de ancho b. Las columnas b ef tramo y b ef apoyo lo muestran.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="75" t="inlineStr"/>
-      <c r="B47" s="76" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr"/>
+      <c r="B47" s="77" t="inlineStr">
         <is>
           <t>PENDIENTE: las invertidas de BORDE (VI 01a, 01b, 07a, 07b, 07c, 11a, 11b, 11c,</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="75" t="inlineStr"/>
-      <c r="B48" s="76" t="inlineStr">
+      <c r="A48" s="76" t="inlineStr"/>
+      <c r="B48" s="77" t="inlineStr">
         <is>
           <t>15a y 15b) reciben la reaccion de la losa de un solo lado, excentrica respecto</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="75" t="inlineStr"/>
-      <c r="B49" s="76" t="inlineStr">
+      <c r="A49" s="76" t="inlineStr"/>
+      <c r="B49" s="77" t="inlineStr">
         <is>
           <t>de su eje, y quedan sometidas a TORSION. Esta planilla no la verifica.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="75" t="inlineStr"/>
-      <c r="B50" s="76" t="inlineStr"/>
+      <c r="A50" s="76" t="inlineStr"/>
+      <c r="B50" s="77" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="75" t="inlineStr">
+      <c r="A51" s="76" t="inlineStr">
         <is>
           <t>7. RESULTADO</t>
         </is>
       </c>
-      <c r="B51" s="75" t="inlineStr">
+      <c r="B51" s="76" t="inlineStr">
         <is>
           <t>30 vigas: 21 del entrepiso PA y 9 de la losa de techo. 28 verifican.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="75" t="inlineStr"/>
-      <c r="B52" s="76" t="inlineStr">
+      <c r="A52" s="76" t="inlineStr"/>
+      <c r="B52" s="77" t="inlineStr">
         <is>
           <t>VI 02 (15x60, 9,88 m): recibe L02 y L03, B = 2,88 m. La armadura de apoyo</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="75" t="inlineStr"/>
-      <c r="B53" s="76" t="inlineStr">
+      <c r="A53" s="76" t="inlineStr"/>
+      <c r="B53" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   necesaria ronda los 25 cm2 y supera la cuantia maxima. Los apoyos estan</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="75" t="inlineStr"/>
-      <c r="B54" s="76" t="inlineStr">
+      <c r="A54" s="76" t="inlineStr"/>
+      <c r="B54" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   confirmados en obra: tabique T07 perpendicular arriba y COL 02 abajo, sin apoyo</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="75" t="inlineStr"/>
-      <c r="B55" s="76" t="inlineStr">
+      <c r="A55" s="76" t="inlineStr"/>
+      <c r="B55" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   intermedio. Para esta carga la seccion necesaria es 15x75.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="75" t="inlineStr"/>
-      <c r="B56" s="76" t="inlineStr">
+      <c r="A56" s="76" t="inlineStr"/>
+      <c r="B56" s="77" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,83 m). Recibe L03, B = 2,08 m, y no</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="75" t="inlineStr"/>
-      <c r="B57" s="76" t="inlineStr">
+      <c r="A57" s="76" t="inlineStr"/>
+      <c r="B57" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   verifica: haria falta mas espesor. Tampoco verifica con B = 0,60 m, asi</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="75" t="inlineStr"/>
-      <c r="B58" s="76" t="inlineStr">
+      <c r="A58" s="76" t="inlineStr"/>
+      <c r="B58" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   que el problema no es la hipotesis de carga sino la relacion luz/espesor. Una viga</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="75" t="inlineStr"/>
-      <c r="B59" s="76" t="inlineStr">
+      <c r="A59" s="76" t="inlineStr"/>
+      <c r="B59" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   chata del mismo espesor que la losa no puede ser apoyo lineal de un pano de 4,15 m.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="75" t="inlineStr"/>
-      <c r="B60" s="76" t="inlineStr">
+      <c r="A60" s="76" t="inlineStr"/>
+      <c r="B60" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   Revisar si tiene un muro debajo que acorte su luz libre.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="75" t="inlineStr"/>
-      <c r="B61" s="76" t="inlineStr">
+      <c r="A61" s="76" t="inlineStr"/>
+      <c r="B61" s="77" t="inlineStr">
         <is>
           <t>VCH 03a (40x13, 3,71 m): excede la cuantia maxima y no llega a la altura minima por</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="75" t="inlineStr"/>
-      <c r="B62" s="76" t="inlineStr">
+      <c r="A62" s="76" t="inlineStr"/>
+      <c r="B62" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">   flecha. Revisar el ancho tributario: si solo recibe el muro y no losa, baja mucho.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="75" t="inlineStr"/>
-      <c r="B63" s="76" t="inlineStr"/>
+      <c r="A63" s="76" t="inlineStr"/>
+      <c r="B63" s="77" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="75" t="inlineStr">
+      <c r="A64" s="76" t="inlineStr">
         <is>
           <t>8. ALCANCE</t>
         </is>
       </c>
-      <c r="B64" s="76" t="inlineStr">
+      <c r="B64" s="77" t="inlineStr">
         <is>
           <t>No se incluyen las 31 vigas de fundacion (VF01 a VF18c): su calculo depende de las</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="75" t="inlineStr"/>
-      <c r="B65" s="76" t="inlineStr">
+      <c r="A65" s="76" t="inlineStr"/>
+      <c r="B65" s="77" t="inlineStr">
         <is>
           <t>cargas que bajan por las columnas y corresponde hacerlo despues. Tampoco losas ni columnas.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="75" t="inlineStr"/>
-      <c r="B66" s="76" t="inlineStr"/>
+      <c r="A66" s="76" t="inlineStr"/>
+      <c r="B66" s="77" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="75" t="inlineStr">
+      <c r="A67" s="76" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B67" s="75" t="inlineStr">
+      <c r="B67" s="76" t="inlineStr">
         <is>
           <t>El ancho tributario B esta relevado solo en</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="75" t="inlineStr"/>
-      <c r="B68" s="76" t="inlineStr">
+      <c r="A68" s="76" t="inlineStr"/>
+      <c r="B68" s="77" t="inlineStr">
         <is>
           <t>VI 02 (0,80 m) y VCH 03a (2,08 m). En las demas sigue adoptado en 2,00 m, a falta</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="75" t="inlineStr"/>
-      <c r="B69" s="76" t="inlineStr">
+      <c r="A69" s="76" t="inlineStr"/>
+      <c r="B69" s="77" t="inlineStr">
         <is>
           <t>hipotesis mas influyente del calculo: ajustarla viga por viga en la columna B trib.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="75" t="inlineStr"/>
-      <c r="B70" s="76" t="inlineStr">
+      <c r="A70" s="76" t="inlineStr"/>
+      <c r="B70" s="77" t="inlineStr">
         <is>
           <t>El esquema se asigno por criterio: continua si integra una serie a-b-c o si supera 5,5 m.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="75" t="inlineStr"/>
-      <c r="B71" s="76" t="inlineStr">
+      <c r="A71" s="76" t="inlineStr"/>
+      <c r="B71" s="77" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -6229,368 +6522,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - LOSAS</t>
         </is>
       </c>
-      <c r="B1" s="75" t="inlineStr"/>
+      <c r="B1" s="76" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="75" t="inlineStr"/>
-      <c r="B2" s="76" t="inlineStr"/>
+      <c r="A2" s="76" t="inlineStr"/>
+      <c r="B2" s="77" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>METODO</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>Tensiones admisibles, igual criterio que la planilla modelo de la catedra.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="75" t="inlineStr"/>
-      <c r="B4" s="76" t="inlineStr">
+      <c r="A4" s="76" t="inlineStr"/>
+      <c r="B4" s="77" t="inlineStr">
         <is>
           <t>Se verifico contra la fila de ejemplo: momentos y reacciones coinciden exactamente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). Tension admisible 2400 kg/cm2.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="76" t="inlineStr">
         <is>
           <t>h = altura util | d = espesor total. Recubrimiento 1,5 cm.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="inlineStr"/>
-      <c r="B7" s="76" t="inlineStr"/>
+      <c r="A7" s="76" t="inlineStr"/>
+      <c r="B7" s="77" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="75" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="76" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q      (cargas de servicio, sin mayorar)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="inlineStr"/>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr"/>
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>Peso propio = 2400 x d / 100, calculado con el espesor propio de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="75" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr">
         <is>
           <t>S/PB</t>
         </is>
       </c>
-      <c r="B10" s="76" t="inlineStr">
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>Terminaciones 242 kg/m2 (contrapiso 130 + carpeta 42 + piso 50 + cielorraso 20)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="75" t="inlineStr"/>
-      <c r="B11" s="76" t="inlineStr">
+      <c r="A11" s="76" t="inlineStr"/>
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>q = 200 kg/m2 (vivienda)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>S/PA</t>
         </is>
       </c>
-      <c r="B12" s="76" t="inlineStr">
+      <c r="B12" s="77" t="inlineStr">
         <is>
           <t>Terminaciones 252 kg/m2 (contrapiso pendiente 140 + carpeta 42 + aislacion 50 +</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="75" t="inlineStr"/>
-      <c r="B13" s="76" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr"/>
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>cielorraso 20).  q = 100 kg/m2 (azotea no accesible)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="75" t="inlineStr"/>
-      <c r="B14" s="76" t="inlineStr"/>
+      <c r="A14" s="76" t="inlineStr"/>
+      <c r="B14" s="77" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
         </is>
       </c>
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>M = coeficiente x p x L2, segun el grado de empotramiento:</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="75" t="inlineStr"/>
-      <c r="B16" s="76" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr"/>
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  1/8 simplemente apoyada    1/10 y 1/14 continua    1/12 biempotrada    1/2 voladizo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="75" t="inlineStr"/>
-      <c r="B17" s="76" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr"/>
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>R = coeficiente x p x L. En voladizo Rx = p x L y Ry no corresponde.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="75" t="inlineStr"/>
-      <c r="B18" s="76" t="inlineStr"/>
+      <c r="A18" s="76" t="inlineStr"/>
+      <c r="B18" s="77" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B19" s="75" t="inlineStr">
+      <c r="B19" s="76" t="inlineStr">
         <is>
           <t>As = M x 100 / (2400 x 0,9 x h)        [cm2/m]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="75" t="inlineStr"/>
-      <c r="B20" s="76" t="inlineStr">
+      <c r="A20" s="76" t="inlineStr"/>
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>separacion = 100 x area de la barra / As, redondeada, con maximo 20 cm</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="75" t="inlineStr"/>
-      <c r="B21" s="76" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr"/>
+      <c r="B21" s="77" t="inlineStr">
         <is>
           <t>Armadura de reparticion = As / 5, con un minimo de 0,30 cm2/m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="75" t="inlineStr"/>
-      <c r="B22" s="76" t="inlineStr"/>
+      <c r="A22" s="76" t="inlineStr"/>
+      <c r="B22" s="77" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="75" t="inlineStr">
+      <c r="A23" s="76" t="inlineStr">
         <is>
           <t>4. ESPESORES</t>
         </is>
       </c>
-      <c r="B23" s="75" t="inlineStr">
+      <c r="B23" s="76" t="inlineStr">
         <is>
           <t>Los espesores d se leyeron del plano: estan escritos debajo del rotulo de cada losa.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="75" t="inlineStr"/>
-      <c r="B24" s="76" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr"/>
+      <c r="B24" s="77" t="inlineStr">
         <is>
           <t>S/PB:  L01 11 | L02 9 | L03 13 | L04 11 | L05 11 | L06 8 | L07 12 | L08 10</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="75" t="inlineStr"/>
-      <c r="B25" s="76" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr"/>
+      <c r="B25" s="77" t="inlineStr">
         <is>
           <t>S/PA:  L09 13 | L10 12</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="75" t="inlineStr"/>
-      <c r="B26" s="76" t="inlineStr"/>
+      <c r="A26" s="76" t="inlineStr"/>
+      <c r="B26" s="77" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="75" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr">
         <is>
           <t>5. LUCES</t>
         </is>
       </c>
-      <c r="B27" s="75" t="inlineStr">
+      <c r="B27" s="76" t="inlineStr">
         <is>
           <t>Relevadas en obra y aportadas por el proyectista. Dos losas son voladizo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="75" t="inlineStr"/>
-      <c r="B28" s="76" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr"/>
+      <c r="B28" s="77" t="inlineStr">
         <is>
           <t>(L02 de 0,80 m y L08 de 0,75 m) y se calculan con M = p L2 / 2.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="75" t="inlineStr"/>
-      <c r="B29" s="76" t="inlineStr"/>
+      <c r="A29" s="76" t="inlineStr"/>
+      <c r="B29" s="77" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="75" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr">
         <is>
           <t>6. LOSAS CRUZADAS</t>
         </is>
       </c>
-      <c r="B30" s="76" t="inlineStr">
+      <c r="B30" s="77" t="inlineStr">
         <is>
           <t>L07 (4,85 x 5,60) y L10 (4,85 x 6,00) apoyan en los cuatro bordes y su relacion</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="75" t="inlineStr"/>
-      <c r="B31" s="76" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr"/>
+      <c r="B31" s="77" t="inlineStr">
         <is>
           <t>de lados es menor que 2, por lo que trabajan en las dos direcciones.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="75" t="inlineStr"/>
-      <c r="B32" s="76" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr"/>
+      <c r="B32" s="77" t="inlineStr">
         <is>
           <t>Se reparte la carga por el metodo de Marcus:   kx = ly4 / (lx4 + ly4)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="75" t="inlineStr"/>
-      <c r="B33" s="76" t="inlineStr">
+      <c r="A33" s="76" t="inlineStr"/>
+      <c r="B33" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  L07: ly/lx = 1,15  -&gt;  64% en la direccion corta, 36% en la larga</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="75" t="inlineStr"/>
-      <c r="B34" s="76" t="inlineStr">
+      <c r="A34" s="76" t="inlineStr"/>
+      <c r="B34" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  L10: ly/lx = 1,24  -&gt;  70% en la direccion corta, 30% en la larga</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="75" t="inlineStr"/>
-      <c r="B35" s="76" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr"/>
+      <c r="B35" s="77" t="inlineStr">
         <is>
           <t>Cada una ocupa dos renglones, uno por direccion, con la fraccion de carga que</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="75" t="inlineStr"/>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr"/>
+      <c r="B36" s="77" t="inlineStr">
         <is>
           <t>le toca ya aplicada en la columna CARGAS. Las dos armaduras se cruzan en obra:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="75" t="inlineStr"/>
-      <c r="B37" s="76" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr"/>
+      <c r="B37" s="77" t="inlineStr">
         <is>
           <t>la de la direccion corta va abajo, la de la larga arriba de aquella.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="75" t="inlineStr"/>
-      <c r="B38" s="76" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr"/>
+      <c r="B38" s="77" t="inlineStr">
         <is>
           <t>La columna auxiliar luz transv. es la que dispara el reparto: si se borra, la</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="75" t="inlineStr"/>
-      <c r="B39" s="76" t="inlineStr">
+      <c r="A39" s="76" t="inlineStr"/>
+      <c r="B39" s="77" t="inlineStr">
         <is>
           <t>fila vuelve a calcularse como losa armada en una direccion.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="75" t="inlineStr"/>
-      <c r="B40" s="76" t="inlineStr"/>
+      <c r="A40" s="76" t="inlineStr"/>
+      <c r="B40" s="77" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="75" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B41" s="75" t="inlineStr">
+      <c r="B41" s="76" t="inlineStr">
         <is>
           <t>El grado de empotramiento esta cargado en 1/8 salvo los dos voladizos (1/2). Si</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="75" t="inlineStr"/>
-      <c r="B42" s="76" t="inlineStr">
+      <c r="A42" s="76" t="inlineStr"/>
+      <c r="B42" s="77" t="inlineStr">
         <is>
           <t>alguna losa es continua sobre una viga corresponde 1/10 o 1/14: corregir en la columna.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="75" t="inlineStr"/>
-      <c r="B43" s="76" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr"/>
+      <c r="B43" s="77" t="inlineStr">
         <is>
           <t>El diagrama de cargas es una imagen fija: si cambias el grado, cambialo a mano.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="75" t="inlineStr"/>
-      <c r="B44" s="76" t="inlineStr">
+      <c r="A44" s="76" t="inlineStr"/>
+      <c r="B44" s="77" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
@@ -6615,384 +6908,384 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="75" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - COLUMNAS</t>
         </is>
       </c>
-      <c r="B1" s="75" t="inlineStr"/>
+      <c r="B1" s="76" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="75" t="inlineStr"/>
-      <c r="B2" s="76" t="inlineStr"/>
+      <c r="A2" s="76" t="inlineStr"/>
+      <c r="B2" s="77" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="inlineStr">
+      <c r="A3" s="76" t="inlineStr">
         <is>
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B3" s="75" t="inlineStr">
+      <c r="B3" s="76" t="inlineStr">
         <is>
           <t>H-21 (f'c 210 kg/cm2). Acero 42/50 (fy 4200). phi compresion 0,65.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="75" t="inlineStr"/>
-      <c r="B4" s="76" t="inlineStr"/>
+      <c r="A4" s="76" t="inlineStr"/>
+      <c r="B4" s="77" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="76" t="inlineStr">
         <is>
           <t>1. RELEVAMIENTO</t>
         </is>
       </c>
-      <c r="B5" s="75" t="inlineStr">
+      <c r="B5" s="76" t="inlineStr">
         <is>
           <t>Las columnas se identificaron en el plano cruzando el rotulo COL con un rectangulo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="inlineStr"/>
-      <c r="B6" s="76" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr"/>
+      <c r="B6" s="77" t="inlineStr">
         <is>
           <t>de la misma seccion a menos de 26 pt. Resultaron 9 en PB y 4 en PA.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="inlineStr"/>
-      <c r="B7" s="76" t="inlineStr">
+      <c r="A7" s="76" t="inlineStr"/>
+      <c r="B7" s="77" t="inlineStr">
         <is>
           <t>Las 4 de PA caen exactamente sobre C6, C7, C8 y C9 de PB, y ademas tienen la misma</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="75" t="inlineStr"/>
-      <c r="B8" s="76" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr"/>
+      <c r="B8" s="77" t="inlineStr">
         <is>
           <t>seccion, lo que confirma que la correspondencia entre plantas es correcta.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="inlineStr"/>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr"/>
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>La C01 de 10x10 esta confirmada por el proyectista aunque el computo metrico no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="75" t="inlineStr"/>
-      <c r="B10" s="76" t="inlineStr">
+      <c r="A10" s="76" t="inlineStr"/>
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>la incluya en su item 4.1.3: ese computo esta incompleto en ese punto.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="75" t="inlineStr"/>
-      <c r="B11" s="76" t="inlineStr"/>
+      <c r="A11" s="76" t="inlineStr"/>
+      <c r="B11" s="77" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="76" t="inlineStr">
         <is>
           <t>2. ALTURAS</t>
         </is>
       </c>
-      <c r="B12" s="75" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
         <is>
           <t>PB 3,15 m y PA 3,22 m, los mismos valores de la planilla de la catedra, coherentes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="75" t="inlineStr"/>
-      <c r="B13" s="76" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr"/>
+      <c r="B13" s="77" t="inlineStr">
         <is>
           <t>con los niveles del plano (N.F.L +3,50 del entrepiso y +6,80 del techo).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="75" t="inlineStr"/>
-      <c r="B14" s="76" t="inlineStr"/>
+      <c r="A14" s="76" t="inlineStr"/>
+      <c r="B14" s="77" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
         </is>
       </c>
-      <c r="B15" s="75" t="inlineStr">
+      <c r="B15" s="76" t="inlineStr">
         <is>
           <t>As = 0,008 x area (cuantia minima, el mismo criterio de la planilla modelo).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="75" t="inlineStr"/>
-      <c r="B16" s="76" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr"/>
+      <c r="B16" s="77" t="inlineStr">
         <is>
           <t>Se adoptan 4 barras del 12 en todas: 4,52 cm2, que cubre la minima en toda seccion.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="75" t="inlineStr"/>
-      <c r="B17" s="76" t="inlineStr">
+      <c r="A17" s="76" t="inlineStr"/>
+      <c r="B17" s="77" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. long. ; 48 x diam. estribo ; lado menor),</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="75" t="inlineStr"/>
-      <c r="B18" s="76" t="inlineStr">
+      <c r="A18" s="76" t="inlineStr"/>
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t>redondeada hacia abajo a multiplo de 5. Para 4d12 con estribo d6 da 10 cm.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="75" t="inlineStr"/>
-      <c r="B19" s="76" t="inlineStr">
+      <c r="A19" s="76" t="inlineStr"/>
+      <c r="B19" s="77" t="inlineStr">
         <is>
           <t>La planilla de la catedra adopta 20 cm: ese valor supera el limite reglamentario.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="75" t="inlineStr"/>
-      <c r="B20" s="76" t="inlineStr"/>
+      <c r="A20" s="76" t="inlineStr"/>
+      <c r="B20" s="77" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="75" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>4. CAPACIDAD</t>
         </is>
       </c>
-      <c r="B21" s="75" t="inlineStr">
+      <c r="B21" s="76" t="inlineStr">
         <is>
           <t>phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]     (columna zunchada con estribos)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="75" t="inlineStr"/>
-      <c r="B22" s="76" t="inlineStr">
+      <c r="A22" s="76" t="inlineStr"/>
+      <c r="B22" s="77" t="inlineStr">
         <is>
           <t xml:space="preserve">  15x30 con 4d12 -&gt; 51,2 t        20x20 con 4d12 -&gt; 46,6 t</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="75" t="inlineStr"/>
-      <c r="B23" s="76" t="inlineStr"/>
+      <c r="A23" s="76" t="inlineStr"/>
+      <c r="B23" s="77" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="75" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>5. CARGAS</t>
         </is>
       </c>
-      <c r="B24" s="75" t="inlineStr">
+      <c r="B24" s="76" t="inlineStr">
         <is>
           <t>La columna CARGA (t) viene cargada con una bajada automatica: suma de las</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="75" t="inlineStr"/>
-      <c r="B25" s="76" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr"/>
+      <c r="B25" s="77" t="inlineStr">
         <is>
           <t>reacciones de las vigas que apoyan en cada columna (tomadas de la planilla de</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="75" t="inlineStr"/>
-      <c r="B26" s="76" t="inlineStr">
+      <c r="A26" s="76" t="inlineStr"/>
+      <c r="B26" s="77" t="inlineStr">
         <is>
           <t>vigas), mas el peso propio, mas lo que baja de la columna del nivel superior.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="75" t="inlineStr"/>
-      <c r="B27" s="76" t="inlineStr">
+      <c r="A27" s="76" t="inlineStr"/>
+      <c r="B27" s="77" t="inlineStr">
         <is>
           <t>ES UNA CARGA PROVISORIA Y ES UN PISO, NO EL VALOR REAL: 20 de los 60 extremos</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="75" t="inlineStr"/>
-      <c r="B28" s="76" t="inlineStr">
+      <c r="A28" s="76" t="inlineStr"/>
+      <c r="B28" s="77" t="inlineStr">
         <is>
           <t>de viga no pudieron asignarse a ninguna columna porque apoyan en otra viga, en</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="75" t="inlineStr"/>
-      <c r="B29" s="76" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr"/>
+      <c r="B29" s="77" t="inlineStr">
         <is>
           <t>un tabique o en la medianera, y esas reacciones no estan sumadas.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="75" t="inlineStr"/>
-      <c r="B30" s="76" t="inlineStr">
+      <c r="A30" s="76" t="inlineStr"/>
+      <c r="B30" s="77" t="inlineStr">
         <is>
           <t>Para cerrarla hay que indicar, para cada uno de esos 20 extremos, en que apoya.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="75" t="inlineStr"/>
-      <c r="B31" s="76" t="inlineStr">
+      <c r="A31" s="76" t="inlineStr"/>
+      <c r="B31" s="77" t="inlineStr">
         <is>
           <t>Mientras tanto la columna es editable: al corregir un valor todo recalcula.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="75" t="inlineStr"/>
-      <c r="B32" s="76" t="inlineStr">
+      <c r="A32" s="76" t="inlineStr"/>
+      <c r="B32" s="77" t="inlineStr">
         <is>
           <t>Ademas son cargas MAYORADAS, coherentes con la planilla de vigas. Si la catedra</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="75" t="inlineStr"/>
-      <c r="B33" s="76" t="inlineStr">
+      <c r="A33" s="76" t="inlineStr"/>
+      <c r="B33" s="77" t="inlineStr">
         <is>
           <t>pide cargas de servicio, dividir por el coeficiente que corresponda.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="75" t="inlineStr"/>
-      <c r="B34" s="76" t="inlineStr"/>
+      <c r="A34" s="76" t="inlineStr"/>
+      <c r="B34" s="77" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="75" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr">
         <is>
           <t>6. ESBELTEZ</t>
         </is>
       </c>
-      <c r="B35" s="75" t="inlineStr">
+      <c r="B35" s="76" t="inlineStr">
         <is>
           <t>Todas las columnas son esbeltas: con lado menor de 15 cm y 3,15 m de altura,</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="75" t="inlineStr"/>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr"/>
+      <c r="B36" s="77" t="inlineStr">
         <is>
           <t>k lu / r = 70, muy por encima del limite de 34 por debajo del cual se puede</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="75" t="inlineStr"/>
-      <c r="B37" s="76" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr"/>
+      <c r="B37" s="77" t="inlineStr">
         <is>
           <t>despreciar el pandeo. En la practica el llenado de mamposteria las arriostra, pero</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="75" t="inlineStr"/>
-      <c r="B38" s="76" t="inlineStr">
+      <c r="A38" s="76" t="inlineStr"/>
+      <c r="B38" s="77" t="inlineStr">
         <is>
           <t>si la catedra lo pide hay que verificar segundo orden. La planilla lo marca.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="75" t="inlineStr"/>
-      <c r="B39" s="76" t="inlineStr"/>
+      <c r="A39" s="76" t="inlineStr"/>
+      <c r="B39" s="77" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="75" t="inlineStr">
+      <c r="A40" s="76" t="inlineStr">
         <is>
           <t>7. LA DE 10x10</t>
         </is>
       </c>
-      <c r="B40" s="75" t="inlineStr">
+      <c r="B40" s="76" t="inlineStr">
         <is>
           <t>Existe, confirmada por el proyectista, y el computo metrico la omite. Con 10 cm</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="75" t="inlineStr"/>
-      <c r="B41" s="76" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr"/>
+      <c r="B41" s="77" t="inlineStr">
         <is>
           <t>de lado y 3,15 m de altura su esbeltez es k lu / r = 105, tres veces el limite</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="75" t="inlineStr"/>
-      <c r="B42" s="76" t="inlineStr">
+      <c r="A42" s="76" t="inlineStr"/>
+      <c r="B42" s="77" t="inlineStr">
         <is>
           <t>por debajo del cual se puede despreciar el pandeo, y su capacidad es de 18,7 t</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="75" t="inlineStr"/>
-      <c r="B43" s="76" t="inlineStr">
+      <c r="A43" s="76" t="inlineStr"/>
+      <c r="B43" s="77" t="inlineStr">
         <is>
           <t>contra los 51 de una 15x30. Es el punto mas delicado del conjunto: conviene</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="75" t="inlineStr"/>
-      <c r="B44" s="76" t="inlineStr">
+      <c r="A44" s="76" t="inlineStr"/>
+      <c r="B44" s="77" t="inlineStr">
         <is>
           <t>verificarla a segundo orden en serio, no con la formula de compresion simple.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="75" t="inlineStr"/>
-      <c r="B45" s="76" t="inlineStr"/>
+      <c r="A45" s="76" t="inlineStr"/>
+      <c r="B45" s="77" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="75" t="inlineStr">
+      <c r="A46" s="76" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
         </is>
       </c>
-      <c r="B46" s="75" t="inlineStr">
+      <c r="B46" s="76" t="inlineStr">
         <is>
           <t>Trabajo academico. Requiere verificacion y firma de profesional matriculado.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="75" t="inlineStr"/>
-      <c r="B47" s="76" t="inlineStr">
+      <c r="A47" s="76" t="inlineStr"/>
+      <c r="B47" s="77" t="inlineStr">
         <is>
           <t>No se verifica flexion compuesta: las columnas de borde reciben momento de las</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="75" t="inlineStr"/>
-      <c r="B48" s="76" t="inlineStr">
+      <c r="A48" s="76" t="inlineStr"/>
+      <c r="B48" s="77" t="inlineStr">
         <is>
           <t>vigas invertidas y trabajan a flexo-compresion, no a compresion simple.</t>
         </is>
@@ -7020,7 +7313,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="77" t="inlineStr">
+      <c r="A1" s="78" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION - inventario. Calculo pendiente: va despues de columnas.</t>
         </is>
@@ -7162,7 +7455,7 @@
       <c r="D9" s="11" t="n">
         <v>533</v>
       </c>
-      <c r="E9" s="78" t="inlineStr">
+      <c r="E9" s="79" t="inlineStr">
         <is>
           <t>Ancho cortado en el PDF: confirmar 20 o 22 cm</t>
         </is>
@@ -7228,7 +7521,7 @@
       <c r="B13" s="11" t="n"/>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="11" t="n"/>
-      <c r="E13" s="78" t="inlineStr">
+      <c r="E13" s="79" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -7243,7 +7536,7 @@
       <c r="B14" s="11" t="n"/>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="11" t="n"/>
-      <c r="E14" s="78" t="inlineStr">
+      <c r="E14" s="79" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -7445,7 +7738,7 @@
       <c r="B26" s="11" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="11" t="n"/>
-      <c r="E26" s="78" t="inlineStr">
+      <c r="E26" s="79" t="inlineStr">
         <is>
           <t>Cota no legible: completar</t>
         </is>
@@ -7616,7 +7909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7840,7 +8133,7 @@
       </c>
       <c r="L7" s="26" t="n"/>
       <c r="M7" s="30">
-        <f>IF(OR(D7="",J7=""),"",IF(J7&lt;=G7,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D7="",J7=""),"",IF(AND(J7&lt;=G7,OR(L7="",L7&lt;=IFERROR(VLOOKUP(K7,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -7885,7 +8178,7 @@
       </c>
       <c r="L8" s="26" t="n"/>
       <c r="M8" s="30">
-        <f>IF(OR(D8="",J8=""),"",IF(J8&lt;=G8,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D8="",J8=""),"",IF(AND(J8&lt;=G8,OR(L8="",L8&lt;=IFERROR(VLOOKUP(K8,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -7930,7 +8223,7 @@
       </c>
       <c r="L9" s="26" t="n"/>
       <c r="M9" s="30">
-        <f>IF(OR(D9="",J9=""),"",IF(J9&lt;=G9,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D9="",J9=""),"",IF(AND(J9&lt;=G9,OR(L9="",L9&lt;=IFERROR(VLOOKUP(K9,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -7975,7 +8268,7 @@
       </c>
       <c r="L10" s="26" t="n"/>
       <c r="M10" s="30">
-        <f>IF(OR(D10="",J10=""),"",IF(J10&lt;=G10,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D10="",J10=""),"",IF(AND(J10&lt;=G10,OR(L10="",L10&lt;=IFERROR(VLOOKUP(K10,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8020,7 +8313,7 @@
       </c>
       <c r="L11" s="26" t="n"/>
       <c r="M11" s="30">
-        <f>IF(OR(D11="",J11=""),"",IF(J11&lt;=G11,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D11="",J11=""),"",IF(AND(J11&lt;=G11,OR(L11="",L11&lt;=IFERROR(VLOOKUP(K11,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8047,7 +8340,7 @@
       <c r="K12" s="25" t="n"/>
       <c r="L12" s="26" t="n"/>
       <c r="M12" s="30">
-        <f>IF(OR(D12="",J12=""),"",IF(J12&lt;=G12,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D12="",J12=""),"",IF(AND(J12&lt;=G12,OR(L12="",L12&lt;=IFERROR(VLOOKUP(K12,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8074,7 +8367,7 @@
       <c r="K13" s="32" t="n"/>
       <c r="L13" s="33" t="n"/>
       <c r="M13" s="37">
-        <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D13="",J13=""),"",IF(AND(J13&lt;=G13,OR(L13="",L13&lt;=IFERROR(VLOOKUP(K13,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8141,7 +8434,7 @@
       </c>
       <c r="L15" s="26" t="n"/>
       <c r="M15" s="30">
-        <f>IF(OR(D15="",J15=""),"",IF(J15&lt;=G15,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D15="",J15=""),"",IF(AND(J15&lt;=G15,OR(L15="",L15&lt;=IFERROR(VLOOKUP(K15,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8186,7 +8479,7 @@
       </c>
       <c r="L16" s="26" t="n"/>
       <c r="M16" s="30">
-        <f>IF(OR(D16="",J16=""),"",IF(J16&lt;=G16,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D16="",J16=""),"",IF(AND(J16&lt;=G16,OR(L16="",L16&lt;=IFERROR(VLOOKUP(K16,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8213,7 +8506,7 @@
       <c r="K17" s="25" t="n"/>
       <c r="L17" s="26" t="n"/>
       <c r="M17" s="30">
-        <f>IF(OR(D17="",J17=""),"",IF(J17&lt;=G17,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D17="",J17=""),"",IF(AND(J17&lt;=G17,OR(L17="",L17&lt;=IFERROR(VLOOKUP(K17,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8240,7 +8533,7 @@
       <c r="K18" s="32" t="n"/>
       <c r="L18" s="33" t="n"/>
       <c r="M18" s="37">
-        <f>IF(OR(D18="",J18=""),"",IF(J18&lt;=G18,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D18="",J18=""),"",IF(AND(J18&lt;=G18,OR(L18="",L18&lt;=IFERROR(VLOOKUP(K18,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8307,7 +8600,7 @@
       </c>
       <c r="L20" s="26" t="n"/>
       <c r="M20" s="30">
-        <f>IF(OR(D20="",J20=""),"",IF(J20&lt;=G20,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D20="",J20=""),"",IF(AND(J20&lt;=G20,OR(L20="",L20&lt;=IFERROR(VLOOKUP(K20,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8352,7 +8645,7 @@
       </c>
       <c r="L21" s="26" t="n"/>
       <c r="M21" s="30">
-        <f>IF(OR(D21="",J21=""),"",IF(J21&lt;=G21,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D21="",J21=""),"",IF(AND(J21&lt;=G21,OR(L21="",L21&lt;=IFERROR(VLOOKUP(K21,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8397,7 +8690,7 @@
       </c>
       <c r="L22" s="26" t="n"/>
       <c r="M22" s="30">
-        <f>IF(OR(D22="",J22=""),"",IF(J22&lt;=G22,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D22="",J22=""),"",IF(AND(J22&lt;=G22,OR(L22="",L22&lt;=IFERROR(VLOOKUP(K22,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8442,7 +8735,7 @@
       </c>
       <c r="L23" s="26" t="n"/>
       <c r="M23" s="30">
-        <f>IF(OR(D23="",J23=""),"",IF(J23&lt;=G23,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D23="",J23=""),"",IF(AND(J23&lt;=G23,OR(L23="",L23&lt;=IFERROR(VLOOKUP(K23,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8487,7 +8780,7 @@
       </c>
       <c r="L24" s="26" t="n"/>
       <c r="M24" s="30">
-        <f>IF(OR(D24="",J24=""),"",IF(J24&lt;=G24,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D24="",J24=""),"",IF(AND(J24&lt;=G24,OR(L24="",L24&lt;=IFERROR(VLOOKUP(K24,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8514,7 +8807,7 @@
       <c r="K25" s="25" t="n"/>
       <c r="L25" s="26" t="n"/>
       <c r="M25" s="30">
-        <f>IF(OR(D25="",J25=""),"",IF(J25&lt;=G25,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D25="",J25=""),"",IF(AND(J25&lt;=G25,OR(L25="",L25&lt;=IFERROR(VLOOKUP(K25,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8541,7 +8834,7 @@
       <c r="K26" s="32" t="n"/>
       <c r="L26" s="33" t="n"/>
       <c r="M26" s="37">
-        <f>IF(OR(D26="",J26=""),"",IF(J26&lt;=G26,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D26="",J26=""),"",IF(AND(J26&lt;=G26,OR(L26="",L26&lt;=IFERROR(VLOOKUP(K26,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8608,7 +8901,7 @@
       </c>
       <c r="L28" s="26" t="n"/>
       <c r="M28" s="30">
-        <f>IF(OR(D28="",J28=""),"",IF(J28&lt;=G28,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D28="",J28=""),"",IF(AND(J28&lt;=G28,OR(L28="",L28&lt;=IFERROR(VLOOKUP(K28,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8653,7 +8946,7 @@
       </c>
       <c r="L29" s="26" t="n"/>
       <c r="M29" s="30">
-        <f>IF(OR(D29="",J29=""),"",IF(J29&lt;=G29,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D29="",J29=""),"",IF(AND(J29&lt;=G29,OR(L29="",L29&lt;=IFERROR(VLOOKUP(K29,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8698,7 +8991,7 @@
       </c>
       <c r="L30" s="26" t="n"/>
       <c r="M30" s="30">
-        <f>IF(OR(D30="",J30=""),"",IF(J30&lt;=G30,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D30="",J30=""),"",IF(AND(J30&lt;=G30,OR(L30="",L30&lt;=IFERROR(VLOOKUP(K30,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8743,7 +9036,7 @@
       </c>
       <c r="L31" s="26" t="n"/>
       <c r="M31" s="30">
-        <f>IF(OR(D31="",J31=""),"",IF(J31&lt;=G31,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D31="",J31=""),"",IF(AND(J31&lt;=G31,OR(L31="",L31&lt;=IFERROR(VLOOKUP(K31,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8788,7 +9081,7 @@
       </c>
       <c r="L32" s="26" t="n"/>
       <c r="M32" s="30">
-        <f>IF(OR(D32="",J32=""),"",IF(J32&lt;=G32,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D32="",J32=""),"",IF(AND(J32&lt;=G32,OR(L32="",L32&lt;=IFERROR(VLOOKUP(K32,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8815,7 +9108,7 @@
       <c r="K33" s="25" t="n"/>
       <c r="L33" s="26" t="n"/>
       <c r="M33" s="30">
-        <f>IF(OR(D33="",J33=""),"",IF(J33&lt;=G33,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D33="",J33=""),"",IF(AND(J33&lt;=G33,OR(L33="",L33&lt;=IFERROR(VLOOKUP(K33,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8842,7 +9135,7 @@
       <c r="K34" s="32" t="n"/>
       <c r="L34" s="33" t="n"/>
       <c r="M34" s="37">
-        <f>IF(OR(D34="",J34=""),"",IF(J34&lt;=G34,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D34="",J34=""),"",IF(AND(J34&lt;=G34,OR(L34="",L34&lt;=IFERROR(VLOOKUP(K34,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8905,7 +9198,7 @@
       <c r="K36" s="25" t="n"/>
       <c r="L36" s="26" t="n"/>
       <c r="M36" s="30">
-        <f>IF(OR(D36="",J36=""),"",IF(J36&lt;=G36,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D36="",J36=""),"",IF(AND(J36&lt;=G36,OR(L36="",L36&lt;=IFERROR(VLOOKUP(K36,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8932,7 +9225,7 @@
       <c r="K37" s="25" t="n"/>
       <c r="L37" s="26" t="n"/>
       <c r="M37" s="30">
-        <f>IF(OR(D37="",J37=""),"",IF(J37&lt;=G37,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D37="",J37=""),"",IF(AND(J37&lt;=G37,OR(L37="",L37&lt;=IFERROR(VLOOKUP(K37,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8959,7 +9252,7 @@
       <c r="K38" s="32" t="n"/>
       <c r="L38" s="33" t="n"/>
       <c r="M38" s="37">
-        <f>IF(OR(D38="",J38=""),"",IF(J38&lt;=G38,"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D38="",J38=""),"",IF(AND(J38&lt;=G38,OR(L38="",L38&lt;=IFERROR(VLOOKUP(K38,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9076,7 +9369,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>Orientacion y factor de exposicion solar: el factor depende de la orientacion y de la proteccion.</t>
+          <t>Orientacion: ya cargada. Factor de exposicion solar: cargarlo en la columna L segun el vidrio</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9093,7 +9386,11 @@
       <c r="M45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="39" t="inlineStr"/>
+      <c r="A46" s="39" t="inlineStr">
+        <is>
+          <t>y la proteccion solar adoptados; la verificacion lo compara contra el maximo del cuadrante,</t>
+        </is>
+      </c>
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -9110,7 +9407,7 @@
     <row r="47">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+          <t>que esta en la tabla de la hoja Datos_higro.</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -9127,11 +9424,7 @@
       <c r="M47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="39" t="inlineStr">
-        <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
-        </is>
-      </c>
+      <c r="A48" s="39" t="inlineStr"/>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n"/>
@@ -9146,7 +9439,11 @@
       <c r="M48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="39" t="inlineStr"/>
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+        </is>
+      </c>
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n"/>
@@ -9163,7 +9460,7 @@
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9180,11 +9477,7 @@
       <c r="M50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="39" t="inlineStr">
-        <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
-        </is>
-      </c>
+      <c r="A51" s="39" t="inlineStr"/>
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n"/>
@@ -9201,7 +9494,7 @@
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9220,7 +9513,7 @@
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B53" s="2" t="n"/>
@@ -9239,7 +9532,7 @@
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
         </is>
       </c>
       <c r="B54" s="2" t="n"/>
@@ -9256,7 +9549,11 @@
       <c r="M54" s="2" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="39" t="inlineStr"/>
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+        </is>
+      </c>
       <c r="B55" s="2" t="n"/>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n"/>
@@ -9273,7 +9570,7 @@
     <row r="56">
       <c r="A56" s="39" t="inlineStr">
         <is>
-          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -9290,11 +9587,7 @@
       <c r="M56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="39" t="inlineStr">
-        <is>
-          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
-        </is>
-      </c>
+      <c r="A57" s="39" t="inlineStr"/>
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n"/>
@@ -9311,7 +9604,7 @@
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9330,7 +9623,7 @@
     <row r="59">
       <c r="A59" s="39" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B59" s="2" t="n"/>
@@ -9349,7 +9642,7 @@
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
         <is>
-          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
         </is>
       </c>
       <c r="B60" s="2" t="n"/>
@@ -9368,7 +9661,7 @@
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
         <is>
-          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
@@ -9387,7 +9680,7 @@
     <row r="62">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t>parecen ser nombres de uso, no orientaciones.</t>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
         </is>
       </c>
       <c r="B62" s="2" t="n"/>
@@ -9404,7 +9697,11 @@
       <c r="M62" s="2" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="39" t="inlineStr"/>
+      <c r="A63" s="39" t="inlineStr">
+        <is>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+        </is>
+      </c>
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n"/>
@@ -9421,7 +9718,7 @@
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9438,11 +9735,7 @@
       <c r="M64" s="2" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="39" t="inlineStr">
-        <is>
-          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
-        </is>
-      </c>
+      <c r="A65" s="39" t="inlineStr"/>
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n"/>
@@ -9457,7 +9750,11 @@
       <c r="M65" s="2" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="39" t="inlineStr"/>
+      <c r="A66" s="39" t="inlineStr">
+        <is>
+          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+        </is>
+      </c>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n"/>
@@ -9474,7 +9771,7 @@
     <row r="67">
       <c r="A67" s="39" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
         </is>
       </c>
       <c r="B67" s="2" t="n"/>
@@ -9508,7 +9805,7 @@
     <row r="69">
       <c r="A69" s="39" t="inlineStr">
         <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
         </is>
       </c>
       <c r="B69" s="2" t="n"/>
@@ -9525,11 +9822,7 @@
       <c r="M69" s="2" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="39" t="inlineStr">
-        <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
-        </is>
-      </c>
+      <c r="A70" s="39" t="inlineStr"/>
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n"/>
@@ -9546,7 +9839,7 @@
     <row r="71">
       <c r="A71" s="39" t="inlineStr">
         <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -9561,6 +9854,44 @@
       <c r="K71" s="2" t="n"/>
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -4953,60 +4953,62 @@
       </c>
       <c r="D4" s="66" t="inlineStr">
         <is>
-          <t>Ordenanza 8757/11. Confirmar el valor segun zona bioambiental y tipo de local.</t>
+          <t>Es el valor que usa la planilla de la catedra en todas las filas.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
+      <c r="A5" s="61" t="inlineStr">
+        <is>
+          <t>K maximo si los vanos superan el 60% de la fachada</t>
+        </is>
+      </c>
+      <c r="B5" s="73" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>W/m2K</t>
+        </is>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>Decreto 1647/2021, Anexo Etapa 3. NO esta aplicado: la planilla usa 2,90 fijo como el ejemplo. Si la fachada es mayormente vidriada, cambiar el valor de arriba por 1,80.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="72" t="inlineStr">
-        <is>
-          <t>TIPOS DE VIDRIO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="59" t="inlineStr">
-        <is>
-          <t>descripcion</t>
-        </is>
-      </c>
-      <c r="B7" s="60" t="inlineStr">
-        <is>
-          <t>K orientativo</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="61" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (el de obra, aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="B8" s="73" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="A8" s="72" t="inlineStr">
+        <is>
+          <t>TIPOS DE VIDRIO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="61" t="inlineStr">
-        <is>
-          <t>Simple incoloro 3 mm</t>
-        </is>
-      </c>
-      <c r="B9" s="73" t="n">
-        <v>5.8</v>
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>K orientativo</t>
+        </is>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
@@ -5014,11 +5016,11 @@
     <row r="10">
       <c r="A10" s="61" t="inlineStr">
         <is>
-          <t>Simple incoloro 6 mm</t>
+          <t>DVH 6+9+3+3 (el de obra, aluminio linea A30)</t>
         </is>
       </c>
       <c r="B10" s="73" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
@@ -5026,11 +5028,11 @@
     <row r="11">
       <c r="A11" s="61" t="inlineStr">
         <is>
-          <t>DVH Incoloro ext; incoloro interior (3+12+3 mm)</t>
+          <t>Simple incoloro 3 mm</t>
         </is>
       </c>
       <c r="B11" s="73" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
@@ -5038,11 +5040,11 @@
     <row r="12">
       <c r="A12" s="61" t="inlineStr">
         <is>
-          <t>DVH Incoloro ext; incoloro interior (4+12+4 mm)</t>
+          <t>Simple incoloro 6 mm</t>
         </is>
       </c>
       <c r="B12" s="73" t="n">
-        <v>2.75</v>
+        <v>5.7</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
@@ -5050,11 +5052,11 @@
     <row r="13">
       <c r="A13" s="61" t="inlineStr">
         <is>
-          <t>DVH con lamina de baja emisividad (3+12+3 mm)</t>
+          <t>DVH Incoloro ext; incoloro interior (3+12+3 mm)</t>
         </is>
       </c>
       <c r="B13" s="73" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
@@ -5062,11 +5064,11 @@
     <row r="14">
       <c r="A14" s="61" t="inlineStr">
         <is>
-          <t>DVH con camara de argon (4+16+4 mm)</t>
+          <t>DVH Incoloro ext; incoloro interior (4+12+4 mm)</t>
         </is>
       </c>
       <c r="B14" s="73" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
@@ -5074,65 +5076,65 @@
     <row r="15">
       <c r="A15" s="61" t="inlineStr">
         <is>
-          <t>Vidrio laminado 3+3 mm</t>
+          <t>DVH con lamina de baja emisividad (3+12+3 mm)</t>
         </is>
       </c>
       <c r="B15" s="73" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
+      <c r="A16" s="61" t="inlineStr">
+        <is>
+          <t>DVH con camara de argon (4+16+4 mm)</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="n">
+        <v>1.6</v>
+      </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="72" t="inlineStr">
-        <is>
-          <t>TIPOS DE PROTECCION</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n"/>
+      <c r="A17" s="61" t="inlineStr">
+        <is>
+          <t>Vidrio laminado 3+3 mm</t>
+        </is>
+      </c>
+      <c r="B17" s="73" t="n">
+        <v>5.6</v>
+      </c>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="59" t="inlineStr">
-        <is>
-          <t>descripcion</t>
-        </is>
-      </c>
-      <c r="B18" s="60" t="inlineStr">
-        <is>
-          <t>FES orientativo</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="inlineStr">
-        <is>
-          <t>Sin Proteccion</t>
-        </is>
-      </c>
-      <c r="B19" s="73" t="n">
-        <v>0.88</v>
-      </c>
+      <c r="A19" s="72" t="inlineStr">
+        <is>
+          <t>TIPOS DE PROTECCION</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="61" t="inlineStr">
-        <is>
-          <t>Parasol horizontal fijo 1:2</t>
-        </is>
-      </c>
-      <c r="B20" s="73" t="n">
-        <v>0.35</v>
+      <c r="A20" s="59" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>FES orientativo</t>
+        </is>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
@@ -5140,11 +5142,11 @@
     <row r="21">
       <c r="A21" s="61" t="inlineStr">
         <is>
-          <t>Parasol horizontal fijo 1:1</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="B21" s="73" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
@@ -5152,11 +5154,11 @@
     <row r="22">
       <c r="A22" s="61" t="inlineStr">
         <is>
-          <t>Alero</t>
+          <t>Parasol horizontal fijo 1:2</t>
         </is>
       </c>
       <c r="B22" s="73" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
@@ -5164,11 +5166,11 @@
     <row r="23">
       <c r="A23" s="61" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Parasol horizontal fijo 1:1</t>
         </is>
       </c>
       <c r="B23" s="73" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
@@ -5176,11 +5178,11 @@
     <row r="24">
       <c r="A24" s="61" t="inlineStr">
         <is>
-          <t>Persiana de madera</t>
+          <t>Alero</t>
         </is>
       </c>
       <c r="B24" s="73" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
@@ -5188,37 +5190,41 @@
     <row r="25">
       <c r="A25" s="61" t="inlineStr">
         <is>
-          <t>Toldo</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="B25" s="73" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
+      <c r="A26" s="61" t="inlineStr">
+        <is>
+          <t>Persiana de madera</t>
+        </is>
+      </c>
+      <c r="B26" s="73" t="n">
+        <v>0.3</v>
+      </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t>Los valores de K y de factor de exposicion solar son ORIENTATIVOS, para que los desplegables tengan contenido.</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
+      <c r="A27" s="61" t="inlineStr">
+        <is>
+          <t>Toldo</t>
+        </is>
+      </c>
+      <c r="B27" s="73" t="n">
+        <v>0.2</v>
+      </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
-        <is>
-          <t>Reemplazarlos por los de las tablas de la ordenanza y los del fabricante de la carpinteria. El factor de exposicion solar depende ademas de la orientacion.</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
@@ -7909,7 +7915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8131,9 +8137,12 @@
           <t>Noreste</t>
         </is>
       </c>
-      <c r="L7" s="26" t="n"/>
+      <c r="L7" s="26">
+        <f>IF(I7="","",IFERROR(VLOOKUP(I7,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M7" s="30">
-        <f>IF(OR(D7="",J7=""),"",IF(AND(J7&lt;=G7,OR(L7="",L7&lt;=IFERROR(VLOOKUP(K7,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D7="",J7=""),"",IF(J7&lt;=G7,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8176,9 +8185,12 @@
           <t>Noreste</t>
         </is>
       </c>
-      <c r="L8" s="26" t="n"/>
+      <c r="L8" s="26">
+        <f>IF(I8="","",IFERROR(VLOOKUP(I8,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M8" s="30">
-        <f>IF(OR(D8="",J8=""),"",IF(AND(J8&lt;=G8,OR(L8="",L8&lt;=IFERROR(VLOOKUP(K8,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D8="",J8=""),"",IF(J8&lt;=G8,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8221,9 +8233,12 @@
           <t>Noreste</t>
         </is>
       </c>
-      <c r="L9" s="26" t="n"/>
+      <c r="L9" s="26">
+        <f>IF(I9="","",IFERROR(VLOOKUP(I9,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M9" s="30">
-        <f>IF(OR(D9="",J9=""),"",IF(AND(J9&lt;=G9,OR(L9="",L9&lt;=IFERROR(VLOOKUP(K9,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D9="",J9=""),"",IF(J9&lt;=G9,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8266,9 +8281,12 @@
           <t>Noreste</t>
         </is>
       </c>
-      <c r="L10" s="26" t="n"/>
+      <c r="L10" s="26">
+        <f>IF(I10="","",IFERROR(VLOOKUP(I10,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M10" s="30">
-        <f>IF(OR(D10="",J10=""),"",IF(AND(J10&lt;=G10,OR(L10="",L10&lt;=IFERROR(VLOOKUP(K10,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D10="",J10=""),"",IF(J10&lt;=G10,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8311,9 +8329,12 @@
           <t>Noreste</t>
         </is>
       </c>
-      <c r="L11" s="26" t="n"/>
+      <c r="L11" s="26">
+        <f>IF(I11="","",IFERROR(VLOOKUP(I11,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M11" s="30">
-        <f>IF(OR(D11="",J11=""),"",IF(AND(J11&lt;=G11,OR(L11="",L11&lt;=IFERROR(VLOOKUP(K11,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D11="",J11=""),"",IF(J11&lt;=G11,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8338,9 +8359,12 @@
       <c r="I12" s="25" t="n"/>
       <c r="J12" s="26" t="n"/>
       <c r="K12" s="25" t="n"/>
-      <c r="L12" s="26" t="n"/>
+      <c r="L12" s="26">
+        <f>IF(I12="","",IFERROR(VLOOKUP(I12,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M12" s="30">
-        <f>IF(OR(D12="",J12=""),"",IF(AND(J12&lt;=G12,OR(L12="",L12&lt;=IFERROR(VLOOKUP(K12,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D12="",J12=""),"",IF(J12&lt;=G12,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8365,9 +8389,12 @@
       <c r="I13" s="32" t="n"/>
       <c r="J13" s="33" t="n"/>
       <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33" t="n"/>
+      <c r="L13" s="33">
+        <f>IF(I13="","",IFERROR(VLOOKUP(I13,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M13" s="37">
-        <f>IF(OR(D13="",J13=""),"",IF(AND(J13&lt;=G13,OR(L13="",L13&lt;=IFERROR(VLOOKUP(K13,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8432,9 +8459,12 @@
           <t>Sudoeste</t>
         </is>
       </c>
-      <c r="L15" s="26" t="n"/>
+      <c r="L15" s="26">
+        <f>IF(I15="","",IFERROR(VLOOKUP(I15,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M15" s="30">
-        <f>IF(OR(D15="",J15=""),"",IF(AND(J15&lt;=G15,OR(L15="",L15&lt;=IFERROR(VLOOKUP(K15,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D15="",J15=""),"",IF(J15&lt;=G15,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8477,9 +8507,12 @@
           <t>Sudoeste</t>
         </is>
       </c>
-      <c r="L16" s="26" t="n"/>
+      <c r="L16" s="26">
+        <f>IF(I16="","",IFERROR(VLOOKUP(I16,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M16" s="30">
-        <f>IF(OR(D16="",J16=""),"",IF(AND(J16&lt;=G16,OR(L16="",L16&lt;=IFERROR(VLOOKUP(K16,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D16="",J16=""),"",IF(J16&lt;=G16,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8504,9 +8537,12 @@
       <c r="I17" s="25" t="n"/>
       <c r="J17" s="26" t="n"/>
       <c r="K17" s="25" t="n"/>
-      <c r="L17" s="26" t="n"/>
+      <c r="L17" s="26">
+        <f>IF(I17="","",IFERROR(VLOOKUP(I17,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M17" s="30">
-        <f>IF(OR(D17="",J17=""),"",IF(AND(J17&lt;=G17,OR(L17="",L17&lt;=IFERROR(VLOOKUP(K17,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D17="",J17=""),"",IF(J17&lt;=G17,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8531,9 +8567,12 @@
       <c r="I18" s="32" t="n"/>
       <c r="J18" s="33" t="n"/>
       <c r="K18" s="32" t="n"/>
-      <c r="L18" s="33" t="n"/>
+      <c r="L18" s="33">
+        <f>IF(I18="","",IFERROR(VLOOKUP(I18,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M18" s="37">
-        <f>IF(OR(D18="",J18=""),"",IF(AND(J18&lt;=G18,OR(L18="",L18&lt;=IFERROR(VLOOKUP(K18,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D18="",J18=""),"",IF(J18&lt;=G18,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8598,9 +8637,12 @@
           <t>Sudeste</t>
         </is>
       </c>
-      <c r="L20" s="26" t="n"/>
+      <c r="L20" s="26">
+        <f>IF(I20="","",IFERROR(VLOOKUP(I20,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M20" s="30">
-        <f>IF(OR(D20="",J20=""),"",IF(AND(J20&lt;=G20,OR(L20="",L20&lt;=IFERROR(VLOOKUP(K20,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D20="",J20=""),"",IF(J20&lt;=G20,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8643,9 +8685,12 @@
           <t>Sudeste</t>
         </is>
       </c>
-      <c r="L21" s="26" t="n"/>
+      <c r="L21" s="26">
+        <f>IF(I21="","",IFERROR(VLOOKUP(I21,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M21" s="30">
-        <f>IF(OR(D21="",J21=""),"",IF(AND(J21&lt;=G21,OR(L21="",L21&lt;=IFERROR(VLOOKUP(K21,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D21="",J21=""),"",IF(J21&lt;=G21,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8688,9 +8733,12 @@
           <t>Sudeste</t>
         </is>
       </c>
-      <c r="L22" s="26" t="n"/>
+      <c r="L22" s="26">
+        <f>IF(I22="","",IFERROR(VLOOKUP(I22,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M22" s="30">
-        <f>IF(OR(D22="",J22=""),"",IF(AND(J22&lt;=G22,OR(L22="",L22&lt;=IFERROR(VLOOKUP(K22,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D22="",J22=""),"",IF(J22&lt;=G22,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8733,9 +8781,12 @@
           <t>Sudeste</t>
         </is>
       </c>
-      <c r="L23" s="26" t="n"/>
+      <c r="L23" s="26">
+        <f>IF(I23="","",IFERROR(VLOOKUP(I23,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M23" s="30">
-        <f>IF(OR(D23="",J23=""),"",IF(AND(J23&lt;=G23,OR(L23="",L23&lt;=IFERROR(VLOOKUP(K23,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D23="",J23=""),"",IF(J23&lt;=G23,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8778,9 +8829,12 @@
           <t>Sudeste</t>
         </is>
       </c>
-      <c r="L24" s="26" t="n"/>
+      <c r="L24" s="26">
+        <f>IF(I24="","",IFERROR(VLOOKUP(I24,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M24" s="30">
-        <f>IF(OR(D24="",J24=""),"",IF(AND(J24&lt;=G24,OR(L24="",L24&lt;=IFERROR(VLOOKUP(K24,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D24="",J24=""),"",IF(J24&lt;=G24,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8805,9 +8859,12 @@
       <c r="I25" s="25" t="n"/>
       <c r="J25" s="26" t="n"/>
       <c r="K25" s="25" t="n"/>
-      <c r="L25" s="26" t="n"/>
+      <c r="L25" s="26">
+        <f>IF(I25="","",IFERROR(VLOOKUP(I25,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M25" s="30">
-        <f>IF(OR(D25="",J25=""),"",IF(AND(J25&lt;=G25,OR(L25="",L25&lt;=IFERROR(VLOOKUP(K25,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D25="",J25=""),"",IF(J25&lt;=G25,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8832,9 +8889,12 @@
       <c r="I26" s="32" t="n"/>
       <c r="J26" s="33" t="n"/>
       <c r="K26" s="32" t="n"/>
-      <c r="L26" s="33" t="n"/>
+      <c r="L26" s="33">
+        <f>IF(I26="","",IFERROR(VLOOKUP(I26,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M26" s="37">
-        <f>IF(OR(D26="",J26=""),"",IF(AND(J26&lt;=G26,OR(L26="",L26&lt;=IFERROR(VLOOKUP(K26,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D26="",J26=""),"",IF(J26&lt;=G26,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8899,9 +8959,12 @@
           <t>Noroeste</t>
         </is>
       </c>
-      <c r="L28" s="26" t="n"/>
+      <c r="L28" s="26">
+        <f>IF(I28="","",IFERROR(VLOOKUP(I28,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M28" s="30">
-        <f>IF(OR(D28="",J28=""),"",IF(AND(J28&lt;=G28,OR(L28="",L28&lt;=IFERROR(VLOOKUP(K28,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D28="",J28=""),"",IF(J28&lt;=G28,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8944,9 +9007,12 @@
           <t>Noroeste</t>
         </is>
       </c>
-      <c r="L29" s="26" t="n"/>
+      <c r="L29" s="26">
+        <f>IF(I29="","",IFERROR(VLOOKUP(I29,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M29" s="30">
-        <f>IF(OR(D29="",J29=""),"",IF(AND(J29&lt;=G29,OR(L29="",L29&lt;=IFERROR(VLOOKUP(K29,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D29="",J29=""),"",IF(J29&lt;=G29,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -8989,9 +9055,12 @@
           <t>Noroeste</t>
         </is>
       </c>
-      <c r="L30" s="26" t="n"/>
+      <c r="L30" s="26">
+        <f>IF(I30="","",IFERROR(VLOOKUP(I30,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M30" s="30">
-        <f>IF(OR(D30="",J30=""),"",IF(AND(J30&lt;=G30,OR(L30="",L30&lt;=IFERROR(VLOOKUP(K30,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D30="",J30=""),"",IF(J30&lt;=G30,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9034,9 +9103,12 @@
           <t>Noroeste</t>
         </is>
       </c>
-      <c r="L31" s="26" t="n"/>
+      <c r="L31" s="26">
+        <f>IF(I31="","",IFERROR(VLOOKUP(I31,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M31" s="30">
-        <f>IF(OR(D31="",J31=""),"",IF(AND(J31&lt;=G31,OR(L31="",L31&lt;=IFERROR(VLOOKUP(K31,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D31="",J31=""),"",IF(J31&lt;=G31,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9079,9 +9151,12 @@
           <t>Noroeste</t>
         </is>
       </c>
-      <c r="L32" s="26" t="n"/>
+      <c r="L32" s="26">
+        <f>IF(I32="","",IFERROR(VLOOKUP(I32,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M32" s="30">
-        <f>IF(OR(D32="",J32=""),"",IF(AND(J32&lt;=G32,OR(L32="",L32&lt;=IFERROR(VLOOKUP(K32,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D32="",J32=""),"",IF(J32&lt;=G32,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9106,9 +9181,12 @@
       <c r="I33" s="25" t="n"/>
       <c r="J33" s="26" t="n"/>
       <c r="K33" s="25" t="n"/>
-      <c r="L33" s="26" t="n"/>
+      <c r="L33" s="26">
+        <f>IF(I33="","",IFERROR(VLOOKUP(I33,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M33" s="30">
-        <f>IF(OR(D33="",J33=""),"",IF(AND(J33&lt;=G33,OR(L33="",L33&lt;=IFERROR(VLOOKUP(K33,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D33="",J33=""),"",IF(J33&lt;=G33,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9133,9 +9211,12 @@
       <c r="I34" s="32" t="n"/>
       <c r="J34" s="33" t="n"/>
       <c r="K34" s="32" t="n"/>
-      <c r="L34" s="33" t="n"/>
+      <c r="L34" s="33">
+        <f>IF(I34="","",IFERROR(VLOOKUP(I34,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M34" s="37">
-        <f>IF(OR(D34="",J34=""),"",IF(AND(J34&lt;=G34,OR(L34="",L34&lt;=IFERROR(VLOOKUP(K34,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D34="",J34=""),"",IF(J34&lt;=G34,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9196,9 +9277,12 @@
         <v>2.8</v>
       </c>
       <c r="K36" s="25" t="n"/>
-      <c r="L36" s="26" t="n"/>
+      <c r="L36" s="26">
+        <f>IF(I36="","",IFERROR(VLOOKUP(I36,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M36" s="30">
-        <f>IF(OR(D36="",J36=""),"",IF(AND(J36&lt;=G36,OR(L36="",L36&lt;=IFERROR(VLOOKUP(K36,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D36="",J36=""),"",IF(J36&lt;=G36,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9223,9 +9307,12 @@
       <c r="I37" s="25" t="n"/>
       <c r="J37" s="26" t="n"/>
       <c r="K37" s="25" t="n"/>
-      <c r="L37" s="26" t="n"/>
+      <c r="L37" s="26">
+        <f>IF(I37="","",IFERROR(VLOOKUP(I37,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M37" s="30">
-        <f>IF(OR(D37="",J37=""),"",IF(AND(J37&lt;=G37,OR(L37="",L37&lt;=IFERROR(VLOOKUP(K37,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D37="",J37=""),"",IF(J37&lt;=G37,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9250,9 +9337,12 @@
       <c r="I38" s="32" t="n"/>
       <c r="J38" s="33" t="n"/>
       <c r="K38" s="32" t="n"/>
-      <c r="L38" s="33" t="n"/>
+      <c r="L38" s="33">
+        <f>IF(I38="","",IFERROR(VLOOKUP(I38,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
       <c r="M38" s="37">
-        <f>IF(OR(D38="",J38=""),"",IF(AND(J38&lt;=G38,OR(L38="",L38&lt;=IFERROR(VLOOKUP(K38,Datos_higro!$A$46:$B$54,2,0),99))),"CUMPLE","NO CUMPLE"))</f>
+        <f>IF(OR(D38="",J38=""),"",IF(J38&lt;=G38,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
@@ -9369,7 +9459,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>Orientacion: ya cargada. Factor de exposicion solar: cargarlo en la columna L segun el vidrio</t>
+          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9388,7 +9478,7 @@
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>y la proteccion solar adoptados; la verificacion lo compara contra el maximo del cuadrante,</t>
+          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -9407,7 +9497,7 @@
     <row r="47">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>que esta en la tabla de la hoja Datos_higro.</t>
+          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -9424,7 +9514,11 @@
       <c r="M47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="39" t="inlineStr"/>
+      <c r="A48" s="39" t="inlineStr">
+        <is>
+          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
+        </is>
+      </c>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n"/>
@@ -9441,7 +9535,7 @@
     <row r="49">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -9458,11 +9552,7 @@
       <c r="M49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
-        </is>
-      </c>
+      <c r="A50" s="39" t="inlineStr"/>
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n"/>
@@ -9477,7 +9567,11 @@
       <c r="M50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="39" t="inlineStr"/>
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+        </is>
+      </c>
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n"/>
@@ -9494,7 +9588,7 @@
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9511,11 +9605,7 @@
       <c r="M52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="39" t="inlineStr">
-        <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
-        </is>
-      </c>
+      <c r="A53" s="39" t="inlineStr"/>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n"/>
@@ -9532,7 +9622,7 @@
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B54" s="2" t="n"/>
@@ -9551,7 +9641,7 @@
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9570,7 +9660,7 @@
     <row r="56">
       <c r="A56" s="39" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -9587,7 +9677,11 @@
       <c r="M56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="39" t="inlineStr"/>
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+        </is>
+      </c>
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n"/>
@@ -9604,7 +9698,7 @@
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9621,11 +9715,7 @@
       <c r="M58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="39" t="inlineStr">
-        <is>
-          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
-        </is>
-      </c>
+      <c r="A59" s="39" t="inlineStr"/>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n"/>
@@ -9642,7 +9732,7 @@
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
         <is>
-          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
         </is>
       </c>
       <c r="B60" s="2" t="n"/>
@@ -9661,7 +9751,7 @@
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
@@ -9680,7 +9770,7 @@
     <row r="62">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
         </is>
       </c>
       <c r="B62" s="2" t="n"/>
@@ -9699,7 +9789,7 @@
     <row r="63">
       <c r="A63" s="39" t="inlineStr">
         <is>
-          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
@@ -9718,7 +9808,7 @@
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>parecen ser nombres de uso, no orientaciones.</t>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9735,7 +9825,11 @@
       <c r="M64" s="2" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="39" t="inlineStr"/>
+      <c r="A65" s="39" t="inlineStr">
+        <is>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+        </is>
+      </c>
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n"/>
@@ -9752,7 +9846,7 @@
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
         <is>
-          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B66" s="2" t="n"/>
@@ -9769,11 +9863,7 @@
       <c r="M66" s="2" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="39" t="inlineStr">
-        <is>
-          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
-        </is>
-      </c>
+      <c r="A67" s="39" t="inlineStr"/>
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n"/>
@@ -9788,7 +9878,11 @@
       <c r="M67" s="2" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="39" t="inlineStr"/>
+      <c r="A68" s="39" t="inlineStr">
+        <is>
+          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+        </is>
+      </c>
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n"/>
@@ -9805,7 +9899,7 @@
     <row r="69">
       <c r="A69" s="39" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
         </is>
       </c>
       <c r="B69" s="2" t="n"/>
@@ -9839,7 +9933,7 @@
     <row r="71">
       <c r="A71" s="39" t="inlineStr">
         <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -9856,11 +9950,7 @@
       <c r="M71" s="2" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="39" t="inlineStr">
-        <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
-        </is>
-      </c>
+      <c r="A72" s="39" t="inlineStr"/>
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n"/>
@@ -9877,7 +9967,7 @@
     <row r="73">
       <c r="A73" s="39" t="inlineStr">
         <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
         </is>
       </c>
       <c r="B73" s="2" t="n"/>
@@ -9892,6 +9982,44 @@
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="39" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="39" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -9920,10 +10048,10 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="H6:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Datos_higro!$A$8:$A$15</formula1>
+      <formula1>=Datos_higro!$A$10:$A$17</formula1>
     </dataValidation>
     <dataValidation sqref="I6:I38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Datos_higro!$A$19:$A$25</formula1>
+      <formula1>=Datos_higro!$A$21:$A$27</formula1>
     </dataValidation>
     <dataValidation sqref="K6:K38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Norte,Sur,Este,Oeste,Noreste,Noroeste,Sudeste,Sudoeste,Horizontal"</formula1>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -7915,7 +7915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8128,7 +8128,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I7" s="25" t="n"/>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J7" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8176,7 +8180,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I8" s="25" t="n"/>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J8" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8224,7 +8232,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I9" s="25" t="n"/>
+      <c r="I9" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J9" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8272,7 +8284,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I10" s="25" t="n"/>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J10" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8320,7 +8336,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I11" s="25" t="n"/>
+      <c r="I11" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J11" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8450,7 +8470,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I15" s="25" t="n"/>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J15" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8498,7 +8522,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I16" s="25" t="n"/>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J16" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8628,7 +8656,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I20" s="25" t="n"/>
+      <c r="I20" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J20" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8676,7 +8708,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I21" s="25" t="n"/>
+      <c r="I21" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J21" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8724,7 +8760,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I22" s="25" t="n"/>
+      <c r="I22" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J22" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8772,7 +8812,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I23" s="25" t="n"/>
+      <c r="I23" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J23" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8820,7 +8864,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I24" s="25" t="n"/>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J24" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8950,7 +8998,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I28" s="25" t="n"/>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J28" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -8998,7 +9050,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I29" s="25" t="n"/>
+      <c r="I29" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J29" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -9046,7 +9102,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I30" s="25" t="n"/>
+      <c r="I30" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J30" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -9094,7 +9154,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I31" s="25" t="n"/>
+      <c r="I31" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J31" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -9142,7 +9206,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I32" s="25" t="n"/>
+      <c r="I32" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J32" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -9272,7 +9340,11 @@
           <t>DVH 6+9+3+3 (aluminio linea A30)</t>
         </is>
       </c>
-      <c r="I36" s="25" t="n"/>
+      <c r="I36" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
       <c r="J36" s="26" t="n">
         <v>2.8</v>
       </c>
@@ -9459,7 +9531,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
+          <t>PROTECCION: se cargo cortina de enrollar exterior en todas las aberturas. Cambiar en la</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9478,7 +9550,7 @@
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
+          <t>columna I las que no la tengan; el factor de exposicion solar se recalcula solo.</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -9495,11 +9567,7 @@
       <c r="M46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="39" t="inlineStr">
-        <is>
-          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
-        </is>
-      </c>
+      <c r="A47" s="39" t="inlineStr"/>
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n"/>
@@ -9516,7 +9584,7 @@
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
+          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
@@ -9535,7 +9603,7 @@
     <row r="49">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
+          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -9552,7 +9620,11 @@
       <c r="M49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="39" t="inlineStr"/>
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
+        </is>
+      </c>
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n"/>
@@ -9569,7 +9641,7 @@
     <row r="51">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
         </is>
       </c>
       <c r="B51" s="2" t="n"/>
@@ -9588,7 +9660,7 @@
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9622,7 +9694,7 @@
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
         </is>
       </c>
       <c r="B54" s="2" t="n"/>
@@ -9641,7 +9713,7 @@
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9658,11 +9730,7 @@
       <c r="M55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="39" t="inlineStr">
-        <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
-        </is>
-      </c>
+      <c r="A56" s="39" t="inlineStr"/>
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
@@ -9679,7 +9747,7 @@
     <row r="57">
       <c r="A57" s="39" t="inlineStr">
         <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B57" s="2" t="n"/>
@@ -9698,7 +9766,7 @@
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9715,7 +9783,11 @@
       <c r="M58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="39" t="inlineStr"/>
+      <c r="A59" s="39" t="inlineStr">
+        <is>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+        </is>
+      </c>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n"/>
@@ -9732,7 +9804,7 @@
     <row r="60">
       <c r="A60" s="39" t="inlineStr">
         <is>
-          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
         </is>
       </c>
       <c r="B60" s="2" t="n"/>
@@ -9751,7 +9823,7 @@
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
         <is>
-          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
@@ -9768,11 +9840,7 @@
       <c r="M61" s="2" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="39" t="inlineStr">
-        <is>
-          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
-        </is>
-      </c>
+      <c r="A62" s="39" t="inlineStr"/>
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n"/>
@@ -9789,7 +9857,7 @@
     <row r="63">
       <c r="A63" s="39" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
@@ -9808,7 +9876,7 @@
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9827,7 +9895,7 @@
     <row r="65">
       <c r="A65" s="39" t="inlineStr">
         <is>
-          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -9846,7 +9914,7 @@
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
         <is>
-          <t>parecen ser nombres de uso, no orientaciones.</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
         </is>
       </c>
       <c r="B66" s="2" t="n"/>
@@ -9863,7 +9931,11 @@
       <c r="M66" s="2" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="39" t="inlineStr"/>
+      <c r="A67" s="39" t="inlineStr">
+        <is>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+        </is>
+      </c>
       <c r="B67" s="2" t="n"/>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n"/>
@@ -9880,7 +9952,7 @@
     <row r="68">
       <c r="A68" s="39" t="inlineStr">
         <is>
-          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
         </is>
       </c>
       <c r="B68" s="2" t="n"/>
@@ -9899,7 +9971,7 @@
     <row r="69">
       <c r="A69" s="39" t="inlineStr">
         <is>
-          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B69" s="2" t="n"/>
@@ -9933,7 +10005,7 @@
     <row r="71">
       <c r="A71" s="39" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -9950,7 +10022,11 @@
       <c r="M71" s="2" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="39" t="inlineStr"/>
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
+        </is>
+      </c>
       <c r="B72" s="2" t="n"/>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n"/>
@@ -9965,11 +10041,7 @@
       <c r="M72" s="2" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="39" t="inlineStr">
-        <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
-        </is>
-      </c>
+      <c r="A73" s="39" t="inlineStr"/>
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n"/>
@@ -9986,7 +10058,7 @@
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
         <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
         </is>
       </c>
       <c r="B74" s="2" t="n"/>
@@ -10003,11 +10075,7 @@
       <c r="M74" s="2" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="39" t="inlineStr">
-        <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
-        </is>
-      </c>
+      <c r="A75" s="39" t="inlineStr"/>
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n"/>
@@ -10020,6 +10088,63 @@
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="39" t="inlineStr">
+        <is>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="39" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
+      <c r="M77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="39" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -7915,7 +7915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J8" s="26" t="n">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J11" s="26" t="n">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J16" s="26" t="n">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="I21" s="25" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J21" s="26" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="I24" s="25" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J24" s="26" t="n">
@@ -9531,7 +9531,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>PROTECCION: se cargo cortina de enrollar exterior en todas las aberturas. Cambiar en la</t>
+          <t>PROTECCION: cortina de enrollar exterior (FES 0,25) en todas, salvo los panos fijos del patio</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9550,7 +9550,7 @@
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>columna I las que no la tengan; el factor de exposicion solar se recalcula solo.</t>
+          <t>(PF01, su gemelo, PF02 y PF03) y PF04, que no la tienen y van Sin Proteccion (FES 0,88).</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -9584,7 +9584,7 @@
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
+          <t>OJO con esas cinco: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
@@ -9603,7 +9603,7 @@
     <row r="49">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
+          <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -9622,7 +9622,7 @@
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
+          <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9641,7 +9641,7 @@
     <row r="51">
       <c r="A51" s="39" t="inlineStr">
         <is>
-          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
+          <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
         </is>
       </c>
       <c r="B51" s="2" t="n"/>
@@ -9660,7 +9660,7 @@
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
+          <t>Hay una salida: si la abertura ocupa menos del 20% del lado expuesto del local, no se verifica</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9677,7 +9677,11 @@
       <c r="M52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="39" t="inlineStr"/>
+      <c r="A53" s="39" t="inlineStr">
+        <is>
+          <t>el FES. Conviene chequearlo local por local.</t>
+        </is>
+      </c>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n"/>
@@ -9692,11 +9696,7 @@
       <c r="M53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr">
-        <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
-        </is>
-      </c>
+      <c r="A54" s="39" t="inlineStr"/>
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n"/>
@@ -9713,7 +9713,7 @@
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9730,7 +9730,11 @@
       <c r="M55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="39" t="inlineStr"/>
+      <c r="A56" s="39" t="inlineStr">
+        <is>
+          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
+        </is>
+      </c>
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
@@ -9747,7 +9751,7 @@
     <row r="57">
       <c r="A57" s="39" t="inlineStr">
         <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
+          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B57" s="2" t="n"/>
@@ -9766,7 +9770,7 @@
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
+          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9785,7 +9789,7 @@
     <row r="59">
       <c r="A59" s="39" t="inlineStr">
         <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B59" s="2" t="n"/>
@@ -9802,11 +9806,7 @@
       <c r="M59" s="2" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="39" t="inlineStr">
-        <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
-        </is>
-      </c>
+      <c r="A60" s="39" t="inlineStr"/>
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n"/>
@@ -9823,7 +9823,7 @@
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
@@ -9840,7 +9840,11 @@
       <c r="M61" s="2" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="39" t="inlineStr"/>
+      <c r="A62" s="39" t="inlineStr">
+        <is>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+        </is>
+      </c>
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n"/>
@@ -9855,11 +9859,7 @@
       <c r="M62" s="2" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="39" t="inlineStr">
-        <is>
-          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
-        </is>
-      </c>
+      <c r="A63" s="39" t="inlineStr"/>
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n"/>
@@ -9876,7 +9876,7 @@
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9895,7 +9895,7 @@
     <row r="65">
       <c r="A65" s="39" t="inlineStr">
         <is>
-          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -9914,7 +9914,7 @@
     <row r="66">
       <c r="A66" s="39" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
         </is>
       </c>
       <c r="B66" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
     <row r="67">
       <c r="A67" s="39" t="inlineStr">
         <is>
-          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
         </is>
       </c>
       <c r="B67" s="2" t="n"/>
@@ -9952,7 +9952,7 @@
     <row r="68">
       <c r="A68" s="39" t="inlineStr">
         <is>
-          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
         </is>
       </c>
       <c r="B68" s="2" t="n"/>
@@ -9969,11 +9969,7 @@
       <c r="M68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="39" t="inlineStr">
-        <is>
-          <t>parecen ser nombres de uso, no orientaciones.</t>
-        </is>
-      </c>
+      <c r="A69" s="39" t="inlineStr"/>
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n"/>
@@ -9988,7 +9984,11 @@
       <c r="M69" s="2" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="39" t="inlineStr"/>
+      <c r="A70" s="39" t="inlineStr">
+        <is>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
+        </is>
+      </c>
       <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n"/>
@@ -10005,7 +10005,7 @@
     <row r="71">
       <c r="A71" s="39" t="inlineStr">
         <is>
-          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -10024,7 +10024,7 @@
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
         <is>
-          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
         </is>
       </c>
       <c r="B72" s="2" t="n"/>
@@ -10041,7 +10041,11 @@
       <c r="M72" s="2" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="39" t="inlineStr"/>
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+        </is>
+      </c>
       <c r="B73" s="2" t="n"/>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n"/>
@@ -10058,7 +10062,7 @@
     <row r="74">
       <c r="A74" s="39" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
         </is>
       </c>
       <c r="B74" s="2" t="n"/>
@@ -10075,7 +10079,11 @@
       <c r="M74" s="2" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="39" t="inlineStr"/>
+      <c r="A75" s="39" t="inlineStr">
+        <is>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+        </is>
+      </c>
       <c r="B75" s="2" t="n"/>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n"/>
@@ -10092,7 +10100,7 @@
     <row r="76">
       <c r="A76" s="39" t="inlineStr">
         <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B76" s="2" t="n"/>
@@ -10109,11 +10117,7 @@
       <c r="M76" s="2" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="39" t="inlineStr">
-        <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
-        </is>
-      </c>
+      <c r="A77" s="39" t="inlineStr"/>
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n"/>
@@ -10130,7 +10134,7 @@
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
         </is>
       </c>
       <c r="B78" s="2" t="n"/>
@@ -10145,6 +10149,131 @@
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="39" t="inlineStr">
+        <is>
+          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="n"/>
+      <c r="M79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="39" t="inlineStr"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="39" t="inlineStr">
+        <is>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="n"/>
+      <c r="L81" s="2" t="n"/>
+      <c r="M81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="39" t="inlineStr"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="39" t="inlineStr">
+        <is>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="n"/>
+      <c r="M83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="39" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I32" s="25" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J32" s="26" t="n">
@@ -9531,7 +9531,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>PROTECCION: cortina de enrollar exterior (FES 0,25) en todas, salvo los panos fijos del patio</t>
+          <t>PROTECCION: ningun pano fijo PF tiene cortina: PF01, su gemelo, PF02, PF03, PF04 y PF05 van</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9550,7 +9550,7 @@
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>(PF01, su gemelo, PF02 y PF03) y PF04, que no la tienen y van Sin Proteccion (FES 0,88).</t>
+          <t>Sin Proteccion (FES 0,88). Las otras doce llevan cortina de enrollar exterior (FES 0,25).</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -9584,7 +9584,7 @@
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>OJO con esas cinco: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
+          <t>OJO con esas seis: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Planilla 3 higrotermica'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla vigas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla vigas'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla losas'!$1:$3</definedName>
@@ -7915,7 +7915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8640,7 +8640,7 @@
         <v/>
       </c>
       <c r="E20" s="28">
-        <f>SUM(D20:D26)</f>
+        <f>SUM(D20:D27)</f>
         <v/>
       </c>
       <c r="F20" s="29">
@@ -8837,14 +8837,14 @@
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>PF02</t>
+          <t>PV04 (2)</t>
         </is>
       </c>
       <c r="B24" s="26" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="C24" s="26" t="n">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="D24" s="27">
         <f>IF(COUNT(B24,C24)&lt;2,"",B24*C24)</f>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="I24" s="25" t="inlineStr">
         <is>
-          <t>Sin Proteccion</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="J24" s="26" t="n">
@@ -8887,9 +8887,17 @@
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="26" t="n"/>
-      <c r="C25" s="26" t="n"/>
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>PF02</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>3.75</v>
+      </c>
       <c r="D25" s="27">
         <f>IF(COUNT(B25,C25)&lt;2,"",B25*C25)</f>
         <v/>
@@ -8903,10 +8911,24 @@
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="25" t="n"/>
-      <c r="J25" s="26" t="n"/>
-      <c r="K25" s="25" t="n"/>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="inlineStr">
+        <is>
+          <t>Sin Proteccion</t>
+        </is>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K25" s="25" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
       <c r="L25" s="26">
         <f>IF(I25="","",IFERROR(VLOOKUP(I25,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
@@ -8917,128 +8939,106 @@
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="32" t="n"/>
-      <c r="B26" s="33" t="n"/>
-      <c r="C26" s="33" t="n"/>
-      <c r="D26" s="34">
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="27">
         <f>IF(COUNT(B26,C26)&lt;2,"",B26*C26)</f>
         <v/>
       </c>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="36">
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="29">
         <f>IF(OR(D26="",$E$20=""),"",D26/$E$20)</f>
         <v/>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="33" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="33">
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="26" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="26">
         <f>IF(I26="","",IFERROR(VLOOKUP(I26,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
       </c>
-      <c r="M26" s="37">
+      <c r="M26" s="30">
         <f>IF(OR(D26="",J26=""),"",IF(J26&lt;=G26,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="32" t="n"/>
+      <c r="B27" s="33" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="34">
+        <f>IF(COUNT(B27,C27)&lt;2,"",B27*C27)</f>
+        <v/>
+      </c>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="36">
+        <f>IF(OR(D27="",$E$20=""),"",D27/$E$20)</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
+      <c r="J27" s="33" t="n"/>
+      <c r="K27" s="32" t="n"/>
+      <c r="L27" s="33">
+        <f>IF(I27="","",IFERROR(VLOOKUP(I27,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M27" s="37">
+        <f>IF(OR(D27="",J27=""),"",IF(J27&lt;=G27,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>Plano: Fachada Noroeste (borde superior)</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>PV03</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="D28" s="27">
-        <f>IF(COUNT(B28,C28)&lt;2,"",B28*C28)</f>
-        <v/>
-      </c>
-      <c r="E28" s="28">
-        <f>SUM(D28:D34)</f>
-        <v/>
-      </c>
-      <c r="F28" s="29">
-        <f>IF(OR(D28="",$E$28=""),"",D28/$E$28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H28" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I28" s="25" t="inlineStr">
-        <is>
-          <t>Cortina de enrollar exterior</t>
-        </is>
-      </c>
-      <c r="J28" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K28" s="25" t="inlineStr">
-        <is>
-          <t>Noroeste</t>
-        </is>
-      </c>
-      <c r="L28" s="26">
-        <f>IF(I28="","",IFERROR(VLOOKUP(I28,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M28" s="30">
-        <f>IF(OR(D28="",J28=""),"",IF(J28&lt;=G28,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>VA02</t>
+          <t>PV03</t>
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="C29" s="26" t="n">
-        <v>0.75</v>
+        <v>1.76</v>
       </c>
       <c r="D29" s="27">
         <f>IF(COUNT(B29,C29)&lt;2,"",B29*C29)</f>
         <v/>
       </c>
-      <c r="E29" s="31" t="n"/>
+      <c r="E29" s="28">
+        <f>SUM(D29:D35)</f>
+        <v/>
+      </c>
       <c r="F29" s="29">
-        <f>IF(OR(D29="",$E$28=""),"",D29/$E$28)</f>
+        <f>IF(OR(D29="",$E$29=""),"",D29/$E$29)</f>
         <v/>
       </c>
       <c r="G29" s="27">
@@ -9075,11 +9075,11 @@
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>PA02</t>
+          <t>VA02</t>
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="C30" s="26" t="n">
         <v>0.75</v>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="E30" s="31" t="n"/>
       <c r="F30" s="29">
-        <f>IF(OR(D30="",$E$28=""),"",D30/$E$28)</f>
+        <f>IF(OR(D30="",$E$29=""),"",D30/$E$29)</f>
         <v/>
       </c>
       <c r="G30" s="27">
@@ -9127,11 +9127,11 @@
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>VA03</t>
+          <t>PA02</t>
         </is>
       </c>
       <c r="B31" s="26" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="C31" s="26" t="n">
         <v>0.75</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="E31" s="31" t="n"/>
       <c r="F31" s="29">
-        <f>IF(OR(D31="",$E$28=""),"",D31/$E$28)</f>
+        <f>IF(OR(D31="",$E$29=""),"",D31/$E$29)</f>
         <v/>
       </c>
       <c r="G31" s="27">
@@ -9179,7 +9179,7 @@
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>PF05</t>
+          <t>VA03</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="E32" s="31" t="n"/>
       <c r="F32" s="29">
-        <f>IF(OR(D32="",$E$28=""),"",D32/$E$28)</f>
+        <f>IF(OR(D32="",$E$29=""),"",D32/$E$29)</f>
         <v/>
       </c>
       <c r="G32" s="27">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I32" s="25" t="inlineStr">
         <is>
-          <t>Sin Proteccion</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="J32" s="26" t="n">
@@ -9229,26 +9229,48 @@
       </c>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="26" t="n"/>
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>PF05</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>0.75</v>
+      </c>
       <c r="D33" s="27">
         <f>IF(COUNT(B33,C33)&lt;2,"",B33*C33)</f>
         <v/>
       </c>
       <c r="E33" s="31" t="n"/>
       <c r="F33" s="29">
-        <f>IF(OR(D33="",$E$28=""),"",D33/$E$28)</f>
+        <f>IF(OR(D33="",$E$29=""),"",D33/$E$29)</f>
         <v/>
       </c>
       <c r="G33" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="25" t="n"/>
-      <c r="J33" s="26" t="n"/>
-      <c r="K33" s="25" t="n"/>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I33" s="25" t="inlineStr">
+        <is>
+          <t>Sin Proteccion</t>
+        </is>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K33" s="25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
       <c r="L33" s="26">
         <f>IF(I33="","",IFERROR(VLOOKUP(I33,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
@@ -9259,167 +9281,124 @@
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="32" t="n"/>
-      <c r="B34" s="33" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="34">
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="27">
         <f>IF(COUNT(B34,C34)&lt;2,"",B34*C34)</f>
         <v/>
       </c>
-      <c r="E34" s="35" t="n"/>
-      <c r="F34" s="36">
-        <f>IF(OR(D34="",$E$28=""),"",D34/$E$28)</f>
-        <v/>
-      </c>
-      <c r="G34" s="34">
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="29">
+        <f>IF(OR(D34="",$E$29=""),"",D34/$E$29)</f>
+        <v/>
+      </c>
+      <c r="G34" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H34" s="32" t="n"/>
-      <c r="I34" s="32" t="n"/>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="32" t="n"/>
-      <c r="L34" s="33">
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="26" t="n"/>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="26">
         <f>IF(I34="","",IFERROR(VLOOKUP(I34,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
       </c>
-      <c r="M34" s="37">
+      <c r="M34" s="30">
         <f>IF(OR(D34="",J34=""),"",IF(J34&lt;=G34,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>Plano: Ubicacion a confirmar</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>PV04 (2)</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="C36" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D36" s="27">
-        <f>IF(COUNT(B36,C36)&lt;2,"",B36*C36)</f>
-        <v/>
-      </c>
-      <c r="E36" s="28">
-        <f>SUM(D36:D38)</f>
-        <v/>
-      </c>
-      <c r="F36" s="29">
-        <f>IF(OR(D36="",$E$36=""),"",D36/$E$36)</f>
-        <v/>
-      </c>
-      <c r="G36" s="27">
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="32" t="n"/>
+      <c r="B35" s="33" t="n"/>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="34">
+        <f>IF(COUNT(B35,C35)&lt;2,"",B35*C35)</f>
+        <v/>
+      </c>
+      <c r="E35" s="35" t="n"/>
+      <c r="F35" s="36">
+        <f>IF(OR(D35="",$E$29=""),"",D35/$E$29)</f>
+        <v/>
+      </c>
+      <c r="G35" s="34">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H36" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I36" s="25" t="inlineStr">
-        <is>
-          <t>Cortina de enrollar exterior</t>
-        </is>
-      </c>
-      <c r="J36" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K36" s="25" t="n"/>
-      <c r="L36" s="26">
-        <f>IF(I36="","",IFERROR(VLOOKUP(I36,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M36" s="30">
-        <f>IF(OR(D36="",J36=""),"",IF(J36&lt;=G36,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="25" t="n"/>
-      <c r="B37" s="26" t="n"/>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="27">
-        <f>IF(COUNT(B37,C37)&lt;2,"",B37*C37)</f>
-        <v/>
-      </c>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="29">
-        <f>IF(OR(D37="",$E$36=""),"",D37/$E$36)</f>
-        <v/>
-      </c>
-      <c r="G37" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="25" t="n"/>
-      <c r="J37" s="26" t="n"/>
-      <c r="K37" s="25" t="n"/>
-      <c r="L37" s="26">
-        <f>IF(I37="","",IFERROR(VLOOKUP(I37,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M37" s="30">
-        <f>IF(OR(D37="",J37=""),"",IF(J37&lt;=G37,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="32" t="n"/>
-      <c r="B38" s="33" t="n"/>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="34">
-        <f>IF(COUNT(B38,C38)&lt;2,"",B38*C38)</f>
-        <v/>
-      </c>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="36">
-        <f>IF(OR(D38="",$E$36=""),"",D38/$E$36)</f>
-        <v/>
-      </c>
-      <c r="G38" s="34">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H38" s="32" t="n"/>
-      <c r="I38" s="32" t="n"/>
-      <c r="J38" s="33" t="n"/>
-      <c r="K38" s="32" t="n"/>
-      <c r="L38" s="33">
-        <f>IF(I38="","",IFERROR(VLOOKUP(I38,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M38" s="37">
-        <f>IF(OR(D38="",J38=""),"",IF(J38&lt;=G38,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+      <c r="H35" s="32" t="n"/>
+      <c r="I35" s="32" t="n"/>
+      <c r="J35" s="33" t="n"/>
+      <c r="K35" s="32" t="n"/>
+      <c r="L35" s="33">
+        <f>IF(I35="","",IFERROR(VLOOKUP(I35,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M35" s="37">
+        <f>IF(OR(D35="",J35=""),"",IF(J35&lt;=G35,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="38" t="inlineStr">
+        <is>
+          <t>COMO SE COMPLETA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
+        </is>
+      </c>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n"/>
@@ -9434,9 +9413,9 @@
       <c r="M39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="38" t="inlineStr">
-        <is>
-          <t>COMO SE COMPLETA</t>
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
@@ -9455,7 +9434,7 @@
     <row r="41">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
+          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
         </is>
       </c>
       <c r="B41" s="2" t="n"/>
@@ -9474,7 +9453,7 @@
     <row r="42">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
+          <t>PROTECCION: ningun pano fijo PF tiene cortina: PF01, su gemelo, PF02, PF03, PF04 y PF05 van</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>
@@ -9493,7 +9472,7 @@
     <row r="43">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
+          <t>Sin Proteccion (FES 0,88). Las otras doce llevan cortina de enrollar exterior (FES 0,25).</t>
         </is>
       </c>
       <c r="B43" s="2" t="n"/>
@@ -9510,11 +9489,7 @@
       <c r="M43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="39" t="inlineStr">
-        <is>
-          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
-        </is>
-      </c>
+      <c r="A44" s="39" t="inlineStr"/>
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
@@ -9531,7 +9506,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>PROTECCION: ningun pano fijo PF tiene cortina: PF01, su gemelo, PF02, PF03, PF04 y PF05 van</t>
+          <t>OJO con esas seis: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9550,7 +9525,7 @@
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>Sin Proteccion (FES 0,88). Las otras doce llevan cortina de enrollar exterior (FES 0,25).</t>
+          <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -9567,7 +9542,11 @@
       <c r="M46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="39" t="inlineStr"/>
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
+        </is>
+      </c>
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n"/>
@@ -9584,7 +9563,7 @@
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>OJO con esas seis: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
+          <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
@@ -9603,7 +9582,7 @@
     <row r="49">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
+          <t>Hay una salida: si la abertura ocupa menos del 20% del lado expuesto del local, no se verifica</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -9622,7 +9601,7 @@
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
+          <t>el FES. Conviene chequearlo local por local.</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9639,11 +9618,7 @@
       <c r="M50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="39" t="inlineStr">
-        <is>
-          <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
-        </is>
-      </c>
+      <c r="A51" s="39" t="inlineStr"/>
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n"/>
@@ -9660,7 +9635,7 @@
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>Hay una salida: si la abertura ocupa menos del 20% del lado expuesto del local, no se verifica</t>
+          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9679,7 +9654,7 @@
     <row r="53">
       <c r="A53" s="39" t="inlineStr">
         <is>
-          <t>el FES. Conviene chequearlo local por local.</t>
+          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
         </is>
       </c>
       <c r="B53" s="2" t="n"/>
@@ -9696,7 +9671,11 @@
       <c r="M53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr"/>
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
+        </is>
+      </c>
       <c r="B54" s="2" t="n"/>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n"/>
@@ -9713,7 +9692,7 @@
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
+          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9732,7 +9711,7 @@
     <row r="56">
       <c r="A56" s="39" t="inlineStr">
         <is>
-          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
+          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -9749,11 +9728,7 @@
       <c r="M56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="39" t="inlineStr">
-        <is>
-          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
-        </is>
-      </c>
+      <c r="A57" s="39" t="inlineStr"/>
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n"/>
@@ -9770,7 +9745,7 @@
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9789,7 +9764,7 @@
     <row r="59">
       <c r="A59" s="39" t="inlineStr">
         <is>
-          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
         </is>
       </c>
       <c r="B59" s="2" t="n"/>
@@ -9823,7 +9798,7 @@
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
         <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
@@ -9842,7 +9817,7 @@
     <row r="62">
       <c r="A62" s="39" t="inlineStr">
         <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B62" s="2" t="n"/>
@@ -9859,7 +9834,11 @@
       <c r="M62" s="2" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="39" t="inlineStr"/>
+      <c r="A63" s="39" t="inlineStr">
+        <is>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+        </is>
+      </c>
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n"/>
@@ -9876,7 +9855,7 @@
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9895,7 +9874,7 @@
     <row r="65">
       <c r="A65" s="39" t="inlineStr">
         <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -9912,11 +9891,7 @@
       <c r="M65" s="2" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="39" t="inlineStr">
-        <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
-        </is>
-      </c>
+      <c r="A66" s="39" t="inlineStr"/>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n"/>
@@ -9933,7 +9908,7 @@
     <row r="67">
       <c r="A67" s="39" t="inlineStr">
         <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
         </is>
       </c>
       <c r="B67" s="2" t="n"/>
@@ -9952,7 +9927,7 @@
     <row r="68">
       <c r="A68" s="39" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B68" s="2" t="n"/>
@@ -9969,7 +9944,11 @@
       <c r="M68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="39" t="inlineStr"/>
+      <c r="A69" s="39" t="inlineStr">
+        <is>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
+        </is>
+      </c>
       <c r="B69" s="2" t="n"/>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n"/>
@@ -9986,7 +9965,7 @@
     <row r="70">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
         </is>
       </c>
       <c r="B70" s="2" t="n"/>
@@ -10005,7 +9984,7 @@
     <row r="71">
       <c r="A71" s="39" t="inlineStr">
         <is>
-          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -10024,7 +10003,7 @@
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
         <is>
-          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
         </is>
       </c>
       <c r="B72" s="2" t="n"/>
@@ -10043,7 +10022,7 @@
     <row r="73">
       <c r="A73" s="39" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B73" s="2" t="n"/>
@@ -10060,11 +10039,7 @@
       <c r="M73" s="2" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="39" t="inlineStr">
-        <is>
-          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
-        </is>
-      </c>
+      <c r="A74" s="39" t="inlineStr"/>
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n"/>
@@ -10081,7 +10056,7 @@
     <row r="75">
       <c r="A75" s="39" t="inlineStr">
         <is>
-          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
         </is>
       </c>
       <c r="B75" s="2" t="n"/>
@@ -10100,7 +10075,7 @@
     <row r="76">
       <c r="A76" s="39" t="inlineStr">
         <is>
-          <t>parecen ser nombres de uso, no orientaciones.</t>
+          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
         </is>
       </c>
       <c r="B76" s="2" t="n"/>
@@ -10134,7 +10109,7 @@
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
         </is>
       </c>
       <c r="B78" s="2" t="n"/>
@@ -10151,11 +10126,7 @@
       <c r="M78" s="2" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="39" t="inlineStr">
-        <is>
-          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
-        </is>
-      </c>
+      <c r="A79" s="39" t="inlineStr"/>
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n"/>
@@ -10170,7 +10141,11 @@
       <c r="M79" s="2" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="39" t="inlineStr"/>
+      <c r="A80" s="39" t="inlineStr">
+        <is>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+        </is>
+      </c>
       <c r="B80" s="2" t="n"/>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n"/>
@@ -10187,7 +10162,7 @@
     <row r="81">
       <c r="A81" s="39" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
         </is>
       </c>
       <c r="B81" s="2" t="n"/>
@@ -10204,7 +10179,11 @@
       <c r="M81" s="2" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="39" t="inlineStr"/>
+      <c r="A82" s="39" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
       <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n"/>
@@ -10218,81 +10197,22 @@
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
     </row>
-    <row r="83">
-      <c r="A83" s="39" t="inlineStr">
-        <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="n"/>
-      <c r="F83" s="2" t="n"/>
-      <c r="G83" s="2" t="n"/>
-      <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="n"/>
-      <c r="L83" s="2" t="n"/>
-      <c r="M83" s="2" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="39" t="inlineStr">
-        <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="n"/>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
-      <c r="L84" s="2" t="n"/>
-      <c r="M84" s="2" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="39" t="inlineStr">
-        <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="n"/>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="n"/>
-      <c r="L85" s="2" t="n"/>
-      <c r="M85" s="2" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="E36:E38"/>
+  <mergeCells count="12">
     <mergeCell ref="A19:M19"/>
     <mergeCell ref="A14:M14"/>
-    <mergeCell ref="E20:E26"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A27:M27"/>
-    <mergeCell ref="E28:E34"/>
     <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="E20:E27"/>
     <mergeCell ref="A4:M4"/>
+    <mergeCell ref="E29:E35"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="E7:E13"/>
     <mergeCell ref="E15:E18"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
-  <conditionalFormatting sqref="M6:M38">
+  <conditionalFormatting sqref="M6:M35">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"CUMPLE"</formula>
     </cfRule>
@@ -10301,13 +10221,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H6:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$10:$A$17</formula1>
     </dataValidation>
-    <dataValidation sqref="I6:I38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$21:$A$27</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Norte,Sur,Este,Oeste,Noreste,Noroeste,Sudeste,Sudoeste,Horizontal"</formula1>
     </dataValidation>
   </dataValidations>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -29,7 +29,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Iluminacion y ventilacion'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Planilla 3 higrotermica'!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planilla 3 higrotermica'!$A$1:$M$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Planilla vigas'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Planilla vigas'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Planilla losas'!$1:$3</definedName>
@@ -7915,7 +7915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8112,7 +8112,7 @@
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>SUM(D7:D13)</f>
+        <f>SUM(D7:D14)</f>
         <v/>
       </c>
       <c r="F7" s="29">
@@ -8257,14 +8257,14 @@
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>PV01</t>
+          <t>VA04 (2)</t>
         </is>
       </c>
       <c r="B10" s="26" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="C10" s="26" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="D10" s="27">
         <f>IF(COUNT(B10,C10)&lt;2,"",B10*C10)</f>
@@ -8309,14 +8309,14 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>PF01</t>
+          <t>PV01</t>
         </is>
       </c>
       <c r="B11" s="26" t="n">
         <v>3</v>
       </c>
       <c r="C11" s="26" t="n">
-        <v>3.55</v>
+        <v>7.7</v>
       </c>
       <c r="D11" s="27">
         <f>IF(COUNT(B11,C11)&lt;2,"",B11*C11)</f>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
-          <t>Sin Proteccion</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="J11" s="26" t="n">
@@ -8359,9 +8359,17 @@
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>PF01</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>3.55</v>
+      </c>
       <c r="D12" s="27">
         <f>IF(COUNT(B12,C12)&lt;2,"",B12*C12)</f>
         <v/>
@@ -8375,10 +8383,24 @@
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="25" t="n"/>
+      <c r="H12" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>Sin Proteccion</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K12" s="25" t="inlineStr">
+        <is>
+          <t>Noreste</t>
+        </is>
+      </c>
       <c r="L12" s="26">
         <f>IF(I12="","",IFERROR(VLOOKUP(I12,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
@@ -8389,128 +8411,106 @@
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="32" t="n"/>
-      <c r="B13" s="33" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="34">
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="27">
         <f>IF(COUNT(B13,C13)&lt;2,"",B13*C13)</f>
         <v/>
       </c>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="36">
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="29">
         <f>IF(OR(D13="",$E$7=""),"",D13/$E$7)</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="33" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="33">
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="25" t="n"/>
+      <c r="J13" s="26" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="26">
         <f>IF(I13="","",IFERROR(VLOOKUP(I13,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
       </c>
-      <c r="M13" s="37">
+      <c r="M13" s="30">
         <f>IF(OR(D13="",J13=""),"",IF(J13&lt;=G13,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="32" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="34">
+        <f>IF(COUNT(B14,C14)&lt;2,"",B14*C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="36">
+        <f>IF(OR(D14="",$E$7=""),"",D14/$E$7)</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H14" s="32" t="n"/>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="33" t="n"/>
+      <c r="K14" s="32" t="n"/>
+      <c r="L14" s="33">
+        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M14" s="37">
+        <f>IF(OR(D14="",J14=""),"",IF(J14&lt;=G14,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Plano: Fachada Sudoeste (borde izquierdo)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>VA01</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D15" s="27">
-        <f>IF(COUNT(B15,C15)&lt;2,"",B15*C15)</f>
-        <v/>
-      </c>
-      <c r="E15" s="28">
-        <f>SUM(D15:D18)</f>
-        <v/>
-      </c>
-      <c r="F15" s="29">
-        <f>IF(OR(D15="",$E$15=""),"",D15/$E$15)</f>
-        <v/>
-      </c>
-      <c r="G15" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H15" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>Cortina de enrollar exterior</t>
-        </is>
-      </c>
-      <c r="J15" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K15" s="25" t="inlineStr">
-        <is>
-          <t>Sudoeste</t>
-        </is>
-      </c>
-      <c r="L15" s="26">
-        <f>IF(I15="","",IFERROR(VLOOKUP(I15,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M15" s="30">
-        <f>IF(OR(D15="",J15=""),"",IF(J15&lt;=G15,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>PF01 (2)</t>
+          <t>VA01</t>
         </is>
       </c>
       <c r="B16" s="26" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="26" t="n">
-        <v>3.55</v>
+        <v>0.75</v>
       </c>
       <c r="D16" s="27">
         <f>IF(COUNT(B16,C16)&lt;2,"",B16*C16)</f>
         <v/>
       </c>
-      <c r="E16" s="31" t="n"/>
+      <c r="E16" s="28">
+        <f>SUM(D16:D19)</f>
+        <v/>
+      </c>
       <c r="F16" s="29">
-        <f>IF(OR(D16="",$E$15=""),"",D16/$E$15)</f>
+        <f>IF(OR(D16="",$E$16=""),"",D16/$E$16)</f>
         <v/>
       </c>
       <c r="G16" s="27">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
-          <t>Sin Proteccion</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="J16" s="26" t="n">
@@ -8545,26 +8545,48 @@
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="26" t="n"/>
-      <c r="C17" s="26" t="n"/>
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>PF01 (2)</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>3.55</v>
+      </c>
       <c r="D17" s="27">
         <f>IF(COUNT(B17,C17)&lt;2,"",B17*C17)</f>
         <v/>
       </c>
       <c r="E17" s="31" t="n"/>
       <c r="F17" s="29">
-        <f>IF(OR(D17="",$E$15=""),"",D17/$E$15)</f>
+        <f>IF(OR(D17="",$E$16=""),"",D17/$E$16)</f>
         <v/>
       </c>
       <c r="G17" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="25" t="n"/>
-      <c r="J17" s="26" t="n"/>
-      <c r="K17" s="25" t="n"/>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Sin Proteccion</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t>Sudoeste</t>
+        </is>
+      </c>
       <c r="L17" s="26">
         <f>IF(I17="","",IFERROR(VLOOKUP(I17,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
@@ -8575,128 +8597,106 @@
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="32" t="n"/>
-      <c r="B18" s="33" t="n"/>
-      <c r="C18" s="33" t="n"/>
-      <c r="D18" s="34">
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="27">
         <f>IF(COUNT(B18,C18)&lt;2,"",B18*C18)</f>
         <v/>
       </c>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="36">
-        <f>IF(OR(D18="",$E$15=""),"",D18/$E$15)</f>
-        <v/>
-      </c>
-      <c r="G18" s="34">
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="29">
+        <f>IF(OR(D18="",$E$16=""),"",D18/$E$16)</f>
+        <v/>
+      </c>
+      <c r="G18" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H18" s="32" t="n"/>
-      <c r="I18" s="32" t="n"/>
-      <c r="J18" s="33" t="n"/>
-      <c r="K18" s="32" t="n"/>
-      <c r="L18" s="33">
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="26" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="26">
         <f>IF(I18="","",IFERROR(VLOOKUP(I18,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="30">
         <f>IF(OR(D18="",J18=""),"",IF(J18&lt;=G18,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="32" t="n"/>
+      <c r="B19" s="33" t="n"/>
+      <c r="C19" s="33" t="n"/>
+      <c r="D19" s="34">
+        <f>IF(COUNT(B19,C19)&lt;2,"",B19*C19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="36">
+        <f>IF(OR(D19="",$E$16=""),"",D19/$E$16)</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="32" t="n"/>
+      <c r="J19" s="33" t="n"/>
+      <c r="K19" s="32" t="n"/>
+      <c r="L19" s="33">
+        <f>IF(I19="","",IFERROR(VLOOKUP(I19,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M19" s="37">
+        <f>IF(OR(D19="",J19=""),"",IF(J19&lt;=G19,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Plano: Fachada Sudeste (borde inferior)</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>PA01</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="27">
-        <f>IF(COUNT(B20,C20)&lt;2,"",B20*C20)</f>
-        <v/>
-      </c>
-      <c r="E20" s="28">
-        <f>SUM(D20:D27)</f>
-        <v/>
-      </c>
-      <c r="F20" s="29">
-        <f>IF(OR(D20="",$E$20=""),"",D20/$E$20)</f>
-        <v/>
-      </c>
-      <c r="G20" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H20" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Cortina de enrollar exterior</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" s="25" t="inlineStr">
-        <is>
-          <t>Sudeste</t>
-        </is>
-      </c>
-      <c r="L20" s="26">
-        <f>IF(I20="","",IFERROR(VLOOKUP(I20,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M20" s="30">
-        <f>IF(OR(D20="",J20=""),"",IF(J20&lt;=G20,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>PF04</t>
+          <t>PA01</t>
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="C21" s="26" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="D21" s="27">
         <f>IF(COUNT(B21,C21)&lt;2,"",B21*C21)</f>
         <v/>
       </c>
-      <c r="E21" s="31" t="n"/>
+      <c r="E21" s="28">
+        <f>SUM(D21:D29)</f>
+        <v/>
+      </c>
       <c r="F21" s="29">
-        <f>IF(OR(D21="",$E$20=""),"",D21/$E$20)</f>
+        <f>IF(OR(D21="",$E$21=""),"",D21/$E$21)</f>
         <v/>
       </c>
       <c r="G21" s="27">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="I21" s="25" t="inlineStr">
         <is>
-          <t>Sin Proteccion</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="J21" s="26" t="n">
@@ -8733,14 +8733,14 @@
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>VA05</t>
+          <t>PF04</t>
         </is>
       </c>
       <c r="B22" s="26" t="n">
-        <v>2.52</v>
+        <v>0.6</v>
       </c>
       <c r="C22" s="26" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="D22" s="27">
         <f>IF(COUNT(B22,C22)&lt;2,"",B22*C22)</f>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="E22" s="31" t="n"/>
       <c r="F22" s="29">
-        <f>IF(OR(D22="",$E$20=""),"",D22/$E$20)</f>
+        <f>IF(OR(D22="",$E$21=""),"",D22/$E$21)</f>
         <v/>
       </c>
       <c r="G22" s="27">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="I22" s="25" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J22" s="26" t="n">
@@ -8785,14 +8785,14 @@
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>PV04</t>
+          <t>VA01 (2)</t>
         </is>
       </c>
       <c r="B23" s="26" t="n">
         <v>3</v>
       </c>
       <c r="C23" s="26" t="n">
-        <v>2.06</v>
+        <v>0.75</v>
       </c>
       <c r="D23" s="27">
         <f>IF(COUNT(B23,C23)&lt;2,"",B23*C23)</f>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="E23" s="31" t="n"/>
       <c r="F23" s="29">
-        <f>IF(OR(D23="",$E$20=""),"",D23/$E$20)</f>
+        <f>IF(OR(D23="",$E$21=""),"",D23/$E$21)</f>
         <v/>
       </c>
       <c r="G23" s="27">
@@ -8837,14 +8837,14 @@
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>PV04 (2)</t>
+          <t>VA05</t>
         </is>
       </c>
       <c r="B24" s="26" t="n">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="C24" s="26" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D24" s="27">
         <f>IF(COUNT(B24,C24)&lt;2,"",B24*C24)</f>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="E24" s="31" t="n"/>
       <c r="F24" s="29">
-        <f>IF(OR(D24="",$E$20=""),"",D24/$E$20)</f>
+        <f>IF(OR(D24="",$E$21=""),"",D24/$E$21)</f>
         <v/>
       </c>
       <c r="G24" s="27">
@@ -8889,14 +8889,14 @@
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>PF02</t>
+          <t>PV04</t>
         </is>
       </c>
       <c r="B25" s="26" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="26" t="n">
-        <v>3.75</v>
+        <v>2.06</v>
       </c>
       <c r="D25" s="27">
         <f>IF(COUNT(B25,C25)&lt;2,"",B25*C25)</f>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="E25" s="31" t="n"/>
       <c r="F25" s="29">
-        <f>IF(OR(D25="",$E$20=""),"",D25/$E$20)</f>
+        <f>IF(OR(D25="",$E$21=""),"",D25/$E$21)</f>
         <v/>
       </c>
       <c r="G25" s="27">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="I25" s="25" t="inlineStr">
         <is>
-          <t>Sin Proteccion</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="J25" s="26" t="n">
@@ -8939,26 +8939,48 @@
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="25" t="n"/>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="26" t="n"/>
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>PV04 (2)</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>1.5</v>
+      </c>
       <c r="D26" s="27">
         <f>IF(COUNT(B26,C26)&lt;2,"",B26*C26)</f>
         <v/>
       </c>
       <c r="E26" s="31" t="n"/>
       <c r="F26" s="29">
-        <f>IF(OR(D26="",$E$20=""),"",D26/$E$20)</f>
+        <f>IF(OR(D26="",$E$21=""),"",D26/$E$21)</f>
         <v/>
       </c>
       <c r="G26" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
-      <c r="J26" s="26" t="n"/>
-      <c r="K26" s="25" t="n"/>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K26" s="25" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
       <c r="L26" s="26">
         <f>IF(I26="","",IFERROR(VLOOKUP(I26,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
@@ -8969,180 +8991,158 @@
       </c>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="32" t="n"/>
-      <c r="B27" s="33" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="34">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>PF02</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D27" s="27">
         <f>IF(COUNT(B27,C27)&lt;2,"",B27*C27)</f>
         <v/>
       </c>
-      <c r="E27" s="35" t="n"/>
-      <c r="F27" s="36">
-        <f>IF(OR(D27="",$E$20=""),"",D27/$E$20)</f>
-        <v/>
-      </c>
-      <c r="G27" s="34">
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="29">
+        <f>IF(OR(D27="",$E$21=""),"",D27/$E$21)</f>
+        <v/>
+      </c>
+      <c r="G27" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="33" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="33">
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I27" s="25" t="inlineStr">
+        <is>
+          <t>Sin Proteccion</t>
+        </is>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K27" s="25" t="inlineStr">
+        <is>
+          <t>Sudeste</t>
+        </is>
+      </c>
+      <c r="L27" s="26">
         <f>IF(I27="","",IFERROR(VLOOKUP(I27,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="30">
         <f>IF(OR(D27="",J27=""),"",IF(J27&lt;=G27,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="27">
+        <f>IF(COUNT(B28,C28)&lt;2,"",B28*C28)</f>
+        <v/>
+      </c>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="29">
+        <f>IF(OR(D28="",$E$21=""),"",D28/$E$21)</f>
+        <v/>
+      </c>
+      <c r="G28" s="27">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="26" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="26">
+        <f>IF(I28="","",IFERROR(VLOOKUP(I28,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M28" s="30">
+        <f>IF(OR(D28="",J28=""),"",IF(J28&lt;=G28,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="32" t="n"/>
+      <c r="B29" s="33" t="n"/>
+      <c r="C29" s="33" t="n"/>
+      <c r="D29" s="34">
+        <f>IF(COUNT(B29,C29)&lt;2,"",B29*C29)</f>
+        <v/>
+      </c>
+      <c r="E29" s="35" t="n"/>
+      <c r="F29" s="36">
+        <f>IF(OR(D29="",$E$21=""),"",D29/$E$21)</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H29" s="32" t="n"/>
+      <c r="I29" s="32" t="n"/>
+      <c r="J29" s="33" t="n"/>
+      <c r="K29" s="32" t="n"/>
+      <c r="L29" s="33">
+        <f>IF(I29="","",IFERROR(VLOOKUP(I29,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M29" s="37">
+        <f>IF(OR(D29="",J29=""),"",IF(J29&lt;=G29,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>Plano: Fachada Noroeste (borde superior)</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>PV03</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="D29" s="27">
-        <f>IF(COUNT(B29,C29)&lt;2,"",B29*C29)</f>
-        <v/>
-      </c>
-      <c r="E29" s="28">
-        <f>SUM(D29:D35)</f>
-        <v/>
-      </c>
-      <c r="F29" s="29">
-        <f>IF(OR(D29="",$E$29=""),"",D29/$E$29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H29" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I29" s="25" t="inlineStr">
-        <is>
-          <t>Cortina de enrollar exterior</t>
-        </is>
-      </c>
-      <c r="J29" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K29" s="25" t="inlineStr">
-        <is>
-          <t>Noroeste</t>
-        </is>
-      </c>
-      <c r="L29" s="26">
-        <f>IF(I29="","",IFERROR(VLOOKUP(I29,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M29" s="30">
-        <f>IF(OR(D29="",J29=""),"",IF(J29&lt;=G29,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>VA02</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C30" s="26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D30" s="27">
-        <f>IF(COUNT(B30,C30)&lt;2,"",B30*C30)</f>
-        <v/>
-      </c>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="29">
-        <f>IF(OR(D30="",$E$29=""),"",D30/$E$29)</f>
-        <v/>
-      </c>
-      <c r="G30" s="27">
-        <f>Datos_higro!$B$4</f>
-        <v/>
-      </c>
-      <c r="H30" s="25" t="inlineStr">
-        <is>
-          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
-        </is>
-      </c>
-      <c r="I30" s="25" t="inlineStr">
-        <is>
-          <t>Cortina de enrollar exterior</t>
-        </is>
-      </c>
-      <c r="J30" s="26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K30" s="25" t="inlineStr">
-        <is>
-          <t>Noroeste</t>
-        </is>
-      </c>
-      <c r="L30" s="26">
-        <f>IF(I30="","",IFERROR(VLOOKUP(I30,Datos_higro!$A$21:$B$27,2,0),""))</f>
-        <v/>
-      </c>
-      <c r="M30" s="30">
-        <f>IF(OR(D30="",J30=""),"",IF(J30&lt;=G30,"CUMPLE","NO CUMPLE"))</f>
-        <v/>
-      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>PA02</t>
+          <t>PV03</t>
         </is>
       </c>
       <c r="B31" s="26" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="26" t="n">
-        <v>0.75</v>
+        <v>1.76</v>
       </c>
       <c r="D31" s="27">
         <f>IF(COUNT(B31,C31)&lt;2,"",B31*C31)</f>
         <v/>
       </c>
-      <c r="E31" s="31" t="n"/>
+      <c r="E31" s="28">
+        <f>SUM(D31:D37)</f>
+        <v/>
+      </c>
       <c r="F31" s="29">
-        <f>IF(OR(D31="",$E$29=""),"",D31/$E$29)</f>
+        <f>IF(OR(D31="",$E$31=""),"",D31/$E$31)</f>
         <v/>
       </c>
       <c r="G31" s="27">
@@ -9179,11 +9179,11 @@
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>VA03</t>
+          <t>VA02</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="C32" s="26" t="n">
         <v>0.75</v>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="E32" s="31" t="n"/>
       <c r="F32" s="29">
-        <f>IF(OR(D32="",$E$29=""),"",D32/$E$29)</f>
+        <f>IF(OR(D32="",$E$31=""),"",D32/$E$31)</f>
         <v/>
       </c>
       <c r="G32" s="27">
@@ -9231,11 +9231,11 @@
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>PF05</t>
+          <t>PA02</t>
         </is>
       </c>
       <c r="B33" s="26" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="C33" s="26" t="n">
         <v>0.75</v>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="E33" s="31" t="n"/>
       <c r="F33" s="29">
-        <f>IF(OR(D33="",$E$29=""),"",D33/$E$29)</f>
+        <f>IF(OR(D33="",$E$31=""),"",D33/$E$31)</f>
         <v/>
       </c>
       <c r="G33" s="27">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="I33" s="25" t="inlineStr">
         <is>
-          <t>Sin Proteccion</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="J33" s="26" t="n">
@@ -9281,26 +9281,48 @@
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="26" t="n"/>
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>VA03</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>0.75</v>
+      </c>
       <c r="D34" s="27">
         <f>IF(COUNT(B34,C34)&lt;2,"",B34*C34)</f>
         <v/>
       </c>
       <c r="E34" s="31" t="n"/>
       <c r="F34" s="29">
-        <f>IF(OR(D34="",$E$29=""),"",D34/$E$29)</f>
+        <f>IF(OR(D34="",$E$31=""),"",D34/$E$31)</f>
         <v/>
       </c>
       <c r="G34" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="25" t="n"/>
+      <c r="H34" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I34" s="25" t="inlineStr">
+        <is>
+          <t>Cortina de enrollar exterior</t>
+        </is>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K34" s="25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
       <c r="L34" s="26">
         <f>IF(I34="","",IFERROR(VLOOKUP(I34,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
@@ -9311,75 +9333,119 @@
       </c>
     </row>
     <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="32" t="n"/>
-      <c r="B35" s="33" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="34">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>PF05</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D35" s="27">
         <f>IF(COUNT(B35,C35)&lt;2,"",B35*C35)</f>
         <v/>
       </c>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="36">
-        <f>IF(OR(D35="",$E$29=""),"",D35/$E$29)</f>
-        <v/>
-      </c>
-      <c r="G35" s="34">
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="29">
+        <f>IF(OR(D35="",$E$31=""),"",D35/$E$31)</f>
+        <v/>
+      </c>
+      <c r="G35" s="27">
         <f>Datos_higro!$B$4</f>
         <v/>
       </c>
-      <c r="H35" s="32" t="n"/>
-      <c r="I35" s="32" t="n"/>
-      <c r="J35" s="33" t="n"/>
-      <c r="K35" s="32" t="n"/>
-      <c r="L35" s="33">
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>DVH 6+9+3+3 (aluminio linea A30)</t>
+        </is>
+      </c>
+      <c r="I35" s="25" t="inlineStr">
+        <is>
+          <t>Sin Proteccion</t>
+        </is>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="L35" s="26">
         <f>IF(I35="","",IFERROR(VLOOKUP(I35,Datos_higro!$A$21:$B$27,2,0),""))</f>
         <v/>
       </c>
-      <c r="M35" s="37">
+      <c r="M35" s="30">
         <f>IF(OR(D35="",J35=""),"",IF(J35&lt;=G35,"CUMPLE","NO CUMPLE"))</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="38" t="inlineStr">
-        <is>
-          <t>COMO SE COMPLETA</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="27">
+        <f>IF(COUNT(B36,C36)&lt;2,"",B36*C36)</f>
+        <v/>
+      </c>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="29">
+        <f>IF(OR(D36="",$E$31=""),"",D36/$E$31)</f>
+        <v/>
+      </c>
+      <c r="G36" s="27">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="26" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="26">
+        <f>IF(I36="","",IFERROR(VLOOKUP(I36,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M36" s="30">
+        <f>IF(OR(D36="",J36=""),"",IF(J36&lt;=G36,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="32" t="n"/>
+      <c r="B37" s="33" t="n"/>
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="34">
+        <f>IF(COUNT(B37,C37)&lt;2,"",B37*C37)</f>
+        <v/>
+      </c>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="36">
+        <f>IF(OR(D37="",$E$31=""),"",D37/$E$31)</f>
+        <v/>
+      </c>
+      <c r="G37" s="34">
+        <f>Datos_higro!$B$4</f>
+        <v/>
+      </c>
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="32" t="n"/>
+      <c r="J37" s="33" t="n"/>
+      <c r="K37" s="32" t="n"/>
+      <c r="L37" s="33">
+        <f>IF(I37="","",IFERROR(VLOOKUP(I37,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <v/>
+      </c>
+      <c r="M37" s="37">
+        <f>IF(OR(D37="",J37=""),"",IF(J37&lt;=G37,"CUMPLE","NO CUMPLE"))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
-        <is>
-          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
       <c r="B38" s="2" t="n"/>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n"/>
@@ -9394,9 +9460,9 @@
       <c r="M38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
-        <is>
-          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
+      <c r="A39" s="38" t="inlineStr">
+        <is>
+          <t>COMO SE COMPLETA</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -9415,7 +9481,7 @@
     <row r="40">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
+          <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
@@ -9434,7 +9500,7 @@
     <row r="41">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
+          <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
         </is>
       </c>
       <c r="B41" s="2" t="n"/>
@@ -9453,7 +9519,7 @@
     <row r="42">
       <c r="A42" s="39" t="inlineStr">
         <is>
-          <t>PROTECCION: ningun pano fijo PF tiene cortina: PF01, su gemelo, PF02, PF03, PF04 y PF05 van</t>
+          <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>
@@ -9472,7 +9538,7 @@
     <row r="43">
       <c r="A43" s="39" t="inlineStr">
         <is>
-          <t>Sin Proteccion (FES 0,88). Las otras doce llevan cortina de enrollar exterior (FES 0,25).</t>
+          <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
         </is>
       </c>
       <c r="B43" s="2" t="n"/>
@@ -9489,7 +9555,11 @@
       <c r="M43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="39" t="inlineStr"/>
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>PROTECCION: ningun pano fijo PF tiene cortina: PF01, su gemelo, PF02, PF03, PF04 y PF05 van</t>
+        </is>
+      </c>
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
@@ -9506,7 +9576,7 @@
     <row r="45">
       <c r="A45" s="39" t="inlineStr">
         <is>
-          <t>OJO con esas seis: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
+          <t>Sin Proteccion (FES 0,88). Las otras doce llevan cortina de enrollar exterior (FES 0,25).</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9523,11 +9593,7 @@
       <c r="M45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="39" t="inlineStr">
-        <is>
-          <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
-        </is>
-      </c>
+      <c r="A46" s="39" t="inlineStr"/>
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -9544,7 +9610,7 @@
     <row r="47">
       <c r="A47" s="39" t="inlineStr">
         <is>
-          <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
+          <t>OJO con esas seis: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -9563,7 +9629,7 @@
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
+          <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
@@ -9582,7 +9648,7 @@
     <row r="49">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>Hay una salida: si la abertura ocupa menos del 20% del lado expuesto del local, no se verifica</t>
+          <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -9601,7 +9667,7 @@
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>el FES. Conviene chequearlo local por local.</t>
+          <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9618,7 +9684,11 @@
       <c r="M50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="39" t="inlineStr"/>
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>Hay una salida: si la abertura ocupa menos del 20% del lado expuesto del local, no se verifica</t>
+        </is>
+      </c>
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n"/>
@@ -9635,7 +9705,7 @@
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
+          <t>el FES. Conviene chequearlo local por local.</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9652,11 +9722,7 @@
       <c r="M52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="39" t="inlineStr">
-        <is>
-          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
-        </is>
-      </c>
+      <c r="A53" s="39" t="inlineStr"/>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n"/>
@@ -9673,7 +9739,7 @@
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
+          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
         </is>
       </c>
       <c r="B54" s="2" t="n"/>
@@ -9692,7 +9758,7 @@
     <row r="55">
       <c r="A55" s="39" t="inlineStr">
         <is>
-          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
+          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9711,7 +9777,7 @@
     <row r="56">
       <c r="A56" s="39" t="inlineStr">
         <is>
-          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
+          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B56" s="2" t="n"/>
@@ -9728,7 +9794,11 @@
       <c r="M56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="39" t="inlineStr"/>
+      <c r="A57" s="39" t="inlineStr">
+        <is>
+          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
+        </is>
+      </c>
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n"/>
@@ -9745,7 +9815,7 @@
     <row r="58">
       <c r="A58" s="39" t="inlineStr">
         <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9762,11 +9832,7 @@
       <c r="M58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="39" t="inlineStr">
-        <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
-        </is>
-      </c>
+      <c r="A59" s="39" t="inlineStr"/>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n"/>
@@ -9781,7 +9847,11 @@
       <c r="M59" s="2" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="39" t="inlineStr"/>
+      <c r="A60" s="39" t="inlineStr">
+        <is>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+        </is>
+      </c>
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n"/>
@@ -9798,7 +9868,7 @@
     <row r="61">
       <c r="A61" s="39" t="inlineStr">
         <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
@@ -9815,11 +9885,7 @@
       <c r="M61" s="2" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="39" t="inlineStr">
-        <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
-        </is>
-      </c>
+      <c r="A62" s="39" t="inlineStr"/>
       <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n"/>
@@ -9836,7 +9902,7 @@
     <row r="63">
       <c r="A63" s="39" t="inlineStr">
         <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
@@ -9855,7 +9921,7 @@
     <row r="64">
       <c r="A64" s="39" t="inlineStr">
         <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9874,7 +9940,7 @@
     <row r="65">
       <c r="A65" s="39" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -9891,7 +9957,11 @@
       <c r="M65" s="2" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="39" t="inlineStr"/>
+      <c r="A66" s="39" t="inlineStr">
+        <is>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+        </is>
+      </c>
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n"/>
@@ -9908,7 +9978,7 @@
     <row r="67">
       <c r="A67" s="39" t="inlineStr">
         <is>
-          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
         </is>
       </c>
       <c r="B67" s="2" t="n"/>
@@ -9925,11 +9995,7 @@
       <c r="M67" s="2" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="39" t="inlineStr">
-        <is>
-          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
-        </is>
-      </c>
+      <c r="A68" s="39" t="inlineStr"/>
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n"/>
@@ -9946,7 +10012,7 @@
     <row r="69">
       <c r="A69" s="39" t="inlineStr">
         <is>
-          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
         </is>
       </c>
       <c r="B69" s="2" t="n"/>
@@ -9965,7 +10031,7 @@
     <row r="70">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B70" s="2" t="n"/>
@@ -9984,7 +10050,7 @@
     <row r="71">
       <c r="A71" s="39" t="inlineStr">
         <is>
-          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
         </is>
       </c>
       <c r="B71" s="2" t="n"/>
@@ -10003,7 +10069,7 @@
     <row r="72">
       <c r="A72" s="39" t="inlineStr">
         <is>
-          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
         </is>
       </c>
       <c r="B72" s="2" t="n"/>
@@ -10022,7 +10088,7 @@
     <row r="73">
       <c r="A73" s="39" t="inlineStr">
         <is>
-          <t>parecen ser nombres de uso, no orientaciones.</t>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
         </is>
       </c>
       <c r="B73" s="2" t="n"/>
@@ -10039,7 +10105,11 @@
       <c r="M73" s="2" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="39" t="inlineStr"/>
+      <c r="A74" s="39" t="inlineStr">
+        <is>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+        </is>
+      </c>
       <c r="B74" s="2" t="n"/>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n"/>
@@ -10056,7 +10126,7 @@
     <row r="75">
       <c r="A75" s="39" t="inlineStr">
         <is>
-          <t>PF01 figura dos veces en el plano, en las dos paredes laterales del patio interno, y por eso</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B75" s="2" t="n"/>
@@ -10073,11 +10143,7 @@
       <c r="M75" s="2" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="39" t="inlineStr">
-        <is>
-          <t>se cargan dos filas. Si fuera una sola abertura rotulada dos veces, borrar la segunda.</t>
-        </is>
-      </c>
+      <c r="A76" s="39" t="inlineStr"/>
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n"/>
@@ -10092,7 +10158,11 @@
       <c r="M76" s="2" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="39" t="inlineStr"/>
+      <c r="A77" s="39" t="inlineStr">
+        <is>
+          <t>CANTIDADES: la planilla de carpinterias trae la cantidad de cada abertura. Tres van dos veces:</t>
+        </is>
+      </c>
       <c r="B77" s="2" t="n"/>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n"/>
@@ -10109,7 +10179,7 @@
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>VA01 (01 Cocina y 09 Suite), VA04 (13 Dormitorio Norte y 14 Play Room) y PF01 (03 Lavadero y</t>
         </is>
       </c>
       <c r="B78" s="2" t="n"/>
@@ -10126,7 +10196,11 @@
       <c r="M78" s="2" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="39" t="inlineStr"/>
+      <c r="A79" s="39" t="inlineStr">
+        <is>
+          <t>07 Hall de ingreso, a los dos lados del patio interno). Por eso la planilla tiene 20 filas y</t>
+        </is>
+      </c>
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n"/>
@@ -10143,7 +10217,7 @@
     <row r="80">
       <c r="A80" s="39" t="inlineStr">
         <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+          <t>no 17. Las demas aberturas son de una sola unidad.</t>
         </is>
       </c>
       <c r="B80" s="2" t="n"/>
@@ -10160,11 +10234,7 @@
       <c r="M80" s="2" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="39" t="inlineStr">
-        <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
-        </is>
-      </c>
+      <c r="A81" s="39" t="inlineStr"/>
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n"/>
@@ -10181,7 +10251,7 @@
     <row r="82">
       <c r="A82" s="39" t="inlineStr">
         <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
         </is>
       </c>
       <c r="B82" s="2" t="n"/>
@@ -10197,22 +10267,94 @@
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
     </row>
+    <row r="83">
+      <c r="A83" s="39" t="inlineStr"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="n"/>
+      <c r="M83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="39" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="39" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" s="2" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A14:M14"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="E7:E14"/>
     <mergeCell ref="A6:M6"/>
-    <mergeCell ref="E20:E27"/>
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="E29:E35"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="E7:E13"/>
-    <mergeCell ref="E15:E18"/>
+    <mergeCell ref="E21:E29"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="A20:M20"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A28:M28"/>
   </mergeCells>
-  <conditionalFormatting sqref="M6:M35">
+  <conditionalFormatting sqref="M6:M37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"CUMPLE"</formula>
     </cfRule>
@@ -10221,13 +10363,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H6:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H6:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$10:$A$17</formula1>
     </dataValidation>
-    <dataValidation sqref="I6:I35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6:I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Datos_higro!$A$21:$A$27</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Norte,Sur,Este,Oeste,Noreste,Noroeste,Sudeste,Sudoeste,Horizontal"</formula1>
     </dataValidation>
   </dataValidations>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -5018,11 +5018,11 @@
     <row r="22">
       <c r="A22" s="34" t="inlineStr">
         <is>
-          <t>Parasol horizontal fijo 1:2</t>
+          <t>Cortina blackout INTERIOR (no computa)</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.35</v>
+        <v>0.88</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
@@ -5030,11 +5030,11 @@
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
         <is>
-          <t>Parasol horizontal fijo 1:1</t>
+          <t>Parasol horizontal fijo 1:2</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
@@ -5042,11 +5042,11 @@
     <row r="24">
       <c r="A24" s="34" t="inlineStr">
         <is>
-          <t>Alero</t>
+          <t>Parasol horizontal fijo 1:1</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
@@ -5054,11 +5054,11 @@
     <row r="25">
       <c r="A25" s="34" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Alero</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
@@ -5066,11 +5066,11 @@
     <row r="26">
       <c r="A26" s="34" t="inlineStr">
         <is>
-          <t>Persiana de madera</t>
+          <t>Cortina de enrollar exterior</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
@@ -5078,18 +5078,24 @@
     <row r="27">
       <c r="A27" s="34" t="inlineStr">
         <is>
-          <t>Toldo</t>
+          <t>Persiana de madera</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>Toldo</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>0.2</v>
+      </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
     </row>
@@ -7779,7 +7785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.4" customWidth="1" min="1" max="1"/>
@@ -7998,7 +8004,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J7" s="8" t="n">
@@ -8010,7 +8016,7 @@
         </is>
       </c>
       <c r="L7" s="8">
-        <f>IF(I7="","",IFERROR(VLOOKUP(I7,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I7="","",IFERROR(VLOOKUP(I7,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M7" s="9">
@@ -8062,7 +8068,7 @@
         </is>
       </c>
       <c r="L8" s="8">
-        <f>IF(I8="","",IFERROR(VLOOKUP(I8,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I8="","",IFERROR(VLOOKUP(I8,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M8" s="9">
@@ -8102,7 +8108,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J9" s="8" t="n">
@@ -8114,7 +8120,7 @@
         </is>
       </c>
       <c r="L9" s="8">
-        <f>IF(I9="","",IFERROR(VLOOKUP(I9,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I9="","",IFERROR(VLOOKUP(I9,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M9" s="9">
@@ -8154,7 +8160,7 @@
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J10" s="8" t="n">
@@ -8166,7 +8172,7 @@
         </is>
       </c>
       <c r="L10" s="8">
-        <f>IF(I10="","",IFERROR(VLOOKUP(I10,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I10="","",IFERROR(VLOOKUP(I10,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M10" s="9">
@@ -8206,7 +8212,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J11" s="8" t="n">
@@ -8218,7 +8224,7 @@
         </is>
       </c>
       <c r="L11" s="8">
-        <f>IF(I11="","",IFERROR(VLOOKUP(I11,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I11="","",IFERROR(VLOOKUP(I11,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M11" s="9">
@@ -8270,7 +8276,7 @@
         </is>
       </c>
       <c r="L12" s="8">
-        <f>IF(I12="","",IFERROR(VLOOKUP(I12,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I12="","",IFERROR(VLOOKUP(I12,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M12" s="9">
@@ -8300,7 +8306,7 @@
       <c r="J13" s="8" t="n"/>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="8">
-        <f>IF(I13="","",IFERROR(VLOOKUP(I13,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I13="","",IFERROR(VLOOKUP(I13,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M13" s="9">
@@ -8330,7 +8336,7 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="13" t="n"/>
       <c r="L14" s="12">
-        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I14="","",IFERROR(VLOOKUP(I14,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M14" s="13">
@@ -8392,7 +8398,7 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J16" s="8" t="n">
@@ -8404,7 +8410,7 @@
         </is>
       </c>
       <c r="L16" s="8">
-        <f>IF(I16="","",IFERROR(VLOOKUP(I16,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I16="","",IFERROR(VLOOKUP(I16,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M16" s="9">
@@ -8456,7 +8462,7 @@
         </is>
       </c>
       <c r="L17" s="8">
-        <f>IF(I17="","",IFERROR(VLOOKUP(I17,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I17="","",IFERROR(VLOOKUP(I17,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M17" s="9">
@@ -8486,7 +8492,7 @@
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="9" t="n"/>
       <c r="L18" s="8">
-        <f>IF(I18="","",IFERROR(VLOOKUP(I18,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I18="","",IFERROR(VLOOKUP(I18,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M18" s="9">
@@ -8516,7 +8522,7 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="13" t="n"/>
       <c r="L19" s="12">
-        <f>IF(I19="","",IFERROR(VLOOKUP(I19,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I19="","",IFERROR(VLOOKUP(I19,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M19" s="13">
@@ -8578,7 +8584,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J21" s="8" t="n">
@@ -8590,7 +8596,7 @@
         </is>
       </c>
       <c r="L21" s="8">
-        <f>IF(I21="","",IFERROR(VLOOKUP(I21,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I21="","",IFERROR(VLOOKUP(I21,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M21" s="9">
@@ -8642,7 +8648,7 @@
         </is>
       </c>
       <c r="L22" s="8">
-        <f>IF(I22="","",IFERROR(VLOOKUP(I22,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I22="","",IFERROR(VLOOKUP(I22,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M22" s="9">
@@ -8682,7 +8688,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J23" s="8" t="n">
@@ -8694,7 +8700,7 @@
         </is>
       </c>
       <c r="L23" s="8">
-        <f>IF(I23="","",IFERROR(VLOOKUP(I23,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I23="","",IFERROR(VLOOKUP(I23,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M23" s="9">
@@ -8734,7 +8740,7 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J24" s="8" t="n">
@@ -8746,7 +8752,7 @@
         </is>
       </c>
       <c r="L24" s="8">
-        <f>IF(I24="","",IFERROR(VLOOKUP(I24,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I24="","",IFERROR(VLOOKUP(I24,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M24" s="9">
@@ -8786,7 +8792,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J25" s="8" t="n">
@@ -8798,7 +8804,7 @@
         </is>
       </c>
       <c r="L25" s="8">
-        <f>IF(I25="","",IFERROR(VLOOKUP(I25,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I25="","",IFERROR(VLOOKUP(I25,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M25" s="9">
@@ -8838,7 +8844,7 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J26" s="8" t="n">
@@ -8850,7 +8856,7 @@
         </is>
       </c>
       <c r="L26" s="8">
-        <f>IF(I26="","",IFERROR(VLOOKUP(I26,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I26="","",IFERROR(VLOOKUP(I26,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M26" s="9">
@@ -8902,7 +8908,7 @@
         </is>
       </c>
       <c r="L27" s="8">
-        <f>IF(I27="","",IFERROR(VLOOKUP(I27,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I27="","",IFERROR(VLOOKUP(I27,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M27" s="9">
@@ -8932,7 +8938,7 @@
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="9" t="n"/>
       <c r="L28" s="8">
-        <f>IF(I28="","",IFERROR(VLOOKUP(I28,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I28="","",IFERROR(VLOOKUP(I28,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M28" s="9">
@@ -8962,7 +8968,7 @@
       <c r="J29" s="12" t="n"/>
       <c r="K29" s="13" t="n"/>
       <c r="L29" s="12">
-        <f>IF(I29="","",IFERROR(VLOOKUP(I29,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I29="","",IFERROR(VLOOKUP(I29,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M29" s="13">
@@ -9024,7 +9030,7 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J31" s="8" t="n">
@@ -9036,7 +9042,7 @@
         </is>
       </c>
       <c r="L31" s="8">
-        <f>IF(I31="","",IFERROR(VLOOKUP(I31,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I31="","",IFERROR(VLOOKUP(I31,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M31" s="9">
@@ -9076,7 +9082,7 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
@@ -9088,7 +9094,7 @@
         </is>
       </c>
       <c r="L32" s="8">
-        <f>IF(I32="","",IFERROR(VLOOKUP(I32,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I32="","",IFERROR(VLOOKUP(I32,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M32" s="9">
@@ -9128,7 +9134,7 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J33" s="8" t="n">
@@ -9140,7 +9146,7 @@
         </is>
       </c>
       <c r="L33" s="8">
-        <f>IF(I33="","",IFERROR(VLOOKUP(I33,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I33="","",IFERROR(VLOOKUP(I33,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M33" s="9">
@@ -9180,7 +9186,7 @@
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>Cortina de enrollar exterior</t>
+          <t>Sin Proteccion</t>
         </is>
       </c>
       <c r="J34" s="8" t="n">
@@ -9192,7 +9198,7 @@
         </is>
       </c>
       <c r="L34" s="8">
-        <f>IF(I34="","",IFERROR(VLOOKUP(I34,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I34="","",IFERROR(VLOOKUP(I34,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M34" s="9">
@@ -9244,7 +9250,7 @@
         </is>
       </c>
       <c r="L35" s="8">
-        <f>IF(I35="","",IFERROR(VLOOKUP(I35,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I35="","",IFERROR(VLOOKUP(I35,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M35" s="9">
@@ -9274,7 +9280,7 @@
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="8">
-        <f>IF(I36="","",IFERROR(VLOOKUP(I36,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I36="","",IFERROR(VLOOKUP(I36,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M36" s="9">
@@ -9304,7 +9310,7 @@
       <c r="J37" s="12" t="n"/>
       <c r="K37" s="13" t="n"/>
       <c r="L37" s="12">
-        <f>IF(I37="","",IFERROR(VLOOKUP(I37,Datos_higro!$A$21:$B$27,2,0),""))</f>
+        <f>IF(I37="","",IFERROR(VLOOKUP(I37,Datos_higro!$A$21:$B$28,2,0),""))</f>
         <v/>
       </c>
       <c r="M37" s="13">
@@ -9425,7 +9431,7 @@
     <row r="44">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t>PROTECCION: ningun pano fijo PF tiene cortina: PF01, su gemelo, PF02, PF03, PF04 y PF05 van</t>
+          <t>PROTECCION: la obra tiene cortinas blackout INTERIORES, y los panos fijos PF no tienen nada.</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
@@ -9444,7 +9450,7 @@
     <row r="45">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>Sin Proteccion (FES 0,88). Las otras doce llevan cortina de enrollar exterior (FES 0,25).</t>
+          <t>Una cortina interior NO computa como proteccion solar: la radiacion ya atraveso el vidrio</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -9461,7 +9467,11 @@
       <c r="M45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="inlineStr"/>
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>cuando llega a la cortina. La ordenanza acredita protecciones exteriores (aleros, parasoles,</t>
+        </is>
+      </c>
       <c r="B46" s="2" t="n"/>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -9478,7 +9488,7 @@
     <row r="47">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>OJO con esas seis: 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
+          <t>cortinas de enrollar exteriores, toldos). Por eso las veinte aberturas van Sin Proteccion.</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -9495,11 +9505,7 @@
       <c r="M47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
-        </is>
-      </c>
+      <c r="A48" s="23" t="inlineStr"/>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n"/>
@@ -9516,7 +9522,7 @@
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
+          <t>CONSECUENCIA: el factor de exposicion solar da 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
         </is>
       </c>
       <c r="B49" s="2" t="n"/>
@@ -9535,7 +9541,7 @@
     <row r="50">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
+          <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
@@ -9554,7 +9560,7 @@
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>Hay una salida: si la abertura ocupa menos del 20% del lado expuesto del local, no se verifica</t>
+          <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
         </is>
       </c>
       <c r="B51" s="2" t="n"/>
@@ -9573,7 +9579,7 @@
     <row r="52">
       <c r="A52" s="23" t="inlineStr">
         <is>
-          <t>el FES. Conviene chequearlo local por local.</t>
+          <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -9590,7 +9596,11 @@
       <c r="M52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="23" t="inlineStr"/>
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>Hay dos salidas posibles: (a) si la abertura ocupa menos del 20% del lado expuesto del local,</t>
+        </is>
+      </c>
       <c r="B53" s="2" t="n"/>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n"/>
@@ -9607,7 +9617,7 @@
     <row r="54">
       <c r="A54" s="23" t="inlineStr">
         <is>
-          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
+          <t>no se verifica el FES; (b) cambiar el vidrio por uno de control solar, que baja el FES sin</t>
         </is>
       </c>
       <c r="B54" s="2" t="n"/>
@@ -9626,7 +9636,7 @@
     <row r="55">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
+          <t>tocar la obra. Agregar una proteccion exterior seria la tercera, pero implica obra.</t>
         </is>
       </c>
       <c r="B55" s="2" t="n"/>
@@ -9643,11 +9653,7 @@
       <c r="M55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
-        <is>
-          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
-        </is>
-      </c>
+      <c r="A56" s="23" t="inlineStr"/>
       <c r="B56" s="2" t="n"/>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
@@ -9664,7 +9670,7 @@
     <row r="57">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
+          <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
         </is>
       </c>
       <c r="B57" s="2" t="n"/>
@@ -9683,7 +9689,7 @@
     <row r="58">
       <c r="A58" s="23" t="inlineStr">
         <is>
-          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
+          <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
         </is>
       </c>
       <c r="B58" s="2" t="n"/>
@@ -9700,7 +9706,11 @@
       <c r="M58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="23" t="inlineStr"/>
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
+        </is>
+      </c>
       <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n"/>
@@ -9717,7 +9727,7 @@
     <row r="60">
       <c r="A60" s="23" t="inlineStr">
         <is>
-          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
+          <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
         </is>
       </c>
       <c r="B60" s="2" t="n"/>
@@ -9736,7 +9746,7 @@
     <row r="61">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
+          <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
         </is>
       </c>
       <c r="B61" s="2" t="n"/>
@@ -9770,7 +9780,7 @@
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
+          <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
@@ -9789,7 +9799,7 @@
     <row r="64">
       <c r="A64" s="23" t="inlineStr">
         <is>
-          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
+          <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
         </is>
       </c>
       <c r="B64" s="2" t="n"/>
@@ -9806,11 +9816,7 @@
       <c r="M64" s="2" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="23" t="inlineStr">
-        <is>
-          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
-        </is>
-      </c>
+      <c r="A65" s="23" t="inlineStr"/>
       <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n"/>
@@ -9827,7 +9833,7 @@
     <row r="66">
       <c r="A66" s="23" t="inlineStr">
         <is>
-          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
+          <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
         </is>
       </c>
       <c r="B66" s="2" t="n"/>
@@ -9846,7 +9852,7 @@
     <row r="67">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
+          <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
         </is>
       </c>
       <c r="B67" s="2" t="n"/>
@@ -9863,7 +9869,11 @@
       <c r="M67" s="2" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="23" t="inlineStr"/>
+      <c r="A68" s="23" t="inlineStr">
+        <is>
+          <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
+        </is>
+      </c>
       <c r="B68" s="2" t="n"/>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n"/>
@@ -9880,7 +9890,7 @@
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
+          <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
         </is>
       </c>
       <c r="B69" s="2" t="n"/>
@@ -9899,7 +9909,7 @@
     <row r="70">
       <c r="A70" s="23" t="inlineStr">
         <is>
-          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
+          <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
         </is>
       </c>
       <c r="B70" s="2" t="n"/>
@@ -9916,11 +9926,7 @@
       <c r="M70" s="2" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="23" t="inlineStr">
-        <is>
-          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
-        </is>
-      </c>
+      <c r="A71" s="23" t="inlineStr"/>
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n"/>
@@ -9937,7 +9943,7 @@
     <row r="72">
       <c r="A72" s="23" t="inlineStr">
         <is>
-          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
+          <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
         </is>
       </c>
       <c r="B72" s="2" t="n"/>
@@ -9956,7 +9962,7 @@
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+          <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
         </is>
       </c>
       <c r="B73" s="2" t="n"/>
@@ -9975,7 +9981,7 @@
     <row r="74">
       <c r="A74" s="23" t="inlineStr">
         <is>
-          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
+          <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
         </is>
       </c>
       <c r="B74" s="2" t="n"/>
@@ -9994,7 +10000,7 @@
     <row r="75">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>parecen ser nombres de uso, no orientaciones.</t>
+          <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
         </is>
       </c>
       <c r="B75" s="2" t="n"/>
@@ -10011,7 +10017,11 @@
       <c r="M75" s="2" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="23" t="inlineStr"/>
+      <c r="A76" s="23" t="inlineStr">
+        <is>
+          <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
+        </is>
+      </c>
       <c r="B76" s="2" t="n"/>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n"/>
@@ -10028,7 +10038,7 @@
     <row r="77">
       <c r="A77" s="23" t="inlineStr">
         <is>
-          <t>CANTIDADES: la planilla de carpinterias trae la cantidad de cada abertura. Tres van dos veces:</t>
+          <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
         </is>
       </c>
       <c r="B77" s="2" t="n"/>
@@ -10047,7 +10057,7 @@
     <row r="78">
       <c r="A78" s="23" t="inlineStr">
         <is>
-          <t>VA01 (01 Cocina y 09 Suite), VA04 (13 Dormitorio Norte y 14 Play Room) y PF01 (03 Lavadero y</t>
+          <t>parecen ser nombres de uso, no orientaciones.</t>
         </is>
       </c>
       <c r="B78" s="2" t="n"/>
@@ -10064,11 +10074,7 @@
       <c r="M78" s="2" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="23" t="inlineStr">
-        <is>
-          <t>07 Hall de ingreso, a los dos lados del patio interno). Por eso la planilla tiene 20 filas y</t>
-        </is>
-      </c>
+      <c r="A79" s="23" t="inlineStr"/>
       <c r="B79" s="2" t="n"/>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n"/>
@@ -10085,7 +10091,7 @@
     <row r="80">
       <c r="A80" s="23" t="inlineStr">
         <is>
-          <t>no 17. Las demas aberturas son de una sola unidad.</t>
+          <t>CANTIDADES: la planilla de carpinterias trae la cantidad de cada abertura. Tres van dos veces:</t>
         </is>
       </c>
       <c r="B80" s="2" t="n"/>
@@ -10102,7 +10108,11 @@
       <c r="M80" s="2" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="23" t="inlineStr"/>
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>VA01 (01 Cocina y 09 Suite), VA04 (13 Dormitorio Norte y 14 Play Room) y PF01 (03 Lavadero y</t>
+        </is>
+      </c>
       <c r="B81" s="2" t="n"/>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n"/>
@@ -10119,7 +10129,7 @@
     <row r="82">
       <c r="A82" s="23" t="inlineStr">
         <is>
-          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
+          <t>07 Hall de ingreso, a los dos lados del patio interno). Por eso la planilla tiene 20 filas y</t>
         </is>
       </c>
       <c r="B82" s="2" t="n"/>
@@ -10136,7 +10146,11 @@
       <c r="M82" s="2" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="23" t="inlineStr"/>
+      <c r="A83" s="23" t="inlineStr">
+        <is>
+          <t>no 17. Las demas aberturas son de una sola unidad.</t>
+        </is>
+      </c>
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n"/>
@@ -10151,11 +10165,7 @@
       <c r="M83" s="2" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="23" t="inlineStr">
-        <is>
-          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
-        </is>
-      </c>
+      <c r="A84" s="23" t="inlineStr"/>
       <c r="B84" s="2" t="n"/>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n"/>
@@ -10172,7 +10182,7 @@
     <row r="85">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+          <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
         </is>
       </c>
       <c r="B85" s="2" t="n"/>
@@ -10189,11 +10199,7 @@
       <c r="M85" s="2" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="23" t="inlineStr">
-        <is>
-          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
-        </is>
-      </c>
+      <c r="A86" s="23" t="inlineStr"/>
       <c r="B86" s="2" t="n"/>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n"/>
@@ -10206,6 +10212,63 @@
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr">
+        <is>
+          <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="2" t="n"/>
+      <c r="M87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="inlineStr">
+        <is>
+          <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="2" t="n"/>
+      <c r="M89" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -10237,7 +10300,7 @@
       <formula1>=Datos_higro!$A$10:$A$17</formula1>
     </dataValidation>
     <dataValidation sqref="I6:I37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Datos_higro!$A$21:$A$27</formula1>
+      <formula1>=Datos_higro!$A$21:$A$28</formula1>
     </dataValidation>
     <dataValidation sqref="K6:K37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Norte,Sur,Este,Oeste,Noreste,Noroeste,Sudeste,Sudoeste,Horizontal"</formula1>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -97,16 +97,16 @@
     <font>
       <name val="Bahnschrift Light Condensed"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Bahnschrift Light Condensed"/>
       <color theme="1"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Bahnschrift Light Condensed"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="9">
@@ -327,33 +327,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="2">
     <dxf>
       <font>
+        <name val="Bahnschrift Light Condensed"/>
         <b val="1"/>
         <color rgb="00006100"/>
-        <sz val="9"/>
+        <sz val="12"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <name val="Bahnschrift Light Condensed"/>
         <b val="1"/>
         <color rgb="009C0006"/>
-        <sz val="9"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00006100"/>
-        <sz val="8"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="009C0006"/>
-        <sz val="8"/>
+        <sz val="12"/>
       </font>
     </dxf>
   </dxfs>
@@ -2616,21 +2604,21 @@
   <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29.9" customWidth="1" min="1" max="1"/>
-    <col width="10.3" customWidth="1" min="2" max="2"/>
-    <col width="10.3" customWidth="1" min="3" max="3"/>
-    <col width="11.5" customWidth="1" min="4" max="4"/>
-    <col width="9.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="13.8" customWidth="1" min="6" max="6"/>
-    <col width="13.8" customWidth="1" min="7" max="7"/>
-    <col width="9.199999999999999" customWidth="1" min="8" max="8"/>
-    <col width="13.8" customWidth="1" min="9" max="9"/>
-    <col width="13.8" customWidth="1" min="10" max="10"/>
-    <col width="16.1" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="35.1" customWidth="1" min="1" max="1"/>
+    <col width="12.2" customWidth="1" min="2" max="2"/>
+    <col width="12.2" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="10.8" customWidth="1" min="5" max="5"/>
+    <col width="16.2" customWidth="1" min="6" max="6"/>
+    <col width="16.2" customWidth="1" min="7" max="7"/>
+    <col width="10.8" customWidth="1" min="8" max="8"/>
+    <col width="16.2" customWidth="1" min="9" max="9"/>
+    <col width="16.2" customWidth="1" min="10" max="10"/>
+    <col width="18.9" customWidth="1" min="11" max="11"/>
+    <col width="54" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PLANILLA DE ILUMINACION Y VENTILACION</t>
@@ -2648,7 +2636,7 @@
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
     </row>
-    <row r="2" ht="29.5" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Local</t>
@@ -2697,7 +2685,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.5" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
@@ -2735,7 +2723,7 @@
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>PB</t>
@@ -2753,7 +2741,7 @@
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>01 - Cocina / comedor</t>
@@ -2797,7 +2785,7 @@
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
-    <row r="6" ht="39.5" customHeight="1">
+    <row r="6" ht="47" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>02 - Deposito</t>
@@ -2854,7 +2842,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>03 - Lavadero</t>
@@ -2898,7 +2886,7 @@
       </c>
       <c r="L7" s="9" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>06 - Living / comedor</t>
@@ -2942,7 +2930,7 @@
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>07 - Hall / ingreso</t>
@@ -2990,7 +2978,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>09 - Dormitorio suite</t>
@@ -3034,7 +3022,7 @@
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>10 - Bano suite</t>
@@ -3086,7 +3074,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>11 - Bano visita</t>
@@ -3138,7 +3126,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>12 - Bano exterior</t>
@@ -3190,7 +3178,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t>PA</t>
@@ -3208,7 +3196,7 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>13 - Dormitorio 1</t>
@@ -3252,7 +3240,7 @@
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>14 - Estar / Playroom</t>
@@ -3300,7 +3288,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>15 - Dormitorio 2</t>
@@ -3344,7 +3332,7 @@
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>17 - Bano</t>
@@ -3424,15 +3412,15 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36.8" customWidth="1" min="1" max="1"/>
-    <col width="14.9" customWidth="1" min="2" max="2"/>
-    <col width="12.6" customWidth="1" min="3" max="3"/>
-    <col width="14.9" customWidth="1" min="4" max="4"/>
-    <col width="14.9" customWidth="1" min="5" max="5"/>
-    <col width="59.8" customWidth="1" min="6" max="6"/>
+    <col width="43.2" customWidth="1" min="1" max="1"/>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="14.9" customWidth="1" min="3" max="3"/>
+    <col width="17.6" customWidth="1" min="4" max="4"/>
+    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="70.2" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - LOSAS</t>
@@ -3442,7 +3430,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
@@ -3458,7 +3446,7 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
     </row>
-    <row r="4" ht="15.8" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="33" t="inlineStr">
         <is>
           <t>MATERIALES Y METODO</t>
@@ -3476,7 +3464,7 @@
       </c>
       <c r="D4" s="2" t="n"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
@@ -3492,7 +3480,7 @@
       </c>
       <c r="D5" s="2" t="n"/>
     </row>
-    <row r="6" ht="14.5" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
@@ -3508,7 +3496,7 @@
       </c>
       <c r="D6" s="2" t="n"/>
     </row>
-    <row r="7" ht="14.5" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Tension admisible del acero</t>
@@ -3524,7 +3512,7 @@
       </c>
       <c r="D7" s="2" t="n"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Brazo elastico  z / h</t>
@@ -3540,7 +3528,7 @@
       </c>
       <c r="D8" s="2" t="n"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
@@ -3556,7 +3544,7 @@
       </c>
       <c r="D9" s="2" t="n"/>
     </row>
-    <row r="10" ht="14.5" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Recubrimiento</t>
@@ -3572,7 +3560,7 @@
       </c>
       <c r="D10" s="2" t="n"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Separacion maxima</t>
@@ -3588,7 +3576,7 @@
       </c>
       <c r="D11" s="2" t="n"/>
     </row>
-    <row r="12" ht="27" customHeight="1">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Armadura de reparticion</t>
@@ -3604,7 +3592,7 @@
       </c>
       <c r="D12" s="2" t="n"/>
     </row>
-    <row r="13" ht="14.5" customHeight="1">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Reparticion minima</t>
@@ -3626,7 +3614,7 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
     </row>
-    <row r="15" ht="29.5" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="33" t="inlineStr">
         <is>
           <t>CARGAS POR NIVEL</t>
@@ -3648,7 +3636,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="35" t="inlineStr">
         <is>
           <t>S/PB</t>
@@ -3666,7 +3654,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="35" t="inlineStr">
         <is>
           <t>S/PA</t>
@@ -3684,7 +3672,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
           <t>El peso propio se suma aparte: 2400 x d / 100</t>
@@ -3700,7 +3688,7 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="33" t="inlineStr">
         <is>
           <t>GRADO DE EMPOTRAMIENTO</t>
@@ -3722,7 +3710,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.8" customHeight="1">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>1/8</t>
@@ -3740,7 +3728,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.8" customHeight="1">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>1/10</t>
@@ -3758,7 +3746,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.8" customHeight="1">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>1/12</t>
@@ -3776,7 +3764,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.8" customHeight="1">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>1/14</t>
@@ -3794,7 +3782,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.8" customHeight="1">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>1/2</t>
@@ -3818,7 +3806,7 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="22" t="inlineStr">
         <is>
           <t>p = peso propio + terminaciones + q   (cargas de servicio)</t>
@@ -3828,7 +3816,7 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="22" t="inlineStr">
         <is>
           <t>M = coef x p x L2        R = coef x p x L        As = M x 100 / (2400 x 0,9 x h)        rep. = As / 5</t>
@@ -3852,13 +3840,13 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41.4" customWidth="1" min="1" max="1"/>
-    <col width="14.9" customWidth="1" min="2" max="2"/>
-    <col width="13.8" customWidth="1" min="3" max="3"/>
-    <col width="71.3" customWidth="1" min="4" max="4"/>
+    <col width="48.6" customWidth="1" min="1" max="1"/>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="16.2" customWidth="1" min="3" max="3"/>
+    <col width="83.7" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - COLUMNAS</t>
@@ -3872,7 +3860,7 @@
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="33" t="inlineStr">
         <is>
           <t>MATERIALES Y CRITERIOS</t>
@@ -3889,7 +3877,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="14.5" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
@@ -3904,7 +3892,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="14.5" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
@@ -3919,7 +3907,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="14.5" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
@@ -3934,7 +3922,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="14.5" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="34" t="inlineStr">
         <is>
           <t>phi compresion (estribos)</t>
@@ -3949,7 +3937,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="14.5" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Cuantia minima</t>
@@ -3964,7 +3952,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="14.5" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Altura PB</t>
@@ -3979,7 +3967,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="14.5" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Altura PA</t>
@@ -3999,7 +3987,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
           <t>As = cuantia minima x area        phi Pn = 0,65 x 0,80 x [0,85 f'c (Ag - As) + fy As]</t>
@@ -4008,7 +3996,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Separacion de estribos = min(12 x diam. longitudinal ; 48 x diam. estribo ; lado menor)</t>
@@ -4031,13 +4019,13 @@
   <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39.1" customWidth="1" min="1" max="1"/>
-    <col width="13.8" customWidth="1" min="2" max="2"/>
-    <col width="13.8" customWidth="1" min="3" max="3"/>
-    <col width="69" customWidth="1" min="4" max="4"/>
+    <col width="45.9" customWidth="1" min="1" max="1"/>
+    <col width="16.2" customWidth="1" min="2" max="2"/>
+    <col width="16.2" customWidth="1" min="3" max="3"/>
+    <col width="81" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - PILOTES</t>
@@ -4057,7 +4045,7 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="33" t="inlineStr">
         <is>
           <t>PARAMETRO</t>
@@ -4081,7 +4069,7 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
     </row>
-    <row r="4" ht="14.5" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Carga admisible por pilote</t>
@@ -4103,7 +4091,7 @@
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Tension admisible del terreno</t>
@@ -4125,7 +4113,7 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
     </row>
-    <row r="6" ht="14.5" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Diametro del pilote</t>
@@ -4147,7 +4135,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
     </row>
-    <row r="7" ht="14.5" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Profundidad</t>
@@ -4169,7 +4157,7 @@
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Coef. de mayoracion adoptado</t>
@@ -4191,7 +4179,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="22" t="inlineStr">
         <is>
           <t>ARMADURA DEL PILOTE  (planilla del Ing. Caggiano, 23-03-22)</t>
@@ -4207,7 +4195,7 @@
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
           <t>TIPOS DE PILOTE  (nota general del plano: CANTIDAD 33 PILOTES)</t>
@@ -4219,7 +4207,7 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
     </row>
-    <row r="11" ht="29.5" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>tipo</t>
@@ -4247,7 +4235,7 @@
       </c>
       <c r="F11" s="2" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Pilote tipo "A"</t>
@@ -4271,7 +4259,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Pilote tipo "B"</t>
@@ -4295,7 +4283,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Pilote tipo "C"</t>
@@ -4319,7 +4307,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Pilote tipo "D"</t>
@@ -4351,7 +4339,7 @@
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="39.7" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
           <t>Los cuatro tipos se funden a -4,50 m; se diferencian en el nivel de llenado de hormigon, o sea en la longitud real del fuste.</t>
@@ -4363,7 +4351,7 @@
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="22" t="inlineStr">
         <is>
           <t>El computo metrico declara 32 pilotes: le falta uno. La nota del plano dice 33, que es la cantidad que se detecta en el dibujo.</t>
@@ -4383,7 +4371,7 @@
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
         <is>
           <t>COMO SE ESTIMO LA CARGA ADMISIBLE</t>
@@ -4395,7 +4383,7 @@
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Pilote O30: area de punta 0,0707 m2. Punta  0,0707 x 20 t/m2 = 1,4 t.</t>
@@ -4407,7 +4395,7 @@
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Area lateral segun el tipo: 3,86 m2 el A, 3,91 el B, 4,19 el C y 4,15 el D.</t>
@@ -4419,7 +4407,7 @@
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
           <t>Con una adherencia de 2,5 t/m2 la capacidad va de 11,1 t el tipo A a 11,9 t el C:</t>
@@ -4431,7 +4419,7 @@
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
           <t>la diferencia entre tipos es menor al 8 por ciento, por eso se usa un unico valor</t>
@@ -4443,7 +4431,7 @@
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
           <t>para todos en lugar de uno por tipo.</t>
@@ -4463,7 +4451,7 @@
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
           <t>DE DONDE SALEN LOS 22 t QUE SE ADOPTAN, Y QUE VALOR TIENEN:</t>
@@ -4475,7 +4463,7 @@
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
           <t>El calculista puso UN solo pilote bajo la columna mas cargada, que baja 21,04 t</t>
@@ -4487,7 +4475,7 @@
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="39.7" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
           <t>de servicio. Si dimensiono asi, es porque para el ese pilote admite al menos eso.</t>
@@ -4499,7 +4487,7 @@
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
           <t>Se adopta 22 t, el redondeo por encima de esa solicitacion.</t>
@@ -4519,7 +4507,7 @@
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="39.7" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
           <t>ESTO NO ES UNA VERIFICACION. Es leer la hipotesis implicita del proyectista y</t>
@@ -4531,7 +4519,7 @@
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="39.7" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
           <t>adoptarla: por construccion, todos los cabezales dan verde. Sirve para completar</t>
@@ -4543,7 +4531,7 @@
       <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="39.7" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
         <is>
           <t>la planilla y para dejar escrito cuanto tiene que resistir el pilote, no para</t>
@@ -4555,7 +4543,7 @@
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="39.7" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
           <t>afirmar que resiste. La verificacion real necesita el estudio de suelos.</t>
@@ -4575,7 +4563,7 @@
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="39.7" customHeight="1">
       <c r="A37" s="23" t="inlineStr">
         <is>
           <t>CONTRASTE: para llegar a 21 t con un O30 de 4,50 m hace falta una adherencia</t>
@@ -4587,7 +4575,7 @@
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="39.7" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
         <is>
           <t>lateral de 4,5 a 4,8 t/m2. En los limos loessicos de la region de Rosario y Funes</t>
@@ -4599,7 +4587,7 @@
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
           <t>los valores habituales van de 2 a 3 t/m2, que darian entre 10 y 14 t. O el estudio</t>
@@ -4611,7 +4599,7 @@
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="39.7" customHeight="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
           <t>dio un suelo mejor del tipico, o las cargas adoptadas en esta planilla estan altas,</t>
@@ -4623,7 +4611,7 @@
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="39.7" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>o el pilote esta ajustado. Es un punto a plantear en el trabajo.</t>
@@ -4643,7 +4631,7 @@
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="39.7" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
           <t>Capacidad ESTRUCTURAL del pilote: con 5d12 (5,65 cm2) en 707 cm2, cuantia 0,8%,</t>
@@ -4655,7 +4643,7 @@
       <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
         <is>
           <t>fi Pn = 77,4 t. La seccion de hormigon no es el limite: manda el suelo.</t>
@@ -4675,7 +4663,7 @@
       <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="39.7" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
         <is>
           <t>FALTA todavia la capacidad geotecnica. Las planillas de armadura de pilotes no</t>
@@ -4687,7 +4675,7 @@
       <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="39.7" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
           <t>la traen: son planillas de doblado de hierro. Ese dato esta en el estudio de suelos.</t>
@@ -4707,7 +4695,7 @@
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="39.7" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
           <t>La tension de 2 kg/cm2 que trae el calculo de bases es la del estrato</t>
@@ -4719,7 +4707,7 @@
       <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="39.7" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
         <is>
           <t>superficial, donde apoyaban las bases. Los pilotes llegan a -4,50 m y</t>
@@ -4731,7 +4719,7 @@
       <c r="E50" s="2" t="n"/>
       <c r="F50" s="2" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="39.7" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
           <t>trabajan sobre todo por friccion: son dos cosas distintas.</t>
@@ -4757,13 +4745,13 @@
   <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52.9" customWidth="1" min="1" max="1"/>
-    <col width="16.1" customWidth="1" min="2" max="2"/>
-    <col width="16.1" customWidth="1" min="3" max="3"/>
-    <col width="55.2" customWidth="1" min="4" max="4"/>
+    <col width="62.1" customWidth="1" min="1" max="1"/>
+    <col width="18.9" customWidth="1" min="2" max="2"/>
+    <col width="18.9" customWidth="1" min="3" max="3"/>
+    <col width="64.8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - PLANILLA 3 HIGROTERMICA</t>
@@ -4779,7 +4767,7 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="33" t="inlineStr">
         <is>
           <t>PARAMETRO</t>
@@ -4801,7 +4789,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="14.5" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Transmitancia maxima admitida</t>
@@ -4821,7 +4809,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="14.5" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>K maximo si los vanos superan el 60% de la fachada</t>
@@ -4853,7 +4841,7 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
           <t>TIPOS DE VIDRIO</t>
@@ -4863,7 +4851,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
     </row>
-    <row r="9" ht="15.8" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="33" t="inlineStr">
         <is>
           <t>descripcion</t>
@@ -4877,7 +4865,7 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="34" t="inlineStr">
         <is>
           <t>DVH 6+9+3+3 (el de obra, aluminio linea A30)</t>
@@ -4889,7 +4877,7 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Simple incoloro 3 mm</t>
@@ -4901,7 +4889,7 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Simple incoloro 6 mm</t>
@@ -4913,7 +4901,7 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="34" t="inlineStr">
         <is>
           <t>DVH Incoloro ext; incoloro interior (3+12+3 mm)</t>
@@ -4925,7 +4913,7 @@
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="34" t="inlineStr">
         <is>
           <t>DVH Incoloro ext; incoloro interior (4+12+4 mm)</t>
@@ -4937,7 +4925,7 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="34" t="inlineStr">
         <is>
           <t>DVH con lamina de baja emisividad (3+12+3 mm)</t>
@@ -4949,7 +4937,7 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="34" t="inlineStr">
         <is>
           <t>DVH con camara de argon (4+16+4 mm)</t>
@@ -4961,7 +4949,7 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="39.7" customHeight="1">
       <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Vidrio laminado 3+3 mm</t>
@@ -4979,7 +4967,7 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
         <is>
           <t>TIPOS DE PROTECCION</t>
@@ -4989,7 +4977,7 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="33" t="inlineStr">
         <is>
           <t>descripcion</t>
@@ -5003,7 +4991,7 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Sin Proteccion</t>
@@ -5015,7 +5003,7 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Cortina blackout INTERIOR (no computa)</t>
@@ -5027,7 +5015,7 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Parasol horizontal fijo 1:2</t>
@@ -5039,7 +5027,7 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Parasol horizontal fijo 1:1</t>
@@ -5051,7 +5039,7 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="34" t="inlineStr">
         <is>
           <t>Alero</t>
@@ -5063,7 +5051,7 @@
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="39.7" customHeight="1">
       <c r="A26" s="34" t="inlineStr">
         <is>
           <t>Cortina de enrollar exterior</t>
@@ -5075,7 +5063,7 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Persiana de madera</t>
@@ -5087,7 +5075,7 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="34" t="inlineStr">
         <is>
           <t>Toldo</t>
@@ -5099,7 +5087,7 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="39.7" customHeight="1">
       <c r="A29" s="22" t="inlineStr">
         <is>
           <t>SUPERFICIE VIDRIADA POR LOCAL  (de la planilla de iluminacion y ventilacion)</t>
@@ -5109,7 +5097,7 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
     </row>
-    <row r="30" ht="15.8" customHeight="1">
+    <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="33" t="inlineStr">
         <is>
           <t>local</t>
@@ -5127,7 +5115,7 @@
       </c>
       <c r="D30" s="2" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="39.7" customHeight="1">
       <c r="A31" s="34" t="inlineStr">
         <is>
           <t>01 - Cocina / comedor</t>
@@ -5141,7 +5129,7 @@
       </c>
       <c r="D31" s="2" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="39.7" customHeight="1">
       <c r="A32" s="34" t="inlineStr">
         <is>
           <t>03 - Lavadero</t>
@@ -5155,7 +5143,7 @@
       </c>
       <c r="D32" s="2" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="39.7" customHeight="1">
       <c r="A33" s="34" t="inlineStr">
         <is>
           <t>06 - Living / comedor</t>
@@ -5169,7 +5157,7 @@
       </c>
       <c r="D33" s="2" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="39.7" customHeight="1">
       <c r="A34" s="34" t="inlineStr">
         <is>
           <t>07 - Hall / ingreso</t>
@@ -5183,7 +5171,7 @@
       </c>
       <c r="D34" s="2" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="39.7" customHeight="1">
       <c r="A35" s="34" t="inlineStr">
         <is>
           <t>09 - Dormitorio suite</t>
@@ -5197,7 +5185,7 @@
       </c>
       <c r="D35" s="2" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="39.7" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
           <t>13 - Dormitorio 1</t>
@@ -5211,7 +5199,7 @@
       </c>
       <c r="D36" s="2" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="39.7" customHeight="1">
       <c r="A37" s="34" t="inlineStr">
         <is>
           <t>14 - Estar / Playroom</t>
@@ -5225,7 +5213,7 @@
       </c>
       <c r="D37" s="2" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="39.7" customHeight="1">
       <c r="A38" s="34" t="inlineStr">
         <is>
           <t>15 - Dormitorio 2</t>
@@ -5239,7 +5227,7 @@
       </c>
       <c r="D38" s="2" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="34" t="inlineStr">
         <is>
           <t>17 - Bano</t>
@@ -5253,7 +5241,7 @@
       </c>
       <c r="D39" s="2" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="39.7" customHeight="1">
       <c r="A40" s="35" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -5271,7 +5259,7 @@
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="39.7" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
         <is>
           <t>La suma da 97.38 m2 de superficie vidriada. El total de vanos de los cuatro planos de la Planilla 3 deberia dar ese orden: sirve de control.</t>
@@ -5287,7 +5275,7 @@
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="22" t="inlineStr">
         <is>
           <t>FACTOR DE EXPOSICION SOLAR MAXIMO ADMITIDO  (Ordenanza 8757/11)</t>
@@ -5297,7 +5285,7 @@
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
     </row>
-    <row r="45" ht="15.8" customHeight="1">
+    <row r="45" ht="39.7" customHeight="1">
       <c r="A45" s="33" t="inlineStr">
         <is>
           <t>orientacion</t>
@@ -5319,7 +5307,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="14.5" customHeight="1">
+    <row r="46" ht="39.7" customHeight="1">
       <c r="A46" s="34" t="inlineStr">
         <is>
           <t>Norte</t>
@@ -5339,7 +5327,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="14.5" customHeight="1">
+    <row r="47" ht="39.7" customHeight="1">
       <c r="A47" s="34" t="inlineStr">
         <is>
           <t>Este</t>
@@ -5359,7 +5347,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="14.5" customHeight="1">
+    <row r="48" ht="39.7" customHeight="1">
       <c r="A48" s="34" t="inlineStr">
         <is>
           <t>Oeste</t>
@@ -5379,7 +5367,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="14.5" customHeight="1">
+    <row r="49" ht="39.7" customHeight="1">
       <c r="A49" s="34" t="inlineStr">
         <is>
           <t>Sur</t>
@@ -5399,7 +5387,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50" ht="39.7" customHeight="1">
       <c r="A50" s="34" t="inlineStr">
         <is>
           <t>Noreste</t>
@@ -5419,7 +5407,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="27" customHeight="1">
+    <row r="51" ht="39.7" customHeight="1">
       <c r="A51" s="34" t="inlineStr">
         <is>
           <t>Sudeste</t>
@@ -5439,7 +5427,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="27" customHeight="1">
+    <row r="52" ht="39.7" customHeight="1">
       <c r="A52" s="34" t="inlineStr">
         <is>
           <t>Sudoeste</t>
@@ -5459,7 +5447,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="27" customHeight="1">
+    <row r="53" ht="39.7" customHeight="1">
       <c r="A53" s="34" t="inlineStr">
         <is>
           <t>Noroeste</t>
@@ -5479,7 +5467,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="14.5" customHeight="1">
+    <row r="54" ht="39.7" customHeight="1">
       <c r="A54" s="34" t="inlineStr">
         <is>
           <t>Horizontal</t>
@@ -5505,7 +5493,7 @@
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n"/>
     </row>
-    <row r="56">
+    <row r="56" ht="39.7" customHeight="1">
       <c r="A56" s="22" t="inlineStr">
         <is>
           <t>La casa esta girada 45 grados respecto del norte, asi que NINGUNA de sus cuatro fachadas</t>
@@ -5515,7 +5503,7 @@
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="39.7" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
           <t>cae en el cuadrante Norte ni en el Sur: las cuatro entran en el cuadrante Este/Oeste, que es</t>
@@ -5525,7 +5513,7 @@
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="39.7" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
         <is>
           <t>el mas exigente (0,30, o 0,39 segun la modificacion de 2021). Conviene confirmarlo en la</t>
@@ -5535,7 +5523,7 @@
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="39.7" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
           <t>Secretaria de Planeamiento antes de presentar: hay versiones distintas dando vueltas.</t>
@@ -5551,7 +5539,7 @@
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="39.7" customHeight="1">
       <c r="A61" s="22" t="inlineStr">
         <is>
           <t>Si la abertura ocupa menos del 20% del lado expuesto del local, NO hay que verificar el FES</t>
@@ -5561,7 +5549,7 @@
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="39.7" customHeight="1">
       <c r="A62" s="23" t="inlineStr">
         <is>
           <t>(si la transmitancia). Fuente: preguntas frecuentes de la Secretaria de Planeamiento.</t>
@@ -5585,11 +5573,11 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25.3" customWidth="1" min="1" max="1"/>
-    <col width="110.4" customWidth="1" min="2" max="2"/>
+    <col width="29.7" customWidth="1" min="1" max="1"/>
+    <col width="129.6" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.5" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="37" t="inlineStr">
         <is>
           <t>MEMORIA - ILUMINACION Y VENTILACION</t>
@@ -5597,11 +5585,11 @@
       </c>
       <c r="B1" s="37" t="inlineStr"/>
     </row>
-    <row r="2" ht="15.8" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="37" t="inlineStr"/>
       <c r="B2" s="38" t="inlineStr"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
           <t>CRITERIO</t>
@@ -5613,7 +5601,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.8" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="37" t="inlineStr"/>
       <c r="B4" s="38" t="inlineStr">
         <is>
@@ -5621,7 +5609,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.8" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="37" t="inlineStr"/>
       <c r="B5" s="38" t="inlineStr">
         <is>
@@ -5629,7 +5617,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.8" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="37" t="inlineStr"/>
       <c r="B6" s="38" t="inlineStr">
         <is>
@@ -5637,11 +5625,11 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.8" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="37" t="inlineStr"/>
       <c r="B7" s="38" t="inlineStr"/>
     </row>
-    <row r="8" ht="15.8" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="37" t="inlineStr">
         <is>
           <t>RESULTADO</t>
@@ -5653,11 +5641,11 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.8" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="37" t="inlineStr"/>
       <c r="B9" s="38" t="inlineStr"/>
     </row>
-    <row r="10" ht="15.8" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="37" t="inlineStr">
         <is>
           <t>CORRECCION</t>
@@ -5669,7 +5657,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.8" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="37" t="inlineStr"/>
       <c r="B11" s="38" t="inlineStr">
         <is>
@@ -5677,7 +5665,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.8" customHeight="1">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="37" t="inlineStr"/>
       <c r="B12" s="38" t="inlineStr">
         <is>
@@ -5685,7 +5673,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.8" customHeight="1">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="37" t="inlineStr"/>
       <c r="B13" s="38" t="inlineStr">
         <is>
@@ -5693,11 +5681,11 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.8" customHeight="1">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="37" t="inlineStr"/>
       <c r="B14" s="38" t="inlineStr"/>
     </row>
-    <row r="15" ht="15.8" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="37" t="inlineStr">
         <is>
           <t>A REVISAR</t>
@@ -5709,7 +5697,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.8" customHeight="1">
+    <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="37" t="inlineStr"/>
       <c r="B16" s="38" t="inlineStr">
         <is>
@@ -5717,7 +5705,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.8" customHeight="1">
+    <row r="17" ht="39.7" customHeight="1">
       <c r="A17" s="37" t="inlineStr"/>
       <c r="B17" s="38" t="inlineStr">
         <is>
@@ -5725,11 +5713,11 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.8" customHeight="1">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="37" t="inlineStr"/>
       <c r="B18" s="38" t="inlineStr"/>
     </row>
-    <row r="19" ht="15.8" customHeight="1">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="37" t="inlineStr"/>
       <c r="B19" s="38" t="inlineStr">
         <is>
@@ -5737,7 +5725,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="37" t="inlineStr"/>
       <c r="B20" s="38" t="inlineStr">
         <is>
@@ -5745,11 +5733,11 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.8" customHeight="1">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="37" t="inlineStr"/>
       <c r="B21" s="38" t="inlineStr"/>
     </row>
-    <row r="22" ht="15.8" customHeight="1">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="37" t="inlineStr">
         <is>
           <t>REDONDEOS</t>
@@ -5761,7 +5749,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.8" customHeight="1">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="37" t="inlineStr"/>
       <c r="B23" s="38" t="inlineStr">
         <is>
@@ -5783,11 +5771,11 @@
   <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27.6" customWidth="1" min="1" max="1"/>
-    <col width="112.7" customWidth="1" min="2" max="2"/>
+    <col width="32.4" customWidth="1" min="1" max="1"/>
+    <col width="132.3" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.5" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="37" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - VIGAS H°A°</t>
@@ -5795,11 +5783,11 @@
       </c>
       <c r="B1" s="37" t="inlineStr"/>
     </row>
-    <row r="2" ht="15.8" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="37" t="inlineStr"/>
       <c r="B2" s="38" t="inlineStr"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
           <t>NORMATIVA</t>
@@ -5811,7 +5799,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.8" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="37" t="inlineStr">
         <is>
           <t>UNIDADES</t>
@@ -5823,7 +5811,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.8" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
@@ -5835,11 +5823,11 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.8" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="37" t="inlineStr"/>
       <c r="B6" s="38" t="inlineStr"/>
     </row>
-    <row r="7" ht="15.8" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="37" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
@@ -5847,7 +5835,7 @@
       </c>
       <c r="B7" s="37" t="inlineStr"/>
     </row>
-    <row r="8" ht="15.8" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="37" t="inlineStr">
         <is>
           <t>Entrepiso PA</t>
@@ -5859,7 +5847,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.8" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="37" t="inlineStr"/>
       <c r="B9" s="38" t="inlineStr">
         <is>
@@ -5867,7 +5855,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.8" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Azotea</t>
@@ -5879,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.8" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="37" t="inlineStr"/>
       <c r="B11" s="38" t="inlineStr">
         <is>
@@ -5887,7 +5875,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.8" customHeight="1">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Mamposteria</t>
@@ -5899,7 +5887,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.8" customHeight="1">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Peso propio</t>
@@ -5911,7 +5899,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.8" customHeight="1">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="37" t="inlineStr">
         <is>
           <t>Carga de calculo</t>
@@ -5923,11 +5911,11 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.8" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="37" t="inlineStr"/>
       <c r="B15" s="38" t="inlineStr"/>
     </row>
-    <row r="16" ht="15.8" customHeight="1">
+    <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="37" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
@@ -5939,7 +5927,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.8" customHeight="1">
+    <row r="17" ht="39.7" customHeight="1">
       <c r="A17" s="37" t="inlineStr"/>
       <c r="B17" s="38" t="inlineStr">
         <is>
@@ -5947,7 +5935,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.8" customHeight="1">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="37" t="inlineStr"/>
       <c r="B18" s="38" t="inlineStr">
         <is>
@@ -5955,7 +5943,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.8" customHeight="1">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="37" t="inlineStr"/>
       <c r="B19" s="38" t="inlineStr">
         <is>
@@ -5963,7 +5951,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="37" t="inlineStr"/>
       <c r="B20" s="38" t="inlineStr">
         <is>
@@ -5971,7 +5959,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.8" customHeight="1">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="37" t="inlineStr"/>
       <c r="B21" s="38" t="inlineStr">
         <is>
@@ -5979,11 +5967,11 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.8" customHeight="1">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="37" t="inlineStr"/>
       <c r="B22" s="38" t="inlineStr"/>
     </row>
-    <row r="23" ht="15.8" customHeight="1">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="37" t="inlineStr">
         <is>
           <t>3. FLEXION</t>
@@ -5995,7 +5983,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.8" customHeight="1">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="37" t="inlineStr"/>
       <c r="B24" s="38" t="inlineStr">
         <is>
@@ -6003,7 +5991,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.8" customHeight="1">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="37" t="inlineStr"/>
       <c r="B25" s="38" t="inlineStr">
         <is>
@@ -6011,11 +5999,11 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.8" customHeight="1">
+    <row r="26" ht="39.7" customHeight="1">
       <c r="A26" s="37" t="inlineStr"/>
       <c r="B26" s="38" t="inlineStr"/>
     </row>
-    <row r="27" ht="15.8" customHeight="1">
+    <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="37" t="inlineStr">
         <is>
           <t>4. CORTE</t>
@@ -6027,7 +6015,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.8" customHeight="1">
+    <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="37" t="inlineStr"/>
       <c r="B28" s="38" t="inlineStr">
         <is>
@@ -6035,7 +6023,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.8" customHeight="1">
+    <row r="29" ht="39.7" customHeight="1">
       <c r="A29" s="37" t="inlineStr"/>
       <c r="B29" s="38" t="inlineStr">
         <is>
@@ -6043,11 +6031,11 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.8" customHeight="1">
+    <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="37" t="inlineStr"/>
       <c r="B30" s="38" t="inlineStr"/>
     </row>
-    <row r="31" ht="15.8" customHeight="1">
+    <row r="31" ht="39.7" customHeight="1">
       <c r="A31" s="37" t="inlineStr">
         <is>
           <t>5. FLECHA</t>
@@ -6059,7 +6047,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.8" customHeight="1">
+    <row r="32" ht="39.7" customHeight="1">
       <c r="A32" s="37" t="inlineStr"/>
       <c r="B32" s="38" t="inlineStr">
         <is>
@@ -6067,11 +6055,11 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.8" customHeight="1">
+    <row r="33" ht="39.7" customHeight="1">
       <c r="A33" s="37" t="inlineStr"/>
       <c r="B33" s="38" t="inlineStr"/>
     </row>
-    <row r="34" ht="15.8" customHeight="1">
+    <row r="34" ht="39.7" customHeight="1">
       <c r="A34" s="37" t="inlineStr">
         <is>
           <t>6. VIGAS INVERTIDAS</t>
@@ -6083,7 +6071,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15.8" customHeight="1">
+    <row r="35" ht="39.7" customHeight="1">
       <c r="A35" s="37" t="inlineStr"/>
       <c r="B35" s="38" t="inlineStr">
         <is>
@@ -6091,7 +6079,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15.8" customHeight="1">
+    <row r="36" ht="39.7" customHeight="1">
       <c r="A36" s="37" t="inlineStr"/>
       <c r="B36" s="38" t="inlineStr">
         <is>
@@ -6099,7 +6087,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15.8" customHeight="1">
+    <row r="37" ht="39.7" customHeight="1">
       <c r="A37" s="37" t="inlineStr"/>
       <c r="B37" s="38" t="inlineStr">
         <is>
@@ -6107,7 +6095,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.8" customHeight="1">
+    <row r="38" ht="39.7" customHeight="1">
       <c r="A38" s="37" t="inlineStr"/>
       <c r="B38" s="38" t="inlineStr">
         <is>
@@ -6115,7 +6103,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15.8" customHeight="1">
+    <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="37" t="inlineStr"/>
       <c r="B39" s="38" t="inlineStr">
         <is>
@@ -6123,7 +6111,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15.8" customHeight="1">
+    <row r="40" ht="39.7" customHeight="1">
       <c r="A40" s="37" t="inlineStr"/>
       <c r="B40" s="38" t="inlineStr">
         <is>
@@ -6131,7 +6119,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15.8" customHeight="1">
+    <row r="41" ht="39.7" customHeight="1">
       <c r="A41" s="37" t="inlineStr"/>
       <c r="B41" s="38" t="inlineStr">
         <is>
@@ -6139,7 +6127,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.8" customHeight="1">
+    <row r="42" ht="39.7" customHeight="1">
       <c r="A42" s="37" t="inlineStr"/>
       <c r="B42" s="38" t="inlineStr">
         <is>
@@ -6147,7 +6135,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15.8" customHeight="1">
+    <row r="43" ht="39.7" customHeight="1">
       <c r="A43" s="37" t="inlineStr"/>
       <c r="B43" s="38" t="inlineStr">
         <is>
@@ -6155,7 +6143,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15.8" customHeight="1">
+    <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="37" t="inlineStr"/>
       <c r="B44" s="38" t="inlineStr">
         <is>
@@ -6163,7 +6151,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.8" customHeight="1">
+    <row r="45" ht="39.7" customHeight="1">
       <c r="A45" s="37" t="inlineStr"/>
       <c r="B45" s="38" t="inlineStr">
         <is>
@@ -6171,7 +6159,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15.8" customHeight="1">
+    <row r="46" ht="39.7" customHeight="1">
       <c r="A46" s="37" t="inlineStr"/>
       <c r="B46" s="38" t="inlineStr">
         <is>
@@ -6179,7 +6167,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.8" customHeight="1">
+    <row r="47" ht="39.7" customHeight="1">
       <c r="A47" s="37" t="inlineStr"/>
       <c r="B47" s="38" t="inlineStr">
         <is>
@@ -6187,7 +6175,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15.8" customHeight="1">
+    <row r="48" ht="39.7" customHeight="1">
       <c r="A48" s="37" t="inlineStr"/>
       <c r="B48" s="38" t="inlineStr">
         <is>
@@ -6195,7 +6183,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15.8" customHeight="1">
+    <row r="49" ht="39.7" customHeight="1">
       <c r="A49" s="37" t="inlineStr"/>
       <c r="B49" s="38" t="inlineStr">
         <is>
@@ -6203,11 +6191,11 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15.8" customHeight="1">
+    <row r="50" ht="39.7" customHeight="1">
       <c r="A50" s="37" t="inlineStr"/>
       <c r="B50" s="38" t="inlineStr"/>
     </row>
-    <row r="51" ht="15.8" customHeight="1">
+    <row r="51" ht="39.7" customHeight="1">
       <c r="A51" s="37" t="inlineStr">
         <is>
           <t>7. RESULTADO</t>
@@ -6219,7 +6207,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15.8" customHeight="1">
+    <row r="52" ht="39.7" customHeight="1">
       <c r="A52" s="37" t="inlineStr"/>
       <c r="B52" s="38" t="inlineStr">
         <is>
@@ -6227,7 +6215,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15.8" customHeight="1">
+    <row r="53" ht="39.7" customHeight="1">
       <c r="A53" s="37" t="inlineStr"/>
       <c r="B53" s="38" t="inlineStr">
         <is>
@@ -6235,7 +6223,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15.8" customHeight="1">
+    <row r="54" ht="39.7" customHeight="1">
       <c r="A54" s="37" t="inlineStr"/>
       <c r="B54" s="38" t="inlineStr">
         <is>
@@ -6243,7 +6231,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="15.8" customHeight="1">
+    <row r="55" ht="39.7" customHeight="1">
       <c r="A55" s="37" t="inlineStr"/>
       <c r="B55" s="38" t="inlineStr">
         <is>
@@ -6251,7 +6239,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="15.8" customHeight="1">
+    <row r="56" ht="39.7" customHeight="1">
       <c r="A56" s="37" t="inlineStr"/>
       <c r="B56" s="38" t="inlineStr">
         <is>
@@ -6259,7 +6247,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="15.8" customHeight="1">
+    <row r="57" ht="39.7" customHeight="1">
       <c r="A57" s="37" t="inlineStr"/>
       <c r="B57" s="38" t="inlineStr">
         <is>
@@ -6267,7 +6255,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15.8" customHeight="1">
+    <row r="58" ht="39.7" customHeight="1">
       <c r="A58" s="37" t="inlineStr"/>
       <c r="B58" s="38" t="inlineStr">
         <is>
@@ -6275,7 +6263,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15.8" customHeight="1">
+    <row r="59" ht="39.7" customHeight="1">
       <c r="A59" s="37" t="inlineStr"/>
       <c r="B59" s="38" t="inlineStr">
         <is>
@@ -6283,7 +6271,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="15.8" customHeight="1">
+    <row r="60" ht="39.7" customHeight="1">
       <c r="A60" s="37" t="inlineStr"/>
       <c r="B60" s="38" t="inlineStr">
         <is>
@@ -6291,7 +6279,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15.8" customHeight="1">
+    <row r="61" ht="39.7" customHeight="1">
       <c r="A61" s="37" t="inlineStr"/>
       <c r="B61" s="38" t="inlineStr">
         <is>
@@ -6299,7 +6287,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15.8" customHeight="1">
+    <row r="62" ht="39.7" customHeight="1">
       <c r="A62" s="37" t="inlineStr"/>
       <c r="B62" s="38" t="inlineStr">
         <is>
@@ -6307,11 +6295,11 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15.8" customHeight="1">
+    <row r="63" ht="39.7" customHeight="1">
       <c r="A63" s="37" t="inlineStr"/>
       <c r="B63" s="38" t="inlineStr"/>
     </row>
-    <row r="64" ht="15.8" customHeight="1">
+    <row r="64" ht="39.7" customHeight="1">
       <c r="A64" s="37" t="inlineStr">
         <is>
           <t>8. ALCANCE</t>
@@ -6323,7 +6311,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15.8" customHeight="1">
+    <row r="65" ht="39.7" customHeight="1">
       <c r="A65" s="37" t="inlineStr"/>
       <c r="B65" s="38" t="inlineStr">
         <is>
@@ -6331,11 +6319,11 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15.8" customHeight="1">
+    <row r="66" ht="39.7" customHeight="1">
       <c r="A66" s="37" t="inlineStr"/>
       <c r="B66" s="38" t="inlineStr"/>
     </row>
-    <row r="67" ht="15.8" customHeight="1">
+    <row r="67" ht="39.7" customHeight="1">
       <c r="A67" s="37" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
@@ -6347,7 +6335,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="15.8" customHeight="1">
+    <row r="68" ht="39.7" customHeight="1">
       <c r="A68" s="37" t="inlineStr"/>
       <c r="B68" s="38" t="inlineStr">
         <is>
@@ -6355,7 +6343,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15.8" customHeight="1">
+    <row r="69" ht="39.7" customHeight="1">
       <c r="A69" s="37" t="inlineStr"/>
       <c r="B69" s="38" t="inlineStr">
         <is>
@@ -6363,7 +6351,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="15.8" customHeight="1">
+    <row r="70" ht="39.7" customHeight="1">
       <c r="A70" s="37" t="inlineStr"/>
       <c r="B70" s="38" t="inlineStr">
         <is>
@@ -6371,7 +6359,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15.8" customHeight="1">
+    <row r="71" ht="39.7" customHeight="1">
       <c r="A71" s="37" t="inlineStr"/>
       <c r="B71" s="38" t="inlineStr">
         <is>
@@ -6393,11 +6381,11 @@
   <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27.6" customWidth="1" min="1" max="1"/>
-    <col width="110.4" customWidth="1" min="2" max="2"/>
+    <col width="32.4" customWidth="1" min="1" max="1"/>
+    <col width="129.6" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.8" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="37" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - LOSAS</t>
@@ -6405,11 +6393,11 @@
       </c>
       <c r="B1" s="37" t="inlineStr"/>
     </row>
-    <row r="2" ht="15.8" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="37" t="inlineStr"/>
       <c r="B2" s="38" t="inlineStr"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
           <t>METODO</t>
@@ -6421,7 +6409,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.8" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="37" t="inlineStr"/>
       <c r="B4" s="38" t="inlineStr">
         <is>
@@ -6429,7 +6417,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.8" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>MATERIALES</t>
@@ -6441,7 +6429,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.8" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="37" t="inlineStr">
         <is>
           <t>DIMENSIONES</t>
@@ -6453,11 +6441,11 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.8" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="37" t="inlineStr"/>
       <c r="B7" s="38" t="inlineStr"/>
     </row>
-    <row r="8" ht="15.8" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="37" t="inlineStr">
         <is>
           <t>1. CARGAS</t>
@@ -6469,7 +6457,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.8" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="37" t="inlineStr"/>
       <c r="B9" s="38" t="inlineStr">
         <is>
@@ -6477,7 +6465,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.8" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="37" t="inlineStr">
         <is>
           <t>S/PB</t>
@@ -6489,7 +6477,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.8" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="37" t="inlineStr"/>
       <c r="B11" s="38" t="inlineStr">
         <is>
@@ -6497,7 +6485,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.8" customHeight="1">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="37" t="inlineStr">
         <is>
           <t>S/PA</t>
@@ -6509,7 +6497,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.8" customHeight="1">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="37" t="inlineStr"/>
       <c r="B13" s="38" t="inlineStr">
         <is>
@@ -6517,11 +6505,11 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.8" customHeight="1">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="37" t="inlineStr"/>
       <c r="B14" s="38" t="inlineStr"/>
     </row>
-    <row r="15" ht="15.8" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="37" t="inlineStr">
         <is>
           <t>2. SOLICITACIONES</t>
@@ -6533,7 +6521,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.8" customHeight="1">
+    <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="37" t="inlineStr"/>
       <c r="B16" s="38" t="inlineStr">
         <is>
@@ -6541,7 +6529,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.8" customHeight="1">
+    <row r="17" ht="39.7" customHeight="1">
       <c r="A17" s="37" t="inlineStr"/>
       <c r="B17" s="38" t="inlineStr">
         <is>
@@ -6549,11 +6537,11 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.8" customHeight="1">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="37" t="inlineStr"/>
       <c r="B18" s="38" t="inlineStr"/>
     </row>
-    <row r="19" ht="15.8" customHeight="1">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="37" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
@@ -6565,7 +6553,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="37" t="inlineStr"/>
       <c r="B20" s="38" t="inlineStr">
         <is>
@@ -6573,7 +6561,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.8" customHeight="1">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="37" t="inlineStr"/>
       <c r="B21" s="38" t="inlineStr">
         <is>
@@ -6581,11 +6569,11 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.8" customHeight="1">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="37" t="inlineStr"/>
       <c r="B22" s="38" t="inlineStr"/>
     </row>
-    <row r="23" ht="15.8" customHeight="1">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="37" t="inlineStr">
         <is>
           <t>4. ESPESORES</t>
@@ -6597,7 +6585,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.8" customHeight="1">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="37" t="inlineStr"/>
       <c r="B24" s="38" t="inlineStr">
         <is>
@@ -6605,7 +6593,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.8" customHeight="1">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="37" t="inlineStr"/>
       <c r="B25" s="38" t="inlineStr">
         <is>
@@ -6613,11 +6601,11 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.8" customHeight="1">
+    <row r="26" ht="39.7" customHeight="1">
       <c r="A26" s="37" t="inlineStr"/>
       <c r="B26" s="38" t="inlineStr"/>
     </row>
-    <row r="27" ht="15.8" customHeight="1">
+    <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="37" t="inlineStr">
         <is>
           <t>5. LUCES</t>
@@ -6629,7 +6617,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.8" customHeight="1">
+    <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="37" t="inlineStr"/>
       <c r="B28" s="38" t="inlineStr">
         <is>
@@ -6637,11 +6625,11 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.8" customHeight="1">
+    <row r="29" ht="39.7" customHeight="1">
       <c r="A29" s="37" t="inlineStr"/>
       <c r="B29" s="38" t="inlineStr"/>
     </row>
-    <row r="30" ht="15.8" customHeight="1">
+    <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="37" t="inlineStr">
         <is>
           <t>6. LOSAS CRUZADAS</t>
@@ -6653,7 +6641,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.8" customHeight="1">
+    <row r="31" ht="39.7" customHeight="1">
       <c r="A31" s="37" t="inlineStr"/>
       <c r="B31" s="38" t="inlineStr">
         <is>
@@ -6661,7 +6649,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.8" customHeight="1">
+    <row r="32" ht="39.7" customHeight="1">
       <c r="A32" s="37" t="inlineStr"/>
       <c r="B32" s="38" t="inlineStr">
         <is>
@@ -6669,7 +6657,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.8" customHeight="1">
+    <row r="33" ht="39.7" customHeight="1">
       <c r="A33" s="37" t="inlineStr"/>
       <c r="B33" s="38" t="inlineStr">
         <is>
@@ -6677,7 +6665,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15.8" customHeight="1">
+    <row r="34" ht="39.7" customHeight="1">
       <c r="A34" s="37" t="inlineStr"/>
       <c r="B34" s="38" t="inlineStr">
         <is>
@@ -6685,7 +6673,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15.8" customHeight="1">
+    <row r="35" ht="39.7" customHeight="1">
       <c r="A35" s="37" t="inlineStr"/>
       <c r="B35" s="38" t="inlineStr">
         <is>
@@ -6693,7 +6681,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15.8" customHeight="1">
+    <row r="36" ht="39.7" customHeight="1">
       <c r="A36" s="37" t="inlineStr"/>
       <c r="B36" s="38" t="inlineStr">
         <is>
@@ -6701,7 +6689,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15.8" customHeight="1">
+    <row r="37" ht="39.7" customHeight="1">
       <c r="A37" s="37" t="inlineStr"/>
       <c r="B37" s="38" t="inlineStr">
         <is>
@@ -6709,7 +6697,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.8" customHeight="1">
+    <row r="38" ht="39.7" customHeight="1">
       <c r="A38" s="37" t="inlineStr"/>
       <c r="B38" s="38" t="inlineStr">
         <is>
@@ -6717,7 +6705,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15.8" customHeight="1">
+    <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="37" t="inlineStr"/>
       <c r="B39" s="38" t="inlineStr">
         <is>
@@ -6725,11 +6713,11 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15.8" customHeight="1">
+    <row r="40" ht="39.7" customHeight="1">
       <c r="A40" s="37" t="inlineStr"/>
       <c r="B40" s="38" t="inlineStr"/>
     </row>
-    <row r="41" ht="15.8" customHeight="1">
+    <row r="41" ht="39.7" customHeight="1">
       <c r="A41" s="37" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
@@ -6741,7 +6729,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.8" customHeight="1">
+    <row r="42" ht="39.7" customHeight="1">
       <c r="A42" s="37" t="inlineStr"/>
       <c r="B42" s="38" t="inlineStr">
         <is>
@@ -6749,7 +6737,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15.8" customHeight="1">
+    <row r="43" ht="39.7" customHeight="1">
       <c r="A43" s="37" t="inlineStr"/>
       <c r="B43" s="38" t="inlineStr">
         <is>
@@ -6757,7 +6745,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15.8" customHeight="1">
+    <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="37" t="inlineStr"/>
       <c r="B44" s="38" t="inlineStr">
         <is>
@@ -6779,11 +6767,11 @@
   <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27.6" customWidth="1" min="1" max="1"/>
-    <col width="112.7" customWidth="1" min="2" max="2"/>
+    <col width="32.4" customWidth="1" min="1" max="1"/>
+    <col width="132.3" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.5" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="37" t="inlineStr">
         <is>
           <t>MEMORIA DE CALCULO - COLUMNAS</t>
@@ -6791,11 +6779,11 @@
       </c>
       <c r="B1" s="37" t="inlineStr"/>
     </row>
-    <row r="2" ht="15.8" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="37" t="inlineStr"/>
       <c r="B2" s="38" t="inlineStr"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
           <t>MATERIALES</t>
@@ -6807,11 +6795,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.8" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="37" t="inlineStr"/>
       <c r="B4" s="38" t="inlineStr"/>
     </row>
-    <row r="5" ht="15.8" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>1. RELEVAMIENTO</t>
@@ -6823,7 +6811,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.8" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="37" t="inlineStr"/>
       <c r="B6" s="38" t="inlineStr">
         <is>
@@ -6831,7 +6819,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15.8" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="37" t="inlineStr"/>
       <c r="B7" s="38" t="inlineStr">
         <is>
@@ -6839,7 +6827,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.8" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="37" t="inlineStr"/>
       <c r="B8" s="38" t="inlineStr">
         <is>
@@ -6847,7 +6835,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15.8" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="37" t="inlineStr"/>
       <c r="B9" s="38" t="inlineStr">
         <is>
@@ -6855,7 +6843,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.8" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="37" t="inlineStr"/>
       <c r="B10" s="38" t="inlineStr">
         <is>
@@ -6863,11 +6851,11 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.8" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="37" t="inlineStr"/>
       <c r="B11" s="38" t="inlineStr"/>
     </row>
-    <row r="12" ht="15.8" customHeight="1">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="37" t="inlineStr">
         <is>
           <t>2. ALTURAS</t>
@@ -6879,7 +6867,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15.8" customHeight="1">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="37" t="inlineStr"/>
       <c r="B13" s="38" t="inlineStr">
         <is>
@@ -6887,11 +6875,11 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.8" customHeight="1">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="37" t="inlineStr"/>
       <c r="B14" s="38" t="inlineStr"/>
     </row>
-    <row r="15" ht="15.8" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="37" t="inlineStr">
         <is>
           <t>3. ARMADURA</t>
@@ -6903,7 +6891,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.8" customHeight="1">
+    <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="37" t="inlineStr"/>
       <c r="B16" s="38" t="inlineStr">
         <is>
@@ -6911,7 +6899,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.8" customHeight="1">
+    <row r="17" ht="39.7" customHeight="1">
       <c r="A17" s="37" t="inlineStr"/>
       <c r="B17" s="38" t="inlineStr">
         <is>
@@ -6919,7 +6907,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.8" customHeight="1">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="37" t="inlineStr"/>
       <c r="B18" s="38" t="inlineStr">
         <is>
@@ -6927,7 +6915,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.8" customHeight="1">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="37" t="inlineStr"/>
       <c r="B19" s="38" t="inlineStr">
         <is>
@@ -6935,11 +6923,11 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="37" t="inlineStr"/>
       <c r="B20" s="38" t="inlineStr"/>
     </row>
-    <row r="21" ht="15.8" customHeight="1">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="37" t="inlineStr">
         <is>
           <t>4. CAPACIDAD</t>
@@ -6951,7 +6939,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.8" customHeight="1">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="37" t="inlineStr"/>
       <c r="B22" s="38" t="inlineStr">
         <is>
@@ -6959,11 +6947,11 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.8" customHeight="1">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="37" t="inlineStr"/>
       <c r="B23" s="38" t="inlineStr"/>
     </row>
-    <row r="24" ht="15.8" customHeight="1">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="37" t="inlineStr">
         <is>
           <t>5. CARGAS</t>
@@ -6975,7 +6963,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.8" customHeight="1">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="37" t="inlineStr"/>
       <c r="B25" s="38" t="inlineStr">
         <is>
@@ -6983,7 +6971,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.8" customHeight="1">
+    <row r="26" ht="39.7" customHeight="1">
       <c r="A26" s="37" t="inlineStr"/>
       <c r="B26" s="38" t="inlineStr">
         <is>
@@ -6991,7 +6979,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.8" customHeight="1">
+    <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="37" t="inlineStr"/>
       <c r="B27" s="38" t="inlineStr">
         <is>
@@ -6999,7 +6987,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15.8" customHeight="1">
+    <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="37" t="inlineStr"/>
       <c r="B28" s="38" t="inlineStr">
         <is>
@@ -7007,7 +6995,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15.8" customHeight="1">
+    <row r="29" ht="39.7" customHeight="1">
       <c r="A29" s="37" t="inlineStr"/>
       <c r="B29" s="38" t="inlineStr">
         <is>
@@ -7015,7 +7003,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.8" customHeight="1">
+    <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="37" t="inlineStr"/>
       <c r="B30" s="38" t="inlineStr">
         <is>
@@ -7023,7 +7011,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15.8" customHeight="1">
+    <row r="31" ht="39.7" customHeight="1">
       <c r="A31" s="37" t="inlineStr"/>
       <c r="B31" s="38" t="inlineStr">
         <is>
@@ -7031,7 +7019,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15.8" customHeight="1">
+    <row r="32" ht="39.7" customHeight="1">
       <c r="A32" s="37" t="inlineStr"/>
       <c r="B32" s="38" t="inlineStr">
         <is>
@@ -7039,7 +7027,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15.8" customHeight="1">
+    <row r="33" ht="39.7" customHeight="1">
       <c r="A33" s="37" t="inlineStr"/>
       <c r="B33" s="38" t="inlineStr">
         <is>
@@ -7047,11 +7035,11 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15.8" customHeight="1">
+    <row r="34" ht="39.7" customHeight="1">
       <c r="A34" s="37" t="inlineStr"/>
       <c r="B34" s="38" t="inlineStr"/>
     </row>
-    <row r="35" ht="15.8" customHeight="1">
+    <row r="35" ht="39.7" customHeight="1">
       <c r="A35" s="37" t="inlineStr">
         <is>
           <t>6. ESBELTEZ</t>
@@ -7063,7 +7051,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15.8" customHeight="1">
+    <row r="36" ht="39.7" customHeight="1">
       <c r="A36" s="37" t="inlineStr"/>
       <c r="B36" s="38" t="inlineStr">
         <is>
@@ -7071,7 +7059,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15.8" customHeight="1">
+    <row r="37" ht="39.7" customHeight="1">
       <c r="A37" s="37" t="inlineStr"/>
       <c r="B37" s="38" t="inlineStr">
         <is>
@@ -7079,7 +7067,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15.8" customHeight="1">
+    <row r="38" ht="39.7" customHeight="1">
       <c r="A38" s="37" t="inlineStr"/>
       <c r="B38" s="38" t="inlineStr">
         <is>
@@ -7087,11 +7075,11 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15.8" customHeight="1">
+    <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="37" t="inlineStr"/>
       <c r="B39" s="38" t="inlineStr"/>
     </row>
-    <row r="40" ht="15.8" customHeight="1">
+    <row r="40" ht="39.7" customHeight="1">
       <c r="A40" s="37" t="inlineStr">
         <is>
           <t>7. LA DE 10x10</t>
@@ -7103,7 +7091,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15.8" customHeight="1">
+    <row r="41" ht="39.7" customHeight="1">
       <c r="A41" s="37" t="inlineStr"/>
       <c r="B41" s="38" t="inlineStr">
         <is>
@@ -7111,7 +7099,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15.8" customHeight="1">
+    <row r="42" ht="39.7" customHeight="1">
       <c r="A42" s="37" t="inlineStr"/>
       <c r="B42" s="38" t="inlineStr">
         <is>
@@ -7119,7 +7107,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15.8" customHeight="1">
+    <row r="43" ht="39.7" customHeight="1">
       <c r="A43" s="37" t="inlineStr"/>
       <c r="B43" s="38" t="inlineStr">
         <is>
@@ -7127,7 +7115,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15.8" customHeight="1">
+    <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="37" t="inlineStr"/>
       <c r="B44" s="38" t="inlineStr">
         <is>
@@ -7135,11 +7123,11 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15.8" customHeight="1">
+    <row r="45" ht="39.7" customHeight="1">
       <c r="A45" s="37" t="inlineStr"/>
       <c r="B45" s="38" t="inlineStr"/>
     </row>
-    <row r="46" ht="15.8" customHeight="1">
+    <row r="46" ht="39.7" customHeight="1">
       <c r="A46" s="37" t="inlineStr">
         <is>
           <t>LIMITACIONES</t>
@@ -7151,7 +7139,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15.8" customHeight="1">
+    <row r="47" ht="39.7" customHeight="1">
       <c r="A47" s="37" t="inlineStr"/>
       <c r="B47" s="38" t="inlineStr">
         <is>
@@ -7159,7 +7147,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15.8" customHeight="1">
+    <row r="48" ht="39.7" customHeight="1">
       <c r="A48" s="37" t="inlineStr"/>
       <c r="B48" s="38" t="inlineStr">
         <is>
@@ -7181,14 +7169,14 @@
   <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16.1" customWidth="1" min="1" max="1"/>
-    <col width="10.3" customWidth="1" min="2" max="2"/>
-    <col width="10.3" customWidth="1" min="3" max="3"/>
-    <col width="12.6" customWidth="1" min="4" max="4"/>
-    <col width="55.2" customWidth="1" min="5" max="5"/>
+    <col width="18.9" customWidth="1" min="1" max="1"/>
+    <col width="12.2" customWidth="1" min="2" max="2"/>
+    <col width="12.2" customWidth="1" min="3" max="3"/>
+    <col width="14.9" customWidth="1" min="4" max="4"/>
+    <col width="64.8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION - inventario. Calculo pendiente: va despues de columnas.</t>
@@ -7206,7 +7194,7 @@
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
     </row>
-    <row r="3" ht="15.8" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>POSICION</t>
@@ -7233,7 +7221,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.8" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>VF01 (1)</t>
@@ -7250,7 +7238,7 @@
       </c>
       <c r="E4" s="7" t="n"/>
     </row>
-    <row r="5" ht="15.8" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>VF01 (2)</t>
@@ -7267,7 +7255,7 @@
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
-    <row r="6" ht="15.8" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>VF01 (3)</t>
@@ -7284,7 +7272,7 @@
       </c>
       <c r="E6" s="7" t="n"/>
     </row>
-    <row r="7" ht="15.8" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>VF02</t>
@@ -7301,7 +7289,7 @@
       </c>
       <c r="E7" s="7" t="n"/>
     </row>
-    <row r="8" ht="15.8" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>VF03</t>
@@ -7318,7 +7306,7 @@
       </c>
       <c r="E8" s="7" t="n"/>
     </row>
-    <row r="9" ht="15.8" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>VF04a</t>
@@ -7337,7 +7325,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15.8" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>VF04b</t>
@@ -7354,7 +7342,7 @@
       </c>
       <c r="E10" s="7" t="n"/>
     </row>
-    <row r="11" ht="15.8" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>VF04c</t>
@@ -7371,7 +7359,7 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12" ht="15.8" customHeight="1">
+    <row r="12" ht="39.7" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>VF05</t>
@@ -7388,7 +7376,7 @@
       </c>
       <c r="E12" s="7" t="n"/>
     </row>
-    <row r="13" ht="15.8" customHeight="1">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>VF06a</t>
@@ -7403,7 +7391,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.8" customHeight="1">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>VF06b</t>
@@ -7418,7 +7406,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.8" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>VF06c</t>
@@ -7435,7 +7423,7 @@
       </c>
       <c r="E15" s="7" t="n"/>
     </row>
-    <row r="16" ht="15.8" customHeight="1">
+    <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>VF06d</t>
@@ -7452,7 +7440,7 @@
       </c>
       <c r="E16" s="7" t="n"/>
     </row>
-    <row r="17" ht="15.8" customHeight="1">
+    <row r="17" ht="39.7" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>VF07</t>
@@ -7469,7 +7457,7 @@
       </c>
       <c r="E17" s="7" t="n"/>
     </row>
-    <row r="18" ht="15.8" customHeight="1">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>VF08</t>
@@ -7486,7 +7474,7 @@
       </c>
       <c r="E18" s="7" t="n"/>
     </row>
-    <row r="19" ht="15.8" customHeight="1">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>VF09 (1)</t>
@@ -7503,7 +7491,7 @@
       </c>
       <c r="E19" s="7" t="n"/>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>VF09 (2)</t>
@@ -7520,7 +7508,7 @@
       </c>
       <c r="E20" s="7" t="n"/>
     </row>
-    <row r="21" ht="15.8" customHeight="1">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>VF10a</t>
@@ -7537,7 +7525,7 @@
       </c>
       <c r="E21" s="7" t="n"/>
     </row>
-    <row r="22" ht="15.8" customHeight="1">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>VF10b</t>
@@ -7554,7 +7542,7 @@
       </c>
       <c r="E22" s="7" t="n"/>
     </row>
-    <row r="23" ht="15.8" customHeight="1">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>VF10c</t>
@@ -7571,7 +7559,7 @@
       </c>
       <c r="E23" s="7" t="n"/>
     </row>
-    <row r="24" ht="15.8" customHeight="1">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>VF11</t>
@@ -7588,7 +7576,7 @@
       </c>
       <c r="E24" s="7" t="n"/>
     </row>
-    <row r="25" ht="15.8" customHeight="1">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>VF12</t>
@@ -7605,7 +7593,7 @@
       </c>
       <c r="E25" s="7" t="n"/>
     </row>
-    <row r="26" ht="15.8" customHeight="1">
+    <row r="26" ht="39.7" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>VF13</t>
@@ -7620,7 +7608,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.8" customHeight="1">
+    <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>VF14</t>
@@ -7637,7 +7625,7 @@
       </c>
       <c r="E27" s="7" t="n"/>
     </row>
-    <row r="28" ht="15.8" customHeight="1">
+    <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>VF15</t>
@@ -7654,7 +7642,7 @@
       </c>
       <c r="E28" s="7" t="n"/>
     </row>
-    <row r="29" ht="15.8" customHeight="1">
+    <row r="29" ht="39.7" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>VF16a</t>
@@ -7671,7 +7659,7 @@
       </c>
       <c r="E29" s="7" t="n"/>
     </row>
-    <row r="30" ht="15.8" customHeight="1">
+    <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>VF16b</t>
@@ -7688,7 +7676,7 @@
       </c>
       <c r="E30" s="7" t="n"/>
     </row>
-    <row r="31" ht="15.8" customHeight="1">
+    <row r="31" ht="39.7" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>VF17</t>
@@ -7705,7 +7693,7 @@
       </c>
       <c r="E31" s="7" t="n"/>
     </row>
-    <row r="32" ht="15.8" customHeight="1">
+    <row r="32" ht="39.7" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>VF18a</t>
@@ -7722,7 +7710,7 @@
       </c>
       <c r="E32" s="7" t="n"/>
     </row>
-    <row r="33" ht="15.8" customHeight="1">
+    <row r="33" ht="39.7" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>VF18b</t>
@@ -7739,7 +7727,7 @@
       </c>
       <c r="E33" s="7" t="n"/>
     </row>
-    <row r="34" ht="15.8" customHeight="1">
+    <row r="34" ht="39.7" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
           <t>VF18c</t>
@@ -7763,7 +7751,7 @@
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="39.7" customHeight="1">
       <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Cabezales: CBZ 01 70x70x65   |   CBZ 02 129x70x70   |   CBZ 03 144x70x70</t>
@@ -7788,22 +7776,22 @@
   <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.4" customWidth="1" min="1" max="1"/>
-    <col width="11.5" customWidth="1" min="2" max="2"/>
-    <col width="11.5" customWidth="1" min="3" max="3"/>
-    <col width="12.6" customWidth="1" min="4" max="4"/>
-    <col width="13.8" customWidth="1" min="5" max="5"/>
-    <col width="13.8" customWidth="1" min="6" max="6"/>
-    <col width="13.8" customWidth="1" min="7" max="7"/>
-    <col width="39.1" customWidth="1" min="8" max="8"/>
-    <col width="27.6" customWidth="1" min="9" max="9"/>
-    <col width="12.6" customWidth="1" min="10" max="10"/>
-    <col width="12.6" customWidth="1" min="11" max="11"/>
-    <col width="12.6" customWidth="1" min="12" max="12"/>
-    <col width="14.9" customWidth="1" min="13" max="13"/>
+    <col width="21.6" customWidth="1" min="1" max="1"/>
+    <col width="13.5" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="14.9" customWidth="1" min="4" max="4"/>
+    <col width="16.2" customWidth="1" min="5" max="5"/>
+    <col width="16.2" customWidth="1" min="6" max="6"/>
+    <col width="16.2" customWidth="1" min="7" max="7"/>
+    <col width="45.9" customWidth="1" min="8" max="8"/>
+    <col width="32.4" customWidth="1" min="9" max="9"/>
+    <col width="14.9" customWidth="1" min="10" max="10"/>
+    <col width="14.9" customWidth="1" min="11" max="11"/>
+    <col width="14.9" customWidth="1" min="12" max="12"/>
+    <col width="17.6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29.5" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="4" t="n"/>
       <c r="B1" s="15" t="inlineStr">
         <is>
@@ -7826,7 +7814,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="7" t="inlineStr">
         <is>
@@ -7845,7 +7833,7 @@
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
     </row>
-    <row r="3" ht="13" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="7" t="inlineStr">
         <is>
@@ -7864,7 +7852,7 @@
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>PLANILLA 3:   Verificacion de transmitancia termica y factor de exposicion solar de cerramientos transparentes.</t>
@@ -7883,7 +7871,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Descripcion</t>
@@ -7950,7 +7938,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15.8" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Plano: Fachada Noreste (borde derecho del plano)</t>
@@ -7969,7 +7957,7 @@
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>PV02</t>
@@ -8024,7 +8012,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>PF03</t>
@@ -8076,7 +8064,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>VA04</t>
@@ -8128,7 +8116,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>VA04 (2)</t>
@@ -8180,7 +8168,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>PV01</t>
@@ -8232,7 +8220,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>PF01</t>
@@ -8284,7 +8272,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="8" t="n"/>
@@ -8314,7 +8302,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="13" t="n"/>
       <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="n"/>
@@ -8344,7 +8332,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="15.8" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Plano: Fachada Sudoeste (borde izquierdo)</t>
@@ -8363,7 +8351,7 @@
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>VA01</t>
@@ -8418,7 +8406,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>PF01 (2)</t>
@@ -8470,7 +8458,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="9" t="n"/>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="8" t="n"/>
@@ -8500,7 +8488,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="13" t="n"/>
       <c r="B19" s="12" t="n"/>
       <c r="C19" s="12" t="n"/>
@@ -8530,7 +8518,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15.8" customHeight="1">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Plano: Fachada Sudeste (borde inferior)</t>
@@ -8549,7 +8537,7 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>PA01</t>
@@ -8604,7 +8592,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>PF04</t>
@@ -8656,7 +8644,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>VA01 (2)</t>
@@ -8708,7 +8696,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>VA05</t>
@@ -8760,7 +8748,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>PV04</t>
@@ -8812,7 +8800,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>PV04 (2)</t>
@@ -8864,7 +8852,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>PF02</t>
@@ -8916,7 +8904,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="9" t="n"/>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
@@ -8946,7 +8934,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="12" t="n"/>
       <c r="C29" s="12" t="n"/>
@@ -8976,7 +8964,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15.8" customHeight="1">
+    <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Plano: Fachada Noroeste (borde superior)</t>
@@ -8995,7 +8983,7 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
     </row>
-    <row r="31" ht="60" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>PV03</t>
@@ -9050,7 +9038,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>VA02</t>
@@ -9102,7 +9090,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
           <t>PA02</t>
@@ -9154,7 +9142,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
           <t>VA03</t>
@@ -9206,7 +9194,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
+    <row r="35" ht="70" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
           <t>PF05</t>
@@ -9258,7 +9246,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36" ht="70" customHeight="1">
       <c r="A36" s="9" t="n"/>
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
@@ -9288,7 +9276,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37" ht="70" customHeight="1">
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="12" t="n"/>
       <c r="C37" s="12" t="n"/>
@@ -9333,7 +9321,7 @@
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="22" t="inlineStr">
         <is>
           <t>COMO SE COMPLETA</t>
@@ -9352,7 +9340,7 @@
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="39.7" customHeight="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Descripcion, altura y ancho del vano: de la planilla de carpinterias.</t>
@@ -9371,7 +9359,7 @@
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="39.7" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Area del vano, area total por plano y porcentaje: se calculan solos.</t>
@@ -9390,7 +9378,7 @@
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="39.7" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Tipo de vidrio y tipo de proteccion: desplegables; sus valores estan en la hoja Datos_higro.</t>
@@ -9409,7 +9397,7 @@
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="39.7" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
           <t>Transmitancia del cerramiento: cargarla segun el vidrio y el marco adoptados.</t>
@@ -9428,7 +9416,7 @@
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
     </row>
-    <row r="44">
+    <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
         <is>
           <t>PROTECCION: la obra tiene cortinas blackout INTERIORES, y los panos fijos PF no tienen nada.</t>
@@ -9447,7 +9435,7 @@
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
     </row>
-    <row r="45">
+    <row r="45" ht="39.7" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
           <t>Una cortina interior NO computa como proteccion solar: la radiacion ya atraveso el vidrio</t>
@@ -9466,7 +9454,7 @@
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="39.7" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
         <is>
           <t>cuando llega a la cortina. La ordenanza acredita protecciones exteriores (aleros, parasoles,</t>
@@ -9485,7 +9473,7 @@
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="39.7" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
           <t>cortinas de enrollar exteriores, toldos). Por eso las veinte aberturas van Sin Proteccion.</t>
@@ -9519,7 +9507,7 @@
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="39.7" customHeight="1">
       <c r="A49" s="23" t="inlineStr">
         <is>
           <t>CONSECUENCIA: el factor de exposicion solar da 0,88 esta muy por encima del maximo de 0,30 que la ordenanza admite para</t>
@@ -9538,7 +9526,7 @@
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="39.7" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
         <is>
           <t>el cuadrante Este/Oeste, donde caen las cuatro fachadas de esta casa por estar girada 45</t>
@@ -9557,7 +9545,7 @@
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="39.7" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
           <t>grados. La verificacion de la planilla no lo controla, igual que la de la catedra, pero si lo</t>
@@ -9576,7 +9564,7 @@
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="39.7" customHeight="1">
       <c r="A52" s="23" t="inlineStr">
         <is>
           <t>presentas en el municipio esas cinco aberturas no pasarian el factor de exposicion solar.</t>
@@ -9595,7 +9583,7 @@
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="39.7" customHeight="1">
       <c r="A53" s="23" t="inlineStr">
         <is>
           <t>Hay dos salidas posibles: (a) si la abertura ocupa menos del 20% del lado expuesto del local,</t>
@@ -9614,7 +9602,7 @@
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
     </row>
-    <row r="54">
+    <row r="54" ht="39.7" customHeight="1">
       <c r="A54" s="23" t="inlineStr">
         <is>
           <t>no se verifica el FES; (b) cambiar el vidrio por uno de control solar, que baja el FES sin</t>
@@ -9633,7 +9621,7 @@
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
     </row>
-    <row r="55">
+    <row r="55" ht="39.7" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
           <t>tocar la obra. Agregar una proteccion exterior seria la tercera, pero implica obra.</t>
@@ -9667,7 +9655,7 @@
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="39.7" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
           <t>Orientacion: ya cargada. Factor de exposicion solar: se completa SOLO al elegir el tipo de</t>
@@ -9686,7 +9674,7 @@
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="39.7" customHeight="1">
       <c r="A58" s="23" t="inlineStr">
         <is>
           <t>proteccion, con los valores de la tabla de Datos_higro (Sin Proteccion 0,88; Parasol</t>
@@ -9705,7 +9693,7 @@
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="39.7" customHeight="1">
       <c r="A59" s="23" t="inlineStr">
         <is>
           <t>horizontal fijo 1:2 0,35), que son los mismos de la planilla de la catedra.</t>
@@ -9724,7 +9712,7 @@
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="39.7" customHeight="1">
       <c r="A60" s="23" t="inlineStr">
         <is>
           <t>En Datos_higro esta ademas el FES maximo admitido por cuadrante segun la ordenanza, como</t>
@@ -9743,7 +9731,7 @@
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="39.7" customHeight="1">
       <c r="A61" s="23" t="inlineStr">
         <is>
           <t>referencia: la verificacion no lo controla, igual que en la planilla de la catedra.</t>
@@ -9777,7 +9765,7 @@
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="39.7" customHeight="1">
       <c r="A63" s="23" t="inlineStr">
         <is>
           <t>CARGADO de la planilla de carpinterias: designacion, ubicacion, ancho y tipo de vidrio</t>
@@ -9796,7 +9784,7 @@
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="39.7" customHeight="1">
       <c r="A64" s="23" t="inlineStr">
         <is>
           <t>(DVH 6+9+3+3, carpinteria de aluminio linea A30 pintado negro, igual en todas las aberturas).</t>
@@ -9830,7 +9818,7 @@
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n"/>
     </row>
-    <row r="66">
+    <row r="66" ht="39.7" customHeight="1">
       <c r="A66" s="23" t="inlineStr">
         <is>
           <t>ALTURAS: medidas sobre el dibujo de las vistas de la planilla de carpinterias, con la escala</t>
@@ -9849,7 +9837,7 @@
       <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="39.7" customHeight="1">
       <c r="A67" s="23" t="inlineStr">
         <is>
           <t>verificada contra los anchos acotados (error menor a 2 cm). La mayoria de las aberturas son de</t>
@@ -9868,7 +9856,7 @@
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n"/>
     </row>
-    <row r="68">
+    <row r="68" ht="39.7" customHeight="1">
       <c r="A68" s="23" t="inlineStr">
         <is>
           <t>piso a cielorraso, 3,00 m. VERIFICARLAS contra el plano antes de presentar.</t>
@@ -9887,7 +9875,7 @@
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="2" t="n"/>
     </row>
-    <row r="69">
+    <row r="69" ht="39.7" customHeight="1">
       <c r="A69" s="23" t="inlineStr">
         <is>
           <t>PF04 es la unica con antepecho: arranca a 1,09 y mide 0,60 de alto. El resto llega al piso.</t>
@@ -9906,7 +9894,7 @@
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n"/>
     </row>
-    <row r="70">
+    <row r="70" ht="39.7" customHeight="1">
       <c r="A70" s="23" t="inlineStr">
         <is>
           <t>Las alturas de PV01 (3,00), PF04 (0,60) y PV04 (2) (2,95) las aporto el autor del proyecto.</t>
@@ -9940,7 +9928,7 @@
       <c r="L71" s="2" t="n"/>
       <c r="M71" s="2" t="n"/>
     </row>
-    <row r="72">
+    <row r="72" ht="39.7" customHeight="1">
       <c r="A72" s="23" t="inlineStr">
         <is>
           <t>ORIENTACION: el simbolo de norte del plano (circulo con aguja, en el patio interno) apunta a</t>
@@ -9959,7 +9947,7 @@
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
     </row>
-    <row r="73">
+    <row r="73" ht="39.7" customHeight="1">
       <c r="A73" s="23" t="inlineStr">
         <is>
           <t>45 grados hacia arriba y a la derecha de la hoja. Entonces las cuatro fachadas NO son N-S-E-O</t>
@@ -9978,7 +9966,7 @@
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
     </row>
-    <row r="74">
+    <row r="74" ht="39.7" customHeight="1">
       <c r="A74" s="23" t="inlineStr">
         <is>
           <t>sino: arriba = Noroeste, derecha = Noreste, abajo = Sudeste, izquierda = Sudoeste.</t>
@@ -9997,7 +9985,7 @@
       <c r="L74" s="2" t="n"/>
       <c r="M74" s="2" t="n"/>
     </row>
-    <row r="75">
+    <row r="75" ht="39.7" customHeight="1">
       <c r="A75" s="23" t="inlineStr">
         <is>
           <t>Cada abertura se asigno a la fachada por su posicion en planta. Las del patio interno se</t>
@@ -10016,7 +10004,7 @@
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
     </row>
-    <row r="76">
+    <row r="76" ht="39.7" customHeight="1">
       <c r="A76" s="23" t="inlineStr">
         <is>
           <t>orientan por la pared en la que estan: miran hacia adentro del patio.</t>
@@ -10035,7 +10023,7 @@
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
     </row>
-    <row r="77">
+    <row r="77" ht="39.7" customHeight="1">
       <c r="A77" s="23" t="inlineStr">
         <is>
           <t>Los rotulos Dormitorio Norte y Dormitorio Sur del plano no coinciden con el norte real;</t>
@@ -10054,7 +10042,7 @@
       <c r="L77" s="2" t="n"/>
       <c r="M77" s="2" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="39.7" customHeight="1">
       <c r="A78" s="23" t="inlineStr">
         <is>
           <t>parecen ser nombres de uso, no orientaciones.</t>
@@ -10088,7 +10076,7 @@
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="39.7" customHeight="1">
       <c r="A80" s="23" t="inlineStr">
         <is>
           <t>CANTIDADES: la planilla de carpinterias trae la cantidad de cada abertura. Tres van dos veces:</t>
@@ -10107,7 +10095,7 @@
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n"/>
     </row>
-    <row r="81">
+    <row r="81" ht="39.7" customHeight="1">
       <c r="A81" s="23" t="inlineStr">
         <is>
           <t>VA01 (01 Cocina y 09 Suite), VA04 (13 Dormitorio Norte y 14 Play Room) y PF01 (03 Lavadero y</t>
@@ -10126,7 +10114,7 @@
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
     </row>
-    <row r="82">
+    <row r="82" ht="39.7" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
         <is>
           <t>07 Hall de ingreso, a los dos lados del patio interno). Por eso la planilla tiene 20 filas y</t>
@@ -10145,7 +10133,7 @@
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
     </row>
-    <row r="83">
+    <row r="83" ht="39.7" customHeight="1">
       <c r="A83" s="23" t="inlineStr">
         <is>
           <t>no 17. Las demas aberturas son de una sola unidad.</t>
@@ -10179,7 +10167,7 @@
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="2" t="n"/>
     </row>
-    <row r="85">
+    <row r="85" ht="39.7" customHeight="1">
       <c r="A85" s="23" t="inlineStr">
         <is>
           <t>Las puertas interiores de madera PM01 a PM08 no se cargan: no son cerramientos exteriores.</t>
@@ -10213,7 +10201,7 @@
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" ht="39.7" customHeight="1">
       <c r="A87" s="23" t="inlineStr">
         <is>
           <t>DATO DE CONTRASTE: la planilla de iluminacion y ventilacion da la superficie vidriada</t>
@@ -10232,7 +10220,7 @@
       <c r="L87" s="2" t="n"/>
       <c r="M87" s="2" t="n"/>
     </row>
-    <row r="88">
+    <row r="88" ht="39.7" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
         <is>
           <t>proyectada de cada local. La suma da 97,4 m2, que es el orden de magnitud que deberia</t>
@@ -10251,7 +10239,7 @@
       <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="39.7" customHeight="1">
       <c r="A89" s="23" t="inlineStr">
         <is>
           <t>dar el total de vanos de los cuatro planos. Sirve para controlar que no falte ninguno.</t>
@@ -10288,10 +10276,10 @@
     <mergeCell ref="B1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="M6:M37">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"CUMPLE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"NO CUMPLE"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10321,43 +10309,43 @@
   <dimension ref="A1:AH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.5" customWidth="1" min="1" max="1"/>
-    <col width="12.6" customWidth="1" min="2" max="2"/>
-    <col width="9.199999999999999" customWidth="1" min="3" max="3"/>
-    <col width="10.3" customWidth="1" min="4" max="4"/>
-    <col width="36.8" customWidth="1" min="5" max="5"/>
-    <col width="10.3" customWidth="1" min="6" max="6"/>
-    <col width="10.3" customWidth="1" min="7" max="7"/>
-    <col width="13.8" customWidth="1" min="8" max="8"/>
-    <col width="13.8" customWidth="1" min="9" max="9"/>
-    <col width="6.9" customWidth="1" min="10" max="10"/>
-    <col width="6.9" customWidth="1" min="11" max="11"/>
-    <col width="6.9" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="5.8" customWidth="1" min="14" max="14"/>
-    <col width="6.9" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="5.8" customWidth="1" min="17" max="17"/>
-    <col width="6.9" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6.9" customWidth="1" min="21" max="21"/>
-    <col width="9.199999999999999" customWidth="1" min="22" max="22"/>
-    <col width="17.2" customWidth="1" min="23" max="23"/>
-    <col width="39.1" customWidth="1" min="24" max="24"/>
-    <col width="19.5" customWidth="1" min="25" max="25"/>
-    <col width="12.6" customWidth="1" min="26" max="26"/>
-    <col width="9.199999999999999" customWidth="1" min="27" max="27"/>
-    <col width="11.5" customWidth="1" min="28" max="28"/>
-    <col width="11.5" customWidth="1" min="29" max="29"/>
-    <col width="12.6" customWidth="1" min="30" max="30"/>
-    <col width="9.199999999999999" customWidth="1" min="31" max="31"/>
-    <col width="9.199999999999999" customWidth="1" min="32" max="32"/>
-    <col width="9.199999999999999" customWidth="1" min="33" max="33"/>
-    <col width="8" customWidth="1" min="34" max="34"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
+    <col width="14.9" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="3" max="3"/>
+    <col width="12.2" customWidth="1" min="4" max="4"/>
+    <col width="43.2" customWidth="1" min="5" max="5"/>
+    <col width="12.2" customWidth="1" min="6" max="6"/>
+    <col width="12.2" customWidth="1" min="7" max="7"/>
+    <col width="16.2" customWidth="1" min="8" max="8"/>
+    <col width="16.2" customWidth="1" min="9" max="9"/>
+    <col width="8.1" customWidth="1" min="10" max="10"/>
+    <col width="8.1" customWidth="1" min="11" max="11"/>
+    <col width="8.1" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="6.8" customWidth="1" min="14" max="14"/>
+    <col width="8.1" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
+    <col width="6.8" customWidth="1" min="17" max="17"/>
+    <col width="8.1" customWidth="1" min="18" max="18"/>
+    <col width="9.5" customWidth="1" min="19" max="19"/>
+    <col width="9.5" customWidth="1" min="20" max="20"/>
+    <col width="8.1" customWidth="1" min="21" max="21"/>
+    <col width="10.8" customWidth="1" min="22" max="22"/>
+    <col width="20.2" customWidth="1" min="23" max="23"/>
+    <col width="45.9" customWidth="1" min="24" max="24"/>
+    <col width="23" customWidth="1" min="25" max="25"/>
+    <col width="14.9" customWidth="1" min="26" max="26"/>
+    <col width="10.8" customWidth="1" min="27" max="27"/>
+    <col width="13.5" customWidth="1" min="28" max="28"/>
+    <col width="13.5" customWidth="1" min="29" max="29"/>
+    <col width="14.9" customWidth="1" min="30" max="30"/>
+    <col width="10.8" customWidth="1" min="31" max="31"/>
+    <col width="10.8" customWidth="1" min="32" max="32"/>
+    <col width="10.8" customWidth="1" min="33" max="33"/>
+    <col width="9.5" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>VIGAS  H°A°        H-21        ACERO 42/50</t>
@@ -10397,7 +10385,7 @@
       <c r="AG1" s="2" t="n"/>
       <c r="AH1" s="2" t="n"/>
     </row>
-    <row r="2" ht="29.5" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>NIVEL</t>
@@ -10493,7 +10481,7 @@
       <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
@@ -10637,7 +10625,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>PA</t>
@@ -10758,7 +10746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="19" t="n"/>
       <c r="B5" s="16" t="inlineStr">
         <is>
@@ -10875,7 +10863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="19" t="n"/>
       <c r="B6" s="16" t="inlineStr">
         <is>
@@ -10992,7 +10980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="19" t="n"/>
       <c r="B7" s="16" t="inlineStr">
         <is>
@@ -11105,7 +11093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="16" t="inlineStr">
         <is>
@@ -11226,7 +11214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="16" t="inlineStr">
         <is>
@@ -11339,7 +11327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="16" t="inlineStr">
         <is>
@@ -11460,7 +11448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="16" t="inlineStr">
         <is>
@@ -11577,7 +11565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="16" t="inlineStr">
         <is>
@@ -11694,7 +11682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="16" t="inlineStr">
         <is>
@@ -11815,7 +11803,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="19" t="n"/>
       <c r="B14" s="16" t="inlineStr">
         <is>
@@ -11928,7 +11916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="19" t="n"/>
       <c r="B15" s="16" t="inlineStr">
         <is>
@@ -12045,7 +12033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="19" t="n"/>
       <c r="B16" s="16" t="inlineStr">
         <is>
@@ -12166,7 +12154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="19" t="n"/>
       <c r="B17" s="16" t="inlineStr">
         <is>
@@ -12279,7 +12267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="19" t="n"/>
       <c r="B18" s="16" t="inlineStr">
         <is>
@@ -12392,7 +12380,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="19" t="n"/>
       <c r="B19" s="16" t="inlineStr">
         <is>
@@ -12505,7 +12493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="19" t="n"/>
       <c r="B20" s="16" t="inlineStr">
         <is>
@@ -12622,7 +12610,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="19" t="n"/>
       <c r="B21" s="16" t="inlineStr">
         <is>
@@ -12739,7 +12727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="19" t="n"/>
       <c r="B22" s="16" t="inlineStr">
         <is>
@@ -12856,7 +12844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="19" t="n"/>
       <c r="B23" s="16" t="inlineStr">
         <is>
@@ -12973,7 +12961,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="19" t="n"/>
       <c r="B24" s="16" t="inlineStr">
         <is>
@@ -13090,7 +13078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="20" t="n"/>
       <c r="B25" s="26" t="inlineStr">
         <is>
@@ -13207,7 +13195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>TECHO</t>
@@ -13324,7 +13312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="19" t="n"/>
       <c r="B27" s="16" t="inlineStr">
         <is>
@@ -13437,7 +13425,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="19" t="n"/>
       <c r="B28" s="16" t="inlineStr">
         <is>
@@ -13550,7 +13538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="19" t="n"/>
       <c r="B29" s="16" t="inlineStr">
         <is>
@@ -13663,7 +13651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="19" t="n"/>
       <c r="B30" s="16" t="inlineStr">
         <is>
@@ -13780,7 +13768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="19" t="n"/>
       <c r="B31" s="16" t="inlineStr">
         <is>
@@ -13897,7 +13885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="19" t="n"/>
       <c r="B32" s="16" t="inlineStr">
         <is>
@@ -14010,7 +13998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="19" t="n"/>
       <c r="B33" s="16" t="inlineStr">
         <is>
@@ -14123,7 +14111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="20" t="n"/>
       <c r="B34" s="26" t="inlineStr">
         <is>
@@ -14301,29 +14289,29 @@
   <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.3" customWidth="1" min="1" max="1"/>
-    <col width="11.5" customWidth="1" min="2" max="2"/>
-    <col width="10.3" customWidth="1" min="3" max="3"/>
-    <col width="14.9" customWidth="1" min="4" max="4"/>
-    <col width="10.3" customWidth="1" min="5" max="5"/>
-    <col width="36.8" customWidth="1" min="6" max="6"/>
-    <col width="6.9" customWidth="1" min="7" max="7"/>
-    <col width="6.9" customWidth="1" min="8" max="8"/>
-    <col width="13.8" customWidth="1" min="9" max="9"/>
-    <col width="9.199999999999999" customWidth="1" min="10" max="10"/>
-    <col width="6.9" customWidth="1" min="11" max="11"/>
-    <col width="9.199999999999999" customWidth="1" min="12" max="12"/>
-    <col width="9.199999999999999" customWidth="1" min="13" max="13"/>
-    <col width="6.9" customWidth="1" min="14" max="14"/>
-    <col width="9.199999999999999" customWidth="1" min="15" max="15"/>
-    <col width="10.3" customWidth="1" min="16" max="16"/>
-    <col width="10.3" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="11.5" customWidth="1" min="19" max="19"/>
-    <col width="9.199999999999999" customWidth="1" min="20" max="20"/>
+    <col width="12.2" customWidth="1" min="1" max="1"/>
+    <col width="13.5" customWidth="1" min="2" max="2"/>
+    <col width="12.2" customWidth="1" min="3" max="3"/>
+    <col width="17.6" customWidth="1" min="4" max="4"/>
+    <col width="12.2" customWidth="1" min="5" max="5"/>
+    <col width="43.2" customWidth="1" min="6" max="6"/>
+    <col width="8.1" customWidth="1" min="7" max="7"/>
+    <col width="8.1" customWidth="1" min="8" max="8"/>
+    <col width="16.2" customWidth="1" min="9" max="9"/>
+    <col width="10.8" customWidth="1" min="10" max="10"/>
+    <col width="8.1" customWidth="1" min="11" max="11"/>
+    <col width="10.8" customWidth="1" min="12" max="12"/>
+    <col width="10.8" customWidth="1" min="13" max="13"/>
+    <col width="8.1" customWidth="1" min="14" max="14"/>
+    <col width="10.8" customWidth="1" min="15" max="15"/>
+    <col width="12.2" customWidth="1" min="16" max="16"/>
+    <col width="12.2" customWidth="1" min="17" max="17"/>
+    <col width="54" customWidth="1" min="18" max="18"/>
+    <col width="13.5" customWidth="1" min="19" max="19"/>
+    <col width="10.8" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>LOSAS DE H°A°   H-21   ACERO 42/50</t>
@@ -14349,7 +14337,7 @@
       <c r="S1" s="2" t="n"/>
       <c r="T1" s="2" t="n"/>
     </row>
-    <row r="2" ht="29.5" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>NIVEL</t>
@@ -14419,7 +14407,7 @@
       </c>
       <c r="T2" s="4" t="n"/>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
@@ -14497,7 +14485,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>S/PB</t>
@@ -14569,7 +14557,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="19" t="n"/>
       <c r="B5" s="16" t="inlineStr">
         <is>
@@ -14641,7 +14629,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="19" t="n"/>
       <c r="B6" s="16" t="inlineStr">
         <is>
@@ -14709,7 +14697,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="19" t="n"/>
       <c r="B7" s="16" t="inlineStr">
         <is>
@@ -14777,7 +14765,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="16" t="inlineStr">
         <is>
@@ -14845,7 +14833,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="16" t="inlineStr">
         <is>
@@ -14913,7 +14901,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="16" t="inlineStr">
         <is>
@@ -14987,7 +14975,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="16" t="inlineStr">
         <is>
@@ -15061,7 +15049,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="20" t="n"/>
       <c r="B12" s="26" t="inlineStr">
         <is>
@@ -15133,7 +15121,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>S/PA</t>
@@ -15205,7 +15193,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="19" t="n"/>
       <c r="B14" s="16" t="inlineStr">
         <is>
@@ -15279,7 +15267,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="20" t="n"/>
       <c r="B15" s="26" t="inlineStr">
         <is>
@@ -15394,27 +15382,27 @@
   <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.3" customWidth="1" min="1" max="1"/>
-    <col width="11.5" customWidth="1" min="2" max="2"/>
-    <col width="11.5" customWidth="1" min="3" max="3"/>
-    <col width="11.5" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="9.199999999999999" customWidth="1" min="7" max="7"/>
-    <col width="9.199999999999999" customWidth="1" min="8" max="8"/>
-    <col width="6.9" customWidth="1" min="9" max="9"/>
-    <col width="6.9" customWidth="1" min="10" max="10"/>
-    <col width="6.9" customWidth="1" min="11" max="11"/>
-    <col width="9.199999999999999" customWidth="1" min="12" max="12"/>
-    <col width="16.1" customWidth="1" min="13" max="13"/>
-    <col width="48.3" customWidth="1" min="14" max="14"/>
-    <col width="10.3" customWidth="1" min="15" max="15"/>
-    <col width="11.5" customWidth="1" min="16" max="16"/>
-    <col width="10.3" customWidth="1" min="17" max="17"/>
-    <col width="13.8" customWidth="1" min="18" max="18"/>
+    <col width="12.2" customWidth="1" min="1" max="1"/>
+    <col width="13.5" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="10.8" customWidth="1" min="7" max="7"/>
+    <col width="10.8" customWidth="1" min="8" max="8"/>
+    <col width="8.1" customWidth="1" min="9" max="9"/>
+    <col width="8.1" customWidth="1" min="10" max="10"/>
+    <col width="8.1" customWidth="1" min="11" max="11"/>
+    <col width="10.8" customWidth="1" min="12" max="12"/>
+    <col width="18.9" customWidth="1" min="13" max="13"/>
+    <col width="56.7" customWidth="1" min="14" max="14"/>
+    <col width="12.2" customWidth="1" min="15" max="15"/>
+    <col width="13.5" customWidth="1" min="16" max="16"/>
+    <col width="12.2" customWidth="1" min="17" max="17"/>
+    <col width="16.2" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="32" t="inlineStr">
         <is>
           <t>COLUMNAS  H°A°        H-21        ACERO 42/50</t>
@@ -15438,7 +15426,7 @@
       <c r="Q1" s="2" t="n"/>
       <c r="R1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>NIVEL</t>
@@ -15498,7 +15486,7 @@
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
@@ -15566,7 +15554,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>PA</t>
@@ -15635,7 +15623,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="19" t="n"/>
       <c r="B5" s="16" t="inlineStr">
         <is>
@@ -15700,7 +15688,7 @@
         <v>22.55</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="19" t="n"/>
       <c r="B6" s="16" t="inlineStr">
         <is>
@@ -15765,7 +15753,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="20" t="n"/>
       <c r="B7" s="26" t="inlineStr">
         <is>
@@ -15830,7 +15818,7 @@
         <v>20.35</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>PB</t>
@@ -15899,7 +15887,7 @@
         <v>2.49</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="16" t="inlineStr">
         <is>
@@ -15964,7 +15952,7 @@
         <v>29.46</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="16" t="inlineStr">
         <is>
@@ -16029,7 +16017,7 @@
         <v>13.89</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="16" t="inlineStr">
         <is>
@@ -16094,7 +16082,7 @@
         <v>10.28</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="16" t="inlineStr">
         <is>
@@ -16159,7 +16147,7 @@
         <v>15.96</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="16" t="inlineStr">
         <is>
@@ -16224,7 +16212,7 @@
         <v>35.39</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="19" t="n"/>
       <c r="B14" s="16" t="inlineStr">
         <is>
@@ -16289,7 +16277,7 @@
         <v>37.78</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="19" t="n"/>
       <c r="B15" s="16" t="inlineStr">
         <is>
@@ -16354,7 +16342,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="20" t="n"/>
       <c r="B16" s="26" t="inlineStr">
         <is>
@@ -16474,35 +16462,35 @@
   <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.6" customWidth="1" min="1" max="1"/>
-    <col width="10.3" customWidth="1" min="2" max="2"/>
-    <col width="19.5" customWidth="1" min="3" max="3"/>
-    <col width="10.3" customWidth="1" min="4" max="4"/>
-    <col width="36.8" customWidth="1" min="5" max="5"/>
-    <col width="10.3" customWidth="1" min="6" max="6"/>
-    <col width="10.3" customWidth="1" min="7" max="7"/>
-    <col width="13.8" customWidth="1" min="8" max="8"/>
-    <col width="13.8" customWidth="1" min="9" max="9"/>
-    <col width="6.9" customWidth="1" min="10" max="10"/>
-    <col width="6.9" customWidth="1" min="11" max="11"/>
-    <col width="6.9" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="5.8" customWidth="1" min="14" max="14"/>
-    <col width="6.9" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="5.8" customWidth="1" min="17" max="17"/>
-    <col width="6.9" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6.9" customWidth="1" min="21" max="21"/>
-    <col width="9.199999999999999" customWidth="1" min="22" max="22"/>
-    <col width="17.2" customWidth="1" min="23" max="23"/>
-    <col width="46" customWidth="1" min="24" max="24"/>
-    <col width="9.199999999999999" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="14.9" customWidth="1" min="1" max="1"/>
+    <col width="12.2" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="12.2" customWidth="1" min="4" max="4"/>
+    <col width="43.2" customWidth="1" min="5" max="5"/>
+    <col width="12.2" customWidth="1" min="6" max="6"/>
+    <col width="12.2" customWidth="1" min="7" max="7"/>
+    <col width="16.2" customWidth="1" min="8" max="8"/>
+    <col width="16.2" customWidth="1" min="9" max="9"/>
+    <col width="8.1" customWidth="1" min="10" max="10"/>
+    <col width="8.1" customWidth="1" min="11" max="11"/>
+    <col width="8.1" customWidth="1" min="12" max="12"/>
+    <col width="9.5" customWidth="1" min="13" max="13"/>
+    <col width="6.8" customWidth="1" min="14" max="14"/>
+    <col width="8.1" customWidth="1" min="15" max="15"/>
+    <col width="9.5" customWidth="1" min="16" max="16"/>
+    <col width="6.8" customWidth="1" min="17" max="17"/>
+    <col width="8.1" customWidth="1" min="18" max="18"/>
+    <col width="9.5" customWidth="1" min="19" max="19"/>
+    <col width="9.5" customWidth="1" min="20" max="20"/>
+    <col width="8.1" customWidth="1" min="21" max="21"/>
+    <col width="10.8" customWidth="1" min="22" max="22"/>
+    <col width="20.2" customWidth="1" min="23" max="23"/>
+    <col width="54" customWidth="1" min="24" max="24"/>
+    <col width="10.8" customWidth="1" min="25" max="25"/>
+    <col width="9.5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>VIGAS DE FUNDACION  H°A°        H-21        ACERO 42/50</t>
@@ -16534,7 +16522,7 @@
       <c r="Y1" s="2" t="n"/>
       <c r="Z1" s="2" t="n"/>
     </row>
-    <row r="2" ht="29.5" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>POSICION</t>
@@ -16618,7 +16606,7 @@
       </c>
       <c r="Z2" s="4" t="n"/>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="5" t="inlineStr">
@@ -16726,7 +16714,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>VF01 (1)</t>
@@ -16817,7 +16805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>VF01 (2)</t>
@@ -16908,7 +16896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>VF01 (3)</t>
@@ -16999,7 +16987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>VF02</t>
@@ -17098,7 +17086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>VF03</t>
@@ -17193,7 +17181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>VF04a</t>
@@ -17288,7 +17276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>VF04b</t>
@@ -17379,7 +17367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>VF04c</t>
@@ -17470,7 +17458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>VF05</t>
@@ -17565,7 +17553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>VF06a</t>
@@ -17656,7 +17644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>VF06b</t>
@@ -17747,7 +17735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>VF06c</t>
@@ -17838,7 +17826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>VF06d</t>
@@ -17929,7 +17917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>VF07</t>
@@ -18024,7 +18012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>VF08</t>
@@ -18123,7 +18111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>VF09 (1)</t>
@@ -18214,7 +18202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>VF09 (2)</t>
@@ -18305,7 +18293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>VF10a</t>
@@ -18400,7 +18388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="70" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>VF10b</t>
@@ -18495,7 +18483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>VF10c</t>
@@ -18590,7 +18578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="70" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>VF11</t>
@@ -18689,7 +18677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="70" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>VF12</t>
@@ -18784,7 +18772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="70" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>VF13</t>
@@ -18879,7 +18867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>VF14</t>
@@ -18978,7 +18966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>VF15</t>
@@ -19073,7 +19061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>VF16a</t>
@@ -19168,7 +19156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="70" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>VF16b</t>
@@ -19259,7 +19247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>VF17</t>
@@ -19354,7 +19342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>VF18a</t>
@@ -19449,7 +19437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="70" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>VF18b</t>
@@ -19540,7 +19528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
+    <row r="34" ht="70" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
           <t>VF18c</t>
@@ -19693,24 +19681,24 @@
   <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.5" customWidth="1" min="1" max="1"/>
-    <col width="14.9" customWidth="1" min="2" max="2"/>
-    <col width="9.199999999999999" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="12.6" customWidth="1" min="7" max="7"/>
-    <col width="12.6" customWidth="1" min="8" max="8"/>
-    <col width="10.3" customWidth="1" min="9" max="9"/>
-    <col width="9.199999999999999" customWidth="1" min="10" max="10"/>
-    <col width="10.3" customWidth="1" min="11" max="11"/>
-    <col width="12.6" customWidth="1" min="12" max="12"/>
-    <col width="12.6" customWidth="1" min="13" max="13"/>
-    <col width="16.1" customWidth="1" min="14" max="14"/>
-    <col width="50.6" customWidth="1" min="15" max="15"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="10.8" customWidth="1" min="3" max="3"/>
+    <col width="9.5" customWidth="1" min="4" max="4"/>
+    <col width="9.5" customWidth="1" min="5" max="5"/>
+    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="14.9" customWidth="1" min="7" max="7"/>
+    <col width="14.9" customWidth="1" min="8" max="8"/>
+    <col width="12.2" customWidth="1" min="9" max="9"/>
+    <col width="10.8" customWidth="1" min="10" max="10"/>
+    <col width="12.2" customWidth="1" min="11" max="11"/>
+    <col width="14.9" customWidth="1" min="12" max="12"/>
+    <col width="14.9" customWidth="1" min="13" max="13"/>
+    <col width="18.9" customWidth="1" min="14" max="14"/>
+    <col width="59.4" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
           <t>PILOTES Y CABEZALES  H°A°        H-21        ACERO 42/50        TODOS LOS PILOTES Ø30  h = -4,50 m</t>
@@ -19731,7 +19719,7 @@
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>POSICION</t>
@@ -19780,7 +19768,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.5" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
@@ -19837,7 +19825,7 @@
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
     </row>
-    <row r="4" ht="52" customHeight="1">
+    <row r="4" ht="62" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>CB1</t>
@@ -19896,7 +19884,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>CB2</t>
@@ -19955,7 +19943,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1">
+    <row r="6" ht="62" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>CB3</t>
@@ -20014,7 +20002,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
+    <row r="7" ht="62" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>CB4</t>
@@ -20073,7 +20061,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="62" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>CB5</t>
@@ -20132,7 +20120,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>CB6</t>
@@ -20191,7 +20179,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>CB7</t>
@@ -20250,7 +20238,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>CB8</t>
@@ -20309,7 +20297,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
           <t>CB9</t>
@@ -20385,7 +20373,7 @@
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Los 33 pilotes del plano: 13 bajo cabezales de columna (los de esta tabla) y 20 repartidos bajo las vigas de fundacion.</t>
@@ -20443,26 +20431,26 @@
   <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9.199999999999999" customWidth="1" min="1" max="1"/>
-    <col width="11.5" customWidth="1" min="2" max="2"/>
-    <col width="11.5" customWidth="1" min="3" max="3"/>
-    <col width="11.5" customWidth="1" min="4" max="4"/>
-    <col width="9.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="9.199999999999999" customWidth="1" min="6" max="6"/>
-    <col width="9.199999999999999" customWidth="1" min="7" max="7"/>
-    <col width="6.9" customWidth="1" min="8" max="8"/>
-    <col width="12.6" customWidth="1" min="9" max="9"/>
-    <col width="9.199999999999999" customWidth="1" min="10" max="10"/>
-    <col width="6.9" customWidth="1" min="11" max="11"/>
-    <col width="12.6" customWidth="1" min="12" max="12"/>
-    <col width="11.5" customWidth="1" min="13" max="13"/>
-    <col width="13.8" customWidth="1" min="14" max="14"/>
-    <col width="11.5" customWidth="1" min="15" max="15"/>
-    <col width="14.9" customWidth="1" min="16" max="16"/>
-    <col width="50.6" customWidth="1" min="17" max="17"/>
+    <col width="10.8" customWidth="1" min="1" max="1"/>
+    <col width="13.5" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="10.8" customWidth="1" min="5" max="5"/>
+    <col width="10.8" customWidth="1" min="6" max="6"/>
+    <col width="10.8" customWidth="1" min="7" max="7"/>
+    <col width="8.1" customWidth="1" min="8" max="8"/>
+    <col width="14.9" customWidth="1" min="9" max="9"/>
+    <col width="10.8" customWidth="1" min="10" max="10"/>
+    <col width="8.1" customWidth="1" min="11" max="11"/>
+    <col width="14.9" customWidth="1" min="12" max="12"/>
+    <col width="13.5" customWidth="1" min="13" max="13"/>
+    <col width="16.2" customWidth="1" min="14" max="14"/>
+    <col width="13.5" customWidth="1" min="15" max="15"/>
+    <col width="17.6" customWidth="1" min="16" max="16"/>
+    <col width="59.4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TABIQUES  H°A°        H-21        ACERO III        espesor 12 cm</t>
@@ -20485,7 +20473,7 @@
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16" customHeight="1">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>NIVEL</t>
@@ -20540,7 +20528,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.5" customHeight="1">
+    <row r="3" ht="39.7" customHeight="1">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
@@ -20607,7 +20595,7 @@
       </c>
       <c r="Q3" s="4" t="n"/>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="70" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>PB</t>
@@ -20672,7 +20660,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="70" customHeight="1">
       <c r="A5" s="19" t="n"/>
       <c r="B5" s="16" t="inlineStr">
         <is>
@@ -20733,7 +20721,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="70" customHeight="1">
       <c r="A6" s="19" t="n"/>
       <c r="B6" s="16" t="inlineStr">
         <is>
@@ -20794,7 +20782,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="70" customHeight="1">
       <c r="A7" s="19" t="n"/>
       <c r="B7" s="16" t="inlineStr">
         <is>
@@ -20855,7 +20843,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="16" t="inlineStr">
         <is>
@@ -20916,7 +20904,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="16" t="inlineStr">
         <is>
@@ -20977,7 +20965,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
+    <row r="10" ht="70" customHeight="1">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="16" t="inlineStr">
         <is>
@@ -21038,7 +21026,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="20" t="n"/>
       <c r="B11" s="26" t="inlineStr">
         <is>
@@ -21099,7 +21087,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="70" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>PA</t>
@@ -21164,7 +21152,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="16" t="inlineStr">
         <is>
@@ -21225,7 +21213,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="19" t="n"/>
       <c r="B14" s="16" t="inlineStr">
         <is>
@@ -21286,7 +21274,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="19" t="n"/>
       <c r="B15" s="16" t="inlineStr">
         <is>
@@ -21347,7 +21335,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="70" customHeight="1">
       <c r="A16" s="20" t="n"/>
       <c r="B16" s="26" t="inlineStr">
         <is>
@@ -21427,7 +21415,7 @@
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
           <t>T1 a T6: cargas y dimensiones tomadas de la planilla de la catedra. Probablemente sean cargas de servicio; compararlas contra fi Pn, que es resistencia ultima, queda del lado inseguro en torno a un 40 por ciento. Con utilizaciones del 10 al 20 por ciento no cambia ningun veredicto, pero conviene saberlo.</t>
@@ -21450,7 +21438,7 @@
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
           <t>T7 y T8: carga tomada de la reaccion de VI 02 y VI 11a en la planilla de vigas, que son MAYORADAS. El criterio no es el mismo que en T1 a T6.</t>
@@ -21473,7 +21461,7 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
           <t>Direccion de la carga: como todas las vigas son invertidas, sobresalen 70 cm por encima del fondo de losa, mientras que los tabiques de planta alta llegan desde el piso hasta ese fondo. El tabique queda debajo y sostiene a la viga, no al reves.</t>
@@ -21496,7 +21484,7 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
           <t>T9 a T13: dimensiones del computo metrico. Las cargas son las reacciones de las vigas de techo que apoyan en cada uno, aportadas por el proyectista: T9 recibe VI 14, T10 recibe VI 12, T11 recibe VI 13b y T12 recibe VI 17 mas VI 15b. T13 no recibe vigas: continua el tabique T06c de planta baja.</t>
@@ -21519,7 +21507,7 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Area: si B es menor o igual al espesor el tabique es recto y el area es A x B; si no, es un tabique en L y el area es (A + B - espesor) x espesor.</t>
@@ -21542,7 +21530,7 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
           <t>fi Pn = 0,55 x 0,65 x f'c x area x [1 - (altura / 32 espesor)^2]   muro portante de hormigon armado con reduccion por esbeltez.</t>
@@ -21565,7 +21553,7 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Armadura vertical en doble malla y horizontal en malla simple, ambas o8 c/20, iguales a las de la planilla de la catedra.</t>
@@ -21628,15 +21616,15 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39.1" customWidth="1" min="1" max="1"/>
-    <col width="14.9" customWidth="1" min="2" max="2"/>
-    <col width="11.5" customWidth="1" min="3" max="3"/>
-    <col width="17.2" customWidth="1" min="4" max="4"/>
-    <col width="17.2" customWidth="1" min="5" max="5"/>
-    <col width="64.40000000000001" customWidth="1" min="6" max="6"/>
+    <col width="45.9" customWidth="1" min="1" max="1"/>
+    <col width="17.6" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="3" max="3"/>
+    <col width="20.2" customWidth="1" min="4" max="4"/>
+    <col width="20.2" customWidth="1" min="5" max="5"/>
+    <col width="75.59999999999999" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="39.7" customHeight="1">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>DATOS DE PARTIDA - HIPOTESIS DE CALCULO</t>
@@ -21648,7 +21636,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="39.7" customHeight="1">
       <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Celdas verdes: editables. La planilla recalcula sola.</t>
@@ -21668,7 +21656,7 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
     </row>
-    <row r="4" ht="15.8" customHeight="1">
+    <row r="4" ht="39.7" customHeight="1">
       <c r="A4" s="33" t="inlineStr">
         <is>
           <t>MATERIALES</t>
@@ -21688,7 +21676,7 @@
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1">
+    <row r="5" ht="39.7" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Hormigon H-21   f'c</t>
@@ -21706,7 +21694,7 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
     </row>
-    <row r="6" ht="14.5" customHeight="1">
+    <row r="6" ht="39.7" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Acero 42/50   fy</t>
@@ -21724,7 +21712,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
     </row>
-    <row r="7" ht="14.5" customHeight="1">
+    <row r="7" ht="39.7" customHeight="1">
       <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Peso especifico H.A.</t>
@@ -21742,7 +21730,7 @@
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1">
+    <row r="8" ht="39.7" customHeight="1">
       <c r="A8" s="34" t="inlineStr">
         <is>
           <t>phi flexion</t>
@@ -21760,7 +21748,7 @@
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1">
+    <row r="9" ht="39.7" customHeight="1">
       <c r="A9" s="34" t="inlineStr">
         <is>
           <t>phi corte</t>
@@ -21778,7 +21766,7 @@
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
     </row>
-    <row r="10" ht="14.5" customHeight="1">
+    <row r="10" ht="39.7" customHeight="1">
       <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Coef. mayoracion permanente</t>
@@ -21796,7 +21784,7 @@
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1">
+    <row r="11" ht="39.7" customHeight="1">
       <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Coef. mayoracion sobrecarga</t>
@@ -21822,7 +21810,7 @@
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
     </row>
-    <row r="13" ht="15.8" customHeight="1">
+    <row r="13" ht="39.7" customHeight="1">
       <c r="A13" s="33" t="inlineStr">
         <is>
           <t>PAQUETES DE CARGA</t>
@@ -21854,7 +21842,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="27" customHeight="1">
+    <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="35" t="inlineStr">
         <is>
           <t>PA</t>
@@ -21878,7 +21866,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="27" customHeight="1">
+    <row r="15" ht="39.7" customHeight="1">
       <c r="A15" s="35" t="inlineStr">
         <is>
           <t>TECHO</t>
@@ -21902,7 +21890,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="14.5" customHeight="1">
+    <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Mamposteria sobre viga</t>
@@ -21932,7 +21920,7 @@
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
     </row>
-    <row r="18" ht="15.8" customHeight="1">
+    <row r="18" ht="39.7" customHeight="1">
       <c r="A18" s="33" t="inlineStr">
         <is>
           <t>COEFICIENTES SEGUN ESQUEMA</t>
@@ -21960,7 +21948,7 @@
       </c>
       <c r="F18" s="2" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="39.7" customHeight="1">
       <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Simplemente apoyada</t>
@@ -21980,7 +21968,7 @@
       </c>
       <c r="F19" s="2" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="39.7" customHeight="1">
       <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Continua</t>
@@ -22000,7 +21988,7 @@
       </c>
       <c r="F20" s="2" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="39.7" customHeight="1">
       <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Empotrada-apoyada</t>
@@ -22020,7 +22008,7 @@
       </c>
       <c r="F21" s="2" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="39.7" customHeight="1">
       <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Biempotrada</t>
@@ -22040,7 +22028,7 @@
       </c>
       <c r="F22" s="2" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Voladizo</t>
@@ -22068,7 +22056,7 @@
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="22" t="inlineStr">
         <is>
           <t>p = 1,2 g + 1,6 q    |    M = coef x p x L2    |    R = coef x p x L</t>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -6055,7 +6055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56.7" customWidth="1" min="1" max="1"/>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Caldaia Lux 700</t>
+          <t>Peisa Tropical 80-500</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>
@@ -6261,11 +6261,11 @@
     <row r="14" ht="39.7" customHeight="1">
       <c r="A14" s="38" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion del radiador</t>
+          <t>Kcal/h por elemento del radiador</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="D14" s="38" t="inlineStr">
         <is>
-          <t>Caldaia Lux 700. Cambiar segun catalogo.</t>
+          <t>Peisa Tropical 80-500, valor de catalogo a salto termico 60 C.</t>
         </is>
       </c>
     </row>
@@ -6294,14 +6294,14 @@
       </c>
       <c r="D15" s="38" t="inlineStr">
         <is>
-          <t>Del formulario modelo.</t>
+          <t>Pasa del salto de catalogo (60 C) al de la instalacion (66 C). (66/60)^1,3 = 1,13.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="39.7" customHeight="1">
       <c r="A16" s="38" t="inlineStr">
         <is>
-          <t>Ancho de cada seccion</t>
+          <t>Ancho de cada elemento</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D16" s="38" t="inlineStr">
         <is>
-          <t>Caldaia Lux 700.</t>
+          <t>Peisa Tropical: 80 mm por elemento.</t>
         </is>
       </c>
     </row>
@@ -6555,33 +6555,33 @@
     <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>4. Confirmar el radiador y sus Kcal/h por seccion.</t>
+          <t>4. Nada: el radiador ya esta cargado (Peisa Tropical 80-500, aluminio inyectado en blanco,</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n"/>
     </row>
-    <row r="40">
-      <c r="A40" s="23" t="inlineStr"/>
+    <row r="40" ht="39.7" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   245 kcal/h por elemento, 80 mm de ancho, 575 mm de alto, 0,375 l por elemento).</t>
+        </is>
+      </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
     </row>
-    <row r="41" ht="39.7" customHeight="1">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t>LO QUE YA VIENE CARGADO</t>
-        </is>
-      </c>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr"/>
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
     </row>
     <row r="42" ht="39.7" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>- Superficie y volumen de cada local, de la planilla de iluminacion y ventilacion.</t>
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>LO QUE YA VIENE CARGADO</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>
@@ -6591,7 +6591,7 @@
     <row r="43" ht="39.7" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>- Las aberturas de cada local con su medida real, del campo UBICACION de la planilla de</t>
+          <t>- Superficie y volumen de cada local, de la planilla de iluminacion y ventilacion.</t>
         </is>
       </c>
       <c r="B43" s="2" t="n"/>
@@ -6601,7 +6601,7 @@
     <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  carpinterias. Son 17 aberturas repartidas en 13 locales.</t>
+          <t>- Las aberturas de cada local con su medida real, del campo UBICACION de la planilla de</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
@@ -6611,7 +6611,7 @@
     <row r="45" ht="39.7" customHeight="1">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>- Techo y piso segun la planta: en PB entrepiso arriba y piso sobre tierra; en PA techo</t>
+          <t xml:space="preserve">  carpinterias. Son 17 aberturas repartidas en 13 locales.</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
@@ -6621,7 +6621,7 @@
     <row r="46" ht="39.7" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  aislado arriba y piso sobre local ocupado. Si algun local no es asi, mover el area de renglon.</t>
+          <t>- Techo y piso segun la planta: en PB entrepiso arriba y piso sobre tierra; en PA techo</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -6631,28 +6631,38 @@
     <row r="47" ht="39.7" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>- Infiltracion segun la cantidad de paredes exteriores que se estimo para cada local.</t>
+          <t xml:space="preserve">  aislado arriba y piso sobre local ocupado. Si algun local no es asi, mover el area de renglon.</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n"/>
     </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr"/>
+    <row r="48" ht="39.7" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>- Infiltracion segun la cantidad de paredes exteriores que se estimo para cada local.</t>
+        </is>
+      </c>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n"/>
     </row>
-    <row r="49" ht="39.7" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>La altura de local adoptada es 3.00 m, de los cortes de la planilla de carpinterias.</t>
-        </is>
-      </c>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr"/>
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="39.7" customHeight="1">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>La altura de local adoptada es 3.00 m, de los cortes de la planilla de carpinterias.</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23522,7 +23532,7 @@
       <c r="A34" s="9" t="n"/>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C34" s="8">
@@ -23540,7 +23550,7 @@
       <c r="A35" s="9" t="n"/>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C35" s="25">
@@ -24318,7 +24328,7 @@
       <c r="A69" s="9" t="n"/>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C69" s="8">
@@ -24336,7 +24346,7 @@
       <c r="A70" s="9" t="n"/>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C70" s="25">
@@ -25084,7 +25094,7 @@
       <c r="A103" s="9" t="n"/>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C103" s="8">
@@ -25102,7 +25112,7 @@
       <c r="A104" s="9" t="n"/>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C104" s="25">
@@ -25846,7 +25856,7 @@
       <c r="A137" s="9" t="n"/>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C137" s="8">
@@ -25864,7 +25874,7 @@
       <c r="A138" s="9" t="n"/>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C138" s="25">
@@ -26642,7 +26652,7 @@
       <c r="A172" s="9" t="n"/>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C172" s="8">
@@ -26660,7 +26670,7 @@
       <c r="A173" s="9" t="n"/>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C173" s="25">
@@ -27408,7 +27418,7 @@
       <c r="A206" s="9" t="n"/>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C206" s="8">
@@ -27426,7 +27436,7 @@
       <c r="A207" s="9" t="n"/>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C207" s="25">
@@ -28170,7 +28180,7 @@
       <c r="A240" s="9" t="n"/>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C240" s="8">
@@ -28188,7 +28198,7 @@
       <c r="A241" s="9" t="n"/>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C241" s="25">
@@ -28966,7 +28976,7 @@
       <c r="A275" s="9" t="n"/>
       <c r="B275" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C275" s="8">
@@ -28984,7 +28994,7 @@
       <c r="A276" s="9" t="n"/>
       <c r="B276" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C276" s="25">
@@ -29732,7 +29742,7 @@
       <c r="A309" s="9" t="n"/>
       <c r="B309" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C309" s="8">
@@ -29750,7 +29760,7 @@
       <c r="A310" s="9" t="n"/>
       <c r="B310" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C310" s="25">
@@ -30528,7 +30538,7 @@
       <c r="A344" s="9" t="n"/>
       <c r="B344" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C344" s="8">
@@ -30546,7 +30556,7 @@
       <c r="A345" s="9" t="n"/>
       <c r="B345" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C345" s="25">
@@ -31290,7 +31300,7 @@
       <c r="A378" s="9" t="n"/>
       <c r="B378" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C378" s="8">
@@ -31308,7 +31318,7 @@
       <c r="A379" s="9" t="n"/>
       <c r="B379" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C379" s="25">
@@ -32056,7 +32066,7 @@
       <c r="A412" s="9" t="n"/>
       <c r="B412" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por seccion</t>
+          <t>Kcal/h por elemento</t>
         </is>
       </c>
       <c r="C412" s="8">
@@ -32074,7 +32084,7 @@
       <c r="A413" s="9" t="n"/>
       <c r="B413" s="10" t="inlineStr">
         <is>
-          <t>Secciones necesarias</t>
+          <t>Elementos necesarios</t>
         </is>
       </c>
       <c r="C413" s="25">

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -6055,7 +6055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56.7" customWidth="1" min="1" max="1"/>
@@ -6318,68 +6318,82 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
+    <row r="17" ht="39.7" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>TOALLEROS (banos)</t>
+        </is>
+      </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
     </row>
     <row r="18" ht="39.7" customHeight="1">
-      <c r="A18" s="22" t="inlineStr">
-        <is>
-          <t>FACTORES DE PERDIDA (Kcal/h por m2, o por m3 en infiltracion)</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t>Toallero Scala / Domino 80</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>632</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Kcal/h</t>
+        </is>
+      </c>
+      <c r="D18" s="38" t="inlineStr">
+        <is>
+          <t>500 x 800 mm. Valor de catalogo a 60 C.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="39.7" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
-        <is>
-          <t>elemento</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>factor</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-    </row>
-    <row r="20" ht="39.7" customHeight="1">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t>Ventana</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>60</v>
-      </c>
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t>Toallero Scala / Domino 150</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Kcal/h</t>
+        </is>
+      </c>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>500 x 1500 mm. Valor de catalogo a 60 C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
     </row>
     <row r="21" ht="39.7" customHeight="1">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t>Pared exterior aislada</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>FACTORES DE PERDIDA (Kcal/h por m2, o por m3 en infiltracion)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
     </row>
     <row r="22" ht="39.7" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>Pared interior</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>25</v>
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>elemento</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
@@ -6387,11 +6401,11 @@
     <row r="23" ht="39.7" customHeight="1">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>Techo no aislado</t>
+          <t>Ventana</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
@@ -6399,7 +6413,7 @@
     <row r="24" ht="39.7" customHeight="1">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>Techo aislado</t>
+          <t>Pared exterior aislada</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
@@ -6411,11 +6425,11 @@
     <row r="25" ht="39.7" customHeight="1">
       <c r="A25" s="38" t="inlineStr">
         <is>
-          <t>Techo entrepiso</t>
+          <t>Pared interior</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
@@ -6423,11 +6437,11 @@
     <row r="26" ht="39.7" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>Piso sobre tierra</t>
+          <t>Techo no aislado</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
@@ -6435,11 +6449,11 @@
     <row r="27" ht="39.7" customHeight="1">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>Piso sobre local ocupado</t>
+          <t>Techo aislado</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
@@ -6447,11 +6461,11 @@
     <row r="28" ht="39.7" customHeight="1">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>Infiltracion, una pared exterior</t>
+          <t>Techo entrepiso</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
@@ -6459,11 +6473,11 @@
     <row r="29" ht="39.7" customHeight="1">
       <c r="A29" s="38" t="inlineStr">
         <is>
-          <t>Infiltracion, dos paredes exteriores</t>
+          <t>Piso sobre tierra</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
@@ -6471,71 +6485,77 @@
     <row r="30" ht="39.7" customHeight="1">
       <c r="A30" s="38" t="inlineStr">
         <is>
-          <t>Infiltracion, tres o mas paredes exteriores</t>
+          <t>Piso sobre local ocupado</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
+    <row r="31" ht="39.7" customHeight="1">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>Infiltracion, una pared exterior</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
     </row>
     <row r="32" ht="39.7" customHeight="1">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>Los factores estan escritos en cada renglon del formulario, no se leen de aca: esta tabla es solo de referencia.</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>Infiltracion, dos paredes exteriores</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
+    <row r="33" ht="39.7" customHeight="1">
+      <c r="A33" s="38" t="inlineStr">
+        <is>
+          <t>Infiltracion, tres o mas paredes exteriores</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>12</v>
+      </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
     </row>
-    <row r="34" ht="39.7" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>QUE FALTA CARGAR</t>
-        </is>
-      </c>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
       <c r="B34" s="2" t="n"/>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
     </row>
     <row r="35" ht="39.7" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>1. Las longitudes de pared de cada local, en las columnas H (largo) e I (alto) del formulario.</t>
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Los factores estan escritos en cada renglon del formulario, no se leen de aca: esta tabla es solo de referencia.</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n"/>
     </row>
-    <row r="36" ht="39.7" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Las celdas estan en naranja. Al cargarlas se completan solas la dimension, el area y la perdida.</t>
-        </is>
-      </c>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n"/>
     </row>
     <row r="37" ht="39.7" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>2. Si el muro es aislado o no: el formulario trae tres renglones de cada tipo, borrar los que sobren.</t>
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>QUE FALTA CARGAR</t>
         </is>
       </c>
       <c r="B37" s="2" t="n"/>
@@ -6545,7 +6565,7 @@
     <row r="38" ht="39.7" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
         <is>
-          <t>3. Las tablas de FO y FZ de la catedra. Por ahora los dos valen 1,00.</t>
+          <t>1. Las longitudes de pared de cada local, en las columnas H (largo) e I (alto) del formulario.</t>
         </is>
       </c>
       <c r="B38" s="2" t="n"/>
@@ -6555,7 +6575,7 @@
     <row r="39" ht="39.7" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>4. Nada: el radiador ya esta cargado (Peisa Tropical 80-500, aluminio inyectado en blanco,</t>
+          <t xml:space="preserve">   Las celdas estan en naranja. Al cargarlas se completan solas la dimension, el area y la perdida.</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -6565,23 +6585,27 @@
     <row r="40" ht="39.7" customHeight="1">
       <c r="A40" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   245 kcal/h por elemento, 80 mm de ancho, 575 mm de alto, 0,375 l por elemento).</t>
+          <t>2. Si el muro es aislado o no: el formulario trae tres renglones de cada tipo, borrar los que sobren.</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
     </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr"/>
+    <row r="41" ht="39.7" customHeight="1">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>3. Las tablas de FO y FZ de la catedra. Por ahora los dos valen 1,00.</t>
+        </is>
+      </c>
       <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
     </row>
     <row r="42" ht="39.7" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>LO QUE YA VIENE CARGADO</t>
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>4. Nada: el radiador ya esta cargado (Peisa Tropical 80-500, aluminio inyectado en blanco,</t>
         </is>
       </c>
       <c r="B42" s="2" t="n"/>
@@ -6591,7 +6615,7 @@
     <row r="43" ht="39.7" customHeight="1">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>- Superficie y volumen de cada local, de la planilla de iluminacion y ventilacion.</t>
+          <t xml:space="preserve">   245 kcal/h por elemento, 80 mm de ancho, 575 mm de alto, 0,375 l por elemento).</t>
         </is>
       </c>
       <c r="B43" s="2" t="n"/>
@@ -6601,27 +6625,23 @@
     <row r="44" ht="39.7" customHeight="1">
       <c r="A44" s="23" t="inlineStr">
         <is>
-          <t>- Las aberturas de cada local con su medida real, del campo UBICACION de la planilla de</t>
+          <t xml:space="preserve">   En los tres banos va toallero Peisa Scala o Domino en vez de radiador de elementos.</t>
         </is>
       </c>
       <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
     </row>
-    <row r="45" ht="39.7" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  carpinterias. Son 17 aberturas repartidas en 13 locales.</t>
-        </is>
-      </c>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr"/>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n"/>
     </row>
     <row r="46" ht="39.7" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
-        <is>
-          <t>- Techo y piso segun la planta: en PB entrepiso arriba y piso sobre tierra; en PA techo</t>
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>LO QUE YA VIENE CARGADO</t>
         </is>
       </c>
       <c r="B46" s="2" t="n"/>
@@ -6631,7 +6651,7 @@
     <row r="47" ht="39.7" customHeight="1">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  aislado arriba y piso sobre local ocupado. Si algun local no es asi, mover el area de renglon.</t>
+          <t>- Superficie y volumen de cada local, de la planilla de iluminacion y ventilacion.</t>
         </is>
       </c>
       <c r="B47" s="2" t="n"/>
@@ -6641,15 +6661,19 @@
     <row r="48" ht="39.7" customHeight="1">
       <c r="A48" s="23" t="inlineStr">
         <is>
-          <t>- Infiltracion segun la cantidad de paredes exteriores que se estimo para cada local.</t>
+          <t>- Las aberturas de cada local con su medida real, del campo UBICACION de la planilla de</t>
         </is>
       </c>
       <c r="B48" s="2" t="n"/>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n"/>
     </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr"/>
+    <row r="49" ht="39.7" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  carpinterias. Son 17 aberturas repartidas en 13 locales.</t>
+        </is>
+      </c>
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n"/>
@@ -6657,12 +6681,48 @@
     <row r="50" ht="39.7" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>La altura de local adoptada es 3.00 m, de los cortes de la planilla de carpinterias.</t>
+          <t>- Techo y piso segun la planta: en PB entrepiso arriba y piso sobre tierra; en PA techo</t>
         </is>
       </c>
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="39.7" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  aislado arriba y piso sobre local ocupado. Si algun local no es asi, mover el area de renglon.</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="39.7" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>- Infiltracion segun la cantidad de paredes exteriores que se estimo para cada local.</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+    </row>
+    <row r="54" ht="39.7" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>La altura de local adoptada es 3.00 m, de los cortes de la planilla de carpinterias.</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27418,11 +27478,11 @@
       <c r="A206" s="9" t="n"/>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C206" s="8">
-        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C206" s="25">
+        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D206" s="2" t="n"/>
@@ -27436,11 +27496,11 @@
       <c r="A207" s="9" t="n"/>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C207" s="25">
-        <f>ROUNDUP(F203/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D207" s="2" t="n"/>
@@ -27450,15 +27510,15 @@
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="2" t="n"/>
     </row>
-    <row r="208" ht="39.7" customHeight="1">
+    <row r="208" ht="47" customHeight="1">
       <c r="A208" s="9" t="n"/>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C208" s="25">
-        <f>ROUNDUP(F203/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+        <f>IF(F203&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F203/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
         <v/>
       </c>
       <c r="D208" s="2" t="n"/>
@@ -27468,15 +27528,15 @@
       <c r="H208" s="2" t="n"/>
       <c r="I208" s="2" t="n"/>
     </row>
-    <row r="209" ht="39.7" customHeight="1">
+    <row r="209" ht="47" customHeight="1">
       <c r="A209" s="13" t="n"/>
       <c r="B209" s="14" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
+          <t>Toallero adoptado</t>
         </is>
       </c>
       <c r="C209" s="13">
-        <f>Datos_balance!$B$13</f>
+        <f>IF(F203&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
         <v/>
       </c>
       <c r="D209" s="20" t="n"/>
@@ -28180,11 +28240,11 @@
       <c r="A240" s="9" t="n"/>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C240" s="8">
-        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C240" s="25">
+        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D240" s="2" t="n"/>
@@ -28198,11 +28258,11 @@
       <c r="A241" s="9" t="n"/>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C241" s="25">
-        <f>ROUNDUP(F237/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D241" s="2" t="n"/>
@@ -28212,15 +28272,15 @@
       <c r="H241" s="2" t="n"/>
       <c r="I241" s="2" t="n"/>
     </row>
-    <row r="242" ht="39.7" customHeight="1">
+    <row r="242" ht="47" customHeight="1">
       <c r="A242" s="9" t="n"/>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C242" s="25">
-        <f>ROUNDUP(F237/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+        <f>IF(F237&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F237/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
         <v/>
       </c>
       <c r="D242" s="2" t="n"/>
@@ -28230,15 +28290,15 @@
       <c r="H242" s="2" t="n"/>
       <c r="I242" s="2" t="n"/>
     </row>
-    <row r="243" ht="39.7" customHeight="1">
+    <row r="243" ht="47" customHeight="1">
       <c r="A243" s="13" t="n"/>
       <c r="B243" s="14" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
+          <t>Toallero adoptado</t>
         </is>
       </c>
       <c r="C243" s="13">
-        <f>Datos_balance!$B$13</f>
+        <f>IF(F237&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
         <v/>
       </c>
       <c r="D243" s="20" t="n"/>
@@ -32066,11 +32126,11 @@
       <c r="A412" s="9" t="n"/>
       <c r="B412" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C412" s="8">
-        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
+        </is>
+      </c>
+      <c r="C412" s="25">
+        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D412" s="2" t="n"/>
@@ -32084,11 +32144,11 @@
       <c r="A413" s="9" t="n"/>
       <c r="B413" s="10" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
         </is>
       </c>
       <c r="C413" s="25">
-        <f>ROUNDUP(F409/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D413" s="2" t="n"/>
@@ -32098,15 +32158,15 @@
       <c r="H413" s="2" t="n"/>
       <c r="I413" s="2" t="n"/>
     </row>
-    <row r="414" ht="39.7" customHeight="1">
+    <row r="414" ht="47" customHeight="1">
       <c r="A414" s="9" t="n"/>
       <c r="B414" s="10" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
+          <t>Toalleros necesarios</t>
         </is>
       </c>
       <c r="C414" s="25">
-        <f>ROUNDUP(F409/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+        <f>IF(F409&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F409/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
         <v/>
       </c>
       <c r="D414" s="2" t="n"/>
@@ -32116,15 +32176,15 @@
       <c r="H414" s="2" t="n"/>
       <c r="I414" s="2" t="n"/>
     </row>
-    <row r="415" ht="39.7" customHeight="1">
+    <row r="415" ht="47" customHeight="1">
       <c r="A415" s="13" t="n"/>
       <c r="B415" s="14" t="inlineStr">
         <is>
-          <t>Radiador adoptado</t>
+          <t>Toallero adoptado</t>
         </is>
       </c>
       <c r="C415" s="13">
-        <f>Datos_balance!$B$13</f>
+        <f>IF(F409&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
         <v/>
       </c>
       <c r="D415" s="20" t="n"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -25486,7 +25486,7 @@
       </c>
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="35" t="n">
-        <v>3.38</v>
+        <v>5.25</v>
       </c>
       <c r="I118" s="35" t="n">
         <v>3</v>
@@ -25516,7 +25516,7 @@
       </c>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="35" t="n">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="I119" s="35" t="n">
         <v>3</v>
@@ -25546,7 +25546,7 @@
       </c>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="35" t="n">
-        <v>3.38</v>
+        <v>5.25</v>
       </c>
       <c r="I120" s="35" t="n">
         <v>3</v>
@@ -25576,7 +25576,7 @@
       </c>
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="35" t="n">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="I121" s="35" t="n">
         <v>3</v>
@@ -25660,7 +25660,7 @@
         </is>
       </c>
       <c r="D125" s="8" t="n">
-        <v>5.88</v>
+        <v>5.72</v>
       </c>
       <c r="E125" s="25" t="n">
         <v>15</v>
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>5.88</v>
+        <v>5.72</v>
       </c>
       <c r="E127" s="25" t="n">
         <v>10</v>
@@ -25773,11 +25773,11 @@
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>5.88 m2 x 3.00</t>
+          <t>5.72 m2 x 3.00</t>
         </is>
       </c>
       <c r="D130" s="8" t="n">
-        <v>17.64</v>
+        <v>17.16</v>
       </c>
       <c r="E130" s="25" t="n">
         <v>6</v>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -42,7 +42,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Vigas de fundacion'!$A$1:$X$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Pilotes y cabezales'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Tabiques'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Balance termico'!$A$1:$F$418</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Balance termico'!$A$1:$F$420</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22778,7 +22778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I415"/>
+  <dimension ref="A1:I417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.1" customWidth="1" min="1" max="1"/>
@@ -30930,7 +30930,7 @@
       </c>
       <c r="G359" s="2" t="n"/>
       <c r="H359" s="35" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="I359" s="35" t="n">
         <v>3</v>
@@ -30960,7 +30960,7 @@
       </c>
       <c r="G360" s="2" t="n"/>
       <c r="H360" s="35" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="I360" s="35" t="n">
         <v>3</v>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="G361" s="2" t="n"/>
       <c r="H361" s="35" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="I361" s="35" t="n">
         <v>3</v>
@@ -31020,85 +31020,96 @@
       </c>
       <c r="G362" s="2" t="n"/>
       <c r="H362" s="35" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="I362" s="35" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="363" ht="39.7" customHeight="1">
-      <c r="A363" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B363" s="33" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C363" s="9" t="n"/>
-      <c r="D363" s="9" t="n"/>
-      <c r="E363" s="9" t="n"/>
-      <c r="F363" s="9" t="n"/>
+    <row r="363" ht="62" customHeight="1">
+      <c r="A363" s="9" t="n"/>
+      <c r="B363" s="34" t="inlineStr">
+        <is>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C363" s="9">
+        <f>IF(COUNT(H363,I363)&lt;2,"",TEXT(H363,"0.00")&amp;" x "&amp;TEXT(I363,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D363" s="8">
+        <f>IF(COUNT(H363,I363)&lt;2,"",ROUND(H363*I363,2))</f>
+        <v/>
+      </c>
+      <c r="E363" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F363" s="28">
+        <f>IF(D363="","",ROUND(D363*E363,1))</f>
+        <v/>
+      </c>
       <c r="G363" s="2" t="n"/>
-      <c r="H363" s="2" t="n"/>
-      <c r="I363" s="2" t="n"/>
+      <c r="H363" s="35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I363" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="364" ht="62" customHeight="1">
       <c r="A364" s="9" t="n"/>
       <c r="B364" s="34" t="inlineStr">
         <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C364" s="9" t="inlineStr"/>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C364" s="9">
+        <f>IF(COUNT(H364,I364)&lt;2,"",TEXT(H364,"0.00")&amp;" x "&amp;TEXT(I364,"0.00"))</f>
+        <v/>
+      </c>
       <c r="D364" s="8">
         <f>IF(COUNT(H364,I364)&lt;2,"",ROUND(H364*I364,2))</f>
         <v/>
       </c>
       <c r="E364" s="25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F364" s="28">
         <f>IF(D364="","",ROUND(D364*E364,1))</f>
         <v/>
       </c>
       <c r="G364" s="2" t="n"/>
-      <c r="H364" s="35" t="n"/>
-      <c r="I364" s="35" t="n"/>
+      <c r="H364" s="35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I364" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="365" ht="39.7" customHeight="1">
-      <c r="A365" s="9" t="n"/>
-      <c r="B365" s="34" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C365" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D365" s="8" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E365" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F365" s="28">
-        <f>IF(D365="","",ROUND(D365*E365,1))</f>
-        <v/>
-      </c>
+      <c r="A365" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B365" s="33" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C365" s="9" t="n"/>
+      <c r="D365" s="9" t="n"/>
+      <c r="E365" s="9" t="n"/>
+      <c r="F365" s="9" t="n"/>
       <c r="G365" s="2" t="n"/>
-      <c r="H365" s="35" t="n"/>
-      <c r="I365" s="35" t="n"/>
+      <c r="H365" s="2" t="n"/>
+      <c r="I365" s="2" t="n"/>
     </row>
     <row r="366" ht="62" customHeight="1">
       <c r="A366" s="9" t="n"/>
       <c r="B366" s="34" t="inlineStr">
         <is>
-          <t>TECHO ENTREPISO</t>
+          <t>TECHO NO AISLADO</t>
         </is>
       </c>
       <c r="C366" s="9" t="inlineStr"/>
@@ -31107,7 +31118,7 @@
         <v/>
       </c>
       <c r="E366" s="25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F366" s="28">
         <f>IF(D366="","",ROUND(D366*E366,1))</f>
@@ -31118,29 +31129,36 @@
       <c r="I366" s="35" t="n"/>
     </row>
     <row r="367" ht="39.7" customHeight="1">
-      <c r="A367" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B367" s="33" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C367" s="9" t="n"/>
-      <c r="D367" s="9" t="n"/>
-      <c r="E367" s="9" t="n"/>
-      <c r="F367" s="9" t="n"/>
+      <c r="A367" s="9" t="n"/>
+      <c r="B367" s="34" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C367" s="9" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D367" s="8" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E367" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F367" s="28">
+        <f>IF(D367="","",ROUND(D367*E367,1))</f>
+        <v/>
+      </c>
       <c r="G367" s="2" t="n"/>
-      <c r="H367" s="2" t="n"/>
-      <c r="I367" s="2" t="n"/>
+      <c r="H367" s="35" t="n"/>
+      <c r="I367" s="35" t="n"/>
     </row>
     <row r="368" ht="62" customHeight="1">
       <c r="A368" s="9" t="n"/>
       <c r="B368" s="34" t="inlineStr">
         <is>
-          <t>SOBRE TIERRA</t>
+          <t>TECHO ENTREPISO</t>
         </is>
       </c>
       <c r="C368" s="9" t="inlineStr"/>
@@ -31149,7 +31167,7 @@
         <v/>
       </c>
       <c r="E368" s="25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F368" s="28">
         <f>IF(D368="","",ROUND(D368*E368,1))</f>
@@ -31160,71 +31178,64 @@
       <c r="I368" s="35" t="n"/>
     </row>
     <row r="369" ht="39.7" customHeight="1">
-      <c r="A369" s="9" t="n"/>
-      <c r="B369" s="34" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C369" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D369" s="8" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E369" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="F369" s="28">
-        <f>IF(D369="","",ROUND(D369*E369,1))</f>
-        <v/>
-      </c>
+      <c r="A369" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B369" s="33" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C369" s="9" t="n"/>
+      <c r="D369" s="9" t="n"/>
+      <c r="E369" s="9" t="n"/>
+      <c r="F369" s="9" t="n"/>
       <c r="G369" s="2" t="n"/>
-      <c r="H369" s="35" t="n"/>
-      <c r="I369" s="35" t="n"/>
-    </row>
-    <row r="370" ht="39.7" customHeight="1">
-      <c r="A370" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B370" s="33" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C370" s="9" t="n"/>
-      <c r="D370" s="16" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E370" s="9" t="n"/>
-      <c r="F370" s="9" t="n"/>
+      <c r="H369" s="2" t="n"/>
+      <c r="I369" s="2" t="n"/>
+    </row>
+    <row r="370" ht="62" customHeight="1">
+      <c r="A370" s="9" t="n"/>
+      <c r="B370" s="34" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C370" s="9" t="inlineStr"/>
+      <c r="D370" s="8">
+        <f>IF(COUNT(H370,I370)&lt;2,"",ROUND(H370*I370,2))</f>
+        <v/>
+      </c>
+      <c r="E370" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F370" s="28">
+        <f>IF(D370="","",ROUND(D370*E370,1))</f>
+        <v/>
+      </c>
       <c r="G370" s="2" t="n"/>
-      <c r="H370" s="2" t="n"/>
-      <c r="I370" s="2" t="n"/>
+      <c r="H370" s="35" t="n"/>
+      <c r="I370" s="35" t="n"/>
     </row>
     <row r="371" ht="39.7" customHeight="1">
       <c r="A371" s="9" t="n"/>
       <c r="B371" s="34" t="inlineStr">
         <is>
-          <t>UNA PARED EXTERIOR</t>
+          <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
       <c r="C371" s="9" t="inlineStr">
         <is>
-          <t>5.85 m2 x 3.00</t>
+          <t>por croquis</t>
         </is>
       </c>
       <c r="D371" s="8" t="n">
-        <v>17.55</v>
+        <v>7.23</v>
       </c>
       <c r="E371" s="25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F371" s="28">
         <f>IF(D371="","",ROUND(D371*E371,1))</f>
@@ -31234,43 +31245,46 @@
       <c r="H371" s="35" t="n"/>
       <c r="I371" s="35" t="n"/>
     </row>
-    <row r="372" ht="62" customHeight="1">
-      <c r="A372" s="9" t="n"/>
-      <c r="B372" s="34" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C372" s="9" t="inlineStr"/>
-      <c r="D372" s="8">
-        <f>IF(COUNT(H372,I372)&lt;2,"",ROUND(H372*I372,2))</f>
-        <v/>
-      </c>
-      <c r="E372" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F372" s="28">
-        <f>IF(D372="","",ROUND(D372*E372,1))</f>
-        <v/>
-      </c>
+    <row r="372" ht="39.7" customHeight="1">
+      <c r="A372" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B372" s="33" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C372" s="9" t="n"/>
+      <c r="D372" s="16" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E372" s="9" t="n"/>
+      <c r="F372" s="9" t="n"/>
       <c r="G372" s="2" t="n"/>
-      <c r="H372" s="35" t="n"/>
-      <c r="I372" s="35" t="n"/>
-    </row>
-    <row r="373" ht="62" customHeight="1">
+      <c r="H372" s="2" t="n"/>
+      <c r="I372" s="2" t="n"/>
+    </row>
+    <row r="373" ht="39.7" customHeight="1">
       <c r="A373" s="9" t="n"/>
       <c r="B373" s="34" t="inlineStr">
         <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C373" s="9" t="inlineStr"/>
-      <c r="D373" s="8">
-        <f>IF(COUNT(H373,I373)&lt;2,"",ROUND(H373*I373,2))</f>
-        <v/>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C373" s="9" t="inlineStr">
+        <is>
+          <t>7.23 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D373" s="8" t="n">
+        <v>21.69</v>
       </c>
       <c r="E373" s="25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F373" s="28">
         <f>IF(D373="","",ROUND(D373*E373,1))</f>
@@ -31280,109 +31294,119 @@
       <c r="H373" s="35" t="n"/>
       <c r="I373" s="35" t="n"/>
     </row>
-    <row r="374" ht="70" customHeight="1">
-      <c r="A374" s="16" t="inlineStr">
+    <row r="374" ht="62" customHeight="1">
+      <c r="A374" s="9" t="n"/>
+      <c r="B374" s="34" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C374" s="9" t="inlineStr"/>
+      <c r="D374" s="8">
+        <f>IF(COUNT(H374,I374)&lt;2,"",ROUND(H374*I374,2))</f>
+        <v/>
+      </c>
+      <c r="E374" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F374" s="28">
+        <f>IF(D374="","",ROUND(D374*E374,1))</f>
+        <v/>
+      </c>
+      <c r="G374" s="2" t="n"/>
+      <c r="H374" s="35" t="n"/>
+      <c r="I374" s="35" t="n"/>
+    </row>
+    <row r="375" ht="62" customHeight="1">
+      <c r="A375" s="9" t="n"/>
+      <c r="B375" s="34" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C375" s="9" t="inlineStr"/>
+      <c r="D375" s="8">
+        <f>IF(COUNT(H375,I375)&lt;2,"",ROUND(H375*I375,2))</f>
+        <v/>
+      </c>
+      <c r="E375" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F375" s="28">
+        <f>IF(D375="","",ROUND(D375*E375,1))</f>
+        <v/>
+      </c>
+      <c r="G375" s="2" t="n"/>
+      <c r="H375" s="35" t="n"/>
+      <c r="I375" s="35" t="n"/>
+    </row>
+    <row r="376" ht="70" customHeight="1">
+      <c r="A376" s="16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B374" s="33" t="inlineStr">
+      <c r="B376" s="33" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C374" s="9" t="n"/>
-      <c r="D374" s="9" t="n"/>
-      <c r="E374" s="9" t="n"/>
-      <c r="F374" s="36">
-        <f>IF(F353="",0,F353)+IF(F355="",0,F355)+IF(F356="",0,F356)+IF(F357="",0,F357)+IF(F358="",0,F358)+IF(F359="",0,F359)+IF(F360="",0,F360)+IF(F361="",0,F361)+IF(F362="",0,F362)+IF(F364="",0,F364)+IF(F365="",0,F365)+IF(F366="",0,F366)+IF(F368="",0,F368)+IF(F369="",0,F369)+IF(F371="",0,F371)+IF(F372="",0,F372)+IF(F373="",0,F373)</f>
-        <v/>
-      </c>
-      <c r="G374" s="2" t="n"/>
-      <c r="H374" s="2" t="n"/>
-      <c r="I374" s="2" t="n"/>
-    </row>
-    <row r="375" ht="47" customHeight="1">
-      <c r="A375" s="16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B375" s="33" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C375" s="9">
-        <f>TEXT(F374,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
-        <v/>
-      </c>
-      <c r="D375" s="2" t="n"/>
-      <c r="E375" s="2" t="n"/>
-      <c r="F375" s="36">
-        <f>ROUND(F374*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
-        <v/>
-      </c>
-      <c r="G375" s="2" t="n"/>
-      <c r="H375" s="2" t="n"/>
-      <c r="I375" s="2" t="n"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="2" t="n"/>
-      <c r="B376" s="2" t="n"/>
-      <c r="C376" s="2" t="n"/>
-      <c r="D376" s="2" t="n"/>
-      <c r="E376" s="2" t="n"/>
-      <c r="F376" s="2" t="n"/>
+      <c r="C376" s="9" t="n"/>
+      <c r="D376" s="9" t="n"/>
+      <c r="E376" s="9" t="n"/>
+      <c r="F376" s="36">
+        <f>IF(F353="",0,F353)+IF(F355="",0,F355)+IF(F356="",0,F356)+IF(F357="",0,F357)+IF(F358="",0,F358)+IF(F359="",0,F359)+IF(F360="",0,F360)+IF(F361="",0,F361)+IF(F362="",0,F362)+IF(F363="",0,F363)+IF(F364="",0,F364)+IF(F366="",0,F366)+IF(F367="",0,F367)+IF(F368="",0,F368)+IF(F370="",0,F370)+IF(F371="",0,F371)+IF(F373="",0,F373)+IF(F374="",0,F374)+IF(F375="",0,F375)</f>
+        <v/>
+      </c>
       <c r="G376" s="2" t="n"/>
       <c r="H376" s="2" t="n"/>
       <c r="I376" s="2" t="n"/>
     </row>
-    <row r="377" ht="62" customHeight="1">
-      <c r="A377" s="9" t="n"/>
-      <c r="B377" s="10" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+    <row r="377" ht="47" customHeight="1">
+      <c r="A377" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B377" s="33" t="inlineStr">
+        <is>
+          <t>PERDIDA TOTAL</t>
         </is>
       </c>
       <c r="C377" s="9">
-        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
+        <f>TEXT(F376,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
         <v/>
       </c>
       <c r="D377" s="2" t="n"/>
       <c r="E377" s="2" t="n"/>
-      <c r="F377" s="9" t="n"/>
+      <c r="F377" s="36">
+        <f>ROUND(F376*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
+        <v/>
+      </c>
       <c r="G377" s="2" t="n"/>
       <c r="H377" s="2" t="n"/>
       <c r="I377" s="2" t="n"/>
     </row>
-    <row r="378" ht="39.7" customHeight="1">
-      <c r="A378" s="9" t="n"/>
-      <c r="B378" s="10" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C378" s="8">
-        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
-        <v/>
-      </c>
+    <row r="378">
+      <c r="A378" s="2" t="n"/>
+      <c r="B378" s="2" t="n"/>
+      <c r="C378" s="2" t="n"/>
       <c r="D378" s="2" t="n"/>
       <c r="E378" s="2" t="n"/>
-      <c r="F378" s="9" t="n"/>
+      <c r="F378" s="2" t="n"/>
       <c r="G378" s="2" t="n"/>
       <c r="H378" s="2" t="n"/>
       <c r="I378" s="2" t="n"/>
     </row>
-    <row r="379" ht="39.7" customHeight="1">
+    <row r="379" ht="62" customHeight="1">
       <c r="A379" s="9" t="n"/>
       <c r="B379" s="10" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C379" s="25">
-        <f>ROUNDUP(F375/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C379" s="9">
+        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
         <v/>
       </c>
       <c r="D379" s="2" t="n"/>
@@ -31396,11 +31420,11 @@
       <c r="A380" s="9" t="n"/>
       <c r="B380" s="10" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C380" s="25">
-        <f>ROUNDUP(F375/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C380" s="8">
+        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
         <v/>
       </c>
       <c r="D380" s="2" t="n"/>
@@ -31411,51 +31435,61 @@
       <c r="I380" s="2" t="n"/>
     </row>
     <row r="381" ht="39.7" customHeight="1">
-      <c r="A381" s="13" t="n"/>
-      <c r="B381" s="14" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C381" s="13">
-        <f>Datos_balance!$B$13</f>
-        <v/>
-      </c>
-      <c r="D381" s="20" t="n"/>
-      <c r="E381" s="20" t="n"/>
-      <c r="F381" s="13" t="n"/>
+      <c r="A381" s="9" t="n"/>
+      <c r="B381" s="10" t="inlineStr">
+        <is>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C381" s="25">
+        <f>ROUNDUP(F377/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+        <v/>
+      </c>
+      <c r="D381" s="2" t="n"/>
+      <c r="E381" s="2" t="n"/>
+      <c r="F381" s="9" t="n"/>
       <c r="G381" s="2" t="n"/>
       <c r="H381" s="2" t="n"/>
       <c r="I381" s="2" t="n"/>
     </row>
-    <row r="382">
-      <c r="A382" s="2" t="n"/>
-      <c r="B382" s="2" t="n"/>
-      <c r="C382" s="2" t="n"/>
+    <row r="382" ht="39.7" customHeight="1">
+      <c r="A382" s="9" t="n"/>
+      <c r="B382" s="10" t="inlineStr">
+        <is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C382" s="25">
+        <f>ROUNDUP(F377/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+        <v/>
+      </c>
       <c r="D382" s="2" t="n"/>
       <c r="E382" s="2" t="n"/>
-      <c r="F382" s="2" t="n"/>
+      <c r="F382" s="9" t="n"/>
       <c r="G382" s="2" t="n"/>
       <c r="H382" s="2" t="n"/>
       <c r="I382" s="2" t="n"/>
     </row>
-    <row r="383">
-      <c r="A383" s="2" t="n"/>
-      <c r="B383" s="2" t="n"/>
-      <c r="C383" s="2" t="n"/>
-      <c r="D383" s="2" t="n"/>
-      <c r="E383" s="2" t="n"/>
-      <c r="F383" s="2" t="n"/>
+    <row r="383" ht="39.7" customHeight="1">
+      <c r="A383" s="13" t="n"/>
+      <c r="B383" s="14" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C383" s="13">
+        <f>Datos_balance!$B$13</f>
+        <v/>
+      </c>
+      <c r="D383" s="20" t="n"/>
+      <c r="E383" s="20" t="n"/>
+      <c r="F383" s="13" t="n"/>
       <c r="G383" s="2" t="n"/>
       <c r="H383" s="2" t="n"/>
       <c r="I383" s="2" t="n"/>
     </row>
-    <row r="384" ht="39.7" customHeight="1">
-      <c r="A384" s="5" t="inlineStr">
-        <is>
-          <t>LOCAL  17 - Bano   (PA)</t>
-        </is>
-      </c>
+    <row r="384">
+      <c r="A384" s="2" t="n"/>
       <c r="B384" s="2" t="n"/>
       <c r="C384" s="2" t="n"/>
       <c r="D384" s="2" t="n"/>
@@ -31465,99 +31499,76 @@
       <c r="H384" s="2" t="n"/>
       <c r="I384" s="2" t="n"/>
     </row>
-    <row r="385" ht="39.7" customHeight="1">
-      <c r="A385" s="3" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B385" s="3" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C385" s="3" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D385" s="3" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E385" s="3" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F385" s="3" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="385">
+      <c r="A385" s="2" t="n"/>
+      <c r="B385" s="2" t="n"/>
+      <c r="C385" s="2" t="n"/>
+      <c r="D385" s="2" t="n"/>
+      <c r="E385" s="2" t="n"/>
+      <c r="F385" s="2" t="n"/>
       <c r="G385" s="2" t="n"/>
       <c r="H385" s="2" t="n"/>
       <c r="I385" s="2" t="n"/>
     </row>
     <row r="386" ht="39.7" customHeight="1">
-      <c r="A386" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B386" s="33" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C386" s="9" t="n"/>
-      <c r="D386" s="9" t="n"/>
-      <c r="E386" s="9" t="n"/>
-      <c r="F386" s="9" t="n"/>
+      <c r="A386" s="5" t="inlineStr">
+        <is>
+          <t>LOCAL  17 - Bano   (PA)</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="n"/>
+      <c r="C386" s="2" t="n"/>
+      <c r="D386" s="2" t="n"/>
+      <c r="E386" s="2" t="n"/>
+      <c r="F386" s="2" t="n"/>
       <c r="G386" s="2" t="n"/>
       <c r="H386" s="2" t="n"/>
       <c r="I386" s="2" t="n"/>
     </row>
-    <row r="387" ht="62" customHeight="1">
-      <c r="A387" s="9" t="n"/>
-      <c r="B387" s="34" t="inlineStr">
-        <is>
-          <t>VA03</t>
-        </is>
-      </c>
-      <c r="C387" s="9">
-        <f>IF(COUNT(H387,I387)&lt;2,"",TEXT(H387,"0.00")&amp;" x "&amp;TEXT(I387,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D387" s="8">
-        <f>IF(COUNT(H387,I387)&lt;2,"",ROUND(H387*I387,2))</f>
-        <v/>
-      </c>
-      <c r="E387" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F387" s="28">
-        <f>IF(D387="","",ROUND(D387*E387,1))</f>
-        <v/>
+    <row r="387" ht="39.7" customHeight="1">
+      <c r="A387" s="3" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E387" s="3" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F387" s="3" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
       </c>
       <c r="G387" s="2" t="n"/>
-      <c r="H387" s="35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I387" s="35" t="n">
-        <v>2.52</v>
-      </c>
+      <c r="H387" s="2" t="n"/>
+      <c r="I387" s="2" t="n"/>
     </row>
     <row r="388" ht="39.7" customHeight="1">
       <c r="A388" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B388" s="33" t="inlineStr">
         <is>
-          <t>PAREDES EXTERIORES</t>
+          <t>VENTANA</t>
         </is>
       </c>
       <c r="C388" s="9" t="n"/>
@@ -31572,7 +31583,7 @@
       <c r="A389" s="9" t="n"/>
       <c r="B389" s="34" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>VA03</t>
         </is>
       </c>
       <c r="C389" s="9">
@@ -31584,41 +31595,38 @@
         <v/>
       </c>
       <c r="E389" s="25" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F389" s="28">
         <f>IF(D389="","",ROUND(D389*E389,1))</f>
         <v/>
       </c>
       <c r="G389" s="2" t="n"/>
-      <c r="H389" s="35" t="n"/>
-      <c r="I389" s="35" t="n"/>
-    </row>
-    <row r="390" ht="62" customHeight="1">
-      <c r="A390" s="9" t="n"/>
-      <c r="B390" s="34" t="inlineStr">
-        <is>
-          <t>AISLADAS (    )</t>
-        </is>
-      </c>
-      <c r="C390" s="9">
-        <f>IF(COUNT(H390,I390)&lt;2,"",TEXT(H390,"0.00")&amp;" x "&amp;TEXT(I390,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D390" s="8">
-        <f>IF(COUNT(H390,I390)&lt;2,"",ROUND(H390*I390,2))</f>
-        <v/>
-      </c>
-      <c r="E390" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F390" s="28">
-        <f>IF(D390="","",ROUND(D390*E390,1))</f>
-        <v/>
-      </c>
+      <c r="H389" s="35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I389" s="35" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="390" ht="39.7" customHeight="1">
+      <c r="A390" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B390" s="33" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C390" s="9" t="n"/>
+      <c r="D390" s="9" t="n"/>
+      <c r="E390" s="9" t="n"/>
+      <c r="F390" s="9" t="n"/>
       <c r="G390" s="2" t="n"/>
-      <c r="H390" s="35" t="n"/>
-      <c r="I390" s="35" t="n"/>
+      <c r="H390" s="2" t="n"/>
+      <c r="I390" s="2" t="n"/>
     </row>
     <row r="391" ht="62" customHeight="1">
       <c r="A391" s="9" t="n"/>
@@ -31676,7 +31684,7 @@
       <c r="A393" s="9" t="n"/>
       <c r="B393" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C393" s="9">
@@ -31688,25 +31696,21 @@
         <v/>
       </c>
       <c r="E393" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F393" s="28">
         <f>IF(D393="","",ROUND(D393*E393,1))</f>
         <v/>
       </c>
       <c r="G393" s="2" t="n"/>
-      <c r="H393" s="35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I393" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H393" s="35" t="n"/>
+      <c r="I393" s="35" t="n"/>
     </row>
     <row r="394" ht="62" customHeight="1">
       <c r="A394" s="9" t="n"/>
       <c r="B394" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C394" s="9">
@@ -31718,19 +31722,15 @@
         <v/>
       </c>
       <c r="E394" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F394" s="28">
         <f>IF(D394="","",ROUND(D394*E394,1))</f>
         <v/>
       </c>
       <c r="G394" s="2" t="n"/>
-      <c r="H394" s="35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I394" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H394" s="35" t="n"/>
+      <c r="I394" s="35" t="n"/>
     </row>
     <row r="395" ht="62" customHeight="1">
       <c r="A395" s="9" t="n"/>
@@ -31792,79 +31792,90 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" ht="39.7" customHeight="1">
-      <c r="A397" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B397" s="33" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C397" s="9" t="n"/>
-      <c r="D397" s="9" t="n"/>
-      <c r="E397" s="9" t="n"/>
-      <c r="F397" s="9" t="n"/>
+    <row r="397" ht="62" customHeight="1">
+      <c r="A397" s="9" t="n"/>
+      <c r="B397" s="34" t="inlineStr">
+        <is>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C397" s="9">
+        <f>IF(COUNT(H397,I397)&lt;2,"",TEXT(H397,"0.00")&amp;" x "&amp;TEXT(I397,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D397" s="8">
+        <f>IF(COUNT(H397,I397)&lt;2,"",ROUND(H397*I397,2))</f>
+        <v/>
+      </c>
+      <c r="E397" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F397" s="28">
+        <f>IF(D397="","",ROUND(D397*E397,1))</f>
+        <v/>
+      </c>
       <c r="G397" s="2" t="n"/>
-      <c r="H397" s="2" t="n"/>
-      <c r="I397" s="2" t="n"/>
+      <c r="H397" s="35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I397" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="398" ht="62" customHeight="1">
       <c r="A398" s="9" t="n"/>
       <c r="B398" s="34" t="inlineStr">
         <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C398" s="9" t="inlineStr"/>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C398" s="9">
+        <f>IF(COUNT(H398,I398)&lt;2,"",TEXT(H398,"0.00")&amp;" x "&amp;TEXT(I398,"0.00"))</f>
+        <v/>
+      </c>
       <c r="D398" s="8">
         <f>IF(COUNT(H398,I398)&lt;2,"",ROUND(H398*I398,2))</f>
         <v/>
       </c>
       <c r="E398" s="25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F398" s="28">
         <f>IF(D398="","",ROUND(D398*E398,1))</f>
         <v/>
       </c>
       <c r="G398" s="2" t="n"/>
-      <c r="H398" s="35" t="n"/>
-      <c r="I398" s="35" t="n"/>
+      <c r="H398" s="35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I398" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="399" ht="39.7" customHeight="1">
-      <c r="A399" s="9" t="n"/>
-      <c r="B399" s="34" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C399" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D399" s="8" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="E399" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F399" s="28">
-        <f>IF(D399="","",ROUND(D399*E399,1))</f>
-        <v/>
-      </c>
+      <c r="A399" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B399" s="33" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C399" s="9" t="n"/>
+      <c r="D399" s="9" t="n"/>
+      <c r="E399" s="9" t="n"/>
+      <c r="F399" s="9" t="n"/>
       <c r="G399" s="2" t="n"/>
-      <c r="H399" s="35" t="n"/>
-      <c r="I399" s="35" t="n"/>
+      <c r="H399" s="2" t="n"/>
+      <c r="I399" s="2" t="n"/>
     </row>
     <row r="400" ht="62" customHeight="1">
       <c r="A400" s="9" t="n"/>
       <c r="B400" s="34" t="inlineStr">
         <is>
-          <t>TECHO ENTREPISO</t>
+          <t>TECHO NO AISLADO</t>
         </is>
       </c>
       <c r="C400" s="9" t="inlineStr"/>
@@ -31873,7 +31884,7 @@
         <v/>
       </c>
       <c r="E400" s="25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F400" s="28">
         <f>IF(D400="","",ROUND(D400*E400,1))</f>
@@ -31884,29 +31895,36 @@
       <c r="I400" s="35" t="n"/>
     </row>
     <row r="401" ht="39.7" customHeight="1">
-      <c r="A401" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B401" s="33" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C401" s="9" t="n"/>
-      <c r="D401" s="9" t="n"/>
-      <c r="E401" s="9" t="n"/>
-      <c r="F401" s="9" t="n"/>
+      <c r="A401" s="9" t="n"/>
+      <c r="B401" s="34" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C401" s="9" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D401" s="8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="E401" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F401" s="28">
+        <f>IF(D401="","",ROUND(D401*E401,1))</f>
+        <v/>
+      </c>
       <c r="G401" s="2" t="n"/>
-      <c r="H401" s="2" t="n"/>
-      <c r="I401" s="2" t="n"/>
+      <c r="H401" s="35" t="n"/>
+      <c r="I401" s="35" t="n"/>
     </row>
     <row r="402" ht="62" customHeight="1">
       <c r="A402" s="9" t="n"/>
       <c r="B402" s="34" t="inlineStr">
         <is>
-          <t>SOBRE TIERRA</t>
+          <t>TECHO ENTREPISO</t>
         </is>
       </c>
       <c r="C402" s="9" t="inlineStr"/>
@@ -31915,7 +31933,7 @@
         <v/>
       </c>
       <c r="E402" s="25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F402" s="28">
         <f>IF(D402="","",ROUND(D402*E402,1))</f>
@@ -31926,71 +31944,64 @@
       <c r="I402" s="35" t="n"/>
     </row>
     <row r="403" ht="39.7" customHeight="1">
-      <c r="A403" s="9" t="n"/>
-      <c r="B403" s="34" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C403" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D403" s="8" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="E403" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="F403" s="28">
-        <f>IF(D403="","",ROUND(D403*E403,1))</f>
-        <v/>
-      </c>
+      <c r="A403" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B403" s="33" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C403" s="9" t="n"/>
+      <c r="D403" s="9" t="n"/>
+      <c r="E403" s="9" t="n"/>
+      <c r="F403" s="9" t="n"/>
       <c r="G403" s="2" t="n"/>
-      <c r="H403" s="35" t="n"/>
-      <c r="I403" s="35" t="n"/>
-    </row>
-    <row r="404" ht="39.7" customHeight="1">
-      <c r="A404" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B404" s="33" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C404" s="9" t="n"/>
-      <c r="D404" s="16" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E404" s="9" t="n"/>
-      <c r="F404" s="9" t="n"/>
+      <c r="H403" s="2" t="n"/>
+      <c r="I403" s="2" t="n"/>
+    </row>
+    <row r="404" ht="62" customHeight="1">
+      <c r="A404" s="9" t="n"/>
+      <c r="B404" s="34" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C404" s="9" t="inlineStr"/>
+      <c r="D404" s="8">
+        <f>IF(COUNT(H404,I404)&lt;2,"",ROUND(H404*I404,2))</f>
+        <v/>
+      </c>
+      <c r="E404" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F404" s="28">
+        <f>IF(D404="","",ROUND(D404*E404,1))</f>
+        <v/>
+      </c>
       <c r="G404" s="2" t="n"/>
-      <c r="H404" s="2" t="n"/>
-      <c r="I404" s="2" t="n"/>
+      <c r="H404" s="35" t="n"/>
+      <c r="I404" s="35" t="n"/>
     </row>
     <row r="405" ht="39.7" customHeight="1">
       <c r="A405" s="9" t="n"/>
       <c r="B405" s="34" t="inlineStr">
         <is>
-          <t>UNA PARED EXTERIOR</t>
+          <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
       <c r="C405" s="9" t="inlineStr">
         <is>
-          <t>3.52 m2 x 3.00</t>
+          <t>por croquis</t>
         </is>
       </c>
       <c r="D405" s="8" t="n">
-        <v>10.56</v>
+        <v>3.52</v>
       </c>
       <c r="E405" s="25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F405" s="28">
         <f>IF(D405="","",ROUND(D405*E405,1))</f>
@@ -32000,43 +32011,46 @@
       <c r="H405" s="35" t="n"/>
       <c r="I405" s="35" t="n"/>
     </row>
-    <row r="406" ht="62" customHeight="1">
-      <c r="A406" s="9" t="n"/>
-      <c r="B406" s="34" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C406" s="9" t="inlineStr"/>
-      <c r="D406" s="8">
-        <f>IF(COUNT(H406,I406)&lt;2,"",ROUND(H406*I406,2))</f>
-        <v/>
-      </c>
-      <c r="E406" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F406" s="28">
-        <f>IF(D406="","",ROUND(D406*E406,1))</f>
-        <v/>
-      </c>
+    <row r="406" ht="39.7" customHeight="1">
+      <c r="A406" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B406" s="33" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C406" s="9" t="n"/>
+      <c r="D406" s="16" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E406" s="9" t="n"/>
+      <c r="F406" s="9" t="n"/>
       <c r="G406" s="2" t="n"/>
-      <c r="H406" s="35" t="n"/>
-      <c r="I406" s="35" t="n"/>
-    </row>
-    <row r="407" ht="62" customHeight="1">
+      <c r="H406" s="2" t="n"/>
+      <c r="I406" s="2" t="n"/>
+    </row>
+    <row r="407" ht="39.7" customHeight="1">
       <c r="A407" s="9" t="n"/>
       <c r="B407" s="34" t="inlineStr">
         <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C407" s="9" t="inlineStr"/>
-      <c r="D407" s="8">
-        <f>IF(COUNT(H407,I407)&lt;2,"",ROUND(H407*I407,2))</f>
-        <v/>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C407" s="9" t="inlineStr">
+        <is>
+          <t>3.52 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D407" s="8" t="n">
+        <v>10.56</v>
       </c>
       <c r="E407" s="25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F407" s="28">
         <f>IF(D407="","",ROUND(D407*E407,1))</f>
@@ -32046,109 +32060,119 @@
       <c r="H407" s="35" t="n"/>
       <c r="I407" s="35" t="n"/>
     </row>
-    <row r="408" ht="70" customHeight="1">
-      <c r="A408" s="16" t="inlineStr">
+    <row r="408" ht="62" customHeight="1">
+      <c r="A408" s="9" t="n"/>
+      <c r="B408" s="34" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C408" s="9" t="inlineStr"/>
+      <c r="D408" s="8">
+        <f>IF(COUNT(H408,I408)&lt;2,"",ROUND(H408*I408,2))</f>
+        <v/>
+      </c>
+      <c r="E408" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F408" s="28">
+        <f>IF(D408="","",ROUND(D408*E408,1))</f>
+        <v/>
+      </c>
+      <c r="G408" s="2" t="n"/>
+      <c r="H408" s="35" t="n"/>
+      <c r="I408" s="35" t="n"/>
+    </row>
+    <row r="409" ht="62" customHeight="1">
+      <c r="A409" s="9" t="n"/>
+      <c r="B409" s="34" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C409" s="9" t="inlineStr"/>
+      <c r="D409" s="8">
+        <f>IF(COUNT(H409,I409)&lt;2,"",ROUND(H409*I409,2))</f>
+        <v/>
+      </c>
+      <c r="E409" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F409" s="28">
+        <f>IF(D409="","",ROUND(D409*E409,1))</f>
+        <v/>
+      </c>
+      <c r="G409" s="2" t="n"/>
+      <c r="H409" s="35" t="n"/>
+      <c r="I409" s="35" t="n"/>
+    </row>
+    <row r="410" ht="70" customHeight="1">
+      <c r="A410" s="16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B408" s="33" t="inlineStr">
+      <c r="B410" s="33" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C408" s="9" t="n"/>
-      <c r="D408" s="9" t="n"/>
-      <c r="E408" s="9" t="n"/>
-      <c r="F408" s="36">
-        <f>IF(F387="",0,F387)+IF(F389="",0,F389)+IF(F390="",0,F390)+IF(F391="",0,F391)+IF(F392="",0,F392)+IF(F393="",0,F393)+IF(F394="",0,F394)+IF(F395="",0,F395)+IF(F396="",0,F396)+IF(F398="",0,F398)+IF(F399="",0,F399)+IF(F400="",0,F400)+IF(F402="",0,F402)+IF(F403="",0,F403)+IF(F405="",0,F405)+IF(F406="",0,F406)+IF(F407="",0,F407)</f>
-        <v/>
-      </c>
-      <c r="G408" s="2" t="n"/>
-      <c r="H408" s="2" t="n"/>
-      <c r="I408" s="2" t="n"/>
-    </row>
-    <row r="409" ht="47" customHeight="1">
-      <c r="A409" s="16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B409" s="33" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C409" s="9">
-        <f>TEXT(F408,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
-        <v/>
-      </c>
-      <c r="D409" s="2" t="n"/>
-      <c r="E409" s="2" t="n"/>
-      <c r="F409" s="36">
-        <f>ROUND(F408*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
-        <v/>
-      </c>
-      <c r="G409" s="2" t="n"/>
-      <c r="H409" s="2" t="n"/>
-      <c r="I409" s="2" t="n"/>
-    </row>
-    <row r="410">
-      <c r="A410" s="2" t="n"/>
-      <c r="B410" s="2" t="n"/>
-      <c r="C410" s="2" t="n"/>
-      <c r="D410" s="2" t="n"/>
-      <c r="E410" s="2" t="n"/>
-      <c r="F410" s="2" t="n"/>
+      <c r="C410" s="9" t="n"/>
+      <c r="D410" s="9" t="n"/>
+      <c r="E410" s="9" t="n"/>
+      <c r="F410" s="36">
+        <f>IF(F389="",0,F389)+IF(F391="",0,F391)+IF(F392="",0,F392)+IF(F393="",0,F393)+IF(F394="",0,F394)+IF(F395="",0,F395)+IF(F396="",0,F396)+IF(F397="",0,F397)+IF(F398="",0,F398)+IF(F400="",0,F400)+IF(F401="",0,F401)+IF(F402="",0,F402)+IF(F404="",0,F404)+IF(F405="",0,F405)+IF(F407="",0,F407)+IF(F408="",0,F408)+IF(F409="",0,F409)</f>
+        <v/>
+      </c>
       <c r="G410" s="2" t="n"/>
       <c r="H410" s="2" t="n"/>
       <c r="I410" s="2" t="n"/>
     </row>
-    <row r="411" ht="62" customHeight="1">
-      <c r="A411" s="9" t="n"/>
-      <c r="B411" s="10" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+    <row r="411" ht="47" customHeight="1">
+      <c r="A411" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B411" s="33" t="inlineStr">
+        <is>
+          <t>PERDIDA TOTAL</t>
         </is>
       </c>
       <c r="C411" s="9">
-        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
+        <f>TEXT(F410,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
         <v/>
       </c>
       <c r="D411" s="2" t="n"/>
       <c r="E411" s="2" t="n"/>
-      <c r="F411" s="9" t="n"/>
+      <c r="F411" s="36">
+        <f>ROUND(F410*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
+        <v/>
+      </c>
       <c r="G411" s="2" t="n"/>
       <c r="H411" s="2" t="n"/>
       <c r="I411" s="2" t="n"/>
     </row>
-    <row r="412" ht="39.7" customHeight="1">
-      <c r="A412" s="9" t="n"/>
-      <c r="B412" s="10" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C412" s="25">
-        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
-        <v/>
-      </c>
+    <row r="412">
+      <c r="A412" s="2" t="n"/>
+      <c r="B412" s="2" t="n"/>
+      <c r="C412" s="2" t="n"/>
       <c r="D412" s="2" t="n"/>
       <c r="E412" s="2" t="n"/>
-      <c r="F412" s="9" t="n"/>
+      <c r="F412" s="2" t="n"/>
       <c r="G412" s="2" t="n"/>
       <c r="H412" s="2" t="n"/>
       <c r="I412" s="2" t="n"/>
     </row>
-    <row r="413" ht="39.7" customHeight="1">
+    <row r="413" ht="62" customHeight="1">
       <c r="A413" s="9" t="n"/>
       <c r="B413" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
-        </is>
-      </c>
-      <c r="C413" s="25">
-        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C413" s="9">
+        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
         <v/>
       </c>
       <c r="D413" s="2" t="n"/>
@@ -32158,15 +32182,15 @@
       <c r="H413" s="2" t="n"/>
       <c r="I413" s="2" t="n"/>
     </row>
-    <row r="414" ht="47" customHeight="1">
+    <row r="414" ht="39.7" customHeight="1">
       <c r="A414" s="9" t="n"/>
       <c r="B414" s="10" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C414" s="25">
-        <f>IF(F409&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F409/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
+        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D414" s="2" t="n"/>
@@ -32176,23 +32200,59 @@
       <c r="H414" s="2" t="n"/>
       <c r="I414" s="2" t="n"/>
     </row>
-    <row r="415" ht="47" customHeight="1">
-      <c r="A415" s="13" t="n"/>
-      <c r="B415" s="14" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C415" s="13">
-        <f>IF(F409&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
-        <v/>
-      </c>
-      <c r="D415" s="20" t="n"/>
-      <c r="E415" s="20" t="n"/>
-      <c r="F415" s="13" t="n"/>
+    <row r="415" ht="39.7" customHeight="1">
+      <c r="A415" s="9" t="n"/>
+      <c r="B415" s="10" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
+        </is>
+      </c>
+      <c r="C415" s="25">
+        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D415" s="2" t="n"/>
+      <c r="E415" s="2" t="n"/>
+      <c r="F415" s="9" t="n"/>
       <c r="G415" s="2" t="n"/>
       <c r="H415" s="2" t="n"/>
       <c r="I415" s="2" t="n"/>
+    </row>
+    <row r="416" ht="47" customHeight="1">
+      <c r="A416" s="9" t="n"/>
+      <c r="B416" s="10" t="inlineStr">
+        <is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C416" s="25">
+        <f>IF(F411&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F411/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
+        <v/>
+      </c>
+      <c r="D416" s="2" t="n"/>
+      <c r="E416" s="2" t="n"/>
+      <c r="F416" s="9" t="n"/>
+      <c r="G416" s="2" t="n"/>
+      <c r="H416" s="2" t="n"/>
+      <c r="I416" s="2" t="n"/>
+    </row>
+    <row r="417" ht="47" customHeight="1">
+      <c r="A417" s="13" t="n"/>
+      <c r="B417" s="14" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C417" s="13">
+        <f>IF(F411&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
+        <v/>
+      </c>
+      <c r="D417" s="20" t="n"/>
+      <c r="E417" s="20" t="n"/>
+      <c r="F417" s="13" t="n"/>
+      <c r="G417" s="2" t="n"/>
+      <c r="H417" s="2" t="n"/>
+      <c r="I417" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="85">
@@ -32204,29 +32264,28 @@
     <mergeCell ref="C413:E413"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="C379:E379"/>
-    <mergeCell ref="A384:F384"/>
     <mergeCell ref="C415:E415"/>
     <mergeCell ref="C71:E71"/>
     <mergeCell ref="C241:E241"/>
     <mergeCell ref="C347:E347"/>
+    <mergeCell ref="A386:F386"/>
     <mergeCell ref="C243:E243"/>
     <mergeCell ref="C140:E140"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C375:E375"/>
     <mergeCell ref="C275:E275"/>
     <mergeCell ref="C344:E344"/>
     <mergeCell ref="C206:E206"/>
     <mergeCell ref="C377:E377"/>
     <mergeCell ref="A315:F315"/>
+    <mergeCell ref="C417:E417"/>
     <mergeCell ref="C309:E309"/>
     <mergeCell ref="C103:E103"/>
     <mergeCell ref="A212:F212"/>
     <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C383:E383"/>
     <mergeCell ref="C311:E311"/>
-    <mergeCell ref="C412:E412"/>
     <mergeCell ref="C169:E169"/>
-    <mergeCell ref="C409:E409"/>
     <mergeCell ref="C380:E380"/>
     <mergeCell ref="C70:E70"/>
     <mergeCell ref="C272:E272"/>
@@ -32240,6 +32299,7 @@
     <mergeCell ref="C104:E104"/>
     <mergeCell ref="A178:F178"/>
     <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C416:E416"/>
     <mergeCell ref="C173:E173"/>
     <mergeCell ref="C276:E276"/>
     <mergeCell ref="C36:E36"/>
@@ -32254,7 +32314,6 @@
     <mergeCell ref="C136:E136"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A350:F350"/>
-    <mergeCell ref="C378:E378"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C172:E172"/>
     <mergeCell ref="A281:F281"/>
@@ -32263,6 +32322,7 @@
     <mergeCell ref="C137:E137"/>
     <mergeCell ref="C134:E134"/>
     <mergeCell ref="A246:F246"/>
+    <mergeCell ref="C382:E382"/>
     <mergeCell ref="C277:E277"/>
     <mergeCell ref="C139:E139"/>
     <mergeCell ref="C105:E105"/>

--- a/planillas/planillas_estructura.xlsx
+++ b/planillas/planillas_estructura.xlsx
@@ -25486,7 +25486,7 @@
       </c>
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="35" t="n">
-        <v>5.25</v>
+        <v>4.87</v>
       </c>
       <c r="I118" s="35" t="n">
         <v>3</v>
@@ -25516,7 +25516,7 @@
       </c>
       <c r="G119" s="2" t="n"/>
       <c r="H119" s="35" t="n">
-        <v>1.09</v>
+        <v>1.66</v>
       </c>
       <c r="I119" s="35" t="n">
         <v>3</v>
@@ -25546,7 +25546,7 @@
       </c>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="35" t="n">
-        <v>5.25</v>
+        <v>3.38</v>
       </c>
       <c r="I120" s="35" t="n">
         <v>3</v>
@@ -25576,94 +25576,105 @@
       </c>
       <c r="G121" s="2" t="n"/>
       <c r="H121" s="35" t="n">
-        <v>1.09</v>
+        <v>0.57</v>
       </c>
       <c r="I121" s="35" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="122" ht="39.7" customHeight="1">
-      <c r="A122" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B122" s="33" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="n"/>
-      <c r="D122" s="9" t="n"/>
-      <c r="E122" s="9" t="n"/>
-      <c r="F122" s="9" t="n"/>
+    <row r="122" ht="62" customHeight="1">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="34" t="inlineStr">
+        <is>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C122" s="9">
+        <f>IF(COUNT(H122,I122)&lt;2,"",TEXT(H122,"0.00")&amp;" x "&amp;TEXT(I122,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D122" s="8">
+        <f>IF(COUNT(H122,I122)&lt;2,"",ROUND(H122*I122,2))</f>
+        <v/>
+      </c>
+      <c r="E122" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F122" s="28">
+        <f>IF(D122="","",ROUND(D122*E122,1))</f>
+        <v/>
+      </c>
       <c r="G122" s="2" t="n"/>
-      <c r="H122" s="2" t="n"/>
-      <c r="I122" s="2" t="n"/>
+      <c r="H122" s="35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I122" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="123" ht="62" customHeight="1">
       <c r="A123" s="9" t="n"/>
       <c r="B123" s="34" t="inlineStr">
         <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C123" s="9" t="inlineStr"/>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C123" s="9">
+        <f>IF(COUNT(H123,I123)&lt;2,"",TEXT(H123,"0.00")&amp;" x "&amp;TEXT(I123,"0.00"))</f>
+        <v/>
+      </c>
       <c r="D123" s="8">
         <f>IF(COUNT(H123,I123)&lt;2,"",ROUND(H123*I123,2))</f>
         <v/>
       </c>
       <c r="E123" s="25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F123" s="28">
         <f>IF(D123="","",ROUND(D123*E123,1))</f>
         <v/>
       </c>
       <c r="G123" s="2" t="n"/>
-      <c r="H123" s="35" t="n"/>
-      <c r="I123" s="35" t="n"/>
-    </row>
-    <row r="124" ht="62" customHeight="1">
-      <c r="A124" s="9" t="n"/>
-      <c r="B124" s="34" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr"/>
-      <c r="D124" s="8">
-        <f>IF(COUNT(H124,I124)&lt;2,"",ROUND(H124*I124,2))</f>
-        <v/>
-      </c>
-      <c r="E124" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F124" s="28">
-        <f>IF(D124="","",ROUND(D124*E124,1))</f>
-        <v/>
-      </c>
+      <c r="H123" s="35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I123" s="35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" ht="39.7" customHeight="1">
+      <c r="A124" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B124" s="33" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="9" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="9" t="n"/>
       <c r="G124" s="2" t="n"/>
-      <c r="H124" s="35" t="n"/>
-      <c r="I124" s="35" t="n"/>
-    </row>
-    <row r="125" ht="39.7" customHeight="1">
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+    </row>
+    <row r="125" ht="62" customHeight="1">
       <c r="A125" s="9" t="n"/>
       <c r="B125" s="34" t="inlineStr">
         <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="n">
-        <v>5.72</v>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr"/>
+      <c r="D125" s="8">
+        <f>IF(COUNT(H125,I125)&lt;2,"",ROUND(H125*I125,2))</f>
+        <v/>
       </c>
       <c r="E125" s="25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F125" s="28">
         <f>IF(D125="","",ROUND(D125*E125,1))</f>
@@ -25673,30 +25684,34 @@
       <c r="H125" s="35" t="n"/>
       <c r="I125" s="35" t="n"/>
     </row>
-    <row r="126" ht="39.7" customHeight="1">
-      <c r="A126" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B126" s="33" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="n"/>
-      <c r="D126" s="9" t="n"/>
-      <c r="E126" s="9" t="n"/>
-      <c r="F126" s="9" t="n"/>
+    <row r="126" ht="62" customHeight="1">
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="34" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr"/>
+      <c r="D126" s="8">
+        <f>IF(COUNT(H126,I126)&lt;2,"",ROUND(H126*I126,2))</f>
+        <v/>
+      </c>
+      <c r="E126" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F126" s="28">
+        <f>IF(D126="","",ROUND(D126*E126,1))</f>
+        <v/>
+      </c>
       <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
+      <c r="H126" s="35" t="n"/>
+      <c r="I126" s="35" t="n"/>
     </row>
     <row r="127" ht="39.7" customHeight="1">
       <c r="A127" s="9" t="n"/>
       <c r="B127" s="34" t="inlineStr">
         <is>
-          <t>SOBRE TIERRA</t>
+          <t>TECHO ENTREPISO</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -25705,10 +25720,10 @@
         </is>
       </c>
       <c r="D127" s="8" t="n">
-        <v>5.72</v>
+        <v>7.23</v>
       </c>
       <c r="E127" s="25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F127" s="28">
         <f>IF(D127="","",ROUND(D127*E127,1))</f>
@@ -25718,69 +25733,65 @@
       <c r="H127" s="35" t="n"/>
       <c r="I127" s="35" t="n"/>
     </row>
-    <row r="128" ht="62" customHeight="1">
-      <c r="A128" s="9" t="n"/>
-      <c r="B128" s="34" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr"/>
-      <c r="D128" s="8">
-        <f>IF(COUNT(H128,I128)&lt;2,"",ROUND(H128*I128,2))</f>
-        <v/>
-      </c>
-      <c r="E128" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="F128" s="28">
-        <f>IF(D128="","",ROUND(D128*E128,1))</f>
-        <v/>
-      </c>
+    <row r="128" ht="39.7" customHeight="1">
+      <c r="A128" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B128" s="33" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="9" t="n"/>
+      <c r="E128" s="9" t="n"/>
+      <c r="F128" s="9" t="n"/>
       <c r="G128" s="2" t="n"/>
-      <c r="H128" s="35" t="n"/>
-      <c r="I128" s="35" t="n"/>
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
     </row>
     <row r="129" ht="39.7" customHeight="1">
-      <c r="A129" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B129" s="33" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="n"/>
-      <c r="D129" s="16" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E129" s="9" t="n"/>
-      <c r="F129" s="9" t="n"/>
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="34" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E129" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F129" s="28">
+        <f>IF(D129="","",ROUND(D129*E129,1))</f>
+        <v/>
+      </c>
       <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="n"/>
-    </row>
-    <row r="130" ht="39.7" customHeight="1">
+      <c r="H129" s="35" t="n"/>
+      <c r="I129" s="35" t="n"/>
+    </row>
+    <row r="130" ht="62" customHeight="1">
       <c r="A130" s="9" t="n"/>
       <c r="B130" s="34" t="inlineStr">
         <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>5.72 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="n">
-        <v>17.16</v>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr"/>
+      <c r="D130" s="8">
+        <f>IF(COUNT(H130,I130)&lt;2,"",ROUND(H130*I130,2))</f>
+        <v/>
       </c>
       <c r="E130" s="25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F130" s="28">
         <f>IF(D130="","",ROUND(D130*E130,1))</f>
@@ -25790,43 +25801,46 @@
       <c r="H130" s="35" t="n"/>
       <c r="I130" s="35" t="n"/>
     </row>
-    <row r="131" ht="62" customHeight="1">
-      <c r="A131" s="9" t="n"/>
-      <c r="B131" s="34" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr"/>
-      <c r="D131" s="8">
-        <f>IF(COUNT(H131,I131)&lt;2,"",ROUND(H131*I131,2))</f>
-        <v/>
-      </c>
-      <c r="E131" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F131" s="28">
-        <f>IF(D131="","",ROUND(D131*E131,1))</f>
-        <v/>
-      </c>
+    <row r="131" ht="39.7" customHeight="1">
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B131" s="33" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="16" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="9" t="n"/>
       <c r="G131" s="2" t="n"/>
-      <c r="H131" s="35" t="n"/>
-      <c r="I131" s="35" t="n"/>
-    </row>
-    <row r="132" ht="62" customHeight="1">
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+    </row>
+    <row r="132" ht="39.7" customHeight="1">
       <c r="A132" s="9" t="n"/>
       <c r="B132" s="34" t="inlineStr">
         <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C132" s="9" t="inlineStr"/>
-      <c r="D132" s="8">
-        <f>IF(COUNT(H132,I132)&lt;2,"",ROUND(H132*I132,2))</f>
-        <v/>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>7.23 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>21.69</v>
       </c>
       <c r="E132" s="25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F132" s="28">
         <f>IF(D132="","",ROUND(D132*E132,1))</f>
@@ -25836,109 +25850,119 @@
       <c r="H132" s="35" t="n"/>
       <c r="I132" s="35" t="n"/>
     </row>
-    <row r="133" ht="70" customHeight="1">
-      <c r="A133" s="16" t="inlineStr">
+    <row r="133" ht="62" customHeight="1">
+      <c r="A133" s="9" t="n"/>
+      <c r="B133" s="34" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr"/>
+      <c r="D133" s="8">
+        <f>IF(COUNT(H133,I133)&lt;2,"",ROUND(H133*I133,2))</f>
+        <v/>
+      </c>
+      <c r="E133" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F133" s="28">
+        <f>IF(D133="","",ROUND(D133*E133,1))</f>
+        <v/>
+      </c>
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="35" t="n"/>
+      <c r="I133" s="35" t="n"/>
+    </row>
+    <row r="134" ht="62" customHeight="1">
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="34" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr"/>
+      <c r="D134" s="8">
+        <f>IF(COUNT(H134,I134)&lt;2,"",ROUND(H134*I134,2))</f>
+        <v/>
+      </c>
+      <c r="E134" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F134" s="28">
+        <f>IF(D134="","",ROUND(D134*E134,1))</f>
+        <v/>
+      </c>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="35" t="n"/>
+      <c r="I134" s="35" t="n"/>
+    </row>
+    <row r="135" ht="70" customHeight="1">
+      <c r="A135" s="16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B133" s="33" t="inlineStr">
+      <c r="B135" s="33" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C133" s="9" t="n"/>
-      <c r="D133" s="9" t="n"/>
-      <c r="E133" s="9" t="n"/>
-      <c r="F133" s="36">
-        <f>IF(F112="",0,F112)+IF(F114="",0,F114)+IF(F115="",0,F115)+IF(F116="",0,F116)+IF(F117="",0,F117)+IF(F118="",0,F118)+IF(F119="",0,F119)+IF(F120="",0,F120)+IF(F121="",0,F121)+IF(F123="",0,F123)+IF(F124="",0,F124)+IF(F125="",0,F125)+IF(F127="",0,F127)+IF(F128="",0,F128)+IF(F130="",0,F130)+IF(F131="",0,F131)+IF(F132="",0,F132)</f>
-        <v/>
-      </c>
-      <c r="G133" s="2" t="n"/>
-      <c r="H133" s="2" t="n"/>
-      <c r="I133" s="2" t="n"/>
-    </row>
-    <row r="134" ht="47" customHeight="1">
-      <c r="A134" s="16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B134" s="33" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C134" s="9">
-        <f>TEXT(F133,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
-        <v/>
-      </c>
-      <c r="D134" s="2" t="n"/>
-      <c r="E134" s="2" t="n"/>
-      <c r="F134" s="36">
-        <f>ROUND(F133*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
-        <v/>
-      </c>
-      <c r="G134" s="2" t="n"/>
-      <c r="H134" s="2" t="n"/>
-      <c r="I134" s="2" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n"/>
-      <c r="B135" s="2" t="n"/>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n"/>
-      <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="n"/>
+      <c r="C135" s="9" t="n"/>
+      <c r="D135" s="9" t="n"/>
+      <c r="E135" s="9" t="n"/>
+      <c r="F135" s="36">
+        <f>IF(F112="",0,F112)+IF(F114="",0,F114)+IF(F115="",0,F115)+IF(F116="",0,F116)+IF(F117="",0,F117)+IF(F118="",0,F118)+IF(F119="",0,F119)+IF(F120="",0,F120)+IF(F121="",0,F121)+IF(F122="",0,F122)+IF(F123="",0,F123)+IF(F125="",0,F125)+IF(F126="",0,F126)+IF(F127="",0,F127)+IF(F129="",0,F129)+IF(F130="",0,F130)+IF(F132="",0,F132)+IF(F133="",0,F133)+IF(F134="",0,F134)</f>
+        <v/>
+      </c>
       <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="n"/>
     </row>
-    <row r="136" ht="62" customHeight="1">
-      <c r="A136" s="9" t="n"/>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+    <row r="136" ht="47" customHeight="1">
+      <c r="A136" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B136" s="33" t="inlineStr">
+        <is>
+          <t>PERDIDA TOTAL</t>
         </is>
       </c>
       <c r="C136" s="9">
-        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
+        <f>TEXT(F135,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
         <v/>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" s="2" t="n"/>
-      <c r="F136" s="9" t="n"/>
+      <c r="F136" s="36">
+        <f>ROUND(F135*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
+        <v/>
+      </c>
       <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="n"/>
     </row>
-    <row r="137" ht="39.7" customHeight="1">
-      <c r="A137" s="9" t="n"/>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C137" s="8">
-        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
-        <v/>
-      </c>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n"/>
       <c r="E137" s="2" t="n"/>
-      <c r="F137" s="9" t="n"/>
+      <c r="F137" s="2" t="n"/>
       <c r="G137" s="2" t="n"/>
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="n"/>
     </row>
-    <row r="138" ht="39.7" customHeight="1">
+    <row r="138" ht="62" customHeight="1">
       <c r="A138" s="9" t="n"/>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C138" s="25">
-        <f>ROUNDUP(F134/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C138" s="9">
+        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
         <v/>
       </c>
       <c r="D138" s="2" t="n"/>
@@ -25952,11 +25976,11 @@
       <c r="A139" s="9" t="n"/>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C139" s="25">
-        <f>ROUNDUP(F134/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C139" s="8">
+        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
         <v/>
       </c>
       <c r="D139" s="2" t="n"/>
@@ -25967,51 +25991,61 @@
       <c r="I139" s="2" t="n"/>
     </row>
     <row r="140" ht="39.7" customHeight="1">
-      <c r="A140" s="13" t="n"/>
-      <c r="B140" s="14" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C140" s="13">
-        <f>Datos_balance!$B$13</f>
-        <v/>
-      </c>
-      <c r="D140" s="20" t="n"/>
-      <c r="E140" s="20" t="n"/>
-      <c r="F140" s="13" t="n"/>
+      <c r="A140" s="9" t="n"/>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C140" s="25">
+        <f>ROUNDUP(F136/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+        <v/>
+      </c>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="9" t="n"/>
       <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="n"/>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="n"/>
-      <c r="B141" s="2" t="n"/>
-      <c r="C141" s="2" t="n"/>
+    <row r="141" ht="39.7" customHeight="1">
+      <c r="A141" s="9" t="n"/>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C141" s="25">
+        <f>ROUNDUP(F136/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+        <v/>
+      </c>
       <c r="D141" s="2" t="n"/>
       <c r="E141" s="2" t="n"/>
-      <c r="F141" s="2" t="n"/>
+      <c r="F141" s="9" t="n"/>
       <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="n"/>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="n"/>
-      <c r="B142" s="2" t="n"/>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="2" t="n"/>
-      <c r="F142" s="2" t="n"/>
+    <row r="142" ht="39.7" customHeight="1">
+      <c r="A142" s="13" t="n"/>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C142" s="13">
+        <f>Datos_balance!$B$13</f>
+        <v/>
+      </c>
+      <c r="D142" s="20" t="n"/>
+      <c r="E142" s="20" t="n"/>
+      <c r="F142" s="13" t="n"/>
       <c r="G142" s="2" t="n"/>
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="2" t="n"/>
     </row>
-    <row r="143" ht="39.7" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>LOCAL  09 - Dormitorio suite   (PB)</t>
-        </is>
-      </c>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
       <c r="B143" s="2" t="n"/>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n"/>
@@ -26021,144 +26055,121 @@
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="n"/>
     </row>
-    <row r="144" ht="39.7" customHeight="1">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n"/>
       <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="n"/>
     </row>
     <row r="145" ht="39.7" customHeight="1">
-      <c r="A145" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B145" s="33" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="n"/>
-      <c r="D145" s="9" t="n"/>
-      <c r="E145" s="9" t="n"/>
-      <c r="F145" s="9" t="n"/>
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>LOCAL  09 - Dormitorio suite   (PB)</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
       <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="n"/>
     </row>
-    <row r="146" ht="62" customHeight="1">
-      <c r="A146" s="9" t="n"/>
-      <c r="B146" s="34" t="inlineStr">
+    <row r="146" ht="39.7" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="n"/>
+      <c r="H146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+    </row>
+    <row r="147" ht="39.7" customHeight="1">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B147" s="33" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="9" t="n"/>
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="9" t="n"/>
+      <c r="G147" s="2" t="n"/>
+      <c r="H147" s="2" t="n"/>
+      <c r="I147" s="2" t="n"/>
+    </row>
+    <row r="148" ht="62" customHeight="1">
+      <c r="A148" s="9" t="n"/>
+      <c r="B148" s="34" t="inlineStr">
         <is>
           <t>VA01 (2)</t>
         </is>
       </c>
-      <c r="C146" s="9">
-        <f>IF(COUNT(H146,I146)&lt;2,"",TEXT(H146,"0.00")&amp;" x "&amp;TEXT(I146,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D146" s="8">
-        <f>IF(COUNT(H146,I146)&lt;2,"",ROUND(H146*I146,2))</f>
-        <v/>
-      </c>
-      <c r="E146" s="25" t="n">
+      <c r="C148" s="9">
+        <f>IF(COUNT(H148,I148)&lt;2,"",TEXT(H148,"0.00")&amp;" x "&amp;TEXT(I148,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D148" s="8">
+        <f>IF(COUNT(H148,I148)&lt;2,"",ROUND(H148*I148,2))</f>
+        <v/>
+      </c>
+      <c r="E148" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="F146" s="28">
-        <f>IF(D146="","",ROUND(D146*E146,1))</f>
-        <v/>
-      </c>
-      <c r="G146" s="2" t="n"/>
-      <c r="H146" s="35" t="n">
+      <c r="F148" s="28">
+        <f>IF(D148="","",ROUND(D148*E148,1))</f>
+        <v/>
+      </c>
+      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="35" t="n">
         <v>0.75</v>
       </c>
-      <c r="I146" s="35" t="n">
+      <c r="I148" s="35" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="147" ht="62" customHeight="1">
-      <c r="A147" s="9" t="n"/>
-      <c r="B147" s="34" t="inlineStr">
-        <is>
-          <t>PV03</t>
-        </is>
-      </c>
-      <c r="C147" s="9">
-        <f>IF(COUNT(H147,I147)&lt;2,"",TEXT(H147,"0.00")&amp;" x "&amp;TEXT(I147,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D147" s="8">
-        <f>IF(COUNT(H147,I147)&lt;2,"",ROUND(H147*I147,2))</f>
-        <v/>
-      </c>
-      <c r="E147" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F147" s="28">
-        <f>IF(D147="","",ROUND(D147*E147,1))</f>
-        <v/>
-      </c>
-      <c r="G147" s="2" t="n"/>
-      <c r="H147" s="35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="I147" s="35" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="148" ht="39.7" customHeight="1">
-      <c r="A148" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B148" s="33" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="n"/>
-      <c r="D148" s="9" t="n"/>
-      <c r="E148" s="9" t="n"/>
-      <c r="F148" s="9" t="n"/>
-      <c r="G148" s="2" t="n"/>
-      <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="n"/>
     </row>
     <row r="149" ht="62" customHeight="1">
       <c r="A149" s="9" t="n"/>
       <c r="B149" s="34" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>PV03</t>
         </is>
       </c>
       <c r="C149" s="9">
@@ -26170,41 +26181,38 @@
         <v/>
       </c>
       <c r="E149" s="25" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F149" s="28">
         <f>IF(D149="","",ROUND(D149*E149,1))</f>
         <v/>
       </c>
       <c r="G149" s="2" t="n"/>
-      <c r="H149" s="35" t="n"/>
-      <c r="I149" s="35" t="n"/>
-    </row>
-    <row r="150" ht="62" customHeight="1">
-      <c r="A150" s="9" t="n"/>
-      <c r="B150" s="34" t="inlineStr">
-        <is>
-          <t>AISLADAS (    )</t>
-        </is>
-      </c>
-      <c r="C150" s="9">
-        <f>IF(COUNT(H150,I150)&lt;2,"",TEXT(H150,"0.00")&amp;" x "&amp;TEXT(I150,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D150" s="8">
-        <f>IF(COUNT(H150,I150)&lt;2,"",ROUND(H150*I150,2))</f>
-        <v/>
-      </c>
-      <c r="E150" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F150" s="28">
-        <f>IF(D150="","",ROUND(D150*E150,1))</f>
-        <v/>
-      </c>
+      <c r="H149" s="35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I149" s="35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" ht="39.7" customHeight="1">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B150" s="33" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="n"/>
+      <c r="D150" s="9" t="n"/>
+      <c r="E150" s="9" t="n"/>
+      <c r="F150" s="9" t="n"/>
       <c r="G150" s="2" t="n"/>
-      <c r="H150" s="35" t="n"/>
-      <c r="I150" s="35" t="n"/>
+      <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
     </row>
     <row r="151" ht="62" customHeight="1">
       <c r="A151" s="9" t="n"/>
@@ -26262,7 +26270,7 @@
       <c r="A153" s="9" t="n"/>
       <c r="B153" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C153" s="9">
@@ -26274,25 +26282,21 @@
         <v/>
       </c>
       <c r="E153" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F153" s="28">
         <f>IF(D153="","",ROUND(D153*E153,1))</f>
         <v/>
       </c>
       <c r="G153" s="2" t="n"/>
-      <c r="H153" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I153" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H153" s="35" t="n"/>
+      <c r="I153" s="35" t="n"/>
     </row>
     <row r="154" ht="62" customHeight="1">
       <c r="A154" s="9" t="n"/>
       <c r="B154" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C154" s="9">
@@ -26304,19 +26308,15 @@
         <v/>
       </c>
       <c r="E154" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F154" s="28">
         <f>IF(D154="","",ROUND(D154*E154,1))</f>
         <v/>
       </c>
       <c r="G154" s="2" t="n"/>
-      <c r="H154" s="35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I154" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H154" s="35" t="n"/>
+      <c r="I154" s="35" t="n"/>
     </row>
     <row r="155" ht="62" customHeight="1">
       <c r="A155" s="9" t="n"/>
@@ -26378,88 +26378,99 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" ht="39.7" customHeight="1">
-      <c r="A157" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B157" s="33" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C157" s="9" t="n"/>
-      <c r="D157" s="9" t="n"/>
-      <c r="E157" s="9" t="n"/>
-      <c r="F157" s="9" t="n"/>
+    <row r="157" ht="62" customHeight="1">
+      <c r="A157" s="9" t="n"/>
+      <c r="B157" s="34" t="inlineStr">
+        <is>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C157" s="9">
+        <f>IF(COUNT(H157,I157)&lt;2,"",TEXT(H157,"0.00")&amp;" x "&amp;TEXT(I157,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D157" s="8">
+        <f>IF(COUNT(H157,I157)&lt;2,"",ROUND(H157*I157,2))</f>
+        <v/>
+      </c>
+      <c r="E157" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F157" s="28">
+        <f>IF(D157="","",ROUND(D157*E157,1))</f>
+        <v/>
+      </c>
       <c r="G157" s="2" t="n"/>
-      <c r="H157" s="2" t="n"/>
-      <c r="I157" s="2" t="n"/>
+      <c r="H157" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I157" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="158" ht="62" customHeight="1">
       <c r="A158" s="9" t="n"/>
       <c r="B158" s="34" t="inlineStr">
         <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="inlineStr"/>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C158" s="9">
+        <f>IF(COUNT(H158,I158)&lt;2,"",TEXT(H158,"0.00")&amp;" x "&amp;TEXT(I158,"0.00"))</f>
+        <v/>
+      </c>
       <c r="D158" s="8">
         <f>IF(COUNT(H158,I158)&lt;2,"",ROUND(H158*I158,2))</f>
         <v/>
       </c>
       <c r="E158" s="25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F158" s="28">
         <f>IF(D158="","",ROUND(D158*E158,1))</f>
         <v/>
       </c>
       <c r="G158" s="2" t="n"/>
-      <c r="H158" s="35" t="n"/>
-      <c r="I158" s="35" t="n"/>
-    </row>
-    <row r="159" ht="62" customHeight="1">
-      <c r="A159" s="9" t="n"/>
-      <c r="B159" s="34" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C159" s="9" t="inlineStr"/>
-      <c r="D159" s="8">
-        <f>IF(COUNT(H159,I159)&lt;2,"",ROUND(H159*I159,2))</f>
-        <v/>
-      </c>
-      <c r="E159" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F159" s="28">
-        <f>IF(D159="","",ROUND(D159*E159,1))</f>
-        <v/>
-      </c>
+      <c r="H158" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I158" s="35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" ht="39.7" customHeight="1">
+      <c r="A159" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B159" s="33" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C159" s="9" t="n"/>
+      <c r="D159" s="9" t="n"/>
+      <c r="E159" s="9" t="n"/>
+      <c r="F159" s="9" t="n"/>
       <c r="G159" s="2" t="n"/>
-      <c r="H159" s="35" t="n"/>
-      <c r="I159" s="35" t="n"/>
-    </row>
-    <row r="160" ht="39.7" customHeight="1">
+      <c r="H159" s="2" t="n"/>
+      <c r="I159" s="2" t="n"/>
+    </row>
+    <row r="160" ht="62" customHeight="1">
       <c r="A160" s="9" t="n"/>
       <c r="B160" s="34" t="inlineStr">
         <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C160" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D160" s="8" t="n">
-        <v>12.25</v>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="inlineStr"/>
+      <c r="D160" s="8">
+        <f>IF(COUNT(H160,I160)&lt;2,"",ROUND(H160*I160,2))</f>
+        <v/>
       </c>
       <c r="E160" s="25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F160" s="28">
         <f>IF(D160="","",ROUND(D160*E160,1))</f>
@@ -26469,30 +26480,34 @@
       <c r="H160" s="35" t="n"/>
       <c r="I160" s="35" t="n"/>
     </row>
-    <row r="161" ht="39.7" customHeight="1">
-      <c r="A161" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B161" s="33" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C161" s="9" t="n"/>
-      <c r="D161" s="9" t="n"/>
-      <c r="E161" s="9" t="n"/>
-      <c r="F161" s="9" t="n"/>
+    <row r="161" ht="62" customHeight="1">
+      <c r="A161" s="9" t="n"/>
+      <c r="B161" s="34" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C161" s="9" t="inlineStr"/>
+      <c r="D161" s="8">
+        <f>IF(COUNT(H161,I161)&lt;2,"",ROUND(H161*I161,2))</f>
+        <v/>
+      </c>
+      <c r="E161" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F161" s="28">
+        <f>IF(D161="","",ROUND(D161*E161,1))</f>
+        <v/>
+      </c>
       <c r="G161" s="2" t="n"/>
-      <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
+      <c r="H161" s="35" t="n"/>
+      <c r="I161" s="35" t="n"/>
     </row>
     <row r="162" ht="39.7" customHeight="1">
       <c r="A162" s="9" t="n"/>
       <c r="B162" s="34" t="inlineStr">
         <is>
-          <t>SOBRE TIERRA</t>
+          <t>TECHO ENTREPISO</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
@@ -26504,7 +26519,7 @@
         <v>12.25</v>
       </c>
       <c r="E162" s="25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F162" s="28">
         <f>IF(D162="","",ROUND(D162*E162,1))</f>
@@ -26514,57 +26529,56 @@
       <c r="H162" s="35" t="n"/>
       <c r="I162" s="35" t="n"/>
     </row>
-    <row r="163" ht="62" customHeight="1">
-      <c r="A163" s="9" t="n"/>
-      <c r="B163" s="34" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="inlineStr"/>
-      <c r="D163" s="8">
-        <f>IF(COUNT(H163,I163)&lt;2,"",ROUND(H163*I163,2))</f>
-        <v/>
-      </c>
-      <c r="E163" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="F163" s="28">
-        <f>IF(D163="","",ROUND(D163*E163,1))</f>
-        <v/>
-      </c>
+    <row r="163" ht="39.7" customHeight="1">
+      <c r="A163" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B163" s="33" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C163" s="9" t="n"/>
+      <c r="D163" s="9" t="n"/>
+      <c r="E163" s="9" t="n"/>
+      <c r="F163" s="9" t="n"/>
       <c r="G163" s="2" t="n"/>
-      <c r="H163" s="35" t="n"/>
-      <c r="I163" s="35" t="n"/>
+      <c r="H163" s="2" t="n"/>
+      <c r="I163" s="2" t="n"/>
     </row>
     <row r="164" ht="39.7" customHeight="1">
-      <c r="A164" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B164" s="33" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C164" s="9" t="n"/>
-      <c r="D164" s="16" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E164" s="9" t="n"/>
-      <c r="F164" s="9" t="n"/>
+      <c r="A164" s="9" t="n"/>
+      <c r="B164" s="34" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="E164" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F164" s="28">
+        <f>IF(D164="","",ROUND(D164*E164,1))</f>
+        <v/>
+      </c>
       <c r="G164" s="2" t="n"/>
-      <c r="H164" s="2" t="n"/>
-      <c r="I164" s="2" t="n"/>
+      <c r="H164" s="35" t="n"/>
+      <c r="I164" s="35" t="n"/>
     </row>
     <row r="165" ht="62" customHeight="1">
       <c r="A165" s="9" t="n"/>
       <c r="B165" s="34" t="inlineStr">
         <is>
-          <t>UNA PARED EXTERIOR</t>
+          <t>SOBRE LOCAL OCUPADO</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr"/>
@@ -26573,7 +26587,7 @@
         <v/>
       </c>
       <c r="E165" s="25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F165" s="28">
         <f>IF(D165="","",ROUND(D165*E165,1))</f>
@@ -26584,36 +26598,33 @@
       <c r="I165" s="35" t="n"/>
     </row>
     <row r="166" ht="39.7" customHeight="1">
-      <c r="A166" s="9" t="n"/>
-      <c r="B166" s="34" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C166" s="9" t="inlineStr">
-        <is>
-          <t>12.25 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="E166" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F166" s="28">
-        <f>IF(D166="","",ROUND(D166*E166,1))</f>
-        <v/>
-      </c>
+      <c r="A166" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B166" s="33" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="n"/>
       <c r="G166" s="2" t="n"/>
-      <c r="H166" s="35" t="n"/>
-      <c r="I166" s="35" t="n"/>
+      <c r="H166" s="2" t="n"/>
+      <c r="I166" s="2" t="n"/>
     </row>
     <row r="167" ht="62" customHeight="1">
       <c r="A167" s="9" t="n"/>
       <c r="B167" s="34" t="inlineStr">
         <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
+          <t>UNA PARED EXTERIOR</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr"/>
@@ -26622,7 +26633,7 @@
         <v/>
       </c>
       <c r="E167" s="25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F167" s="28">
         <f>IF(D167="","",ROUND(D167*E167,1))</f>
@@ -26632,109 +26643,122 @@
       <c r="H167" s="35" t="n"/>
       <c r="I167" s="35" t="n"/>
     </row>
-    <row r="168" ht="70" customHeight="1">
-      <c r="A168" s="16" t="inlineStr">
+    <row r="168" ht="39.7" customHeight="1">
+      <c r="A168" s="9" t="n"/>
+      <c r="B168" s="34" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>12.25 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="E168" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F168" s="28">
+        <f>IF(D168="","",ROUND(D168*E168,1))</f>
+        <v/>
+      </c>
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="35" t="n"/>
+      <c r="I168" s="35" t="n"/>
+    </row>
+    <row r="169" ht="62" customHeight="1">
+      <c r="A169" s="9" t="n"/>
+      <c r="B169" s="34" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr"/>
+      <c r="D169" s="8">
+        <f>IF(COUNT(H169,I169)&lt;2,"",ROUND(H169*I169,2))</f>
+        <v/>
+      </c>
+      <c r="E169" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F169" s="28">
+        <f>IF(D169="","",ROUND(D169*E169,1))</f>
+        <v/>
+      </c>
+      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="35" t="n"/>
+      <c r="I169" s="35" t="n"/>
+    </row>
+    <row r="170" ht="70" customHeight="1">
+      <c r="A170" s="16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B168" s="33" t="inlineStr">
+      <c r="B170" s="33" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C168" s="9" t="n"/>
-      <c r="D168" s="9" t="n"/>
-      <c r="E168" s="9" t="n"/>
-      <c r="F168" s="36">
-        <f>IF(F146="",0,F146)+IF(F147="",0,F147)+IF(F149="",0,F149)+IF(F150="",0,F150)+IF(F151="",0,F151)+IF(F152="",0,F152)+IF(F153="",0,F153)+IF(F154="",0,F154)+IF(F155="",0,F155)+IF(F156="",0,F156)+IF(F158="",0,F158)+IF(F159="",0,F159)+IF(F160="",0,F160)+IF(F162="",0,F162)+IF(F163="",0,F163)+IF(F165="",0,F165)+IF(F166="",0,F166)+IF(F167="",0,F167)</f>
-        <v/>
-      </c>
-      <c r="G168" s="2" t="n"/>
-      <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="n"/>
-    </row>
-    <row r="169" ht="47" customHeight="1">
-      <c r="A169" s="16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B169" s="33" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C169" s="9">
-        <f>TEXT(F168,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
-        <v/>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" s="2" t="n"/>
-      <c r="F169" s="36">
-        <f>ROUND(F168*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
-        <v/>
-      </c>
-      <c r="G169" s="2" t="n"/>
-      <c r="H169" s="2" t="n"/>
-      <c r="I169" s="2" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="n"/>
-      <c r="B170" s="2" t="n"/>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n"/>
-      <c r="E170" s="2" t="n"/>
-      <c r="F170" s="2" t="n"/>
+      <c r="C170" s="9" t="n"/>
+      <c r="D170" s="9" t="n"/>
+      <c r="E170" s="9" t="n"/>
+      <c r="F170" s="36">
+        <f>IF(F148="",0,F148)+IF(F149="",0,F149)+IF(F151="",0,F151)+IF(F152="",0,F152)+IF(F153="",0,F153)+IF(F154="",0,F154)+IF(F155="",0,F155)+IF(F156="",0,F156)+IF(F157="",0,F157)+IF(F158="",0,F158)+IF(F160="",0,F160)+IF(F161="",0,F161)+IF(F162="",0,F162)+IF(F164="",0,F164)+IF(F165="",0,F165)+IF(F167="",0,F167)+IF(F168="",0,F168)+IF(F169="",0,F169)</f>
+        <v/>
+      </c>
       <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="n"/>
     </row>
-    <row r="171" ht="62" customHeight="1">
-      <c r="A171" s="9" t="n"/>
-      <c r="B171" s="10" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+    <row r="171" ht="47" customHeight="1">
+      <c r="A171" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B171" s="33" t="inlineStr">
+        <is>
+          <t>PERDIDA TOTAL</t>
         </is>
       </c>
       <c r="C171" s="9">
-        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
+        <f>TEXT(F170,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
         <v/>
       </c>
       <c r="D171" s="2" t="n"/>
       <c r="E171" s="2" t="n"/>
-      <c r="F171" s="9" t="n"/>
+      <c r="F171" s="36">
+        <f>ROUND(F170*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
+        <v/>
+      </c>
       <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="n"/>
     </row>
-    <row r="172" ht="39.7" customHeight="1">
-      <c r="A172" s="9" t="n"/>
-      <c r="B172" s="10" t="inlineStr">
-        <is>
-          <t>Kcal/h por elemento</t>
-        </is>
-      </c>
-      <c r="C172" s="8">
-        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
-        <v/>
-      </c>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
       <c r="D172" s="2" t="n"/>
       <c r="E172" s="2" t="n"/>
-      <c r="F172" s="9" t="n"/>
+      <c r="F172" s="2" t="n"/>
       <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="n"/>
     </row>
-    <row r="173" ht="39.7" customHeight="1">
+    <row r="173" ht="62" customHeight="1">
       <c r="A173" s="9" t="n"/>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>Elementos necesarios</t>
-        </is>
-      </c>
-      <c r="C173" s="25">
-        <f>ROUNDUP(F169/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C173" s="9">
+        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
         <v/>
       </c>
       <c r="D173" s="2" t="n"/>
@@ -26748,11 +26772,11 @@
       <c r="A174" s="9" t="n"/>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Ancho del radiador (cm)</t>
-        </is>
-      </c>
-      <c r="C174" s="25">
-        <f>ROUNDUP(F169/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+          <t>Kcal/h por elemento</t>
+        </is>
+      </c>
+      <c r="C174" s="8">
+        <f>ROUND(Datos_balance!$B$14*Datos_balance!$B$15,2)</f>
         <v/>
       </c>
       <c r="D174" s="2" t="n"/>
@@ -26763,51 +26787,61 @@
       <c r="I174" s="2" t="n"/>
     </row>
     <row r="175" ht="39.7" customHeight="1">
-      <c r="A175" s="13" t="n"/>
-      <c r="B175" s="14" t="inlineStr">
-        <is>
-          <t>Radiador adoptado</t>
-        </is>
-      </c>
-      <c r="C175" s="13">
-        <f>Datos_balance!$B$13</f>
-        <v/>
-      </c>
-      <c r="D175" s="20" t="n"/>
-      <c r="E175" s="20" t="n"/>
-      <c r="F175" s="13" t="n"/>
+      <c r="A175" s="9" t="n"/>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>Elementos necesarios</t>
+        </is>
+      </c>
+      <c r="C175" s="25">
+        <f>ROUNDUP(F171/(Datos_balance!$B$14*Datos_balance!$B$15),0)</f>
+        <v/>
+      </c>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="9" t="n"/>
       <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="n"/>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="n"/>
-      <c r="B176" s="2" t="n"/>
-      <c r="C176" s="2" t="n"/>
+    <row r="176" ht="39.7" customHeight="1">
+      <c r="A176" s="9" t="n"/>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>Ancho del radiador (cm)</t>
+        </is>
+      </c>
+      <c r="C176" s="25">
+        <f>ROUNDUP(F171/(Datos_balance!$B$14*Datos_balance!$B$15),0)*Datos_balance!$B$16</f>
+        <v/>
+      </c>
       <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="n"/>
-      <c r="F176" s="2" t="n"/>
+      <c r="F176" s="9" t="n"/>
       <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="n"/>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="n"/>
-      <c r="B177" s="2" t="n"/>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" s="2" t="n"/>
-      <c r="F177" s="2" t="n"/>
+    <row r="177" ht="39.7" customHeight="1">
+      <c r="A177" s="13" t="n"/>
+      <c r="B177" s="14" t="inlineStr">
+        <is>
+          <t>Radiador adoptado</t>
+        </is>
+      </c>
+      <c r="C177" s="13">
+        <f>Datos_balance!$B$13</f>
+        <v/>
+      </c>
+      <c r="D177" s="20" t="n"/>
+      <c r="E177" s="20" t="n"/>
+      <c r="F177" s="13" t="n"/>
       <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="n"/>
     </row>
-    <row r="178" ht="39.7" customHeight="1">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>LOCAL  10 - Bano suite   (PB)</t>
-        </is>
-      </c>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
       <c r="B178" s="2" t="n"/>
       <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="n"/>
@@ -26817,99 +26851,76 @@
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="n"/>
     </row>
-    <row r="179" ht="39.7" customHeight="1">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F179" s="3" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="2" t="n"/>
       <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="2" t="n"/>
     </row>
     <row r="180" ht="39.7" customHeight="1">
-      <c r="A180" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B180" s="33" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C180" s="9" t="n"/>
-      <c r="D180" s="9" t="n"/>
-      <c r="E180" s="9" t="n"/>
-      <c r="F180" s="9" t="n"/>
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>LOCAL  10 - Bano suite   (PB)</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
       <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="n"/>
     </row>
-    <row r="181" ht="62" customHeight="1">
-      <c r="A181" s="9" t="n"/>
-      <c r="B181" s="34" t="inlineStr">
-        <is>
-          <t>VA02</t>
-        </is>
-      </c>
-      <c r="C181" s="9">
-        <f>IF(COUNT(H181,I181)&lt;2,"",TEXT(H181,"0.00")&amp;" x "&amp;TEXT(I181,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D181" s="8">
-        <f>IF(COUNT(H181,I181)&lt;2,"",ROUND(H181*I181,2))</f>
-        <v/>
-      </c>
-      <c r="E181" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F181" s="28">
-        <f>IF(D181="","",ROUND(D181*E181,1))</f>
-        <v/>
+    <row r="181" ht="39.7" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
       </c>
       <c r="G181" s="2" t="n"/>
-      <c r="H181" s="35" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I181" s="35" t="n">
-        <v>2.15</v>
-      </c>
+      <c r="H181" s="2" t="n"/>
+      <c r="I181" s="2" t="n"/>
     </row>
     <row r="182" ht="39.7" customHeight="1">
       <c r="A182" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B182" s="33" t="inlineStr">
         <is>
-          <t>PAREDES EXTERIORES</t>
+          <t>VENTANA</t>
         </is>
       </c>
       <c r="C182" s="9" t="n"/>
@@ -26924,7 +26935,7 @@
       <c r="A183" s="9" t="n"/>
       <c r="B183" s="34" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>VA02</t>
         </is>
       </c>
       <c r="C183" s="9">
@@ -26936,41 +26947,38 @@
         <v/>
       </c>
       <c r="E183" s="25" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F183" s="28">
         <f>IF(D183="","",ROUND(D183*E183,1))</f>
         <v/>
       </c>
       <c r="G183" s="2" t="n"/>
-      <c r="H183" s="35" t="n"/>
-      <c r="I183" s="35" t="n"/>
-    </row>
-    <row r="184" ht="62" customHeight="1">
-      <c r="A184" s="9" t="n"/>
-      <c r="B184" s="34" t="inlineStr">
-        <is>
-          <t>AISLADAS (    )</t>
-        </is>
-      </c>
-      <c r="C184" s="9">
-        <f>IF(COUNT(H184,I184)&lt;2,"",TEXT(H184,"0.00")&amp;" x "&amp;TEXT(I184,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D184" s="8">
-        <f>IF(COUNT(H184,I184)&lt;2,"",ROUND(H184*I184,2))</f>
-        <v/>
-      </c>
-      <c r="E184" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F184" s="28">
-        <f>IF(D184="","",ROUND(D184*E184,1))</f>
-        <v/>
-      </c>
+      <c r="H183" s="35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I183" s="35" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="184" ht="39.7" customHeight="1">
+      <c r="A184" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B184" s="33" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="n"/>
+      <c r="D184" s="9" t="n"/>
+      <c r="E184" s="9" t="n"/>
+      <c r="F184" s="9" t="n"/>
       <c r="G184" s="2" t="n"/>
-      <c r="H184" s="35" t="n"/>
-      <c r="I184" s="35" t="n"/>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
     </row>
     <row r="185" ht="62" customHeight="1">
       <c r="A185" s="9" t="n"/>
@@ -27028,7 +27036,7 @@
       <c r="A187" s="9" t="n"/>
       <c r="B187" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C187" s="9">
@@ -27040,25 +27048,21 @@
         <v/>
       </c>
       <c r="E187" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F187" s="28">
         <f>IF(D187="","",ROUND(D187*E187,1))</f>
         <v/>
       </c>
       <c r="G187" s="2" t="n"/>
-      <c r="H187" s="35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I187" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H187" s="35" t="n"/>
+      <c r="I187" s="35" t="n"/>
     </row>
     <row r="188" ht="62" customHeight="1">
       <c r="A188" s="9" t="n"/>
       <c r="B188" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C188" s="9">
@@ -27070,19 +27074,15 @@
         <v/>
       </c>
       <c r="E188" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F188" s="28">
         <f>IF(D188="","",ROUND(D188*E188,1))</f>
         <v/>
       </c>
       <c r="G188" s="2" t="n"/>
-      <c r="H188" s="35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I188" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H188" s="35" t="n"/>
+      <c r="I188" s="35" t="n"/>
     </row>
     <row r="189" ht="62" customHeight="1">
       <c r="A189" s="9" t="n"/>
@@ -27144,88 +27144,99 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" ht="39.7" customHeight="1">
-      <c r="A191" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B191" s="33" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C191" s="9" t="n"/>
-      <c r="D191" s="9" t="n"/>
-      <c r="E191" s="9" t="n"/>
-      <c r="F191" s="9" t="n"/>
+    <row r="191" ht="62" customHeight="1">
+      <c r="A191" s="9" t="n"/>
+      <c r="B191" s="34" t="inlineStr">
+        <is>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C191" s="9">
+        <f>IF(COUNT(H191,I191)&lt;2,"",TEXT(H191,"0.00")&amp;" x "&amp;TEXT(I191,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D191" s="8">
+        <f>IF(COUNT(H191,I191)&lt;2,"",ROUND(H191*I191,2))</f>
+        <v/>
+      </c>
+      <c r="E191" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F191" s="28">
+        <f>IF(D191="","",ROUND(D191*E191,1))</f>
+        <v/>
+      </c>
       <c r="G191" s="2" t="n"/>
-      <c r="H191" s="2" t="n"/>
-      <c r="I191" s="2" t="n"/>
+      <c r="H191" s="35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I191" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="192" ht="62" customHeight="1">
       <c r="A192" s="9" t="n"/>
       <c r="B192" s="34" t="inlineStr">
         <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C192" s="9" t="inlineStr"/>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C192" s="9">
+        <f>IF(COUNT(H192,I192)&lt;2,"",TEXT(H192,"0.00")&amp;" x "&amp;TEXT(I192,"0.00"))</f>
+        <v/>
+      </c>
       <c r="D192" s="8">
         <f>IF(COUNT(H192,I192)&lt;2,"",ROUND(H192*I192,2))</f>
         <v/>
       </c>
       <c r="E192" s="25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F192" s="28">
         <f>IF(D192="","",ROUND(D192*E192,1))</f>
         <v/>
       </c>
       <c r="G192" s="2" t="n"/>
-      <c r="H192" s="35" t="n"/>
-      <c r="I192" s="35" t="n"/>
-    </row>
-    <row r="193" ht="62" customHeight="1">
-      <c r="A193" s="9" t="n"/>
-      <c r="B193" s="34" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C193" s="9" t="inlineStr"/>
-      <c r="D193" s="8">
-        <f>IF(COUNT(H193,I193)&lt;2,"",ROUND(H193*I193,2))</f>
-        <v/>
-      </c>
-      <c r="E193" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F193" s="28">
-        <f>IF(D193="","",ROUND(D193*E193,1))</f>
-        <v/>
-      </c>
+      <c r="H192" s="35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I192" s="35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" ht="39.7" customHeight="1">
+      <c r="A193" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B193" s="33" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C193" s="9" t="n"/>
+      <c r="D193" s="9" t="n"/>
+      <c r="E193" s="9" t="n"/>
+      <c r="F193" s="9" t="n"/>
       <c r="G193" s="2" t="n"/>
-      <c r="H193" s="35" t="n"/>
-      <c r="I193" s="35" t="n"/>
-    </row>
-    <row r="194" ht="39.7" customHeight="1">
+      <c r="H193" s="2" t="n"/>
+      <c r="I193" s="2" t="n"/>
+    </row>
+    <row r="194" ht="62" customHeight="1">
       <c r="A194" s="9" t="n"/>
       <c r="B194" s="34" t="inlineStr">
         <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C194" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D194" s="8" t="n">
-        <v>5.61</v>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="inlineStr"/>
+      <c r="D194" s="8">
+        <f>IF(COUNT(H194,I194)&lt;2,"",ROUND(H194*I194,2))</f>
+        <v/>
       </c>
       <c r="E194" s="25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F194" s="28">
         <f>IF(D194="","",ROUND(D194*E194,1))</f>
@@ -27235,30 +27246,34 @@
       <c r="H194" s="35" t="n"/>
       <c r="I194" s="35" t="n"/>
     </row>
-    <row r="195" ht="39.7" customHeight="1">
-      <c r="A195" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B195" s="33" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C195" s="9" t="n"/>
-      <c r="D195" s="9" t="n"/>
-      <c r="E195" s="9" t="n"/>
-      <c r="F195" s="9" t="n"/>
+    <row r="195" ht="62" customHeight="1">
+      <c r="A195" s="9" t="n"/>
+      <c r="B195" s="34" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C195" s="9" t="inlineStr"/>
+      <c r="D195" s="8">
+        <f>IF(COUNT(H195,I195)&lt;2,"",ROUND(H195*I195,2))</f>
+        <v/>
+      </c>
+      <c r="E195" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F195" s="28">
+        <f>IF(D195="","",ROUND(D195*E195,1))</f>
+        <v/>
+      </c>
       <c r="G195" s="2" t="n"/>
-      <c r="H195" s="2" t="n"/>
-      <c r="I195" s="2" t="n"/>
+      <c r="H195" s="35" t="n"/>
+      <c r="I195" s="35" t="n"/>
     </row>
     <row r="196" ht="39.7" customHeight="1">
       <c r="A196" s="9" t="n"/>
       <c r="B196" s="34" t="inlineStr">
         <is>
-          <t>SOBRE TIERRA</t>
+          <t>TECHO ENTREPISO</t>
         </is>
       </c>
       <c r="C196" s="9" t="inlineStr">
@@ -27270,7 +27285,7 @@
         <v>5.61</v>
       </c>
       <c r="E196" s="25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F196" s="28">
         <f>IF(D196="","",ROUND(D196*E196,1))</f>
@@ -27280,69 +27295,65 @@
       <c r="H196" s="35" t="n"/>
       <c r="I196" s="35" t="n"/>
     </row>
-    <row r="197" ht="62" customHeight="1">
-      <c r="A197" s="9" t="n"/>
-      <c r="B197" s="34" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C197" s="9" t="inlineStr"/>
-      <c r="D197" s="8">
-        <f>IF(COUNT(H197,I197)&lt;2,"",ROUND(H197*I197,2))</f>
-        <v/>
-      </c>
-      <c r="E197" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="F197" s="28">
-        <f>IF(D197="","",ROUND(D197*E197,1))</f>
-        <v/>
-      </c>
+    <row r="197" ht="39.7" customHeight="1">
+      <c r="A197" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B197" s="33" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C197" s="9" t="n"/>
+      <c r="D197" s="9" t="n"/>
+      <c r="E197" s="9" t="n"/>
+      <c r="F197" s="9" t="n"/>
       <c r="G197" s="2" t="n"/>
-      <c r="H197" s="35" t="n"/>
-      <c r="I197" s="35" t="n"/>
+      <c r="H197" s="2" t="n"/>
+      <c r="I197" s="2" t="n"/>
     </row>
     <row r="198" ht="39.7" customHeight="1">
-      <c r="A198" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B198" s="33" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C198" s="9" t="n"/>
-      <c r="D198" s="16" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E198" s="9" t="n"/>
-      <c r="F198" s="9" t="n"/>
+      <c r="A198" s="9" t="n"/>
+      <c r="B198" s="34" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="E198" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F198" s="28">
+        <f>IF(D198="","",ROUND(D198*E198,1))</f>
+        <v/>
+      </c>
       <c r="G198" s="2" t="n"/>
-      <c r="H198" s="2" t="n"/>
-      <c r="I198" s="2" t="n"/>
-    </row>
-    <row r="199" ht="39.7" customHeight="1">
+      <c r="H198" s="35" t="n"/>
+      <c r="I198" s="35" t="n"/>
+    </row>
+    <row r="199" ht="62" customHeight="1">
       <c r="A199" s="9" t="n"/>
       <c r="B199" s="34" t="inlineStr">
         <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C199" s="9" t="inlineStr">
-        <is>
-          <t>5.61 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D199" s="8" t="n">
-        <v>16.83</v>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C199" s="9" t="inlineStr"/>
+      <c r="D199" s="8">
+        <f>IF(COUNT(H199,I199)&lt;2,"",ROUND(H199*I199,2))</f>
+        <v/>
       </c>
       <c r="E199" s="25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F199" s="28">
         <f>IF(D199="","",ROUND(D199*E199,1))</f>
@@ -27352,43 +27363,46 @@
       <c r="H199" s="35" t="n"/>
       <c r="I199" s="35" t="n"/>
     </row>
-    <row r="200" ht="62" customHeight="1">
-      <c r="A200" s="9" t="n"/>
-      <c r="B200" s="34" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C200" s="9" t="inlineStr"/>
-      <c r="D200" s="8">
-        <f>IF(COUNT(H200,I200)&lt;2,"",ROUND(H200*I200,2))</f>
-        <v/>
-      </c>
-      <c r="E200" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F200" s="28">
-        <f>IF(D200="","",ROUND(D200*E200,1))</f>
-        <v/>
-      </c>
+    <row r="200" ht="39.7" customHeight="1">
+      <c r="A200" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B200" s="33" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C200" s="9" t="n"/>
+      <c r="D200" s="16" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E200" s="9" t="n"/>
+      <c r="F200" s="9" t="n"/>
       <c r="G200" s="2" t="n"/>
-      <c r="H200" s="35" t="n"/>
-      <c r="I200" s="35" t="n"/>
-    </row>
-    <row r="201" ht="62" customHeight="1">
+      <c r="H200" s="2" t="n"/>
+      <c r="I200" s="2" t="n"/>
+    </row>
+    <row r="201" ht="39.7" customHeight="1">
       <c r="A201" s="9" t="n"/>
       <c r="B201" s="34" t="inlineStr">
         <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C201" s="9" t="inlineStr"/>
-      <c r="D201" s="8">
-        <f>IF(COUNT(H201,I201)&lt;2,"",ROUND(H201*I201,2))</f>
-        <v/>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>5.61 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D201" s="8" t="n">
+        <v>16.83</v>
       </c>
       <c r="E201" s="25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F201" s="28">
         <f>IF(D201="","",ROUND(D201*E201,1))</f>
@@ -27398,109 +27412,119 @@
       <c r="H201" s="35" t="n"/>
       <c r="I201" s="35" t="n"/>
     </row>
-    <row r="202" ht="70" customHeight="1">
-      <c r="A202" s="16" t="inlineStr">
+    <row r="202" ht="62" customHeight="1">
+      <c r="A202" s="9" t="n"/>
+      <c r="B202" s="34" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C202" s="9" t="inlineStr"/>
+      <c r="D202" s="8">
+        <f>IF(COUNT(H202,I202)&lt;2,"",ROUND(H202*I202,2))</f>
+        <v/>
+      </c>
+      <c r="E202" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F202" s="28">
+        <f>IF(D202="","",ROUND(D202*E202,1))</f>
+        <v/>
+      </c>
+      <c r="G202" s="2" t="n"/>
+      <c r="H202" s="35" t="n"/>
+      <c r="I202" s="35" t="n"/>
+    </row>
+    <row r="203" ht="62" customHeight="1">
+      <c r="A203" s="9" t="n"/>
+      <c r="B203" s="34" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C203" s="9" t="inlineStr"/>
+      <c r="D203" s="8">
+        <f>IF(COUNT(H203,I203)&lt;2,"",ROUND(H203*I203,2))</f>
+        <v/>
+      </c>
+      <c r="E203" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F203" s="28">
+        <f>IF(D203="","",ROUND(D203*E203,1))</f>
+        <v/>
+      </c>
+      <c r="G203" s="2" t="n"/>
+      <c r="H203" s="35" t="n"/>
+      <c r="I203" s="35" t="n"/>
+    </row>
+    <row r="204" ht="70" customHeight="1">
+      <c r="A204" s="16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B202" s="33" t="inlineStr">
+      <c r="B204" s="33" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C202" s="9" t="n"/>
-      <c r="D202" s="9" t="n"/>
-      <c r="E202" s="9" t="n"/>
-      <c r="F202" s="36">
-        <f>IF(F181="",0,F181)+IF(F183="",0,F183)+IF(F184="",0,F184)+IF(F185="",0,F185)+IF(F186="",0,F186)+IF(F187="",0,F187)+IF(F188="",0,F188)+IF(F189="",0,F189)+IF(F190="",0,F190)+IF(F192="",0,F192)+IF(F193="",0,F193)+IF(F194="",0,F194)+IF(F196="",0,F196)+IF(F197="",0,F197)+IF(F199="",0,F199)+IF(F200="",0,F200)+IF(F201="",0,F201)</f>
-        <v/>
-      </c>
-      <c r="G202" s="2" t="n"/>
-      <c r="H202" s="2" t="n"/>
-      <c r="I202" s="2" t="n"/>
-    </row>
-    <row r="203" ht="47" customHeight="1">
-      <c r="A203" s="16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B203" s="33" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C203" s="9">
-        <f>TEXT(F202,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
-        <v/>
-      </c>
-      <c r="D203" s="2" t="n"/>
-      <c r="E203" s="2" t="n"/>
-      <c r="F203" s="36">
-        <f>ROUND(F202*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
-        <v/>
-      </c>
-      <c r="G203" s="2" t="n"/>
-      <c r="H203" s="2" t="n"/>
-      <c r="I203" s="2" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="n"/>
-      <c r="B204" s="2" t="n"/>
-      <c r="C204" s="2" t="n"/>
-      <c r="D204" s="2" t="n"/>
-      <c r="E204" s="2" t="n"/>
-      <c r="F204" s="2" t="n"/>
+      <c r="C204" s="9" t="n"/>
+      <c r="D204" s="9" t="n"/>
+      <c r="E204" s="9" t="n"/>
+      <c r="F204" s="36">
+        <f>IF(F183="",0,F183)+IF(F185="",0,F185)+IF(F186="",0,F186)+IF(F187="",0,F187)+IF(F188="",0,F188)+IF(F189="",0,F189)+IF(F190="",0,F190)+IF(F191="",0,F191)+IF(F192="",0,F192)+IF(F194="",0,F194)+IF(F195="",0,F195)+IF(F196="",0,F196)+IF(F198="",0,F198)+IF(F199="",0,F199)+IF(F201="",0,F201)+IF(F202="",0,F202)+IF(F203="",0,F203)</f>
+        <v/>
+      </c>
       <c r="G204" s="2" t="n"/>
       <c r="H204" s="2" t="n"/>
       <c r="I204" s="2" t="n"/>
     </row>
-    <row r="205" ht="62" customHeight="1">
-      <c r="A205" s="9" t="n"/>
-      <c r="B205" s="10" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+    <row r="205" ht="47" customHeight="1">
+      <c r="A205" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B205" s="33" t="inlineStr">
+        <is>
+          <t>PERDIDA TOTAL</t>
         </is>
       </c>
       <c r="C205" s="9">
-        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
+        <f>TEXT(F204,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
         <v/>
       </c>
       <c r="D205" s="2" t="n"/>
       <c r="E205" s="2" t="n"/>
-      <c r="F205" s="9" t="n"/>
+      <c r="F205" s="36">
+        <f>ROUND(F204*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
+        <v/>
+      </c>
       <c r="G205" s="2" t="n"/>
       <c r="H205" s="2" t="n"/>
       <c r="I205" s="2" t="n"/>
     </row>
-    <row r="206" ht="39.7" customHeight="1">
-      <c r="A206" s="9" t="n"/>
-      <c r="B206" s="10" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C206" s="25">
-        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
-        <v/>
-      </c>
+    <row r="206">
+      <c r="A206" s="2" t="n"/>
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="2" t="n"/>
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="2" t="n"/>
-      <c r="F206" s="9" t="n"/>
+      <c r="F206" s="2" t="n"/>
       <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
       <c r="I206" s="2" t="n"/>
     </row>
-    <row r="207" ht="39.7" customHeight="1">
+    <row r="207" ht="62" customHeight="1">
       <c r="A207" s="9" t="n"/>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
-        </is>
-      </c>
-      <c r="C207" s="25">
-        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C207" s="9">
+        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
         <v/>
       </c>
       <c r="D207" s="2" t="n"/>
@@ -27510,15 +27534,15 @@
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="2" t="n"/>
     </row>
-    <row r="208" ht="47" customHeight="1">
+    <row r="208" ht="39.7" customHeight="1">
       <c r="A208" s="9" t="n"/>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C208" s="25">
-        <f>IF(F203&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F203/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
+        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D208" s="2" t="n"/>
@@ -27528,52 +27552,62 @@
       <c r="H208" s="2" t="n"/>
       <c r="I208" s="2" t="n"/>
     </row>
-    <row r="209" ht="47" customHeight="1">
-      <c r="A209" s="13" t="n"/>
-      <c r="B209" s="14" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C209" s="13">
-        <f>IF(F203&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
-        <v/>
-      </c>
-      <c r="D209" s="20" t="n"/>
-      <c r="E209" s="20" t="n"/>
-      <c r="F209" s="13" t="n"/>
+    <row r="209" ht="39.7" customHeight="1">
+      <c r="A209" s="9" t="n"/>
+      <c r="B209" s="10" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
+        </is>
+      </c>
+      <c r="C209" s="25">
+        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="n"/>
+      <c r="F209" s="9" t="n"/>
       <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
       <c r="I209" s="2" t="n"/>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="n"/>
-      <c r="B210" s="2" t="n"/>
-      <c r="C210" s="2" t="n"/>
+    <row r="210" ht="47" customHeight="1">
+      <c r="A210" s="9" t="n"/>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C210" s="25">
+        <f>IF(F205&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F205/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
+        <v/>
+      </c>
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="2" t="n"/>
-      <c r="F210" s="2" t="n"/>
+      <c r="F210" s="9" t="n"/>
       <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
       <c r="I210" s="2" t="n"/>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="n"/>
-      <c r="B211" s="2" t="n"/>
-      <c r="C211" s="2" t="n"/>
-      <c r="D211" s="2" t="n"/>
-      <c r="E211" s="2" t="n"/>
-      <c r="F211" s="2" t="n"/>
+    <row r="211" ht="47" customHeight="1">
+      <c r="A211" s="13" t="n"/>
+      <c r="B211" s="14" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C211" s="13">
+        <f>IF(F205&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
+        <v/>
+      </c>
+      <c r="D211" s="20" t="n"/>
+      <c r="E211" s="20" t="n"/>
+      <c r="F211" s="13" t="n"/>
       <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
       <c r="I211" s="2" t="n"/>
     </row>
-    <row r="212" ht="39.7" customHeight="1">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>LOCAL  11 - Bano visitas   (PB)</t>
-        </is>
-      </c>
+    <row r="212">
+      <c r="A212" s="2" t="n"/>
       <c r="B212" s="2" t="n"/>
       <c r="C212" s="2" t="n"/>
       <c r="D212" s="2" t="n"/>
@@ -27583,95 +27617,76 @@
       <c r="H212" s="2" t="n"/>
       <c r="I212" s="2" t="n"/>
     </row>
-    <row r="213" ht="39.7" customHeight="1">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="213">
+      <c r="A213" s="2" t="n"/>
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="2" t="n"/>
+      <c r="D213" s="2" t="n"/>
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="2" t="n"/>
       <c r="G213" s="2" t="n"/>
       <c r="H213" s="2" t="n"/>
       <c r="I213" s="2" t="n"/>
     </row>
     <row r="214" ht="39.7" customHeight="1">
-      <c r="A214" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B214" s="33" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C214" s="9" t="n"/>
-      <c r="D214" s="9" t="n"/>
-      <c r="E214" s="9" t="n"/>
-      <c r="F214" s="9" t="n"/>
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>LOCAL  11 - Bano visitas   (PB)</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="n"/>
       <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
       <c r="I214" s="2" t="n"/>
     </row>
-    <row r="215" ht="62" customHeight="1">
-      <c r="A215" s="9" t="n"/>
-      <c r="B215" s="34" t="inlineStr">
-        <is>
-          <t>(sin aberturas)</t>
-        </is>
-      </c>
-      <c r="C215" s="9">
-        <f>IF(COUNT(H215,I215)&lt;2,"",TEXT(H215,"0.00")&amp;" x "&amp;TEXT(I215,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D215" s="8">
-        <f>IF(COUNT(H215,I215)&lt;2,"",ROUND(H215*I215,2))</f>
-        <v/>
-      </c>
-      <c r="E215" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F215" s="28">
-        <f>IF(D215="","",ROUND(D215*E215,1))</f>
-        <v/>
+    <row r="215" ht="39.7" customHeight="1">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
       </c>
       <c r="G215" s="2" t="n"/>
-      <c r="H215" s="35" t="n"/>
-      <c r="I215" s="35" t="n"/>
+      <c r="H215" s="2" t="n"/>
+      <c r="I215" s="2" t="n"/>
     </row>
     <row r="216" ht="39.7" customHeight="1">
       <c r="A216" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B216" s="33" t="inlineStr">
         <is>
-          <t>PAREDES EXTERIORES</t>
+          <t>VENTANA</t>
         </is>
       </c>
       <c r="C216" s="9" t="n"/>
@@ -27686,7 +27701,7 @@
       <c r="A217" s="9" t="n"/>
       <c r="B217" s="34" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>(sin aberturas)</t>
         </is>
       </c>
       <c r="C217" s="9">
@@ -27698,7 +27713,7 @@
         <v/>
       </c>
       <c r="E217" s="25" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F217" s="28">
         <f>IF(D217="","",ROUND(D217*E217,1))</f>
@@ -27708,31 +27723,24 @@
       <c r="H217" s="35" t="n"/>
       <c r="I217" s="35" t="n"/>
     </row>
-    <row r="218" ht="62" customHeight="1">
-      <c r="A218" s="9" t="n"/>
-      <c r="B218" s="34" t="inlineStr">
-        <is>
-          <t>AISLADAS (    )</t>
-        </is>
-      </c>
-      <c r="C218" s="9">
-        <f>IF(COUNT(H218,I218)&lt;2,"",TEXT(H218,"0.00")&amp;" x "&amp;TEXT(I218,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D218" s="8">
-        <f>IF(COUNT(H218,I218)&lt;2,"",ROUND(H218*I218,2))</f>
-        <v/>
-      </c>
-      <c r="E218" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F218" s="28">
-        <f>IF(D218="","",ROUND(D218*E218,1))</f>
-        <v/>
-      </c>
+    <row r="218" ht="39.7" customHeight="1">
+      <c r="A218" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B218" s="33" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C218" s="9" t="n"/>
+      <c r="D218" s="9" t="n"/>
+      <c r="E218" s="9" t="n"/>
+      <c r="F218" s="9" t="n"/>
       <c r="G218" s="2" t="n"/>
-      <c r="H218" s="35" t="n"/>
-      <c r="I218" s="35" t="n"/>
+      <c r="H218" s="2" t="n"/>
+      <c r="I218" s="2" t="n"/>
     </row>
     <row r="219" ht="62" customHeight="1">
       <c r="A219" s="9" t="n"/>
@@ -27790,7 +27798,7 @@
       <c r="A221" s="9" t="n"/>
       <c r="B221" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C221" s="9">
@@ -27802,25 +27810,21 @@
         <v/>
       </c>
       <c r="E221" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F221" s="28">
         <f>IF(D221="","",ROUND(D221*E221,1))</f>
         <v/>
       </c>
       <c r="G221" s="2" t="n"/>
-      <c r="H221" s="35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I221" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H221" s="35" t="n"/>
+      <c r="I221" s="35" t="n"/>
     </row>
     <row r="222" ht="62" customHeight="1">
       <c r="A222" s="9" t="n"/>
       <c r="B222" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C222" s="9">
@@ -27832,19 +27836,15 @@
         <v/>
       </c>
       <c r="E222" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F222" s="28">
         <f>IF(D222="","",ROUND(D222*E222,1))</f>
         <v/>
       </c>
       <c r="G222" s="2" t="n"/>
-      <c r="H222" s="35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I222" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H222" s="35" t="n"/>
+      <c r="I222" s="35" t="n"/>
     </row>
     <row r="223" ht="62" customHeight="1">
       <c r="A223" s="9" t="n"/>
@@ -27906,88 +27906,99 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" ht="39.7" customHeight="1">
-      <c r="A225" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B225" s="33" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C225" s="9" t="n"/>
-      <c r="D225" s="9" t="n"/>
-      <c r="E225" s="9" t="n"/>
-      <c r="F225" s="9" t="n"/>
+    <row r="225" ht="62" customHeight="1">
+      <c r="A225" s="9" t="n"/>
+      <c r="B225" s="34" t="inlineStr">
+        <is>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C225" s="9">
+        <f>IF(COUNT(H225,I225)&lt;2,"",TEXT(H225,"0.00")&amp;" x "&amp;TEXT(I225,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D225" s="8">
+        <f>IF(COUNT(H225,I225)&lt;2,"",ROUND(H225*I225,2))</f>
+        <v/>
+      </c>
+      <c r="E225" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F225" s="28">
+        <f>IF(D225="","",ROUND(D225*E225,1))</f>
+        <v/>
+      </c>
       <c r="G225" s="2" t="n"/>
-      <c r="H225" s="2" t="n"/>
-      <c r="I225" s="2" t="n"/>
+      <c r="H225" s="35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I225" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="226" ht="62" customHeight="1">
       <c r="A226" s="9" t="n"/>
       <c r="B226" s="34" t="inlineStr">
         <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C226" s="9" t="inlineStr"/>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C226" s="9">
+        <f>IF(COUNT(H226,I226)&lt;2,"",TEXT(H226,"0.00")&amp;" x "&amp;TEXT(I226,"0.00"))</f>
+        <v/>
+      </c>
       <c r="D226" s="8">
         <f>IF(COUNT(H226,I226)&lt;2,"",ROUND(H226*I226,2))</f>
         <v/>
       </c>
       <c r="E226" s="25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F226" s="28">
         <f>IF(D226="","",ROUND(D226*E226,1))</f>
         <v/>
       </c>
       <c r="G226" s="2" t="n"/>
-      <c r="H226" s="35" t="n"/>
-      <c r="I226" s="35" t="n"/>
-    </row>
-    <row r="227" ht="62" customHeight="1">
-      <c r="A227" s="9" t="n"/>
-      <c r="B227" s="34" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C227" s="9" t="inlineStr"/>
-      <c r="D227" s="8">
-        <f>IF(COUNT(H227,I227)&lt;2,"",ROUND(H227*I227,2))</f>
-        <v/>
-      </c>
-      <c r="E227" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F227" s="28">
-        <f>IF(D227="","",ROUND(D227*E227,1))</f>
-        <v/>
-      </c>
+      <c r="H226" s="35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I226" s="35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" ht="39.7" customHeight="1">
+      <c r="A227" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B227" s="33" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C227" s="9" t="n"/>
+      <c r="D227" s="9" t="n"/>
+      <c r="E227" s="9" t="n"/>
+      <c r="F227" s="9" t="n"/>
       <c r="G227" s="2" t="n"/>
-      <c r="H227" s="35" t="n"/>
-      <c r="I227" s="35" t="n"/>
-    </row>
-    <row r="228" ht="39.7" customHeight="1">
+      <c r="H227" s="2" t="n"/>
+      <c r="I227" s="2" t="n"/>
+    </row>
+    <row r="228" ht="62" customHeight="1">
       <c r="A228" s="9" t="n"/>
       <c r="B228" s="34" t="inlineStr">
         <is>
-          <t>TECHO ENTREPISO</t>
-        </is>
-      </c>
-      <c r="C228" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D228" s="8" t="n">
-        <v>3.12</v>
+          <t>TECHO NO AISLADO</t>
+        </is>
+      </c>
+      <c r="C228" s="9" t="inlineStr"/>
+      <c r="D228" s="8">
+        <f>IF(COUNT(H228,I228)&lt;2,"",ROUND(H228*I228,2))</f>
+        <v/>
       </c>
       <c r="E228" s="25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F228" s="28">
         <f>IF(D228="","",ROUND(D228*E228,1))</f>
@@ -27997,30 +28008,34 @@
       <c r="H228" s="35" t="n"/>
       <c r="I228" s="35" t="n"/>
     </row>
-    <row r="229" ht="39.7" customHeight="1">
-      <c r="A229" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B229" s="33" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C229" s="9" t="n"/>
-      <c r="D229" s="9" t="n"/>
-      <c r="E229" s="9" t="n"/>
-      <c r="F229" s="9" t="n"/>
+    <row r="229" ht="62" customHeight="1">
+      <c r="A229" s="9" t="n"/>
+      <c r="B229" s="34" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C229" s="9" t="inlineStr"/>
+      <c r="D229" s="8">
+        <f>IF(COUNT(H229,I229)&lt;2,"",ROUND(H229*I229,2))</f>
+        <v/>
+      </c>
+      <c r="E229" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F229" s="28">
+        <f>IF(D229="","",ROUND(D229*E229,1))</f>
+        <v/>
+      </c>
       <c r="G229" s="2" t="n"/>
-      <c r="H229" s="2" t="n"/>
-      <c r="I229" s="2" t="n"/>
+      <c r="H229" s="35" t="n"/>
+      <c r="I229" s="35" t="n"/>
     </row>
     <row r="230" ht="39.7" customHeight="1">
       <c r="A230" s="9" t="n"/>
       <c r="B230" s="34" t="inlineStr">
         <is>
-          <t>SOBRE TIERRA</t>
+          <t>TECHO ENTREPISO</t>
         </is>
       </c>
       <c r="C230" s="9" t="inlineStr">
@@ -28032,7 +28047,7 @@
         <v>3.12</v>
       </c>
       <c r="E230" s="25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F230" s="28">
         <f>IF(D230="","",ROUND(D230*E230,1))</f>
@@ -28042,69 +28057,65 @@
       <c r="H230" s="35" t="n"/>
       <c r="I230" s="35" t="n"/>
     </row>
-    <row r="231" ht="62" customHeight="1">
-      <c r="A231" s="9" t="n"/>
-      <c r="B231" s="34" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C231" s="9" t="inlineStr"/>
-      <c r="D231" s="8">
-        <f>IF(COUNT(H231,I231)&lt;2,"",ROUND(H231*I231,2))</f>
-        <v/>
-      </c>
-      <c r="E231" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="F231" s="28">
-        <f>IF(D231="","",ROUND(D231*E231,1))</f>
-        <v/>
-      </c>
+    <row r="231" ht="39.7" customHeight="1">
+      <c r="A231" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B231" s="33" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="C231" s="9" t="n"/>
+      <c r="D231" s="9" t="n"/>
+      <c r="E231" s="9" t="n"/>
+      <c r="F231" s="9" t="n"/>
       <c r="G231" s="2" t="n"/>
-      <c r="H231" s="35" t="n"/>
-      <c r="I231" s="35" t="n"/>
+      <c r="H231" s="2" t="n"/>
+      <c r="I231" s="2" t="n"/>
     </row>
     <row r="232" ht="39.7" customHeight="1">
-      <c r="A232" s="16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B232" s="33" t="inlineStr">
-        <is>
-          <t>INFILTRACION</t>
-        </is>
-      </c>
-      <c r="C232" s="9" t="n"/>
-      <c r="D232" s="16" t="inlineStr">
-        <is>
-          <t>VOLUMEN (m3)</t>
-        </is>
-      </c>
-      <c r="E232" s="9" t="n"/>
-      <c r="F232" s="9" t="n"/>
+      <c r="A232" s="9" t="n"/>
+      <c r="B232" s="34" t="inlineStr">
+        <is>
+          <t>SOBRE TIERRA</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E232" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F232" s="28">
+        <f>IF(D232="","",ROUND(D232*E232,1))</f>
+        <v/>
+      </c>
       <c r="G232" s="2" t="n"/>
-      <c r="H232" s="2" t="n"/>
-      <c r="I232" s="2" t="n"/>
-    </row>
-    <row r="233" ht="39.7" customHeight="1">
+      <c r="H232" s="35" t="n"/>
+      <c r="I232" s="35" t="n"/>
+    </row>
+    <row r="233" ht="62" customHeight="1">
       <c r="A233" s="9" t="n"/>
       <c r="B233" s="34" t="inlineStr">
         <is>
-          <t>UNA PARED EXTERIOR</t>
-        </is>
-      </c>
-      <c r="C233" s="9" t="inlineStr">
-        <is>
-          <t>3.12 m2 x 3.00</t>
-        </is>
-      </c>
-      <c r="D233" s="8" t="n">
-        <v>9.359999999999999</v>
+          <t>SOBRE LOCAL OCUPADO</t>
+        </is>
+      </c>
+      <c r="C233" s="9" t="inlineStr"/>
+      <c r="D233" s="8">
+        <f>IF(COUNT(H233,I233)&lt;2,"",ROUND(H233*I233,2))</f>
+        <v/>
       </c>
       <c r="E233" s="25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F233" s="28">
         <f>IF(D233="","",ROUND(D233*E233,1))</f>
@@ -28114,43 +28125,46 @@
       <c r="H233" s="35" t="n"/>
       <c r="I233" s="35" t="n"/>
     </row>
-    <row r="234" ht="62" customHeight="1">
-      <c r="A234" s="9" t="n"/>
-      <c r="B234" s="34" t="inlineStr">
-        <is>
-          <t>DOS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C234" s="9" t="inlineStr"/>
-      <c r="D234" s="8">
-        <f>IF(COUNT(H234,I234)&lt;2,"",ROUND(H234*I234,2))</f>
-        <v/>
-      </c>
-      <c r="E234" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="F234" s="28">
-        <f>IF(D234="","",ROUND(D234*E234,1))</f>
-        <v/>
-      </c>
+    <row r="234" ht="39.7" customHeight="1">
+      <c r="A234" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B234" s="33" t="inlineStr">
+        <is>
+          <t>INFILTRACION</t>
+        </is>
+      </c>
+      <c r="C234" s="9" t="n"/>
+      <c r="D234" s="16" t="inlineStr">
+        <is>
+          <t>VOLUMEN (m3)</t>
+        </is>
+      </c>
+      <c r="E234" s="9" t="n"/>
+      <c r="F234" s="9" t="n"/>
       <c r="G234" s="2" t="n"/>
-      <c r="H234" s="35" t="n"/>
-      <c r="I234" s="35" t="n"/>
-    </row>
-    <row r="235" ht="62" customHeight="1">
+      <c r="H234" s="2" t="n"/>
+      <c r="I234" s="2" t="n"/>
+    </row>
+    <row r="235" ht="39.7" customHeight="1">
       <c r="A235" s="9" t="n"/>
       <c r="B235" s="34" t="inlineStr">
         <is>
-          <t>TRES O MAS PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C235" s="9" t="inlineStr"/>
-      <c r="D235" s="8">
-        <f>IF(COUNT(H235,I235)&lt;2,"",ROUND(H235*I235,2))</f>
-        <v/>
+          <t>UNA PARED EXTERIOR</t>
+        </is>
+      </c>
+      <c r="C235" s="9" t="inlineStr">
+        <is>
+          <t>3.12 m2 x 3.00</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="n">
+        <v>9.359999999999999</v>
       </c>
       <c r="E235" s="25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F235" s="28">
         <f>IF(D235="","",ROUND(D235*E235,1))</f>
@@ -28160,109 +28174,119 @@
       <c r="H235" s="35" t="n"/>
       <c r="I235" s="35" t="n"/>
     </row>
-    <row r="236" ht="70" customHeight="1">
-      <c r="A236" s="16" t="inlineStr">
+    <row r="236" ht="62" customHeight="1">
+      <c r="A236" s="9" t="n"/>
+      <c r="B236" s="34" t="inlineStr">
+        <is>
+          <t>DOS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C236" s="9" t="inlineStr"/>
+      <c r="D236" s="8">
+        <f>IF(COUNT(H236,I236)&lt;2,"",ROUND(H236*I236,2))</f>
+        <v/>
+      </c>
+      <c r="E236" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="F236" s="28">
+        <f>IF(D236="","",ROUND(D236*E236,1))</f>
+        <v/>
+      </c>
+      <c r="G236" s="2" t="n"/>
+      <c r="H236" s="35" t="n"/>
+      <c r="I236" s="35" t="n"/>
+    </row>
+    <row r="237" ht="62" customHeight="1">
+      <c r="A237" s="9" t="n"/>
+      <c r="B237" s="34" t="inlineStr">
+        <is>
+          <t>TRES O MAS PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C237" s="9" t="inlineStr"/>
+      <c r="D237" s="8">
+        <f>IF(COUNT(H237,I237)&lt;2,"",ROUND(H237*I237,2))</f>
+        <v/>
+      </c>
+      <c r="E237" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F237" s="28">
+        <f>IF(D237="","",ROUND(D237*E237,1))</f>
+        <v/>
+      </c>
+      <c r="G237" s="2" t="n"/>
+      <c r="H237" s="35" t="n"/>
+      <c r="I237" s="35" t="n"/>
+    </row>
+    <row r="238" ht="70" customHeight="1">
+      <c r="A238" s="16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B236" s="33" t="inlineStr">
+      <c r="B238" s="33" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C236" s="9" t="n"/>
-      <c r="D236" s="9" t="n"/>
-      <c r="E236" s="9" t="n"/>
-      <c r="F236" s="36">
-        <f>IF(F215="",0,F215)+IF(F217="",0,F217)+IF(F218="",0,F218)+IF(F219="",0,F219)+IF(F220="",0,F220)+IF(F221="",0,F221)+IF(F222="",0,F222)+IF(F223="",0,F223)+IF(F224="",0,F224)+IF(F226="",0,F226)+IF(F227="",0,F227)+IF(F228="",0,F228)+IF(F230="",0,F230)+IF(F231="",0,F231)+IF(F233="",0,F233)+IF(F234="",0,F234)+IF(F235="",0,F235)</f>
-        <v/>
-      </c>
-      <c r="G236" s="2" t="n"/>
-      <c r="H236" s="2" t="n"/>
-      <c r="I236" s="2" t="n"/>
-    </row>
-    <row r="237" ht="47" customHeight="1">
-      <c r="A237" s="16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B237" s="33" t="inlineStr">
-        <is>
-          <t>PERDIDA TOTAL</t>
-        </is>
-      </c>
-      <c r="C237" s="9">
-        <f>TEXT(F236,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
-        <v/>
-      </c>
-      <c r="D237" s="2" t="n"/>
-      <c r="E237" s="2" t="n"/>
-      <c r="F237" s="36">
-        <f>ROUND(F236*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
-        <v/>
-      </c>
-      <c r="G237" s="2" t="n"/>
-      <c r="H237" s="2" t="n"/>
-      <c r="I237" s="2" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="n"/>
-      <c r="B238" s="2" t="n"/>
-      <c r="C238" s="2" t="n"/>
-      <c r="D238" s="2" t="n"/>
-      <c r="E238" s="2" t="n"/>
-      <c r="F238" s="2" t="n"/>
+      <c r="C238" s="9" t="n"/>
+      <c r="D238" s="9" t="n"/>
+      <c r="E238" s="9" t="n"/>
+      <c r="F238" s="36">
+        <f>IF(F217="",0,F217)+IF(F219="",0,F219)+IF(F220="",0,F220)+IF(F221="",0,F221)+IF(F222="",0,F222)+IF(F223="",0,F223)+IF(F224="",0,F224)+IF(F225="",0,F225)+IF(F226="",0,F226)+IF(F228="",0,F228)+IF(F229="",0,F229)+IF(F230="",0,F230)+IF(F232="",0,F232)+IF(F233="",0,F233)+IF(F235="",0,F235)+IF(F236="",0,F236)+IF(F237="",0,F237)</f>
+        <v/>
+      </c>
       <c r="G238" s="2" t="n"/>
       <c r="H238" s="2" t="n"/>
       <c r="I238" s="2" t="n"/>
     </row>
-    <row r="239" ht="62" customHeight="1">
-      <c r="A239" s="9" t="n"/>
-      <c r="B239" s="10" t="inlineStr">
-        <is>
-          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+    <row r="239" ht="47" customHeight="1">
+      <c r="A239" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B239" s="33" t="inlineStr">
+        <is>
+          <t>PERDIDA TOTAL</t>
         </is>
       </c>
       <c r="C239" s="9">
-        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
+        <f>TEXT(F238,"0.00")&amp;"  X  "&amp;Datos_balance!$B$4&amp;" (FI)  X  "&amp;Datos_balance!$B$5&amp;" (FO)  X  "&amp;Datos_balance!$B$6&amp;" (FZ)"</f>
         <v/>
       </c>
       <c r="D239" s="2" t="n"/>
       <c r="E239" s="2" t="n"/>
-      <c r="F239" s="9" t="n"/>
+      <c r="F239" s="36">
+        <f>ROUND(F238*Datos_balance!$B$4*Datos_balance!$B$5*Datos_balance!$B$6,1)</f>
+        <v/>
+      </c>
       <c r="G239" s="2" t="n"/>
       <c r="H239" s="2" t="n"/>
       <c r="I239" s="2" t="n"/>
     </row>
-    <row r="240" ht="39.7" customHeight="1">
-      <c r="A240" s="9" t="n"/>
-      <c r="B240" s="10" t="inlineStr">
-        <is>
-          <t>Kcal/h del toallero Scala/Domino 80</t>
-        </is>
-      </c>
-      <c r="C240" s="25">
-        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
-        <v/>
-      </c>
+    <row r="240">
+      <c r="A240" s="2" t="n"/>
+      <c r="B240" s="2" t="n"/>
+      <c r="C240" s="2" t="n"/>
       <c r="D240" s="2" t="n"/>
       <c r="E240" s="2" t="n"/>
-      <c r="F240" s="9" t="n"/>
+      <c r="F240" s="2" t="n"/>
       <c r="G240" s="2" t="n"/>
       <c r="H240" s="2" t="n"/>
       <c r="I240" s="2" t="n"/>
     </row>
-    <row r="241" ht="39.7" customHeight="1">
+    <row r="241" ht="62" customHeight="1">
       <c r="A241" s="9" t="n"/>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>Kcal/h del toallero Scala/Domino 150</t>
-        </is>
-      </c>
-      <c r="C241" s="25">
-        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
+          <t>Salto termico:  dt = (te+ts)/2 - ti</t>
+        </is>
+      </c>
+      <c r="C241" s="9">
+        <f>TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2,"0")&amp;" - "&amp;TEXT(Datos_balance!$B$11,"0")&amp;" = "&amp;TEXT((Datos_balance!$B$9+Datos_balance!$B$10)/2-Datos_balance!$B$11,"0")&amp;" C"</f>
         <v/>
       </c>
       <c r="D241" s="2" t="n"/>
@@ -28272,15 +28296,15 @@
       <c r="H241" s="2" t="n"/>
       <c r="I241" s="2" t="n"/>
     </row>
-    <row r="242" ht="47" customHeight="1">
+    <row r="242" ht="39.7" customHeight="1">
       <c r="A242" s="9" t="n"/>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>Toalleros necesarios</t>
+          <t>Kcal/h del toallero Scala/Domino 80</t>
         </is>
       </c>
       <c r="C242" s="25">
-        <f>IF(F237&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F237/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
+        <f>ROUND(Datos_balance!$B$18*Datos_balance!$B$15,0)</f>
         <v/>
       </c>
       <c r="D242" s="2" t="n"/>
@@ -28290,52 +28314,62 @@
       <c r="H242" s="2" t="n"/>
       <c r="I242" s="2" t="n"/>
     </row>
-    <row r="243" ht="47" customHeight="1">
-      <c r="A243" s="13" t="n"/>
-      <c r="B243" s="14" t="inlineStr">
-        <is>
-          <t>Toallero adoptado</t>
-        </is>
-      </c>
-      <c r="C243" s="13">
-        <f>IF(F237&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
-        <v/>
-      </c>
-      <c r="D243" s="20" t="n"/>
-      <c r="E243" s="20" t="n"/>
-      <c r="F243" s="13" t="n"/>
+    <row r="243" ht="39.7" customHeight="1">
+      <c r="A243" s="9" t="n"/>
+      <c r="B243" s="10" t="inlineStr">
+        <is>
+          <t>Kcal/h del toallero Scala/Domino 150</t>
+        </is>
+      </c>
+      <c r="C243" s="25">
+        <f>ROUND(Datos_balance!$B$19*Datos_balance!$B$15,0)</f>
+        <v/>
+      </c>
+      <c r="D243" s="2" t="n"/>
+      <c r="E243" s="2" t="n"/>
+      <c r="F243" s="9" t="n"/>
       <c r="G243" s="2" t="n"/>
       <c r="H243" s="2" t="n"/>
       <c r="I243" s="2" t="n"/>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="n"/>
-      <c r="B244" s="2" t="n"/>
-      <c r="C244" s="2" t="n"/>
+    <row r="244" ht="47" customHeight="1">
+      <c r="A244" s="9" t="n"/>
+      <c r="B244" s="10" t="inlineStr">
+        <is>
+          <t>Toalleros necesarios</t>
+        </is>
+      </c>
+      <c r="C244" s="25">
+        <f>IF(F239&lt;=Datos_balance!$B$18*Datos_balance!$B$15,1,ROUNDUP(F239/(Datos_balance!$B$19*Datos_balance!$B$15),0))</f>
+        <v/>
+      </c>
       <c r="D244" s="2" t="n"/>
       <c r="E244" s="2" t="n"/>
-      <c r="F244" s="2" t="n"/>
+      <c r="F244" s="9" t="n"/>
       <c r="G244" s="2" t="n"/>
       <c r="H244" s="2" t="n"/>
       <c r="I244" s="2" t="n"/>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="n"/>
-      <c r="B245" s="2" t="n"/>
-      <c r="C245" s="2" t="n"/>
-      <c r="D245" s="2" t="n"/>
-      <c r="E245" s="2" t="n"/>
-      <c r="F245" s="2" t="n"/>
+    <row r="245" ht="47" customHeight="1">
+      <c r="A245" s="13" t="n"/>
+      <c r="B245" s="14" t="inlineStr">
+        <is>
+          <t>Toallero adoptado</t>
+        </is>
+      </c>
+      <c r="C245" s="13">
+        <f>IF(F239&lt;=Datos_balance!$B$18*Datos_balance!$B$15,"Peisa Scala / Domino 80  (500 x 800 mm)","Peisa Scala / Domino 150  (500 x 1500 mm)")</f>
+        <v/>
+      </c>
+      <c r="D245" s="20" t="n"/>
+      <c r="E245" s="20" t="n"/>
+      <c r="F245" s="13" t="n"/>
       <c r="G245" s="2" t="n"/>
       <c r="H245" s="2" t="n"/>
       <c r="I245" s="2" t="n"/>
     </row>
-    <row r="246" ht="39.7" customHeight="1">
-      <c r="A246" s="5" t="inlineStr">
-        <is>
-          <t>LOCAL  13 - Dormitorio Norte   (PA)</t>
-        </is>
-      </c>
+    <row r="246">
+      <c r="A246" s="2" t="n"/>
       <c r="B246" s="2" t="n"/>
       <c r="C246" s="2" t="n"/>
       <c r="D246" s="2" t="n"/>
@@ -28345,144 +28379,121 @@
       <c r="H246" s="2" t="n"/>
       <c r="I246" s="2" t="n"/>
     </row>
-    <row r="247" ht="39.7" customHeight="1">
-      <c r="A247" s="3" t="inlineStr">
-        <is>
-          <t>Nro</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="inlineStr">
-        <is>
-          <t>DESCRIPCION</t>
-        </is>
-      </c>
-      <c r="C247" s="3" t="inlineStr">
-        <is>
-          <t>DIMENSIONES (m)</t>
-        </is>
-      </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>AREA (m2)</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>FACTOR</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>PERDIDA CALOR (Kcal/h)</t>
-        </is>
-      </c>
+    <row r="247">
+      <c r="A247" s="2" t="n"/>
+      <c r="B247" s="2" t="n"/>
+      <c r="C247" s="2" t="n"/>
+      <c r="D247" s="2" t="n"/>
+      <c r="E247" s="2" t="n"/>
+      <c r="F247" s="2" t="n"/>
       <c r="G247" s="2" t="n"/>
       <c r="H247" s="2" t="n"/>
       <c r="I247" s="2" t="n"/>
     </row>
     <row r="248" ht="39.7" customHeight="1">
-      <c r="A248" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B248" s="33" t="inlineStr">
-        <is>
-          <t>VENTANA</t>
-        </is>
-      </c>
-      <c r="C248" s="9" t="n"/>
-      <c r="D248" s="9" t="n"/>
-      <c r="E248" s="9" t="n"/>
-      <c r="F248" s="9" t="n"/>
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t>LOCAL  13 - Dormitorio Norte   (PA)</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="n"/>
+      <c r="C248" s="2" t="n"/>
+      <c r="D248" s="2" t="n"/>
+      <c r="E248" s="2" t="n"/>
+      <c r="F248" s="2" t="n"/>
       <c r="G248" s="2" t="n"/>
       <c r="H248" s="2" t="n"/>
       <c r="I248" s="2" t="n"/>
     </row>
-    <row r="249" ht="62" customHeight="1">
-      <c r="A249" s="9" t="n"/>
-      <c r="B249" s="34" t="inlineStr">
+    <row r="249" ht="39.7" customHeight="1">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>Nro</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>DESCRIPCION</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>DIMENSIONES (m)</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>FACTOR</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>PERDIDA CALOR (Kcal/h)</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="n"/>
+      <c r="H249" s="2" t="n"/>
+      <c r="I249" s="2" t="n"/>
+    </row>
+    <row r="250" ht="39.7" customHeight="1">
+      <c r="A250" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B250" s="33" t="inlineStr">
+        <is>
+          <t>VENTANA</t>
+        </is>
+      </c>
+      <c r="C250" s="9" t="n"/>
+      <c r="D250" s="9" t="n"/>
+      <c r="E250" s="9" t="n"/>
+      <c r="F250" s="9" t="n"/>
+      <c r="G250" s="2" t="n"/>
+      <c r="H250" s="2" t="n"/>
+      <c r="I250" s="2" t="n"/>
+    </row>
+    <row r="251" ht="62" customHeight="1">
+      <c r="A251" s="9" t="n"/>
+      <c r="B251" s="34" t="inlineStr">
         <is>
           <t>VA04</t>
         </is>
       </c>
-      <c r="C249" s="9">
-        <f>IF(COUNT(H249,I249)&lt;2,"",TEXT(H249,"0.00")&amp;" x "&amp;TEXT(I249,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D249" s="8">
-        <f>IF(COUNT(H249,I249)&lt;2,"",ROUND(H249*I249,2))</f>
-        <v/>
-      </c>
-      <c r="E249" s="25" t="n">
+      <c r="C251" s="9">
+        <f>IF(COUNT(H251,I251)&lt;2,"",TEXT(H251,"0.00")&amp;" x "&amp;TEXT(I251,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D251" s="8">
+        <f>IF(COUNT(H251,I251)&lt;2,"",ROUND(H251*I251,2))</f>
+        <v/>
+      </c>
+      <c r="E251" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="F249" s="28">
-        <f>IF(D249="","",ROUND(D249*E249,1))</f>
-        <v/>
-      </c>
-      <c r="G249" s="2" t="n"/>
-      <c r="H249" s="35" t="n">
+      <c r="F251" s="28">
+        <f>IF(D251="","",ROUND(D251*E251,1))</f>
+        <v/>
+      </c>
+      <c r="G251" s="2" t="n"/>
+      <c r="H251" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="I249" s="35" t="n">
+      <c r="I251" s="35" t="n">
         <v>2.52</v>
       </c>
-    </row>
-    <row r="250" ht="62" customHeight="1">
-      <c r="A250" s="9" t="n"/>
-      <c r="B250" s="34" t="inlineStr">
-        <is>
-          <t>VA05</t>
-        </is>
-      </c>
-      <c r="C250" s="9">
-        <f>IF(COUNT(H250,I250)&lt;2,"",TEXT(H250,"0.00")&amp;" x "&amp;TEXT(I250,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D250" s="8">
-        <f>IF(COUNT(H250,I250)&lt;2,"",ROUND(H250*I250,2))</f>
-        <v/>
-      </c>
-      <c r="E250" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F250" s="28">
-        <f>IF(D250="","",ROUND(D250*E250,1))</f>
-        <v/>
-      </c>
-      <c r="G250" s="2" t="n"/>
-      <c r="H250" s="35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I250" s="35" t="n">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="251" ht="39.7" customHeight="1">
-      <c r="A251" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B251" s="33" t="inlineStr">
-        <is>
-          <t>PAREDES EXTERIORES</t>
-        </is>
-      </c>
-      <c r="C251" s="9" t="n"/>
-      <c r="D251" s="9" t="n"/>
-      <c r="E251" s="9" t="n"/>
-      <c r="F251" s="9" t="n"/>
-      <c r="G251" s="2" t="n"/>
-      <c r="H251" s="2" t="n"/>
-      <c r="I251" s="2" t="n"/>
     </row>
     <row r="252" ht="62" customHeight="1">
       <c r="A252" s="9" t="n"/>
       <c r="B252" s="34" t="inlineStr">
         <is>
-          <t>AISLADAS (    )</t>
+          <t>VA05</t>
         </is>
       </c>
       <c r="C252" s="9">
@@ -28494,41 +28505,38 @@
         <v/>
       </c>
       <c r="E252" s="25" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F252" s="28">
         <f>IF(D252="","",ROUND(D252*E252,1))</f>
         <v/>
       </c>
       <c r="G252" s="2" t="n"/>
-      <c r="H252" s="35" t="n"/>
-      <c r="I252" s="35" t="n"/>
-    </row>
-    <row r="253" ht="62" customHeight="1">
-      <c r="A253" s="9" t="n"/>
-      <c r="B253" s="34" t="inlineStr">
-        <is>
-          <t>AISLADAS (    )</t>
-        </is>
-      </c>
-      <c r="C253" s="9">
-        <f>IF(COUNT(H253,I253)&lt;2,"",TEXT(H253,"0.00")&amp;" x "&amp;TEXT(I253,"0.00"))</f>
-        <v/>
-      </c>
-      <c r="D253" s="8">
-        <f>IF(COUNT(H253,I253)&lt;2,"",ROUND(H253*I253,2))</f>
-        <v/>
-      </c>
-      <c r="E253" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F253" s="28">
-        <f>IF(D253="","",ROUND(D253*E253,1))</f>
-        <v/>
-      </c>
+      <c r="H252" s="35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I252" s="35" t="n">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="253" ht="39.7" customHeight="1">
+      <c r="A253" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B253" s="33" t="inlineStr">
+        <is>
+          <t>PAREDES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="C253" s="9" t="n"/>
+      <c r="D253" s="9" t="n"/>
+      <c r="E253" s="9" t="n"/>
+      <c r="F253" s="9" t="n"/>
       <c r="G253" s="2" t="n"/>
-      <c r="H253" s="35" t="n"/>
-      <c r="I253" s="35" t="n"/>
+      <c r="H253" s="2" t="n"/>
+      <c r="I253" s="2" t="n"/>
     </row>
     <row r="254" ht="62" customHeight="1">
       <c r="A254" s="9" t="n"/>
@@ -28586,7 +28594,7 @@
       <c r="A256" s="9" t="n"/>
       <c r="B256" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C256" s="9">
@@ -28598,25 +28606,21 @@
         <v/>
       </c>
       <c r="E256" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F256" s="28">
         <f>IF(D256="","",ROUND(D256*E256,1))</f>
         <v/>
       </c>
       <c r="G256" s="2" t="n"/>
-      <c r="H256" s="35" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="I256" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H256" s="35" t="n"/>
+      <c r="I256" s="35" t="n"/>
     </row>
     <row r="257" ht="62" customHeight="1">
       <c r="A257" s="9" t="n"/>
       <c r="B257" s="34" t="inlineStr">
         <is>
-          <t>INTERIORES (    )</t>
+          <t>AISLADAS (    )</t>
         </is>
       </c>
       <c r="C257" s="9">
@@ -28628,19 +28632,15 @@
         <v/>
       </c>
       <c r="E257" s="25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F257" s="28">
         <f>IF(D257="","",ROUND(D257*E257,1))</f>
         <v/>
       </c>
       <c r="G257" s="2" t="n"/>
-      <c r="H257" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="I257" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="H257" s="35" t="n"/>
+      <c r="I257" s="35" t="n"/>
     </row>
     <row r="258" ht="62" customHeight="1">
       <c r="A258" s="9" t="n"/>
@@ -28702,79 +28702,90 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" ht="39.7" customHeight="1">
-      <c r="A260" s="16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B260" s="33" t="inlineStr">
-        <is>
-          <t>TECHOS O CIELORRASOS</t>
-        </is>
-      </c>
-      <c r="C260" s="9" t="n"/>
-      <c r="D260" s="9" t="n"/>
-      <c r="E260" s="9" t="n"/>
-      <c r="F260" s="9" t="n"/>
+    <row r="260" ht="62" customHeight="1">
+      <c r="A260" s="9" t="n"/>
+      <c r="B260" s="34" t="inlineStr">
+        <is>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C260" s="9">
+        <f>IF(COUNT(H260,I260)&lt;2,"",TEXT(H260,"0.00")&amp;" x "&amp;TEXT(I260,"0.00"))</f>
+        <v/>
+      </c>
+      <c r="D260" s="8">
+        <f>IF(COUNT(H260,I260)&lt;2,"",ROUND(H260*I260,2))</f>
+        <v/>
+      </c>
+      <c r="E260" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="F260" s="28">
+        <f>IF(D260="","",ROUND(D260*E260,1))</f>
+        <v/>
+      </c>
       <c r="G260" s="2" t="n"/>
-      <c r="H260" s="2" t="n"/>
-      <c r="I260" s="2" t="n"/>
+      <c r="H260" s="35" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I260" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="261" ht="62" customHeight="1">
       <c r="A261" s="9" t="n"/>
       <c r="B261" s="34" t="inlineStr">
         <is>
-          <t>TECHO NO AISLADO</t>
-        </is>
-      </c>
-      <c r="C261" s="9" t="inlineStr"/>
+          <t>INTERIORES (    )</t>
+        </is>
+      </c>
+      <c r="C261" s="9">
+        <f>IF(COUNT(H261,I261)&lt;2,"",TEXT(H261,"0.00")&amp;" x "&amp;TEXT(I261,"0.00"))</f>
+        <v/>
+      </c>
       <c r="D261" s="8">
         <f>IF(COUNT(H261,I261)&lt;2,"",ROUND(H261*I261,2))</f>
         <v/>
       </c>
       <c r="E261" s="25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F261" s="28">
         <f>IF(D261="","",ROUND(D261*E261,1))</f>
         <v/>
       </c>
       <c r="G261" s="2" t="n"/>
-      <c r="H261" s="35" t="n"/>
-      <c r="I261" s="35" t="n"/>
+      <c r="H261" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I261" s="35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="262" ht="39.7" customHeight="1">
-      <c r="A262" s="9" t="n"/>
-      <c r="B262" s="34" t="inlineStr">
-        <is>
-          <t>TECHO AISLADO</t>
-        </is>
-      </c>
-      <c r="C262" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D262" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E262" s="25" t="n">
-        <v>20</v>
-      </c>
-      <c r="F262" s="28">
-        <f>IF(D262="","",ROUND(D262*E262,1))</f>
-        <v/>
-      </c>
+      <c r="A262" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B262" s="33" t="inlineStr">
+        <is>
+          <t>TECHOS O CIELORRASOS</t>
+        </is>
+      </c>
+      <c r="C262" s="9" t="n"/>
+      <c r="D262" s="9" t="n"/>
+      <c r="E262" s="9" t="n"/>
+      <c r="F262" s="9" t="n"/>
       <c r="G262" s="2" t="n"/>
-      <c r="H262" s="35" t="n"/>
-      <c r="I262" s="35" t="n"/>
+      <c r="H262" s="2" t="n"/>
+      <c r="I262" s="2" t="n"/>
     </row>
     <row r="263" ht="62" customHeight="1">
       <c r="A263" s="9" t="n"/>
       <c r="B263" s="34" t="inlineStr">
         <is>
-          <t>TECHO ENTREPISO</t>
+          <t>TECHO NO AISLADO</t>
         </is>
       </c>
       <c r="C263" s="9" t="inlineStr"/>
@@ -28783,7 +28794,7 @@
         <v/>
       </c>
       <c r="E263" s="25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F263" s="28">
         <f>IF(D263="","",ROUND(D263*E263,1))</f>
@@ -28794,29 +28805,36 @@
       <c r="I263" s="35" t="n"/>
     </row>
     <row r="264" ht="39.7" customHeight="1">
-      <c r="A264" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B264" s="33" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="C264" s="9" t="n"/>
-      <c r="D264" s="9" t="n"/>
-      <c r="E264" s="9" t="n"/>
-      <c r="F264" s="9" t="n"/>
+      <c r="A264" s="9" t="n"/>
+      <c r="B264" s="34" t="inlineStr">
+        <is>
+          <t>TECHO AISLADO</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>por croquis</t>
+        </is>
+      </c>
+      <c r="D264" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E264" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F264" s="28">
+        <f>IF(D264="","",ROUND(D264*E264,1))</f>
+        <v/>
+      </c>
       <c r="G264" s="2" t="n"/>
-      <c r="H264" s="2" t="n"/>
-      <c r="I264" s="2" t="n"/>
+      <c r="H264" s="35" t="n"/>
+      <c r="I264" s="35" t="n"/>
     </row>
     <row r="265" ht="62" customHeight="1">
       <c r="A265" s="9" t="n"/>
       <c r="B265" s="34" t="inlineStr">
         <is>
-          <t>SOBRE TIERRA</t>
+          <t>TECHO ENTREPISO</t>
         </is>
       </c>
       <c r="C265" s="9" t="inlineStr"/>
@@ -28825,7 +28843,7 @@
         <v/>
       </c>
       <c r="E265" s="25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F265" s="28">
         <f>IF(D265="","",ROUND(D265*E265,1))</f>
@@ -28836,68 +28854,64 @@
       <c r="I265" s="35" t="n"/>
     </row>
     <row r="266" ht="39.7" customHeight="1">
-      <c r="A266" s="9" t="n"/>
-      <c r="B266" s="34" t="inlineStr">
-        <is>
-          <t>SOBRE LOCAL OCUPADO</t>
-        </is>
-      </c>
-      <c r="C266" s="9" t="inlineStr">
-        <is>
-          <t>por croquis</t>
-        </is>
-      </c>
-      <c r="D266" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E266" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="F266" s="28">
-        <f>IF(D266="","",ROUND(D266*E266,1))</f>
-        <v/>
-      </c>
+      <c r="A266" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+